--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="149">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,213 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Estonian Premier League</t>
+  </si>
+  <si>
+    <t>UEFA Europa League</t>
+  </si>
+  <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:20:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:45:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>Blooming Santa Cruz</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Internacional de Bogot</t>
+  </si>
+  <si>
+    <t>ZED FC</t>
+  </si>
+  <si>
+    <t>FCI Tallinn</t>
+  </si>
+  <si>
+    <t>OFI</t>
+  </si>
+  <si>
+    <t>PFC Levski Sofia</t>
+  </si>
+  <si>
+    <t>FC Stockholm Internazionale</t>
+  </si>
+  <si>
+    <t>Rosengard</t>
+  </si>
+  <si>
+    <t>Eskilsminne</t>
+  </si>
+  <si>
+    <t>Kristianstads</t>
+  </si>
+  <si>
+    <t>Vasalunds IF</t>
+  </si>
+  <si>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Skovde AIK</t>
+  </si>
+  <si>
+    <t>FC Jarfalla</t>
+  </si>
+  <si>
+    <t>Assyriska FF</t>
+  </si>
+  <si>
+    <t>Plzen</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Lillestrom</t>
+  </si>
+  <si>
+    <t>Besiktas</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Malaga</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medel</t>
+  </si>
+  <si>
+    <t>Olympic El Qanal</t>
+  </si>
+  <si>
+    <t>Tammeka Tartu</t>
+  </si>
+  <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
+    <t>Red Bull Salzburg</t>
+  </si>
+  <si>
+    <t>IFK Stocksund</t>
+  </si>
+  <si>
+    <t>Trelleborgs</t>
+  </si>
+  <si>
+    <t>Tvaakers</t>
+  </si>
+  <si>
+    <t>BK Olympic</t>
+  </si>
+  <si>
+    <t>Hammarby TFF</t>
+  </si>
+  <si>
+    <t>Getafe</t>
+  </si>
+  <si>
+    <t>Pyramids</t>
+  </si>
+  <si>
+    <t>FC Trollhattan</t>
+  </si>
+  <si>
+    <t>Karlbergs BK</t>
+  </si>
+  <si>
+    <t>AFC Eskilstuna</t>
+  </si>
+  <si>
+    <t>Union St Gilloise</t>
+  </si>
+  <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>NEC Nijmegen</t>
+  </si>
+  <si>
+    <t>Ferencvaros</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>2026-09-15 10:44:18</t>
   </si>
 </sst>
 </file>
@@ -585,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1035,6056 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2">
+        <v>1.11</v>
+      </c>
+      <c r="G2">
+        <v>990</v>
+      </c>
+      <c r="H2">
+        <v>1.11</v>
+      </c>
+      <c r="I2">
+        <v>990</v>
+      </c>
+      <c r="J2">
+        <v>1.15</v>
+      </c>
+      <c r="K2">
+        <v>950</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.3</v>
+      </c>
+      <c r="O2">
+        <v>1.14</v>
+      </c>
+      <c r="P2">
+        <v>1.29</v>
+      </c>
+      <c r="Q2">
+        <v>1.14</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>1.14</v>
+      </c>
+      <c r="T2">
+        <v>1.11</v>
+      </c>
+      <c r="U2">
+        <v>1.11</v>
+      </c>
+      <c r="V2">
+        <v>1.07</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.12</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.12</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.12</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.12</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.12</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.12</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.12</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.12</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.12</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.12</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3">
+        <v>1.97</v>
+      </c>
+      <c r="G3">
+        <v>2.02</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>5.4</v>
+      </c>
+      <c r="J3">
+        <v>3.2</v>
+      </c>
+      <c r="K3">
+        <v>3.3</v>
+      </c>
+      <c r="L3">
+        <v>1.64</v>
+      </c>
+      <c r="M3">
+        <v>1.14</v>
+      </c>
+      <c r="N3">
+        <v>2.44</v>
+      </c>
+      <c r="O3">
+        <v>1.64</v>
+      </c>
+      <c r="P3">
+        <v>1.48</v>
+      </c>
+      <c r="Q3">
+        <v>2.96</v>
+      </c>
+      <c r="R3">
+        <v>1.17</v>
+      </c>
+      <c r="S3">
+        <v>6.4</v>
+      </c>
+      <c r="T3">
+        <v>2.5</v>
+      </c>
+      <c r="U3">
+        <v>1.61</v>
+      </c>
+      <c r="V3">
+        <v>1.22</v>
+      </c>
+      <c r="W3">
+        <v>1.98</v>
+      </c>
+      <c r="X3">
+        <v>7.8</v>
+      </c>
+      <c r="Y3">
+        <v>12</v>
+      </c>
+      <c r="Z3">
+        <v>38</v>
+      </c>
+      <c r="AA3">
+        <v>180</v>
+      </c>
+      <c r="AB3">
+        <v>5.8</v>
+      </c>
+      <c r="AC3">
+        <v>8</v>
+      </c>
+      <c r="AD3">
+        <v>24</v>
+      </c>
+      <c r="AE3">
+        <v>120</v>
+      </c>
+      <c r="AF3">
+        <v>10</v>
+      </c>
+      <c r="AG3">
+        <v>12</v>
+      </c>
+      <c r="AH3">
+        <v>34</v>
+      </c>
+      <c r="AI3">
+        <v>160</v>
+      </c>
+      <c r="AJ3">
+        <v>25</v>
+      </c>
+      <c r="AK3">
+        <v>32</v>
+      </c>
+      <c r="AL3">
+        <v>75</v>
+      </c>
+      <c r="AM3">
+        <v>310</v>
+      </c>
+      <c r="AN3">
+        <v>29</v>
+      </c>
+      <c r="AO3">
+        <v>230</v>
+      </c>
+      <c r="AP3">
+        <v>7</v>
+      </c>
+      <c r="AQ3">
+        <v>11</v>
+      </c>
+      <c r="AR3">
+        <v>30</v>
+      </c>
+      <c r="AS3">
+        <v>14.5</v>
+      </c>
+      <c r="AT3">
+        <v>5.6</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>20</v>
+      </c>
+      <c r="AW3">
+        <v>15</v>
+      </c>
+      <c r="AX3">
+        <v>9</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>28</v>
+      </c>
+      <c r="BA3">
+        <v>14</v>
+      </c>
+      <c r="BB3">
+        <v>21</v>
+      </c>
+      <c r="BC3">
+        <v>27</v>
+      </c>
+      <c r="BD3">
+        <v>14.5</v>
+      </c>
+      <c r="BE3">
+        <v>14</v>
+      </c>
+      <c r="BF3">
+        <v>23</v>
+      </c>
+      <c r="BG3">
+        <v>14.5</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.21</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.04</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.04</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.04</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.04</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.04</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.04</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.04</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4">
+        <v>3.9</v>
+      </c>
+      <c r="G4">
+        <v>4.8</v>
+      </c>
+      <c r="H4">
+        <v>1.99</v>
+      </c>
+      <c r="I4">
+        <v>2.12</v>
+      </c>
+      <c r="J4">
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <v>3.85</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>3.6</v>
+      </c>
+      <c r="O4">
+        <v>1.32</v>
+      </c>
+      <c r="P4">
+        <v>1.83</v>
+      </c>
+      <c r="Q4">
+        <v>1.92</v>
+      </c>
+      <c r="R4">
+        <v>1.32</v>
+      </c>
+      <c r="S4">
+        <v>3.2</v>
+      </c>
+      <c r="T4">
+        <v>1.73</v>
+      </c>
+      <c r="U4">
+        <v>1.12</v>
+      </c>
+      <c r="V4">
+        <v>1.89</v>
+      </c>
+      <c r="W4">
+        <v>1.27</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>1.01</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.01</v>
+      </c>
+      <c r="AY4">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.12</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.12</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.12</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.12</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.12</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.12</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.12</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.12</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.12</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.12</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5">
+        <v>2.06</v>
+      </c>
+      <c r="G5">
+        <v>2.24</v>
+      </c>
+      <c r="H5">
+        <v>4.6</v>
+      </c>
+      <c r="I5">
+        <v>5.2</v>
+      </c>
+      <c r="J5">
+        <v>2.94</v>
+      </c>
+      <c r="K5">
+        <v>3.2</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.41</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>2.38</v>
+      </c>
+      <c r="U5">
+        <v>1.63</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>7.4</v>
+      </c>
+      <c r="Y5">
+        <v>13</v>
+      </c>
+      <c r="Z5">
+        <v>40</v>
+      </c>
+      <c r="AA5">
+        <v>170</v>
+      </c>
+      <c r="AB5">
+        <v>6.2</v>
+      </c>
+      <c r="AC5">
+        <v>7.6</v>
+      </c>
+      <c r="AD5">
+        <v>26</v>
+      </c>
+      <c r="AE5">
+        <v>120</v>
+      </c>
+      <c r="AF5">
+        <v>13</v>
+      </c>
+      <c r="AG5">
+        <v>14</v>
+      </c>
+      <c r="AH5">
+        <v>34</v>
+      </c>
+      <c r="AI5">
+        <v>160</v>
+      </c>
+      <c r="AJ5">
+        <v>34</v>
+      </c>
+      <c r="AK5">
+        <v>40</v>
+      </c>
+      <c r="AL5">
+        <v>90</v>
+      </c>
+      <c r="AM5">
+        <v>330</v>
+      </c>
+      <c r="AN5">
+        <v>42</v>
+      </c>
+      <c r="AO5">
+        <v>220</v>
+      </c>
+      <c r="AP5">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR5">
+        <v>6.8</v>
+      </c>
+      <c r="AS5">
+        <v>7.8</v>
+      </c>
+      <c r="AT5">
+        <v>5.4</v>
+      </c>
+      <c r="AU5">
+        <v>6.4</v>
+      </c>
+      <c r="AV5">
+        <v>16.5</v>
+      </c>
+      <c r="AW5">
+        <v>6.8</v>
+      </c>
+      <c r="AX5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY5">
+        <v>10.5</v>
+      </c>
+      <c r="AZ5">
+        <v>6.6</v>
+      </c>
+      <c r="BA5">
+        <v>7.8</v>
+      </c>
+      <c r="BB5">
+        <v>6.6</v>
+      </c>
+      <c r="BC5">
+        <v>6.8</v>
+      </c>
+      <c r="BD5">
+        <v>7.6</v>
+      </c>
+      <c r="BE5">
+        <v>8</v>
+      </c>
+      <c r="BF5">
+        <v>6.8</v>
+      </c>
+      <c r="BG5">
+        <v>7</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6">
+        <v>1.1</v>
+      </c>
+      <c r="G6">
+        <v>600</v>
+      </c>
+      <c r="H6">
+        <v>1.1</v>
+      </c>
+      <c r="I6">
+        <v>870</v>
+      </c>
+      <c r="J6">
+        <v>1.11</v>
+      </c>
+      <c r="K6">
+        <v>950</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7">
+        <v>7.8</v>
+      </c>
+      <c r="G7">
+        <v>8.6</v>
+      </c>
+      <c r="H7">
+        <v>1.45</v>
+      </c>
+      <c r="I7">
+        <v>1.48</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>5.4</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>2.44</v>
+      </c>
+      <c r="Q7">
+        <v>1.6</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1.83</v>
+      </c>
+      <c r="U7">
+        <v>2.04</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>26</v>
+      </c>
+      <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>10</v>
+      </c>
+      <c r="AA7">
+        <v>13.5</v>
+      </c>
+      <c r="AB7">
+        <v>32</v>
+      </c>
+      <c r="AC7">
+        <v>12</v>
+      </c>
+      <c r="AD7">
+        <v>11</v>
+      </c>
+      <c r="AE7">
+        <v>15</v>
+      </c>
+      <c r="AF7">
+        <v>90</v>
+      </c>
+      <c r="AG7">
+        <v>34</v>
+      </c>
+      <c r="AH7">
+        <v>25</v>
+      </c>
+      <c r="AI7">
+        <v>36</v>
+      </c>
+      <c r="AJ7">
+        <v>300</v>
+      </c>
+      <c r="AK7">
+        <v>130</v>
+      </c>
+      <c r="AL7">
+        <v>110</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>150</v>
+      </c>
+      <c r="AO7">
+        <v>5.7</v>
+      </c>
+      <c r="AP7">
+        <v>20</v>
+      </c>
+      <c r="AQ7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR7">
+        <v>8.4</v>
+      </c>
+      <c r="AS7">
+        <v>11</v>
+      </c>
+      <c r="AT7">
+        <v>21</v>
+      </c>
+      <c r="AU7">
+        <v>10</v>
+      </c>
+      <c r="AV7">
+        <v>9</v>
+      </c>
+      <c r="AW7">
+        <v>12.5</v>
+      </c>
+      <c r="AX7">
+        <v>8.6</v>
+      </c>
+      <c r="AY7">
+        <v>7.4</v>
+      </c>
+      <c r="AZ7">
+        <v>19.5</v>
+      </c>
+      <c r="BA7">
+        <v>7.6</v>
+      </c>
+      <c r="BB7">
+        <v>9.4</v>
+      </c>
+      <c r="BC7">
+        <v>9</v>
+      </c>
+      <c r="BD7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE7">
+        <v>9</v>
+      </c>
+      <c r="BF7">
+        <v>9</v>
+      </c>
+      <c r="BG7">
+        <v>5</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8">
+        <v>3.2</v>
+      </c>
+      <c r="G8">
+        <v>3.25</v>
+      </c>
+      <c r="H8">
+        <v>2.4</v>
+      </c>
+      <c r="I8">
+        <v>2.42</v>
+      </c>
+      <c r="J8">
+        <v>3.55</v>
+      </c>
+      <c r="K8">
+        <v>3.7</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>2.28</v>
+      </c>
+      <c r="Q8">
+        <v>1.71</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1.61</v>
+      </c>
+      <c r="U8">
+        <v>2.56</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>21</v>
+      </c>
+      <c r="Y8">
+        <v>13.5</v>
+      </c>
+      <c r="Z8">
+        <v>18</v>
+      </c>
+      <c r="AA8">
+        <v>32</v>
+      </c>
+      <c r="AB8">
+        <v>16.5</v>
+      </c>
+      <c r="AC8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD8">
+        <v>12</v>
+      </c>
+      <c r="AE8">
+        <v>23</v>
+      </c>
+      <c r="AF8">
+        <v>25</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>15</v>
+      </c>
+      <c r="AI8">
+        <v>30</v>
+      </c>
+      <c r="AJ8">
+        <v>55</v>
+      </c>
+      <c r="AK8">
+        <v>36</v>
+      </c>
+      <c r="AL8">
+        <v>44</v>
+      </c>
+      <c r="AM8">
+        <v>460</v>
+      </c>
+      <c r="AN8">
+        <v>32</v>
+      </c>
+      <c r="AO8">
+        <v>16.5</v>
+      </c>
+      <c r="AP8">
+        <v>16.5</v>
+      </c>
+      <c r="AQ8">
+        <v>12</v>
+      </c>
+      <c r="AR8">
+        <v>15.5</v>
+      </c>
+      <c r="AS8">
+        <v>21</v>
+      </c>
+      <c r="AT8">
+        <v>14.5</v>
+      </c>
+      <c r="AU8">
+        <v>7.6</v>
+      </c>
+      <c r="AV8">
+        <v>10.5</v>
+      </c>
+      <c r="AW8">
+        <v>20</v>
+      </c>
+      <c r="AX8">
+        <v>21</v>
+      </c>
+      <c r="AY8">
+        <v>12.5</v>
+      </c>
+      <c r="AZ8">
+        <v>13</v>
+      </c>
+      <c r="BA8">
+        <v>20</v>
+      </c>
+      <c r="BB8">
+        <v>28</v>
+      </c>
+      <c r="BC8">
+        <v>20</v>
+      </c>
+      <c r="BD8">
+        <v>23</v>
+      </c>
+      <c r="BE8">
+        <v>29</v>
+      </c>
+      <c r="BF8">
+        <v>19</v>
+      </c>
+      <c r="BG8">
+        <v>12</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9">
+        <v>1.1</v>
+      </c>
+      <c r="G9">
+        <v>600</v>
+      </c>
+      <c r="H9">
+        <v>1.1</v>
+      </c>
+      <c r="I9">
+        <v>870</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10">
+        <v>1.1</v>
+      </c>
+      <c r="G10">
+        <v>600</v>
+      </c>
+      <c r="H10">
+        <v>1.1</v>
+      </c>
+      <c r="I10">
+        <v>870</v>
+      </c>
+      <c r="J10">
+        <v>1.11</v>
+      </c>
+      <c r="K10">
+        <v>950</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.24</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11">
+        <v>1.1</v>
+      </c>
+      <c r="G11">
+        <v>600</v>
+      </c>
+      <c r="H11">
+        <v>1.1</v>
+      </c>
+      <c r="I11">
+        <v>870</v>
+      </c>
+      <c r="J11">
+        <v>1.11</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.24</v>
+      </c>
+      <c r="Q11">
+        <v>1.01</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12">
+        <v>1.1</v>
+      </c>
+      <c r="G12">
+        <v>600</v>
+      </c>
+      <c r="H12">
+        <v>1.1</v>
+      </c>
+      <c r="I12">
+        <v>870</v>
+      </c>
+      <c r="J12">
+        <v>1.1</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13">
+        <v>1.1</v>
+      </c>
+      <c r="G13">
+        <v>600</v>
+      </c>
+      <c r="H13">
+        <v>1.1</v>
+      </c>
+      <c r="I13">
+        <v>870</v>
+      </c>
+      <c r="J13">
+        <v>1.1</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.24</v>
+      </c>
+      <c r="Q13">
+        <v>1.01</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14">
+        <v>1.71</v>
+      </c>
+      <c r="G14">
+        <v>1.72</v>
+      </c>
+      <c r="H14">
+        <v>6.2</v>
+      </c>
+      <c r="I14">
+        <v>6.4</v>
+      </c>
+      <c r="J14">
+        <v>3.85</v>
+      </c>
+      <c r="K14">
+        <v>3.9</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.09</v>
+      </c>
+      <c r="N14">
+        <v>3.15</v>
+      </c>
+      <c r="O14">
+        <v>1.43</v>
+      </c>
+      <c r="P14">
+        <v>1.76</v>
+      </c>
+      <c r="Q14">
+        <v>2.28</v>
+      </c>
+      <c r="R14">
+        <v>1.27</v>
+      </c>
+      <c r="S14">
+        <v>4.4</v>
+      </c>
+      <c r="T14">
+        <v>2.2</v>
+      </c>
+      <c r="U14">
+        <v>1.79</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>11.5</v>
+      </c>
+      <c r="Y14">
+        <v>17</v>
+      </c>
+      <c r="Z14">
+        <v>55</v>
+      </c>
+      <c r="AA14">
+        <v>250</v>
+      </c>
+      <c r="AB14">
+        <v>6.8</v>
+      </c>
+      <c r="AC14">
+        <v>8.6</v>
+      </c>
+      <c r="AD14">
+        <v>25</v>
+      </c>
+      <c r="AE14">
+        <v>120</v>
+      </c>
+      <c r="AF14">
+        <v>9</v>
+      </c>
+      <c r="AG14">
+        <v>10.5</v>
+      </c>
+      <c r="AH14">
+        <v>26</v>
+      </c>
+      <c r="AI14">
+        <v>120</v>
+      </c>
+      <c r="AJ14">
+        <v>17</v>
+      </c>
+      <c r="AK14">
+        <v>21</v>
+      </c>
+      <c r="AL14">
+        <v>48</v>
+      </c>
+      <c r="AM14">
+        <v>230</v>
+      </c>
+      <c r="AN14">
+        <v>13.5</v>
+      </c>
+      <c r="AO14">
+        <v>220</v>
+      </c>
+      <c r="AP14">
+        <v>10</v>
+      </c>
+      <c r="AQ14">
+        <v>15</v>
+      </c>
+      <c r="AR14">
+        <v>25</v>
+      </c>
+      <c r="AS14">
+        <v>44</v>
+      </c>
+      <c r="AT14">
+        <v>6.2</v>
+      </c>
+      <c r="AU14">
+        <v>8</v>
+      </c>
+      <c r="AV14">
+        <v>22</v>
+      </c>
+      <c r="AW14">
+        <v>38</v>
+      </c>
+      <c r="AX14">
+        <v>8.4</v>
+      </c>
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
+        <v>22</v>
+      </c>
+      <c r="BA14">
+        <v>40</v>
+      </c>
+      <c r="BB14">
+        <v>15</v>
+      </c>
+      <c r="BC14">
+        <v>18.5</v>
+      </c>
+      <c r="BD14">
+        <v>40</v>
+      </c>
+      <c r="BE14">
+        <v>46</v>
+      </c>
+      <c r="BF14">
+        <v>12.5</v>
+      </c>
+      <c r="BG14">
+        <v>44</v>
+      </c>
+      <c r="BH14">
+        <v>3.05</v>
+      </c>
+      <c r="BI14">
+        <v>2.8</v>
+      </c>
+      <c r="BJ14">
+        <v>14</v>
+      </c>
+      <c r="BK14">
+        <v>10</v>
+      </c>
+      <c r="BL14">
+        <v>240</v>
+      </c>
+      <c r="BM14">
+        <v>8</v>
+      </c>
+      <c r="BN14">
+        <v>4.1</v>
+      </c>
+      <c r="BO14">
+        <v>3.7</v>
+      </c>
+      <c r="BP14">
+        <v>14.5</v>
+      </c>
+      <c r="BQ14">
+        <v>10.5</v>
+      </c>
+      <c r="BR14">
+        <v>40</v>
+      </c>
+      <c r="BS14">
+        <v>6.8</v>
+      </c>
+      <c r="BT14">
+        <v>11.5</v>
+      </c>
+      <c r="BU14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BV14">
+        <v>80</v>
+      </c>
+      <c r="BW14">
+        <v>7.4</v>
+      </c>
+      <c r="BX14">
+        <v>95</v>
+      </c>
+      <c r="BY14">
+        <v>7.6</v>
+      </c>
+      <c r="BZ14">
+        <v>34</v>
+      </c>
+      <c r="CA14">
+        <v>6.8</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15">
+        <v>8.6</v>
+      </c>
+      <c r="G15">
+        <v>10.5</v>
+      </c>
+      <c r="H15">
+        <v>1.51</v>
+      </c>
+      <c r="I15">
+        <v>1.6</v>
+      </c>
+      <c r="J15">
+        <v>3.8</v>
+      </c>
+      <c r="K15">
+        <v>4.2</v>
+      </c>
+      <c r="L15">
+        <v>1.43</v>
+      </c>
+      <c r="M15">
+        <v>1.11</v>
+      </c>
+      <c r="N15">
+        <v>2.72</v>
+      </c>
+      <c r="O15">
+        <v>1.47</v>
+      </c>
+      <c r="P15">
+        <v>1.6</v>
+      </c>
+      <c r="Q15">
+        <v>2.28</v>
+      </c>
+      <c r="R15">
+        <v>1.23</v>
+      </c>
+      <c r="S15">
+        <v>4.6</v>
+      </c>
+      <c r="T15">
+        <v>2.42</v>
+      </c>
+      <c r="U15">
+        <v>1.58</v>
+      </c>
+      <c r="V15">
+        <v>2.66</v>
+      </c>
+      <c r="W15">
+        <v>1.1</v>
+      </c>
+      <c r="X15">
+        <v>13</v>
+      </c>
+      <c r="Y15">
+        <v>6</v>
+      </c>
+      <c r="Z15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA15">
+        <v>17</v>
+      </c>
+      <c r="AB15">
+        <v>26</v>
+      </c>
+      <c r="AC15">
+        <v>12</v>
+      </c>
+      <c r="AD15">
+        <v>13</v>
+      </c>
+      <c r="AE15">
+        <v>26</v>
+      </c>
+      <c r="AF15">
+        <v>110</v>
+      </c>
+      <c r="AG15">
+        <v>46</v>
+      </c>
+      <c r="AH15">
+        <v>42</v>
+      </c>
+      <c r="AI15">
+        <v>75</v>
+      </c>
+      <c r="AJ15">
+        <v>550</v>
+      </c>
+      <c r="AK15">
+        <v>280</v>
+      </c>
+      <c r="AL15">
+        <v>260</v>
+      </c>
+      <c r="AM15">
+        <v>380</v>
+      </c>
+      <c r="AN15">
+        <v>590</v>
+      </c>
+      <c r="AO15">
+        <v>15.5</v>
+      </c>
+      <c r="AP15">
+        <v>9</v>
+      </c>
+      <c r="AQ15">
+        <v>5</v>
+      </c>
+      <c r="AR15">
+        <v>6.4</v>
+      </c>
+      <c r="AS15">
+        <v>11.5</v>
+      </c>
+      <c r="AT15">
+        <v>16</v>
+      </c>
+      <c r="AU15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW15">
+        <v>15</v>
+      </c>
+      <c r="AX15">
+        <v>4.7</v>
+      </c>
+      <c r="AY15">
+        <v>4.7</v>
+      </c>
+      <c r="AZ15">
+        <v>4.7</v>
+      </c>
+      <c r="BA15">
+        <v>4.9</v>
+      </c>
+      <c r="BB15">
+        <v>4.9</v>
+      </c>
+      <c r="BC15">
+        <v>4.8</v>
+      </c>
+      <c r="BD15">
+        <v>4.8</v>
+      </c>
+      <c r="BE15">
+        <v>4.8</v>
+      </c>
+      <c r="BF15">
+        <v>4.9</v>
+      </c>
+      <c r="BG15">
+        <v>10.5</v>
+      </c>
+      <c r="BH15">
+        <v>3.4</v>
+      </c>
+      <c r="BI15">
+        <v>2.4</v>
+      </c>
+      <c r="BJ15">
+        <v>16.5</v>
+      </c>
+      <c r="BK15">
+        <v>3.85</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>5</v>
+      </c>
+      <c r="BN15">
+        <v>14.5</v>
+      </c>
+      <c r="BO15">
+        <v>3.75</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>4.8</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>4.9</v>
+      </c>
+      <c r="BT15">
+        <v>4.3</v>
+      </c>
+      <c r="BU15">
+        <v>2.9</v>
+      </c>
+      <c r="BV15">
+        <v>13</v>
+      </c>
+      <c r="BW15">
+        <v>3.65</v>
+      </c>
+      <c r="BX15">
+        <v>44</v>
+      </c>
+      <c r="BY15">
+        <v>4.5</v>
+      </c>
+      <c r="BZ15">
+        <v>34</v>
+      </c>
+      <c r="CA15">
+        <v>4.4</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16">
+        <v>1.1</v>
+      </c>
+      <c r="G16">
+        <v>600</v>
+      </c>
+      <c r="H16">
+        <v>1.1</v>
+      </c>
+      <c r="I16">
+        <v>870</v>
+      </c>
+      <c r="J16">
+        <v>1.11</v>
+      </c>
+      <c r="K16">
+        <v>950</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.24</v>
+      </c>
+      <c r="Q16">
+        <v>1.01</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17">
+        <v>1.1</v>
+      </c>
+      <c r="G17">
+        <v>600</v>
+      </c>
+      <c r="H17">
+        <v>1.1</v>
+      </c>
+      <c r="I17">
+        <v>870</v>
+      </c>
+      <c r="J17">
+        <v>1.11</v>
+      </c>
+      <c r="K17">
+        <v>950</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.24</v>
+      </c>
+      <c r="Q17">
+        <v>1.01</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18">
+        <v>1.1</v>
+      </c>
+      <c r="G18">
+        <v>600</v>
+      </c>
+      <c r="H18">
+        <v>1.1</v>
+      </c>
+      <c r="I18">
+        <v>870</v>
+      </c>
+      <c r="J18">
+        <v>1.1</v>
+      </c>
+      <c r="K18">
+        <v>950</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.24</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19">
+        <v>2.86</v>
+      </c>
+      <c r="G19">
+        <v>2.92</v>
+      </c>
+      <c r="H19">
+        <v>2.6</v>
+      </c>
+      <c r="I19">
+        <v>2.64</v>
+      </c>
+      <c r="J19">
+        <v>3.55</v>
+      </c>
+      <c r="K19">
+        <v>3.65</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2.08</v>
+      </c>
+      <c r="Q19">
+        <v>1.84</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1.71</v>
+      </c>
+      <c r="U19">
+        <v>2.3</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>17.5</v>
+      </c>
+      <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
+        <v>19</v>
+      </c>
+      <c r="AA19">
+        <v>38</v>
+      </c>
+      <c r="AB19">
+        <v>13.5</v>
+      </c>
+      <c r="AC19">
+        <v>8</v>
+      </c>
+      <c r="AD19">
+        <v>12.5</v>
+      </c>
+      <c r="AE19">
+        <v>28</v>
+      </c>
+      <c r="AF19">
+        <v>21</v>
+      </c>
+      <c r="AG19">
+        <v>13</v>
+      </c>
+      <c r="AH19">
+        <v>16.5</v>
+      </c>
+      <c r="AI19">
+        <v>38</v>
+      </c>
+      <c r="AJ19">
+        <v>44</v>
+      </c>
+      <c r="AK19">
+        <v>30</v>
+      </c>
+      <c r="AL19">
+        <v>38</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>23</v>
+      </c>
+      <c r="AO19">
+        <v>21</v>
+      </c>
+      <c r="AP19">
+        <v>15</v>
+      </c>
+      <c r="AQ19">
+        <v>11</v>
+      </c>
+      <c r="AR19">
+        <v>16</v>
+      </c>
+      <c r="AS19">
+        <v>32</v>
+      </c>
+      <c r="AT19">
+        <v>11.5</v>
+      </c>
+      <c r="AU19">
+        <v>7.4</v>
+      </c>
+      <c r="AV19">
+        <v>10.5</v>
+      </c>
+      <c r="AW19">
+        <v>18</v>
+      </c>
+      <c r="AX19">
+        <v>17</v>
+      </c>
+      <c r="AY19">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19">
+        <v>14</v>
+      </c>
+      <c r="BA19">
+        <v>30</v>
+      </c>
+      <c r="BB19">
+        <v>25</v>
+      </c>
+      <c r="BC19">
+        <v>24</v>
+      </c>
+      <c r="BD19">
+        <v>28</v>
+      </c>
+      <c r="BE19">
+        <v>34</v>
+      </c>
+      <c r="BF19">
+        <v>19.5</v>
+      </c>
+      <c r="BG19">
+        <v>18</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20">
+        <v>1.43</v>
+      </c>
+      <c r="G20">
+        <v>1.46</v>
+      </c>
+      <c r="H20">
+        <v>8</v>
+      </c>
+      <c r="I20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J20">
+        <v>5.2</v>
+      </c>
+      <c r="K20">
+        <v>5.6</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>4.9</v>
+      </c>
+      <c r="O20">
+        <v>1.22</v>
+      </c>
+      <c r="P20">
+        <v>2.44</v>
+      </c>
+      <c r="Q20">
+        <v>1.67</v>
+      </c>
+      <c r="R20">
+        <v>1.54</v>
+      </c>
+      <c r="S20">
+        <v>2.68</v>
+      </c>
+      <c r="T20">
+        <v>1.93</v>
+      </c>
+      <c r="U20">
+        <v>2</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>24</v>
+      </c>
+      <c r="Y20">
+        <v>30</v>
+      </c>
+      <c r="Z20">
+        <v>95</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>10</v>
+      </c>
+      <c r="AC20">
+        <v>12</v>
+      </c>
+      <c r="AD20">
+        <v>32</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>9.4</v>
+      </c>
+      <c r="AG20">
+        <v>10.5</v>
+      </c>
+      <c r="AH20">
+        <v>26</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>12</v>
+      </c>
+      <c r="AK20">
+        <v>15.5</v>
+      </c>
+      <c r="AL20">
+        <v>36</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>5.9</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>19.5</v>
+      </c>
+      <c r="AQ20">
+        <v>18.5</v>
+      </c>
+      <c r="AR20">
+        <v>32</v>
+      </c>
+      <c r="AS20">
+        <v>100</v>
+      </c>
+      <c r="AT20">
+        <v>8.4</v>
+      </c>
+      <c r="AU20">
+        <v>10.5</v>
+      </c>
+      <c r="AV20">
+        <v>22</v>
+      </c>
+      <c r="AW20">
+        <v>38</v>
+      </c>
+      <c r="AX20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY20">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20">
+        <v>21</v>
+      </c>
+      <c r="BA20">
+        <v>36</v>
+      </c>
+      <c r="BB20">
+        <v>11</v>
+      </c>
+      <c r="BC20">
+        <v>13</v>
+      </c>
+      <c r="BD20">
+        <v>26</v>
+      </c>
+      <c r="BE20">
+        <v>42</v>
+      </c>
+      <c r="BF20">
+        <v>5.3</v>
+      </c>
+      <c r="BG20">
+        <v>42</v>
+      </c>
+      <c r="BH20">
+        <v>4.2</v>
+      </c>
+      <c r="BI20">
+        <v>3.65</v>
+      </c>
+      <c r="BJ20">
+        <v>12.5</v>
+      </c>
+      <c r="BK20">
+        <v>5</v>
+      </c>
+      <c r="BL20">
+        <v>150</v>
+      </c>
+      <c r="BM20">
+        <v>7.6</v>
+      </c>
+      <c r="BN20">
+        <v>4.1</v>
+      </c>
+      <c r="BO20">
+        <v>3.6</v>
+      </c>
+      <c r="BP20">
+        <v>9.6</v>
+      </c>
+      <c r="BQ20">
+        <v>7.4</v>
+      </c>
+      <c r="BR20">
+        <v>26</v>
+      </c>
+      <c r="BS20">
+        <v>6.2</v>
+      </c>
+      <c r="BT20">
+        <v>13.5</v>
+      </c>
+      <c r="BU20">
+        <v>5.1</v>
+      </c>
+      <c r="BV20">
+        <v>80</v>
+      </c>
+      <c r="BW20">
+        <v>7.4</v>
+      </c>
+      <c r="BX20">
+        <v>75</v>
+      </c>
+      <c r="BY20">
+        <v>7.2</v>
+      </c>
+      <c r="BZ20">
+        <v>15</v>
+      </c>
+      <c r="CA20">
+        <v>5.4</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21">
+        <v>1.57</v>
+      </c>
+      <c r="G21">
+        <v>1.63</v>
+      </c>
+      <c r="H21">
+        <v>5.9</v>
+      </c>
+      <c r="I21">
+        <v>6.6</v>
+      </c>
+      <c r="J21">
+        <v>4.6</v>
+      </c>
+      <c r="K21">
+        <v>5</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.38</v>
+      </c>
+      <c r="Q21">
+        <v>1.65</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1.77</v>
+      </c>
+      <c r="U21">
+        <v>2.18</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>28</v>
+      </c>
+      <c r="Y21">
+        <v>30</v>
+      </c>
+      <c r="Z21">
+        <v>65</v>
+      </c>
+      <c r="AA21">
+        <v>190</v>
+      </c>
+      <c r="AB21">
+        <v>11</v>
+      </c>
+      <c r="AC21">
+        <v>11</v>
+      </c>
+      <c r="AD21">
+        <v>29</v>
+      </c>
+      <c r="AE21">
+        <v>90</v>
+      </c>
+      <c r="AF21">
+        <v>11</v>
+      </c>
+      <c r="AG21">
+        <v>10.5</v>
+      </c>
+      <c r="AH21">
+        <v>21</v>
+      </c>
+      <c r="AI21">
+        <v>85</v>
+      </c>
+      <c r="AJ21">
+        <v>15.5</v>
+      </c>
+      <c r="AK21">
+        <v>16</v>
+      </c>
+      <c r="AL21">
+        <v>36</v>
+      </c>
+      <c r="AM21">
+        <v>110</v>
+      </c>
+      <c r="AN21">
+        <v>6.8</v>
+      </c>
+      <c r="AO21">
+        <v>90</v>
+      </c>
+      <c r="AP21">
+        <v>20</v>
+      </c>
+      <c r="AQ21">
+        <v>21</v>
+      </c>
+      <c r="AR21">
+        <v>7.8</v>
+      </c>
+      <c r="AS21">
+        <v>8.6</v>
+      </c>
+      <c r="AT21">
+        <v>9.6</v>
+      </c>
+      <c r="AU21">
+        <v>9.6</v>
+      </c>
+      <c r="AV21">
+        <v>20</v>
+      </c>
+      <c r="AW21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21">
+        <v>17.5</v>
+      </c>
+      <c r="BA21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB21">
+        <v>13.5</v>
+      </c>
+      <c r="BC21">
+        <v>14</v>
+      </c>
+      <c r="BD21">
+        <v>7</v>
+      </c>
+      <c r="BE21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF21">
+        <v>6</v>
+      </c>
+      <c r="BG21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22">
+        <v>1.85</v>
+      </c>
+      <c r="G22">
+        <v>1.86</v>
+      </c>
+      <c r="H22">
+        <v>4.6</v>
+      </c>
+      <c r="I22">
+        <v>4.7</v>
+      </c>
+      <c r="J22">
+        <v>4.1</v>
+      </c>
+      <c r="K22">
+        <v>4.2</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.48</v>
+      </c>
+      <c r="Q22">
+        <v>1.64</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1.64</v>
+      </c>
+      <c r="U22">
+        <v>2.46</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>24</v>
+      </c>
+      <c r="Y22">
+        <v>23</v>
+      </c>
+      <c r="Z22">
+        <v>40</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>13</v>
+      </c>
+      <c r="AC22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>19</v>
+      </c>
+      <c r="AE22">
+        <v>50</v>
+      </c>
+      <c r="AF22">
+        <v>13.5</v>
+      </c>
+      <c r="AG22">
+        <v>10.5</v>
+      </c>
+      <c r="AH22">
+        <v>17</v>
+      </c>
+      <c r="AI22">
+        <v>50</v>
+      </c>
+      <c r="AJ22">
+        <v>21</v>
+      </c>
+      <c r="AK22">
+        <v>17.5</v>
+      </c>
+      <c r="AL22">
+        <v>29</v>
+      </c>
+      <c r="AM22">
+        <v>85</v>
+      </c>
+      <c r="AN22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO22">
+        <v>40</v>
+      </c>
+      <c r="AP22">
+        <v>20</v>
+      </c>
+      <c r="AQ22">
+        <v>18</v>
+      </c>
+      <c r="AR22">
+        <v>23</v>
+      </c>
+      <c r="AS22">
+        <v>36</v>
+      </c>
+      <c r="AT22">
+        <v>11</v>
+      </c>
+      <c r="AU22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV22">
+        <v>15.5</v>
+      </c>
+      <c r="AW22">
+        <v>26</v>
+      </c>
+      <c r="AX22">
+        <v>11.5</v>
+      </c>
+      <c r="AY22">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22">
+        <v>14.5</v>
+      </c>
+      <c r="BA22">
+        <v>27</v>
+      </c>
+      <c r="BB22">
+        <v>17</v>
+      </c>
+      <c r="BC22">
+        <v>14.5</v>
+      </c>
+      <c r="BD22">
+        <v>20</v>
+      </c>
+      <c r="BE22">
+        <v>32</v>
+      </c>
+      <c r="BF22">
+        <v>7.6</v>
+      </c>
+      <c r="BG22">
+        <v>24</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23">
+        <v>1.25</v>
+      </c>
+      <c r="G23">
+        <v>1.27</v>
+      </c>
+      <c r="H23">
+        <v>13</v>
+      </c>
+      <c r="I23">
+        <v>15.5</v>
+      </c>
+      <c r="J23">
+        <v>6.8</v>
+      </c>
+      <c r="K23">
+        <v>7.4</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.03</v>
+      </c>
+      <c r="N23">
+        <v>6.4</v>
+      </c>
+      <c r="O23">
+        <v>1.16</v>
+      </c>
+      <c r="P23">
+        <v>2.86</v>
+      </c>
+      <c r="Q23">
+        <v>1.49</v>
+      </c>
+      <c r="R23">
+        <v>1.75</v>
+      </c>
+      <c r="S23">
+        <v>2.2</v>
+      </c>
+      <c r="T23">
+        <v>2.04</v>
+      </c>
+      <c r="U23">
+        <v>1.88</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>34</v>
+      </c>
+      <c r="Y23">
+        <v>55</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>12</v>
+      </c>
+      <c r="AC23">
+        <v>16.5</v>
+      </c>
+      <c r="AD23">
+        <v>55</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG23">
+        <v>12.5</v>
+      </c>
+      <c r="AH23">
+        <v>34</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK23">
+        <v>14.5</v>
+      </c>
+      <c r="AL23">
+        <v>40</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>3.7</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>21</v>
+      </c>
+      <c r="AQ23">
+        <v>26</v>
+      </c>
+      <c r="AR23">
+        <v>42</v>
+      </c>
+      <c r="AS23">
+        <v>13.5</v>
+      </c>
+      <c r="AT23">
+        <v>10.5</v>
+      </c>
+      <c r="AU23">
+        <v>14</v>
+      </c>
+      <c r="AV23">
+        <v>40</v>
+      </c>
+      <c r="AW23">
+        <v>48</v>
+      </c>
+      <c r="AX23">
+        <v>8</v>
+      </c>
+      <c r="AY23">
+        <v>10.5</v>
+      </c>
+      <c r="AZ23">
+        <v>26</v>
+      </c>
+      <c r="BA23">
+        <v>44</v>
+      </c>
+      <c r="BB23">
+        <v>8.6</v>
+      </c>
+      <c r="BC23">
+        <v>12.5</v>
+      </c>
+      <c r="BD23">
+        <v>23</v>
+      </c>
+      <c r="BE23">
+        <v>44</v>
+      </c>
+      <c r="BF23">
+        <v>3.45</v>
+      </c>
+      <c r="BG23">
+        <v>50</v>
+      </c>
+      <c r="BH23">
+        <v>5</v>
+      </c>
+      <c r="BI23">
+        <v>4.3</v>
+      </c>
+      <c r="BJ23">
+        <v>13</v>
+      </c>
+      <c r="BK23">
+        <v>6.2</v>
+      </c>
+      <c r="BL23">
+        <v>150</v>
+      </c>
+      <c r="BM23">
+        <v>10.5</v>
+      </c>
+      <c r="BN23">
+        <v>3.95</v>
+      </c>
+      <c r="BO23">
+        <v>3.45</v>
+      </c>
+      <c r="BP23">
+        <v>7</v>
+      </c>
+      <c r="BQ23">
+        <v>5.8</v>
+      </c>
+      <c r="BR23">
+        <v>22</v>
+      </c>
+      <c r="BS23">
+        <v>7.6</v>
+      </c>
+      <c r="BT23">
+        <v>17</v>
+      </c>
+      <c r="BU23">
+        <v>6.8</v>
+      </c>
+      <c r="BV23">
+        <v>120</v>
+      </c>
+      <c r="BW23">
+        <v>10.5</v>
+      </c>
+      <c r="BX23">
+        <v>90</v>
+      </c>
+      <c r="BY23">
+        <v>10</v>
+      </c>
+      <c r="BZ23">
+        <v>9</v>
+      </c>
+      <c r="CA23">
+        <v>5.1</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24">
+        <v>1.76</v>
+      </c>
+      <c r="G24">
+        <v>1.77</v>
+      </c>
+      <c r="H24">
+        <v>5.1</v>
+      </c>
+      <c r="I24">
+        <v>5.3</v>
+      </c>
+      <c r="J24">
+        <v>4.1</v>
+      </c>
+      <c r="K24">
+        <v>4.3</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1.04</v>
+      </c>
+      <c r="N24">
+        <v>5.7</v>
+      </c>
+      <c r="O24">
+        <v>1.2</v>
+      </c>
+      <c r="P24">
+        <v>2.58</v>
+      </c>
+      <c r="Q24">
+        <v>1.59</v>
+      </c>
+      <c r="R24">
+        <v>1.64</v>
+      </c>
+      <c r="S24">
+        <v>2.46</v>
+      </c>
+      <c r="T24">
+        <v>1.61</v>
+      </c>
+      <c r="U24">
+        <v>2.56</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>26</v>
+      </c>
+      <c r="Y24">
+        <v>25</v>
+      </c>
+      <c r="Z24">
+        <v>48</v>
+      </c>
+      <c r="AA24">
+        <v>120</v>
+      </c>
+      <c r="AB24">
+        <v>13</v>
+      </c>
+      <c r="AC24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD24">
+        <v>21</v>
+      </c>
+      <c r="AE24">
+        <v>60</v>
+      </c>
+      <c r="AF24">
+        <v>13.5</v>
+      </c>
+      <c r="AG24">
+        <v>10.5</v>
+      </c>
+      <c r="AH24">
+        <v>16.5</v>
+      </c>
+      <c r="AI24">
+        <v>50</v>
+      </c>
+      <c r="AJ24">
+        <v>21</v>
+      </c>
+      <c r="AK24">
+        <v>16.5</v>
+      </c>
+      <c r="AL24">
+        <v>27</v>
+      </c>
+      <c r="AM24">
+        <v>70</v>
+      </c>
+      <c r="AN24">
+        <v>7.6</v>
+      </c>
+      <c r="AO24">
+        <v>42</v>
+      </c>
+      <c r="AP24">
+        <v>22</v>
+      </c>
+      <c r="AQ24">
+        <v>20</v>
+      </c>
+      <c r="AR24">
+        <v>32</v>
+      </c>
+      <c r="AS24">
+        <v>40</v>
+      </c>
+      <c r="AT24">
+        <v>11</v>
+      </c>
+      <c r="AU24">
+        <v>9</v>
+      </c>
+      <c r="AV24">
+        <v>17</v>
+      </c>
+      <c r="AW24">
+        <v>38</v>
+      </c>
+      <c r="AX24">
+        <v>11.5</v>
+      </c>
+      <c r="AY24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24">
+        <v>14</v>
+      </c>
+      <c r="BA24">
+        <v>27</v>
+      </c>
+      <c r="BB24">
+        <v>17</v>
+      </c>
+      <c r="BC24">
+        <v>14.5</v>
+      </c>
+      <c r="BD24">
+        <v>19</v>
+      </c>
+      <c r="BE24">
+        <v>30</v>
+      </c>
+      <c r="BF24">
+        <v>7</v>
+      </c>
+      <c r="BG24">
+        <v>25</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.52</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.86</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>2.16</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.55</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>2.16</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>2.16</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.86</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>2.16</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>2.16</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>2.16</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25">
+        <v>2.88</v>
+      </c>
+      <c r="G25">
+        <v>2.98</v>
+      </c>
+      <c r="H25">
+        <v>2.52</v>
+      </c>
+      <c r="I25">
+        <v>2.62</v>
+      </c>
+      <c r="J25">
+        <v>3.65</v>
+      </c>
+      <c r="K25">
+        <v>3.7</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1.05</v>
+      </c>
+      <c r="N25">
+        <v>4.6</v>
+      </c>
+      <c r="O25">
+        <v>1.25</v>
+      </c>
+      <c r="P25">
+        <v>2.26</v>
+      </c>
+      <c r="Q25">
+        <v>1.78</v>
+      </c>
+      <c r="R25">
+        <v>1.48</v>
+      </c>
+      <c r="S25">
+        <v>2.88</v>
+      </c>
+      <c r="T25">
+        <v>1.64</v>
+      </c>
+      <c r="U25">
+        <v>2.48</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>19</v>
+      </c>
+      <c r="Y25">
+        <v>13.5</v>
+      </c>
+      <c r="Z25">
+        <v>18.5</v>
+      </c>
+      <c r="AA25">
+        <v>36</v>
+      </c>
+      <c r="AB25">
+        <v>14.5</v>
+      </c>
+      <c r="AC25">
+        <v>8.4</v>
+      </c>
+      <c r="AD25">
+        <v>12</v>
+      </c>
+      <c r="AE25">
+        <v>26</v>
+      </c>
+      <c r="AF25">
+        <v>21</v>
+      </c>
+      <c r="AG25">
+        <v>13</v>
+      </c>
+      <c r="AH25">
+        <v>14</v>
+      </c>
+      <c r="AI25">
+        <v>36</v>
+      </c>
+      <c r="AJ25">
+        <v>80</v>
+      </c>
+      <c r="AK25">
+        <v>32</v>
+      </c>
+      <c r="AL25">
+        <v>38</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>22</v>
+      </c>
+      <c r="AO25">
+        <v>17.5</v>
+      </c>
+      <c r="AP25">
+        <v>16.5</v>
+      </c>
+      <c r="AQ25">
+        <v>12</v>
+      </c>
+      <c r="AR25">
+        <v>16.5</v>
+      </c>
+      <c r="AS25">
+        <v>22</v>
+      </c>
+      <c r="AT25">
+        <v>13</v>
+      </c>
+      <c r="AU25">
+        <v>7.6</v>
+      </c>
+      <c r="AV25">
+        <v>11</v>
+      </c>
+      <c r="AW25">
+        <v>19</v>
+      </c>
+      <c r="AX25">
+        <v>18.5</v>
+      </c>
+      <c r="AY25">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25">
+        <v>13</v>
+      </c>
+      <c r="BA25">
+        <v>26</v>
+      </c>
+      <c r="BB25">
+        <v>25</v>
+      </c>
+      <c r="BC25">
+        <v>19</v>
+      </c>
+      <c r="BD25">
+        <v>27</v>
+      </c>
+      <c r="BE25">
+        <v>32</v>
+      </c>
+      <c r="BF25">
+        <v>19.5</v>
+      </c>
+      <c r="BG25">
+        <v>15.5</v>
+      </c>
+      <c r="BH25">
+        <v>3.85</v>
+      </c>
+      <c r="BI25">
+        <v>3.15</v>
+      </c>
+      <c r="BJ25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK25">
+        <v>5.9</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>14</v>
+      </c>
+      <c r="BN25">
+        <v>6.2</v>
+      </c>
+      <c r="BO25">
+        <v>5.5</v>
+      </c>
+      <c r="BP25">
+        <v>21</v>
+      </c>
+      <c r="BQ25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR25">
+        <v>30</v>
+      </c>
+      <c r="BS25">
+        <v>10.5</v>
+      </c>
+      <c r="BT25">
+        <v>5.7</v>
+      </c>
+      <c r="BU25">
+        <v>5.1</v>
+      </c>
+      <c r="BV25">
+        <v>18</v>
+      </c>
+      <c r="BW25">
+        <v>8.6</v>
+      </c>
+      <c r="BX25">
+        <v>28</v>
+      </c>
+      <c r="BY25">
+        <v>10.5</v>
+      </c>
+      <c r="BZ25">
+        <v>21</v>
+      </c>
+      <c r="CA25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26">
+        <v>3.7</v>
+      </c>
+      <c r="G26">
+        <v>3.8</v>
+      </c>
+      <c r="H26">
+        <v>2.04</v>
+      </c>
+      <c r="I26">
+        <v>2.06</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26">
+        <v>4.1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1.04</v>
+      </c>
+      <c r="N26">
+        <v>5.2</v>
+      </c>
+      <c r="O26">
+        <v>1.22</v>
+      </c>
+      <c r="P26">
+        <v>2.42</v>
+      </c>
+      <c r="Q26">
+        <v>1.66</v>
+      </c>
+      <c r="R26">
+        <v>1.59</v>
+      </c>
+      <c r="S26">
+        <v>2.64</v>
+      </c>
+      <c r="T26">
+        <v>1.62</v>
+      </c>
+      <c r="U26">
+        <v>2.52</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>23</v>
+      </c>
+      <c r="Y26">
+        <v>13.5</v>
+      </c>
+      <c r="Z26">
+        <v>14.5</v>
+      </c>
+      <c r="AA26">
+        <v>25</v>
+      </c>
+      <c r="AB26">
+        <v>19</v>
+      </c>
+      <c r="AC26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD26">
+        <v>11</v>
+      </c>
+      <c r="AE26">
+        <v>18.5</v>
+      </c>
+      <c r="AF26">
+        <v>32</v>
+      </c>
+      <c r="AG26">
+        <v>16</v>
+      </c>
+      <c r="AH26">
+        <v>16</v>
+      </c>
+      <c r="AI26">
+        <v>30</v>
+      </c>
+      <c r="AJ26">
+        <v>70</v>
+      </c>
+      <c r="AK26">
+        <v>40</v>
+      </c>
+      <c r="AL26">
+        <v>42</v>
+      </c>
+      <c r="AM26">
+        <v>65</v>
+      </c>
+      <c r="AN26">
+        <v>30</v>
+      </c>
+      <c r="AO26">
+        <v>10.5</v>
+      </c>
+      <c r="AP26">
+        <v>19.5</v>
+      </c>
+      <c r="AQ26">
+        <v>12</v>
+      </c>
+      <c r="AR26">
+        <v>13.5</v>
+      </c>
+      <c r="AS26">
+        <v>21</v>
+      </c>
+      <c r="AT26">
+        <v>17</v>
+      </c>
+      <c r="AU26">
+        <v>8.6</v>
+      </c>
+      <c r="AV26">
+        <v>10</v>
+      </c>
+      <c r="AW26">
+        <v>17.5</v>
+      </c>
+      <c r="AX26">
+        <v>19.5</v>
+      </c>
+      <c r="AY26">
+        <v>14</v>
+      </c>
+      <c r="AZ26">
+        <v>14</v>
+      </c>
+      <c r="BA26">
+        <v>25</v>
+      </c>
+      <c r="BB26">
+        <v>32</v>
+      </c>
+      <c r="BC26">
+        <v>32</v>
+      </c>
+      <c r="BD26">
+        <v>24</v>
+      </c>
+      <c r="BE26">
+        <v>30</v>
+      </c>
+      <c r="BF26">
+        <v>19.5</v>
+      </c>
+      <c r="BG26">
+        <v>9.4</v>
+      </c>
+      <c r="BH26">
+        <v>4</v>
+      </c>
+      <c r="BI26">
+        <v>3.7</v>
+      </c>
+      <c r="BJ26">
+        <v>11</v>
+      </c>
+      <c r="BK26">
+        <v>7.8</v>
+      </c>
+      <c r="BL26">
+        <v>110</v>
+      </c>
+      <c r="BM26">
+        <v>7.8</v>
+      </c>
+      <c r="BN26">
+        <v>7.2</v>
+      </c>
+      <c r="BO26">
+        <v>6.6</v>
+      </c>
+      <c r="BP26">
+        <v>34</v>
+      </c>
+      <c r="BQ26">
+        <v>6.6</v>
+      </c>
+      <c r="BR26">
+        <v>40</v>
+      </c>
+      <c r="BS26">
+        <v>6.8</v>
+      </c>
+      <c r="BT26">
+        <v>5.1</v>
+      </c>
+      <c r="BU26">
+        <v>4.6</v>
+      </c>
+      <c r="BV26">
+        <v>16.5</v>
+      </c>
+      <c r="BW26">
+        <v>5.7</v>
+      </c>
+      <c r="BX26">
+        <v>29</v>
+      </c>
+      <c r="BY26">
+        <v>6.4</v>
+      </c>
+      <c r="BZ26">
+        <v>21</v>
+      </c>
+      <c r="CA26">
+        <v>6.2</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="160">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,12 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
+    <t>Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Georgian Umaglesi Liga</t>
+  </si>
+  <si>
     <t>Estonian Premier League</t>
   </si>
   <si>
@@ -292,6 +298,9 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
@@ -322,6 +331,18 @@
     <t>ZED FC</t>
   </si>
   <si>
+    <t>FC Astana</t>
+  </si>
+  <si>
+    <t>Tobol Kostanay</t>
+  </si>
+  <si>
+    <t>FC Iberia 1999</t>
+  </si>
+  <si>
+    <t>FK Atyrau</t>
+  </si>
+  <si>
     <t>FCI Tallinn</t>
   </si>
   <si>
@@ -337,10 +358,13 @@
     <t>Rosengard</t>
   </si>
   <si>
+    <t>Kristianstads</t>
+  </si>
+  <si>
     <t>Eskilsminne</t>
   </si>
   <si>
-    <t>Kristianstads</t>
+    <t>Skovde AIK</t>
   </si>
   <si>
     <t>Vasalunds IF</t>
@@ -352,36 +376,33 @@
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Skovde AIK</t>
-  </si>
-  <si>
     <t>FC Jarfalla</t>
   </si>
   <si>
     <t>Assyriska FF</t>
   </si>
   <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Lillestrom</t>
+  </si>
+  <si>
+    <t>Besiktas</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
     <t>Plzen</t>
   </si>
   <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Lillestrom</t>
-  </si>
-  <si>
-    <t>Besiktas</t>
-  </si>
-  <si>
-    <t>Juventus</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
     <t>Malaga</t>
   </si>
   <si>
@@ -397,6 +418,18 @@
     <t>Olympic El Qanal</t>
   </si>
   <si>
+    <t>Kairat Almaty</t>
+  </si>
+  <si>
+    <t>Elimai FC</t>
+  </si>
+  <si>
+    <t>Dila Gori</t>
+  </si>
+  <si>
+    <t>FC Ordabasy</t>
+  </si>
+  <si>
     <t>Tammeka Tartu</t>
   </si>
   <si>
@@ -412,10 +445,13 @@
     <t>Trelleborgs</t>
   </si>
   <si>
+    <t>BK Olympic</t>
+  </si>
+  <si>
     <t>Tvaakers</t>
   </si>
   <si>
-    <t>BK Olympic</t>
+    <t>FC Trollhattan</t>
   </si>
   <si>
     <t>Hammarby TFF</t>
@@ -427,40 +463,37 @@
     <t>Pyramids</t>
   </si>
   <si>
-    <t>FC Trollhattan</t>
-  </si>
-  <si>
     <t>Karlbergs BK</t>
   </si>
   <si>
     <t>AFC Eskilstuna</t>
   </si>
   <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>NEC Nijmegen</t>
+  </si>
+  <si>
+    <t>Ferencvaros</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
     <t>Union St Gilloise</t>
   </si>
   <si>
-    <t>Lech Poznan</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t>NEC Nijmegen</t>
-  </si>
-  <si>
-    <t>Ferencvaros</t>
-  </si>
-  <si>
-    <t>Bournemouth</t>
-  </si>
-  <si>
     <t>Villarreal</t>
   </si>
   <si>
-    <t>2026-09-15 10:44:18</t>
+    <t>2026-09-15 13:01:24</t>
   </si>
 </sst>
 </file>
@@ -792,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1042,25 +1075,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G2">
         <v>990</v>
       </c>
       <c r="H2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I2">
         <v>990</v>
@@ -1276,7 +1309,7 @@
         <v>1.12</v>
       </c>
       <c r="CB2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1284,19 +1317,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G3">
         <v>2.02</v>
@@ -1311,19 +1344,19 @@
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.64</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P3">
         <v>1.48</v>
@@ -1338,13 +1371,13 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
         <v>1.98</v>
@@ -1359,16 +1392,16 @@
         <v>38</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AC3">
         <v>8</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE3">
         <v>120</v>
@@ -1380,10 +1413,10 @@
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ3">
         <v>25</v>
@@ -1398,10 +1431,10 @@
         <v>310</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO3">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP3">
         <v>7</v>
@@ -1410,10 +1443,10 @@
         <v>11</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
@@ -1425,7 +1458,7 @@
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AX3">
         <v>9</v>
@@ -1449,7 +1482,7 @@
         <v>14.5</v>
       </c>
       <c r="BE3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF3">
         <v>23</v>
@@ -1461,7 +1494,7 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1518,7 +1551,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1526,31 +1559,31 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F4">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="G4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H4">
+        <v>1.92</v>
+      </c>
+      <c r="I4">
         <v>1.99</v>
       </c>
-      <c r="I4">
-        <v>2.12</v>
-      </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
         <v>3.85</v>
@@ -1559,145 +1592,145 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O4">
         <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>1.12</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="W4">
         <v>1.27</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1760,7 +1793,7 @@
         <v>1.12</v>
       </c>
       <c r="CB4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1768,28 +1801,28 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F5">
         <v>2.06</v>
       </c>
       <c r="G5">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J5">
         <v>2.94</v>
@@ -1798,211 +1831,211 @@
         <v>3.2</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P5">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T5">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="U5">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X5">
+        <v>970</v>
+      </c>
+      <c r="Y5">
+        <v>13.5</v>
+      </c>
+      <c r="Z5">
+        <v>46</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>8</v>
+      </c>
+      <c r="AC5">
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <v>950</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>13.5</v>
+      </c>
+      <c r="AG5">
+        <v>15.5</v>
+      </c>
+      <c r="AH5">
+        <v>950</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>40</v>
+      </c>
+      <c r="AK5">
+        <v>46</v>
+      </c>
+      <c r="AL5">
+        <v>100</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>48</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>5.3</v>
+      </c>
+      <c r="AQ5">
+        <v>7.6</v>
+      </c>
+      <c r="AR5">
+        <v>3.35</v>
+      </c>
+      <c r="AS5">
+        <v>3.6</v>
+      </c>
+      <c r="AT5">
+        <v>4.9</v>
+      </c>
+      <c r="AU5">
+        <v>5.7</v>
+      </c>
+      <c r="AV5">
+        <v>14</v>
+      </c>
+      <c r="AW5">
+        <v>3.6</v>
+      </c>
+      <c r="AX5">
         <v>7.4</v>
       </c>
-      <c r="Y5">
-        <v>13</v>
-      </c>
-      <c r="Z5">
-        <v>40</v>
-      </c>
-      <c r="AA5">
-        <v>170</v>
-      </c>
-      <c r="AB5">
-        <v>6.2</v>
-      </c>
-      <c r="AC5">
-        <v>7.6</v>
-      </c>
-      <c r="AD5">
-        <v>26</v>
-      </c>
-      <c r="AE5">
-        <v>120</v>
-      </c>
-      <c r="AF5">
-        <v>13</v>
-      </c>
-      <c r="AG5">
-        <v>14</v>
-      </c>
-      <c r="AH5">
-        <v>34</v>
-      </c>
-      <c r="AI5">
-        <v>160</v>
-      </c>
-      <c r="AJ5">
-        <v>34</v>
-      </c>
-      <c r="AK5">
-        <v>40</v>
-      </c>
-      <c r="AL5">
-        <v>90</v>
-      </c>
-      <c r="AM5">
-        <v>330</v>
-      </c>
-      <c r="AN5">
-        <v>42</v>
-      </c>
-      <c r="AO5">
-        <v>220</v>
-      </c>
-      <c r="AP5">
-        <v>6.4</v>
-      </c>
-      <c r="AQ5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR5">
-        <v>6.8</v>
-      </c>
-      <c r="AS5">
-        <v>7.8</v>
-      </c>
-      <c r="AT5">
-        <v>5.4</v>
-      </c>
-      <c r="AU5">
-        <v>6.4</v>
-      </c>
-      <c r="AV5">
-        <v>16.5</v>
-      </c>
-      <c r="AW5">
-        <v>6.8</v>
-      </c>
-      <c r="AX5">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="BB5">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BC5">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="BF5">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BG5">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2010,16 +2043,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F6">
         <v>1.1</v>
@@ -2034,459 +2067,459 @@
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
         <v>950</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
         <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F7">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="G7">
-        <v>8.6</v>
+        <v>990</v>
       </c>
       <c r="H7">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="I7">
-        <v>1.48</v>
+        <v>990</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.44</v>
+        <v>1.28</v>
       </c>
       <c r="Q7">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2494,483 +2527,483 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F8">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="G8">
-        <v>3.25</v>
+        <v>600</v>
       </c>
       <c r="H8">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>2.42</v>
+        <v>870</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>1.62</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="K9">
         <v>950</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2978,16 +3011,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -3002,7 +3035,7 @@
         <v>870</v>
       </c>
       <c r="J10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3212,42 +3245,42 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="G11">
-        <v>600</v>
+        <v>8.6</v>
       </c>
       <c r="H11">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>1.48</v>
       </c>
       <c r="J11">
-        <v>1.11</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3262,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3274,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3286,112 +3319,112 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH11">
         <v>0</v>
@@ -3454,42 +3487,42 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="G12">
-        <v>600</v>
+        <v>3.25</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="I12">
-        <v>870</v>
+        <v>2.46</v>
       </c>
       <c r="J12">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3504,10 +3537,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3516,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3528,112 +3561,112 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH12">
         <v>0</v>
@@ -3696,24 +3729,24 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F13">
         <v>1.1</v>
@@ -3938,72 +3971,72 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F14">
-        <v>1.71</v>
+        <v>1.1</v>
       </c>
       <c r="G14">
-        <v>1.72</v>
+        <v>600</v>
       </c>
       <c r="H14">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="I14">
-        <v>6.4</v>
+        <v>870</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>1.12</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q14">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4012,434 +4045,434 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BH14">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F15">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="G15">
-        <v>10.5</v>
+        <v>600</v>
       </c>
       <c r="H15">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="I15">
-        <v>1.6</v>
+        <v>870</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L15">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q15">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R15">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="AO15">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BG15">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BH15">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI15">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BJ15">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BK15">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BN15">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BO15">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ15">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS15">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BT15">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BU15">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BV15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BW15">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BX15">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY15">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BZ15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F16">
         <v>1.1</v>
@@ -4454,7 +4487,7 @@
         <v>870</v>
       </c>
       <c r="J16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -4664,24 +4697,24 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F17">
         <v>1.1</v>
@@ -4696,7 +4729,7 @@
         <v>870</v>
       </c>
       <c r="J17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4906,24 +4939,24 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F18">
         <v>1.1</v>
@@ -5148,72 +5181,72 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F19">
-        <v>2.86</v>
+        <v>1.71</v>
       </c>
       <c r="G19">
-        <v>2.92</v>
+        <v>1.73</v>
       </c>
       <c r="H19">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="I19">
-        <v>2.64</v>
+        <v>6.4</v>
       </c>
       <c r="J19">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P19">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="Q19">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T19">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="U19">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5222,452 +5255,452 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>6.8</v>
+      </c>
+      <c r="AC19">
+        <v>8.6</v>
+      </c>
+      <c r="AD19">
+        <v>25</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG19">
+        <v>10.5</v>
+      </c>
+      <c r="AH19">
+        <v>25</v>
+      </c>
+      <c r="AI19">
+        <v>110</v>
+      </c>
+      <c r="AJ19">
+        <v>17</v>
+      </c>
+      <c r="AK19">
+        <v>21</v>
+      </c>
+      <c r="AL19">
+        <v>48</v>
+      </c>
+      <c r="AM19">
+        <v>230</v>
+      </c>
+      <c r="AN19">
+        <v>14</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>10</v>
+      </c>
+      <c r="AQ19">
+        <v>15</v>
+      </c>
+      <c r="AR19">
+        <v>34</v>
+      </c>
+      <c r="AS19">
+        <v>44</v>
+      </c>
+      <c r="AT19">
+        <v>6.4</v>
+      </c>
+      <c r="AU19">
+        <v>8</v>
+      </c>
+      <c r="AV19">
+        <v>21</v>
+      </c>
+      <c r="AW19">
         <v>38</v>
       </c>
-      <c r="AB19">
-        <v>13.5</v>
-      </c>
-      <c r="AC19">
-        <v>8</v>
-      </c>
-      <c r="AD19">
+      <c r="AX19">
+        <v>8.4</v>
+      </c>
+      <c r="AY19">
+        <v>9.4</v>
+      </c>
+      <c r="AZ19">
+        <v>22</v>
+      </c>
+      <c r="BA19">
+        <v>40</v>
+      </c>
+      <c r="BB19">
+        <v>15.5</v>
+      </c>
+      <c r="BC19">
+        <v>18.5</v>
+      </c>
+      <c r="BD19">
+        <v>36</v>
+      </c>
+      <c r="BE19">
+        <v>46</v>
+      </c>
+      <c r="BF19">
         <v>12.5</v>
       </c>
-      <c r="AE19">
-        <v>28</v>
-      </c>
-      <c r="AF19">
-        <v>21</v>
-      </c>
-      <c r="AG19">
-        <v>13</v>
-      </c>
-      <c r="AH19">
-        <v>16.5</v>
-      </c>
-      <c r="AI19">
-        <v>38</v>
-      </c>
-      <c r="AJ19">
-        <v>44</v>
-      </c>
-      <c r="AK19">
-        <v>30</v>
-      </c>
-      <c r="AL19">
-        <v>38</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>23</v>
-      </c>
-      <c r="AO19">
-        <v>21</v>
-      </c>
-      <c r="AP19">
-        <v>15</v>
-      </c>
-      <c r="AQ19">
-        <v>11</v>
-      </c>
-      <c r="AR19">
-        <v>16</v>
-      </c>
-      <c r="AS19">
-        <v>32</v>
-      </c>
-      <c r="AT19">
-        <v>11.5</v>
-      </c>
-      <c r="AU19">
-        <v>7.4</v>
-      </c>
-      <c r="AV19">
-        <v>10.5</v>
-      </c>
-      <c r="AW19">
-        <v>18</v>
-      </c>
-      <c r="AX19">
-        <v>17</v>
-      </c>
-      <c r="AY19">
-        <v>11.5</v>
-      </c>
-      <c r="AZ19">
-        <v>14</v>
-      </c>
-      <c r="BA19">
-        <v>30</v>
-      </c>
-      <c r="BB19">
-        <v>25</v>
-      </c>
-      <c r="BC19">
-        <v>24</v>
-      </c>
-      <c r="BD19">
-        <v>28</v>
-      </c>
-      <c r="BE19">
-        <v>34</v>
-      </c>
-      <c r="BF19">
-        <v>19.5</v>
-      </c>
       <c r="BG19">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="CB19" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F20">
-        <v>1.43</v>
+        <v>7.6</v>
       </c>
       <c r="G20">
-        <v>1.46</v>
+        <v>12.5</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>1.48</v>
       </c>
       <c r="I20">
-        <v>8.800000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="J20">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="N20">
+        <v>2.92</v>
+      </c>
+      <c r="O20">
+        <v>1.47</v>
+      </c>
+      <c r="P20">
+        <v>1.61</v>
+      </c>
+      <c r="Q20">
+        <v>2.28</v>
+      </c>
+      <c r="R20">
+        <v>1.2</v>
+      </c>
+      <c r="S20">
+        <v>3.75</v>
+      </c>
+      <c r="T20">
+        <v>2.42</v>
+      </c>
+      <c r="U20">
+        <v>1.53</v>
+      </c>
+      <c r="V20">
+        <v>2.58</v>
+      </c>
+      <c r="W20">
+        <v>1.09</v>
+      </c>
+      <c r="X20">
+        <v>970</v>
+      </c>
+      <c r="Y20">
+        <v>7</v>
+      </c>
+      <c r="Z20">
+        <v>10.5</v>
+      </c>
+      <c r="AA20">
+        <v>20</v>
+      </c>
+      <c r="AB20">
+        <v>950</v>
+      </c>
+      <c r="AC20">
+        <v>970</v>
+      </c>
+      <c r="AD20">
+        <v>970</v>
+      </c>
+      <c r="AE20">
+        <v>30</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>950</v>
+      </c>
+      <c r="AH20">
+        <v>950</v>
+      </c>
+      <c r="AI20">
+        <v>90</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>970</v>
+      </c>
+      <c r="AP20">
+        <v>2.2</v>
+      </c>
+      <c r="AQ20">
         <v>4.9</v>
       </c>
-      <c r="O20">
-        <v>1.22</v>
-      </c>
-      <c r="P20">
-        <v>2.44</v>
-      </c>
-      <c r="Q20">
-        <v>1.67</v>
-      </c>
-      <c r="R20">
-        <v>1.54</v>
-      </c>
-      <c r="S20">
-        <v>2.68</v>
-      </c>
-      <c r="T20">
-        <v>1.93</v>
-      </c>
-      <c r="U20">
-        <v>2</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>24</v>
-      </c>
-      <c r="Y20">
-        <v>30</v>
-      </c>
-      <c r="Z20">
-        <v>95</v>
-      </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
+      <c r="AR20">
+        <v>5.8</v>
+      </c>
+      <c r="AS20">
         <v>10</v>
       </c>
-      <c r="AC20">
-        <v>12</v>
-      </c>
-      <c r="AD20">
+      <c r="AT20">
+        <v>15</v>
+      </c>
+      <c r="AU20">
+        <v>7.2</v>
+      </c>
+      <c r="AV20">
+        <v>8.6</v>
+      </c>
+      <c r="AW20">
+        <v>15</v>
+      </c>
+      <c r="AX20">
+        <v>2.58</v>
+      </c>
+      <c r="AY20">
+        <v>2.48</v>
+      </c>
+      <c r="AZ20">
+        <v>2.46</v>
+      </c>
+      <c r="BA20">
+        <v>2.52</v>
+      </c>
+      <c r="BB20">
+        <v>2.58</v>
+      </c>
+      <c r="BC20">
+        <v>2.58</v>
+      </c>
+      <c r="BD20">
+        <v>2.58</v>
+      </c>
+      <c r="BE20">
+        <v>2.58</v>
+      </c>
+      <c r="BF20">
+        <v>2.58</v>
+      </c>
+      <c r="BG20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH20">
+        <v>3.4</v>
+      </c>
+      <c r="BI20">
+        <v>2.4</v>
+      </c>
+      <c r="BJ20">
+        <v>16.5</v>
+      </c>
+      <c r="BK20">
+        <v>3.9</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>5</v>
+      </c>
+      <c r="BN20">
+        <v>15</v>
+      </c>
+      <c r="BO20">
+        <v>3.8</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>4.9</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>4.9</v>
+      </c>
+      <c r="BT20">
+        <v>4.3</v>
+      </c>
+      <c r="BU20">
+        <v>2.9</v>
+      </c>
+      <c r="BV20">
+        <v>12.5</v>
+      </c>
+      <c r="BW20">
+        <v>3.6</v>
+      </c>
+      <c r="BX20">
+        <v>44</v>
+      </c>
+      <c r="BY20">
+        <v>4.5</v>
+      </c>
+      <c r="BZ20">
         <v>32</v>
       </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>9.4</v>
-      </c>
-      <c r="AG20">
-        <v>10.5</v>
-      </c>
-      <c r="AH20">
-        <v>26</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>12</v>
-      </c>
-      <c r="AK20">
-        <v>15.5</v>
-      </c>
-      <c r="AL20">
-        <v>36</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>5.9</v>
-      </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
-        <v>19.5</v>
-      </c>
-      <c r="AQ20">
-        <v>18.5</v>
-      </c>
-      <c r="AR20">
-        <v>32</v>
-      </c>
-      <c r="AS20">
-        <v>100</v>
-      </c>
-      <c r="AT20">
-        <v>8.4</v>
-      </c>
-      <c r="AU20">
-        <v>10.5</v>
-      </c>
-      <c r="AV20">
-        <v>22</v>
-      </c>
-      <c r="AW20">
-        <v>38</v>
-      </c>
-      <c r="AX20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY20">
-        <v>9.4</v>
-      </c>
-      <c r="AZ20">
-        <v>21</v>
-      </c>
-      <c r="BA20">
-        <v>36</v>
-      </c>
-      <c r="BB20">
-        <v>11</v>
-      </c>
-      <c r="BC20">
-        <v>13</v>
-      </c>
-      <c r="BD20">
-        <v>26</v>
-      </c>
-      <c r="BE20">
-        <v>42</v>
-      </c>
-      <c r="BF20">
-        <v>5.3</v>
-      </c>
-      <c r="BG20">
-        <v>42</v>
-      </c>
-      <c r="BH20">
-        <v>4.2</v>
-      </c>
-      <c r="BI20">
-        <v>3.65</v>
-      </c>
-      <c r="BJ20">
-        <v>12.5</v>
-      </c>
-      <c r="BK20">
-        <v>5</v>
-      </c>
-      <c r="BL20">
-        <v>150</v>
-      </c>
-      <c r="BM20">
-        <v>7.6</v>
-      </c>
-      <c r="BN20">
-        <v>4.1</v>
-      </c>
-      <c r="BO20">
-        <v>3.6</v>
-      </c>
-      <c r="BP20">
-        <v>9.6</v>
-      </c>
-      <c r="BQ20">
-        <v>7.4</v>
-      </c>
-      <c r="BR20">
-        <v>26</v>
-      </c>
-      <c r="BS20">
-        <v>6.2</v>
-      </c>
-      <c r="BT20">
-        <v>13.5</v>
-      </c>
-      <c r="BU20">
-        <v>5.1</v>
-      </c>
-      <c r="BV20">
-        <v>80</v>
-      </c>
-      <c r="BW20">
-        <v>7.4</v>
-      </c>
-      <c r="BX20">
-        <v>75</v>
-      </c>
-      <c r="BY20">
-        <v>7.2</v>
-      </c>
-      <c r="BZ20">
-        <v>15</v>
-      </c>
       <c r="CA20">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="CB20" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F21">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="G21">
-        <v>1.63</v>
+        <v>600</v>
       </c>
       <c r="H21">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="I21">
-        <v>6.6</v>
+        <v>870</v>
       </c>
       <c r="J21">
-        <v>4.6</v>
+        <v>1.12</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5682,10 +5715,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q21">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5694,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5706,112 +5739,112 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BG21">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BH21">
         <v>0</v>
@@ -5874,42 +5907,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F22">
-        <v>1.85</v>
+        <v>1.1</v>
       </c>
       <c r="G22">
-        <v>1.86</v>
+        <v>600</v>
       </c>
       <c r="H22">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="I22">
-        <v>4.7</v>
+        <v>870</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5924,10 +5957,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q22">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -5936,10 +5969,10 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -5948,112 +5981,112 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN22">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ22">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AR22">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU22">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV22">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW22">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AX22">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY22">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ22">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA22">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB22">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BC22">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BE22">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF22">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BG22">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BH22">
         <v>0</v>
@@ -6116,314 +6149,314 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23">
+        <v>1.43</v>
+      </c>
+      <c r="G23">
+        <v>1.45</v>
+      </c>
+      <c r="H23">
+        <v>7.8</v>
+      </c>
+      <c r="I23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J23">
+        <v>5.2</v>
+      </c>
+      <c r="K23">
+        <v>5.5</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.04</v>
+      </c>
+      <c r="N23">
+        <v>5.1</v>
+      </c>
+      <c r="O23">
+        <v>1.22</v>
+      </c>
+      <c r="P23">
+        <v>2.44</v>
+      </c>
+      <c r="Q23">
+        <v>1.67</v>
+      </c>
+      <c r="R23">
+        <v>1.55</v>
+      </c>
+      <c r="S23">
+        <v>2.66</v>
+      </c>
+      <c r="T23">
+        <v>1.91</v>
+      </c>
+      <c r="U23">
+        <v>2</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>24</v>
+      </c>
+      <c r="Y23">
+        <v>30</v>
+      </c>
+      <c r="Z23">
         <v>85</v>
       </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s">
-        <v>144</v>
-      </c>
-      <c r="F23">
-        <v>1.25</v>
-      </c>
-      <c r="G23">
-        <v>1.27</v>
-      </c>
-      <c r="H23">
-        <v>13</v>
-      </c>
-      <c r="I23">
-        <v>15.5</v>
-      </c>
-      <c r="J23">
-        <v>6.8</v>
-      </c>
-      <c r="K23">
-        <v>7.4</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1.03</v>
-      </c>
-      <c r="N23">
-        <v>6.4</v>
-      </c>
-      <c r="O23">
-        <v>1.16</v>
-      </c>
-      <c r="P23">
-        <v>2.86</v>
-      </c>
-      <c r="Q23">
-        <v>1.49</v>
-      </c>
-      <c r="R23">
-        <v>1.75</v>
-      </c>
-      <c r="S23">
-        <v>2.2</v>
-      </c>
-      <c r="T23">
-        <v>2.04</v>
-      </c>
-      <c r="U23">
-        <v>1.88</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>34</v>
-      </c>
-      <c r="Y23">
-        <v>55</v>
-      </c>
-      <c r="Z23">
-        <v>1000</v>
-      </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
+        <v>10</v>
+      </c>
+      <c r="AC23">
         <v>12</v>
       </c>
-      <c r="AC23">
-        <v>16.5</v>
-      </c>
       <c r="AD23">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AE23">
         <v>1000</v>
       </c>
       <c r="AF23">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ23">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AK23">
         <v>14.5</v>
       </c>
       <c r="AL23">
+        <v>36</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>5.8</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>19.5</v>
+      </c>
+      <c r="AQ23">
+        <v>19</v>
+      </c>
+      <c r="AR23">
+        <v>32</v>
+      </c>
+      <c r="AS23">
+        <v>50</v>
+      </c>
+      <c r="AT23">
+        <v>9</v>
+      </c>
+      <c r="AU23">
+        <v>10.5</v>
+      </c>
+      <c r="AV23">
+        <v>22</v>
+      </c>
+      <c r="AW23">
         <v>40</v>
       </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>3.7</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
+      <c r="AX23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY23">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23">
         <v>21</v>
       </c>
-      <c r="AQ23">
-        <v>26</v>
-      </c>
-      <c r="AR23">
-        <v>42</v>
-      </c>
-      <c r="AS23">
-        <v>13.5</v>
-      </c>
-      <c r="AT23">
-        <v>10.5</v>
-      </c>
-      <c r="AU23">
-        <v>14</v>
-      </c>
-      <c r="AV23">
-        <v>40</v>
-      </c>
-      <c r="AW23">
-        <v>48</v>
-      </c>
-      <c r="AX23">
-        <v>8</v>
-      </c>
-      <c r="AY23">
-        <v>10.5</v>
-      </c>
-      <c r="AZ23">
-        <v>26</v>
-      </c>
       <c r="BA23">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BB23">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BC23">
         <v>12.5</v>
       </c>
       <c r="BD23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF23">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="BG23">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH23">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BI23">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BJ23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK23">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL23">
         <v>150</v>
       </c>
       <c r="BM23">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BN23">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO23">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BP23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ23">
+        <v>7.4</v>
+      </c>
+      <c r="BR23">
+        <v>26</v>
+      </c>
+      <c r="BS23">
+        <v>6</v>
+      </c>
+      <c r="BT23">
+        <v>13.5</v>
+      </c>
+      <c r="BU23">
+        <v>5.1</v>
+      </c>
+      <c r="BV23">
+        <v>80</v>
+      </c>
+      <c r="BW23">
         <v>7</v>
       </c>
-      <c r="BQ23">
-        <v>5.8</v>
-      </c>
-      <c r="BR23">
-        <v>22</v>
-      </c>
-      <c r="BS23">
-        <v>7.6</v>
-      </c>
-      <c r="BT23">
-        <v>17</v>
-      </c>
-      <c r="BU23">
-        <v>6.8</v>
-      </c>
-      <c r="BV23">
-        <v>120</v>
-      </c>
-      <c r="BW23">
-        <v>10.5</v>
-      </c>
       <c r="BX23">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BY23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BZ23">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="CA23">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="CB23" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F24">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="G24">
+        <v>1.63</v>
+      </c>
+      <c r="H24">
+        <v>5.9</v>
+      </c>
+      <c r="I24">
+        <v>6.4</v>
+      </c>
+      <c r="J24">
+        <v>4.6</v>
+      </c>
+      <c r="K24">
+        <v>5</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>2.4</v>
+      </c>
+      <c r="Q24">
+        <v>1.65</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
         <v>1.77</v>
       </c>
-      <c r="H24">
-        <v>5.1</v>
-      </c>
-      <c r="I24">
-        <v>5.3</v>
-      </c>
-      <c r="J24">
-        <v>4.1</v>
-      </c>
-      <c r="K24">
-        <v>4.3</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>1.04</v>
-      </c>
-      <c r="N24">
-        <v>5.7</v>
-      </c>
-      <c r="O24">
-        <v>1.2</v>
-      </c>
-      <c r="P24">
-        <v>2.58</v>
-      </c>
-      <c r="Q24">
-        <v>1.59</v>
-      </c>
-      <c r="R24">
-        <v>1.64</v>
-      </c>
-      <c r="S24">
-        <v>2.46</v>
-      </c>
-      <c r="T24">
-        <v>1.61</v>
-      </c>
       <c r="U24">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -6432,234 +6465,234 @@
         <v>0</v>
       </c>
       <c r="X24">
+        <v>28</v>
+      </c>
+      <c r="Y24">
         <v>26</v>
       </c>
-      <c r="Y24">
-        <v>25</v>
-      </c>
       <c r="Z24">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA24">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AB24">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC24">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD24">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE24">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AF24">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AI24">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AJ24">
+        <v>15.5</v>
+      </c>
+      <c r="AK24">
+        <v>16</v>
+      </c>
+      <c r="AL24">
+        <v>36</v>
+      </c>
+      <c r="AM24">
+        <v>110</v>
+      </c>
+      <c r="AN24">
+        <v>6.8</v>
+      </c>
+      <c r="AO24">
+        <v>90</v>
+      </c>
+      <c r="AP24">
+        <v>20</v>
+      </c>
+      <c r="AQ24">
         <v>21</v>
       </c>
-      <c r="AK24">
-        <v>16.5</v>
-      </c>
-      <c r="AL24">
-        <v>27</v>
-      </c>
-      <c r="AM24">
-        <v>70</v>
-      </c>
-      <c r="AN24">
-        <v>7.6</v>
-      </c>
-      <c r="AO24">
-        <v>42</v>
-      </c>
-      <c r="AP24">
-        <v>22</v>
-      </c>
-      <c r="AQ24">
+      <c r="AR24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS24">
+        <v>9</v>
+      </c>
+      <c r="AT24">
+        <v>9.6</v>
+      </c>
+      <c r="AU24">
+        <v>9.6</v>
+      </c>
+      <c r="AV24">
         <v>20</v>
       </c>
-      <c r="AR24">
-        <v>32</v>
-      </c>
-      <c r="AS24">
-        <v>40</v>
-      </c>
-      <c r="AT24">
-        <v>11</v>
-      </c>
-      <c r="AU24">
-        <v>9</v>
-      </c>
-      <c r="AV24">
-        <v>17</v>
-      </c>
       <c r="AW24">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="AX24">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY24">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
+        <v>17.5</v>
+      </c>
+      <c r="BA24">
+        <v>8.6</v>
+      </c>
+      <c r="BB24">
+        <v>13.5</v>
+      </c>
+      <c r="BC24">
         <v>14</v>
       </c>
-      <c r="BA24">
-        <v>27</v>
-      </c>
-      <c r="BB24">
-        <v>17</v>
-      </c>
-      <c r="BC24">
-        <v>14.5</v>
-      </c>
       <c r="BD24">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BE24">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BG24">
-        <v>25</v>
+        <v>8.6</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI24">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK24">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM24">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO24">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ24">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS24">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU24">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW24">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY24">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA24">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F25">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="G25">
-        <v>2.98</v>
+        <v>1.86</v>
       </c>
       <c r="H25">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="I25">
-        <v>2.62</v>
+        <v>4.7</v>
       </c>
       <c r="J25">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K25">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q25">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="R25">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T25">
         <v>1.64</v>
@@ -6674,175 +6707,175 @@
         <v>0</v>
       </c>
       <c r="X25">
+        <v>24</v>
+      </c>
+      <c r="Y25">
+        <v>23</v>
+      </c>
+      <c r="Z25">
+        <v>40</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>13</v>
+      </c>
+      <c r="AC25">
+        <v>9.6</v>
+      </c>
+      <c r="AD25">
         <v>19</v>
       </c>
-      <c r="Y25">
+      <c r="AE25">
+        <v>50</v>
+      </c>
+      <c r="AF25">
         <v>13.5</v>
       </c>
-      <c r="Z25">
-        <v>18.5</v>
-      </c>
-      <c r="AA25">
+      <c r="AG25">
+        <v>10.5</v>
+      </c>
+      <c r="AH25">
+        <v>17</v>
+      </c>
+      <c r="AI25">
+        <v>50</v>
+      </c>
+      <c r="AJ25">
+        <v>21</v>
+      </c>
+      <c r="AK25">
+        <v>17.5</v>
+      </c>
+      <c r="AL25">
+        <v>29</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>8.4</v>
+      </c>
+      <c r="AO25">
+        <v>40</v>
+      </c>
+      <c r="AP25">
+        <v>20</v>
+      </c>
+      <c r="AQ25">
+        <v>18</v>
+      </c>
+      <c r="AR25">
+        <v>23</v>
+      </c>
+      <c r="AS25">
         <v>36</v>
       </c>
-      <c r="AB25">
+      <c r="AT25">
+        <v>11</v>
+      </c>
+      <c r="AU25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV25">
+        <v>16</v>
+      </c>
+      <c r="AW25">
+        <v>26</v>
+      </c>
+      <c r="AX25">
+        <v>11.5</v>
+      </c>
+      <c r="AY25">
+        <v>9.6</v>
+      </c>
+      <c r="AZ25">
         <v>14.5</v>
       </c>
-      <c r="AC25">
-        <v>8.4</v>
-      </c>
-      <c r="AD25">
-        <v>12</v>
-      </c>
-      <c r="AE25">
-        <v>26</v>
-      </c>
-      <c r="AF25">
-        <v>21</v>
-      </c>
-      <c r="AG25">
-        <v>13</v>
-      </c>
-      <c r="AH25">
-        <v>14</v>
-      </c>
-      <c r="AI25">
+      <c r="BA25">
         <v>36</v>
       </c>
-      <c r="AJ25">
-        <v>80</v>
-      </c>
-      <c r="AK25">
-        <v>32</v>
-      </c>
-      <c r="AL25">
-        <v>38</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>22</v>
-      </c>
-      <c r="AO25">
+      <c r="BB25">
         <v>17.5</v>
       </c>
-      <c r="AP25">
-        <v>16.5</v>
-      </c>
-      <c r="AQ25">
-        <v>12</v>
-      </c>
-      <c r="AR25">
-        <v>16.5</v>
-      </c>
-      <c r="AS25">
-        <v>22</v>
-      </c>
-      <c r="AT25">
-        <v>13</v>
-      </c>
-      <c r="AU25">
-        <v>7.6</v>
-      </c>
-      <c r="AV25">
-        <v>11</v>
-      </c>
-      <c r="AW25">
-        <v>19</v>
-      </c>
-      <c r="AX25">
-        <v>18.5</v>
-      </c>
-      <c r="AY25">
-        <v>11.5</v>
-      </c>
-      <c r="AZ25">
-        <v>13</v>
-      </c>
-      <c r="BA25">
-        <v>26</v>
-      </c>
-      <c r="BB25">
-        <v>25</v>
-      </c>
       <c r="BC25">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BE25">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BF25">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG25">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BH25">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BI25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ25">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK25">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM25">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BN25">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO25">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP25">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ25">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR25">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BS25">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT25">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BU25">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV25">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BW25">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BX25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BY25">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ25">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA25">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6850,241 +6883,1209 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F26">
+        <v>1.26</v>
+      </c>
+      <c r="G26">
+        <v>1.28</v>
+      </c>
+      <c r="H26">
+        <v>13</v>
+      </c>
+      <c r="I26">
+        <v>15</v>
+      </c>
+      <c r="J26">
+        <v>6.8</v>
+      </c>
+      <c r="K26">
+        <v>7.4</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1.03</v>
+      </c>
+      <c r="N26">
+        <v>6.4</v>
+      </c>
+      <c r="O26">
+        <v>1.16</v>
+      </c>
+      <c r="P26">
+        <v>2.86</v>
+      </c>
+      <c r="Q26">
+        <v>1.49</v>
+      </c>
+      <c r="R26">
+        <v>1.75</v>
+      </c>
+      <c r="S26">
+        <v>2.22</v>
+      </c>
+      <c r="T26">
+        <v>2.06</v>
+      </c>
+      <c r="U26">
+        <v>1.88</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>34</v>
+      </c>
+      <c r="Y26">
+        <v>55</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>12</v>
+      </c>
+      <c r="AC26">
+        <v>16.5</v>
+      </c>
+      <c r="AD26">
+        <v>55</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG26">
+        <v>12.5</v>
+      </c>
+      <c r="AH26">
+        <v>36</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK26">
+        <v>14.5</v>
+      </c>
+      <c r="AL26">
+        <v>40</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
         <v>3.7</v>
       </c>
-      <c r="G26">
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>21</v>
+      </c>
+      <c r="AQ26">
+        <v>26</v>
+      </c>
+      <c r="AR26">
+        <v>42</v>
+      </c>
+      <c r="AS26">
+        <v>110</v>
+      </c>
+      <c r="AT26">
+        <v>10.5</v>
+      </c>
+      <c r="AU26">
+        <v>14</v>
+      </c>
+      <c r="AV26">
+        <v>26</v>
+      </c>
+      <c r="AW26">
+        <v>48</v>
+      </c>
+      <c r="AX26">
+        <v>8</v>
+      </c>
+      <c r="AY26">
+        <v>10.5</v>
+      </c>
+      <c r="AZ26">
+        <v>26</v>
+      </c>
+      <c r="BA26">
+        <v>44</v>
+      </c>
+      <c r="BB26">
+        <v>8.6</v>
+      </c>
+      <c r="BC26">
+        <v>12</v>
+      </c>
+      <c r="BD26">
+        <v>23</v>
+      </c>
+      <c r="BE26">
+        <v>44</v>
+      </c>
+      <c r="BF26">
+        <v>3.45</v>
+      </c>
+      <c r="BG26">
+        <v>50</v>
+      </c>
+      <c r="BH26">
+        <v>5</v>
+      </c>
+      <c r="BI26">
+        <v>4.3</v>
+      </c>
+      <c r="BJ26">
+        <v>13</v>
+      </c>
+      <c r="BK26">
+        <v>6.4</v>
+      </c>
+      <c r="BL26">
+        <v>150</v>
+      </c>
+      <c r="BM26">
+        <v>11</v>
+      </c>
+      <c r="BN26">
+        <v>3.95</v>
+      </c>
+      <c r="BO26">
+        <v>3.45</v>
+      </c>
+      <c r="BP26">
+        <v>6.8</v>
+      </c>
+      <c r="BQ26">
+        <v>5.8</v>
+      </c>
+      <c r="BR26">
+        <v>22</v>
+      </c>
+      <c r="BS26">
+        <v>7.8</v>
+      </c>
+      <c r="BT26">
+        <v>17</v>
+      </c>
+      <c r="BU26">
+        <v>7.2</v>
+      </c>
+      <c r="BV26">
+        <v>120</v>
+      </c>
+      <c r="BW26">
+        <v>11</v>
+      </c>
+      <c r="BX26">
+        <v>90</v>
+      </c>
+      <c r="BY26">
+        <v>10.5</v>
+      </c>
+      <c r="BZ26">
+        <v>9</v>
+      </c>
+      <c r="CA26">
+        <v>5.2</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27">
+        <v>1.76</v>
+      </c>
+      <c r="G27">
+        <v>1.78</v>
+      </c>
+      <c r="H27">
+        <v>5.1</v>
+      </c>
+      <c r="I27">
+        <v>5.3</v>
+      </c>
+      <c r="J27">
+        <v>4.1</v>
+      </c>
+      <c r="K27">
+        <v>4.3</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1.04</v>
+      </c>
+      <c r="N27">
+        <v>5.7</v>
+      </c>
+      <c r="O27">
+        <v>1.2</v>
+      </c>
+      <c r="P27">
+        <v>2.58</v>
+      </c>
+      <c r="Q27">
+        <v>1.59</v>
+      </c>
+      <c r="R27">
+        <v>1.64</v>
+      </c>
+      <c r="S27">
+        <v>2.46</v>
+      </c>
+      <c r="T27">
+        <v>1.6</v>
+      </c>
+      <c r="U27">
+        <v>2.56</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>25</v>
+      </c>
+      <c r="Y27">
+        <v>26</v>
+      </c>
+      <c r="Z27">
+        <v>48</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>13</v>
+      </c>
+      <c r="AC27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD27">
+        <v>21</v>
+      </c>
+      <c r="AE27">
+        <v>60</v>
+      </c>
+      <c r="AF27">
+        <v>14</v>
+      </c>
+      <c r="AG27">
+        <v>10.5</v>
+      </c>
+      <c r="AH27">
+        <v>16</v>
+      </c>
+      <c r="AI27">
+        <v>55</v>
+      </c>
+      <c r="AJ27">
+        <v>19.5</v>
+      </c>
+      <c r="AK27">
+        <v>16.5</v>
+      </c>
+      <c r="AL27">
+        <v>26</v>
+      </c>
+      <c r="AM27">
+        <v>70</v>
+      </c>
+      <c r="AN27">
+        <v>7.4</v>
+      </c>
+      <c r="AO27">
+        <v>44</v>
+      </c>
+      <c r="AP27">
+        <v>21</v>
+      </c>
+      <c r="AQ27">
+        <v>21</v>
+      </c>
+      <c r="AR27">
+        <v>25</v>
+      </c>
+      <c r="AS27">
+        <v>40</v>
+      </c>
+      <c r="AT27">
+        <v>11</v>
+      </c>
+      <c r="AU27">
+        <v>9</v>
+      </c>
+      <c r="AV27">
+        <v>17.5</v>
+      </c>
+      <c r="AW27">
+        <v>28</v>
+      </c>
+      <c r="AX27">
+        <v>12</v>
+      </c>
+      <c r="AY27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ27">
+        <v>13.5</v>
+      </c>
+      <c r="BA27">
+        <v>27</v>
+      </c>
+      <c r="BB27">
+        <v>17</v>
+      </c>
+      <c r="BC27">
+        <v>14.5</v>
+      </c>
+      <c r="BD27">
+        <v>21</v>
+      </c>
+      <c r="BE27">
+        <v>30</v>
+      </c>
+      <c r="BF27">
+        <v>7</v>
+      </c>
+      <c r="BG27">
+        <v>25</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.5</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.84</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>2.14</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.56</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>2.14</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>2.14</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.84</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>2.14</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>2.14</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>2.14</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28">
+        <v>3.05</v>
+      </c>
+      <c r="G28">
+        <v>3.1</v>
+      </c>
+      <c r="H28">
+        <v>2.46</v>
+      </c>
+      <c r="I28">
+        <v>2.5</v>
+      </c>
+      <c r="J28">
+        <v>3.65</v>
+      </c>
+      <c r="K28">
+        <v>3.7</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1.05</v>
+      </c>
+      <c r="N28">
+        <v>4.6</v>
+      </c>
+      <c r="O28">
+        <v>1.25</v>
+      </c>
+      <c r="P28">
+        <v>2.26</v>
+      </c>
+      <c r="Q28">
+        <v>1.77</v>
+      </c>
+      <c r="R28">
+        <v>1.48</v>
+      </c>
+      <c r="S28">
+        <v>2.92</v>
+      </c>
+      <c r="T28">
+        <v>1.64</v>
+      </c>
+      <c r="U28">
+        <v>2.46</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>19</v>
+      </c>
+      <c r="Y28">
+        <v>13</v>
+      </c>
+      <c r="Z28">
+        <v>17.5</v>
+      </c>
+      <c r="AA28">
+        <v>34</v>
+      </c>
+      <c r="AB28">
+        <v>15.5</v>
+      </c>
+      <c r="AC28">
+        <v>8.4</v>
+      </c>
+      <c r="AD28">
+        <v>11.5</v>
+      </c>
+      <c r="AE28">
+        <v>25</v>
+      </c>
+      <c r="AF28">
+        <v>23</v>
+      </c>
+      <c r="AG28">
+        <v>13.5</v>
+      </c>
+      <c r="AH28">
+        <v>14</v>
+      </c>
+      <c r="AI28">
+        <v>34</v>
+      </c>
+      <c r="AJ28">
+        <v>80</v>
+      </c>
+      <c r="AK28">
+        <v>34</v>
+      </c>
+      <c r="AL28">
+        <v>40</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>29</v>
+      </c>
+      <c r="AO28">
+        <v>16.5</v>
+      </c>
+      <c r="AP28">
+        <v>16.5</v>
+      </c>
+      <c r="AQ28">
+        <v>11.5</v>
+      </c>
+      <c r="AR28">
+        <v>15</v>
+      </c>
+      <c r="AS28">
+        <v>21</v>
+      </c>
+      <c r="AT28">
+        <v>13.5</v>
+      </c>
+      <c r="AU28">
+        <v>7.6</v>
+      </c>
+      <c r="AV28">
+        <v>10.5</v>
+      </c>
+      <c r="AW28">
+        <v>21</v>
+      </c>
+      <c r="AX28">
+        <v>20</v>
+      </c>
+      <c r="AY28">
+        <v>11.5</v>
+      </c>
+      <c r="AZ28">
+        <v>13</v>
+      </c>
+      <c r="BA28">
+        <v>21</v>
+      </c>
+      <c r="BB28">
+        <v>26</v>
+      </c>
+      <c r="BC28">
+        <v>19</v>
+      </c>
+      <c r="BD28">
+        <v>28</v>
+      </c>
+      <c r="BE28">
+        <v>32</v>
+      </c>
+      <c r="BF28">
+        <v>20</v>
+      </c>
+      <c r="BG28">
+        <v>14.5</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.36</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>2.02</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.04</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.63</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.04</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.04</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.58</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.04</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.04</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.04</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29">
+        <v>2.92</v>
+      </c>
+      <c r="G29">
+        <v>2.96</v>
+      </c>
+      <c r="H29">
+        <v>2.6</v>
+      </c>
+      <c r="I29">
+        <v>2.62</v>
+      </c>
+      <c r="J29">
+        <v>3.6</v>
+      </c>
+      <c r="K29">
+        <v>3.65</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>2.08</v>
+      </c>
+      <c r="Q29">
+        <v>1.84</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>1.69</v>
+      </c>
+      <c r="U29">
+        <v>2.32</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>17.5</v>
+      </c>
+      <c r="Y29">
+        <v>13</v>
+      </c>
+      <c r="Z29">
+        <v>19</v>
+      </c>
+      <c r="AA29">
+        <v>40</v>
+      </c>
+      <c r="AB29">
+        <v>13.5</v>
+      </c>
+      <c r="AC29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD29">
+        <v>12.5</v>
+      </c>
+      <c r="AE29">
+        <v>28</v>
+      </c>
+      <c r="AF29">
+        <v>21</v>
+      </c>
+      <c r="AG29">
+        <v>13</v>
+      </c>
+      <c r="AH29">
+        <v>16.5</v>
+      </c>
+      <c r="AI29">
+        <v>38</v>
+      </c>
+      <c r="AJ29">
+        <v>44</v>
+      </c>
+      <c r="AK29">
+        <v>30</v>
+      </c>
+      <c r="AL29">
+        <v>40</v>
+      </c>
+      <c r="AM29">
+        <v>80</v>
+      </c>
+      <c r="AN29">
+        <v>23</v>
+      </c>
+      <c r="AO29">
+        <v>21</v>
+      </c>
+      <c r="AP29">
+        <v>15</v>
+      </c>
+      <c r="AQ29">
+        <v>11</v>
+      </c>
+      <c r="AR29">
+        <v>16</v>
+      </c>
+      <c r="AS29">
+        <v>28</v>
+      </c>
+      <c r="AT29">
+        <v>11.5</v>
+      </c>
+      <c r="AU29">
+        <v>7.4</v>
+      </c>
+      <c r="AV29">
+        <v>10.5</v>
+      </c>
+      <c r="AW29">
+        <v>21</v>
+      </c>
+      <c r="AX29">
+        <v>17</v>
+      </c>
+      <c r="AY29">
+        <v>11.5</v>
+      </c>
+      <c r="AZ29">
+        <v>14</v>
+      </c>
+      <c r="BA29">
+        <v>23</v>
+      </c>
+      <c r="BB29">
+        <v>25</v>
+      </c>
+      <c r="BC29">
+        <v>24</v>
+      </c>
+      <c r="BD29">
+        <v>28</v>
+      </c>
+      <c r="BE29">
+        <v>34</v>
+      </c>
+      <c r="BF29">
+        <v>19.5</v>
+      </c>
+      <c r="BG29">
+        <v>17.5</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30">
+        <v>3.75</v>
+      </c>
+      <c r="G30">
         <v>3.8</v>
       </c>
-      <c r="H26">
+      <c r="H30">
         <v>2.04</v>
       </c>
-      <c r="I26">
+      <c r="I30">
         <v>2.06</v>
       </c>
-      <c r="J26">
+      <c r="J30">
         <v>4</v>
       </c>
-      <c r="K26">
+      <c r="K30">
         <v>4.1</v>
       </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>1.04</v>
       </c>
-      <c r="N26">
+      <c r="N30">
         <v>5.2</v>
       </c>
-      <c r="O26">
+      <c r="O30">
         <v>1.22</v>
       </c>
-      <c r="P26">
+      <c r="P30">
         <v>2.42</v>
       </c>
-      <c r="Q26">
+      <c r="Q30">
         <v>1.66</v>
       </c>
-      <c r="R26">
+      <c r="R30">
         <v>1.59</v>
       </c>
-      <c r="S26">
-        <v>2.64</v>
-      </c>
-      <c r="T26">
+      <c r="S30">
+        <v>2.66</v>
+      </c>
+      <c r="T30">
         <v>1.62</v>
       </c>
-      <c r="U26">
+      <c r="U30">
         <v>2.52</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>22</v>
+      </c>
+      <c r="Y30">
+        <v>13</v>
+      </c>
+      <c r="Z30">
+        <v>14.5</v>
+      </c>
+      <c r="AA30">
+        <v>25</v>
+      </c>
+      <c r="AB30">
+        <v>19</v>
+      </c>
+      <c r="AC30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD30">
+        <v>11</v>
+      </c>
+      <c r="AE30">
+        <v>18.5</v>
+      </c>
+      <c r="AF30">
+        <v>32</v>
+      </c>
+      <c r="AG30">
+        <v>16</v>
+      </c>
+      <c r="AH30">
+        <v>15.5</v>
+      </c>
+      <c r="AI30">
+        <v>30</v>
+      </c>
+      <c r="AJ30">
+        <v>70</v>
+      </c>
+      <c r="AK30">
+        <v>40</v>
+      </c>
+      <c r="AL30">
+        <v>42</v>
+      </c>
+      <c r="AM30">
+        <v>70</v>
+      </c>
+      <c r="AN30">
+        <v>32</v>
+      </c>
+      <c r="AO30">
+        <v>10.5</v>
+      </c>
+      <c r="AP30">
+        <v>20</v>
+      </c>
+      <c r="AQ30">
+        <v>12</v>
+      </c>
+      <c r="AR30">
+        <v>13.5</v>
+      </c>
+      <c r="AS30">
+        <v>22</v>
+      </c>
+      <c r="AT30">
+        <v>17</v>
+      </c>
+      <c r="AU30">
+        <v>8.4</v>
+      </c>
+      <c r="AV30">
+        <v>10</v>
+      </c>
+      <c r="AW30">
+        <v>17.5</v>
+      </c>
+      <c r="AX30">
+        <v>19.5</v>
+      </c>
+      <c r="AY30">
+        <v>14</v>
+      </c>
+      <c r="AZ30">
+        <v>14</v>
+      </c>
+      <c r="BA30">
+        <v>19</v>
+      </c>
+      <c r="BB30">
+        <v>32</v>
+      </c>
+      <c r="BC30">
         <v>23</v>
       </c>
-      <c r="Y26">
-        <v>13.5</v>
-      </c>
-      <c r="Z26">
-        <v>14.5</v>
-      </c>
-      <c r="AA26">
-        <v>25</v>
-      </c>
-      <c r="AB26">
-        <v>19</v>
-      </c>
-      <c r="AC26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD26">
+      <c r="BD30">
+        <v>24</v>
+      </c>
+      <c r="BE30">
+        <v>32</v>
+      </c>
+      <c r="BF30">
+        <v>24</v>
+      </c>
+      <c r="BG30">
+        <v>9.4</v>
+      </c>
+      <c r="BH30">
+        <v>4</v>
+      </c>
+      <c r="BI30">
+        <v>3.65</v>
+      </c>
+      <c r="BJ30">
         <v>11</v>
       </c>
-      <c r="AE26">
-        <v>18.5</v>
-      </c>
-      <c r="AF26">
-        <v>32</v>
-      </c>
-      <c r="AG26">
-        <v>16</v>
-      </c>
-      <c r="AH26">
-        <v>16</v>
-      </c>
-      <c r="AI26">
-        <v>30</v>
-      </c>
-      <c r="AJ26">
-        <v>70</v>
-      </c>
-      <c r="AK26">
+      <c r="BK30">
+        <v>7.8</v>
+      </c>
+      <c r="BL30">
+        <v>110</v>
+      </c>
+      <c r="BM30">
+        <v>7.8</v>
+      </c>
+      <c r="BN30">
+        <v>7.2</v>
+      </c>
+      <c r="BO30">
+        <v>6.6</v>
+      </c>
+      <c r="BP30">
+        <v>34</v>
+      </c>
+      <c r="BQ30">
+        <v>6.6</v>
+      </c>
+      <c r="BR30">
         <v>40</v>
       </c>
-      <c r="AL26">
-        <v>42</v>
-      </c>
-      <c r="AM26">
-        <v>65</v>
-      </c>
-      <c r="AN26">
-        <v>30</v>
-      </c>
-      <c r="AO26">
-        <v>10.5</v>
-      </c>
-      <c r="AP26">
-        <v>19.5</v>
-      </c>
-      <c r="AQ26">
-        <v>12</v>
-      </c>
-      <c r="AR26">
-        <v>13.5</v>
-      </c>
-      <c r="AS26">
+      <c r="BS30">
+        <v>6.8</v>
+      </c>
+      <c r="BT30">
+        <v>5.1</v>
+      </c>
+      <c r="BU30">
+        <v>4.6</v>
+      </c>
+      <c r="BV30">
+        <v>16.5</v>
+      </c>
+      <c r="BW30">
+        <v>5.7</v>
+      </c>
+      <c r="BX30">
+        <v>29</v>
+      </c>
+      <c r="BY30">
+        <v>6.4</v>
+      </c>
+      <c r="BZ30">
         <v>21</v>
       </c>
-      <c r="AT26">
-        <v>17</v>
-      </c>
-      <c r="AU26">
-        <v>8.6</v>
-      </c>
-      <c r="AV26">
-        <v>10</v>
-      </c>
-      <c r="AW26">
-        <v>17.5</v>
-      </c>
-      <c r="AX26">
-        <v>19.5</v>
-      </c>
-      <c r="AY26">
-        <v>14</v>
-      </c>
-      <c r="AZ26">
-        <v>14</v>
-      </c>
-      <c r="BA26">
-        <v>25</v>
-      </c>
-      <c r="BB26">
-        <v>32</v>
-      </c>
-      <c r="BC26">
-        <v>32</v>
-      </c>
-      <c r="BD26">
-        <v>24</v>
-      </c>
-      <c r="BE26">
-        <v>30</v>
-      </c>
-      <c r="BF26">
-        <v>19.5</v>
-      </c>
-      <c r="BG26">
-        <v>9.4</v>
-      </c>
-      <c r="BH26">
-        <v>4</v>
-      </c>
-      <c r="BI26">
-        <v>3.7</v>
-      </c>
-      <c r="BJ26">
-        <v>11</v>
-      </c>
-      <c r="BK26">
-        <v>7.8</v>
-      </c>
-      <c r="BL26">
-        <v>110</v>
-      </c>
-      <c r="BM26">
-        <v>7.8</v>
-      </c>
-      <c r="BN26">
-        <v>7.2</v>
-      </c>
-      <c r="BO26">
-        <v>6.6</v>
-      </c>
-      <c r="BP26">
-        <v>34</v>
-      </c>
-      <c r="BQ26">
-        <v>6.6</v>
-      </c>
-      <c r="BR26">
-        <v>40</v>
-      </c>
-      <c r="BS26">
-        <v>6.8</v>
-      </c>
-      <c r="BT26">
-        <v>5.1</v>
-      </c>
-      <c r="BU26">
-        <v>4.6</v>
-      </c>
-      <c r="BV26">
-        <v>16.5</v>
-      </c>
-      <c r="BW26">
-        <v>5.7</v>
-      </c>
-      <c r="BX26">
-        <v>29</v>
-      </c>
-      <c r="BY26">
-        <v>6.4</v>
-      </c>
-      <c r="BZ26">
-        <v>21</v>
-      </c>
-      <c r="CA26">
+      <c r="CA30">
         <v>6.2</v>
       </c>
-      <c r="CB26" t="s">
-        <v>148</v>
+      <c r="CB30" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="163">
   <si>
     <t>League</t>
   </si>
@@ -286,6 +286,9 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>South African Premier Division</t>
+  </si>
+  <si>
     <t>2026-09-17</t>
   </si>
   <si>
@@ -376,6 +379,9 @@
     <t>ENPPI</t>
   </si>
   <si>
+    <t>Orlando Pirates (SA)</t>
+  </si>
+  <si>
     <t>FC Jarfalla</t>
   </si>
   <si>
@@ -463,6 +469,9 @@
     <t>Pyramids</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>Karlbergs BK</t>
   </si>
   <si>
@@ -493,7 +502,7 @@
     <t>Villarreal</t>
   </si>
   <si>
-    <t>2026-09-15 13:01:24</t>
+    <t>2026-09-15 15:16:31</t>
   </si>
 </sst>
 </file>
@@ -825,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1075,16 +1084,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F2">
         <v>1.12</v>
@@ -1099,7 +1108,7 @@
         <v>990</v>
       </c>
       <c r="J2">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -1135,10 +1144,10 @@
         <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1309,7 +1318,7 @@
         <v>1.12</v>
       </c>
       <c r="CB2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1317,31 +1326,31 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F3">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
         <v>3.25</v>
@@ -1353,16 +1362,16 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
         <v>1.48</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R3">
         <v>1.17</v>
@@ -1380,34 +1389,34 @@
         <v>1.23</v>
       </c>
       <c r="W3">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X3">
         <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
         <v>38</v>
       </c>
       <c r="AA3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB3">
         <v>6</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
         <v>23</v>
       </c>
       <c r="AE3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
         <v>12</v>
@@ -1419,7 +1428,7 @@
         <v>150</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK3">
         <v>32</v>
@@ -1431,7 +1440,7 @@
         <v>310</v>
       </c>
       <c r="AN3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO3">
         <v>210</v>
@@ -1443,7 +1452,7 @@
         <v>11</v>
       </c>
       <c r="AR3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS3">
         <v>14</v>
@@ -1458,10 +1467,10 @@
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1473,7 +1482,7 @@
         <v>14</v>
       </c>
       <c r="BB3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC3">
         <v>27</v>
@@ -1485,10 +1494,10 @@
         <v>14.5</v>
       </c>
       <c r="BF3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BG3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1551,7 +1560,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1559,25 +1568,25 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F4">
         <v>4.3</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H4">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I4">
         <v>1.99</v>
@@ -1601,25 +1610,25 @@
         <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
         <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U4">
         <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W4">
         <v>1.27</v>
@@ -1631,10 +1640,10 @@
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AB4">
         <v>19</v>
@@ -1646,7 +1655,7 @@
         <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF4">
         <v>40</v>
@@ -1658,7 +1667,7 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ4">
         <v>120</v>
@@ -1676,10 +1685,10 @@
         <v>75</v>
       </c>
       <c r="AO4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
         <v>8</v>
@@ -1700,10 +1709,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY4">
         <v>15.5</v>
@@ -1712,25 +1721,25 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB4">
+        <v>5.4</v>
+      </c>
+      <c r="BC4">
+        <v>5.2</v>
+      </c>
+      <c r="BD4">
         <v>5.3</v>
       </c>
-      <c r="BC4">
-        <v>5.1</v>
-      </c>
-      <c r="BD4">
-        <v>5.2</v>
-      </c>
       <c r="BE4">
+        <v>5.4</v>
+      </c>
+      <c r="BF4">
         <v>5.3</v>
       </c>
-      <c r="BF4">
-        <v>5.2</v>
-      </c>
       <c r="BG4">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1793,7 +1802,7 @@
         <v>1.12</v>
       </c>
       <c r="CB4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1801,19 +1810,19 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
         <v>2.22</v>
@@ -1822,10 +1831,10 @@
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K5">
         <v>3.2</v>
@@ -1840,10 +1849,10 @@
         <v>2.28</v>
       </c>
       <c r="O5">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P5">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q5">
         <v>2.92</v>
@@ -2035,7 +2044,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2043,31 +2052,31 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F6">
         <v>1.1</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>3.05</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2103,10 +2112,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2277,7 +2286,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2285,16 +2294,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F7">
         <v>1.1</v>
@@ -2321,13 +2330,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q7">
         <v>1.25</v>
@@ -2336,7 +2345,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2345,10 +2354,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2519,7 +2528,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2527,16 +2536,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F8">
         <v>1.1</v>
@@ -2587,10 +2596,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2647,52 +2656,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2761,7 +2770,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2769,16 +2778,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F9">
         <v>2.68</v>
@@ -2793,7 +2802,7 @@
         <v>1.62</v>
       </c>
       <c r="J9">
-        <v>2.62</v>
+        <v>1.12</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2805,16 +2814,16 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R9">
         <v>1.08</v>
@@ -2832,7 +2841,7 @@
         <v>2.6</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3003,7 +3012,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3011,16 +3020,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -3041,211 +3050,211 @@
         <v>950</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="P10">
         <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3253,19 +3262,19 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G11">
         <v>8.6</v>
@@ -3283,28 +3292,28 @@
         <v>5.5</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q11">
         <v>1.61</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T11">
         <v>1.83</v>
@@ -3313,10 +3322,10 @@
         <v>2.06</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3331,13 +3340,13 @@
         <v>13</v>
       </c>
       <c r="AB11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC11">
         <v>12</v>
       </c>
       <c r="AD11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE11">
         <v>14.5</v>
@@ -3346,16 +3355,16 @@
         <v>90</v>
       </c>
       <c r="AG11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH11">
         <v>25</v>
       </c>
       <c r="AI11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AK11">
         <v>130</v>
@@ -3376,7 +3385,7 @@
         <v>20</v>
       </c>
       <c r="AQ11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11">
         <v>8.4</v>
@@ -3391,103 +3400,103 @@
         <v>10</v>
       </c>
       <c r="AV11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11">
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY11">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11">
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB11">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BC11">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BD11">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE11">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF11">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG11">
         <v>5.1</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3495,79 +3504,79 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F12">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H12">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="I12">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T12">
         <v>1.6</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X12">
         <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA12">
         <v>34</v>
@@ -3576,10 +3585,10 @@
         <v>16.5</v>
       </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE12">
         <v>23</v>
@@ -3588,31 +3597,31 @@
         <v>25</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12">
         <v>15</v>
       </c>
       <c r="AI12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ12">
         <v>55</v>
       </c>
       <c r="AK12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AM12">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="AN12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
@@ -3624,7 +3633,7 @@
         <v>15.5</v>
       </c>
       <c r="AS12">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AT12">
         <v>14.5</v>
@@ -3639,97 +3648,97 @@
         <v>20</v>
       </c>
       <c r="AX12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY12">
         <v>12.5</v>
       </c>
       <c r="AZ12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BB12">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BC12">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BD12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE12">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3737,241 +3746,241 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F13">
         <v>1.1</v>
       </c>
       <c r="G13">
-        <v>600</v>
+        <v>1.4</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="I13">
         <v>870</v>
       </c>
       <c r="J13">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="K13">
         <v>950</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q13">
         <v>1.01</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3979,232 +3988,232 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="G14">
-        <v>600</v>
+        <v>2.98</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="I14">
-        <v>870</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P14">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4213,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4221,241 +4230,241 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F15">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="G15">
-        <v>600</v>
+        <v>3.75</v>
       </c>
       <c r="H15">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="I15">
-        <v>870</v>
+        <v>3</v>
       </c>
       <c r="J15">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4463,232 +4472,232 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F16">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="G16">
-        <v>600</v>
+        <v>2.54</v>
       </c>
       <c r="H16">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="I16">
-        <v>870</v>
+        <v>3.6</v>
       </c>
       <c r="J16">
-        <v>1.12</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4697,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4705,232 +4714,232 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F17">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>3.25</v>
       </c>
       <c r="H17">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="I17">
-        <v>870</v>
+        <v>3.25</v>
       </c>
       <c r="J17">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="K17">
         <v>950</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P17">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -4939,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4947,241 +4956,241 @@
         <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F18">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="G18">
-        <v>600</v>
+        <v>5.3</v>
       </c>
       <c r="H18">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="I18">
-        <v>870</v>
+        <v>2.02</v>
       </c>
       <c r="J18">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K18">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5189,22 +5198,22 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F19">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G19">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H19">
         <v>6.2</v>
@@ -5213,13 +5222,13 @@
         <v>6.4</v>
       </c>
       <c r="J19">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
         <v>3.9</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M19">
         <v>1.09</v>
@@ -5234,7 +5243,7 @@
         <v>1.75</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
         <v>1.27</v>
@@ -5249,22 +5258,22 @@
         <v>1.8</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y19">
         <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB19">
         <v>6.8</v>
@@ -5276,10 +5285,10 @@
         <v>25</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF19">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG19">
         <v>10.5</v>
@@ -5300,34 +5309,34 @@
         <v>48</v>
       </c>
       <c r="AM19">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AN19">
         <v>14</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR19">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AS19">
         <v>44</v>
       </c>
       <c r="AT19">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU19">
         <v>8</v>
       </c>
       <c r="AV19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW19">
         <v>38</v>
@@ -5336,10 +5345,10 @@
         <v>8.4</v>
       </c>
       <c r="AY19">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA19">
         <v>40</v>
@@ -5351,7 +5360,7 @@
         <v>18.5</v>
       </c>
       <c r="BD19">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE19">
         <v>46</v>
@@ -5360,25 +5369,25 @@
         <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH19">
         <v>3.2</v>
       </c>
       <c r="BI19">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>2.48</v>
+        <v>34</v>
       </c>
       <c r="BN19">
         <v>4.8</v>
@@ -5390,40 +5399,40 @@
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>2.48</v>
+        <v>13</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>2.48</v>
+        <v>15.5</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>2.48</v>
+        <v>18</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>2.48</v>
+        <v>10.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5431,16 +5440,16 @@
         <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F20">
         <v>7.6</v>
@@ -5449,16 +5458,16 @@
         <v>12.5</v>
       </c>
       <c r="H20">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="I20">
         <v>1.63</v>
       </c>
       <c r="J20">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K20">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.42</v>
@@ -5473,7 +5482,7 @@
         <v>1.47</v>
       </c>
       <c r="P20">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q20">
         <v>2.28</v>
@@ -5485,10 +5494,10 @@
         <v>3.75</v>
       </c>
       <c r="T20">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="U20">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V20">
         <v>2.58</v>
@@ -5557,7 +5566,7 @@
         <v>4.9</v>
       </c>
       <c r="AR20">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS20">
         <v>10</v>
@@ -5614,7 +5623,7 @@
         <v>16.5</v>
       </c>
       <c r="BK20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BL20">
         <v>1000</v>
@@ -5623,16 +5632,16 @@
         <v>5</v>
       </c>
       <c r="BN20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BO20">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR20">
         <v>1000</v>
@@ -5644,13 +5653,13 @@
         <v>4.3</v>
       </c>
       <c r="BU20">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BV20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BW20">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BX20">
         <v>44</v>
@@ -5659,255 +5668,255 @@
         <v>4.5</v>
       </c>
       <c r="BZ20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA20">
         <v>4.4</v>
       </c>
       <c r="CB20" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F21">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="G21">
-        <v>600</v>
+        <v>1.48</v>
       </c>
       <c r="H21">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I21">
         <v>870</v>
       </c>
       <c r="J21">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P21">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5915,232 +5924,232 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F22">
-        <v>1.1</v>
+        <v>2.98</v>
       </c>
       <c r="G22">
-        <v>600</v>
+        <v>5.2</v>
       </c>
       <c r="H22">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="I22">
-        <v>870</v>
+        <v>2.18</v>
       </c>
       <c r="J22">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P22">
+        <v>2.02</v>
+      </c>
+      <c r="Q22">
+        <v>1.5</v>
+      </c>
+      <c r="R22">
+        <v>1.41</v>
+      </c>
+      <c r="S22">
+        <v>2.22</v>
+      </c>
+      <c r="T22">
+        <v>1.01</v>
+      </c>
+      <c r="U22">
+        <v>1.01</v>
+      </c>
+      <c r="V22">
+        <v>1.84</v>
+      </c>
+      <c r="W22">
         <v>1.24</v>
       </c>
-      <c r="Q22">
-        <v>1.01</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6149,249 +6158,249 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
         <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F23">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="G23">
-        <v>1.45</v>
+        <v>600</v>
       </c>
       <c r="H23">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="I23">
-        <v>8.800000000000001</v>
+        <v>870</v>
       </c>
       <c r="J23">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="K23">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>5.1</v>
+        <v>1.24</v>
       </c>
       <c r="O23">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P23">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q23">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R23">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="S23">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="T23">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
         <v>1000</v>
       </c>
       <c r="AF23">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6399,64 +6408,64 @@
         <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F24">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="G24">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="H24">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="I24">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P24">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T24">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="U24">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -6465,175 +6474,175 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y24">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Z24">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AA24">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD24">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AE24">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI24">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ24">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AK24">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL24">
         <v>36</v>
       </c>
       <c r="AM24">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO24">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ24">
+        <v>19</v>
+      </c>
+      <c r="AR24">
+        <v>32</v>
+      </c>
+      <c r="AS24">
+        <v>100</v>
+      </c>
+      <c r="AT24">
+        <v>9</v>
+      </c>
+      <c r="AU24">
+        <v>10.5</v>
+      </c>
+      <c r="AV24">
+        <v>24</v>
+      </c>
+      <c r="AW24">
+        <v>40</v>
+      </c>
+      <c r="AX24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY24">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24">
         <v>21</v>
       </c>
-      <c r="AR24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS24">
-        <v>9</v>
-      </c>
-      <c r="AT24">
-        <v>9.6</v>
-      </c>
-      <c r="AU24">
-        <v>9.6</v>
-      </c>
-      <c r="AV24">
-        <v>20</v>
-      </c>
-      <c r="AW24">
-        <v>8.6</v>
-      </c>
-      <c r="AX24">
+      <c r="BA24">
+        <v>60</v>
+      </c>
+      <c r="BB24">
+        <v>11</v>
+      </c>
+      <c r="BC24">
+        <v>12.5</v>
+      </c>
+      <c r="BD24">
+        <v>22</v>
+      </c>
+      <c r="BE24">
+        <v>70</v>
+      </c>
+      <c r="BF24">
+        <v>5.3</v>
+      </c>
+      <c r="BG24">
+        <v>42</v>
+      </c>
+      <c r="BH24">
+        <v>4.2</v>
+      </c>
+      <c r="BI24">
+        <v>3.7</v>
+      </c>
+      <c r="BJ24">
+        <v>12.5</v>
+      </c>
+      <c r="BK24">
+        <v>4.9</v>
+      </c>
+      <c r="BL24">
+        <v>150</v>
+      </c>
+      <c r="BM24">
+        <v>7.4</v>
+      </c>
+      <c r="BN24">
+        <v>4.1</v>
+      </c>
+      <c r="BO24">
+        <v>3.6</v>
+      </c>
+      <c r="BP24">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ24">
-        <v>17.5</v>
-      </c>
-      <c r="BA24">
-        <v>8.6</v>
-      </c>
-      <c r="BB24">
+      <c r="BQ24">
+        <v>7.4</v>
+      </c>
+      <c r="BR24">
+        <v>26</v>
+      </c>
+      <c r="BS24">
+        <v>6</v>
+      </c>
+      <c r="BT24">
         <v>13.5</v>
       </c>
-      <c r="BC24">
-        <v>14</v>
-      </c>
-      <c r="BD24">
-        <v>7.4</v>
-      </c>
-      <c r="BE24">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF24">
-        <v>6</v>
-      </c>
-      <c r="BG24">
-        <v>8.6</v>
-      </c>
-      <c r="BH24">
-        <v>0</v>
-      </c>
-      <c r="BI24">
-        <v>0</v>
-      </c>
-      <c r="BJ24">
-        <v>0</v>
-      </c>
-      <c r="BK24">
-        <v>0</v>
-      </c>
-      <c r="BL24">
-        <v>0</v>
-      </c>
-      <c r="BM24">
-        <v>0</v>
-      </c>
-      <c r="BN24">
-        <v>0</v>
-      </c>
-      <c r="BO24">
-        <v>0</v>
-      </c>
-      <c r="BP24">
-        <v>0</v>
-      </c>
-      <c r="BQ24">
-        <v>0</v>
-      </c>
-      <c r="BR24">
-        <v>0</v>
-      </c>
-      <c r="BS24">
-        <v>0</v>
-      </c>
-      <c r="BT24">
-        <v>0</v>
-      </c>
       <c r="BU24">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="CB24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6641,178 +6650,178 @@
         <v>87</v>
       </c>
       <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25">
+        <v>1.57</v>
+      </c>
+      <c r="G25">
+        <v>1.63</v>
+      </c>
+      <c r="H25">
+        <v>5.9</v>
+      </c>
+      <c r="I25">
+        <v>6.4</v>
+      </c>
+      <c r="J25">
+        <v>4.6</v>
+      </c>
+      <c r="K25">
+        <v>4.9</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>2.4</v>
+      </c>
+      <c r="Q25">
+        <v>1.65</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1.77</v>
+      </c>
+      <c r="U25">
+        <v>2.18</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>28</v>
+      </c>
+      <c r="Y25">
+        <v>26</v>
+      </c>
+      <c r="Z25">
+        <v>65</v>
+      </c>
+      <c r="AA25">
+        <v>190</v>
+      </c>
+      <c r="AB25">
+        <v>11</v>
+      </c>
+      <c r="AC25">
+        <v>11</v>
+      </c>
+      <c r="AD25">
+        <v>24</v>
+      </c>
+      <c r="AE25">
         <v>90</v>
       </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" t="s">
-        <v>153</v>
-      </c>
-      <c r="F25">
-        <v>1.85</v>
-      </c>
-      <c r="G25">
-        <v>1.86</v>
-      </c>
-      <c r="H25">
-        <v>4.6</v>
-      </c>
-      <c r="I25">
-        <v>4.7</v>
-      </c>
-      <c r="J25">
-        <v>4.1</v>
-      </c>
-      <c r="K25">
-        <v>4.2</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>2.48</v>
-      </c>
-      <c r="Q25">
-        <v>1.64</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>1.64</v>
-      </c>
-      <c r="U25">
-        <v>2.48</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>24</v>
-      </c>
-      <c r="Y25">
-        <v>23</v>
-      </c>
-      <c r="Z25">
-        <v>40</v>
-      </c>
-      <c r="AA25">
-        <v>1000</v>
-      </c>
-      <c r="AB25">
-        <v>13</v>
-      </c>
-      <c r="AC25">
-        <v>9.6</v>
-      </c>
-      <c r="AD25">
-        <v>19</v>
-      </c>
-      <c r="AE25">
-        <v>50</v>
-      </c>
       <c r="AF25">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG25">
         <v>10.5</v>
       </c>
       <c r="AH25">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI25">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AJ25">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AK25">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL25">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN25">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO25">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AP25">
         <v>20</v>
       </c>
       <c r="AQ25">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AR25">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS25">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="AT25">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AU25">
+        <v>9.6</v>
+      </c>
+      <c r="AV25">
+        <v>20</v>
+      </c>
+      <c r="AW25">
+        <v>8.6</v>
+      </c>
+      <c r="AX25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25">
+        <v>17.5</v>
+      </c>
+      <c r="BA25">
+        <v>8.6</v>
+      </c>
+      <c r="BB25">
+        <v>13.5</v>
+      </c>
+      <c r="BC25">
+        <v>14</v>
+      </c>
+      <c r="BD25">
+        <v>7.4</v>
+      </c>
+      <c r="BE25">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV25">
-        <v>16</v>
-      </c>
-      <c r="AW25">
-        <v>26</v>
-      </c>
-      <c r="AX25">
-        <v>11.5</v>
-      </c>
-      <c r="AY25">
-        <v>9.6</v>
-      </c>
-      <c r="AZ25">
-        <v>14.5</v>
-      </c>
-      <c r="BA25">
-        <v>36</v>
-      </c>
-      <c r="BB25">
-        <v>17.5</v>
-      </c>
-      <c r="BC25">
-        <v>14.5</v>
-      </c>
-      <c r="BD25">
-        <v>20</v>
-      </c>
-      <c r="BE25">
-        <v>44</v>
-      </c>
       <c r="BF25">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BG25">
-        <v>24</v>
+        <v>8.6</v>
       </c>
       <c r="BH25">
         <v>0</v>
@@ -6875,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6883,241 +6892,241 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F26">
-        <v>1.26</v>
+        <v>1.81</v>
       </c>
       <c r="G26">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="H26">
+        <v>4.6</v>
+      </c>
+      <c r="I26">
+        <v>4.7</v>
+      </c>
+      <c r="J26">
+        <v>4.2</v>
+      </c>
+      <c r="K26">
+        <v>4.3</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>2.48</v>
+      </c>
+      <c r="Q26">
+        <v>1.64</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>1.64</v>
+      </c>
+      <c r="U26">
+        <v>2.44</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>24</v>
+      </c>
+      <c r="Y26">
+        <v>23</v>
+      </c>
+      <c r="Z26">
+        <v>40</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
         <v>13</v>
       </c>
-      <c r="I26">
-        <v>15</v>
-      </c>
-      <c r="J26">
-        <v>6.8</v>
-      </c>
-      <c r="K26">
-        <v>7.4</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>1.03</v>
-      </c>
-      <c r="N26">
-        <v>6.4</v>
-      </c>
-      <c r="O26">
-        <v>1.16</v>
-      </c>
-      <c r="P26">
-        <v>2.86</v>
-      </c>
-      <c r="Q26">
-        <v>1.49</v>
-      </c>
-      <c r="R26">
-        <v>1.75</v>
-      </c>
-      <c r="S26">
-        <v>2.22</v>
-      </c>
-      <c r="T26">
-        <v>2.06</v>
-      </c>
-      <c r="U26">
-        <v>1.88</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>34</v>
-      </c>
-      <c r="Y26">
+      <c r="AC26">
+        <v>9.6</v>
+      </c>
+      <c r="AD26">
+        <v>19</v>
+      </c>
+      <c r="AE26">
         <v>55</v>
       </c>
-      <c r="Z26">
-        <v>1000</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>12</v>
-      </c>
-      <c r="AC26">
-        <v>16.5</v>
-      </c>
-      <c r="AD26">
-        <v>55</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
       <c r="AF26">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AG26">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ26">
-        <v>9.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="AK26">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AL26">
+        <v>29</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>8</v>
+      </c>
+      <c r="AO26">
         <v>40</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>3.7</v>
-      </c>
-      <c r="AO26">
-        <v>1000</v>
       </c>
       <c r="AP26">
         <v>21</v>
       </c>
       <c r="AQ26">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AR26">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AS26">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AT26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU26">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AW26">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AX26">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AY26">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BA26">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BB26">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="BC26">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BD26">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BE26">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BF26">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BG26">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="BH26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BI26">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BJ26">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK26">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL26">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM26">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN26">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BO26">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BP26">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BQ26">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BR26">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS26">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BT26">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BU26">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BV26">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BW26">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX26">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BY26">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ26">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CA26">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7125,241 +7134,241 @@
         <v>87</v>
       </c>
       <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27">
+        <v>1.25</v>
+      </c>
+      <c r="G27">
+        <v>1.27</v>
+      </c>
+      <c r="H27">
+        <v>13</v>
+      </c>
+      <c r="I27">
+        <v>15.5</v>
+      </c>
+      <c r="J27">
+        <v>7</v>
+      </c>
+      <c r="K27">
+        <v>7.6</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1.02</v>
+      </c>
+      <c r="N27">
+        <v>6.6</v>
+      </c>
+      <c r="O27">
+        <v>1.16</v>
+      </c>
+      <c r="P27">
+        <v>2.86</v>
+      </c>
+      <c r="Q27">
+        <v>1.49</v>
+      </c>
+      <c r="R27">
+        <v>1.75</v>
+      </c>
+      <c r="S27">
+        <v>2.18</v>
+      </c>
+      <c r="T27">
+        <v>2.04</v>
+      </c>
+      <c r="U27">
+        <v>1.89</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>34</v>
+      </c>
+      <c r="Y27">
+        <v>55</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>12</v>
+      </c>
+      <c r="AC27">
+        <v>17</v>
+      </c>
+      <c r="AD27">
+        <v>55</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG27">
+        <v>12.5</v>
+      </c>
+      <c r="AH27">
+        <v>36</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK27">
+        <v>14.5</v>
+      </c>
+      <c r="AL27">
+        <v>40</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>3.65</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>27</v>
+      </c>
+      <c r="AQ27">
+        <v>26</v>
+      </c>
+      <c r="AR27">
+        <v>42</v>
+      </c>
+      <c r="AS27">
+        <v>110</v>
+      </c>
+      <c r="AT27">
+        <v>10.5</v>
+      </c>
+      <c r="AU27">
+        <v>14</v>
+      </c>
+      <c r="AV27">
+        <v>40</v>
+      </c>
+      <c r="AW27">
+        <v>48</v>
+      </c>
+      <c r="AX27">
+        <v>8</v>
+      </c>
+      <c r="AY27">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27">
+        <v>21</v>
+      </c>
+      <c r="BA27">
+        <v>44</v>
+      </c>
+      <c r="BB27">
+        <v>8.6</v>
+      </c>
+      <c r="BC27">
+        <v>12</v>
+      </c>
+      <c r="BD27">
+        <v>27</v>
+      </c>
+      <c r="BE27">
+        <v>44</v>
+      </c>
+      <c r="BF27">
+        <v>3.45</v>
+      </c>
+      <c r="BG27">
+        <v>50</v>
+      </c>
+      <c r="BH27">
+        <v>5</v>
+      </c>
+      <c r="BI27">
+        <v>4.3</v>
+      </c>
+      <c r="BJ27">
+        <v>13</v>
+      </c>
+      <c r="BK27">
+        <v>6.2</v>
+      </c>
+      <c r="BL27">
+        <v>150</v>
+      </c>
+      <c r="BM27">
+        <v>10.5</v>
+      </c>
+      <c r="BN27">
+        <v>3.95</v>
+      </c>
+      <c r="BO27">
+        <v>3.45</v>
+      </c>
+      <c r="BP27">
+        <v>7</v>
+      </c>
+      <c r="BQ27">
+        <v>5.8</v>
+      </c>
+      <c r="BR27">
+        <v>22</v>
+      </c>
+      <c r="BS27">
+        <v>7.6</v>
+      </c>
+      <c r="BT27">
+        <v>17</v>
+      </c>
+      <c r="BU27">
+        <v>6.8</v>
+      </c>
+      <c r="BV27">
+        <v>120</v>
+      </c>
+      <c r="BW27">
+        <v>10.5</v>
+      </c>
+      <c r="BX27">
         <v>90</v>
       </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>155</v>
-      </c>
-      <c r="F27">
-        <v>1.76</v>
-      </c>
-      <c r="G27">
-        <v>1.78</v>
-      </c>
-      <c r="H27">
+      <c r="BY27">
+        <v>10</v>
+      </c>
+      <c r="BZ27">
+        <v>9</v>
+      </c>
+      <c r="CA27">
         <v>5.1</v>
       </c>
-      <c r="I27">
-        <v>5.3</v>
-      </c>
-      <c r="J27">
-        <v>4.1</v>
-      </c>
-      <c r="K27">
-        <v>4.3</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>1.04</v>
-      </c>
-      <c r="N27">
-        <v>5.7</v>
-      </c>
-      <c r="O27">
-        <v>1.2</v>
-      </c>
-      <c r="P27">
-        <v>2.58</v>
-      </c>
-      <c r="Q27">
-        <v>1.59</v>
-      </c>
-      <c r="R27">
-        <v>1.64</v>
-      </c>
-      <c r="S27">
-        <v>2.46</v>
-      </c>
-      <c r="T27">
-        <v>1.6</v>
-      </c>
-      <c r="U27">
-        <v>2.56</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>25</v>
-      </c>
-      <c r="Y27">
-        <v>26</v>
-      </c>
-      <c r="Z27">
-        <v>48</v>
-      </c>
-      <c r="AA27">
-        <v>1000</v>
-      </c>
-      <c r="AB27">
-        <v>13</v>
-      </c>
-      <c r="AC27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD27">
-        <v>21</v>
-      </c>
-      <c r="AE27">
-        <v>60</v>
-      </c>
-      <c r="AF27">
-        <v>14</v>
-      </c>
-      <c r="AG27">
-        <v>10.5</v>
-      </c>
-      <c r="AH27">
-        <v>16</v>
-      </c>
-      <c r="AI27">
-        <v>55</v>
-      </c>
-      <c r="AJ27">
-        <v>19.5</v>
-      </c>
-      <c r="AK27">
-        <v>16.5</v>
-      </c>
-      <c r="AL27">
-        <v>26</v>
-      </c>
-      <c r="AM27">
-        <v>70</v>
-      </c>
-      <c r="AN27">
-        <v>7.4</v>
-      </c>
-      <c r="AO27">
-        <v>44</v>
-      </c>
-      <c r="AP27">
-        <v>21</v>
-      </c>
-      <c r="AQ27">
-        <v>21</v>
-      </c>
-      <c r="AR27">
-        <v>25</v>
-      </c>
-      <c r="AS27">
-        <v>40</v>
-      </c>
-      <c r="AT27">
-        <v>11</v>
-      </c>
-      <c r="AU27">
-        <v>9</v>
-      </c>
-      <c r="AV27">
-        <v>17.5</v>
-      </c>
-      <c r="AW27">
-        <v>28</v>
-      </c>
-      <c r="AX27">
-        <v>12</v>
-      </c>
-      <c r="AY27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ27">
-        <v>13.5</v>
-      </c>
-      <c r="BA27">
-        <v>27</v>
-      </c>
-      <c r="BB27">
-        <v>17</v>
-      </c>
-      <c r="BC27">
-        <v>14.5</v>
-      </c>
-      <c r="BD27">
-        <v>21</v>
-      </c>
-      <c r="BE27">
-        <v>30</v>
-      </c>
-      <c r="BF27">
-        <v>7</v>
-      </c>
-      <c r="BG27">
-        <v>25</v>
-      </c>
-      <c r="BH27">
-        <v>1000</v>
-      </c>
-      <c r="BI27">
-        <v>1.5</v>
-      </c>
-      <c r="BJ27">
-        <v>1000</v>
-      </c>
-      <c r="BK27">
-        <v>1.84</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>2.14</v>
-      </c>
-      <c r="BN27">
-        <v>1000</v>
-      </c>
-      <c r="BO27">
-        <v>1.56</v>
-      </c>
-      <c r="BP27">
-        <v>1000</v>
-      </c>
-      <c r="BQ27">
-        <v>2.14</v>
-      </c>
-      <c r="BR27">
-        <v>1000</v>
-      </c>
-      <c r="BS27">
-        <v>2.14</v>
-      </c>
-      <c r="BT27">
-        <v>1000</v>
-      </c>
-      <c r="BU27">
-        <v>1.84</v>
-      </c>
-      <c r="BV27">
-        <v>1000</v>
-      </c>
-      <c r="BW27">
-        <v>2.14</v>
-      </c>
-      <c r="BX27">
-        <v>1000</v>
-      </c>
-      <c r="BY27">
-        <v>2.14</v>
-      </c>
-      <c r="BZ27">
-        <v>1000</v>
-      </c>
-      <c r="CA27">
-        <v>2.14</v>
-      </c>
       <c r="CB27" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7367,64 +7376,64 @@
         <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F28">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
       <c r="G28">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="H28">
+        <v>5.1</v>
+      </c>
+      <c r="I28">
+        <v>5.3</v>
+      </c>
+      <c r="J28">
+        <v>4.1</v>
+      </c>
+      <c r="K28">
+        <v>4.3</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1.04</v>
+      </c>
+      <c r="N28">
+        <v>5.7</v>
+      </c>
+      <c r="O28">
+        <v>1.2</v>
+      </c>
+      <c r="P28">
+        <v>2.58</v>
+      </c>
+      <c r="Q28">
+        <v>1.59</v>
+      </c>
+      <c r="R28">
+        <v>1.64</v>
+      </c>
+      <c r="S28">
         <v>2.46</v>
       </c>
-      <c r="I28">
-        <v>2.5</v>
-      </c>
-      <c r="J28">
-        <v>3.65</v>
-      </c>
-      <c r="K28">
-        <v>3.7</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>1.05</v>
-      </c>
-      <c r="N28">
-        <v>4.6</v>
-      </c>
-      <c r="O28">
-        <v>1.25</v>
-      </c>
-      <c r="P28">
-        <v>2.26</v>
-      </c>
-      <c r="Q28">
-        <v>1.77</v>
-      </c>
-      <c r="R28">
-        <v>1.48</v>
-      </c>
-      <c r="S28">
-        <v>2.92</v>
-      </c>
       <c r="T28">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U28">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -7433,175 +7442,175 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Y28">
+        <v>26</v>
+      </c>
+      <c r="Z28">
+        <v>46</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
         <v>13</v>
       </c>
-      <c r="Z28">
+      <c r="AC28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD28">
+        <v>21</v>
+      </c>
+      <c r="AE28">
+        <v>260</v>
+      </c>
+      <c r="AF28">
+        <v>14</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+      <c r="AH28">
+        <v>16</v>
+      </c>
+      <c r="AI28">
+        <v>55</v>
+      </c>
+      <c r="AJ28">
+        <v>20</v>
+      </c>
+      <c r="AK28">
+        <v>16.5</v>
+      </c>
+      <c r="AL28">
+        <v>26</v>
+      </c>
+      <c r="AM28">
+        <v>70</v>
+      </c>
+      <c r="AN28">
+        <v>7.4</v>
+      </c>
+      <c r="AO28">
+        <v>44</v>
+      </c>
+      <c r="AP28">
+        <v>22</v>
+      </c>
+      <c r="AQ28">
+        <v>21</v>
+      </c>
+      <c r="AR28">
+        <v>25</v>
+      </c>
+      <c r="AS28">
+        <v>40</v>
+      </c>
+      <c r="AT28">
+        <v>11</v>
+      </c>
+      <c r="AU28">
+        <v>9</v>
+      </c>
+      <c r="AV28">
         <v>17.5</v>
       </c>
-      <c r="AA28">
-        <v>34</v>
-      </c>
-      <c r="AB28">
-        <v>15.5</v>
-      </c>
-      <c r="AC28">
-        <v>8.4</v>
-      </c>
-      <c r="AD28">
-        <v>11.5</v>
-      </c>
-      <c r="AE28">
+      <c r="AW28">
+        <v>28</v>
+      </c>
+      <c r="AX28">
+        <v>12</v>
+      </c>
+      <c r="AY28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28">
+        <v>13.5</v>
+      </c>
+      <c r="BA28">
+        <v>27</v>
+      </c>
+      <c r="BB28">
+        <v>17</v>
+      </c>
+      <c r="BC28">
+        <v>14.5</v>
+      </c>
+      <c r="BD28">
+        <v>22</v>
+      </c>
+      <c r="BE28">
+        <v>40</v>
+      </c>
+      <c r="BF28">
+        <v>7</v>
+      </c>
+      <c r="BG28">
         <v>25</v>
       </c>
-      <c r="AF28">
-        <v>23</v>
-      </c>
-      <c r="AG28">
-        <v>13.5</v>
-      </c>
-      <c r="AH28">
-        <v>14</v>
-      </c>
-      <c r="AI28">
-        <v>34</v>
-      </c>
-      <c r="AJ28">
-        <v>80</v>
-      </c>
-      <c r="AK28">
-        <v>34</v>
-      </c>
-      <c r="AL28">
-        <v>40</v>
-      </c>
-      <c r="AM28">
-        <v>1000</v>
-      </c>
-      <c r="AN28">
-        <v>29</v>
-      </c>
-      <c r="AO28">
-        <v>16.5</v>
-      </c>
-      <c r="AP28">
-        <v>16.5</v>
-      </c>
-      <c r="AQ28">
-        <v>11.5</v>
-      </c>
-      <c r="AR28">
-        <v>15</v>
-      </c>
-      <c r="AS28">
-        <v>21</v>
-      </c>
-      <c r="AT28">
-        <v>13.5</v>
-      </c>
-      <c r="AU28">
-        <v>7.6</v>
-      </c>
-      <c r="AV28">
-        <v>10.5</v>
-      </c>
-      <c r="AW28">
-        <v>21</v>
-      </c>
-      <c r="AX28">
-        <v>20</v>
-      </c>
-      <c r="AY28">
-        <v>11.5</v>
-      </c>
-      <c r="AZ28">
-        <v>13</v>
-      </c>
-      <c r="BA28">
-        <v>21</v>
-      </c>
-      <c r="BB28">
-        <v>26</v>
-      </c>
-      <c r="BC28">
-        <v>19</v>
-      </c>
-      <c r="BD28">
-        <v>28</v>
-      </c>
-      <c r="BE28">
-        <v>32</v>
-      </c>
-      <c r="BF28">
-        <v>20</v>
-      </c>
-      <c r="BG28">
-        <v>14.5</v>
-      </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="CB28" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7609,64 +7618,64 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F29">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="H29">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="I29">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="J29">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K29">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P29">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="Q29">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T29">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U29">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -7675,76 +7684,76 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y29">
         <v>13</v>
       </c>
       <c r="Z29">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA29">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB29">
+        <v>15</v>
+      </c>
+      <c r="AC29">
+        <v>8.4</v>
+      </c>
+      <c r="AD29">
+        <v>11.5</v>
+      </c>
+      <c r="AE29">
+        <v>25</v>
+      </c>
+      <c r="AF29">
+        <v>23</v>
+      </c>
+      <c r="AG29">
         <v>13.5</v>
       </c>
-      <c r="AC29">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD29">
-        <v>12.5</v>
-      </c>
-      <c r="AE29">
-        <v>28</v>
-      </c>
-      <c r="AF29">
-        <v>21</v>
-      </c>
-      <c r="AG29">
-        <v>13</v>
-      </c>
       <c r="AH29">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AI29">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ29">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AK29">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL29">
         <v>40</v>
       </c>
       <c r="AM29">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO29">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AP29">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS29">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AT29">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU29">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV29">
         <v>10.5</v>
@@ -7753,162 +7762,162 @@
         <v>21</v>
       </c>
       <c r="AX29">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY29">
         <v>11.5</v>
       </c>
       <c r="AZ29">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC29">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD29">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG29">
+        <v>15</v>
+      </c>
+      <c r="BH29">
+        <v>3.85</v>
+      </c>
+      <c r="BI29">
+        <v>3.15</v>
+      </c>
+      <c r="BJ29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK29">
+        <v>5.8</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>13.5</v>
+      </c>
+      <c r="BN29">
+        <v>6.4</v>
+      </c>
+      <c r="BO29">
+        <v>5.6</v>
+      </c>
+      <c r="BP29">
+        <v>21</v>
+      </c>
+      <c r="BQ29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR29">
+        <v>30</v>
+      </c>
+      <c r="BS29">
+        <v>10.5</v>
+      </c>
+      <c r="BT29">
+        <v>5.7</v>
+      </c>
+      <c r="BU29">
+        <v>5.1</v>
+      </c>
+      <c r="BV29">
         <v>17.5</v>
       </c>
-      <c r="BH29">
-        <v>0</v>
-      </c>
-      <c r="BI29">
-        <v>0</v>
-      </c>
-      <c r="BJ29">
-        <v>0</v>
-      </c>
-      <c r="BK29">
-        <v>0</v>
-      </c>
-      <c r="BL29">
-        <v>0</v>
-      </c>
-      <c r="BM29">
-        <v>0</v>
-      </c>
-      <c r="BN29">
-        <v>0</v>
-      </c>
-      <c r="BO29">
-        <v>0</v>
-      </c>
-      <c r="BP29">
-        <v>0</v>
-      </c>
-      <c r="BQ29">
-        <v>0</v>
-      </c>
-      <c r="BR29">
-        <v>0</v>
-      </c>
-      <c r="BS29">
-        <v>0</v>
-      </c>
-      <c r="BT29">
-        <v>0</v>
-      </c>
-      <c r="BU29">
-        <v>0</v>
-      </c>
-      <c r="BV29">
-        <v>0</v>
-      </c>
       <c r="BW29">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB29" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F30">
-        <v>3.75</v>
+        <v>2.86</v>
       </c>
       <c r="G30">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="H30">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="I30">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K30">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="R30">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U30">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -7917,97 +7926,97 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y30">
         <v>13</v>
       </c>
       <c r="Z30">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AA30">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AB30">
+        <v>13.5</v>
+      </c>
+      <c r="AC30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD30">
+        <v>12.5</v>
+      </c>
+      <c r="AE30">
+        <v>28</v>
+      </c>
+      <c r="AF30">
+        <v>21</v>
+      </c>
+      <c r="AG30">
+        <v>13</v>
+      </c>
+      <c r="AH30">
+        <v>16.5</v>
+      </c>
+      <c r="AI30">
+        <v>38</v>
+      </c>
+      <c r="AJ30">
+        <v>44</v>
+      </c>
+      <c r="AK30">
+        <v>30</v>
+      </c>
+      <c r="AL30">
+        <v>38</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>20</v>
+      </c>
+      <c r="AO30">
+        <v>21</v>
+      </c>
+      <c r="AP30">
+        <v>15</v>
+      </c>
+      <c r="AQ30">
+        <v>11</v>
+      </c>
+      <c r="AR30">
+        <v>16</v>
+      </c>
+      <c r="AS30">
+        <v>32</v>
+      </c>
+      <c r="AT30">
+        <v>12</v>
+      </c>
+      <c r="AU30">
+        <v>7.4</v>
+      </c>
+      <c r="AV30">
+        <v>10.5</v>
+      </c>
+      <c r="AW30">
         <v>19</v>
       </c>
-      <c r="AC30">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD30">
-        <v>11</v>
-      </c>
-      <c r="AE30">
-        <v>18.5</v>
-      </c>
-      <c r="AF30">
-        <v>32</v>
-      </c>
-      <c r="AG30">
-        <v>16</v>
-      </c>
-      <c r="AH30">
-        <v>15.5</v>
-      </c>
-      <c r="AI30">
-        <v>30</v>
-      </c>
-      <c r="AJ30">
-        <v>70</v>
-      </c>
-      <c r="AK30">
-        <v>40</v>
-      </c>
-      <c r="AL30">
-        <v>42</v>
-      </c>
-      <c r="AM30">
-        <v>70</v>
-      </c>
-      <c r="AN30">
-        <v>32</v>
-      </c>
-      <c r="AO30">
-        <v>10.5</v>
-      </c>
-      <c r="AP30">
-        <v>20</v>
-      </c>
-      <c r="AQ30">
-        <v>12</v>
-      </c>
-      <c r="AR30">
-        <v>13.5</v>
-      </c>
-      <c r="AS30">
-        <v>22</v>
-      </c>
-      <c r="AT30">
+      <c r="AX30">
         <v>17</v>
       </c>
-      <c r="AU30">
-        <v>8.4</v>
-      </c>
-      <c r="AV30">
-        <v>10</v>
-      </c>
-      <c r="AW30">
-        <v>17.5</v>
-      </c>
-      <c r="AX30">
-        <v>19.5</v>
-      </c>
       <c r="AY30">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BB30">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BC30">
         <v>23</v>
@@ -8016,76 +8025,318 @@
         <v>24</v>
       </c>
       <c r="BE30">
+        <v>34</v>
+      </c>
+      <c r="BF30">
+        <v>19</v>
+      </c>
+      <c r="BG30">
+        <v>17.5</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30">
+        <v>0</v>
+      </c>
+      <c r="BK30">
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <v>0</v>
+      </c>
+      <c r="BN30">
+        <v>0</v>
+      </c>
+      <c r="BO30">
+        <v>0</v>
+      </c>
+      <c r="BP30">
+        <v>0</v>
+      </c>
+      <c r="BQ30">
+        <v>0</v>
+      </c>
+      <c r="BR30">
+        <v>0</v>
+      </c>
+      <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
+        <v>0</v>
+      </c>
+      <c r="BU30">
+        <v>0</v>
+      </c>
+      <c r="BV30">
+        <v>0</v>
+      </c>
+      <c r="BW30">
+        <v>0</v>
+      </c>
+      <c r="BX30">
+        <v>0</v>
+      </c>
+      <c r="BY30">
+        <v>0</v>
+      </c>
+      <c r="BZ30">
+        <v>0</v>
+      </c>
+      <c r="CA30">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31">
+        <v>3.8</v>
+      </c>
+      <c r="G31">
+        <v>3.85</v>
+      </c>
+      <c r="H31">
+        <v>2.04</v>
+      </c>
+      <c r="I31">
+        <v>2.06</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31">
+        <v>4.1</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>1.04</v>
+      </c>
+      <c r="N31">
+        <v>5.2</v>
+      </c>
+      <c r="O31">
+        <v>1.22</v>
+      </c>
+      <c r="P31">
+        <v>2.42</v>
+      </c>
+      <c r="Q31">
+        <v>1.66</v>
+      </c>
+      <c r="R31">
+        <v>1.59</v>
+      </c>
+      <c r="S31">
+        <v>2.66</v>
+      </c>
+      <c r="T31">
+        <v>1.62</v>
+      </c>
+      <c r="U31">
+        <v>2.52</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>22</v>
+      </c>
+      <c r="Y31">
+        <v>13</v>
+      </c>
+      <c r="Z31">
+        <v>14.5</v>
+      </c>
+      <c r="AA31">
+        <v>25</v>
+      </c>
+      <c r="AB31">
+        <v>19</v>
+      </c>
+      <c r="AC31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD31">
+        <v>11</v>
+      </c>
+      <c r="AE31">
+        <v>18.5</v>
+      </c>
+      <c r="AF31">
         <v>32</v>
       </c>
-      <c r="BF30">
+      <c r="AG31">
+        <v>15.5</v>
+      </c>
+      <c r="AH31">
+        <v>15.5</v>
+      </c>
+      <c r="AI31">
+        <v>30</v>
+      </c>
+      <c r="AJ31">
+        <v>70</v>
+      </c>
+      <c r="AK31">
+        <v>38</v>
+      </c>
+      <c r="AL31">
+        <v>42</v>
+      </c>
+      <c r="AM31">
+        <v>65</v>
+      </c>
+      <c r="AN31">
+        <v>30</v>
+      </c>
+      <c r="AO31">
+        <v>10.5</v>
+      </c>
+      <c r="AP31">
+        <v>20</v>
+      </c>
+      <c r="AQ31">
+        <v>12</v>
+      </c>
+      <c r="AR31">
+        <v>13.5</v>
+      </c>
+      <c r="AS31">
+        <v>22</v>
+      </c>
+      <c r="AT31">
+        <v>17</v>
+      </c>
+      <c r="AU31">
+        <v>8.6</v>
+      </c>
+      <c r="AV31">
+        <v>10</v>
+      </c>
+      <c r="AW31">
+        <v>17.5</v>
+      </c>
+      <c r="AX31">
+        <v>19.5</v>
+      </c>
+      <c r="AY31">
+        <v>14</v>
+      </c>
+      <c r="AZ31">
+        <v>14</v>
+      </c>
+      <c r="BA31">
+        <v>19</v>
+      </c>
+      <c r="BB31">
+        <v>32</v>
+      </c>
+      <c r="BC31">
+        <v>23</v>
+      </c>
+      <c r="BD31">
         <v>24</v>
       </c>
-      <c r="BG30">
-        <v>9.4</v>
-      </c>
-      <c r="BH30">
+      <c r="BE31">
+        <v>32</v>
+      </c>
+      <c r="BF31">
+        <v>25</v>
+      </c>
+      <c r="BG31">
+        <v>9.6</v>
+      </c>
+      <c r="BH31">
         <v>4</v>
       </c>
-      <c r="BI30">
+      <c r="BI31">
         <v>3.65</v>
       </c>
-      <c r="BJ30">
+      <c r="BJ31">
         <v>11</v>
       </c>
-      <c r="BK30">
+      <c r="BK31">
         <v>7.8</v>
       </c>
-      <c r="BL30">
+      <c r="BL31">
         <v>110</v>
       </c>
-      <c r="BM30">
+      <c r="BM31">
         <v>7.8</v>
       </c>
-      <c r="BN30">
+      <c r="BN31">
         <v>7.2</v>
       </c>
-      <c r="BO30">
+      <c r="BO31">
         <v>6.6</v>
       </c>
-      <c r="BP30">
+      <c r="BP31">
         <v>34</v>
       </c>
-      <c r="BQ30">
+      <c r="BQ31">
         <v>6.6</v>
       </c>
-      <c r="BR30">
+      <c r="BR31">
         <v>40</v>
       </c>
-      <c r="BS30">
+      <c r="BS31">
         <v>6.8</v>
       </c>
-      <c r="BT30">
+      <c r="BT31">
         <v>5.1</v>
       </c>
-      <c r="BU30">
+      <c r="BU31">
         <v>4.6</v>
       </c>
-      <c r="BV30">
+      <c r="BV31">
         <v>16.5</v>
       </c>
-      <c r="BW30">
+      <c r="BW31">
         <v>5.7</v>
       </c>
-      <c r="BX30">
+      <c r="BX31">
         <v>29</v>
       </c>
-      <c r="BY30">
+      <c r="BY31">
         <v>6.4</v>
       </c>
-      <c r="BZ30">
+      <c r="BZ31">
         <v>21</v>
       </c>
-      <c r="CA30">
+      <c r="CA31">
         <v>6.2</v>
       </c>
-      <c r="CB30" t="s">
-        <v>159</v>
+      <c r="CB31" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="169">
   <si>
     <t>League</t>
   </si>
@@ -286,9 +286,15 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>South African Premier Division</t>
   </si>
   <si>
+    <t>English Sky Bet League 1</t>
+  </si>
+  <si>
     <t>2026-09-17</t>
   </si>
   <si>
@@ -379,6 +385,9 @@
     <t>ENPPI</t>
   </si>
   <si>
+    <t>US Biskra</t>
+  </si>
+  <si>
     <t>Orlando Pirates (SA)</t>
   </si>
   <si>
@@ -388,6 +397,9 @@
     <t>Assyriska FF</t>
   </si>
   <si>
+    <t>AFC Wimbledon</t>
+  </si>
+  <si>
     <t>Crystal Palace</t>
   </si>
   <si>
@@ -469,6 +481,9 @@
     <t>Pyramids</t>
   </si>
   <si>
+    <t>Belouizdad</t>
+  </si>
+  <si>
     <t>Durban City</t>
   </si>
   <si>
@@ -478,6 +493,9 @@
     <t>AFC Eskilstuna</t>
   </si>
   <si>
+    <t>MK Dons</t>
+  </si>
+  <si>
     <t>Lech Poznan</t>
   </si>
   <si>
@@ -502,7 +520,7 @@
     <t>Villarreal</t>
   </si>
   <si>
-    <t>2026-09-15 15:16:31</t>
+    <t>2026-09-15 17:30:29</t>
   </si>
 </sst>
 </file>
@@ -834,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB31"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1084,31 +1102,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F2">
         <v>1.12</v>
       </c>
       <c r="G2">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H2">
         <v>1.12</v>
       </c>
       <c r="I2">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="J2">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -1129,13 +1147,13 @@
         <v>1.29</v>
       </c>
       <c r="Q2">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="R2">
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="T2">
         <v>1.11</v>
@@ -1144,10 +1162,10 @@
         <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1261,64 +1279,64 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1326,16 +1344,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F3">
         <v>2.02</v>
@@ -1353,13 +1371,13 @@
         <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M3">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
         <v>2.44</v>
@@ -1368,22 +1386,22 @@
         <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V3">
         <v>1.23</v>
@@ -1395,31 +1413,31 @@
         <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA3">
         <v>160</v>
       </c>
       <c r="AB3">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE3">
         <v>110</v>
       </c>
       <c r="AF3">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AH3">
         <v>32</v>
@@ -1437,7 +1455,7 @@
         <v>75</v>
       </c>
       <c r="AM3">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN3">
         <v>32</v>
@@ -1446,121 +1464,121 @@
         <v>210</v>
       </c>
       <c r="AP3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>4.9</v>
       </c>
       <c r="AS3">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV3">
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AX3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY3">
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA3">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="BB3">
         <v>22</v>
       </c>
       <c r="BC3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="BF3">
         <v>25</v>
       </c>
       <c r="BG3">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="CB3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1568,28 +1586,28 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J4">
         <v>3.6</v>
@@ -1604,205 +1622,205 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.32</v>
       </c>
       <c r="P4">
+        <v>1.89</v>
+      </c>
+      <c r="Q4">
         <v>1.94</v>
       </c>
-      <c r="Q4">
-        <v>1.93</v>
-      </c>
       <c r="R4">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
         <v>1.82</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X4">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="Z4">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AP4">
-        <v>13</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>1.26</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>1.31</v>
       </c>
       <c r="AS4">
-        <v>20</v>
+        <v>1.38</v>
       </c>
       <c r="AT4">
-        <v>13.5</v>
+        <v>1.38</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AW4">
-        <v>17.5</v>
+        <v>1.38</v>
       </c>
       <c r="AX4">
-        <v>5</v>
+        <v>1.38</v>
       </c>
       <c r="AY4">
-        <v>15.5</v>
+        <v>1.38</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>1.38</v>
       </c>
       <c r="BA4">
-        <v>5</v>
+        <v>1.38</v>
       </c>
       <c r="BB4">
-        <v>5.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC4">
-        <v>5.2</v>
+        <v>1.38</v>
       </c>
       <c r="BD4">
-        <v>5.3</v>
+        <v>1.38</v>
       </c>
       <c r="BE4">
-        <v>5.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF4">
-        <v>5.3</v>
+        <v>1.38</v>
       </c>
       <c r="BG4">
-        <v>12.5</v>
+        <v>1.33</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1810,31 +1828,31 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G5">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
         <v>3.2</v>
@@ -1843,145 +1861,145 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N5">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="O5">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P5">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q5">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="R5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S5">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="T5">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U5">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="V5">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="X5">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="Y5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z5">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB5">
+        <v>6.4</v>
+      </c>
+      <c r="AC5">
+        <v>7.6</v>
+      </c>
+      <c r="AD5">
+        <v>23</v>
+      </c>
+      <c r="AE5">
+        <v>120</v>
+      </c>
+      <c r="AF5">
+        <v>12.5</v>
+      </c>
+      <c r="AG5">
+        <v>14</v>
+      </c>
+      <c r="AH5">
+        <v>32</v>
+      </c>
+      <c r="AI5">
+        <v>160</v>
+      </c>
+      <c r="AJ5">
+        <v>32</v>
+      </c>
+      <c r="AK5">
+        <v>36</v>
+      </c>
+      <c r="AL5">
+        <v>90</v>
+      </c>
+      <c r="AM5">
+        <v>330</v>
+      </c>
+      <c r="AN5">
+        <v>36</v>
+      </c>
+      <c r="AO5">
+        <v>220</v>
+      </c>
+      <c r="AP5">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR5">
+        <v>7.2</v>
+      </c>
+      <c r="AS5">
         <v>8</v>
       </c>
-      <c r="AC5">
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <v>950</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>13.5</v>
-      </c>
-      <c r="AG5">
-        <v>15.5</v>
-      </c>
-      <c r="AH5">
-        <v>950</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>40</v>
-      </c>
-      <c r="AK5">
-        <v>46</v>
-      </c>
-      <c r="AL5">
-        <v>100</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>48</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>5.3</v>
-      </c>
-      <c r="AQ5">
-        <v>7.6</v>
-      </c>
-      <c r="AR5">
-        <v>3.35</v>
-      </c>
-      <c r="AS5">
-        <v>3.6</v>
-      </c>
       <c r="AT5">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AU5">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX5">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="BA5">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="BC5">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="BD5">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2044,7 +2062,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2052,19 +2070,19 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G6">
         <v>3.05</v>
@@ -2076,7 +2094,7 @@
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2094,10 +2112,10 @@
         <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
         <v>1.08</v>
@@ -2112,10 +2130,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2286,7 +2304,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2294,16 +2312,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F7">
         <v>1.1</v>
@@ -2330,13 +2348,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
         <v>1.25</v>
@@ -2345,7 +2363,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2528,7 +2546,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2536,16 +2554,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F8">
         <v>1.1</v>
@@ -2560,7 +2578,7 @@
         <v>870</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2581,13 +2599,13 @@
         <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R8">
         <v>1.07</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2770,7 +2788,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2778,16 +2796,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F9">
         <v>2.68</v>
@@ -2796,7 +2814,7 @@
         <v>600</v>
       </c>
       <c r="H9">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
         <v>1.62</v>
@@ -2814,10 +2832,10 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
         <v>1.25</v>
@@ -2898,52 +2916,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3012,7 +3030,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3020,16 +3038,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -3056,7 +3074,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O10">
         <v>1.05</v>
@@ -3065,13 +3083,13 @@
         <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3080,10 +3098,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3140,52 +3158,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3254,7 +3272,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3262,16 +3280,16 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F11">
         <v>7.8</v>
@@ -3283,37 +3301,37 @@
         <v>1.45</v>
       </c>
       <c r="I11">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K11">
         <v>5.5</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q11">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S11">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="T11">
         <v>1.83</v>
@@ -3349,10 +3367,10 @@
         <v>10.5</v>
       </c>
       <c r="AE11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG11">
         <v>32</v>
@@ -3364,7 +3382,7 @@
         <v>36</v>
       </c>
       <c r="AJ11">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AK11">
         <v>130</v>
@@ -3385,7 +3403,7 @@
         <v>20</v>
       </c>
       <c r="AQ11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
         <v>8.4</v>
@@ -3400,103 +3418,103 @@
         <v>10</v>
       </c>
       <c r="AV11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW11">
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ11">
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD11">
         <v>10</v>
       </c>
       <c r="BE11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG11">
         <v>5.1</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO11">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BQ11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>17.5</v>
+        <v>46</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BU11">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BW11">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3504,19 +3522,19 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G12">
         <v>3.3</v>
@@ -3528,28 +3546,28 @@
         <v>2.36</v>
       </c>
       <c r="J12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
         <v>3.8</v>
       </c>
       <c r="L12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M12">
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R12">
         <v>1.53</v>
@@ -3558,19 +3576,19 @@
         <v>2.76</v>
       </c>
       <c r="T12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U12">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="W12">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="X12">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y12">
         <v>13.5</v>
@@ -3579,19 +3597,19 @@
         <v>17.5</v>
       </c>
       <c r="AA12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC12">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12">
         <v>11.5</v>
       </c>
       <c r="AE12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF12">
         <v>25</v>
@@ -3615,13 +3633,13 @@
         <v>38</v>
       </c>
       <c r="AM12">
-        <v>510</v>
+        <v>75</v>
       </c>
       <c r="AN12">
         <v>23</v>
       </c>
       <c r="AO12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
@@ -3642,16 +3660,16 @@
         <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW12">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AX12">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ12">
         <v>13.5</v>
@@ -3660,25 +3678,25 @@
         <v>27</v>
       </c>
       <c r="BB12">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BC12">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BD12">
         <v>32</v>
       </c>
       <c r="BE12">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BF12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG12">
         <v>12</v>
       </c>
       <c r="BH12">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
         <v>3.25</v>
@@ -3693,7 +3711,7 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
         <v>1000</v>
@@ -3705,13 +3723,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
         <v>1000</v>
@@ -3729,16 +3747,16 @@
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3746,31 +3764,31 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G13">
-        <v>1.4</v>
+        <v>600</v>
       </c>
       <c r="H13">
-        <v>7.8</v>
+        <v>1.12</v>
       </c>
       <c r="I13">
         <v>870</v>
       </c>
       <c r="J13">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3782,22 +3800,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="Q13">
         <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="S13">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3809,7 +3827,7 @@
         <v>1.01</v>
       </c>
       <c r="W13">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3980,7 +3998,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3988,34 +4006,34 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F14">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="G14">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="H14">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="J14">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4024,22 +4042,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O14">
         <v>1.01</v>
       </c>
       <c r="P14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R14">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S14">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4051,7 +4069,7 @@
         <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4108,52 +4126,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4222,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4230,34 +4248,34 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F15">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G15">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H15">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J15">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="K15">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4266,22 +4284,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="O15">
         <v>1.01</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q15">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R15">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="S15">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4290,10 +4308,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W15">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4350,52 +4368,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4464,7 +4482,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4472,25 +4490,25 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F16">
         <v>2.16</v>
       </c>
       <c r="G16">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H16">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I16">
         <v>3.6</v>
@@ -4508,19 +4526,19 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="P16">
         <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R16">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S16">
         <v>2.12</v>
@@ -4535,7 +4553,7 @@
         <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4706,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4714,31 +4732,31 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F17">
-        <v>2.24</v>
+        <v>1.1</v>
       </c>
       <c r="G17">
-        <v>3.25</v>
+        <v>600</v>
       </c>
       <c r="H17">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="I17">
-        <v>3.25</v>
+        <v>870</v>
       </c>
       <c r="J17">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4750,19 +4768,19 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="O17">
         <v>1.01</v>
       </c>
       <c r="P17">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q17">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="S17">
         <v>2.52</v>
@@ -4774,10 +4792,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4834,52 +4852,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4948,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4956,34 +4974,34 @@
         <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F18">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G18">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I18">
         <v>2.02</v>
       </c>
       <c r="J18">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K18">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4992,7 +5010,7 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O18">
         <v>1.01</v>
@@ -5001,13 +5019,13 @@
         <v>2.22</v>
       </c>
       <c r="Q18">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S18">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5016,10 +5034,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W18">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5190,7 +5208,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5198,25 +5216,25 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F19">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G19">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H19">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>6.4</v>
@@ -5228,13 +5246,13 @@
         <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M19">
         <v>1.09</v>
       </c>
       <c r="N19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
         <v>1.43</v>
@@ -5249,10 +5267,10 @@
         <v>1.27</v>
       </c>
       <c r="S19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
         <v>1.8</v>
@@ -5261,7 +5279,7 @@
         <v>1.18</v>
       </c>
       <c r="W19">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="X19">
         <v>11</v>
@@ -5276,13 +5294,13 @@
         <v>200</v>
       </c>
       <c r="AB19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>8.6</v>
       </c>
       <c r="AD19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE19">
         <v>110</v>
@@ -5306,10 +5324,10 @@
         <v>21</v>
       </c>
       <c r="AL19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM19">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN19">
         <v>14</v>
@@ -5330,7 +5348,7 @@
         <v>44</v>
       </c>
       <c r="AT19">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5348,7 +5366,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA19">
         <v>40</v>
@@ -5372,67 +5390,67 @@
         <v>44</v>
       </c>
       <c r="BH19">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI19">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM19">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="BN19">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BO19">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS19">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU19">
-        <v>2.44</v>
+        <v>8</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW19">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY19">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA19">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB19" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5440,40 +5458,40 @@
         <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F20">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G20">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="H20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I20">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="J20">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
         <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N20">
         <v>2.92</v>
@@ -5482,55 +5500,55 @@
         <v>1.47</v>
       </c>
       <c r="P20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q20">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R20">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S20">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="T20">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U20">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="V20">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA20">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AB20">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AC20">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD20">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE20">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG20">
         <v>950</v>
@@ -5539,142 +5557,142 @@
         <v>950</v>
       </c>
       <c r="AI20">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AO20">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AP20">
-        <v>2.2</v>
+        <v>9</v>
       </c>
       <c r="AQ20">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR20">
+        <v>6.6</v>
+      </c>
+      <c r="AS20">
+        <v>12</v>
+      </c>
+      <c r="AT20">
+        <v>17.5</v>
+      </c>
+      <c r="AU20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW20">
+        <v>18</v>
+      </c>
+      <c r="AX20">
+        <v>5.8</v>
+      </c>
+      <c r="AY20">
+        <v>5.5</v>
+      </c>
+      <c r="AZ20">
+        <v>5.4</v>
+      </c>
+      <c r="BA20">
+        <v>5.8</v>
+      </c>
+      <c r="BB20">
         <v>6</v>
       </c>
-      <c r="AS20">
-        <v>10</v>
-      </c>
-      <c r="AT20">
-        <v>15</v>
-      </c>
-      <c r="AU20">
-        <v>7.2</v>
-      </c>
-      <c r="AV20">
-        <v>8.6</v>
-      </c>
-      <c r="AW20">
-        <v>15</v>
-      </c>
-      <c r="AX20">
-        <v>2.58</v>
-      </c>
-      <c r="AY20">
-        <v>2.48</v>
-      </c>
-      <c r="AZ20">
-        <v>2.46</v>
-      </c>
-      <c r="BA20">
-        <v>2.52</v>
-      </c>
-      <c r="BB20">
-        <v>2.58</v>
-      </c>
       <c r="BC20">
-        <v>2.58</v>
+        <v>6</v>
       </c>
       <c r="BD20">
-        <v>2.58</v>
+        <v>6</v>
       </c>
       <c r="BE20">
-        <v>2.58</v>
+        <v>6</v>
       </c>
       <c r="BF20">
-        <v>2.58</v>
+        <v>6</v>
       </c>
       <c r="BG20">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH20">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.4</v>
+        <v>1.27</v>
       </c>
       <c r="BJ20">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>3.85</v>
+        <v>1.27</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="BN20">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.75</v>
+        <v>1.27</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>4.8</v>
+        <v>1.27</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="BT20">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>3.65</v>
+        <v>1.27</v>
       </c>
       <c r="BX20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>4.5</v>
+        <v>1.27</v>
       </c>
       <c r="BZ20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>4.4</v>
+        <v>1.27</v>
       </c>
       <c r="CB20" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5682,34 +5700,34 @@
         <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F21">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="G21">
-        <v>1.48</v>
+        <v>1000</v>
       </c>
       <c r="H21">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="I21">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J21">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="K21">
-        <v>8</v>
+        <v>950</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5718,22 +5736,22 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>2.8</v>
+        <v>1.08</v>
       </c>
       <c r="O21">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P21">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="Q21">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R21">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="S21">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5745,7 +5763,7 @@
         <v>1.01</v>
       </c>
       <c r="W21">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5802,52 +5820,52 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -5856,10 +5874,10 @@
         <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5916,42 +5934,42 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F22">
-        <v>2.98</v>
+        <v>1.35</v>
       </c>
       <c r="G22">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="H22">
-        <v>1.74</v>
+        <v>8.6</v>
       </c>
       <c r="I22">
-        <v>2.18</v>
+        <v>870</v>
       </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5960,22 +5978,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P22">
+        <v>1.54</v>
+      </c>
+      <c r="Q22">
         <v>2.02</v>
       </c>
-      <c r="Q22">
-        <v>1.5</v>
-      </c>
       <c r="R22">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="S22">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -5984,10 +6002,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="W22">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6044,52 +6062,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6152,13 +6170,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6166,31 +6184,31 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F23">
-        <v>1.1</v>
+        <v>2.26</v>
       </c>
       <c r="G23">
-        <v>600</v>
+        <v>7.4</v>
       </c>
       <c r="H23">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="I23">
-        <v>870</v>
+        <v>2.14</v>
       </c>
       <c r="J23">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6202,22 +6220,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O23">
         <v>1.01</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R23">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="S23">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6286,52 +6304,52 @@
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23">
         <v>1.01</v>
@@ -6394,497 +6412,497 @@
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F24">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
-        <v>1.45</v>
+        <v>600</v>
       </c>
       <c r="H24">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
-        <v>8.800000000000001</v>
+        <v>870</v>
       </c>
       <c r="J24">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="K24">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="O24">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q24">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R24">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="S24">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="T24">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F25">
-        <v>1.57</v>
+        <v>2.96</v>
       </c>
       <c r="G25">
+        <v>3.2</v>
+      </c>
+      <c r="H25">
+        <v>2.42</v>
+      </c>
+      <c r="I25">
+        <v>2.6</v>
+      </c>
+      <c r="J25">
+        <v>3.5</v>
+      </c>
+      <c r="K25">
+        <v>3.65</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.06</v>
+      </c>
+      <c r="N25">
+        <v>3.75</v>
+      </c>
+      <c r="O25">
+        <v>1.3</v>
+      </c>
+      <c r="P25">
+        <v>1.96</v>
+      </c>
+      <c r="Q25">
+        <v>1.89</v>
+      </c>
+      <c r="R25">
+        <v>1.38</v>
+      </c>
+      <c r="S25">
+        <v>3.2</v>
+      </c>
+      <c r="T25">
+        <v>1.7</v>
+      </c>
+      <c r="U25">
+        <v>2.22</v>
+      </c>
+      <c r="V25">
         <v>1.63</v>
       </c>
-      <c r="H25">
-        <v>5.9</v>
-      </c>
-      <c r="I25">
-        <v>6.4</v>
-      </c>
-      <c r="J25">
-        <v>4.6</v>
-      </c>
-      <c r="K25">
-        <v>4.9</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>2.4</v>
-      </c>
-      <c r="Q25">
-        <v>1.65</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>1.77</v>
-      </c>
-      <c r="U25">
-        <v>2.18</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X25">
+        <v>15.5</v>
+      </c>
+      <c r="Y25">
+        <v>11.5</v>
+      </c>
+      <c r="Z25">
+        <v>17.5</v>
+      </c>
+      <c r="AA25">
+        <v>38</v>
+      </c>
+      <c r="AB25">
+        <v>13.5</v>
+      </c>
+      <c r="AC25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD25">
+        <v>12.5</v>
+      </c>
+      <c r="AE25">
         <v>28</v>
       </c>
-      <c r="Y25">
-        <v>26</v>
-      </c>
-      <c r="Z25">
-        <v>65</v>
-      </c>
-      <c r="AA25">
-        <v>190</v>
-      </c>
-      <c r="AB25">
+      <c r="AF25">
+        <v>23</v>
+      </c>
+      <c r="AG25">
+        <v>14.5</v>
+      </c>
+      <c r="AH25">
+        <v>17.5</v>
+      </c>
+      <c r="AI25">
+        <v>40</v>
+      </c>
+      <c r="AJ25">
+        <v>55</v>
+      </c>
+      <c r="AK25">
+        <v>38</v>
+      </c>
+      <c r="AL25">
+        <v>46</v>
+      </c>
+      <c r="AM25">
+        <v>80</v>
+      </c>
+      <c r="AN25">
+        <v>32</v>
+      </c>
+      <c r="AO25">
+        <v>20</v>
+      </c>
+      <c r="AP25">
+        <v>13</v>
+      </c>
+      <c r="AQ25">
+        <v>9.6</v>
+      </c>
+      <c r="AR25">
+        <v>14.5</v>
+      </c>
+      <c r="AS25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT25">
         <v>11</v>
       </c>
-      <c r="AC25">
-        <v>11</v>
-      </c>
-      <c r="AD25">
-        <v>24</v>
-      </c>
-      <c r="AE25">
-        <v>90</v>
-      </c>
-      <c r="AF25">
-        <v>11</v>
-      </c>
-      <c r="AG25">
-        <v>10.5</v>
-      </c>
-      <c r="AH25">
-        <v>24</v>
-      </c>
-      <c r="AI25">
-        <v>85</v>
-      </c>
-      <c r="AJ25">
-        <v>15.5</v>
-      </c>
-      <c r="AK25">
-        <v>16</v>
-      </c>
-      <c r="AL25">
+      <c r="AU25">
+        <v>6.8</v>
+      </c>
+      <c r="AV25">
+        <v>10</v>
+      </c>
+      <c r="AW25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX25">
+        <v>19</v>
+      </c>
+      <c r="AY25">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25">
+        <v>14.5</v>
+      </c>
+      <c r="BA25">
+        <v>8.4</v>
+      </c>
+      <c r="BB25">
+        <v>9.6</v>
+      </c>
+      <c r="BC25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD25">
         <v>36</v>
-      </c>
-      <c r="AM25">
-        <v>110</v>
-      </c>
-      <c r="AN25">
-        <v>6.8</v>
-      </c>
-      <c r="AO25">
-        <v>90</v>
-      </c>
-      <c r="AP25">
-        <v>20</v>
-      </c>
-      <c r="AQ25">
-        <v>22</v>
-      </c>
-      <c r="AR25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS25">
-        <v>9</v>
-      </c>
-      <c r="AT25">
-        <v>9.6</v>
-      </c>
-      <c r="AU25">
-        <v>9.6</v>
-      </c>
-      <c r="AV25">
-        <v>20</v>
-      </c>
-      <c r="AW25">
-        <v>8.6</v>
-      </c>
-      <c r="AX25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ25">
-        <v>17.5</v>
-      </c>
-      <c r="BA25">
-        <v>8.6</v>
-      </c>
-      <c r="BB25">
-        <v>13.5</v>
-      </c>
-      <c r="BC25">
-        <v>14</v>
-      </c>
-      <c r="BD25">
-        <v>7.4</v>
       </c>
       <c r="BE25">
         <v>8.800000000000001</v>
       </c>
       <c r="BF25">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BG25">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6892,241 +6910,241 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F26">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="G26">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="H26">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="I26">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="K26">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P26">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q26">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T26">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="U26">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X26">
         <v>24</v>
       </c>
       <c r="Y26">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Z26">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA26">
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AD26">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AE26">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG26">
         <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AI26">
+        <v>110</v>
+      </c>
+      <c r="AJ26">
+        <v>12</v>
+      </c>
+      <c r="AK26">
+        <v>15</v>
+      </c>
+      <c r="AL26">
+        <v>36</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>5.7</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>20</v>
+      </c>
+      <c r="AQ26">
+        <v>19.5</v>
+      </c>
+      <c r="AR26">
+        <v>32</v>
+      </c>
+      <c r="AS26">
         <v>50</v>
       </c>
-      <c r="AJ26">
+      <c r="AT26">
+        <v>9</v>
+      </c>
+      <c r="AU26">
+        <v>10.5</v>
+      </c>
+      <c r="AV26">
+        <v>24</v>
+      </c>
+      <c r="AW26">
+        <v>40</v>
+      </c>
+      <c r="AX26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY26">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26">
         <v>21</v>
       </c>
-      <c r="AK26">
-        <v>17</v>
-      </c>
-      <c r="AL26">
-        <v>29</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
+      <c r="BA26">
+        <v>60</v>
+      </c>
+      <c r="BB26">
+        <v>11</v>
+      </c>
+      <c r="BC26">
+        <v>13</v>
+      </c>
+      <c r="BD26">
+        <v>25</v>
+      </c>
+      <c r="BE26">
+        <v>42</v>
+      </c>
+      <c r="BF26">
+        <v>5.3</v>
+      </c>
+      <c r="BG26">
+        <v>42</v>
+      </c>
+      <c r="BH26">
+        <v>4.2</v>
+      </c>
+      <c r="BI26">
+        <v>3.75</v>
+      </c>
+      <c r="BJ26">
+        <v>12.5</v>
+      </c>
+      <c r="BK26">
+        <v>9.4</v>
+      </c>
+      <c r="BL26">
+        <v>150</v>
+      </c>
+      <c r="BM26">
+        <v>8.4</v>
+      </c>
+      <c r="BN26">
+        <v>4.1</v>
+      </c>
+      <c r="BO26">
+        <v>3.65</v>
+      </c>
+      <c r="BP26">
+        <v>8.6</v>
+      </c>
+      <c r="BQ26">
+        <v>7.4</v>
+      </c>
+      <c r="BR26">
+        <v>26</v>
+      </c>
+      <c r="BS26">
+        <v>6.8</v>
+      </c>
+      <c r="BT26">
+        <v>13.5</v>
+      </c>
+      <c r="BU26">
+        <v>5.4</v>
+      </c>
+      <c r="BV26">
+        <v>80</v>
+      </c>
+      <c r="BW26">
         <v>8</v>
       </c>
-      <c r="AO26">
-        <v>40</v>
-      </c>
-      <c r="AP26">
-        <v>21</v>
-      </c>
-      <c r="AQ26">
-        <v>19</v>
-      </c>
-      <c r="AR26">
-        <v>23</v>
-      </c>
-      <c r="AS26">
-        <v>38</v>
-      </c>
-      <c r="AT26">
-        <v>11</v>
-      </c>
-      <c r="AU26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV26">
-        <v>16.5</v>
-      </c>
-      <c r="AW26">
-        <v>27</v>
-      </c>
-      <c r="AX26">
-        <v>11.5</v>
-      </c>
-      <c r="AY26">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26">
-        <v>14.5</v>
-      </c>
-      <c r="BA26">
-        <v>36</v>
-      </c>
-      <c r="BB26">
-        <v>17</v>
-      </c>
-      <c r="BC26">
-        <v>14.5</v>
-      </c>
-      <c r="BD26">
-        <v>19</v>
-      </c>
-      <c r="BE26">
-        <v>32</v>
-      </c>
-      <c r="BF26">
-        <v>7.6</v>
-      </c>
-      <c r="BG26">
-        <v>24</v>
-      </c>
-      <c r="BH26">
-        <v>0</v>
-      </c>
-      <c r="BI26">
-        <v>0</v>
-      </c>
-      <c r="BJ26">
-        <v>0</v>
-      </c>
-      <c r="BK26">
-        <v>0</v>
-      </c>
-      <c r="BL26">
-        <v>0</v>
-      </c>
-      <c r="BM26">
-        <v>0</v>
-      </c>
-      <c r="BN26">
-        <v>0</v>
-      </c>
-      <c r="BO26">
-        <v>0</v>
-      </c>
-      <c r="BP26">
-        <v>0</v>
-      </c>
-      <c r="BQ26">
-        <v>0</v>
-      </c>
-      <c r="BR26">
-        <v>0</v>
-      </c>
-      <c r="BS26">
-        <v>0</v>
-      </c>
-      <c r="BT26">
-        <v>0</v>
-      </c>
-      <c r="BU26">
-        <v>0</v>
-      </c>
-      <c r="BV26">
-        <v>0</v>
-      </c>
-      <c r="BW26">
-        <v>0</v>
-      </c>
       <c r="BX26">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB26" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7134,241 +7152,241 @@
         <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F27">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="G27">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="H27">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="I27">
+        <v>6.4</v>
+      </c>
+      <c r="J27">
+        <v>4.6</v>
+      </c>
+      <c r="K27">
+        <v>4.8</v>
+      </c>
+      <c r="L27">
+        <v>1.32</v>
+      </c>
+      <c r="M27">
+        <v>1.04</v>
+      </c>
+      <c r="N27">
+        <v>5.1</v>
+      </c>
+      <c r="O27">
+        <v>1.21</v>
+      </c>
+      <c r="P27">
+        <v>2.4</v>
+      </c>
+      <c r="Q27">
+        <v>1.64</v>
+      </c>
+      <c r="R27">
+        <v>1.56</v>
+      </c>
+      <c r="S27">
+        <v>2.62</v>
+      </c>
+      <c r="T27">
+        <v>1.77</v>
+      </c>
+      <c r="U27">
+        <v>2.18</v>
+      </c>
+      <c r="V27">
+        <v>1.18</v>
+      </c>
+      <c r="W27">
+        <v>2.6</v>
+      </c>
+      <c r="X27">
+        <v>24</v>
+      </c>
+      <c r="Y27">
+        <v>26</v>
+      </c>
+      <c r="Z27">
+        <v>65</v>
+      </c>
+      <c r="AA27">
+        <v>190</v>
+      </c>
+      <c r="AB27">
+        <v>11</v>
+      </c>
+      <c r="AC27">
+        <v>11</v>
+      </c>
+      <c r="AD27">
+        <v>25</v>
+      </c>
+      <c r="AE27">
+        <v>90</v>
+      </c>
+      <c r="AF27">
+        <v>11</v>
+      </c>
+      <c r="AG27">
+        <v>10.5</v>
+      </c>
+      <c r="AH27">
+        <v>20</v>
+      </c>
+      <c r="AI27">
+        <v>85</v>
+      </c>
+      <c r="AJ27">
         <v>15.5</v>
       </c>
-      <c r="J27">
-        <v>7</v>
-      </c>
-      <c r="K27">
-        <v>7.6</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>1.02</v>
-      </c>
-      <c r="N27">
-        <v>6.6</v>
-      </c>
-      <c r="O27">
-        <v>1.16</v>
-      </c>
-      <c r="P27">
-        <v>2.86</v>
-      </c>
-      <c r="Q27">
-        <v>1.49</v>
-      </c>
-      <c r="R27">
-        <v>1.75</v>
-      </c>
-      <c r="S27">
-        <v>2.18</v>
-      </c>
-      <c r="T27">
-        <v>2.04</v>
-      </c>
-      <c r="U27">
-        <v>1.89</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>34</v>
-      </c>
-      <c r="Y27">
-        <v>55</v>
-      </c>
-      <c r="Z27">
-        <v>1000</v>
-      </c>
-      <c r="AA27">
-        <v>1000</v>
-      </c>
-      <c r="AB27">
+      <c r="AK27">
+        <v>16</v>
+      </c>
+      <c r="AL27">
+        <v>36</v>
+      </c>
+      <c r="AM27">
+        <v>110</v>
+      </c>
+      <c r="AN27">
+        <v>6.8</v>
+      </c>
+      <c r="AO27">
+        <v>90</v>
+      </c>
+      <c r="AP27">
+        <v>20</v>
+      </c>
+      <c r="AQ27">
+        <v>22</v>
+      </c>
+      <c r="AR27">
+        <v>9</v>
+      </c>
+      <c r="AS27">
+        <v>10</v>
+      </c>
+      <c r="AT27">
+        <v>9.6</v>
+      </c>
+      <c r="AU27">
+        <v>9.6</v>
+      </c>
+      <c r="AV27">
+        <v>20</v>
+      </c>
+      <c r="AW27">
+        <v>9.4</v>
+      </c>
+      <c r="AX27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ27">
+        <v>17.5</v>
+      </c>
+      <c r="BA27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB27">
+        <v>13.5</v>
+      </c>
+      <c r="BC27">
+        <v>14</v>
+      </c>
+      <c r="BD27">
+        <v>8</v>
+      </c>
+      <c r="BE27">
+        <v>9.6</v>
+      </c>
+      <c r="BF27">
+        <v>6.2</v>
+      </c>
+      <c r="BG27">
+        <v>9.4</v>
+      </c>
+      <c r="BH27">
+        <v>4.1</v>
+      </c>
+      <c r="BI27">
+        <v>3.8</v>
+      </c>
+      <c r="BJ27">
         <v>12</v>
       </c>
-      <c r="AC27">
-        <v>17</v>
-      </c>
-      <c r="AD27">
-        <v>55</v>
-      </c>
-      <c r="AE27">
-        <v>1000</v>
-      </c>
-      <c r="AF27">
+      <c r="BK27">
         <v>8.800000000000001</v>
       </c>
-      <c r="AG27">
-        <v>12.5</v>
-      </c>
-      <c r="AH27">
-        <v>36</v>
-      </c>
-      <c r="AI27">
-        <v>1000</v>
-      </c>
-      <c r="AJ27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK27">
-        <v>14.5</v>
-      </c>
-      <c r="AL27">
-        <v>40</v>
-      </c>
-      <c r="AM27">
-        <v>1000</v>
-      </c>
-      <c r="AN27">
-        <v>3.65</v>
-      </c>
-      <c r="AO27">
-        <v>1000</v>
-      </c>
-      <c r="AP27">
-        <v>27</v>
-      </c>
-      <c r="AQ27">
-        <v>26</v>
-      </c>
-      <c r="AR27">
-        <v>42</v>
-      </c>
-      <c r="AS27">
-        <v>110</v>
-      </c>
-      <c r="AT27">
-        <v>10.5</v>
-      </c>
-      <c r="AU27">
-        <v>14</v>
-      </c>
-      <c r="AV27">
-        <v>40</v>
-      </c>
-      <c r="AW27">
-        <v>48</v>
-      </c>
-      <c r="AX27">
-        <v>8</v>
-      </c>
-      <c r="AY27">
-        <v>10.5</v>
-      </c>
-      <c r="AZ27">
+      <c r="BL27">
+        <v>130</v>
+      </c>
+      <c r="BM27">
         <v>21</v>
       </c>
-      <c r="BA27">
-        <v>44</v>
-      </c>
-      <c r="BB27">
+      <c r="BN27">
+        <v>4.4</v>
+      </c>
+      <c r="BO27">
+        <v>3.95</v>
+      </c>
+      <c r="BP27">
+        <v>9.6</v>
+      </c>
+      <c r="BQ27">
         <v>8.6</v>
-      </c>
-      <c r="BC27">
-        <v>12</v>
-      </c>
-      <c r="BD27">
-        <v>27</v>
-      </c>
-      <c r="BE27">
-        <v>44</v>
-      </c>
-      <c r="BF27">
-        <v>3.45</v>
-      </c>
-      <c r="BG27">
-        <v>50</v>
-      </c>
-      <c r="BH27">
-        <v>5</v>
-      </c>
-      <c r="BI27">
-        <v>4.3</v>
-      </c>
-      <c r="BJ27">
-        <v>13</v>
-      </c>
-      <c r="BK27">
-        <v>6.2</v>
-      </c>
-      <c r="BL27">
-        <v>150</v>
-      </c>
-      <c r="BM27">
-        <v>10.5</v>
-      </c>
-      <c r="BN27">
-        <v>3.95</v>
-      </c>
-      <c r="BO27">
-        <v>3.45</v>
-      </c>
-      <c r="BP27">
-        <v>7</v>
-      </c>
-      <c r="BQ27">
-        <v>5.8</v>
       </c>
       <c r="BR27">
         <v>22</v>
       </c>
       <c r="BS27">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BT27">
+        <v>12</v>
+      </c>
+      <c r="BU27">
+        <v>8.6</v>
+      </c>
+      <c r="BV27">
+        <v>60</v>
+      </c>
+      <c r="BW27">
+        <v>34</v>
+      </c>
+      <c r="BX27">
+        <v>60</v>
+      </c>
+      <c r="BY27">
+        <v>34</v>
+      </c>
+      <c r="BZ27">
         <v>17</v>
       </c>
-      <c r="BU27">
-        <v>6.8</v>
-      </c>
-      <c r="BV27">
-        <v>120</v>
-      </c>
-      <c r="BW27">
-        <v>10.5</v>
-      </c>
-      <c r="BX27">
-        <v>90</v>
-      </c>
-      <c r="BY27">
+      <c r="CA27">
         <v>10</v>
       </c>
-      <c r="BZ27">
-        <v>9</v>
-      </c>
-      <c r="CA27">
-        <v>5.1</v>
-      </c>
       <c r="CB27" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7376,136 +7394,136 @@
         <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28">
+        <v>1.81</v>
+      </c>
+      <c r="G28">
+        <v>1.82</v>
+      </c>
+      <c r="H28">
+        <v>4.6</v>
+      </c>
+      <c r="I28">
+        <v>4.7</v>
+      </c>
+      <c r="J28">
+        <v>4.2</v>
+      </c>
+      <c r="K28">
+        <v>4.4</v>
+      </c>
+      <c r="L28">
+        <v>1.3</v>
+      </c>
+      <c r="M28">
+        <v>1.03</v>
+      </c>
+      <c r="N28">
+        <v>5.2</v>
+      </c>
+      <c r="O28">
+        <v>1.19</v>
+      </c>
+      <c r="P28">
+        <v>2.48</v>
+      </c>
+      <c r="Q28">
+        <v>1.6</v>
+      </c>
+      <c r="R28">
+        <v>1.6</v>
+      </c>
+      <c r="S28">
+        <v>2.44</v>
+      </c>
+      <c r="T28">
+        <v>1.63</v>
+      </c>
+      <c r="U28">
+        <v>2.5</v>
+      </c>
+      <c r="V28">
+        <v>1.21</v>
+      </c>
+      <c r="W28">
+        <v>2.04</v>
+      </c>
+      <c r="X28">
+        <v>23</v>
+      </c>
+      <c r="Y28">
+        <v>23</v>
+      </c>
+      <c r="Z28">
+        <v>40</v>
+      </c>
+      <c r="AA28">
         <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" t="s">
-        <v>158</v>
-      </c>
-      <c r="F28">
-        <v>1.76</v>
-      </c>
-      <c r="G28">
-        <v>1.78</v>
-      </c>
-      <c r="H28">
-        <v>5.1</v>
-      </c>
-      <c r="I28">
-        <v>5.3</v>
-      </c>
-      <c r="J28">
-        <v>4.1</v>
-      </c>
-      <c r="K28">
-        <v>4.3</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>1.04</v>
-      </c>
-      <c r="N28">
-        <v>5.7</v>
-      </c>
-      <c r="O28">
-        <v>1.2</v>
-      </c>
-      <c r="P28">
-        <v>2.58</v>
-      </c>
-      <c r="Q28">
-        <v>1.59</v>
-      </c>
-      <c r="R28">
-        <v>1.64</v>
-      </c>
-      <c r="S28">
-        <v>2.46</v>
-      </c>
-      <c r="T28">
-        <v>1.6</v>
-      </c>
-      <c r="U28">
-        <v>2.56</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>25</v>
-      </c>
-      <c r="Y28">
-        <v>26</v>
-      </c>
-      <c r="Z28">
-        <v>46</v>
-      </c>
-      <c r="AA28">
-        <v>1000</v>
       </c>
       <c r="AB28">
         <v>13</v>
       </c>
       <c r="AC28">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD28">
+        <v>18.5</v>
+      </c>
+      <c r="AE28">
+        <v>50</v>
+      </c>
+      <c r="AF28">
+        <v>13.5</v>
+      </c>
+      <c r="AG28">
+        <v>10.5</v>
+      </c>
+      <c r="AH28">
+        <v>17</v>
+      </c>
+      <c r="AI28">
+        <v>48</v>
+      </c>
+      <c r="AJ28">
         <v>21</v>
       </c>
-      <c r="AE28">
-        <v>260</v>
-      </c>
-      <c r="AF28">
-        <v>14</v>
-      </c>
-      <c r="AG28">
-        <v>10</v>
-      </c>
-      <c r="AH28">
-        <v>16</v>
-      </c>
-      <c r="AI28">
-        <v>55</v>
-      </c>
-      <c r="AJ28">
-        <v>20</v>
-      </c>
       <c r="AK28">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL28">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM28">
         <v>70</v>
       </c>
       <c r="AN28">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AO28">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ28">
         <v>21</v>
       </c>
       <c r="AR28">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AS28">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT28">
         <v>11</v>
@@ -7514,103 +7532,103 @@
         <v>9</v>
       </c>
       <c r="AV28">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW28">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AX28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA28">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BB28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC28">
         <v>14.5</v>
       </c>
       <c r="BD28">
+        <v>23</v>
+      </c>
+      <c r="BE28">
+        <v>55</v>
+      </c>
+      <c r="BF28">
+        <v>7.4</v>
+      </c>
+      <c r="BG28">
+        <v>29</v>
+      </c>
+      <c r="BH28">
+        <v>4.4</v>
+      </c>
+      <c r="BI28">
+        <v>3.85</v>
+      </c>
+      <c r="BJ28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK28">
+        <v>7.8</v>
+      </c>
+      <c r="BL28">
+        <v>90</v>
+      </c>
+      <c r="BM28">
+        <v>21</v>
+      </c>
+      <c r="BN28">
+        <v>5</v>
+      </c>
+      <c r="BO28">
+        <v>4.2</v>
+      </c>
+      <c r="BP28">
+        <v>12</v>
+      </c>
+      <c r="BQ28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR28">
         <v>22</v>
       </c>
-      <c r="BE28">
-        <v>40</v>
-      </c>
-      <c r="BF28">
-        <v>7</v>
-      </c>
-      <c r="BG28">
-        <v>25</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>1.5</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>1.84</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>2.14</v>
-      </c>
-      <c r="BN28">
-        <v>1000</v>
-      </c>
-      <c r="BO28">
-        <v>1.56</v>
-      </c>
-      <c r="BP28">
-        <v>1000</v>
-      </c>
-      <c r="BQ28">
-        <v>2.14</v>
-      </c>
-      <c r="BR28">
-        <v>1000</v>
-      </c>
       <c r="BS28">
-        <v>2.14</v>
+        <v>16.5</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU28">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW28">
-        <v>2.14</v>
+        <v>24</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY28">
-        <v>2.14</v>
+        <v>27</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA28">
-        <v>2.14</v>
+        <v>11.5</v>
       </c>
       <c r="CB28" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7618,241 +7636,241 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="G29">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="H29">
-        <v>2.48</v>
+        <v>13</v>
       </c>
       <c r="I29">
-        <v>2.54</v>
+        <v>15.5</v>
       </c>
       <c r="J29">
+        <v>7</v>
+      </c>
+      <c r="K29">
+        <v>7.4</v>
+      </c>
+      <c r="L29">
+        <v>1.25</v>
+      </c>
+      <c r="M29">
+        <v>1.02</v>
+      </c>
+      <c r="N29">
+        <v>6.6</v>
+      </c>
+      <c r="O29">
+        <v>1.16</v>
+      </c>
+      <c r="P29">
+        <v>2.88</v>
+      </c>
+      <c r="Q29">
+        <v>1.49</v>
+      </c>
+      <c r="R29">
+        <v>1.76</v>
+      </c>
+      <c r="S29">
+        <v>2.2</v>
+      </c>
+      <c r="T29">
+        <v>2.04</v>
+      </c>
+      <c r="U29">
+        <v>1.88</v>
+      </c>
+      <c r="V29">
+        <v>1.07</v>
+      </c>
+      <c r="W29">
+        <v>4.7</v>
+      </c>
+      <c r="X29">
+        <v>32</v>
+      </c>
+      <c r="Y29">
+        <v>55</v>
+      </c>
+      <c r="Z29">
+        <v>150</v>
+      </c>
+      <c r="AA29">
+        <v>720</v>
+      </c>
+      <c r="AB29">
+        <v>12</v>
+      </c>
+      <c r="AC29">
+        <v>16.5</v>
+      </c>
+      <c r="AD29">
+        <v>50</v>
+      </c>
+      <c r="AE29">
+        <v>220</v>
+      </c>
+      <c r="AF29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG29">
+        <v>11.5</v>
+      </c>
+      <c r="AH29">
+        <v>34</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK29">
+        <v>14.5</v>
+      </c>
+      <c r="AL29">
+        <v>38</v>
+      </c>
+      <c r="AM29">
+        <v>160</v>
+      </c>
+      <c r="AN29">
         <v>3.65</v>
       </c>
-      <c r="K29">
-        <v>3.7</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>1.05</v>
-      </c>
-      <c r="N29">
-        <v>4.6</v>
-      </c>
-      <c r="O29">
-        <v>1.25</v>
-      </c>
-      <c r="P29">
-        <v>2.26</v>
-      </c>
-      <c r="Q29">
-        <v>1.77</v>
-      </c>
-      <c r="R29">
-        <v>1.48</v>
-      </c>
-      <c r="S29">
-        <v>2.9</v>
-      </c>
-      <c r="T29">
-        <v>1.64</v>
-      </c>
-      <c r="U29">
-        <v>2.46</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>19</v>
-      </c>
-      <c r="Y29">
-        <v>13</v>
-      </c>
-      <c r="Z29">
-        <v>17.5</v>
-      </c>
-      <c r="AA29">
-        <v>34</v>
-      </c>
-      <c r="AB29">
-        <v>15</v>
-      </c>
-      <c r="AC29">
-        <v>8.4</v>
-      </c>
-      <c r="AD29">
-        <v>11.5</v>
-      </c>
-      <c r="AE29">
-        <v>25</v>
-      </c>
-      <c r="AF29">
-        <v>23</v>
-      </c>
-      <c r="AG29">
-        <v>13.5</v>
-      </c>
-      <c r="AH29">
+      <c r="AO29">
+        <v>240</v>
+      </c>
+      <c r="AP29">
+        <v>21</v>
+      </c>
+      <c r="AQ29">
+        <v>42</v>
+      </c>
+      <c r="AR29">
+        <v>42</v>
+      </c>
+      <c r="AS29">
+        <v>55</v>
+      </c>
+      <c r="AT29">
+        <v>10.5</v>
+      </c>
+      <c r="AU29">
         <v>14</v>
       </c>
-      <c r="AI29">
-        <v>34</v>
-      </c>
-      <c r="AJ29">
+      <c r="AV29">
+        <v>42</v>
+      </c>
+      <c r="AW29">
+        <v>48</v>
+      </c>
+      <c r="AX29">
+        <v>8</v>
+      </c>
+      <c r="AY29">
+        <v>10.5</v>
+      </c>
+      <c r="AZ29">
+        <v>27</v>
+      </c>
+      <c r="BA29">
+        <v>44</v>
+      </c>
+      <c r="BB29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC29">
+        <v>12.5</v>
+      </c>
+      <c r="BD29">
+        <v>30</v>
+      </c>
+      <c r="BE29">
+        <v>44</v>
+      </c>
+      <c r="BF29">
+        <v>3.5</v>
+      </c>
+      <c r="BG29">
         <v>50</v>
       </c>
-      <c r="AK29">
-        <v>34</v>
-      </c>
-      <c r="AL29">
-        <v>40</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>24</v>
-      </c>
-      <c r="AO29">
-        <v>16.5</v>
-      </c>
-      <c r="AP29">
-        <v>16.5</v>
-      </c>
-      <c r="AQ29">
-        <v>11.5</v>
-      </c>
-      <c r="AR29">
-        <v>15.5</v>
-      </c>
-      <c r="AS29">
-        <v>22</v>
-      </c>
-      <c r="AT29">
-        <v>13.5</v>
-      </c>
-      <c r="AU29">
-        <v>7.8</v>
-      </c>
-      <c r="AV29">
-        <v>10.5</v>
-      </c>
-      <c r="AW29">
-        <v>21</v>
-      </c>
-      <c r="AX29">
-        <v>20</v>
-      </c>
-      <c r="AY29">
-        <v>11.5</v>
-      </c>
-      <c r="AZ29">
-        <v>13</v>
-      </c>
-      <c r="BA29">
-        <v>22</v>
-      </c>
-      <c r="BB29">
-        <v>26</v>
-      </c>
-      <c r="BC29">
-        <v>27</v>
-      </c>
-      <c r="BD29">
-        <v>32</v>
-      </c>
-      <c r="BE29">
-        <v>32</v>
-      </c>
-      <c r="BF29">
-        <v>20</v>
-      </c>
-      <c r="BG29">
-        <v>15</v>
-      </c>
       <c r="BH29">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.15</v>
+        <v>1.54</v>
       </c>
       <c r="BJ29">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>5.8</v>
+        <v>2.14</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN29">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO29">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="BP29">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
+        <v>5.3</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>2.14</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>2.14</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>9.6</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
         <v>9.199999999999999</v>
       </c>
-      <c r="BR29">
-        <v>30</v>
-      </c>
-      <c r="BS29">
-        <v>10.5</v>
-      </c>
-      <c r="BT29">
-        <v>5.7</v>
-      </c>
-      <c r="BU29">
-        <v>5.1</v>
-      </c>
-      <c r="BV29">
-        <v>17.5</v>
-      </c>
-      <c r="BW29">
-        <v>8.4</v>
-      </c>
-      <c r="BX29">
-        <v>27</v>
-      </c>
-      <c r="BY29">
-        <v>10</v>
-      </c>
       <c r="BZ29">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="CB29" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7860,483 +7878,967 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30">
+        <v>1.78</v>
+      </c>
+      <c r="G30">
+        <v>1.8</v>
+      </c>
+      <c r="H30">
+        <v>4.9</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30">
+        <v>4.1</v>
+      </c>
+      <c r="K30">
+        <v>4.3</v>
+      </c>
+      <c r="L30">
+        <v>1.29</v>
+      </c>
+      <c r="M30">
+        <v>1.04</v>
+      </c>
+      <c r="N30">
+        <v>5.2</v>
+      </c>
+      <c r="O30">
+        <v>1.19</v>
+      </c>
+      <c r="P30">
+        <v>2.46</v>
+      </c>
+      <c r="Q30">
+        <v>1.59</v>
+      </c>
+      <c r="R30">
+        <v>1.59</v>
+      </c>
+      <c r="S30">
+        <v>2.44</v>
+      </c>
+      <c r="T30">
+        <v>1.61</v>
+      </c>
+      <c r="U30">
+        <v>2.56</v>
+      </c>
+      <c r="V30">
+        <v>1.25</v>
+      </c>
+      <c r="W30">
+        <v>2.24</v>
+      </c>
+      <c r="X30">
+        <v>24</v>
+      </c>
+      <c r="Y30">
+        <v>26</v>
+      </c>
+      <c r="Z30">
         <v>100</v>
       </c>
-      <c r="D30" t="s">
-        <v>130</v>
-      </c>
-      <c r="E30" t="s">
-        <v>160</v>
-      </c>
-      <c r="F30">
-        <v>2.86</v>
-      </c>
-      <c r="G30">
-        <v>2.96</v>
-      </c>
-      <c r="H30">
-        <v>2.6</v>
-      </c>
-      <c r="I30">
-        <v>2.64</v>
-      </c>
-      <c r="J30">
-        <v>3.6</v>
-      </c>
-      <c r="K30">
-        <v>3.65</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>2.12</v>
-      </c>
-      <c r="Q30">
-        <v>1.82</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>1.67</v>
-      </c>
-      <c r="U30">
-        <v>2.38</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>17.5</v>
-      </c>
-      <c r="Y30">
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
         <v>13</v>
       </c>
-      <c r="Z30">
-        <v>19</v>
-      </c>
-      <c r="AA30">
+      <c r="AC30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD30">
+        <v>21</v>
+      </c>
+      <c r="AE30">
+        <v>55</v>
+      </c>
+      <c r="AF30">
+        <v>13.5</v>
+      </c>
+      <c r="AG30">
+        <v>10.5</v>
+      </c>
+      <c r="AH30">
+        <v>16</v>
+      </c>
+      <c r="AI30">
+        <v>180</v>
+      </c>
+      <c r="AJ30">
+        <v>19.5</v>
+      </c>
+      <c r="AK30">
+        <v>16</v>
+      </c>
+      <c r="AL30">
+        <v>28</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>7.8</v>
+      </c>
+      <c r="AO30">
+        <v>42</v>
+      </c>
+      <c r="AP30">
+        <v>20</v>
+      </c>
+      <c r="AQ30">
+        <v>21</v>
+      </c>
+      <c r="AR30">
+        <v>32</v>
+      </c>
+      <c r="AS30">
         <v>38</v>
       </c>
-      <c r="AB30">
-        <v>13.5</v>
-      </c>
-      <c r="AC30">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD30">
-        <v>12.5</v>
-      </c>
-      <c r="AE30">
-        <v>28</v>
-      </c>
-      <c r="AF30">
-        <v>21</v>
-      </c>
-      <c r="AG30">
-        <v>13</v>
-      </c>
-      <c r="AH30">
-        <v>16.5</v>
-      </c>
-      <c r="AI30">
-        <v>38</v>
-      </c>
-      <c r="AJ30">
-        <v>44</v>
-      </c>
-      <c r="AK30">
-        <v>30</v>
-      </c>
-      <c r="AL30">
-        <v>38</v>
-      </c>
-      <c r="AM30">
-        <v>1000</v>
-      </c>
-      <c r="AN30">
-        <v>20</v>
-      </c>
-      <c r="AO30">
-        <v>21</v>
-      </c>
-      <c r="AP30">
-        <v>15</v>
-      </c>
-      <c r="AQ30">
-        <v>11</v>
-      </c>
-      <c r="AR30">
-        <v>16</v>
-      </c>
-      <c r="AS30">
-        <v>32</v>
-      </c>
       <c r="AT30">
+        <v>11.5</v>
+      </c>
+      <c r="AU30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV30">
+        <v>17</v>
+      </c>
+      <c r="AW30">
+        <v>27</v>
+      </c>
+      <c r="AX30">
         <v>12</v>
       </c>
-      <c r="AU30">
-        <v>7.4</v>
-      </c>
-      <c r="AV30">
-        <v>10.5</v>
-      </c>
-      <c r="AW30">
-        <v>19</v>
-      </c>
-      <c r="AX30">
-        <v>17</v>
-      </c>
       <c r="AY30">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
+        <v>26</v>
+      </c>
+      <c r="BB30">
+        <v>17.5</v>
+      </c>
+      <c r="BC30">
+        <v>14.5</v>
+      </c>
+      <c r="BD30">
+        <v>23</v>
+      </c>
+      <c r="BE30">
         <v>30</v>
       </c>
-      <c r="BB30">
+      <c r="BF30">
+        <v>7.2</v>
+      </c>
+      <c r="BG30">
         <v>25</v>
       </c>
-      <c r="BC30">
-        <v>23</v>
-      </c>
-      <c r="BD30">
-        <v>24</v>
-      </c>
-      <c r="BE30">
-        <v>34</v>
-      </c>
-      <c r="BF30">
-        <v>19</v>
-      </c>
-      <c r="BG30">
-        <v>17.5</v>
-      </c>
       <c r="BH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="CB30" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F31">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="H31">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="I31">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K31">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N31">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P31">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="Q31">
+        <v>1.76</v>
+      </c>
+      <c r="R31">
+        <v>1.48</v>
+      </c>
+      <c r="S31">
+        <v>2.88</v>
+      </c>
+      <c r="T31">
+        <v>1.63</v>
+      </c>
+      <c r="U31">
+        <v>2.46</v>
+      </c>
+      <c r="V31">
         <v>1.66</v>
       </c>
-      <c r="R31">
-        <v>1.59</v>
-      </c>
-      <c r="S31">
-        <v>2.66</v>
-      </c>
-      <c r="T31">
-        <v>1.62</v>
-      </c>
-      <c r="U31">
-        <v>2.52</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X31">
+        <v>18</v>
+      </c>
+      <c r="Y31">
+        <v>13.5</v>
+      </c>
+      <c r="Z31">
+        <v>18</v>
+      </c>
+      <c r="AA31">
+        <v>34</v>
+      </c>
+      <c r="AB31">
+        <v>15</v>
+      </c>
+      <c r="AC31">
+        <v>8.4</v>
+      </c>
+      <c r="AD31">
+        <v>11.5</v>
+      </c>
+      <c r="AE31">
+        <v>25</v>
+      </c>
+      <c r="AF31">
         <v>22</v>
       </c>
-      <c r="Y31">
+      <c r="AG31">
         <v>13</v>
       </c>
-      <c r="Z31">
-        <v>14.5</v>
-      </c>
-      <c r="AA31">
-        <v>25</v>
-      </c>
-      <c r="AB31">
-        <v>19</v>
-      </c>
-      <c r="AC31">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD31">
-        <v>11</v>
-      </c>
-      <c r="AE31">
-        <v>18.5</v>
-      </c>
-      <c r="AF31">
+      <c r="AH31">
+        <v>14</v>
+      </c>
+      <c r="AI31">
+        <v>34</v>
+      </c>
+      <c r="AJ31">
+        <v>150</v>
+      </c>
+      <c r="AK31">
         <v>32</v>
       </c>
-      <c r="AG31">
-        <v>15.5</v>
-      </c>
-      <c r="AH31">
-        <v>15.5</v>
-      </c>
-      <c r="AI31">
-        <v>30</v>
-      </c>
-      <c r="AJ31">
+      <c r="AL31">
+        <v>38</v>
+      </c>
+      <c r="AM31">
         <v>70</v>
       </c>
-      <c r="AK31">
-        <v>38</v>
-      </c>
-      <c r="AL31">
-        <v>42</v>
-      </c>
-      <c r="AM31">
-        <v>65</v>
-      </c>
       <c r="AN31">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AO31">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AP31">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AQ31">
         <v>12</v>
       </c>
       <c r="AR31">
+        <v>15.5</v>
+      </c>
+      <c r="AS31">
+        <v>29</v>
+      </c>
+      <c r="AT31">
+        <v>13</v>
+      </c>
+      <c r="AU31">
+        <v>7.6</v>
+      </c>
+      <c r="AV31">
+        <v>10.5</v>
+      </c>
+      <c r="AW31">
+        <v>22</v>
+      </c>
+      <c r="AX31">
+        <v>19</v>
+      </c>
+      <c r="AY31">
+        <v>11.5</v>
+      </c>
+      <c r="AZ31">
+        <v>13</v>
+      </c>
+      <c r="BA31">
+        <v>29</v>
+      </c>
+      <c r="BB31">
+        <v>42</v>
+      </c>
+      <c r="BC31">
+        <v>27</v>
+      </c>
+      <c r="BD31">
+        <v>32</v>
+      </c>
+      <c r="BE31">
+        <v>55</v>
+      </c>
+      <c r="BF31">
+        <v>20</v>
+      </c>
+      <c r="BG31">
+        <v>15</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.52</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>2</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>2.38</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.85</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>2.38</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>2.38</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.79</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>2.38</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>2.38</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>2.38</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32">
+        <v>2.88</v>
+      </c>
+      <c r="G32">
+        <v>2.94</v>
+      </c>
+      <c r="H32">
+        <v>2.6</v>
+      </c>
+      <c r="I32">
+        <v>2.64</v>
+      </c>
+      <c r="J32">
+        <v>3.6</v>
+      </c>
+      <c r="K32">
+        <v>3.65</v>
+      </c>
+      <c r="L32">
+        <v>1.37</v>
+      </c>
+      <c r="M32">
+        <v>1.05</v>
+      </c>
+      <c r="N32">
+        <v>4.2</v>
+      </c>
+      <c r="O32">
+        <v>1.26</v>
+      </c>
+      <c r="P32">
+        <v>2.08</v>
+      </c>
+      <c r="Q32">
+        <v>1.79</v>
+      </c>
+      <c r="R32">
+        <v>1.42</v>
+      </c>
+      <c r="S32">
+        <v>2.98</v>
+      </c>
+      <c r="T32">
+        <v>1.68</v>
+      </c>
+      <c r="U32">
+        <v>2.36</v>
+      </c>
+      <c r="V32">
+        <v>1.56</v>
+      </c>
+      <c r="W32">
+        <v>1.51</v>
+      </c>
+      <c r="X32">
+        <v>17</v>
+      </c>
+      <c r="Y32">
+        <v>13</v>
+      </c>
+      <c r="Z32">
+        <v>18.5</v>
+      </c>
+      <c r="AA32">
+        <v>40</v>
+      </c>
+      <c r="AB32">
         <v>13.5</v>
       </c>
-      <c r="AS31">
+      <c r="AC32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD32">
+        <v>12</v>
+      </c>
+      <c r="AE32">
+        <v>27</v>
+      </c>
+      <c r="AF32">
+        <v>21</v>
+      </c>
+      <c r="AG32">
+        <v>13</v>
+      </c>
+      <c r="AH32">
+        <v>16.5</v>
+      </c>
+      <c r="AI32">
+        <v>38</v>
+      </c>
+      <c r="AJ32">
+        <v>44</v>
+      </c>
+      <c r="AK32">
+        <v>30</v>
+      </c>
+      <c r="AL32">
+        <v>38</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>23</v>
+      </c>
+      <c r="AO32">
+        <v>20</v>
+      </c>
+      <c r="AP32">
+        <v>15</v>
+      </c>
+      <c r="AQ32">
+        <v>11.5</v>
+      </c>
+      <c r="AR32">
+        <v>16.5</v>
+      </c>
+      <c r="AS32">
+        <v>34</v>
+      </c>
+      <c r="AT32">
+        <v>12.5</v>
+      </c>
+      <c r="AU32">
+        <v>7.4</v>
+      </c>
+      <c r="AV32">
+        <v>11</v>
+      </c>
+      <c r="AW32">
+        <v>23</v>
+      </c>
+      <c r="AX32">
+        <v>17.5</v>
+      </c>
+      <c r="AY32">
+        <v>11.5</v>
+      </c>
+      <c r="AZ32">
+        <v>14.5</v>
+      </c>
+      <c r="BA32">
+        <v>30</v>
+      </c>
+      <c r="BB32">
+        <v>38</v>
+      </c>
+      <c r="BC32">
+        <v>26</v>
+      </c>
+      <c r="BD32">
+        <v>34</v>
+      </c>
+      <c r="BE32">
+        <v>34</v>
+      </c>
+      <c r="BF32">
+        <v>19.5</v>
+      </c>
+      <c r="BG32">
+        <v>17.5</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>2.92</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>6.4</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.01</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>4.7</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>12</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.01</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>4.6</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>11.5</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.01</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33">
+        <v>3.75</v>
+      </c>
+      <c r="G33">
+        <v>3.85</v>
+      </c>
+      <c r="H33">
+        <v>2.04</v>
+      </c>
+      <c r="I33">
+        <v>2.06</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+      <c r="K33">
+        <v>4.1</v>
+      </c>
+      <c r="L33">
+        <v>1.31</v>
+      </c>
+      <c r="M33">
+        <v>1.04</v>
+      </c>
+      <c r="N33">
+        <v>5.2</v>
+      </c>
+      <c r="O33">
+        <v>1.22</v>
+      </c>
+      <c r="P33">
+        <v>2.4</v>
+      </c>
+      <c r="Q33">
+        <v>1.64</v>
+      </c>
+      <c r="R33">
+        <v>1.58</v>
+      </c>
+      <c r="S33">
+        <v>2.6</v>
+      </c>
+      <c r="T33">
+        <v>1.62</v>
+      </c>
+      <c r="U33">
+        <v>2.52</v>
+      </c>
+      <c r="V33">
+        <v>1.91</v>
+      </c>
+      <c r="W33">
+        <v>1.35</v>
+      </c>
+      <c r="X33">
         <v>22</v>
       </c>
-      <c r="AT31">
-        <v>17</v>
-      </c>
-      <c r="AU31">
+      <c r="Y33">
+        <v>13</v>
+      </c>
+      <c r="Z33">
+        <v>14.5</v>
+      </c>
+      <c r="AA33">
+        <v>24</v>
+      </c>
+      <c r="AB33">
+        <v>18.5</v>
+      </c>
+      <c r="AC33">
+        <v>9</v>
+      </c>
+      <c r="AD33">
+        <v>11</v>
+      </c>
+      <c r="AE33">
+        <v>18.5</v>
+      </c>
+      <c r="AF33">
+        <v>32</v>
+      </c>
+      <c r="AG33">
+        <v>16</v>
+      </c>
+      <c r="AH33">
+        <v>15.5</v>
+      </c>
+      <c r="AI33">
+        <v>28</v>
+      </c>
+      <c r="AJ33">
+        <v>70</v>
+      </c>
+      <c r="AK33">
+        <v>38</v>
+      </c>
+      <c r="AL33">
+        <v>42</v>
+      </c>
+      <c r="AM33">
+        <v>65</v>
+      </c>
+      <c r="AN33">
+        <v>28</v>
+      </c>
+      <c r="AO33">
+        <v>10.5</v>
+      </c>
+      <c r="AP33">
+        <v>20</v>
+      </c>
+      <c r="AQ33">
+        <v>12</v>
+      </c>
+      <c r="AR33">
+        <v>13.5</v>
+      </c>
+      <c r="AS33">
+        <v>22</v>
+      </c>
+      <c r="AT33">
+        <v>18</v>
+      </c>
+      <c r="AU33">
         <v>8.6</v>
       </c>
-      <c r="AV31">
+      <c r="AV33">
         <v>10</v>
       </c>
-      <c r="AW31">
+      <c r="AW33">
         <v>17.5</v>
       </c>
-      <c r="AX31">
-        <v>19.5</v>
-      </c>
-      <c r="AY31">
+      <c r="AX33">
+        <v>27</v>
+      </c>
+      <c r="AY33">
         <v>14</v>
       </c>
-      <c r="AZ31">
+      <c r="AZ33">
         <v>14</v>
       </c>
-      <c r="BA31">
-        <v>19</v>
-      </c>
-      <c r="BB31">
-        <v>32</v>
-      </c>
-      <c r="BC31">
-        <v>23</v>
-      </c>
-      <c r="BD31">
-        <v>24</v>
-      </c>
-      <c r="BE31">
-        <v>32</v>
-      </c>
-      <c r="BF31">
+      <c r="BA33">
         <v>25</v>
       </c>
-      <c r="BG31">
-        <v>9.6</v>
-      </c>
-      <c r="BH31">
+      <c r="BB33">
+        <v>55</v>
+      </c>
+      <c r="BC33">
+        <v>34</v>
+      </c>
+      <c r="BD33">
+        <v>36</v>
+      </c>
+      <c r="BE33">
+        <v>55</v>
+      </c>
+      <c r="BF33">
+        <v>25</v>
+      </c>
+      <c r="BG33">
+        <v>9.4</v>
+      </c>
+      <c r="BH33">
         <v>4</v>
       </c>
-      <c r="BI31">
+      <c r="BI33">
         <v>3.65</v>
       </c>
-      <c r="BJ31">
-        <v>11</v>
-      </c>
-      <c r="BK31">
+      <c r="BJ33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK33">
         <v>7.8</v>
       </c>
-      <c r="BL31">
+      <c r="BL33">
         <v>110</v>
       </c>
-      <c r="BM31">
+      <c r="BM33">
+        <v>9.4</v>
+      </c>
+      <c r="BN33">
+        <v>7.2</v>
+      </c>
+      <c r="BO33">
+        <v>6.6</v>
+      </c>
+      <c r="BP33">
+        <v>34</v>
+      </c>
+      <c r="BQ33">
+        <v>8</v>
+      </c>
+      <c r="BR33">
+        <v>40</v>
+      </c>
+      <c r="BS33">
+        <v>8.4</v>
+      </c>
+      <c r="BT33">
+        <v>5.1</v>
+      </c>
+      <c r="BU33">
+        <v>4.7</v>
+      </c>
+      <c r="BV33">
+        <v>16.5</v>
+      </c>
+      <c r="BW33">
+        <v>11.5</v>
+      </c>
+      <c r="BX33">
+        <v>29</v>
+      </c>
+      <c r="BY33">
         <v>7.8</v>
       </c>
-      <c r="BN31">
+      <c r="BZ33">
+        <v>21</v>
+      </c>
+      <c r="CA33">
         <v>7.2</v>
       </c>
-      <c r="BO31">
-        <v>6.6</v>
-      </c>
-      <c r="BP31">
-        <v>34</v>
-      </c>
-      <c r="BQ31">
-        <v>6.6</v>
-      </c>
-      <c r="BR31">
-        <v>40</v>
-      </c>
-      <c r="BS31">
-        <v>6.8</v>
-      </c>
-      <c r="BT31">
-        <v>5.1</v>
-      </c>
-      <c r="BU31">
-        <v>4.6</v>
-      </c>
-      <c r="BV31">
-        <v>16.5</v>
-      </c>
-      <c r="BW31">
-        <v>5.7</v>
-      </c>
-      <c r="BX31">
-        <v>29</v>
-      </c>
-      <c r="BY31">
-        <v>6.4</v>
-      </c>
-      <c r="BZ31">
-        <v>21</v>
-      </c>
-      <c r="CA31">
-        <v>6.2</v>
-      </c>
-      <c r="CB31" t="s">
-        <v>162</v>
+      <c r="CB33" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -520,7 +520,7 @@
     <t>Villarreal</t>
   </si>
   <si>
-    <t>2026-09-15 17:30:29</t>
+    <t>2026-09-15 19:54:03</t>
   </si>
 </sst>
 </file>
@@ -1117,16 +1117,16 @@
         <v>1.12</v>
       </c>
       <c r="G2">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H2">
         <v>1.12</v>
       </c>
       <c r="I2">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J2">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -1147,7 +1147,7 @@
         <v>1.29</v>
       </c>
       <c r="Q2">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="R2">
         <v>1.18</v>
@@ -1162,10 +1162,10 @@
         <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1374,13 +1374,13 @@
         <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1389,7 +1389,7 @@
         <v>1.47</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R3">
         <v>1.16</v>
@@ -1401,7 +1401,7 @@
         <v>2.48</v>
       </c>
       <c r="U3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
         <v>1.23</v>
@@ -1413,31 +1413,31 @@
         <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA3">
         <v>160</v>
       </c>
       <c r="AB3">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE3">
         <v>110</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AG3">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
         <v>32</v>
@@ -1452,10 +1452,10 @@
         <v>32</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN3">
         <v>32</v>
@@ -1470,10 +1470,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>4.9</v>
+        <v>30</v>
       </c>
       <c r="AS3">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
@@ -1485,7 +1485,7 @@
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="AX3">
         <v>9</v>
@@ -1494,28 +1494,28 @@
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BB3">
         <v>22</v>
       </c>
       <c r="BC3">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BD3">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="BF3">
         <v>25</v>
       </c>
       <c r="BG3">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1527,25 +1527,25 @@
         <v>18</v>
       </c>
       <c r="BK3">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BN3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
         <v>1.29</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ3">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1554,28 +1554,28 @@
         <v>1.66</v>
       </c>
       <c r="BT3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU3">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="CB3" t="s">
         <v>168</v>
@@ -1598,16 +1598,16 @@
         <v>138</v>
       </c>
       <c r="F4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G4">
         <v>4.8</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I4">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J4">
         <v>3.6</v>
@@ -1622,142 +1622,142 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q4">
         <v>1.94</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="V4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W4">
         <v>1.26</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y4">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AP4">
-        <v>1.38</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>1.26</v>
+        <v>8</v>
       </c>
       <c r="AR4">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>1.38</v>
+        <v>4.7</v>
       </c>
       <c r="AT4">
-        <v>1.38</v>
+        <v>14</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>1.38</v>
+        <v>18</v>
       </c>
       <c r="AX4">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="AY4">
-        <v>1.38</v>
+        <v>15.5</v>
       </c>
       <c r="AZ4">
-        <v>1.38</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="BB4">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="BC4">
-        <v>1.38</v>
+        <v>5.2</v>
       </c>
       <c r="BD4">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BE4">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="BF4">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BG4">
-        <v>1.33</v>
+        <v>12.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1840,19 +1840,19 @@
         <v>139</v>
       </c>
       <c r="F5">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K5">
         <v>3.2</v>
@@ -1861,22 +1861,22 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="O5">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="P5">
         <v>1.46</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="R5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S5">
         <v>6.4</v>
@@ -1888,16 +1888,16 @@
         <v>1.64</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="X5">
         <v>7.4</v>
       </c>
       <c r="Y5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
         <v>36</v>
@@ -1918,10 +1918,10 @@
         <v>120</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH5">
         <v>32</v>
@@ -1954,10 +1954,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT5">
         <v>5.4</v>
@@ -1969,7 +1969,7 @@
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5">
         <v>9.800000000000001</v>
@@ -1978,28 +1978,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG5">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2094,7 +2094,7 @@
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2106,22 +2106,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O6">
         <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R6">
         <v>1.08</v>
       </c>
       <c r="S6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2130,10 +2130,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2348,7 +2348,7 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
         <v>1.25</v>
@@ -2363,7 +2363,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2590,13 +2590,13 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
         <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>1.33</v>
@@ -2605,7 +2605,7 @@
         <v>1.07</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2841,7 +2841,7 @@
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R9">
         <v>1.08</v>
@@ -3074,7 +3074,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="O10">
         <v>1.05</v>
@@ -3083,13 +3083,13 @@
         <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R10">
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3098,10 +3098,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3292,22 +3292,22 @@
         <v>145</v>
       </c>
       <c r="F11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G11">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H11">
+        <v>1.42</v>
+      </c>
+      <c r="I11">
         <v>1.45</v>
       </c>
-      <c r="I11">
-        <v>1.47</v>
-      </c>
       <c r="J11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K11">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
         <v>1.31</v>
@@ -3316,37 +3316,37 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q11">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T11">
         <v>1.83</v>
       </c>
       <c r="U11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="W11">
         <v>1.13</v>
       </c>
       <c r="X11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y11">
         <v>11</v>
@@ -3361,7 +3361,7 @@
         <v>34</v>
       </c>
       <c r="AC11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD11">
         <v>10.5</v>
@@ -3370,19 +3370,19 @@
         <v>15</v>
       </c>
       <c r="AF11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AG11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH11">
         <v>25</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AK11">
         <v>130</v>
@@ -3397,10 +3397,10 @@
         <v>150</v>
       </c>
       <c r="AO11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AP11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11">
         <v>9.4</v>
@@ -3415,103 +3415,103 @@
         <v>23</v>
       </c>
       <c r="AU11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV11">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW11">
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY11">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AZ11">
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BD11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG11">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH11">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BP11">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BV11">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>168</v>
@@ -3534,13 +3534,13 @@
         <v>146</v>
       </c>
       <c r="F12">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G12">
         <v>3.3</v>
       </c>
       <c r="H12">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I12">
         <v>2.36</v>
@@ -3552,7 +3552,7 @@
         <v>3.8</v>
       </c>
       <c r="L12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M12">
         <v>1.05</v>
@@ -3561,13 +3561,13 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
         <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
         <v>1.53</v>
@@ -3579,16 +3579,16 @@
         <v>1.61</v>
       </c>
       <c r="U12">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="V12">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W12">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="X12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y12">
         <v>13.5</v>
@@ -3600,16 +3600,16 @@
         <v>32</v>
       </c>
       <c r="AB12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC12">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
         <v>11.5</v>
       </c>
       <c r="AE12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF12">
         <v>25</v>
@@ -3633,7 +3633,7 @@
         <v>38</v>
       </c>
       <c r="AM12">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN12">
         <v>23</v>
@@ -3660,16 +3660,16 @@
         <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AX12">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AY12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12">
         <v>13.5</v>
@@ -3678,19 +3678,19 @@
         <v>27</v>
       </c>
       <c r="BB12">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BC12">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BD12">
         <v>32</v>
       </c>
       <c r="BE12">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG12">
         <v>12</v>
@@ -3699,7 +3699,7 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3717,7 +3717,7 @@
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP12">
         <v>1000</v>
@@ -3735,13 +3735,13 @@
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BX12">
         <v>1000</v>
@@ -3776,13 +3776,13 @@
         <v>147</v>
       </c>
       <c r="F13">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>600</v>
+        <v>1.26</v>
       </c>
       <c r="H13">
-        <v>1.12</v>
+        <v>12</v>
       </c>
       <c r="I13">
         <v>870</v>
@@ -3800,13 +3800,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q13">
         <v>1.01</v>
@@ -3815,7 +3815,7 @@
         <v>1.94</v>
       </c>
       <c r="S13">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3827,7 +3827,7 @@
         <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4018,22 +4018,22 @@
         <v>148</v>
       </c>
       <c r="F14">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="G14">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="H14">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="I14">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="J14">
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4272,7 +4272,7 @@
         <v>2.94</v>
       </c>
       <c r="J15">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="K15">
         <v>6.8</v>
@@ -4284,7 +4284,7 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="O15">
         <v>1.01</v>
@@ -4296,10 +4296,10 @@
         <v>1.43</v>
       </c>
       <c r="R15">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4308,10 +4308,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4529,7 +4529,7 @@
         <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
         <v>2.12</v>
@@ -4744,19 +4744,19 @@
         <v>151</v>
       </c>
       <c r="F17">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>2.98</v>
       </c>
       <c r="H17">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="I17">
-        <v>870</v>
+        <v>2.94</v>
       </c>
       <c r="J17">
-        <v>1.12</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4768,19 +4768,19 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q17">
         <v>1.52</v>
       </c>
       <c r="R17">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="S17">
         <v>2.52</v>
@@ -4792,10 +4792,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5022,7 +5022,7 @@
         <v>1.58</v>
       </c>
       <c r="R18">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
         <v>2.34</v>
@@ -5228,16 +5228,16 @@
         <v>153</v>
       </c>
       <c r="F19">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G19">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H19">
         <v>6</v>
       </c>
       <c r="I19">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J19">
         <v>3.85</v>
@@ -5246,7 +5246,7 @@
         <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M19">
         <v>1.09</v>
@@ -5267,7 +5267,7 @@
         <v>1.27</v>
       </c>
       <c r="S19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T19">
         <v>2.2</v>
@@ -5276,13 +5276,13 @@
         <v>1.8</v>
       </c>
       <c r="V19">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W19">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
         <v>16.5</v>
@@ -5306,7 +5306,7 @@
         <v>110</v>
       </c>
       <c r="AF19">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG19">
         <v>10.5</v>
@@ -5324,7 +5324,7 @@
         <v>21</v>
       </c>
       <c r="AL19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM19">
         <v>220</v>
@@ -5342,7 +5342,7 @@
         <v>15.5</v>
       </c>
       <c r="AR19">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AS19">
         <v>44</v>
@@ -5366,7 +5366,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA19">
         <v>40</v>
@@ -5387,10 +5387,10 @@
         <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH19">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI19">
         <v>2.82</v>
@@ -5470,28 +5470,28 @@
         <v>154</v>
       </c>
       <c r="F20">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="G20">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="H20">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I20">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N20">
         <v>2.92</v>
@@ -5500,136 +5500,136 @@
         <v>1.47</v>
       </c>
       <c r="P20">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="Q20">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="R20">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S20">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="T20">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="U20">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="V20">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="Z20">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AA20">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD20">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>9</v>
+        <v>1.41</v>
       </c>
       <c r="AQ20">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AR20">
-        <v>6.6</v>
+        <v>1.24</v>
       </c>
       <c r="AS20">
-        <v>12</v>
+        <v>1.41</v>
       </c>
       <c r="AT20">
-        <v>17.5</v>
+        <v>1.41</v>
       </c>
       <c r="AU20">
-        <v>8.199999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="AV20">
-        <v>9.199999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="AW20">
-        <v>18</v>
+        <v>1.41</v>
       </c>
       <c r="AX20">
-        <v>5.8</v>
+        <v>1.41</v>
       </c>
       <c r="AY20">
-        <v>5.5</v>
+        <v>1.41</v>
       </c>
       <c r="AZ20">
-        <v>5.4</v>
+        <v>1.41</v>
       </c>
       <c r="BA20">
-        <v>5.8</v>
+        <v>1.41</v>
       </c>
       <c r="BB20">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="BC20">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="BD20">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="BE20">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="BF20">
-        <v>6</v>
+        <v>1.41</v>
       </c>
       <c r="BG20">
-        <v>10.5</v>
+        <v>1.41</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5712,19 +5712,19 @@
         <v>155</v>
       </c>
       <c r="F21">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="H21">
-        <v>1.1</v>
+        <v>1.91</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="J21">
-        <v>1.1</v>
+        <v>2.96</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5736,22 +5736,22 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>1.08</v>
+        <v>2.48</v>
       </c>
       <c r="O21">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P21">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R21">
         <v>1.08</v>
       </c>
       <c r="S21">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5760,10 +5760,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5877,7 +5877,7 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5913,7 +5913,7 @@
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -5954,7 +5954,7 @@
         <v>156</v>
       </c>
       <c r="F22">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="G22">
         <v>1.5</v>
@@ -5969,22 +5969,22 @@
         <v>4</v>
       </c>
       <c r="K22">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P22">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q22">
         <v>2.02</v>
@@ -6002,7 +6002,7 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W22">
         <v>3</v>
@@ -6116,7 +6116,7 @@
         <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI22">
         <v>1.01</v>
@@ -6125,55 +6125,55 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB22" t="s">
         <v>168</v>
@@ -6196,10 +6196,10 @@
         <v>157</v>
       </c>
       <c r="F23">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="H23">
         <v>1.73</v>
@@ -6211,7 +6211,7 @@
         <v>3.5</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6220,7 +6220,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="O23">
         <v>1.01</v>
@@ -6244,10 +6244,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6462,7 +6462,7 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="O24">
         <v>1.01</v>
@@ -6477,7 +6477,7 @@
         <v>1.07</v>
       </c>
       <c r="S24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6680,19 +6680,19 @@
         <v>159</v>
       </c>
       <c r="F25">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G25">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H25">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I25">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K25">
         <v>3.65</v>
@@ -6704,7 +6704,7 @@
         <v>1.06</v>
       </c>
       <c r="N25">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O25">
         <v>1.3</v>
@@ -6728,10 +6728,10 @@
         <v>2.22</v>
       </c>
       <c r="V25">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W25">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X25">
         <v>15.5</v>
@@ -6797,19 +6797,19 @@
         <v>14.5</v>
       </c>
       <c r="AS25">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT25">
         <v>11</v>
       </c>
       <c r="AU25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV25">
         <v>10</v>
       </c>
       <c r="AW25">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX25">
         <v>19</v>
@@ -6827,16 +6827,16 @@
         <v>9.6</v>
       </c>
       <c r="BC25">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD25">
         <v>36</v>
       </c>
       <c r="BE25">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF25">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG25">
         <v>16.5</v>
@@ -6922,58 +6922,58 @@
         <v>160</v>
       </c>
       <c r="F26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G26">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H26">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26">
         <v>5.2</v>
       </c>
       <c r="K26">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P26">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q26">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R26">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S26">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="T26">
         <v>1.92</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V26">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W26">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="X26">
         <v>24</v>
@@ -6988,7 +6988,7 @@
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC26">
         <v>12</v>
@@ -7003,7 +7003,7 @@
         <v>9.4</v>
       </c>
       <c r="AG26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH26">
         <v>26</v>
@@ -7012,7 +7012,7 @@
         <v>110</v>
       </c>
       <c r="AJ26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK26">
         <v>15</v>
@@ -7024,19 +7024,19 @@
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AO26">
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ26">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AR26">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AS26">
         <v>50</v>
@@ -7057,7 +7057,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY26">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ26">
         <v>21</v>
@@ -7066,7 +7066,7 @@
         <v>60</v>
       </c>
       <c r="BB26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC26">
         <v>13</v>
@@ -7075,10 +7075,10 @@
         <v>25</v>
       </c>
       <c r="BE26">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF26">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG26">
         <v>42</v>
@@ -7099,7 +7099,7 @@
         <v>150</v>
       </c>
       <c r="BM26">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN26">
         <v>4.1</v>
@@ -7114,34 +7114,34 @@
         <v>7.4</v>
       </c>
       <c r="BR26">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT26">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU26">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV26">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BW26">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX26">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY26">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ26">
         <v>15.5</v>
       </c>
       <c r="CA26">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB26" t="s">
         <v>168</v>
@@ -7167,13 +7167,13 @@
         <v>1.57</v>
       </c>
       <c r="G27">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H27">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J27">
         <v>4.6</v>
@@ -7188,25 +7188,25 @@
         <v>1.04</v>
       </c>
       <c r="N27">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O27">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P27">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q27">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R27">
         <v>1.56</v>
       </c>
       <c r="S27">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T27">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U27">
         <v>2.18</v>
@@ -7215,13 +7215,13 @@
         <v>1.18</v>
       </c>
       <c r="W27">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X27">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Z27">
         <v>65</v>
@@ -7236,19 +7236,19 @@
         <v>11</v>
       </c>
       <c r="AD27">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE27">
         <v>90</v>
       </c>
       <c r="AF27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG27">
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI27">
         <v>85</v>
@@ -7257,7 +7257,7 @@
         <v>15.5</v>
       </c>
       <c r="AK27">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL27">
         <v>36</v>
@@ -7278,10 +7278,10 @@
         <v>22</v>
       </c>
       <c r="AR27">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AS27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT27">
         <v>9.6</v>
@@ -7293,10 +7293,10 @@
         <v>20</v>
       </c>
       <c r="AW27">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX27">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY27">
         <v>9.199999999999999</v>
@@ -7305,7 +7305,7 @@
         <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB27">
         <v>13.5</v>
@@ -7314,76 +7314,76 @@
         <v>14</v>
       </c>
       <c r="BD27">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BE27">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF27">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG27">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH27">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BJ27">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BK27">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BL27">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
         <v>21</v>
       </c>
       <c r="BN27">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BO27">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BP27">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BQ27">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR27">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BS27">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BT27">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BU27">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BX27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BZ27">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CA27">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="CB27" t="s">
         <v>168</v>
@@ -7406,16 +7406,16 @@
         <v>162</v>
       </c>
       <c r="F28">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="G28">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H28">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I28">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J28">
         <v>4.2</v>
@@ -7424,67 +7424,67 @@
         <v>4.4</v>
       </c>
       <c r="L28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O28">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P28">
+        <v>2.52</v>
+      </c>
+      <c r="Q28">
+        <v>1.62</v>
+      </c>
+      <c r="R28">
+        <v>1.61</v>
+      </c>
+      <c r="S28">
+        <v>2.56</v>
+      </c>
+      <c r="T28">
+        <v>1.64</v>
+      </c>
+      <c r="U28">
         <v>2.48</v>
       </c>
-      <c r="Q28">
-        <v>1.6</v>
-      </c>
-      <c r="R28">
-        <v>1.6</v>
-      </c>
-      <c r="S28">
-        <v>2.44</v>
-      </c>
-      <c r="T28">
-        <v>1.63</v>
-      </c>
-      <c r="U28">
-        <v>2.5</v>
-      </c>
       <c r="V28">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W28">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="X28">
         <v>23</v>
       </c>
       <c r="Y28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z28">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA28">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC28">
         <v>10</v>
       </c>
       <c r="AD28">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE28">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF28">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG28">
         <v>10.5</v>
@@ -7493,49 +7493,49 @@
         <v>17</v>
       </c>
       <c r="AI28">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ28">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK28">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL28">
         <v>28</v>
       </c>
       <c r="AM28">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
         <v>8</v>
       </c>
       <c r="AO28">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP28">
         <v>21</v>
       </c>
       <c r="AQ28">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR28">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS28">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT28">
         <v>11</v>
       </c>
       <c r="AU28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW28">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX28">
         <v>11.5</v>
@@ -7547,7 +7547,7 @@
         <v>15</v>
       </c>
       <c r="BA28">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB28">
         <v>18</v>
@@ -7559,73 +7559,73 @@
         <v>23</v>
       </c>
       <c r="BE28">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF28">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG28">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH28">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>3.85</v>
+        <v>1.49</v>
       </c>
       <c r="BJ28">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL28">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>21</v>
+        <v>2.12</v>
       </c>
       <c r="BN28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO28">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>9.800000000000001</v>
+        <v>2.12</v>
       </c>
       <c r="BR28">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>16.5</v>
+        <v>2.12</v>
       </c>
       <c r="BT28">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV28">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>24</v>
+        <v>2.12</v>
       </c>
       <c r="BX28">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>27</v>
+        <v>2.12</v>
       </c>
       <c r="BZ28">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>11.5</v>
+        <v>2.12</v>
       </c>
       <c r="CB28" t="s">
         <v>168</v>
@@ -7648,7 +7648,7 @@
         <v>163</v>
       </c>
       <c r="F29">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G29">
         <v>1.27</v>
@@ -7657,43 +7657,43 @@
         <v>13</v>
       </c>
       <c r="I29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J29">
         <v>7</v>
       </c>
       <c r="K29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L29">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M29">
         <v>1.02</v>
       </c>
       <c r="N29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O29">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Q29">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R29">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="S29">
         <v>2.2</v>
       </c>
       <c r="T29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U29">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V29">
         <v>1.07</v>
@@ -7711,13 +7711,13 @@
         <v>150</v>
       </c>
       <c r="AA29">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="AB29">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD29">
         <v>50</v>
@@ -7741,7 +7741,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK29">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL29">
         <v>38</v>
@@ -7750,10 +7750,10 @@
         <v>160</v>
       </c>
       <c r="AN29">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AO29">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP29">
         <v>21</v>
@@ -7780,7 +7780,7 @@
         <v>48</v>
       </c>
       <c r="AX29">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY29">
         <v>10.5</v>
@@ -7792,7 +7792,7 @@
         <v>44</v>
       </c>
       <c r="BB29">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC29">
         <v>12.5</v>
@@ -7804,70 +7804,70 @@
         <v>44</v>
       </c>
       <c r="BF29">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BG29">
         <v>50</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI29">
-        <v>1.54</v>
+        <v>4.4</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK29">
-        <v>2.14</v>
+        <v>8.4</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM29">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BN29">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BO29">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BQ29">
+        <v>5.8</v>
+      </c>
+      <c r="BR29">
+        <v>22</v>
+      </c>
+      <c r="BS29">
+        <v>8.4</v>
+      </c>
+      <c r="BT29">
+        <v>16.5</v>
+      </c>
+      <c r="BU29">
+        <v>7.4</v>
+      </c>
+      <c r="BV29">
+        <v>110</v>
+      </c>
+      <c r="BW29">
+        <v>11</v>
+      </c>
+      <c r="BX29">
+        <v>90</v>
+      </c>
+      <c r="BY29">
+        <v>10.5</v>
+      </c>
+      <c r="BZ29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CA29">
         <v>5.3</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>2.14</v>
-      </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
-        <v>2.14</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>9.6</v>
-      </c>
-      <c r="BX29">
-        <v>1000</v>
-      </c>
-      <c r="BY29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
-        <v>4.5</v>
       </c>
       <c r="CB29" t="s">
         <v>168</v>
@@ -7896,7 +7896,7 @@
         <v>1.8</v>
       </c>
       <c r="H30">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -7914,22 +7914,22 @@
         <v>1.04</v>
       </c>
       <c r="N30">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="O30">
         <v>1.19</v>
       </c>
       <c r="P30">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="Q30">
         <v>1.59</v>
       </c>
       <c r="R30">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="S30">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T30">
         <v>1.61</v>
@@ -7947,22 +7947,22 @@
         <v>24</v>
       </c>
       <c r="Y30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z30">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB30">
         <v>13</v>
       </c>
       <c r="AC30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE30">
         <v>55</v>
@@ -7977,37 +7977,37 @@
         <v>16</v>
       </c>
       <c r="AI30">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AJ30">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK30">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL30">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN30">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO30">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP30">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ30">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR30">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AS30">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT30">
         <v>11.5</v>
@@ -8019,19 +8019,19 @@
         <v>17</v>
       </c>
       <c r="AW30">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AX30">
         <v>12</v>
       </c>
       <c r="AY30">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BB30">
         <v>17.5</v>
@@ -8043,25 +8043,25 @@
         <v>23</v>
       </c>
       <c r="BE30">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG30">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BH30">
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.98</v>
+        <v>6.2</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8073,13 +8073,13 @@
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>1.66</v>
+        <v>3.9</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BR30">
         <v>1000</v>
@@ -8138,10 +8138,10 @@
         <v>3.1</v>
       </c>
       <c r="H31">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I31">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J31">
         <v>3.65</v>
@@ -8150,37 +8150,37 @@
         <v>3.7</v>
       </c>
       <c r="L31">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M31">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N31">
         <v>4.7</v>
       </c>
       <c r="O31">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P31">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q31">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R31">
         <v>1.48</v>
       </c>
       <c r="S31">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T31">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U31">
         <v>2.46</v>
       </c>
       <c r="V31">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W31">
         <v>1.47</v>
@@ -8189,10 +8189,10 @@
         <v>18</v>
       </c>
       <c r="Y31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA31">
         <v>34</v>
@@ -8222,10 +8222,10 @@
         <v>34</v>
       </c>
       <c r="AJ31">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AK31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL31">
         <v>38</v>
@@ -8234,10 +8234,10 @@
         <v>70</v>
       </c>
       <c r="AN31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO31">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP31">
         <v>16.5</v>
@@ -8246,7 +8246,7 @@
         <v>12</v>
       </c>
       <c r="AR31">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS31">
         <v>29</v>
@@ -8255,7 +8255,7 @@
         <v>13</v>
       </c>
       <c r="AU31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV31">
         <v>10.5</v>
@@ -8267,7 +8267,7 @@
         <v>19</v>
       </c>
       <c r="AY31">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ31">
         <v>13</v>
@@ -8297,13 +8297,13 @@
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8315,7 +8315,7 @@
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP31">
         <v>1000</v>
@@ -8333,7 +8333,7 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8377,7 +8377,7 @@
         <v>2.88</v>
       </c>
       <c r="G32">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H32">
         <v>2.6</v>
@@ -8392,28 +8392,28 @@
         <v>3.65</v>
       </c>
       <c r="L32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M32">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N32">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O32">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P32">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q32">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R32">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S32">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T32">
         <v>1.68</v>
@@ -8422,10 +8422,10 @@
         <v>2.36</v>
       </c>
       <c r="V32">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X32">
         <v>17</v>
@@ -8437,7 +8437,7 @@
         <v>18.5</v>
       </c>
       <c r="AA32">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB32">
         <v>13.5</v>
@@ -8452,7 +8452,7 @@
         <v>27</v>
       </c>
       <c r="AF32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG32">
         <v>13</v>
@@ -8497,10 +8497,10 @@
         <v>12.5</v>
       </c>
       <c r="AU32">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV32">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW32">
         <v>23</v>
@@ -8515,7 +8515,7 @@
         <v>14.5</v>
       </c>
       <c r="BA32">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB32">
         <v>38</v>
@@ -8530,16 +8530,16 @@
         <v>34</v>
       </c>
       <c r="BF32">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG32">
         <v>17.5</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI32">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
@@ -8557,7 +8557,7 @@
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP32">
         <v>1000</v>
@@ -8575,13 +8575,13 @@
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX32">
         <v>1000</v>
@@ -8616,61 +8616,61 @@
         <v>167</v>
       </c>
       <c r="F33">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M33">
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O33">
         <v>1.22</v>
       </c>
       <c r="P33">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q33">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R33">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S33">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T33">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W33">
         <v>1.35</v>
       </c>
       <c r="X33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y33">
         <v>13</v>
@@ -8712,13 +8712,13 @@
         <v>38</v>
       </c>
       <c r="AL33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM33">
         <v>65</v>
       </c>
       <c r="AN33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO33">
         <v>10.5</v>
@@ -8754,13 +8754,13 @@
         <v>14</v>
       </c>
       <c r="AZ33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA33">
         <v>25</v>
       </c>
       <c r="BB33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC33">
         <v>34</v>
@@ -8772,10 +8772,10 @@
         <v>55</v>
       </c>
       <c r="BF33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH33">
         <v>4</v>
@@ -8784,16 +8784,16 @@
         <v>3.65</v>
       </c>
       <c r="BJ33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK33">
         <v>7.8</v>
       </c>
       <c r="BL33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM33">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN33">
         <v>7.2</v>
@@ -8805,37 +8805,37 @@
         <v>34</v>
       </c>
       <c r="BQ33">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR33">
         <v>40</v>
       </c>
       <c r="BS33">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT33">
         <v>5.1</v>
       </c>
       <c r="BU33">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV33">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BW33">
         <v>11.5</v>
       </c>
       <c r="BX33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY33">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ33">
         <v>21</v>
       </c>
       <c r="CA33">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB33" t="s">
         <v>168</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -520,7 +520,7 @@
     <t>Villarreal</t>
   </si>
   <si>
-    <t>2026-09-15 19:54:03</t>
+    <t>2026-09-15 22:16:00</t>
   </si>
 </sst>
 </file>
@@ -1114,22 +1114,22 @@
         <v>136</v>
       </c>
       <c r="F2">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="G2">
-        <v>990</v>
+        <v>1.82</v>
       </c>
       <c r="H2">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>990</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2">
-        <v>1.19</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1138,22 +1138,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.3</v>
+        <v>2.58</v>
       </c>
       <c r="O2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P2">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="Q2">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="T2">
         <v>1.11</v>
@@ -1162,10 +1162,10 @@
         <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB2">
         <v>1000</v>
@@ -1228,7 +1228,7 @@
         <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
@@ -1249,7 +1249,7 @@
         <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ2">
         <v>1.01</v>
@@ -1356,16 +1356,16 @@
         <v>137</v>
       </c>
       <c r="F3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H3">
         <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1380,7 +1380,7 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1398,7 +1398,7 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
         <v>1.62</v>
@@ -1407,19 +1407,19 @@
         <v>1.23</v>
       </c>
       <c r="W3">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y3">
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA3">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB3">
         <v>6.2</v>
@@ -1443,10 +1443,10 @@
         <v>32</v>
       </c>
       <c r="AI3">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK3">
         <v>32</v>
@@ -1455,7 +1455,7 @@
         <v>90</v>
       </c>
       <c r="AM3">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AN3">
         <v>32</v>
@@ -1473,7 +1473,7 @@
         <v>30</v>
       </c>
       <c r="AS3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT3">
         <v>5.6</v>
@@ -1488,25 +1488,25 @@
         <v>14</v>
       </c>
       <c r="AX3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3">
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BC3">
         <v>27</v>
       </c>
       <c r="BD3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE3">
         <v>13</v>
@@ -1521,7 +1521,7 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BJ3">
         <v>18</v>
@@ -1533,7 +1533,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BN3">
         <v>5.3</v>
@@ -1545,13 +1545,13 @@
         <v>24</v>
       </c>
       <c r="BQ3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BT3">
         <v>11.5</v>
@@ -1563,19 +1563,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CB3" t="s">
         <v>168</v>
@@ -1613,7 +1613,7 @@
         <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1622,7 +1622,7 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
         <v>1.33</v>
@@ -1631,16 +1631,16 @@
         <v>1.93</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
         <v>1.36</v>
       </c>
       <c r="S4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
         <v>2.1</v>
@@ -1658,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
         <v>27</v>
@@ -1673,7 +1673,7 @@
         <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF4">
         <v>42</v>
@@ -1715,7 +1715,7 @@
         <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT4">
         <v>14</v>
@@ -1730,7 +1730,7 @@
         <v>18</v>
       </c>
       <c r="AX4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AY4">
         <v>15.5</v>
@@ -1739,22 +1739,22 @@
         <v>16</v>
       </c>
       <c r="BA4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC4">
+        <v>5.1</v>
+      </c>
+      <c r="BD4">
         <v>5.2</v>
       </c>
-      <c r="BD4">
+      <c r="BE4">
         <v>5.3</v>
       </c>
-      <c r="BE4">
-        <v>5.4</v>
-      </c>
       <c r="BF4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG4">
         <v>12.5</v>
@@ -1846,7 +1846,7 @@
         <v>2.22</v>
       </c>
       <c r="H5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
         <v>5.2</v>
@@ -1861,7 +1861,7 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N5">
         <v>2.24</v>
@@ -1876,10 +1876,10 @@
         <v>2.76</v>
       </c>
       <c r="R5">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S5">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T5">
         <v>2.38</v>
@@ -1897,7 +1897,7 @@
         <v>7.4</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z5">
         <v>36</v>
@@ -1918,7 +1918,7 @@
         <v>120</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG5">
         <v>13</v>
@@ -1954,10 +1954,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5">
         <v>5.4</v>
@@ -1969,7 +1969,7 @@
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AX5">
         <v>9.800000000000001</v>
@@ -1978,28 +1978,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
+        <v>7</v>
+      </c>
+      <c r="BA5">
         <v>8.199999999999999</v>
       </c>
-      <c r="BA5">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BB5">
+        <v>7</v>
+      </c>
+      <c r="BC5">
+        <v>7.2</v>
+      </c>
+      <c r="BD5">
+        <v>8.4</v>
+      </c>
+      <c r="BE5">
+        <v>8.4</v>
+      </c>
+      <c r="BF5">
+        <v>7.2</v>
+      </c>
+      <c r="BG5">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BC5">
-        <v>8.4</v>
-      </c>
-      <c r="BD5">
-        <v>8.6</v>
-      </c>
-      <c r="BE5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF5">
-        <v>8.4</v>
-      </c>
-      <c r="BG5">
-        <v>9</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2085,16 +2085,16 @@
         <v>1.12</v>
       </c>
       <c r="G6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2106,22 +2106,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
+        <v>1.01</v>
+      </c>
+      <c r="O6">
+        <v>1.24</v>
+      </c>
+      <c r="P6">
         <v>1.29</v>
       </c>
-      <c r="O6">
-        <v>1.01</v>
-      </c>
-      <c r="P6">
-        <v>1.28</v>
-      </c>
       <c r="Q6">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="R6">
         <v>1.08</v>
       </c>
       <c r="S6">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2133,7 +2133,7 @@
         <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2814,7 +2814,7 @@
         <v>600</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="I9">
         <v>1.62</v>
@@ -2841,7 +2841,7 @@
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R9">
         <v>1.08</v>
@@ -3074,13 +3074,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
         <v>1.05</v>
@@ -3089,7 +3089,7 @@
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3292,13 +3292,13 @@
         <v>145</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I11">
         <v>1.45</v>
@@ -3307,10 +3307,10 @@
         <v>5.2</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M11">
         <v>1.04</v>
@@ -3343,10 +3343,10 @@
         <v>3.2</v>
       </c>
       <c r="W11">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y11">
         <v>11</v>
@@ -3364,7 +3364,7 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE11">
         <v>15</v>
@@ -3376,19 +3376,19 @@
         <v>34</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AK11">
         <v>130</v>
       </c>
       <c r="AL11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM11">
         <v>130</v>
@@ -3409,7 +3409,7 @@
         <v>8.4</v>
       </c>
       <c r="AS11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT11">
         <v>23</v>
@@ -3433,25 +3433,25 @@
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB11">
         <v>10</v>
       </c>
       <c r="BC11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD11">
         <v>9.6</v>
       </c>
       <c r="BE11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3537,13 +3537,13 @@
         <v>3.2</v>
       </c>
       <c r="G12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H12">
         <v>2.34</v>
       </c>
       <c r="I12">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J12">
         <v>3.7</v>
@@ -3564,10 +3564,10 @@
         <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
         <v>1.53</v>
@@ -3579,13 +3579,13 @@
         <v>1.61</v>
       </c>
       <c r="U12">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X12">
         <v>19</v>
@@ -3690,7 +3690,7 @@
         <v>50</v>
       </c>
       <c r="BF12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG12">
         <v>12</v>
@@ -3779,7 +3779,7 @@
         <v>1.1</v>
       </c>
       <c r="G13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -4018,22 +4018,22 @@
         <v>148</v>
       </c>
       <c r="F14">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="G14">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="H14">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="I14">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4045,19 +4045,19 @@
         <v>3.6</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
         <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
         <v>1.37</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4066,10 +4066,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4287,7 +4287,7 @@
         <v>2.68</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="P15">
         <v>2.22</v>
@@ -4529,7 +4529,7 @@
         <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="P16">
         <v>2.12</v>
@@ -4747,19 +4747,19 @@
         <v>2.22</v>
       </c>
       <c r="G17">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="H17">
         <v>2.22</v>
       </c>
       <c r="I17">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="J17">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4768,19 +4768,19 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O17">
         <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q17">
         <v>1.52</v>
       </c>
       <c r="R17">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S17">
         <v>2.52</v>
@@ -4792,10 +4792,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5228,7 +5228,7 @@
         <v>153</v>
       </c>
       <c r="F19">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G19">
         <v>1.74</v>
@@ -5294,7 +5294,7 @@
         <v>200</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC19">
         <v>8.6</v>
@@ -5339,7 +5339,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ19">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR19">
         <v>25</v>
@@ -5366,7 +5366,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA19">
         <v>40</v>
@@ -5405,7 +5405,7 @@
         <v>230</v>
       </c>
       <c r="BM19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN19">
         <v>4.1</v>
@@ -5423,7 +5423,7 @@
         <v>40</v>
       </c>
       <c r="BS19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT19">
         <v>9.4</v>
@@ -5435,19 +5435,19 @@
         <v>75</v>
       </c>
       <c r="BW19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX19">
         <v>90</v>
       </c>
       <c r="BY19">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ19">
         <v>36</v>
       </c>
       <c r="CA19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="s">
         <v>168</v>
@@ -5470,7 +5470,7 @@
         <v>154</v>
       </c>
       <c r="F20">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G20">
         <v>13</v>
@@ -5479,13 +5479,13 @@
         <v>1.49</v>
       </c>
       <c r="I20">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="J20">
         <v>3.65</v>
       </c>
       <c r="K20">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5500,16 +5500,16 @@
         <v>1.47</v>
       </c>
       <c r="P20">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q20">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S20">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="T20">
         <v>2.34</v>
@@ -5518,13 +5518,13 @@
         <v>1.53</v>
       </c>
       <c r="V20">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="W20">
         <v>1.09</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y20">
         <v>970</v>
@@ -5581,55 +5581,55 @@
         <v>1.41</v>
       </c>
       <c r="AQ20">
-        <v>4.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AS20">
+        <v>1.54</v>
+      </c>
+      <c r="AT20">
+        <v>1.54</v>
+      </c>
+      <c r="AU20">
         <v>1.41</v>
       </c>
-      <c r="AT20">
-        <v>1.41</v>
-      </c>
-      <c r="AU20">
-        <v>1.29</v>
-      </c>
       <c r="AV20">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AW20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AX20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AY20">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AZ20">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="BA20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BB20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BC20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BD20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BE20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BF20">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="BG20">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5671,7 +5671,7 @@
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BV20">
         <v>1000</v>
@@ -5712,7 +5712,7 @@
         <v>155</v>
       </c>
       <c r="F21">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G21">
         <v>5.7</v>
@@ -5754,7 +5754,7 @@
         <v>3</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U21">
         <v>1.01</v>
@@ -5954,13 +5954,13 @@
         <v>156</v>
       </c>
       <c r="F22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G22">
         <v>1.5</v>
       </c>
       <c r="H22">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>870</v>
@@ -5969,7 +5969,7 @@
         <v>4</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5978,13 +5978,13 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="O22">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P22">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="Q22">
         <v>2.02</v>
@@ -6002,7 +6002,7 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
         <v>3</v>
@@ -6119,7 +6119,7 @@
         <v>3.8</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
@@ -6211,7 +6211,7 @@
         <v>3.5</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6223,7 +6223,7 @@
         <v>2.74</v>
       </c>
       <c r="O23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P23">
         <v>2.28</v>
@@ -6465,13 +6465,13 @@
         <v>1.24</v>
       </c>
       <c r="O24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P24">
         <v>1.24</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R24">
         <v>1.07</v>
@@ -6680,7 +6680,7 @@
         <v>159</v>
       </c>
       <c r="F25">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G25">
         <v>3.15</v>
@@ -6689,10 +6689,10 @@
         <v>2.44</v>
       </c>
       <c r="I25">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J25">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K25">
         <v>3.65</v>
@@ -6710,7 +6710,7 @@
         <v>1.3</v>
       </c>
       <c r="P25">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q25">
         <v>1.89</v>
@@ -6725,7 +6725,7 @@
         <v>1.7</v>
       </c>
       <c r="U25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
         <v>1.64</v>
@@ -6797,7 +6797,7 @@
         <v>14.5</v>
       </c>
       <c r="AS25">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT25">
         <v>11</v>
@@ -6821,22 +6821,22 @@
         <v>14.5</v>
       </c>
       <c r="BA25">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25">
         <v>9.6</v>
       </c>
       <c r="BC25">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BD25">
         <v>36</v>
       </c>
       <c r="BE25">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF25">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG25">
         <v>16.5</v>
@@ -6946,7 +6946,7 @@
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O26">
         <v>1.22</v>
@@ -6958,16 +6958,16 @@
         <v>1.67</v>
       </c>
       <c r="R26">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S26">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T26">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U26">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V26">
         <v>1.13</v>
@@ -6979,7 +6979,7 @@
         <v>24</v>
       </c>
       <c r="Y26">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z26">
         <v>85</v>
@@ -6988,7 +6988,7 @@
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC26">
         <v>12</v>
@@ -7000,13 +7000,13 @@
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI26">
         <v>110</v>
@@ -7033,16 +7033,16 @@
         <v>19.5</v>
       </c>
       <c r="AQ26">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AR26">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AS26">
         <v>50</v>
       </c>
       <c r="AT26">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU26">
         <v>10.5</v>
@@ -7057,7 +7057,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY26">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26">
         <v>21</v>
@@ -7078,7 +7078,7 @@
         <v>70</v>
       </c>
       <c r="BF26">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG26">
         <v>42</v>
@@ -7099,7 +7099,7 @@
         <v>150</v>
       </c>
       <c r="BM26">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN26">
         <v>4.1</v>
@@ -7117,28 +7117,28 @@
         <v>24</v>
       </c>
       <c r="BS26">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT26">
         <v>12.5</v>
       </c>
       <c r="BU26">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV26">
         <v>70</v>
       </c>
       <c r="BW26">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX26">
         <v>70</v>
       </c>
       <c r="BY26">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ26">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="CA26">
         <v>9.199999999999999</v>
@@ -7173,13 +7173,13 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
         <v>4.6</v>
       </c>
       <c r="K27">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>1.32</v>
@@ -7218,10 +7218,10 @@
         <v>2.66</v>
       </c>
       <c r="X27">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y27">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Z27">
         <v>65</v>
@@ -7236,13 +7236,13 @@
         <v>11</v>
       </c>
       <c r="AD27">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE27">
         <v>90</v>
       </c>
       <c r="AF27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG27">
         <v>10.5</v>
@@ -7257,7 +7257,7 @@
         <v>15.5</v>
       </c>
       <c r="AK27">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL27">
         <v>36</v>
@@ -7278,10 +7278,10 @@
         <v>22</v>
       </c>
       <c r="AR27">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS27">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT27">
         <v>9.6</v>
@@ -7293,19 +7293,19 @@
         <v>20</v>
       </c>
       <c r="AW27">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX27">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY27">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ27">
         <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB27">
         <v>13.5</v>
@@ -7314,16 +7314,16 @@
         <v>14</v>
       </c>
       <c r="BD27">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE27">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27">
         <v>6</v>
       </c>
       <c r="BG27">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7383,7 +7383,7 @@
         <v>20</v>
       </c>
       <c r="CA27">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB27" t="s">
         <v>168</v>
@@ -7406,10 +7406,10 @@
         <v>162</v>
       </c>
       <c r="F28">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G28">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H28">
         <v>4.8</v>
@@ -7418,7 +7418,7 @@
         <v>4.9</v>
       </c>
       <c r="J28">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K28">
         <v>4.4</v>
@@ -7451,13 +7451,13 @@
         <v>1.64</v>
       </c>
       <c r="U28">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V28">
         <v>1.25</v>
       </c>
       <c r="W28">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X28">
         <v>23</v>
@@ -7499,7 +7499,7 @@
         <v>19.5</v>
       </c>
       <c r="AK28">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL28">
         <v>28</v>
@@ -7508,10 +7508,10 @@
         <v>1000</v>
       </c>
       <c r="AN28">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO28">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP28">
         <v>21</v>
@@ -7529,7 +7529,7 @@
         <v>11</v>
       </c>
       <c r="AU28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV28">
         <v>17</v>
@@ -7541,7 +7541,7 @@
         <v>11.5</v>
       </c>
       <c r="AY28">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28">
         <v>15</v>
@@ -7559,19 +7559,19 @@
         <v>23</v>
       </c>
       <c r="BE28">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF28">
         <v>7.2</v>
       </c>
       <c r="BG28">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
@@ -7583,10 +7583,10 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BN28">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
         <v>3.55</v>
@@ -7595,37 +7595,37 @@
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CB28" t="s">
         <v>168</v>
@@ -7672,28 +7672,28 @@
         <v>1.02</v>
       </c>
       <c r="N29">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q29">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R29">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S29">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T29">
         <v>2.06</v>
       </c>
       <c r="U29">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V29">
         <v>1.07</v>
@@ -7702,7 +7702,7 @@
         <v>4.7</v>
       </c>
       <c r="X29">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y29">
         <v>55</v>
@@ -7717,7 +7717,7 @@
         <v>12.5</v>
       </c>
       <c r="AC29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD29">
         <v>50</v>
@@ -7726,16 +7726,16 @@
         <v>220</v>
       </c>
       <c r="AF29">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG29">
         <v>11.5</v>
       </c>
       <c r="AH29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ29">
         <v>9.800000000000001</v>
@@ -7747,16 +7747,16 @@
         <v>38</v>
       </c>
       <c r="AM29">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AO29">
         <v>230</v>
       </c>
       <c r="AP29">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AQ29">
         <v>42</v>
@@ -7768,7 +7768,7 @@
         <v>55</v>
       </c>
       <c r="AT29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU29">
         <v>14</v>
@@ -7792,13 +7792,13 @@
         <v>44</v>
       </c>
       <c r="BB29">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC29">
         <v>12.5</v>
       </c>
       <c r="BD29">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE29">
         <v>44</v>
@@ -7810,64 +7810,64 @@
         <v>50</v>
       </c>
       <c r="BH29">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ29">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>8.4</v>
+        <v>2.06</v>
       </c>
       <c r="BL29">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>3.3</v>
+      </c>
+      <c r="BP29">
+        <v>8.6</v>
+      </c>
+      <c r="BQ29">
+        <v>1.67</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>2.06</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>2.06</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>8</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>8</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
         <v>3.95</v>
-      </c>
-      <c r="BO29">
-        <v>3.5</v>
-      </c>
-      <c r="BP29">
-        <v>6.8</v>
-      </c>
-      <c r="BQ29">
-        <v>5.8</v>
-      </c>
-      <c r="BR29">
-        <v>22</v>
-      </c>
-      <c r="BS29">
-        <v>8.4</v>
-      </c>
-      <c r="BT29">
-        <v>16.5</v>
-      </c>
-      <c r="BU29">
-        <v>7.4</v>
-      </c>
-      <c r="BV29">
-        <v>110</v>
-      </c>
-      <c r="BW29">
-        <v>11</v>
-      </c>
-      <c r="BX29">
-        <v>90</v>
-      </c>
-      <c r="BY29">
-        <v>10.5</v>
-      </c>
-      <c r="BZ29">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CA29">
-        <v>5.3</v>
       </c>
       <c r="CB29" t="s">
         <v>168</v>
@@ -7890,10 +7890,10 @@
         <v>164</v>
       </c>
       <c r="F30">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G30">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H30">
         <v>4.8</v>
@@ -7902,7 +7902,7 @@
         <v>5</v>
       </c>
       <c r="J30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K30">
         <v>4.3</v>
@@ -7941,7 +7941,7 @@
         <v>1.25</v>
       </c>
       <c r="W30">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X30">
         <v>24</v>
@@ -7983,7 +7983,7 @@
         <v>20</v>
       </c>
       <c r="AK30">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL30">
         <v>27</v>
@@ -7995,7 +7995,7 @@
         <v>7.6</v>
       </c>
       <c r="AO30">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP30">
         <v>22</v>
@@ -8079,7 +8079,7 @@
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="BR30">
         <v>1000</v>
@@ -8153,13 +8153,13 @@
         <v>1.36</v>
       </c>
       <c r="M31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N31">
         <v>4.7</v>
       </c>
       <c r="O31">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P31">
         <v>2.26</v>
@@ -8222,10 +8222,10 @@
         <v>34</v>
       </c>
       <c r="AJ31">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL31">
         <v>38</v>
@@ -8407,7 +8407,7 @@
         <v>2.12</v>
       </c>
       <c r="Q32">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R32">
         <v>1.44</v>
@@ -8479,7 +8479,7 @@
         <v>23</v>
       </c>
       <c r="AO32">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP32">
         <v>15</v>
@@ -8488,7 +8488,7 @@
         <v>11.5</v>
       </c>
       <c r="AR32">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS32">
         <v>34</v>
@@ -8542,7 +8542,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK32">
         <v>6.4</v>
@@ -8581,7 +8581,7 @@
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX32">
         <v>1000</v>
@@ -8616,22 +8616,22 @@
         <v>167</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L33">
         <v>1.33</v>
@@ -8652,16 +8652,16 @@
         <v>1.66</v>
       </c>
       <c r="R33">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S33">
         <v>2.68</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V33">
         <v>1.94</v>
@@ -8670,7 +8670,7 @@
         <v>1.35</v>
       </c>
       <c r="X33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y33">
         <v>13</v>
@@ -8718,13 +8718,13 @@
         <v>65</v>
       </c>
       <c r="AN33">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO33">
         <v>10.5</v>
       </c>
       <c r="AP33">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AQ33">
         <v>12</v>
@@ -8733,7 +8733,7 @@
         <v>13.5</v>
       </c>
       <c r="AS33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT33">
         <v>18</v>
@@ -8748,7 +8748,7 @@
         <v>17.5</v>
       </c>
       <c r="AX33">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY33">
         <v>14</v>
@@ -8769,7 +8769,7 @@
         <v>36</v>
       </c>
       <c r="BE33">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF33">
         <v>26</v>
@@ -8811,7 +8811,7 @@
         <v>40</v>
       </c>
       <c r="BS33">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT33">
         <v>5.1</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="175">
   <si>
     <t>League</t>
   </si>
@@ -328,6 +328,12 @@
     <t>19:30:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Blooming Santa Cruz</t>
   </si>
   <si>
@@ -370,24 +376,24 @@
     <t>Kristianstads</t>
   </si>
   <si>
+    <t>Skovde AIK</t>
+  </si>
+  <si>
     <t>Eskilsminne</t>
   </si>
   <si>
-    <t>Skovde AIK</t>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>US Biskra</t>
   </si>
   <si>
     <t>Vasalunds IF</t>
   </si>
   <si>
-    <t>Betis</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>US Biskra</t>
-  </si>
-  <si>
     <t>Orlando Pirates (SA)</t>
   </si>
   <si>
@@ -397,12 +403,12 @@
     <t>Assyriska FF</t>
   </si>
   <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
     <t>AFC Wimbledon</t>
   </si>
   <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
     <t>Lillestrom</t>
   </si>
   <si>
@@ -424,6 +430,12 @@
     <t>Malaga</t>
   </si>
   <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
+    <t>Atletico Bucaramanga</t>
+  </si>
+  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
@@ -466,24 +478,24 @@
     <t>BK Olympic</t>
   </si>
   <si>
+    <t>FC Trollhattan</t>
+  </si>
+  <si>
     <t>Tvaakers</t>
   </si>
   <si>
-    <t>FC Trollhattan</t>
+    <t>Getafe</t>
+  </si>
+  <si>
+    <t>Pyramids</t>
+  </si>
+  <si>
+    <t>Belouizdad</t>
   </si>
   <si>
     <t>Hammarby TFF</t>
   </si>
   <si>
-    <t>Getafe</t>
-  </si>
-  <si>
-    <t>Pyramids</t>
-  </si>
-  <si>
-    <t>Belouizdad</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
@@ -493,12 +505,12 @@
     <t>AFC Eskilstuna</t>
   </si>
   <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
     <t>MK Dons</t>
   </si>
   <si>
-    <t>Lech Poznan</t>
-  </si>
-  <si>
     <t>Torreense</t>
   </si>
   <si>
@@ -520,7 +532,13 @@
     <t>Villarreal</t>
   </si>
   <si>
-    <t>2026-09-15 22:16:00</t>
+    <t>Oriente Petrolero</t>
+  </si>
+  <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
+    <t>2026-09-16 00:29:29</t>
   </si>
 </sst>
 </file>
@@ -852,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1108,172 +1126,172 @@
         <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F2">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="G2">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I2">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>500</v>
+        <v>5.4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
+        <v>5.7</v>
+      </c>
+      <c r="O2">
+        <v>1.16</v>
+      </c>
+      <c r="P2">
+        <v>2.66</v>
+      </c>
+      <c r="Q2">
+        <v>1.49</v>
+      </c>
+      <c r="R2">
+        <v>1.65</v>
+      </c>
+      <c r="S2">
+        <v>2.22</v>
+      </c>
+      <c r="T2">
+        <v>1.56</v>
+      </c>
+      <c r="U2">
+        <v>2.3</v>
+      </c>
+      <c r="V2">
+        <v>1.18</v>
+      </c>
+      <c r="W2">
         <v>2.58</v>
       </c>
-      <c r="O2">
-        <v>1.13</v>
-      </c>
-      <c r="P2">
-        <v>2.12</v>
-      </c>
-      <c r="Q2">
-        <v>1.47</v>
-      </c>
-      <c r="R2">
-        <v>1.5</v>
-      </c>
-      <c r="S2">
-        <v>1.94</v>
-      </c>
-      <c r="T2">
-        <v>1.11</v>
-      </c>
-      <c r="U2">
-        <v>1.11</v>
-      </c>
-      <c r="V2">
-        <v>1.17</v>
-      </c>
-      <c r="W2">
-        <v>2.22</v>
-      </c>
       <c r="X2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>1.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1336,7 +1354,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1350,22 +1368,22 @@
         <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1374,40 +1392,40 @@
         <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M3">
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X3">
         <v>7.6</v>
@@ -1419,25 +1437,25 @@
         <v>36</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE3">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>32</v>
@@ -1452,16 +1470,16 @@
         <v>32</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM3">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="AN3">
         <v>32</v>
       </c>
       <c r="AO3">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AP3">
         <v>6.8</v>
@@ -1473,10 +1491,10 @@
         <v>30</v>
       </c>
       <c r="AS3">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1485,7 +1503,7 @@
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX3">
         <v>8.800000000000001</v>
@@ -1497,31 +1515,31 @@
         <v>28</v>
       </c>
       <c r="BA3">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BB3">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
         <v>27</v>
       </c>
       <c r="BD3">
-        <v>14.5</v>
+        <v>65</v>
       </c>
       <c r="BE3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BF3">
         <v>25</v>
       </c>
       <c r="BG3">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BJ3">
         <v>18</v>
@@ -1533,7 +1551,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BN3">
         <v>5.3</v>
@@ -1545,7 +1563,7 @@
         <v>24</v>
       </c>
       <c r="BQ3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1569,7 +1587,7 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
@@ -1578,7 +1596,7 @@
         <v>1.68</v>
       </c>
       <c r="CB3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1592,22 +1610,22 @@
         <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H4">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I4">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="J4">
         <v>3.6</v>
@@ -1622,31 +1640,31 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q4">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
         <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W4">
         <v>1.26</v>
@@ -1655,43 +1673,43 @@
         <v>17.5</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA4">
         <v>27</v>
       </c>
       <c r="AB4">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>44</v>
       </c>
       <c r="AJ4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK4">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AL4">
         <v>80</v>
@@ -1700,10 +1718,10 @@
         <v>130</v>
       </c>
       <c r="AN4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP4">
         <v>12.5</v>
@@ -1712,52 +1730,52 @@
         <v>8</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS4">
         <v>4.6</v>
       </c>
       <c r="AT4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX4">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="AY4">
         <v>15.5</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
         <v>4.9</v>
       </c>
       <c r="BB4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC4">
+        <v>36</v>
+      </c>
+      <c r="BD4">
+        <v>5</v>
+      </c>
+      <c r="BE4">
+        <v>5.4</v>
+      </c>
+      <c r="BF4">
         <v>5.1</v>
       </c>
-      <c r="BD4">
-        <v>5.2</v>
-      </c>
-      <c r="BE4">
-        <v>5.3</v>
-      </c>
-      <c r="BF4">
-        <v>5.2</v>
-      </c>
       <c r="BG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1820,7 +1838,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1834,10 +1852,10 @@
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F5">
         <v>2.06</v>
@@ -1852,13 +1870,13 @@
         <v>5.2</v>
       </c>
       <c r="J5">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="M5">
         <v>1.16</v>
@@ -1867,13 +1885,13 @@
         <v>2.24</v>
       </c>
       <c r="O5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="P5">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Q5">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R5">
         <v>1.13</v>
@@ -1882,7 +1900,7 @@
         <v>5.7</v>
       </c>
       <c r="T5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U5">
         <v>1.64</v>
@@ -1894,10 +1912,10 @@
         <v>1.82</v>
       </c>
       <c r="X5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
         <v>36</v>
@@ -1918,7 +1936,7 @@
         <v>120</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG5">
         <v>13</v>
@@ -1930,7 +1948,7 @@
         <v>160</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK5">
         <v>36</v>
@@ -1954,13 +1972,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
@@ -1969,7 +1987,7 @@
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
         <v>9.800000000000001</v>
@@ -1978,34 +1996,34 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA5">
+        <v>9.4</v>
+      </c>
+      <c r="BB5">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB5">
-        <v>7</v>
-      </c>
       <c r="BC5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD5">
+        <v>9.4</v>
+      </c>
+      <c r="BE5">
+        <v>10</v>
+      </c>
+      <c r="BF5">
         <v>8.4</v>
       </c>
-      <c r="BE5">
-        <v>8.4</v>
-      </c>
-      <c r="BF5">
-        <v>7.2</v>
-      </c>
       <c r="BG5">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -2062,7 +2080,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2076,25 +2094,25 @@
         <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F6">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H6">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2106,22 +2124,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="R6">
         <v>1.08</v>
       </c>
       <c r="S6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2130,10 +2148,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W6">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2304,7 +2322,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2318,19 +2336,19 @@
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="I7">
         <v>990</v>
@@ -2348,13 +2366,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q7">
         <v>1.25</v>
@@ -2363,7 +2381,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2372,10 +2390,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2546,7 +2564,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2560,19 +2578,19 @@
         <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G8">
         <v>600</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I8">
         <v>870</v>
@@ -2614,10 +2632,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2788,7 +2806,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2802,19 +2820,19 @@
         <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F9">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="I9">
         <v>1.62</v>
@@ -2859,7 +2877,7 @@
         <v>2.6</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3030,7 +3048,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3044,10 +3062,10 @@
         <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -3098,10 +3116,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3272,7 +3290,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3286,13 +3304,13 @@
         <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>8.800000000000001</v>
@@ -3376,19 +3394,19 @@
         <v>34</v>
       </c>
       <c r="AH11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI11">
         <v>36</v>
       </c>
       <c r="AJ11">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AK11">
         <v>130</v>
       </c>
       <c r="AL11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM11">
         <v>130</v>
@@ -3424,7 +3442,7 @@
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY11">
         <v>22</v>
@@ -3433,22 +3451,22 @@
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BB11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC11">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD11">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG11">
         <v>4.8</v>
@@ -3514,7 +3532,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3528,10 +3546,10 @@
         <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F12">
         <v>3.2</v>
@@ -3561,7 +3579,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P12">
         <v>2.34</v>
@@ -3573,7 +3591,7 @@
         <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
         <v>1.61</v>
@@ -3756,7 +3774,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3770,10 +3788,10 @@
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F13">
         <v>1.1</v>
@@ -3998,7 +4016,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4012,10 +4030,10 @@
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F14">
         <v>2.34</v>
@@ -4240,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4254,10 +4272,10 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F15">
         <v>2.68</v>
@@ -4482,7 +4500,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4496,28 +4514,28 @@
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F16">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G16">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="H16">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="I16">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J16">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4526,22 +4544,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S16">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4550,10 +4568,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4724,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4738,28 +4756,28 @@
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F17">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G17">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="H17">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="I17">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J17">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4768,34 +4786,34 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="P17">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="R17">
+        <v>1.41</v>
+      </c>
+      <c r="S17">
+        <v>2.12</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
         <v>1.38</v>
       </c>
-      <c r="S17">
-        <v>2.52</v>
-      </c>
-      <c r="T17">
-        <v>1.01</v>
-      </c>
-      <c r="U17">
-        <v>1.01</v>
-      </c>
-      <c r="V17">
-        <v>1.44</v>
-      </c>
       <c r="W17">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4966,12 +4984,12 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
         <v>93</v>
@@ -4980,240 +4998,240 @@
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F18">
+        <v>1.72</v>
+      </c>
+      <c r="G18">
+        <v>1.74</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <v>6.2</v>
+      </c>
+      <c r="J18">
+        <v>3.85</v>
+      </c>
+      <c r="K18">
+        <v>3.9</v>
+      </c>
+      <c r="L18">
+        <v>1.5</v>
+      </c>
+      <c r="M18">
+        <v>1.09</v>
+      </c>
+      <c r="N18">
+        <v>3.2</v>
+      </c>
+      <c r="O18">
+        <v>1.43</v>
+      </c>
+      <c r="P18">
+        <v>1.75</v>
+      </c>
+      <c r="Q18">
+        <v>2.3</v>
+      </c>
+      <c r="R18">
+        <v>1.27</v>
+      </c>
+      <c r="S18">
+        <v>4.4</v>
+      </c>
+      <c r="T18">
+        <v>2.2</v>
+      </c>
+      <c r="U18">
+        <v>1.8</v>
+      </c>
+      <c r="V18">
+        <v>1.19</v>
+      </c>
+      <c r="W18">
+        <v>2.34</v>
+      </c>
+      <c r="X18">
+        <v>11.5</v>
+      </c>
+      <c r="Y18">
+        <v>16.5</v>
+      </c>
+      <c r="Z18">
+        <v>48</v>
+      </c>
+      <c r="AA18">
+        <v>200</v>
+      </c>
+      <c r="AB18">
+        <v>6.8</v>
+      </c>
+      <c r="AC18">
+        <v>8.6</v>
+      </c>
+      <c r="AD18">
+        <v>24</v>
+      </c>
+      <c r="AE18">
+        <v>110</v>
+      </c>
+      <c r="AF18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG18">
+        <v>10.5</v>
+      </c>
+      <c r="AH18">
+        <v>25</v>
+      </c>
+      <c r="AI18">
+        <v>110</v>
+      </c>
+      <c r="AJ18">
+        <v>17</v>
+      </c>
+      <c r="AK18">
+        <v>21</v>
+      </c>
+      <c r="AL18">
+        <v>48</v>
+      </c>
+      <c r="AM18">
+        <v>230</v>
+      </c>
+      <c r="AN18">
+        <v>14.5</v>
+      </c>
+      <c r="AO18">
+        <v>170</v>
+      </c>
+      <c r="AP18">
+        <v>10.5</v>
+      </c>
+      <c r="AQ18">
+        <v>14.5</v>
+      </c>
+      <c r="AR18">
+        <v>25</v>
+      </c>
+      <c r="AS18">
+        <v>44</v>
+      </c>
+      <c r="AT18">
+        <v>6.4</v>
+      </c>
+      <c r="AU18">
+        <v>8</v>
+      </c>
+      <c r="AV18">
+        <v>22</v>
+      </c>
+      <c r="AW18">
+        <v>38</v>
+      </c>
+      <c r="AX18">
+        <v>8.4</v>
+      </c>
+      <c r="AY18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18">
+        <v>24</v>
+      </c>
+      <c r="BA18">
+        <v>40</v>
+      </c>
+      <c r="BB18">
+        <v>15.5</v>
+      </c>
+      <c r="BC18">
+        <v>18.5</v>
+      </c>
+      <c r="BD18">
+        <v>42</v>
+      </c>
+      <c r="BE18">
+        <v>46</v>
+      </c>
+      <c r="BF18">
+        <v>12.5</v>
+      </c>
+      <c r="BG18">
+        <v>42</v>
+      </c>
+      <c r="BH18">
+        <v>3</v>
+      </c>
+      <c r="BI18">
+        <v>2.82</v>
+      </c>
+      <c r="BJ18">
+        <v>11.5</v>
+      </c>
+      <c r="BK18">
+        <v>10</v>
+      </c>
+      <c r="BL18">
+        <v>230</v>
+      </c>
+      <c r="BM18">
+        <v>13.5</v>
+      </c>
+      <c r="BN18">
+        <v>4.1</v>
+      </c>
+      <c r="BO18">
         <v>3.75</v>
       </c>
-      <c r="G18">
-        <v>5.2</v>
-      </c>
-      <c r="H18">
-        <v>1.75</v>
-      </c>
-      <c r="I18">
-        <v>2.02</v>
-      </c>
-      <c r="J18">
-        <v>3.8</v>
-      </c>
-      <c r="K18">
-        <v>6.2</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>2.62</v>
-      </c>
-      <c r="O18">
-        <v>1.01</v>
-      </c>
-      <c r="P18">
-        <v>2.22</v>
-      </c>
-      <c r="Q18">
-        <v>1.58</v>
-      </c>
-      <c r="R18">
-        <v>1.4</v>
-      </c>
-      <c r="S18">
-        <v>2.34</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.99</v>
-      </c>
-      <c r="W18">
-        <v>1.24</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>1000</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>1000</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18">
-        <v>1.03</v>
-      </c>
-      <c r="AR18">
-        <v>1.03</v>
-      </c>
-      <c r="AS18">
-        <v>1.03</v>
-      </c>
-      <c r="AT18">
-        <v>1.03</v>
-      </c>
-      <c r="AU18">
-        <v>1.03</v>
-      </c>
-      <c r="AV18">
-        <v>1.03</v>
-      </c>
-      <c r="AW18">
-        <v>1.03</v>
-      </c>
-      <c r="AX18">
-        <v>1.03</v>
-      </c>
-      <c r="AY18">
-        <v>1.03</v>
-      </c>
-      <c r="AZ18">
-        <v>1.03</v>
-      </c>
-      <c r="BA18">
-        <v>1.03</v>
-      </c>
-      <c r="BB18">
-        <v>1.03</v>
-      </c>
-      <c r="BC18">
-        <v>1.03</v>
-      </c>
-      <c r="BD18">
-        <v>1.03</v>
-      </c>
-      <c r="BE18">
-        <v>1.03</v>
-      </c>
-      <c r="BF18">
-        <v>1.01</v>
-      </c>
-      <c r="BG18">
-        <v>1.01</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.01</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.01</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.01</v>
-      </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB18" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
         <v>93</v>
@@ -5222,240 +5240,240 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F19">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="G19">
-        <v>1.74</v>
+        <v>13</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>1.49</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K19">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
+        <v>1.11</v>
+      </c>
+      <c r="N19">
+        <v>2.92</v>
+      </c>
+      <c r="O19">
+        <v>1.47</v>
+      </c>
+      <c r="P19">
+        <v>1.56</v>
+      </c>
+      <c r="Q19">
+        <v>2.26</v>
+      </c>
+      <c r="R19">
+        <v>1.2</v>
+      </c>
+      <c r="S19">
+        <v>4.2</v>
+      </c>
+      <c r="T19">
+        <v>2.34</v>
+      </c>
+      <c r="U19">
+        <v>1.53</v>
+      </c>
+      <c r="V19">
+        <v>2.54</v>
+      </c>
+      <c r="W19">
         <v>1.09</v>
       </c>
-      <c r="N19">
-        <v>3.2</v>
-      </c>
-      <c r="O19">
-        <v>1.43</v>
-      </c>
-      <c r="P19">
-        <v>1.75</v>
-      </c>
-      <c r="Q19">
-        <v>2.3</v>
-      </c>
-      <c r="R19">
+      <c r="X19">
+        <v>970</v>
+      </c>
+      <c r="Y19">
+        <v>970</v>
+      </c>
+      <c r="Z19">
+        <v>970</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>970</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.41</v>
+      </c>
+      <c r="AQ19">
+        <v>1.29</v>
+      </c>
+      <c r="AR19">
+        <v>1.35</v>
+      </c>
+      <c r="AS19">
+        <v>1.54</v>
+      </c>
+      <c r="AT19">
+        <v>1.54</v>
+      </c>
+      <c r="AU19">
+        <v>1.41</v>
+      </c>
+      <c r="AV19">
+        <v>1.54</v>
+      </c>
+      <c r="AW19">
+        <v>1.55</v>
+      </c>
+      <c r="AX19">
+        <v>1.55</v>
+      </c>
+      <c r="AY19">
+        <v>1.54</v>
+      </c>
+      <c r="AZ19">
+        <v>1.54</v>
+      </c>
+      <c r="BA19">
+        <v>1.55</v>
+      </c>
+      <c r="BB19">
+        <v>1.55</v>
+      </c>
+      <c r="BC19">
+        <v>1.55</v>
+      </c>
+      <c r="BD19">
+        <v>1.55</v>
+      </c>
+      <c r="BE19">
+        <v>1.55</v>
+      </c>
+      <c r="BF19">
+        <v>1.55</v>
+      </c>
+      <c r="BG19">
+        <v>1.54</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
         <v>1.27</v>
       </c>
-      <c r="S19">
-        <v>4.4</v>
-      </c>
-      <c r="T19">
-        <v>2.2</v>
-      </c>
-      <c r="U19">
-        <v>1.8</v>
-      </c>
-      <c r="V19">
-        <v>1.19</v>
-      </c>
-      <c r="W19">
-        <v>2.34</v>
-      </c>
-      <c r="X19">
-        <v>11.5</v>
-      </c>
-      <c r="Y19">
-        <v>16.5</v>
-      </c>
-      <c r="Z19">
-        <v>48</v>
-      </c>
-      <c r="AA19">
-        <v>200</v>
-      </c>
-      <c r="AB19">
-        <v>6.8</v>
-      </c>
-      <c r="AC19">
-        <v>8.6</v>
-      </c>
-      <c r="AD19">
-        <v>24</v>
-      </c>
-      <c r="AE19">
-        <v>110</v>
-      </c>
-      <c r="AF19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG19">
-        <v>10.5</v>
-      </c>
-      <c r="AH19">
-        <v>25</v>
-      </c>
-      <c r="AI19">
-        <v>110</v>
-      </c>
-      <c r="AJ19">
-        <v>17</v>
-      </c>
-      <c r="AK19">
-        <v>21</v>
-      </c>
-      <c r="AL19">
-        <v>48</v>
-      </c>
-      <c r="AM19">
-        <v>220</v>
-      </c>
-      <c r="AN19">
-        <v>14</v>
-      </c>
-      <c r="AO19">
-        <v>170</v>
-      </c>
-      <c r="AP19">
-        <v>10.5</v>
-      </c>
-      <c r="AQ19">
-        <v>14.5</v>
-      </c>
-      <c r="AR19">
-        <v>25</v>
-      </c>
-      <c r="AS19">
-        <v>44</v>
-      </c>
-      <c r="AT19">
-        <v>6.4</v>
-      </c>
-      <c r="AU19">
-        <v>8</v>
-      </c>
-      <c r="AV19">
-        <v>22</v>
-      </c>
-      <c r="AW19">
-        <v>38</v>
-      </c>
-      <c r="AX19">
-        <v>8.4</v>
-      </c>
-      <c r="AY19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ19">
-        <v>24</v>
-      </c>
-      <c r="BA19">
-        <v>40</v>
-      </c>
-      <c r="BB19">
-        <v>15.5</v>
-      </c>
-      <c r="BC19">
-        <v>18.5</v>
-      </c>
-      <c r="BD19">
-        <v>42</v>
-      </c>
-      <c r="BE19">
-        <v>46</v>
-      </c>
-      <c r="BF19">
-        <v>12.5</v>
-      </c>
-      <c r="BG19">
-        <v>42</v>
-      </c>
-      <c r="BH19">
-        <v>3</v>
-      </c>
-      <c r="BI19">
-        <v>2.82</v>
-      </c>
       <c r="BJ19">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>10</v>
+        <v>1.27</v>
       </c>
       <c r="BL19">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>13.5</v>
+        <v>1.27</v>
       </c>
       <c r="BN19">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.75</v>
+        <v>1.27</v>
       </c>
       <c r="BP19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>11</v>
+        <v>1.27</v>
       </c>
       <c r="BR19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>1.27</v>
       </c>
       <c r="BT19">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="BV19">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>12</v>
+        <v>1.27</v>
       </c>
       <c r="BX19">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>12.5</v>
+        <v>1.27</v>
       </c>
       <c r="BZ19">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>10</v>
+        <v>1.27</v>
       </c>
       <c r="CB19" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
         <v>93</v>
@@ -5464,73 +5482,73 @@
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F20">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="G20">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="H20">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="I20">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="O20">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Q20">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="S20">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="U20">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
         <v>1000</v>
@@ -5539,7 +5557,7 @@
         <v>1000</v>
       </c>
       <c r="AC20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
         <v>1000</v>
@@ -5578,126 +5596,126 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
         <v>93</v>
@@ -5706,64 +5724,64 @@
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F21">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="G21">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H21">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="I21">
+        <v>2.02</v>
+      </c>
+      <c r="J21">
+        <v>3.8</v>
+      </c>
+      <c r="K21">
+        <v>6.2</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>2.62</v>
+      </c>
+      <c r="O21">
+        <v>1.01</v>
+      </c>
+      <c r="P21">
         <v>2.22</v>
       </c>
-      <c r="J21">
-        <v>2.96</v>
-      </c>
-      <c r="K21">
-        <v>950</v>
-      </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>2.48</v>
-      </c>
-      <c r="O21">
-        <v>1.33</v>
-      </c>
-      <c r="P21">
-        <v>1.52</v>
-      </c>
       <c r="Q21">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="R21">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="T21">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="W21">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5877,7 +5895,7 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5913,7 +5931,7 @@
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -5934,7 +5952,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5948,10 +5966,10 @@
         <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F22">
         <v>1.33</v>
@@ -6176,7 +6194,7 @@
         <v>1.37</v>
       </c>
       <c r="CB22" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6190,10 +6208,10 @@
         <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -6211,7 +6229,7 @@
         <v>3.5</v>
       </c>
       <c r="K23">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6418,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6432,10 +6450,10 @@
         <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F24">
         <v>1.1</v>
@@ -6486,10 +6504,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6660,12 +6678,12 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
         <v>93</v>
@@ -6674,240 +6692,240 @@
         <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="G25">
-        <v>3.15</v>
+        <v>1.45</v>
       </c>
       <c r="H25">
+        <v>8</v>
+      </c>
+      <c r="I25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J25">
+        <v>5.2</v>
+      </c>
+      <c r="K25">
+        <v>5.4</v>
+      </c>
+      <c r="L25">
+        <v>1.33</v>
+      </c>
+      <c r="M25">
+        <v>1.04</v>
+      </c>
+      <c r="N25">
+        <v>5.1</v>
+      </c>
+      <c r="O25">
+        <v>1.22</v>
+      </c>
+      <c r="P25">
         <v>2.44</v>
       </c>
-      <c r="I25">
-        <v>2.54</v>
-      </c>
-      <c r="J25">
-        <v>3.5</v>
-      </c>
-      <c r="K25">
-        <v>3.65</v>
-      </c>
-      <c r="L25">
-        <v>1.01</v>
-      </c>
-      <c r="M25">
-        <v>1.06</v>
-      </c>
-      <c r="N25">
-        <v>3.85</v>
-      </c>
-      <c r="O25">
-        <v>1.3</v>
-      </c>
-      <c r="P25">
+      <c r="Q25">
+        <v>1.67</v>
+      </c>
+      <c r="R25">
+        <v>1.54</v>
+      </c>
+      <c r="S25">
+        <v>2.72</v>
+      </c>
+      <c r="T25">
+        <v>1.9</v>
+      </c>
+      <c r="U25">
         <v>2</v>
       </c>
-      <c r="Q25">
-        <v>1.89</v>
-      </c>
-      <c r="R25">
-        <v>1.38</v>
-      </c>
-      <c r="S25">
+      <c r="V25">
+        <v>1.13</v>
+      </c>
+      <c r="W25">
         <v>3.2</v>
       </c>
-      <c r="T25">
-        <v>1.7</v>
-      </c>
-      <c r="U25">
-        <v>2.2</v>
-      </c>
-      <c r="V25">
-        <v>1.64</v>
-      </c>
-      <c r="W25">
-        <v>1.46</v>
-      </c>
       <c r="X25">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="Y25">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="Z25">
-        <v>17.5</v>
+        <v>80</v>
       </c>
       <c r="AA25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AC25">
+        <v>12</v>
+      </c>
+      <c r="AD25">
+        <v>32</v>
+      </c>
+      <c r="AE25">
+        <v>130</v>
+      </c>
+      <c r="AF25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG25">
+        <v>10.5</v>
+      </c>
+      <c r="AH25">
+        <v>25</v>
+      </c>
+      <c r="AI25">
+        <v>110</v>
+      </c>
+      <c r="AJ25">
+        <v>12.5</v>
+      </c>
+      <c r="AK25">
+        <v>14.5</v>
+      </c>
+      <c r="AL25">
+        <v>34</v>
+      </c>
+      <c r="AM25">
+        <v>130</v>
+      </c>
+      <c r="AN25">
+        <v>5.9</v>
+      </c>
+      <c r="AO25">
+        <v>130</v>
+      </c>
+      <c r="AP25">
+        <v>19.5</v>
+      </c>
+      <c r="AQ25">
+        <v>26</v>
+      </c>
+      <c r="AR25">
+        <v>32</v>
+      </c>
+      <c r="AS25">
+        <v>50</v>
+      </c>
+      <c r="AT25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU25">
+        <v>10.5</v>
+      </c>
+      <c r="AV25">
+        <v>26</v>
+      </c>
+      <c r="AW25">
+        <v>40</v>
+      </c>
+      <c r="AX25">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD25">
-        <v>12.5</v>
-      </c>
-      <c r="AE25">
+      <c r="AY25">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25">
+        <v>21</v>
+      </c>
+      <c r="BA25">
+        <v>75</v>
+      </c>
+      <c r="BB25">
+        <v>10.5</v>
+      </c>
+      <c r="BC25">
+        <v>13</v>
+      </c>
+      <c r="BD25">
         <v>28</v>
       </c>
-      <c r="AF25">
-        <v>23</v>
-      </c>
-      <c r="AG25">
-        <v>14.5</v>
-      </c>
-      <c r="AH25">
-        <v>17.5</v>
-      </c>
-      <c r="AI25">
-        <v>40</v>
-      </c>
-      <c r="AJ25">
-        <v>55</v>
-      </c>
-      <c r="AK25">
-        <v>38</v>
-      </c>
-      <c r="AL25">
-        <v>46</v>
-      </c>
-      <c r="AM25">
-        <v>80</v>
-      </c>
-      <c r="AN25">
-        <v>32</v>
-      </c>
-      <c r="AO25">
-        <v>20</v>
-      </c>
-      <c r="AP25">
-        <v>13</v>
-      </c>
-      <c r="AQ25">
-        <v>9.6</v>
-      </c>
-      <c r="AR25">
-        <v>14.5</v>
-      </c>
-      <c r="AS25">
-        <v>8</v>
-      </c>
-      <c r="AT25">
-        <v>11</v>
-      </c>
-      <c r="AU25">
-        <v>7</v>
-      </c>
-      <c r="AV25">
-        <v>10</v>
-      </c>
-      <c r="AW25">
-        <v>23</v>
-      </c>
-      <c r="AX25">
-        <v>19</v>
-      </c>
-      <c r="AY25">
-        <v>11.5</v>
-      </c>
-      <c r="AZ25">
-        <v>14.5</v>
-      </c>
-      <c r="BA25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB25">
-        <v>9.6</v>
-      </c>
-      <c r="BC25">
-        <v>8</v>
-      </c>
-      <c r="BD25">
-        <v>36</v>
-      </c>
       <c r="BE25">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BF25">
+        <v>5.5</v>
+      </c>
+      <c r="BG25">
+        <v>42</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>3.35</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
         <v>8.4</v>
       </c>
-      <c r="BG25">
-        <v>16.5</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.04</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.04</v>
-      </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB25" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
         <v>93</v>
@@ -6916,235 +6934,235 @@
         <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F26">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="G26">
+        <v>3.15</v>
+      </c>
+      <c r="H26">
+        <v>2.44</v>
+      </c>
+      <c r="I26">
+        <v>2.54</v>
+      </c>
+      <c r="J26">
+        <v>3.55</v>
+      </c>
+      <c r="K26">
+        <v>3.65</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.06</v>
+      </c>
+      <c r="N26">
+        <v>4.1</v>
+      </c>
+      <c r="O26">
+        <v>1.28</v>
+      </c>
+      <c r="P26">
+        <v>2.06</v>
+      </c>
+      <c r="Q26">
+        <v>1.79</v>
+      </c>
+      <c r="R26">
+        <v>1.43</v>
+      </c>
+      <c r="S26">
+        <v>3</v>
+      </c>
+      <c r="T26">
+        <v>1.65</v>
+      </c>
+      <c r="U26">
+        <v>2.28</v>
+      </c>
+      <c r="V26">
+        <v>1.64</v>
+      </c>
+      <c r="W26">
         <v>1.46</v>
       </c>
-      <c r="H26">
+      <c r="X26">
+        <v>17.5</v>
+      </c>
+      <c r="Y26">
+        <v>12</v>
+      </c>
+      <c r="Z26">
+        <v>17.5</v>
+      </c>
+      <c r="AA26">
+        <v>38</v>
+      </c>
+      <c r="AB26">
+        <v>14</v>
+      </c>
+      <c r="AC26">
+        <v>8.6</v>
+      </c>
+      <c r="AD26">
+        <v>12.5</v>
+      </c>
+      <c r="AE26">
+        <v>27</v>
+      </c>
+      <c r="AF26">
+        <v>23</v>
+      </c>
+      <c r="AG26">
+        <v>14</v>
+      </c>
+      <c r="AH26">
+        <v>17</v>
+      </c>
+      <c r="AI26">
+        <v>38</v>
+      </c>
+      <c r="AJ26">
+        <v>55</v>
+      </c>
+      <c r="AK26">
+        <v>34</v>
+      </c>
+      <c r="AL26">
+        <v>44</v>
+      </c>
+      <c r="AM26">
+        <v>80</v>
+      </c>
+      <c r="AN26">
+        <v>26</v>
+      </c>
+      <c r="AO26">
+        <v>18.5</v>
+      </c>
+      <c r="AP26">
+        <v>14</v>
+      </c>
+      <c r="AQ26">
+        <v>10.5</v>
+      </c>
+      <c r="AR26">
+        <v>15</v>
+      </c>
+      <c r="AS26">
         <v>8</v>
       </c>
-      <c r="I26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J26">
-        <v>5.2</v>
-      </c>
-      <c r="K26">
-        <v>5.5</v>
-      </c>
-      <c r="L26">
-        <v>1.33</v>
-      </c>
-      <c r="M26">
+      <c r="AT26">
+        <v>11.5</v>
+      </c>
+      <c r="AU26">
+        <v>7.2</v>
+      </c>
+      <c r="AV26">
+        <v>10</v>
+      </c>
+      <c r="AW26">
+        <v>22</v>
+      </c>
+      <c r="AX26">
+        <v>18.5</v>
+      </c>
+      <c r="AY26">
+        <v>11.5</v>
+      </c>
+      <c r="AZ26">
+        <v>14</v>
+      </c>
+      <c r="BA26">
+        <v>8</v>
+      </c>
+      <c r="BB26">
+        <v>8.6</v>
+      </c>
+      <c r="BC26">
+        <v>7.8</v>
+      </c>
+      <c r="BD26">
+        <v>8.4</v>
+      </c>
+      <c r="BE26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF26">
+        <v>21</v>
+      </c>
+      <c r="BG26">
+        <v>15</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
         <v>1.04</v>
       </c>
-      <c r="N26">
-        <v>5.1</v>
-      </c>
-      <c r="O26">
-        <v>1.22</v>
-      </c>
-      <c r="P26">
-        <v>2.44</v>
-      </c>
-      <c r="Q26">
-        <v>1.67</v>
-      </c>
-      <c r="R26">
-        <v>1.56</v>
-      </c>
-      <c r="S26">
-        <v>2.72</v>
-      </c>
-      <c r="T26">
-        <v>1.91</v>
-      </c>
-      <c r="U26">
-        <v>1.99</v>
-      </c>
-      <c r="V26">
-        <v>1.13</v>
-      </c>
-      <c r="W26">
-        <v>3.15</v>
-      </c>
-      <c r="X26">
-        <v>24</v>
-      </c>
-      <c r="Y26">
-        <v>30</v>
-      </c>
-      <c r="Z26">
-        <v>85</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>10</v>
-      </c>
-      <c r="AC26">
-        <v>12</v>
-      </c>
-      <c r="AD26">
-        <v>32</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
-      <c r="AF26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG26">
-        <v>10.5</v>
-      </c>
-      <c r="AH26">
-        <v>25</v>
-      </c>
-      <c r="AI26">
-        <v>110</v>
-      </c>
-      <c r="AJ26">
-        <v>12.5</v>
-      </c>
-      <c r="AK26">
-        <v>15</v>
-      </c>
-      <c r="AL26">
-        <v>36</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>5.9</v>
-      </c>
-      <c r="AO26">
-        <v>1000</v>
-      </c>
-      <c r="AP26">
-        <v>19.5</v>
-      </c>
-      <c r="AQ26">
-        <v>19</v>
-      </c>
-      <c r="AR26">
-        <v>32</v>
-      </c>
-      <c r="AS26">
-        <v>50</v>
-      </c>
-      <c r="AT26">
-        <v>8.6</v>
-      </c>
-      <c r="AU26">
-        <v>10.5</v>
-      </c>
-      <c r="AV26">
-        <v>24</v>
-      </c>
-      <c r="AW26">
-        <v>40</v>
-      </c>
-      <c r="AX26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY26">
-        <v>9.4</v>
-      </c>
-      <c r="AZ26">
-        <v>21</v>
-      </c>
-      <c r="BA26">
-        <v>60</v>
-      </c>
-      <c r="BB26">
-        <v>10.5</v>
-      </c>
-      <c r="BC26">
-        <v>13</v>
-      </c>
-      <c r="BD26">
-        <v>25</v>
-      </c>
-      <c r="BE26">
-        <v>70</v>
-      </c>
-      <c r="BF26">
-        <v>5.3</v>
-      </c>
-      <c r="BG26">
-        <v>42</v>
-      </c>
-      <c r="BH26">
-        <v>4.2</v>
-      </c>
-      <c r="BI26">
-        <v>3.75</v>
-      </c>
       <c r="BJ26">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7158,10 +7176,10 @@
         <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F27">
         <v>1.57</v>
@@ -7173,7 +7191,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J27">
         <v>4.6</v>
@@ -7332,7 +7350,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ27">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
         <v>7.2</v>
@@ -7344,7 +7362,7 @@
         <v>21</v>
       </c>
       <c r="BN27">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO27">
         <v>3.5</v>
@@ -7362,7 +7380,7 @@
         <v>13</v>
       </c>
       <c r="BT27">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU27">
         <v>6.8</v>
@@ -7383,10 +7401,10 @@
         <v>20</v>
       </c>
       <c r="CA27">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="CB27" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7400,22 +7418,22 @@
         <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F28">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G28">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H28">
+        <v>4.6</v>
+      </c>
+      <c r="I28">
         <v>4.8</v>
-      </c>
-      <c r="I28">
-        <v>4.9</v>
       </c>
       <c r="J28">
         <v>4.3</v>
@@ -7451,13 +7469,13 @@
         <v>1.64</v>
       </c>
       <c r="U28">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W28">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X28">
         <v>23</v>
@@ -7511,16 +7529,16 @@
         <v>7.8</v>
       </c>
       <c r="AO28">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS28">
         <v>38</v>
@@ -7532,7 +7550,7 @@
         <v>9</v>
       </c>
       <c r="AV28">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW28">
         <v>44</v>
@@ -7571,7 +7589,7 @@
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
@@ -7583,7 +7601,7 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BN28">
         <v>1000</v>
@@ -7595,13 +7613,13 @@
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BT28">
         <v>1000</v>
@@ -7613,22 +7631,22 @@
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="CB28" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7642,22 +7660,22 @@
         <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F29">
         <v>1.25</v>
       </c>
       <c r="G29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I29">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J29">
         <v>7</v>
@@ -7666,7 +7684,7 @@
         <v>7.6</v>
       </c>
       <c r="L29">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M29">
         <v>1.02</v>
@@ -7690,16 +7708,16 @@
         <v>2.16</v>
       </c>
       <c r="T29">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U29">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V29">
         <v>1.07</v>
       </c>
       <c r="W29">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X29">
         <v>34</v>
@@ -7717,7 +7735,7 @@
         <v>12.5</v>
       </c>
       <c r="AC29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD29">
         <v>50</v>
@@ -7732,7 +7750,7 @@
         <v>11.5</v>
       </c>
       <c r="AH29">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI29">
         <v>160</v>
@@ -7747,10 +7765,10 @@
         <v>38</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN29">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AO29">
         <v>230</v>
@@ -7792,7 +7810,7 @@
         <v>44</v>
       </c>
       <c r="BB29">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC29">
         <v>12.5</v>
@@ -7825,7 +7843,7 @@
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="BN29">
         <v>1000</v>
@@ -7855,22 +7873,22 @@
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>3.95</v>
+        <v>2.06</v>
       </c>
       <c r="CB29" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7884,10 +7902,10 @@
         <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F30">
         <v>1.77</v>
@@ -7935,7 +7953,7 @@
         <v>1.61</v>
       </c>
       <c r="U30">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V30">
         <v>1.25</v>
@@ -7995,7 +8013,7 @@
         <v>7.6</v>
       </c>
       <c r="AO30">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP30">
         <v>22</v>
@@ -8049,7 +8067,7 @@
         <v>7</v>
       </c>
       <c r="BG30">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8112,7 +8130,7 @@
         <v>2.34</v>
       </c>
       <c r="CB30" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8126,22 +8144,22 @@
         <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G31">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H31">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I31">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J31">
         <v>3.65</v>
@@ -8171,7 +8189,7 @@
         <v>1.48</v>
       </c>
       <c r="S31">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T31">
         <v>1.64</v>
@@ -8180,13 +8198,13 @@
         <v>2.46</v>
       </c>
       <c r="V31">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W31">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y31">
         <v>13</v>
@@ -8222,10 +8240,10 @@
         <v>34</v>
       </c>
       <c r="AJ31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL31">
         <v>38</v>
@@ -8234,7 +8252,7 @@
         <v>70</v>
       </c>
       <c r="AN31">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO31">
         <v>16.5</v>
@@ -8252,10 +8270,10 @@
         <v>29</v>
       </c>
       <c r="AT31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV31">
         <v>10.5</v>
@@ -8264,7 +8282,7 @@
         <v>22</v>
       </c>
       <c r="AX31">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY31">
         <v>12</v>
@@ -8354,7 +8372,7 @@
         <v>2.38</v>
       </c>
       <c r="CB31" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8368,10 +8386,10 @@
         <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F32">
         <v>2.88</v>
@@ -8542,7 +8560,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ32">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
         <v>6.4</v>
@@ -8596,7 +8614,7 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8610,10 +8628,10 @@
         <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F33">
         <v>3.75</v>
@@ -8670,7 +8688,7 @@
         <v>1.35</v>
       </c>
       <c r="X33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y33">
         <v>13</v>
@@ -8682,7 +8700,7 @@
         <v>24</v>
       </c>
       <c r="AB33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -8697,7 +8715,7 @@
         <v>32</v>
       </c>
       <c r="AG33">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH33">
         <v>15.5</v>
@@ -8718,13 +8736,13 @@
         <v>65</v>
       </c>
       <c r="AN33">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO33">
         <v>10.5</v>
       </c>
       <c r="AP33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ33">
         <v>12</v>
@@ -8745,13 +8763,13 @@
         <v>10</v>
       </c>
       <c r="AW33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ33">
         <v>14.5</v>
@@ -8838,7 +8856,491 @@
         <v>7.8</v>
       </c>
       <c r="CB33" t="s">
-        <v>168</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34">
+        <v>1.17</v>
+      </c>
+      <c r="G34">
+        <v>600</v>
+      </c>
+      <c r="H34">
+        <v>1.17</v>
+      </c>
+      <c r="I34">
+        <v>870</v>
+      </c>
+      <c r="J34">
+        <v>1.2</v>
+      </c>
+      <c r="K34">
+        <v>950</v>
+      </c>
+      <c r="L34">
+        <v>1.01</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
+        <v>1.26</v>
+      </c>
+      <c r="O34">
+        <v>1.15</v>
+      </c>
+      <c r="P34">
+        <v>1.25</v>
+      </c>
+      <c r="Q34">
+        <v>1.15</v>
+      </c>
+      <c r="R34">
+        <v>1.08</v>
+      </c>
+      <c r="S34">
+        <v>1.15</v>
+      </c>
+      <c r="T34">
+        <v>1.01</v>
+      </c>
+      <c r="U34">
+        <v>1.01</v>
+      </c>
+      <c r="V34">
+        <v>1.07</v>
+      </c>
+      <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1000</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>1000</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>1000</v>
+      </c>
+      <c r="AC34">
+        <v>1000</v>
+      </c>
+      <c r="AD34">
+        <v>1000</v>
+      </c>
+      <c r="AE34">
+        <v>1000</v>
+      </c>
+      <c r="AF34">
+        <v>1000</v>
+      </c>
+      <c r="AG34">
+        <v>1000</v>
+      </c>
+      <c r="AH34">
+        <v>1000</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>1000</v>
+      </c>
+      <c r="AK34">
+        <v>1000</v>
+      </c>
+      <c r="AL34">
+        <v>1000</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.03</v>
+      </c>
+      <c r="AQ34">
+        <v>1.03</v>
+      </c>
+      <c r="AR34">
+        <v>1.03</v>
+      </c>
+      <c r="AS34">
+        <v>1.03</v>
+      </c>
+      <c r="AT34">
+        <v>1.03</v>
+      </c>
+      <c r="AU34">
+        <v>1.03</v>
+      </c>
+      <c r="AV34">
+        <v>1.03</v>
+      </c>
+      <c r="AW34">
+        <v>1.03</v>
+      </c>
+      <c r="AX34">
+        <v>1.03</v>
+      </c>
+      <c r="AY34">
+        <v>1.03</v>
+      </c>
+      <c r="AZ34">
+        <v>1.03</v>
+      </c>
+      <c r="BA34">
+        <v>1.03</v>
+      </c>
+      <c r="BB34">
+        <v>1.03</v>
+      </c>
+      <c r="BC34">
+        <v>1.03</v>
+      </c>
+      <c r="BD34">
+        <v>1.03</v>
+      </c>
+      <c r="BE34">
+        <v>1.03</v>
+      </c>
+      <c r="BF34">
+        <v>1.01</v>
+      </c>
+      <c r="BG34">
+        <v>1.01</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.01</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.01</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.01</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.01</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.01</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35">
+        <v>2.16</v>
+      </c>
+      <c r="G35">
+        <v>2.5</v>
+      </c>
+      <c r="H35">
+        <v>3.2</v>
+      </c>
+      <c r="I35">
+        <v>4.6</v>
+      </c>
+      <c r="J35">
+        <v>3.1</v>
+      </c>
+      <c r="K35">
+        <v>3.75</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>2.7</v>
+      </c>
+      <c r="O35">
+        <v>1.42</v>
+      </c>
+      <c r="P35">
+        <v>1.58</v>
+      </c>
+      <c r="Q35">
+        <v>2.02</v>
+      </c>
+      <c r="R35">
+        <v>1.21</v>
+      </c>
+      <c r="S35">
+        <v>3.85</v>
+      </c>
+      <c r="T35">
+        <v>1.01</v>
+      </c>
+      <c r="U35">
+        <v>1.01</v>
+      </c>
+      <c r="V35">
+        <v>1.29</v>
+      </c>
+      <c r="W35">
+        <v>1.66</v>
+      </c>
+      <c r="X35">
+        <v>1000</v>
+      </c>
+      <c r="Y35">
+        <v>1000</v>
+      </c>
+      <c r="Z35">
+        <v>1000</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>1000</v>
+      </c>
+      <c r="AD35">
+        <v>1000</v>
+      </c>
+      <c r="AE35">
+        <v>1000</v>
+      </c>
+      <c r="AF35">
+        <v>1000</v>
+      </c>
+      <c r="AG35">
+        <v>1000</v>
+      </c>
+      <c r="AH35">
+        <v>1000</v>
+      </c>
+      <c r="AI35">
+        <v>1000</v>
+      </c>
+      <c r="AJ35">
+        <v>1000</v>
+      </c>
+      <c r="AK35">
+        <v>1000</v>
+      </c>
+      <c r="AL35">
+        <v>1000</v>
+      </c>
+      <c r="AM35">
+        <v>1000</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>1.01</v>
+      </c>
+      <c r="AQ35">
+        <v>1.01</v>
+      </c>
+      <c r="AR35">
+        <v>1.01</v>
+      </c>
+      <c r="AS35">
+        <v>1.01</v>
+      </c>
+      <c r="AT35">
+        <v>1.01</v>
+      </c>
+      <c r="AU35">
+        <v>1.01</v>
+      </c>
+      <c r="AV35">
+        <v>1.01</v>
+      </c>
+      <c r="AW35">
+        <v>1.01</v>
+      </c>
+      <c r="AX35">
+        <v>1.01</v>
+      </c>
+      <c r="AY35">
+        <v>1.01</v>
+      </c>
+      <c r="AZ35">
+        <v>1.01</v>
+      </c>
+      <c r="BA35">
+        <v>1.01</v>
+      </c>
+      <c r="BB35">
+        <v>1.01</v>
+      </c>
+      <c r="BC35">
+        <v>1.01</v>
+      </c>
+      <c r="BD35">
+        <v>1.01</v>
+      </c>
+      <c r="BE35">
+        <v>1.01</v>
+      </c>
+      <c r="BF35">
+        <v>1.01</v>
+      </c>
+      <c r="BG35">
+        <v>1.01</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.01</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.01</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="178">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Georgian Umaglesi Liga</t>
   </si>
   <si>
+    <t>Nigerian Premier League</t>
+  </si>
+  <si>
     <t>Estonian Premier League</t>
   </si>
   <si>
@@ -358,6 +361,9 @@
     <t>FK Atyrau</t>
   </si>
   <si>
+    <t>Enugu Rangers International</t>
+  </si>
+  <si>
     <t>FCI Tallinn</t>
   </si>
   <si>
@@ -460,6 +466,9 @@
     <t>FC Ordabasy</t>
   </si>
   <si>
+    <t>Nasarawa United</t>
+  </si>
+  <si>
     <t>Tammeka Tartu</t>
   </si>
   <si>
@@ -538,7 +547,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 00:29:29</t>
+    <t>2026-09-16 02:44:11</t>
   </si>
 </sst>
 </file>
@@ -870,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB35"/>
+  <dimension ref="A1:CB36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1120,19 +1129,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F2">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G2">
         <v>1.63</v>
@@ -1141,70 +1150,70 @@
         <v>5.3</v>
       </c>
       <c r="I2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
         <v>4.6</v>
       </c>
       <c r="K2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P2">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q2">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S2">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="T2">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="U2">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
         <v>2.58</v>
       </c>
       <c r="X2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z2">
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE2">
         <v>75</v>
@@ -1216,16 +1225,16 @@
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI2">
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL2">
         <v>28</v>
@@ -1234,34 +1243,34 @@
         <v>85</v>
       </c>
       <c r="AN2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ2">
         <v>23</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AT2">
         <v>11</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2">
         <v>19</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1273,25 +1282,25 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BB2">
+        <v>13.5</v>
+      </c>
+      <c r="BC2">
         <v>13</v>
       </c>
-      <c r="BC2">
-        <v>12.5</v>
-      </c>
       <c r="BD2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1354,7 +1363,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1362,73 +1371,73 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F3">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
         <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M3">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="T3">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="U3">
         <v>1.6</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Y3">
         <v>12</v>
@@ -1440,7 +1449,7 @@
         <v>170</v>
       </c>
       <c r="AB3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1452,19 +1461,19 @@
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG3">
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK3">
         <v>32</v>
@@ -1473,16 +1482,16 @@
         <v>85</v>
       </c>
       <c r="AM3">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO3">
         <v>220</v>
       </c>
       <c r="AP3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
@@ -1491,22 +1500,22 @@
         <v>30</v>
       </c>
       <c r="AS3">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU3">
         <v>7</v>
       </c>
       <c r="AV3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW3">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1515,10 +1524,10 @@
         <v>28</v>
       </c>
       <c r="BA3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BB3">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BC3">
         <v>27</v>
@@ -1527,13 +1536,13 @@
         <v>65</v>
       </c>
       <c r="BE3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BG3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1545,7 +1554,7 @@
         <v>18</v>
       </c>
       <c r="BK3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1560,7 +1569,7 @@
         <v>1.29</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
         <v>1.59</v>
@@ -1575,7 +1584,7 @@
         <v>11.5</v>
       </c>
       <c r="BU3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1596,7 +1605,7 @@
         <v>1.68</v>
       </c>
       <c r="CB3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1604,16 +1613,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F4">
         <v>4.6</v>
@@ -1634,13 +1643,13 @@
         <v>3.8</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
         <v>1.32</v>
@@ -1649,22 +1658,22 @@
         <v>1.94</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W4">
         <v>1.26</v>
@@ -1673,43 +1682,43 @@
         <v>17.5</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG4">
         <v>23</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ4">
         <v>130</v>
       </c>
       <c r="AK4">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AL4">
         <v>80</v>
@@ -1721,7 +1730,7 @@
         <v>85</v>
       </c>
       <c r="AO4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP4">
         <v>12.5</v>
@@ -1733,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="AS4">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="AT4">
         <v>14.5</v>
@@ -1742,40 +1751,40 @@
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX4">
-        <v>23</v>
+        <v>5.8</v>
       </c>
       <c r="AY4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4">
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BB4">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC4">
-        <v>36</v>
+        <v>6.2</v>
       </c>
       <c r="BD4">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1838,7 +1847,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1846,16 +1855,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F5">
         <v>2.06</v>
@@ -1897,7 +1906,7 @@
         <v>1.13</v>
       </c>
       <c r="S5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T5">
         <v>2.4</v>
@@ -2080,7 +2089,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2088,16 +2097,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F6">
         <v>1.16</v>
@@ -2112,7 +2121,7 @@
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2130,7 +2139,7 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
         <v>1.26</v>
@@ -2148,7 +2157,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
         <v>1.52</v>
@@ -2322,7 +2331,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2330,16 +2339,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F7">
         <v>1.15</v>
@@ -2369,10 +2378,10 @@
         <v>1.1</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q7">
         <v>1.25</v>
@@ -2390,10 +2399,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2564,7 +2573,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2572,16 +2581,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F8">
         <v>1.12</v>
@@ -2590,7 +2599,7 @@
         <v>600</v>
       </c>
       <c r="H8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
         <v>870</v>
@@ -2632,10 +2641,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2806,7 +2815,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2814,16 +2823,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F9">
         <v>3.1</v>
@@ -2832,7 +2841,7 @@
         <v>600</v>
       </c>
       <c r="H9">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="I9">
         <v>1.62</v>
@@ -2856,16 +2865,16 @@
         <v>1.27</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q9">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S9">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3048,7 +3057,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3056,34 +3065,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
         <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F10">
         <v>1.1</v>
       </c>
       <c r="G10">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H10">
         <v>1.1</v>
       </c>
       <c r="I10">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3092,16 +3101,16 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Q10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>1.08</v>
@@ -3116,10 +3125,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3176,52 +3185,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3290,7 +3299,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3298,190 +3307,190 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
         <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="G11">
-        <v>8.800000000000001</v>
+        <v>600</v>
       </c>
       <c r="H11">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="I11">
-        <v>1.45</v>
+        <v>870</v>
       </c>
       <c r="J11">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
-        <v>5.6</v>
+        <v>950</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5.5</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="P11">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.62</v>
+        <v>1.05</v>
       </c>
       <c r="R11">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="S11">
-        <v>2.56</v>
+        <v>1.06</v>
       </c>
       <c r="T11">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3493,7 +3502,7 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -3511,13 +3520,13 @@
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
@@ -3532,249 +3541,249 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H12">
+        <v>1.41</v>
+      </c>
+      <c r="I12">
+        <v>1.44</v>
+      </c>
+      <c r="J12">
+        <v>5.2</v>
+      </c>
+      <c r="K12">
+        <v>5.6</v>
+      </c>
+      <c r="L12">
+        <v>1.3</v>
+      </c>
+      <c r="M12">
+        <v>1.03</v>
+      </c>
+      <c r="N12">
+        <v>5.5</v>
+      </c>
+      <c r="O12">
+        <v>1.2</v>
+      </c>
+      <c r="P12">
+        <v>2.54</v>
+      </c>
+      <c r="Q12">
+        <v>1.61</v>
+      </c>
+      <c r="R12">
+        <v>1.61</v>
+      </c>
+      <c r="S12">
+        <v>2.56</v>
+      </c>
+      <c r="T12">
+        <v>1.84</v>
+      </c>
+      <c r="U12">
+        <v>2.06</v>
+      </c>
+      <c r="V12">
+        <v>3.25</v>
+      </c>
+      <c r="W12">
+        <v>1.12</v>
+      </c>
+      <c r="X12">
+        <v>27</v>
+      </c>
+      <c r="Y12">
+        <v>11</v>
+      </c>
+      <c r="Z12">
+        <v>10</v>
+      </c>
+      <c r="AA12">
+        <v>13</v>
+      </c>
+      <c r="AB12">
+        <v>36</v>
+      </c>
+      <c r="AC12">
+        <v>12.5</v>
+      </c>
+      <c r="AD12">
+        <v>11</v>
+      </c>
+      <c r="AE12">
+        <v>15</v>
+      </c>
+      <c r="AF12">
+        <v>90</v>
+      </c>
+      <c r="AG12">
+        <v>34</v>
+      </c>
+      <c r="AH12">
+        <v>25</v>
+      </c>
+      <c r="AI12">
+        <v>34</v>
+      </c>
+      <c r="AJ12">
+        <v>310</v>
+      </c>
+      <c r="AK12">
+        <v>130</v>
+      </c>
+      <c r="AL12">
+        <v>110</v>
+      </c>
+      <c r="AM12">
+        <v>130</v>
+      </c>
+      <c r="AN12">
         <v>150</v>
       </c>
-      <c r="F12">
-        <v>3.2</v>
-      </c>
-      <c r="G12">
-        <v>3.25</v>
-      </c>
-      <c r="H12">
-        <v>2.34</v>
-      </c>
-      <c r="I12">
-        <v>2.38</v>
-      </c>
-      <c r="J12">
-        <v>3.7</v>
-      </c>
-      <c r="K12">
-        <v>3.8</v>
-      </c>
-      <c r="L12">
-        <v>1.34</v>
-      </c>
-      <c r="M12">
-        <v>1.05</v>
-      </c>
-      <c r="N12">
-        <v>5</v>
-      </c>
-      <c r="O12">
-        <v>1.23</v>
-      </c>
-      <c r="P12">
-        <v>2.34</v>
-      </c>
-      <c r="Q12">
-        <v>1.73</v>
-      </c>
-      <c r="R12">
-        <v>1.53</v>
-      </c>
-      <c r="S12">
-        <v>2.78</v>
-      </c>
-      <c r="T12">
-        <v>1.61</v>
-      </c>
-      <c r="U12">
-        <v>2.52</v>
-      </c>
-      <c r="V12">
-        <v>1.72</v>
-      </c>
-      <c r="W12">
-        <v>1.44</v>
-      </c>
-      <c r="X12">
-        <v>19</v>
-      </c>
-      <c r="Y12">
-        <v>13.5</v>
-      </c>
-      <c r="Z12">
+      <c r="AO12">
+        <v>5.5</v>
+      </c>
+      <c r="AP12">
+        <v>19.5</v>
+      </c>
+      <c r="AQ12">
+        <v>9.4</v>
+      </c>
+      <c r="AR12">
+        <v>8.4</v>
+      </c>
+      <c r="AS12">
+        <v>10.5</v>
+      </c>
+      <c r="AT12">
+        <v>23</v>
+      </c>
+      <c r="AU12">
+        <v>10.5</v>
+      </c>
+      <c r="AV12">
+        <v>9.4</v>
+      </c>
+      <c r="AW12">
+        <v>12.5</v>
+      </c>
+      <c r="AX12">
+        <v>9</v>
+      </c>
+      <c r="AY12">
+        <v>22</v>
+      </c>
+      <c r="AZ12">
+        <v>19.5</v>
+      </c>
+      <c r="BA12">
+        <v>23</v>
+      </c>
+      <c r="BB12">
+        <v>9.6</v>
+      </c>
+      <c r="BC12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG12">
+        <v>4.8</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>3.5</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>7.4</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>26</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>7.8</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>17</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
         <v>17.5</v>
       </c>
-      <c r="AA12">
-        <v>32</v>
-      </c>
-      <c r="AB12">
-        <v>16.5</v>
-      </c>
-      <c r="AC12">
-        <v>8.6</v>
-      </c>
-      <c r="AD12">
-        <v>11.5</v>
-      </c>
-      <c r="AE12">
-        <v>23</v>
-      </c>
-      <c r="AF12">
-        <v>25</v>
-      </c>
-      <c r="AG12">
-        <v>14</v>
-      </c>
-      <c r="AH12">
-        <v>15</v>
-      </c>
-      <c r="AI12">
-        <v>30</v>
-      </c>
-      <c r="AJ12">
-        <v>55</v>
-      </c>
-      <c r="AK12">
-        <v>34</v>
-      </c>
-      <c r="AL12">
-        <v>38</v>
-      </c>
-      <c r="AM12">
-        <v>65</v>
-      </c>
-      <c r="AN12">
-        <v>23</v>
-      </c>
-      <c r="AO12">
-        <v>14</v>
-      </c>
-      <c r="AP12">
-        <v>17.5</v>
-      </c>
-      <c r="AQ12">
-        <v>12</v>
-      </c>
-      <c r="AR12">
-        <v>15.5</v>
-      </c>
-      <c r="AS12">
-        <v>28</v>
-      </c>
-      <c r="AT12">
-        <v>14.5</v>
-      </c>
-      <c r="AU12">
-        <v>7.8</v>
-      </c>
-      <c r="AV12">
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>3.35</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>5.3</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
         <v>10</v>
       </c>
-      <c r="AW12">
-        <v>20</v>
-      </c>
-      <c r="AX12">
-        <v>22</v>
-      </c>
-      <c r="AY12">
-        <v>12.5</v>
-      </c>
-      <c r="AZ12">
-        <v>13.5</v>
-      </c>
-      <c r="BA12">
-        <v>27</v>
-      </c>
-      <c r="BB12">
-        <v>46</v>
-      </c>
-      <c r="BC12">
-        <v>29</v>
-      </c>
-      <c r="BD12">
-        <v>32</v>
-      </c>
-      <c r="BE12">
-        <v>50</v>
-      </c>
-      <c r="BF12">
-        <v>20</v>
-      </c>
-      <c r="BG12">
-        <v>12</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>3.3</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>6.2</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.01</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>4.3</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.01</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.01</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>3.85</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>8.6</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.01</v>
-      </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3782,276 +3791,276 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="G13">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="H13">
+        <v>2.34</v>
+      </c>
+      <c r="I13">
+        <v>2.38</v>
+      </c>
+      <c r="J13">
+        <v>3.7</v>
+      </c>
+      <c r="K13">
+        <v>3.75</v>
+      </c>
+      <c r="L13">
+        <v>1.34</v>
+      </c>
+      <c r="M13">
+        <v>1.05</v>
+      </c>
+      <c r="N13">
+        <v>4.9</v>
+      </c>
+      <c r="O13">
+        <v>1.24</v>
+      </c>
+      <c r="P13">
+        <v>2.3</v>
+      </c>
+      <c r="Q13">
+        <v>1.74</v>
+      </c>
+      <c r="R13">
+        <v>1.53</v>
+      </c>
+      <c r="S13">
+        <v>2.78</v>
+      </c>
+      <c r="T13">
+        <v>1.62</v>
+      </c>
+      <c r="U13">
+        <v>2.52</v>
+      </c>
+      <c r="V13">
+        <v>1.72</v>
+      </c>
+      <c r="W13">
+        <v>1.43</v>
+      </c>
+      <c r="X13">
+        <v>19</v>
+      </c>
+      <c r="Y13">
+        <v>13.5</v>
+      </c>
+      <c r="Z13">
+        <v>17.5</v>
+      </c>
+      <c r="AA13">
+        <v>32</v>
+      </c>
+      <c r="AB13">
+        <v>16.5</v>
+      </c>
+      <c r="AC13">
+        <v>8.6</v>
+      </c>
+      <c r="AD13">
+        <v>11.5</v>
+      </c>
+      <c r="AE13">
+        <v>23</v>
+      </c>
+      <c r="AF13">
+        <v>25</v>
+      </c>
+      <c r="AG13">
+        <v>14</v>
+      </c>
+      <c r="AH13">
+        <v>15</v>
+      </c>
+      <c r="AI13">
+        <v>32</v>
+      </c>
+      <c r="AJ13">
+        <v>55</v>
+      </c>
+      <c r="AK13">
+        <v>34</v>
+      </c>
+      <c r="AL13">
+        <v>38</v>
+      </c>
+      <c r="AM13">
+        <v>65</v>
+      </c>
+      <c r="AN13">
+        <v>24</v>
+      </c>
+      <c r="AO13">
+        <v>14.5</v>
+      </c>
+      <c r="AP13">
+        <v>17</v>
+      </c>
+      <c r="AQ13">
         <v>12</v>
       </c>
-      <c r="I13">
-        <v>870</v>
-      </c>
-      <c r="J13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K13">
-        <v>950</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>3.6</v>
-      </c>
-      <c r="O13">
-        <v>1.01</v>
-      </c>
-      <c r="P13">
-        <v>3.6</v>
-      </c>
-      <c r="Q13">
-        <v>1.01</v>
-      </c>
-      <c r="R13">
-        <v>1.94</v>
-      </c>
-      <c r="S13">
-        <v>1.6</v>
-      </c>
-      <c r="T13">
-        <v>1.01</v>
-      </c>
-      <c r="U13">
-        <v>1.01</v>
-      </c>
-      <c r="V13">
-        <v>1.01</v>
-      </c>
-      <c r="W13">
-        <v>4.8</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>1000</v>
-      </c>
-      <c r="AC13">
-        <v>1000</v>
-      </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
-        <v>1000</v>
-      </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.03</v>
-      </c>
-      <c r="AQ13">
-        <v>1.03</v>
-      </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH13">
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F14">
-        <v>2.34</v>
+        <v>1.1</v>
       </c>
       <c r="G14">
-        <v>2.82</v>
+        <v>1.25</v>
       </c>
       <c r="H14">
-        <v>2.52</v>
+        <v>12</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>870</v>
       </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K14">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4060,22 +4069,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="O14">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P14">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q14">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="R14">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="S14">
-        <v>2.64</v>
+        <v>1.6</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4084,10 +4093,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>1.54</v>
+        <v>4.8</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4252,48 +4261,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F15">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="G15">
-        <v>3.65</v>
+        <v>2.82</v>
       </c>
       <c r="H15">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="I15">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4302,22 +4311,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="O15">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="P15">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q15">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S15">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4326,10 +4335,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4494,72 +4503,72 @@
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F16">
+        <v>2.68</v>
+      </c>
+      <c r="G16">
+        <v>3.65</v>
+      </c>
+      <c r="H16">
+        <v>2.1</v>
+      </c>
+      <c r="I16">
+        <v>2.94</v>
+      </c>
+      <c r="J16">
+        <v>3.2</v>
+      </c>
+      <c r="K16">
+        <v>6.8</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>2.68</v>
+      </c>
+      <c r="O16">
+        <v>1.11</v>
+      </c>
+      <c r="P16">
         <v>2.22</v>
       </c>
-      <c r="G16">
-        <v>3.3</v>
-      </c>
-      <c r="H16">
-        <v>2.22</v>
-      </c>
-      <c r="I16">
-        <v>3.25</v>
-      </c>
-      <c r="J16">
-        <v>3.25</v>
-      </c>
-      <c r="K16">
-        <v>15</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>4.4</v>
-      </c>
-      <c r="O16">
-        <v>1.21</v>
-      </c>
-      <c r="P16">
-        <v>2.08</v>
-      </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="R16">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S16">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4568,10 +4577,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4736,48 +4745,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F17">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G17">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="H17">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="I17">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J17">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K17">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4786,22 +4795,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O17">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q17">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S17">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4810,10 +4819,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4984,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4992,563 +5001,563 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F18">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="G18">
-        <v>1.74</v>
+        <v>2.46</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="I18">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="J18">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="K18">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="L18">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="O18">
+        <v>1.01</v>
+      </c>
+      <c r="P18">
+        <v>2.12</v>
+      </c>
+      <c r="Q18">
+        <v>1.62</v>
+      </c>
+      <c r="R18">
         <v>1.43</v>
       </c>
-      <c r="P18">
-        <v>1.75</v>
-      </c>
-      <c r="Q18">
-        <v>2.3</v>
-      </c>
-      <c r="R18">
-        <v>1.27</v>
-      </c>
       <c r="S18">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="T18">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="W18">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="X18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA18">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F19">
-        <v>7.4</v>
+        <v>1.72</v>
       </c>
       <c r="G19">
-        <v>13</v>
+        <v>1.74</v>
       </c>
       <c r="H19">
-        <v>1.49</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>1.63</v>
+        <v>6.4</v>
       </c>
       <c r="J19">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M19">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="P19">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S19">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T19">
+        <v>2.2</v>
+      </c>
+      <c r="U19">
+        <v>1.8</v>
+      </c>
+      <c r="V19">
+        <v>1.18</v>
+      </c>
+      <c r="W19">
         <v>2.34</v>
       </c>
-      <c r="U19">
-        <v>1.53</v>
-      </c>
-      <c r="V19">
-        <v>2.54</v>
-      </c>
-      <c r="W19">
-        <v>1.09</v>
-      </c>
       <c r="X19">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP19">
-        <v>1.41</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19">
-        <v>1.29</v>
+        <v>15</v>
       </c>
       <c r="AR19">
-        <v>1.35</v>
+        <v>30</v>
       </c>
       <c r="AS19">
-        <v>1.54</v>
+        <v>44</v>
       </c>
       <c r="AT19">
-        <v>1.54</v>
+        <v>6.4</v>
       </c>
       <c r="AU19">
-        <v>1.41</v>
+        <v>8</v>
       </c>
       <c r="AV19">
-        <v>1.54</v>
+        <v>22</v>
       </c>
       <c r="AW19">
-        <v>1.55</v>
+        <v>38</v>
       </c>
       <c r="AX19">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="AY19">
-        <v>1.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>1.54</v>
+        <v>24</v>
       </c>
       <c r="BA19">
-        <v>1.55</v>
+        <v>40</v>
       </c>
       <c r="BB19">
-        <v>1.55</v>
+        <v>15.5</v>
       </c>
       <c r="BC19">
-        <v>1.55</v>
+        <v>18.5</v>
       </c>
       <c r="BD19">
-        <v>1.55</v>
+        <v>42</v>
       </c>
       <c r="BE19">
-        <v>1.55</v>
+        <v>46</v>
       </c>
       <c r="BF19">
-        <v>1.55</v>
+        <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>1.54</v>
+        <v>42</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI19">
-        <v>1.27</v>
+        <v>2.82</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
-        <v>1.27</v>
+        <v>10</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM19">
-        <v>1.27</v>
+        <v>34</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO19">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19">
-        <v>1.27</v>
+        <v>11</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS19">
-        <v>1.27</v>
+        <v>10.5</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU19">
-        <v>1.49</v>
+        <v>8</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW19">
-        <v>1.27</v>
+        <v>12</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY19">
-        <v>1.27</v>
+        <v>12.5</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA19">
-        <v>1.27</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F20">
+        <v>7.6</v>
+      </c>
+      <c r="G20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H20">
+        <v>1.55</v>
+      </c>
+      <c r="I20">
+        <v>1.59</v>
+      </c>
+      <c r="J20">
+        <v>3.85</v>
+      </c>
+      <c r="K20">
         <v>4.2</v>
       </c>
-      <c r="G20">
-        <v>5.7</v>
-      </c>
-      <c r="H20">
-        <v>1.91</v>
-      </c>
-      <c r="I20">
-        <v>2.22</v>
-      </c>
-      <c r="J20">
-        <v>2.96</v>
-      </c>
-      <c r="K20">
-        <v>950</v>
-      </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N20">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="O20">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="P20">
+        <v>1.64</v>
+      </c>
+      <c r="Q20">
+        <v>2.46</v>
+      </c>
+      <c r="R20">
+        <v>1.23</v>
+      </c>
+      <c r="S20">
+        <v>4.9</v>
+      </c>
+      <c r="T20">
+        <v>2.34</v>
+      </c>
+      <c r="U20">
         <v>1.52</v>
       </c>
-      <c r="Q20">
-        <v>1.96</v>
-      </c>
-      <c r="R20">
-        <v>1.08</v>
-      </c>
-      <c r="S20">
-        <v>3</v>
-      </c>
-      <c r="T20">
-        <v>2.14</v>
-      </c>
-      <c r="U20">
-        <v>1.01</v>
-      </c>
       <c r="V20">
-        <v>1.82</v>
+        <v>2.68</v>
       </c>
       <c r="W20">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA20">
         <v>1000</v>
@@ -5557,7 +5566,7 @@
         <v>1000</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD20">
         <v>1000</v>
@@ -5596,180 +5605,180 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.28</v>
+        <v>1.27</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>3.25</v>
+        <v>1.49</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="CB20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F21">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="G21">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H21">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="I21">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="J21">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="K21">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N21">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="O21">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P21">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="Q21">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="R21">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="S21">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5778,10 +5787,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="W21">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5895,7 +5904,7 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5931,7 +5940,7 @@
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -5952,66 +5961,66 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
         <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F22">
-        <v>1.33</v>
+        <v>3.75</v>
       </c>
       <c r="G22">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="H22">
-        <v>9</v>
+        <v>1.75</v>
       </c>
       <c r="I22">
-        <v>870</v>
+        <v>2.02</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K22">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="O22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P22">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="R22">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="S22">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6020,10 +6029,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="W22">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6134,344 +6143,344 @@
         <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="G23">
+        <v>1.53</v>
+      </c>
+      <c r="H23">
+        <v>8.6</v>
+      </c>
+      <c r="I23">
+        <v>870</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
         <v>5.1</v>
       </c>
-      <c r="H23">
-        <v>1.73</v>
-      </c>
-      <c r="I23">
-        <v>2.14</v>
-      </c>
-      <c r="J23">
-        <v>3.5</v>
-      </c>
-      <c r="K23">
-        <v>16.5</v>
-      </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="O23">
+        <v>1.06</v>
+      </c>
+      <c r="P23">
+        <v>1.52</v>
+      </c>
+      <c r="Q23">
+        <v>2.02</v>
+      </c>
+      <c r="R23">
+        <v>1.17</v>
+      </c>
+      <c r="S23">
+        <v>2.78</v>
+      </c>
+      <c r="T23">
+        <v>1.01</v>
+      </c>
+      <c r="U23">
+        <v>1.01</v>
+      </c>
+      <c r="V23">
+        <v>1.01</v>
+      </c>
+      <c r="W23">
+        <v>2.88</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>1000</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>1000</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23">
+        <v>1.03</v>
+      </c>
+      <c r="AR23">
+        <v>1.03</v>
+      </c>
+      <c r="AS23">
+        <v>1.03</v>
+      </c>
+      <c r="AT23">
+        <v>1.03</v>
+      </c>
+      <c r="AU23">
+        <v>1.03</v>
+      </c>
+      <c r="AV23">
+        <v>1.03</v>
+      </c>
+      <c r="AW23">
+        <v>1.03</v>
+      </c>
+      <c r="AX23">
+        <v>1.03</v>
+      </c>
+      <c r="AY23">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23">
+        <v>1.03</v>
+      </c>
+      <c r="BA23">
+        <v>1.03</v>
+      </c>
+      <c r="BB23">
+        <v>1.03</v>
+      </c>
+      <c r="BC23">
+        <v>1.03</v>
+      </c>
+      <c r="BD23">
+        <v>1.03</v>
+      </c>
+      <c r="BE23">
+        <v>1.03</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>3.8</v>
+      </c>
+      <c r="BI23">
         <v>1.02</v>
       </c>
-      <c r="P23">
-        <v>2.28</v>
-      </c>
-      <c r="Q23">
-        <v>1.41</v>
-      </c>
-      <c r="R23">
-        <v>1.54</v>
-      </c>
-      <c r="S23">
-        <v>2.24</v>
-      </c>
-      <c r="T23">
-        <v>1.01</v>
-      </c>
-      <c r="U23">
-        <v>1.01</v>
-      </c>
-      <c r="V23">
-        <v>1.87</v>
-      </c>
-      <c r="W23">
-        <v>1.24</v>
-      </c>
-      <c r="X23">
-        <v>1000</v>
-      </c>
-      <c r="Y23">
-        <v>1000</v>
-      </c>
-      <c r="Z23">
-        <v>1000</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>1000</v>
-      </c>
-      <c r="AC23">
-        <v>1000</v>
-      </c>
-      <c r="AD23">
-        <v>1000</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
-        <v>1000</v>
-      </c>
-      <c r="AG23">
-        <v>1000</v>
-      </c>
-      <c r="AH23">
-        <v>1000</v>
-      </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>1000</v>
-      </c>
-      <c r="AK23">
-        <v>1000</v>
-      </c>
-      <c r="AL23">
-        <v>1000</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>1000</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>1.03</v>
-      </c>
-      <c r="AQ23">
-        <v>1.03</v>
-      </c>
-      <c r="AR23">
-        <v>1.03</v>
-      </c>
-      <c r="AS23">
-        <v>1.03</v>
-      </c>
-      <c r="AT23">
-        <v>1.03</v>
-      </c>
-      <c r="AU23">
-        <v>1.03</v>
-      </c>
-      <c r="AV23">
-        <v>1.03</v>
-      </c>
-      <c r="AW23">
-        <v>1.03</v>
-      </c>
-      <c r="AX23">
-        <v>1.03</v>
-      </c>
-      <c r="AY23">
-        <v>1.03</v>
-      </c>
-      <c r="AZ23">
-        <v>1.03</v>
-      </c>
-      <c r="BA23">
-        <v>1.03</v>
-      </c>
-      <c r="BB23">
-        <v>1.03</v>
-      </c>
-      <c r="BC23">
-        <v>1.03</v>
-      </c>
-      <c r="BD23">
-        <v>1.03</v>
-      </c>
-      <c r="BE23">
-        <v>1.03</v>
-      </c>
-      <c r="BF23">
-        <v>1.01</v>
-      </c>
-      <c r="BG23">
-        <v>1.01</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.01</v>
-      </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="CB23" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F24">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>600</v>
+        <v>5.1</v>
       </c>
       <c r="H24">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="I24">
-        <v>870</v>
+        <v>2.14</v>
       </c>
       <c r="J24">
-        <v>1.12</v>
+        <v>3.5</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6480,35 +6489,35 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="O24">
         <v>1.02</v>
       </c>
       <c r="P24">
+        <v>2.28</v>
+      </c>
+      <c r="Q24">
+        <v>1.41</v>
+      </c>
+      <c r="R24">
+        <v>1.54</v>
+      </c>
+      <c r="S24">
+        <v>2.24</v>
+      </c>
+      <c r="T24">
+        <v>1.01</v>
+      </c>
+      <c r="U24">
+        <v>1.01</v>
+      </c>
+      <c r="V24">
+        <v>1.87</v>
+      </c>
+      <c r="W24">
         <v>1.24</v>
       </c>
-      <c r="Q24">
-        <v>1.02</v>
-      </c>
-      <c r="R24">
-        <v>1.07</v>
-      </c>
-      <c r="S24">
-        <v>1.02</v>
-      </c>
-      <c r="T24">
-        <v>1.01</v>
-      </c>
-      <c r="U24">
-        <v>1.01</v>
-      </c>
-      <c r="V24">
-        <v>1.03</v>
-      </c>
-      <c r="W24">
-        <v>1.03</v>
-      </c>
       <c r="X24">
         <v>1000</v>
       </c>
@@ -6672,1817 +6681,1817 @@
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F25">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="G25">
-        <v>1.45</v>
+        <v>600</v>
       </c>
       <c r="H25">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="I25">
-        <v>8.800000000000001</v>
+        <v>870</v>
       </c>
       <c r="J25">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="K25">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L25">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>1.24</v>
+      </c>
+      <c r="O25">
+        <v>1.02</v>
+      </c>
+      <c r="P25">
+        <v>1.24</v>
+      </c>
+      <c r="Q25">
+        <v>1.02</v>
+      </c>
+      <c r="R25">
+        <v>1.07</v>
+      </c>
+      <c r="S25">
+        <v>1.02</v>
+      </c>
+      <c r="T25">
+        <v>1.01</v>
+      </c>
+      <c r="U25">
+        <v>1.01</v>
+      </c>
+      <c r="V25">
         <v>1.04</v>
       </c>
-      <c r="N25">
-        <v>5.1</v>
-      </c>
-      <c r="O25">
-        <v>1.22</v>
-      </c>
-      <c r="P25">
-        <v>2.44</v>
-      </c>
-      <c r="Q25">
-        <v>1.67</v>
-      </c>
-      <c r="R25">
-        <v>1.54</v>
-      </c>
-      <c r="S25">
-        <v>2.72</v>
-      </c>
-      <c r="T25">
-        <v>1.9</v>
-      </c>
-      <c r="U25">
-        <v>2</v>
-      </c>
-      <c r="V25">
-        <v>1.13</v>
-      </c>
       <c r="W25">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AR25">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AT25">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU25">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV25">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AX25">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY25">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BA25">
-        <v>75</v>
+        <v>1.03</v>
       </c>
       <c r="BB25">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC25">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD25">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="BF25">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F26">
+        <v>1.43</v>
+      </c>
+      <c r="G26">
+        <v>1.45</v>
+      </c>
+      <c r="H26">
+        <v>8</v>
+      </c>
+      <c r="I26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J26">
+        <v>5.2</v>
+      </c>
+      <c r="K26">
+        <v>5.4</v>
+      </c>
+      <c r="L26">
+        <v>1.33</v>
+      </c>
+      <c r="M26">
+        <v>1.04</v>
+      </c>
+      <c r="N26">
+        <v>5.2</v>
+      </c>
+      <c r="O26">
+        <v>1.22</v>
+      </c>
+      <c r="P26">
+        <v>2.44</v>
+      </c>
+      <c r="Q26">
+        <v>1.67</v>
+      </c>
+      <c r="R26">
+        <v>1.55</v>
+      </c>
+      <c r="S26">
+        <v>2.74</v>
+      </c>
+      <c r="T26">
+        <v>1.9</v>
+      </c>
+      <c r="U26">
+        <v>2</v>
+      </c>
+      <c r="V26">
+        <v>1.13</v>
+      </c>
+      <c r="W26">
+        <v>3.2</v>
+      </c>
+      <c r="X26">
+        <v>23</v>
+      </c>
+      <c r="Y26">
+        <v>30</v>
+      </c>
+      <c r="Z26">
+        <v>75</v>
+      </c>
+      <c r="AA26">
+        <v>280</v>
+      </c>
+      <c r="AB26">
+        <v>10</v>
+      </c>
+      <c r="AC26">
+        <v>12</v>
+      </c>
+      <c r="AD26">
+        <v>32</v>
+      </c>
+      <c r="AE26">
+        <v>120</v>
+      </c>
+      <c r="AF26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG26">
+        <v>10.5</v>
+      </c>
+      <c r="AH26">
+        <v>25</v>
+      </c>
+      <c r="AI26">
+        <v>110</v>
+      </c>
+      <c r="AJ26">
+        <v>12.5</v>
+      </c>
+      <c r="AK26">
+        <v>14.5</v>
+      </c>
+      <c r="AL26">
+        <v>34</v>
+      </c>
+      <c r="AM26">
         <v>130</v>
       </c>
-      <c r="E26" t="s">
-        <v>164</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>3.15</v>
-      </c>
-      <c r="H26">
-        <v>2.44</v>
-      </c>
-      <c r="I26">
-        <v>2.54</v>
-      </c>
-      <c r="J26">
-        <v>3.55</v>
-      </c>
-      <c r="K26">
-        <v>3.65</v>
-      </c>
-      <c r="L26">
-        <v>1.01</v>
-      </c>
-      <c r="M26">
-        <v>1.06</v>
-      </c>
-      <c r="N26">
-        <v>4.1</v>
-      </c>
-      <c r="O26">
-        <v>1.28</v>
-      </c>
-      <c r="P26">
-        <v>2.06</v>
-      </c>
-      <c r="Q26">
-        <v>1.79</v>
-      </c>
-      <c r="R26">
-        <v>1.43</v>
-      </c>
-      <c r="S26">
-        <v>3</v>
-      </c>
-      <c r="T26">
-        <v>1.65</v>
-      </c>
-      <c r="U26">
-        <v>2.28</v>
-      </c>
-      <c r="V26">
-        <v>1.64</v>
-      </c>
-      <c r="W26">
-        <v>1.46</v>
-      </c>
-      <c r="X26">
+      <c r="AN26">
+        <v>5.9</v>
+      </c>
+      <c r="AO26">
+        <v>130</v>
+      </c>
+      <c r="AP26">
+        <v>19.5</v>
+      </c>
+      <c r="AQ26">
+        <v>26</v>
+      </c>
+      <c r="AR26">
+        <v>32</v>
+      </c>
+      <c r="AS26">
+        <v>50</v>
+      </c>
+      <c r="AT26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU26">
+        <v>10.5</v>
+      </c>
+      <c r="AV26">
+        <v>26</v>
+      </c>
+      <c r="AW26">
+        <v>40</v>
+      </c>
+      <c r="AX26">
+        <v>8.4</v>
+      </c>
+      <c r="AY26">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26">
+        <v>21</v>
+      </c>
+      <c r="BA26">
+        <v>75</v>
+      </c>
+      <c r="BB26">
+        <v>11</v>
+      </c>
+      <c r="BC26">
+        <v>13</v>
+      </c>
+      <c r="BD26">
+        <v>28</v>
+      </c>
+      <c r="BE26">
+        <v>42</v>
+      </c>
+      <c r="BF26">
+        <v>5.5</v>
+      </c>
+      <c r="BG26">
+        <v>42</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>3.35</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>8.4</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>3.4</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>2.1</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>6.4</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>2.3</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>17</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
         <v>17.5</v>
       </c>
-      <c r="Y26">
-        <v>12</v>
-      </c>
-      <c r="Z26">
-        <v>17.5</v>
-      </c>
-      <c r="AA26">
-        <v>38</v>
-      </c>
-      <c r="AB26">
-        <v>14</v>
-      </c>
-      <c r="AC26">
-        <v>8.6</v>
-      </c>
-      <c r="AD26">
-        <v>12.5</v>
-      </c>
-      <c r="AE26">
-        <v>27</v>
-      </c>
-      <c r="AF26">
-        <v>23</v>
-      </c>
-      <c r="AG26">
-        <v>14</v>
-      </c>
-      <c r="AH26">
-        <v>17</v>
-      </c>
-      <c r="AI26">
-        <v>38</v>
-      </c>
-      <c r="AJ26">
-        <v>55</v>
-      </c>
-      <c r="AK26">
-        <v>34</v>
-      </c>
-      <c r="AL26">
-        <v>44</v>
-      </c>
-      <c r="AM26">
-        <v>80</v>
-      </c>
-      <c r="AN26">
-        <v>26</v>
-      </c>
-      <c r="AO26">
-        <v>18.5</v>
-      </c>
-      <c r="AP26">
-        <v>14</v>
-      </c>
-      <c r="AQ26">
-        <v>10.5</v>
-      </c>
-      <c r="AR26">
-        <v>15</v>
-      </c>
-      <c r="AS26">
-        <v>8</v>
-      </c>
-      <c r="AT26">
-        <v>11.5</v>
-      </c>
-      <c r="AU26">
-        <v>7.2</v>
-      </c>
-      <c r="AV26">
-        <v>10</v>
-      </c>
-      <c r="AW26">
-        <v>22</v>
-      </c>
-      <c r="AX26">
-        <v>18.5</v>
-      </c>
-      <c r="AY26">
-        <v>11.5</v>
-      </c>
-      <c r="AZ26">
-        <v>14</v>
-      </c>
-      <c r="BA26">
-        <v>8</v>
-      </c>
-      <c r="BB26">
-        <v>8.6</v>
-      </c>
-      <c r="BC26">
-        <v>7.8</v>
-      </c>
-      <c r="BD26">
-        <v>8.4</v>
-      </c>
-      <c r="BE26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF26">
-        <v>21</v>
-      </c>
-      <c r="BG26">
-        <v>15</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.04</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>1.04</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>1.04</v>
-      </c>
-      <c r="BN26">
-        <v>1000</v>
-      </c>
-      <c r="BO26">
-        <v>1.04</v>
-      </c>
-      <c r="BP26">
-        <v>1000</v>
-      </c>
-      <c r="BQ26">
-        <v>1.04</v>
-      </c>
-      <c r="BR26">
-        <v>1000</v>
-      </c>
-      <c r="BS26">
-        <v>1.04</v>
-      </c>
-      <c r="BT26">
-        <v>1000</v>
-      </c>
-      <c r="BU26">
-        <v>1.04</v>
-      </c>
-      <c r="BV26">
-        <v>1000</v>
-      </c>
-      <c r="BW26">
-        <v>1.04</v>
-      </c>
-      <c r="BX26">
-        <v>1000</v>
-      </c>
-      <c r="BY26">
-        <v>1.04</v>
-      </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F27">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>1.6</v>
+        <v>3.15</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>2.44</v>
       </c>
       <c r="I27">
-        <v>6.6</v>
+        <v>2.52</v>
       </c>
       <c r="J27">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="L27">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
+        <v>1.06</v>
+      </c>
+      <c r="N27">
+        <v>3.9</v>
+      </c>
+      <c r="O27">
+        <v>1.29</v>
+      </c>
+      <c r="P27">
+        <v>2</v>
+      </c>
+      <c r="Q27">
+        <v>1.85</v>
+      </c>
+      <c r="R27">
+        <v>1.4</v>
+      </c>
+      <c r="S27">
+        <v>3.15</v>
+      </c>
+      <c r="T27">
+        <v>1.67</v>
+      </c>
+      <c r="U27">
+        <v>2.22</v>
+      </c>
+      <c r="V27">
+        <v>1.65</v>
+      </c>
+      <c r="W27">
+        <v>1.46</v>
+      </c>
+      <c r="X27">
+        <v>16.5</v>
+      </c>
+      <c r="Y27">
+        <v>12</v>
+      </c>
+      <c r="Z27">
+        <v>17.5</v>
+      </c>
+      <c r="AA27">
+        <v>36</v>
+      </c>
+      <c r="AB27">
+        <v>14</v>
+      </c>
+      <c r="AC27">
+        <v>8.6</v>
+      </c>
+      <c r="AD27">
+        <v>12.5</v>
+      </c>
+      <c r="AE27">
+        <v>27</v>
+      </c>
+      <c r="AF27">
+        <v>23</v>
+      </c>
+      <c r="AG27">
+        <v>14</v>
+      </c>
+      <c r="AH27">
+        <v>17</v>
+      </c>
+      <c r="AI27">
+        <v>38</v>
+      </c>
+      <c r="AJ27">
+        <v>55</v>
+      </c>
+      <c r="AK27">
+        <v>38</v>
+      </c>
+      <c r="AL27">
+        <v>44</v>
+      </c>
+      <c r="AM27">
+        <v>80</v>
+      </c>
+      <c r="AN27">
+        <v>28</v>
+      </c>
+      <c r="AO27">
+        <v>19</v>
+      </c>
+      <c r="AP27">
+        <v>13.5</v>
+      </c>
+      <c r="AQ27">
+        <v>10</v>
+      </c>
+      <c r="AR27">
+        <v>14.5</v>
+      </c>
+      <c r="AS27">
+        <v>7.8</v>
+      </c>
+      <c r="AT27">
+        <v>11.5</v>
+      </c>
+      <c r="AU27">
+        <v>7</v>
+      </c>
+      <c r="AV27">
+        <v>10</v>
+      </c>
+      <c r="AW27">
+        <v>22</v>
+      </c>
+      <c r="AX27">
+        <v>18.5</v>
+      </c>
+      <c r="AY27">
+        <v>11.5</v>
+      </c>
+      <c r="AZ27">
+        <v>14</v>
+      </c>
+      <c r="BA27">
+        <v>8</v>
+      </c>
+      <c r="BB27">
+        <v>8.4</v>
+      </c>
+      <c r="BC27">
+        <v>8</v>
+      </c>
+      <c r="BD27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE27">
+        <v>9</v>
+      </c>
+      <c r="BF27">
+        <v>7.4</v>
+      </c>
+      <c r="BG27">
+        <v>15.5</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
         <v>1.04</v>
       </c>
-      <c r="N27">
-        <v>5.2</v>
-      </c>
-      <c r="O27">
-        <v>1.22</v>
-      </c>
-      <c r="P27">
-        <v>2.42</v>
-      </c>
-      <c r="Q27">
-        <v>1.65</v>
-      </c>
-      <c r="R27">
-        <v>1.56</v>
-      </c>
-      <c r="S27">
-        <v>2.68</v>
-      </c>
-      <c r="T27">
-        <v>1.76</v>
-      </c>
-      <c r="U27">
-        <v>2.18</v>
-      </c>
-      <c r="V27">
-        <v>1.18</v>
-      </c>
-      <c r="W27">
-        <v>2.66</v>
-      </c>
-      <c r="X27">
-        <v>24</v>
-      </c>
-      <c r="Y27">
-        <v>26</v>
-      </c>
-      <c r="Z27">
-        <v>65</v>
-      </c>
-      <c r="AA27">
-        <v>190</v>
-      </c>
-      <c r="AB27">
-        <v>11</v>
-      </c>
-      <c r="AC27">
-        <v>11</v>
-      </c>
-      <c r="AD27">
-        <v>25</v>
-      </c>
-      <c r="AE27">
-        <v>90</v>
-      </c>
-      <c r="AF27">
-        <v>11</v>
-      </c>
-      <c r="AG27">
-        <v>10.5</v>
-      </c>
-      <c r="AH27">
-        <v>23</v>
-      </c>
-      <c r="AI27">
-        <v>85</v>
-      </c>
-      <c r="AJ27">
-        <v>15.5</v>
-      </c>
-      <c r="AK27">
-        <v>16.5</v>
-      </c>
-      <c r="AL27">
-        <v>36</v>
-      </c>
-      <c r="AM27">
-        <v>110</v>
-      </c>
-      <c r="AN27">
-        <v>6.8</v>
-      </c>
-      <c r="AO27">
-        <v>90</v>
-      </c>
-      <c r="AP27">
-        <v>20</v>
-      </c>
-      <c r="AQ27">
-        <v>22</v>
-      </c>
-      <c r="AR27">
-        <v>8.4</v>
-      </c>
-      <c r="AS27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT27">
-        <v>9.6</v>
-      </c>
-      <c r="AU27">
-        <v>9.6</v>
-      </c>
-      <c r="AV27">
-        <v>20</v>
-      </c>
-      <c r="AW27">
-        <v>8.6</v>
-      </c>
-      <c r="AX27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY27">
-        <v>9</v>
-      </c>
-      <c r="AZ27">
-        <v>17.5</v>
-      </c>
-      <c r="BA27">
-        <v>8.6</v>
-      </c>
-      <c r="BB27">
-        <v>13.5</v>
-      </c>
-      <c r="BC27">
-        <v>14</v>
-      </c>
-      <c r="BD27">
-        <v>7.4</v>
-      </c>
-      <c r="BE27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF27">
-        <v>6</v>
-      </c>
-      <c r="BG27">
-        <v>8.6</v>
-      </c>
-      <c r="BH27">
-        <v>1000</v>
-      </c>
-      <c r="BI27">
-        <v>3.45</v>
-      </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F28">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="G28">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>6.6</v>
+      </c>
+      <c r="J28">
         <v>4.6</v>
       </c>
-      <c r="I28">
-        <v>4.8</v>
-      </c>
-      <c r="J28">
-        <v>4.3</v>
-      </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O28">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P28">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q28">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R28">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="S28">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T28">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="U28">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="V28">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="W28">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="X28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y28">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z28">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AA28">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="AB28">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD28">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AE28">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AF28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG28">
         <v>10.5</v>
       </c>
       <c r="AH28">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AI28">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ28">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK28">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL28">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN28">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AO28">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AP28">
         <v>20</v>
       </c>
       <c r="AQ28">
+        <v>22</v>
+      </c>
+      <c r="AR28">
+        <v>24</v>
+      </c>
+      <c r="AS28">
+        <v>9.6</v>
+      </c>
+      <c r="AT28">
+        <v>9.6</v>
+      </c>
+      <c r="AU28">
+        <v>9.6</v>
+      </c>
+      <c r="AV28">
         <v>20</v>
       </c>
-      <c r="AR28">
-        <v>34</v>
-      </c>
-      <c r="AS28">
-        <v>38</v>
-      </c>
-      <c r="AT28">
-        <v>11</v>
-      </c>
-      <c r="AU28">
+      <c r="AW28">
         <v>9</v>
       </c>
-      <c r="AV28">
-        <v>16.5</v>
-      </c>
-      <c r="AW28">
-        <v>44</v>
-      </c>
       <c r="AX28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY28">
+        <v>9</v>
+      </c>
+      <c r="AZ28">
+        <v>17.5</v>
+      </c>
+      <c r="BA28">
+        <v>30</v>
+      </c>
+      <c r="BB28">
+        <v>13.5</v>
+      </c>
+      <c r="BC28">
+        <v>14</v>
+      </c>
+      <c r="BD28">
+        <v>14.5</v>
+      </c>
+      <c r="BE28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF28">
+        <v>6</v>
+      </c>
+      <c r="BG28">
+        <v>9</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>3.45</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>7.2</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>25</v>
+      </c>
+      <c r="BN28">
+        <v>4.6</v>
+      </c>
+      <c r="BO28">
+        <v>3.5</v>
+      </c>
+      <c r="BP28">
         <v>11.5</v>
       </c>
-      <c r="AY28">
-        <v>9.6</v>
-      </c>
-      <c r="AZ28">
-        <v>15</v>
-      </c>
-      <c r="BA28">
-        <v>42</v>
-      </c>
-      <c r="BB28">
-        <v>18</v>
-      </c>
-      <c r="BC28">
-        <v>14.5</v>
-      </c>
-      <c r="BD28">
-        <v>23</v>
-      </c>
-      <c r="BE28">
-        <v>55</v>
-      </c>
-      <c r="BF28">
-        <v>7.2</v>
-      </c>
-      <c r="BG28">
-        <v>34</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>1.5</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>6.4</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>2.16</v>
-      </c>
-      <c r="BN28">
-        <v>1000</v>
-      </c>
-      <c r="BO28">
-        <v>3.55</v>
-      </c>
-      <c r="BP28">
-        <v>1000</v>
-      </c>
       <c r="BQ28">
-        <v>2.16</v>
+        <v>6.8</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS28">
-        <v>2.16</v>
+        <v>13</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU28">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>2.16</v>
+        <v>21</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.16</v>
+        <v>21</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA28">
-        <v>2.16</v>
+        <v>8.4</v>
       </c>
       <c r="CB28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F29">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="G29">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="H29">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="I29">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="K29">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="L29">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="M29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N29">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="O29">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="P29">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="Q29">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="R29">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="S29">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="T29">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="U29">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="V29">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="W29">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="X29">
+        <v>23</v>
+      </c>
+      <c r="Y29">
+        <v>23</v>
+      </c>
+      <c r="Z29">
+        <v>38</v>
+      </c>
+      <c r="AA29">
+        <v>100</v>
+      </c>
+      <c r="AB29">
+        <v>13</v>
+      </c>
+      <c r="AC29">
+        <v>10</v>
+      </c>
+      <c r="AD29">
+        <v>18.5</v>
+      </c>
+      <c r="AE29">
+        <v>48</v>
+      </c>
+      <c r="AF29">
+        <v>13</v>
+      </c>
+      <c r="AG29">
+        <v>10.5</v>
+      </c>
+      <c r="AH29">
+        <v>16.5</v>
+      </c>
+      <c r="AI29">
+        <v>48</v>
+      </c>
+      <c r="AJ29">
+        <v>20</v>
+      </c>
+      <c r="AK29">
+        <v>17</v>
+      </c>
+      <c r="AL29">
+        <v>28</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>7.8</v>
+      </c>
+      <c r="AO29">
+        <v>40</v>
+      </c>
+      <c r="AP29">
+        <v>20</v>
+      </c>
+      <c r="AQ29">
+        <v>20</v>
+      </c>
+      <c r="AR29">
         <v>34</v>
       </c>
-      <c r="Y29">
-        <v>55</v>
-      </c>
-      <c r="Z29">
-        <v>150</v>
-      </c>
-      <c r="AA29">
-        <v>700</v>
-      </c>
-      <c r="AB29">
-        <v>12.5</v>
-      </c>
-      <c r="AC29">
-        <v>17</v>
-      </c>
-      <c r="AD29">
-        <v>50</v>
-      </c>
-      <c r="AE29">
-        <v>220</v>
-      </c>
-      <c r="AF29">
-        <v>9</v>
-      </c>
-      <c r="AG29">
+      <c r="AS29">
+        <v>36</v>
+      </c>
+      <c r="AT29">
         <v>11.5</v>
       </c>
-      <c r="AH29">
-        <v>34</v>
-      </c>
-      <c r="AI29">
-        <v>160</v>
-      </c>
-      <c r="AJ29">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK29">
-        <v>14</v>
-      </c>
-      <c r="AL29">
-        <v>38</v>
-      </c>
-      <c r="AM29">
-        <v>160</v>
-      </c>
-      <c r="AN29">
-        <v>3.5</v>
-      </c>
-      <c r="AO29">
-        <v>230</v>
-      </c>
-      <c r="AP29">
-        <v>28</v>
-      </c>
-      <c r="AQ29">
+      <c r="AU29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV29">
+        <v>16</v>
+      </c>
+      <c r="AW29">
         <v>42</v>
       </c>
-      <c r="AR29">
-        <v>42</v>
-      </c>
-      <c r="AS29">
-        <v>55</v>
-      </c>
-      <c r="AT29">
-        <v>11</v>
-      </c>
-      <c r="AU29">
-        <v>14</v>
-      </c>
-      <c r="AV29">
-        <v>42</v>
-      </c>
-      <c r="AW29">
-        <v>48</v>
-      </c>
       <c r="AX29">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY29">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="BA29">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BB29">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BC29">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BD29">
         <v>23</v>
       </c>
       <c r="BE29">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BF29">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BG29">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>2.06</v>
+        <v>6.4</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>2.06</v>
+        <v>21</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BP29">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>2.06</v>
+        <v>13</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>2.06</v>
+        <v>14.5</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>2.06</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB29" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F30">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="G30">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="H30">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="J30">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="L30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="P30">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="R30">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="S30">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="T30">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="U30">
-        <v>2.54</v>
+        <v>1.89</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="W30">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="X30">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Y30">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="Z30">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AA30">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AB30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AD30">
-        <v>19.5</v>
+        <v>50</v>
       </c>
       <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG30">
+        <v>11.5</v>
+      </c>
+      <c r="AH30">
+        <v>32</v>
+      </c>
+      <c r="AI30">
+        <v>160</v>
+      </c>
+      <c r="AJ30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK30">
+        <v>14</v>
+      </c>
+      <c r="AL30">
+        <v>38</v>
+      </c>
+      <c r="AM30">
+        <v>160</v>
+      </c>
+      <c r="AN30">
+        <v>3.5</v>
+      </c>
+      <c r="AO30">
+        <v>210</v>
+      </c>
+      <c r="AP30">
+        <v>28</v>
+      </c>
+      <c r="AQ30">
+        <v>44</v>
+      </c>
+      <c r="AR30">
+        <v>42</v>
+      </c>
+      <c r="AS30">
         <v>55</v>
       </c>
-      <c r="AF30">
-        <v>13.5</v>
-      </c>
-      <c r="AG30">
+      <c r="AT30">
+        <v>11</v>
+      </c>
+      <c r="AU30">
+        <v>14.5</v>
+      </c>
+      <c r="AV30">
+        <v>42</v>
+      </c>
+      <c r="AW30">
+        <v>48</v>
+      </c>
+      <c r="AX30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY30">
         <v>10.5</v>
       </c>
-      <c r="AH30">
-        <v>16</v>
-      </c>
-      <c r="AI30">
-        <v>48</v>
-      </c>
-      <c r="AJ30">
-        <v>20</v>
-      </c>
-      <c r="AK30">
-        <v>16</v>
-      </c>
-      <c r="AL30">
+      <c r="AZ30">
         <v>27</v>
       </c>
-      <c r="AM30">
-        <v>65</v>
-      </c>
-      <c r="AN30">
-        <v>7.6</v>
-      </c>
-      <c r="AO30">
-        <v>42</v>
-      </c>
-      <c r="AP30">
-        <v>22</v>
-      </c>
-      <c r="AQ30">
-        <v>22</v>
-      </c>
-      <c r="AR30">
-        <v>24</v>
-      </c>
-      <c r="AS30">
-        <v>40</v>
-      </c>
-      <c r="AT30">
-        <v>11.5</v>
-      </c>
-      <c r="AU30">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV30">
-        <v>17</v>
-      </c>
-      <c r="AW30">
+      <c r="BA30">
         <v>44</v>
       </c>
-      <c r="AX30">
-        <v>12</v>
-      </c>
-      <c r="AY30">
-        <v>9.4</v>
-      </c>
-      <c r="AZ30">
-        <v>14</v>
-      </c>
-      <c r="BA30">
-        <v>42</v>
-      </c>
       <c r="BB30">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC30">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD30">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE30">
+        <v>44</v>
+      </c>
+      <c r="BF30">
+        <v>3.35</v>
+      </c>
+      <c r="BG30">
         <v>50</v>
       </c>
-      <c r="BF30">
-        <v>7</v>
-      </c>
-      <c r="BG30">
-        <v>34</v>
-      </c>
       <c r="BH30">
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>6.2</v>
+        <v>2.06</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>2.34</v>
+        <v>28</v>
       </c>
       <c r="BN30">
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ30">
-        <v>7.4</v>
+        <v>1.67</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>2.34</v>
+        <v>19</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>2.34</v>
+        <v>5.1</v>
       </c>
       <c r="CB30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F31">
-        <v>2.98</v>
+        <v>1.77</v>
       </c>
       <c r="G31">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="H31">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31">
+        <v>4.2</v>
+      </c>
+      <c r="K31">
+        <v>4.3</v>
+      </c>
+      <c r="L31">
+        <v>1.29</v>
+      </c>
+      <c r="M31">
+        <v>1.04</v>
+      </c>
+      <c r="N31">
+        <v>6</v>
+      </c>
+      <c r="O31">
+        <v>1.19</v>
+      </c>
+      <c r="P31">
+        <v>2.66</v>
+      </c>
+      <c r="Q31">
+        <v>1.59</v>
+      </c>
+      <c r="R31">
+        <v>1.66</v>
+      </c>
+      <c r="S31">
+        <v>2.44</v>
+      </c>
+      <c r="T31">
+        <v>1.61</v>
+      </c>
+      <c r="U31">
         <v>2.54</v>
       </c>
-      <c r="J31">
-        <v>3.65</v>
-      </c>
-      <c r="K31">
+      <c r="V31">
+        <v>1.25</v>
+      </c>
+      <c r="W31">
+        <v>2.26</v>
+      </c>
+      <c r="X31">
+        <v>24</v>
+      </c>
+      <c r="Y31">
+        <v>25</v>
+      </c>
+      <c r="Z31">
+        <v>46</v>
+      </c>
+      <c r="AA31">
+        <v>120</v>
+      </c>
+      <c r="AB31">
+        <v>13</v>
+      </c>
+      <c r="AC31">
+        <v>10</v>
+      </c>
+      <c r="AD31">
+        <v>20</v>
+      </c>
+      <c r="AE31">
+        <v>55</v>
+      </c>
+      <c r="AF31">
+        <v>13.5</v>
+      </c>
+      <c r="AG31">
+        <v>10.5</v>
+      </c>
+      <c r="AH31">
+        <v>16</v>
+      </c>
+      <c r="AI31">
+        <v>48</v>
+      </c>
+      <c r="AJ31">
+        <v>20</v>
+      </c>
+      <c r="AK31">
+        <v>16</v>
+      </c>
+      <c r="AL31">
+        <v>27</v>
+      </c>
+      <c r="AM31">
+        <v>65</v>
+      </c>
+      <c r="AN31">
+        <v>7.4</v>
+      </c>
+      <c r="AO31">
+        <v>42</v>
+      </c>
+      <c r="AP31">
+        <v>22</v>
+      </c>
+      <c r="AQ31">
+        <v>22</v>
+      </c>
+      <c r="AR31">
+        <v>32</v>
+      </c>
+      <c r="AS31">
+        <v>38</v>
+      </c>
+      <c r="AT31">
+        <v>11.5</v>
+      </c>
+      <c r="AU31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV31">
+        <v>17.5</v>
+      </c>
+      <c r="AW31">
+        <v>44</v>
+      </c>
+      <c r="AX31">
+        <v>12</v>
+      </c>
+      <c r="AY31">
+        <v>9.4</v>
+      </c>
+      <c r="AZ31">
+        <v>14</v>
+      </c>
+      <c r="BA31">
+        <v>42</v>
+      </c>
+      <c r="BB31">
+        <v>17.5</v>
+      </c>
+      <c r="BC31">
+        <v>14.5</v>
+      </c>
+      <c r="BD31">
+        <v>23</v>
+      </c>
+      <c r="BE31">
+        <v>50</v>
+      </c>
+      <c r="BF31">
+        <v>7</v>
+      </c>
+      <c r="BG31">
+        <v>32</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
         <v>3.7</v>
       </c>
-      <c r="L31">
-        <v>1.36</v>
-      </c>
-      <c r="M31">
-        <v>1.05</v>
-      </c>
-      <c r="N31">
-        <v>4.7</v>
-      </c>
-      <c r="O31">
-        <v>1.25</v>
-      </c>
-      <c r="P31">
-        <v>2.26</v>
-      </c>
-      <c r="Q31">
-        <v>1.77</v>
-      </c>
-      <c r="R31">
-        <v>1.48</v>
-      </c>
-      <c r="S31">
-        <v>2.96</v>
-      </c>
-      <c r="T31">
-        <v>1.64</v>
-      </c>
-      <c r="U31">
-        <v>2.46</v>
-      </c>
-      <c r="V31">
-        <v>1.64</v>
-      </c>
-      <c r="W31">
-        <v>1.48</v>
-      </c>
-      <c r="X31">
-        <v>17.5</v>
-      </c>
-      <c r="Y31">
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.99</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>19</v>
+      </c>
+      <c r="BN31">
+        <v>5.7</v>
+      </c>
+      <c r="BO31">
+        <v>3.9</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>2.1</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>2.34</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.98</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
         <v>13</v>
       </c>
-      <c r="Z31">
-        <v>17.5</v>
-      </c>
-      <c r="AA31">
-        <v>34</v>
-      </c>
-      <c r="AB31">
-        <v>15</v>
-      </c>
-      <c r="AC31">
-        <v>8.4</v>
-      </c>
-      <c r="AD31">
-        <v>11.5</v>
-      </c>
-      <c r="AE31">
-        <v>25</v>
-      </c>
-      <c r="AF31">
-        <v>22</v>
-      </c>
-      <c r="AG31">
-        <v>13</v>
-      </c>
-      <c r="AH31">
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
         <v>14</v>
       </c>
-      <c r="AI31">
-        <v>34</v>
-      </c>
-      <c r="AJ31">
-        <v>50</v>
-      </c>
-      <c r="AK31">
-        <v>30</v>
-      </c>
-      <c r="AL31">
-        <v>38</v>
-      </c>
-      <c r="AM31">
-        <v>70</v>
-      </c>
-      <c r="AN31">
-        <v>23</v>
-      </c>
-      <c r="AO31">
-        <v>16.5</v>
-      </c>
-      <c r="AP31">
-        <v>16.5</v>
-      </c>
-      <c r="AQ31">
-        <v>12</v>
-      </c>
-      <c r="AR31">
-        <v>16</v>
-      </c>
-      <c r="AS31">
-        <v>29</v>
-      </c>
-      <c r="AT31">
-        <v>14</v>
-      </c>
-      <c r="AU31">
-        <v>8</v>
-      </c>
-      <c r="AV31">
-        <v>10.5</v>
-      </c>
-      <c r="AW31">
-        <v>22</v>
-      </c>
-      <c r="AX31">
-        <v>19.5</v>
-      </c>
-      <c r="AY31">
-        <v>12</v>
-      </c>
-      <c r="AZ31">
-        <v>13</v>
-      </c>
-      <c r="BA31">
-        <v>29</v>
-      </c>
-      <c r="BB31">
-        <v>42</v>
-      </c>
-      <c r="BC31">
-        <v>27</v>
-      </c>
-      <c r="BD31">
-        <v>32</v>
-      </c>
-      <c r="BE31">
-        <v>55</v>
-      </c>
-      <c r="BF31">
-        <v>20</v>
-      </c>
-      <c r="BG31">
-        <v>15</v>
-      </c>
-      <c r="BH31">
-        <v>1000</v>
-      </c>
-      <c r="BI31">
-        <v>1.54</v>
-      </c>
-      <c r="BJ31">
-        <v>1000</v>
-      </c>
-      <c r="BK31">
-        <v>5.6</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>2.38</v>
-      </c>
-      <c r="BN31">
-        <v>1000</v>
-      </c>
-      <c r="BO31">
-        <v>4.3</v>
-      </c>
-      <c r="BP31">
-        <v>1000</v>
-      </c>
-      <c r="BQ31">
-        <v>2.38</v>
-      </c>
-      <c r="BR31">
-        <v>1000</v>
-      </c>
-      <c r="BS31">
-        <v>2.38</v>
-      </c>
-      <c r="BT31">
-        <v>1000</v>
-      </c>
-      <c r="BU31">
-        <v>4.2</v>
-      </c>
-      <c r="BV31">
-        <v>1000</v>
-      </c>
-      <c r="BW31">
-        <v>2.38</v>
-      </c>
-      <c r="BX31">
-        <v>1000</v>
-      </c>
-      <c r="BY31">
-        <v>2.38</v>
-      </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CB31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F32">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="G32">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="H32">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I32">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="J32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L32">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N32">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O32">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P32">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q32">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="R32">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S32">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T32">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="U32">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="V32">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W32">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X32">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y32">
         <v>13</v>
       </c>
       <c r="Z32">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA32">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB32">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC32">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE32">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF32">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG32">
         <v>13</v>
       </c>
       <c r="AH32">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AI32">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ32">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK32">
         <v>30</v>
@@ -8491,856 +8500,1098 @@
         <v>38</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN32">
         <v>23</v>
       </c>
       <c r="AO32">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AP32">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR32">
         <v>16</v>
       </c>
       <c r="AS32">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AT32">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU32">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV32">
         <v>10.5</v>
       </c>
       <c r="AW32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX32">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ32">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA32">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BB32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BC32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD32">
         <v>34</v>
       </c>
       <c r="BE32">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG32">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BH32">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>3.05</v>
+        <v>1.54</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>11.5</v>
+        <v>2.38</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
         <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F33">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="G33">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="H33">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="I33">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K33">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L33">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M33">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N33">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="O33">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P33">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="R33">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S33">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="T33">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="U33">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="V33">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="X33">
+        <v>17</v>
+      </c>
+      <c r="Y33">
+        <v>12.5</v>
+      </c>
+      <c r="Z33">
+        <v>18.5</v>
+      </c>
+      <c r="AA33">
+        <v>38</v>
+      </c>
+      <c r="AB33">
+        <v>13.5</v>
+      </c>
+      <c r="AC33">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33">
+        <v>12</v>
+      </c>
+      <c r="AE33">
+        <v>27</v>
+      </c>
+      <c r="AF33">
+        <v>20</v>
+      </c>
+      <c r="AG33">
+        <v>13</v>
+      </c>
+      <c r="AH33">
+        <v>16.5</v>
+      </c>
+      <c r="AI33">
+        <v>38</v>
+      </c>
+      <c r="AJ33">
+        <v>44</v>
+      </c>
+      <c r="AK33">
+        <v>30</v>
+      </c>
+      <c r="AL33">
+        <v>38</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>23</v>
+      </c>
+      <c r="AO33">
         <v>21</v>
       </c>
-      <c r="Y33">
-        <v>13</v>
-      </c>
-      <c r="Z33">
-        <v>14.5</v>
-      </c>
-      <c r="AA33">
+      <c r="AP33">
+        <v>15</v>
+      </c>
+      <c r="AQ33">
+        <v>11.5</v>
+      </c>
+      <c r="AR33">
+        <v>16</v>
+      </c>
+      <c r="AS33">
+        <v>34</v>
+      </c>
+      <c r="AT33">
+        <v>12.5</v>
+      </c>
+      <c r="AU33">
+        <v>7.6</v>
+      </c>
+      <c r="AV33">
+        <v>11</v>
+      </c>
+      <c r="AW33">
         <v>24</v>
       </c>
-      <c r="AB33">
-        <v>19</v>
-      </c>
-      <c r="AC33">
-        <v>9</v>
-      </c>
-      <c r="AD33">
-        <v>11</v>
-      </c>
-      <c r="AE33">
-        <v>18.5</v>
-      </c>
-      <c r="AF33">
-        <v>32</v>
-      </c>
-      <c r="AG33">
-        <v>15.5</v>
-      </c>
-      <c r="AH33">
-        <v>15.5</v>
-      </c>
-      <c r="AI33">
-        <v>28</v>
-      </c>
-      <c r="AJ33">
-        <v>70</v>
-      </c>
-      <c r="AK33">
-        <v>38</v>
-      </c>
-      <c r="AL33">
-        <v>40</v>
-      </c>
-      <c r="AM33">
-        <v>65</v>
-      </c>
-      <c r="AN33">
-        <v>32</v>
-      </c>
-      <c r="AO33">
-        <v>10.5</v>
-      </c>
-      <c r="AP33">
-        <v>19</v>
-      </c>
-      <c r="AQ33">
-        <v>12</v>
-      </c>
-      <c r="AR33">
-        <v>13.5</v>
-      </c>
-      <c r="AS33">
-        <v>21</v>
-      </c>
-      <c r="AT33">
-        <v>18</v>
-      </c>
-      <c r="AU33">
-        <v>8.6</v>
-      </c>
-      <c r="AV33">
-        <v>10</v>
-      </c>
-      <c r="AW33">
-        <v>17</v>
-      </c>
       <c r="AX33">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AY33">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ33">
         <v>14.5</v>
       </c>
       <c r="BA33">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BB33">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BC33">
+        <v>26</v>
+      </c>
+      <c r="BD33">
         <v>34</v>
       </c>
-      <c r="BD33">
-        <v>36</v>
-      </c>
       <c r="BE33">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF33">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BG33">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI33">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="BJ33">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL33">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BN33">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BP33">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BR33">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BT33">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV33">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
         <v>11.5</v>
       </c>
       <c r="BX33">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BZ33">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="CB33" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F34">
-        <v>1.17</v>
+        <v>3.8</v>
       </c>
       <c r="G34">
-        <v>600</v>
+        <v>3.85</v>
       </c>
       <c r="H34">
-        <v>1.17</v>
+        <v>2.04</v>
       </c>
       <c r="I34">
-        <v>870</v>
+        <v>2.06</v>
       </c>
       <c r="J34">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="K34">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N34">
-        <v>1.26</v>
+        <v>5.3</v>
       </c>
       <c r="O34">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="P34">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q34">
-        <v>1.15</v>
+        <v>1.66</v>
       </c>
       <c r="R34">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="S34">
-        <v>1.15</v>
+        <v>2.68</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V34">
-        <v>1.07</v>
+        <v>1.94</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP34">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AQ34">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR34">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT34">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AU34">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV34">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW34">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AX34">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AY34">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AZ34">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA34">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="BB34">
-        <v>1.03</v>
+        <v>60</v>
       </c>
       <c r="BC34">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BD34">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BE34">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL34">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR34">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA34">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB34" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
         <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F35">
+        <v>1.17</v>
+      </c>
+      <c r="G35">
+        <v>600</v>
+      </c>
+      <c r="H35">
+        <v>1.17</v>
+      </c>
+      <c r="I35">
+        <v>870</v>
+      </c>
+      <c r="J35">
+        <v>1.2</v>
+      </c>
+      <c r="K35">
+        <v>950</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>1.26</v>
+      </c>
+      <c r="O35">
+        <v>1.15</v>
+      </c>
+      <c r="P35">
+        <v>1.26</v>
+      </c>
+      <c r="Q35">
+        <v>1.15</v>
+      </c>
+      <c r="R35">
+        <v>1.08</v>
+      </c>
+      <c r="S35">
+        <v>1.16</v>
+      </c>
+      <c r="T35">
+        <v>1.01</v>
+      </c>
+      <c r="U35">
+        <v>1.01</v>
+      </c>
+      <c r="V35">
+        <v>1.08</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1000</v>
+      </c>
+      <c r="Y35">
+        <v>1000</v>
+      </c>
+      <c r="Z35">
+        <v>1000</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>1000</v>
+      </c>
+      <c r="AD35">
+        <v>1000</v>
+      </c>
+      <c r="AE35">
+        <v>1000</v>
+      </c>
+      <c r="AF35">
+        <v>1000</v>
+      </c>
+      <c r="AG35">
+        <v>1000</v>
+      </c>
+      <c r="AH35">
+        <v>1000</v>
+      </c>
+      <c r="AI35">
+        <v>1000</v>
+      </c>
+      <c r="AJ35">
+        <v>1000</v>
+      </c>
+      <c r="AK35">
+        <v>1000</v>
+      </c>
+      <c r="AL35">
+        <v>1000</v>
+      </c>
+      <c r="AM35">
+        <v>1000</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35">
+        <v>1.03</v>
+      </c>
+      <c r="AR35">
+        <v>1.03</v>
+      </c>
+      <c r="AS35">
+        <v>1.03</v>
+      </c>
+      <c r="AT35">
+        <v>1.03</v>
+      </c>
+      <c r="AU35">
+        <v>1.03</v>
+      </c>
+      <c r="AV35">
+        <v>1.03</v>
+      </c>
+      <c r="AW35">
+        <v>1.03</v>
+      </c>
+      <c r="AX35">
+        <v>1.03</v>
+      </c>
+      <c r="AY35">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35">
+        <v>1.03</v>
+      </c>
+      <c r="BA35">
+        <v>1.03</v>
+      </c>
+      <c r="BB35">
+        <v>1.03</v>
+      </c>
+      <c r="BC35">
+        <v>1.03</v>
+      </c>
+      <c r="BD35">
+        <v>1.03</v>
+      </c>
+      <c r="BE35">
+        <v>1.03</v>
+      </c>
+      <c r="BF35">
+        <v>1.01</v>
+      </c>
+      <c r="BG35">
+        <v>1.01</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.01</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.01</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" t="s">
+        <v>176</v>
+      </c>
+      <c r="F36">
         <v>2.16</v>
       </c>
-      <c r="G35">
+      <c r="G36">
         <v>2.5</v>
       </c>
-      <c r="H35">
+      <c r="H36">
         <v>3.2</v>
       </c>
-      <c r="I35">
+      <c r="I36">
         <v>4.6</v>
       </c>
-      <c r="J35">
+      <c r="J36">
         <v>3.1</v>
       </c>
-      <c r="K35">
+      <c r="K36">
         <v>3.75</v>
       </c>
-      <c r="L35">
-        <v>1.01</v>
-      </c>
-      <c r="M35">
-        <v>1.01</v>
-      </c>
-      <c r="N35">
+      <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.01</v>
+      </c>
+      <c r="N36">
         <v>2.7</v>
       </c>
-      <c r="O35">
+      <c r="O36">
         <v>1.42</v>
       </c>
-      <c r="P35">
+      <c r="P36">
         <v>1.58</v>
       </c>
-      <c r="Q35">
+      <c r="Q36">
         <v>2.02</v>
       </c>
-      <c r="R35">
+      <c r="R36">
         <v>1.21</v>
       </c>
-      <c r="S35">
+      <c r="S36">
         <v>3.85</v>
       </c>
-      <c r="T35">
-        <v>1.01</v>
-      </c>
-      <c r="U35">
-        <v>1.01</v>
-      </c>
-      <c r="V35">
+      <c r="T36">
+        <v>1.01</v>
+      </c>
+      <c r="U36">
+        <v>1.01</v>
+      </c>
+      <c r="V36">
         <v>1.29</v>
       </c>
-      <c r="W35">
+      <c r="W36">
         <v>1.66</v>
       </c>
-      <c r="X35">
-        <v>1000</v>
-      </c>
-      <c r="Y35">
-        <v>1000</v>
-      </c>
-      <c r="Z35">
-        <v>1000</v>
-      </c>
-      <c r="AA35">
-        <v>1000</v>
-      </c>
-      <c r="AB35">
-        <v>1000</v>
-      </c>
-      <c r="AC35">
-        <v>1000</v>
-      </c>
-      <c r="AD35">
-        <v>1000</v>
-      </c>
-      <c r="AE35">
-        <v>1000</v>
-      </c>
-      <c r="AF35">
-        <v>1000</v>
-      </c>
-      <c r="AG35">
-        <v>1000</v>
-      </c>
-      <c r="AH35">
-        <v>1000</v>
-      </c>
-      <c r="AI35">
-        <v>1000</v>
-      </c>
-      <c r="AJ35">
-        <v>1000</v>
-      </c>
-      <c r="AK35">
-        <v>1000</v>
-      </c>
-      <c r="AL35">
-        <v>1000</v>
-      </c>
-      <c r="AM35">
-        <v>1000</v>
-      </c>
-      <c r="AN35">
-        <v>1000</v>
-      </c>
-      <c r="AO35">
-        <v>1000</v>
-      </c>
-      <c r="AP35">
-        <v>1.01</v>
-      </c>
-      <c r="AQ35">
-        <v>1.01</v>
-      </c>
-      <c r="AR35">
-        <v>1.01</v>
-      </c>
-      <c r="AS35">
-        <v>1.01</v>
-      </c>
-      <c r="AT35">
-        <v>1.01</v>
-      </c>
-      <c r="AU35">
-        <v>1.01</v>
-      </c>
-      <c r="AV35">
-        <v>1.01</v>
-      </c>
-      <c r="AW35">
-        <v>1.01</v>
-      </c>
-      <c r="AX35">
-        <v>1.01</v>
-      </c>
-      <c r="AY35">
-        <v>1.01</v>
-      </c>
-      <c r="AZ35">
-        <v>1.01</v>
-      </c>
-      <c r="BA35">
-        <v>1.01</v>
-      </c>
-      <c r="BB35">
-        <v>1.01</v>
-      </c>
-      <c r="BC35">
-        <v>1.01</v>
-      </c>
-      <c r="BD35">
-        <v>1.01</v>
-      </c>
-      <c r="BE35">
-        <v>1.01</v>
-      </c>
-      <c r="BF35">
-        <v>1.01</v>
-      </c>
-      <c r="BG35">
-        <v>1.01</v>
-      </c>
-      <c r="BH35">
-        <v>1000</v>
-      </c>
-      <c r="BI35">
-        <v>1.01</v>
-      </c>
-      <c r="BJ35">
-        <v>1000</v>
-      </c>
-      <c r="BK35">
-        <v>1.01</v>
-      </c>
-      <c r="BL35">
-        <v>1000</v>
-      </c>
-      <c r="BM35">
-        <v>1.01</v>
-      </c>
-      <c r="BN35">
-        <v>1000</v>
-      </c>
-      <c r="BO35">
-        <v>1.01</v>
-      </c>
-      <c r="BP35">
-        <v>1000</v>
-      </c>
-      <c r="BQ35">
-        <v>1.01</v>
-      </c>
-      <c r="BR35">
-        <v>1000</v>
-      </c>
-      <c r="BS35">
-        <v>1.01</v>
-      </c>
-      <c r="BT35">
-        <v>1000</v>
-      </c>
-      <c r="BU35">
-        <v>1.01</v>
-      </c>
-      <c r="BV35">
-        <v>1000</v>
-      </c>
-      <c r="BW35">
-        <v>1.01</v>
-      </c>
-      <c r="BX35">
-        <v>1000</v>
-      </c>
-      <c r="BY35">
-        <v>1.01</v>
-      </c>
-      <c r="BZ35">
-        <v>1000</v>
-      </c>
-      <c r="CA35">
-        <v>1.01</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>174</v>
+      <c r="X36">
+        <v>1000</v>
+      </c>
+      <c r="Y36">
+        <v>1000</v>
+      </c>
+      <c r="Z36">
+        <v>1000</v>
+      </c>
+      <c r="AA36">
+        <v>1000</v>
+      </c>
+      <c r="AB36">
+        <v>1000</v>
+      </c>
+      <c r="AC36">
+        <v>1000</v>
+      </c>
+      <c r="AD36">
+        <v>1000</v>
+      </c>
+      <c r="AE36">
+        <v>1000</v>
+      </c>
+      <c r="AF36">
+        <v>1000</v>
+      </c>
+      <c r="AG36">
+        <v>1000</v>
+      </c>
+      <c r="AH36">
+        <v>1000</v>
+      </c>
+      <c r="AI36">
+        <v>1000</v>
+      </c>
+      <c r="AJ36">
+        <v>1000</v>
+      </c>
+      <c r="AK36">
+        <v>1000</v>
+      </c>
+      <c r="AL36">
+        <v>1000</v>
+      </c>
+      <c r="AM36">
+        <v>1000</v>
+      </c>
+      <c r="AN36">
+        <v>1000</v>
+      </c>
+      <c r="AO36">
+        <v>1000</v>
+      </c>
+      <c r="AP36">
+        <v>1.01</v>
+      </c>
+      <c r="AQ36">
+        <v>1.01</v>
+      </c>
+      <c r="AR36">
+        <v>1.01</v>
+      </c>
+      <c r="AS36">
+        <v>1.01</v>
+      </c>
+      <c r="AT36">
+        <v>1.01</v>
+      </c>
+      <c r="AU36">
+        <v>1.01</v>
+      </c>
+      <c r="AV36">
+        <v>1.01</v>
+      </c>
+      <c r="AW36">
+        <v>1.01</v>
+      </c>
+      <c r="AX36">
+        <v>1.01</v>
+      </c>
+      <c r="AY36">
+        <v>1.01</v>
+      </c>
+      <c r="AZ36">
+        <v>1.01</v>
+      </c>
+      <c r="BA36">
+        <v>1.01</v>
+      </c>
+      <c r="BB36">
+        <v>1.01</v>
+      </c>
+      <c r="BC36">
+        <v>1.01</v>
+      </c>
+      <c r="BD36">
+        <v>1.01</v>
+      </c>
+      <c r="BE36">
+        <v>1.01</v>
+      </c>
+      <c r="BF36">
+        <v>1.01</v>
+      </c>
+      <c r="BG36">
+        <v>1.01</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
+        <v>1.01</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
+        <v>1.01</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>1.01</v>
+      </c>
+      <c r="BN36">
+        <v>1000</v>
+      </c>
+      <c r="BO36">
+        <v>1.01</v>
+      </c>
+      <c r="BP36">
+        <v>1000</v>
+      </c>
+      <c r="BQ36">
+        <v>1.01</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>1.01</v>
+      </c>
+      <c r="BT36">
+        <v>1000</v>
+      </c>
+      <c r="BU36">
+        <v>1.01</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
+        <v>1.01</v>
+      </c>
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
+        <v>1.01</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -547,7 +547,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 02:44:11</t>
+    <t>2026-09-16 04:59:18</t>
   </si>
 </sst>
 </file>
@@ -1141,10 +1141,10 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H2">
         <v>5.3</v>
@@ -1156,7 +1156,7 @@
         <v>4.6</v>
       </c>
       <c r="K2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L2">
         <v>1.27</v>
@@ -1165,10 +1165,10 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P2">
         <v>2.72</v>
@@ -1180,7 +1180,7 @@
         <v>1.69</v>
       </c>
       <c r="S2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T2">
         <v>1.64</v>
@@ -1192,13 +1192,13 @@
         <v>1.19</v>
       </c>
       <c r="W2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X2">
+        <v>29</v>
+      </c>
+      <c r="Y2">
         <v>28</v>
-      </c>
-      <c r="Y2">
-        <v>27</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1210,7 +1210,7 @@
         <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD2">
         <v>23</v>
@@ -1222,10 +1222,10 @@
         <v>13</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI2">
         <v>65</v>
@@ -1234,7 +1234,7 @@
         <v>18.5</v>
       </c>
       <c r="AK2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AL2">
         <v>28</v>
@@ -1243,46 +1243,46 @@
         <v>85</v>
       </c>
       <c r="AN2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO2">
         <v>60</v>
       </c>
       <c r="AP2">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AT2">
         <v>11</v>
       </c>
       <c r="AU2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV2">
         <v>19</v>
       </c>
       <c r="AW2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BB2">
         <v>13.5</v>
@@ -1291,16 +1291,16 @@
         <v>13</v>
       </c>
       <c r="BD2">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF2">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1383,13 +1383,13 @@
         <v>143</v>
       </c>
       <c r="F3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G3">
         <v>2.06</v>
       </c>
       <c r="H3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>5.3</v>
@@ -1401,10 +1401,10 @@
         <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
         <v>2.34</v>
@@ -1428,7 +1428,7 @@
         <v>2.58</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V3">
         <v>1.23</v>
@@ -1437,7 +1437,7 @@
         <v>1.94</v>
       </c>
       <c r="X3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y3">
         <v>12</v>
@@ -1455,7 +1455,7 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3">
         <v>120</v>
@@ -1473,7 +1473,7 @@
         <v>170</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK3">
         <v>32</v>
@@ -1482,13 +1482,13 @@
         <v>85</v>
       </c>
       <c r="AM3">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AN3">
         <v>34</v>
       </c>
       <c r="AO3">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AP3">
         <v>6.4</v>
@@ -1500,7 +1500,7 @@
         <v>30</v>
       </c>
       <c r="AS3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT3">
         <v>5.3</v>
@@ -1512,7 +1512,7 @@
         <v>21</v>
       </c>
       <c r="AW3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1524,7 +1524,7 @@
         <v>28</v>
       </c>
       <c r="BA3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BB3">
         <v>23</v>
@@ -1536,73 +1536,73 @@
         <v>65</v>
       </c>
       <c r="BE3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BF3">
         <v>28</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="BI3">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.7</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO3">
-        <v>1.29</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="BQ3">
-        <v>1.59</v>
+        <v>8</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
-        <v>1.67</v>
+        <v>11</v>
       </c>
       <c r="BT3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU3">
+        <v>6.8</v>
+      </c>
+      <c r="BV3">
+        <v>70</v>
+      </c>
+      <c r="BW3">
         <v>11.5</v>
       </c>
-      <c r="BU3">
-        <v>3.25</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>1.68</v>
-      </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.7</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA3">
-        <v>1.68</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,115 +1625,115 @@
         <v>144</v>
       </c>
       <c r="F4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G4">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="H4">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="I4">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
         <v>1.32</v>
       </c>
       <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4">
         <v>1.94</v>
       </c>
-      <c r="Q4">
-        <v>1.98</v>
-      </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
         <v>2.06</v>
       </c>
       <c r="V4">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="W4">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X4">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
         <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AB4">
+        <v>18</v>
+      </c>
+      <c r="AC4">
+        <v>8.6</v>
+      </c>
+      <c r="AD4">
+        <v>10.5</v>
+      </c>
+      <c r="AE4">
         <v>21</v>
       </c>
-      <c r="AC4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD4">
+      <c r="AF4">
+        <v>40</v>
+      </c>
+      <c r="AG4">
+        <v>19.5</v>
+      </c>
+      <c r="AH4">
+        <v>22</v>
+      </c>
+      <c r="AI4">
+        <v>42</v>
+      </c>
+      <c r="AJ4">
+        <v>140</v>
+      </c>
+      <c r="AK4">
+        <v>70</v>
+      </c>
+      <c r="AL4">
+        <v>75</v>
+      </c>
+      <c r="AM4">
+        <v>120</v>
+      </c>
+      <c r="AN4">
+        <v>75</v>
+      </c>
+      <c r="AO4">
+        <v>12.5</v>
+      </c>
+      <c r="AP4">
         <v>13</v>
-      </c>
-      <c r="AE4">
-        <v>25</v>
-      </c>
-      <c r="AF4">
-        <v>42</v>
-      </c>
-      <c r="AG4">
-        <v>23</v>
-      </c>
-      <c r="AH4">
-        <v>23</v>
-      </c>
-      <c r="AI4">
-        <v>46</v>
-      </c>
-      <c r="AJ4">
-        <v>130</v>
-      </c>
-      <c r="AK4">
-        <v>75</v>
-      </c>
-      <c r="AL4">
-        <v>80</v>
-      </c>
-      <c r="AM4">
-        <v>130</v>
-      </c>
-      <c r="AN4">
-        <v>85</v>
-      </c>
-      <c r="AO4">
-        <v>16</v>
-      </c>
-      <c r="AP4">
-        <v>12.5</v>
       </c>
       <c r="AQ4">
         <v>8</v>
@@ -1742,13 +1742,13 @@
         <v>10</v>
       </c>
       <c r="AS4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
         <v>9.199999999999999</v>
@@ -1757,94 +1757,94 @@
         <v>17</v>
       </c>
       <c r="AX4">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="AY4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BC4">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>48</v>
       </c>
       <c r="BF4">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1873,13 +1873,13 @@
         <v>2.22</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5">
         <v>5.2</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K5">
         <v>3.15</v>
@@ -1888,25 +1888,25 @@
         <v>1.62</v>
       </c>
       <c r="M5">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="O5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P5">
         <v>1.39</v>
       </c>
       <c r="Q5">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S5">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="T5">
         <v>2.4</v>
@@ -1918,7 +1918,7 @@
         <v>1.24</v>
       </c>
       <c r="W5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X5">
         <v>7.2</v>
@@ -2109,19 +2109,19 @@
         <v>146</v>
       </c>
       <c r="F6">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="G6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.75</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2139,7 +2139,7 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
         <v>1.26</v>
@@ -2157,10 +2157,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2351,19 +2351,19 @@
         <v>147</v>
       </c>
       <c r="F7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2381,13 +2381,13 @@
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q7">
         <v>1.25</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S7">
         <v>1.26</v>
@@ -2399,10 +2399,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2599,13 +2599,13 @@
         <v>600</v>
       </c>
       <c r="H8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
         <v>870</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2641,10 +2641,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2835,19 +2835,19 @@
         <v>149</v>
       </c>
       <c r="F9">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="I9">
         <v>1.62</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>2.9</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2868,10 +2868,10 @@
         <v>1.26</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R9">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="S9">
         <v>1.01</v>
@@ -3080,19 +3080,19 @@
         <v>1.1</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H10">
         <v>1.1</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J10">
         <v>1.1</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3101,22 +3101,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
         <v>1.1</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R10">
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3125,10 +3125,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3319,7 +3319,7 @@
         <v>151</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G11">
         <v>600</v>
@@ -3331,7 +3331,7 @@
         <v>870</v>
       </c>
       <c r="J11">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3352,25 +3352,25 @@
         <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R11">
         <v>1.08</v>
       </c>
       <c r="S11">
+        <v>1.07</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
+        <v>1.01</v>
+      </c>
+      <c r="W11">
         <v>1.06</v>
-      </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>1.05</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3561,13 +3561,13 @@
         <v>152</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I12">
         <v>1.44</v>
@@ -3576,13 +3576,13 @@
         <v>5.2</v>
       </c>
       <c r="K12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L12">
         <v>1.3</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
         <v>5.5</v>
@@ -3597,7 +3597,7 @@
         <v>1.61</v>
       </c>
       <c r="R12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S12">
         <v>2.56</v>
@@ -3606,7 +3606,7 @@
         <v>1.84</v>
       </c>
       <c r="U12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
         <v>3.25</v>
@@ -3651,7 +3651,7 @@
         <v>34</v>
       </c>
       <c r="AJ12">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AK12">
         <v>130</v>
@@ -3669,7 +3669,7 @@
         <v>5.5</v>
       </c>
       <c r="AP12">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ12">
         <v>9.4</v>
@@ -3687,13 +3687,13 @@
         <v>10.5</v>
       </c>
       <c r="AV12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12">
         <v>12.5</v>
       </c>
       <c r="AX12">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AY12">
         <v>22</v>
@@ -3711,7 +3711,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD12">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE12">
         <v>9.199999999999999</v>
@@ -3806,7 +3806,7 @@
         <v>3.2</v>
       </c>
       <c r="G13">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H13">
         <v>2.34</v>
@@ -3818,7 +3818,7 @@
         <v>3.7</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
         <v>1.34</v>
@@ -3833,10 +3833,10 @@
         <v>1.24</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
         <v>1.53</v>
@@ -3854,7 +3854,7 @@
         <v>1.72</v>
       </c>
       <c r="W13">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
         <v>19</v>
@@ -3887,7 +3887,7 @@
         <v>14</v>
       </c>
       <c r="AH13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI13">
         <v>32</v>
@@ -3926,7 +3926,7 @@
         <v>14.5</v>
       </c>
       <c r="AU13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV13">
         <v>10.5</v>
@@ -3965,61 +3965,61 @@
         <v>12</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI13">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM13">
         <v>21</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO13">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ13">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS13">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU13">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY13">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA13">
         <v>9.199999999999999</v>
@@ -4045,7 +4045,7 @@
         <v>154</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G14">
         <v>1.25</v>
@@ -4096,7 +4096,7 @@
         <v>1.01</v>
       </c>
       <c r="W14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4287,22 +4287,22 @@
         <v>155</v>
       </c>
       <c r="F15">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="G15">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H15">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="I15">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J15">
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4335,10 +4335,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4544,7 +4544,7 @@
         <v>3.2</v>
       </c>
       <c r="K16">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4774,19 +4774,19 @@
         <v>2.22</v>
       </c>
       <c r="G17">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="H17">
         <v>2.22</v>
       </c>
       <c r="I17">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="J17">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4795,7 +4795,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
         <v>1.21</v>
@@ -4819,10 +4819,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5013,22 +5013,22 @@
         <v>158</v>
       </c>
       <c r="F18">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="H18">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I18">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J18">
         <v>3.5</v>
       </c>
       <c r="K18">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5037,7 +5037,7 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
         <v>1.01</v>
@@ -5049,7 +5049,7 @@
         <v>1.62</v>
       </c>
       <c r="R18">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S18">
         <v>2</v>
@@ -5061,10 +5061,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5258,7 +5258,7 @@
         <v>1.72</v>
       </c>
       <c r="G19">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -5306,7 +5306,7 @@
         <v>1.18</v>
       </c>
       <c r="W19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X19">
         <v>11.5</v>
@@ -5339,7 +5339,7 @@
         <v>10.5</v>
       </c>
       <c r="AH19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI19">
         <v>110</v>
@@ -5357,7 +5357,7 @@
         <v>230</v>
       </c>
       <c r="AN19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO19">
         <v>170</v>
@@ -5497,7 +5497,7 @@
         <v>160</v>
       </c>
       <c r="F20">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G20">
         <v>9.800000000000001</v>
@@ -5506,7 +5506,7 @@
         <v>1.55</v>
       </c>
       <c r="I20">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="J20">
         <v>3.85</v>
@@ -5527,7 +5527,7 @@
         <v>1.47</v>
       </c>
       <c r="P20">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q20">
         <v>2.46</v>
@@ -5545,10 +5545,10 @@
         <v>1.52</v>
       </c>
       <c r="V20">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
         <v>970</v>
@@ -5739,22 +5739,22 @@
         <v>161</v>
       </c>
       <c r="F21">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="G21">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I21">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J21">
         <v>2.96</v>
       </c>
       <c r="K21">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5787,10 +5787,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="W21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5981,157 +5981,157 @@
         <v>162</v>
       </c>
       <c r="F22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G22">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H22">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="I22">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="K22">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q22">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R22">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S22">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W22">
         <v>1.24</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
         <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
         <v>1.03</v>
@@ -6223,118 +6223,118 @@
         <v>163</v>
       </c>
       <c r="F23">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="G23">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="H23">
-        <v>8.6</v>
+        <v>1.12</v>
       </c>
       <c r="I23">
-        <v>870</v>
+        <v>17.5</v>
       </c>
       <c r="J23">
         <v>4</v>
       </c>
       <c r="K23">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="O23">
+        <v>1.34</v>
+      </c>
+      <c r="P23">
+        <v>1.67</v>
+      </c>
+      <c r="Q23">
+        <v>2.08</v>
+      </c>
+      <c r="R23">
+        <v>1.23</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
+      </c>
+      <c r="T23">
+        <v>2.36</v>
+      </c>
+      <c r="U23">
+        <v>1.43</v>
+      </c>
+      <c r="V23">
         <v>1.06</v>
       </c>
-      <c r="P23">
-        <v>1.52</v>
-      </c>
-      <c r="Q23">
-        <v>2.02</v>
-      </c>
-      <c r="R23">
-        <v>1.17</v>
-      </c>
-      <c r="S23">
-        <v>2.78</v>
-      </c>
-      <c r="T23">
-        <v>1.01</v>
-      </c>
-      <c r="U23">
-        <v>1.01</v>
-      </c>
-      <c r="V23">
-        <v>1.01</v>
-      </c>
       <c r="W23">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
         <v>1.03</v>
@@ -6343,34 +6343,34 @@
         <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
         <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
         <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
         <v>1.03</v>
@@ -6707,13 +6707,13 @@
         <v>165</v>
       </c>
       <c r="F25">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G25">
         <v>600</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I25">
         <v>870</v>
@@ -6755,10 +6755,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6991,7 +6991,7 @@
         <v>2.74</v>
       </c>
       <c r="T26">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U26">
         <v>2</v>
@@ -7012,7 +7012,7 @@
         <v>75</v>
       </c>
       <c r="AA26">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -7036,13 +7036,13 @@
         <v>25</v>
       </c>
       <c r="AI26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ26">
         <v>12.5</v>
       </c>
       <c r="AK26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL26">
         <v>34</v>
@@ -7057,13 +7057,13 @@
         <v>130</v>
       </c>
       <c r="AP26">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ26">
         <v>26</v>
       </c>
       <c r="AR26">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AS26">
         <v>50</v>
@@ -7111,64 +7111,64 @@
         <v>42</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI26">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK26">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL26">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM26">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO26">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ26">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS26">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU26">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW26">
         <v>17</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY26">
         <v>17.5</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA26">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7200,7 +7200,7 @@
         <v>2.44</v>
       </c>
       <c r="I27">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J27">
         <v>3.55</v>
@@ -7215,37 +7215,37 @@
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>1.29</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q27">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T27">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="U27">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W27">
         <v>1.46</v>
       </c>
       <c r="X27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y27">
         <v>12</v>
@@ -7257,10 +7257,10 @@
         <v>36</v>
       </c>
       <c r="AB27">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC27">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD27">
         <v>12.5</v>
@@ -7284,7 +7284,7 @@
         <v>55</v>
       </c>
       <c r="AK27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL27">
         <v>44</v>
@@ -7308,13 +7308,13 @@
         <v>14.5</v>
       </c>
       <c r="AS27">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AT27">
         <v>11.5</v>
       </c>
       <c r="AU27">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV27">
         <v>10</v>
@@ -7329,25 +7329,25 @@
         <v>11.5</v>
       </c>
       <c r="AZ27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA27">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BB27">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC27">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BD27">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE27">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BG27">
         <v>15.5</v>
@@ -7433,10 +7433,10 @@
         <v>168</v>
       </c>
       <c r="F28">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G28">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H28">
         <v>6</v>
@@ -7475,7 +7475,7 @@
         <v>2.68</v>
       </c>
       <c r="T28">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U28">
         <v>2.18</v>
@@ -7484,7 +7484,7 @@
         <v>1.18</v>
       </c>
       <c r="W28">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X28">
         <v>24</v>
@@ -7574,7 +7574,7 @@
         <v>17.5</v>
       </c>
       <c r="BA28">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BB28">
         <v>13.5</v>
@@ -7678,10 +7678,10 @@
         <v>1.81</v>
       </c>
       <c r="G29">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H29">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I29">
         <v>4.7</v>
@@ -7690,7 +7690,7 @@
         <v>4.2</v>
       </c>
       <c r="K29">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L29">
         <v>1.32</v>
@@ -7702,7 +7702,7 @@
         <v>5.5</v>
       </c>
       <c r="O29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P29">
         <v>2.52</v>
@@ -7711,16 +7711,16 @@
         <v>1.62</v>
       </c>
       <c r="R29">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S29">
         <v>2.56</v>
       </c>
       <c r="T29">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U29">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V29">
         <v>1.27</v>
@@ -7777,7 +7777,7 @@
         <v>1000</v>
       </c>
       <c r="AN29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO29">
         <v>40</v>
@@ -7798,7 +7798,7 @@
         <v>11.5</v>
       </c>
       <c r="AU29">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV29">
         <v>16</v>
@@ -7831,7 +7831,7 @@
         <v>55</v>
       </c>
       <c r="BF29">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG29">
         <v>24</v>
@@ -7840,7 +7840,7 @@
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
@@ -7864,7 +7864,7 @@
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BR29">
         <v>1000</v>
@@ -7876,7 +7876,7 @@
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BV29">
         <v>1000</v>
@@ -7971,7 +7971,7 @@
         <v>4.7</v>
       </c>
       <c r="X30">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y30">
         <v>55</v>
@@ -7995,10 +7995,10 @@
         <v>1000</v>
       </c>
       <c r="AF30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG30">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH30">
         <v>32</v>
@@ -8022,7 +8022,7 @@
         <v>3.5</v>
       </c>
       <c r="AO30">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AP30">
         <v>28</v>
@@ -8067,7 +8067,7 @@
         <v>12.5</v>
       </c>
       <c r="BD30">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE30">
         <v>44</v>
@@ -8079,64 +8079,64 @@
         <v>50</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI30">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK30">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM30">
         <v>28</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO30">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BP30">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BQ30">
-        <v>1.67</v>
+        <v>5.7</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS30">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BU30">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BW30">
-        <v>2.06</v>
+        <v>22</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY30">
         <v>19</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="CA30">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB30" t="s">
         <v>177</v>
@@ -8267,13 +8267,13 @@
         <v>42</v>
       </c>
       <c r="AP31">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ31">
         <v>22</v>
       </c>
       <c r="AR31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AS31">
         <v>38</v>
@@ -8378,7 +8378,7 @@
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>2.34</v>
+        <v>7.8</v>
       </c>
       <c r="CB31" t="s">
         <v>177</v>
@@ -8407,10 +8407,10 @@
         <v>3.05</v>
       </c>
       <c r="H32">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I32">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J32">
         <v>3.65</v>
@@ -8449,10 +8449,10 @@
         <v>2.46</v>
       </c>
       <c r="V32">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W32">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X32">
         <v>17.5</v>
@@ -8476,7 +8476,7 @@
         <v>11.5</v>
       </c>
       <c r="AE32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF32">
         <v>22</v>
@@ -8491,7 +8491,7 @@
         <v>34</v>
       </c>
       <c r="AJ32">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK32">
         <v>30</v>
@@ -8515,7 +8515,7 @@
         <v>12</v>
       </c>
       <c r="AR32">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS32">
         <v>29</v>
@@ -8542,7 +8542,7 @@
         <v>13</v>
       </c>
       <c r="BA32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB32">
         <v>42</v>
@@ -8614,7 +8614,7 @@
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>2.38</v>
+        <v>12</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
@@ -8676,7 +8676,7 @@
         <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R33">
         <v>1.44</v>
@@ -8688,7 +8688,7 @@
         <v>1.68</v>
       </c>
       <c r="U33">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V33">
         <v>1.6</v>
@@ -8715,7 +8715,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD33">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE33">
         <v>27</v>
@@ -8730,7 +8730,7 @@
         <v>16.5</v>
       </c>
       <c r="AI33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ33">
         <v>44</v>
@@ -8748,7 +8748,7 @@
         <v>23</v>
       </c>
       <c r="AO33">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP33">
         <v>15</v>
@@ -8757,13 +8757,13 @@
         <v>11.5</v>
       </c>
       <c r="AR33">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS33">
         <v>34</v>
       </c>
       <c r="AT33">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU33">
         <v>7.6</v>
@@ -8891,10 +8891,10 @@
         <v>3.85</v>
       </c>
       <c r="H34">
+        <v>2.02</v>
+      </c>
+      <c r="I34">
         <v>2.04</v>
-      </c>
-      <c r="I34">
-        <v>2.06</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -8933,7 +8933,7 @@
         <v>2.52</v>
       </c>
       <c r="V34">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W34">
         <v>1.35</v>
@@ -8966,7 +8966,7 @@
         <v>32</v>
       </c>
       <c r="AG34">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH34">
         <v>15.5</v>
@@ -8987,7 +8987,7 @@
         <v>65</v>
       </c>
       <c r="AN34">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO34">
         <v>10.5</v>
@@ -9020,7 +9020,7 @@
         <v>28</v>
       </c>
       <c r="AY34">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ34">
         <v>14.5</v>
@@ -9038,7 +9038,7 @@
         <v>36</v>
       </c>
       <c r="BE34">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BF34">
         <v>26</v>
@@ -9071,7 +9071,7 @@
         <v>6.6</v>
       </c>
       <c r="BP34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ34">
         <v>8.800000000000001</v>
@@ -9127,19 +9127,19 @@
         <v>175</v>
       </c>
       <c r="F35">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G35">
         <v>600</v>
       </c>
       <c r="H35">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I35">
         <v>870</v>
       </c>
       <c r="J35">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9175,10 +9175,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9369,7 +9369,7 @@
         <v>176</v>
       </c>
       <c r="F36">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="G36">
         <v>2.5</v>
@@ -9378,13 +9378,13 @@
         <v>3.2</v>
       </c>
       <c r="I36">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J36">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="K36">
-        <v>3.75</v>
+        <v>500</v>
       </c>
       <c r="L36">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="177">
   <si>
     <t>League</t>
   </si>
@@ -274,9 +274,6 @@
     <t>Georgian Umaglesi Liga</t>
   </si>
   <si>
-    <t>Nigerian Premier League</t>
-  </si>
-  <si>
     <t>Estonian Premier League</t>
   </si>
   <si>
@@ -361,9 +358,6 @@
     <t>FK Atyrau</t>
   </si>
   <si>
-    <t>Enugu Rangers International</t>
-  </si>
-  <si>
     <t>FCI Tallinn</t>
   </si>
   <si>
@@ -379,15 +373,15 @@
     <t>Rosengard</t>
   </si>
   <si>
+    <t>Eskilsminne</t>
+  </si>
+  <si>
+    <t>Skovde AIK</t>
+  </si>
+  <si>
     <t>Kristianstads</t>
   </si>
   <si>
-    <t>Skovde AIK</t>
-  </si>
-  <si>
-    <t>Eskilsminne</t>
-  </si>
-  <si>
     <t>Betis</t>
   </si>
   <si>
@@ -409,30 +403,33 @@
     <t>Assyriska FF</t>
   </si>
   <si>
+    <t>Plzen</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
     <t>Crystal Palace</t>
   </si>
   <si>
+    <t>Lillestrom</t>
+  </si>
+  <si>
     <t>AFC Wimbledon</t>
   </si>
   <si>
-    <t>Lillestrom</t>
+    <t>Cr Temouchent</t>
   </si>
   <si>
     <t>Besiktas</t>
   </si>
   <si>
-    <t>Juventus</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Plzen</t>
-  </si>
-  <si>
     <t>Malaga</t>
   </si>
   <si>
@@ -466,9 +463,6 @@
     <t>FC Ordabasy</t>
   </si>
   <si>
-    <t>Nasarawa United</t>
-  </si>
-  <si>
     <t>Tammeka Tartu</t>
   </si>
   <si>
@@ -484,15 +478,15 @@
     <t>Trelleborgs</t>
   </si>
   <si>
+    <t>Tvaakers</t>
+  </si>
+  <si>
+    <t>FC Trollhattan</t>
+  </si>
+  <si>
     <t>BK Olympic</t>
   </si>
   <si>
-    <t>FC Trollhattan</t>
-  </si>
-  <si>
-    <t>Tvaakers</t>
-  </si>
-  <si>
     <t>Getafe</t>
   </si>
   <si>
@@ -514,30 +508,33 @@
     <t>AFC Eskilstuna</t>
   </si>
   <si>
+    <t>Union St Gilloise</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>Ferencvaros</t>
+  </si>
+  <si>
+    <t>NEC Nijmegen</t>
+  </si>
+  <si>
     <t>Lech Poznan</t>
   </si>
   <si>
+    <t>Torreense</t>
+  </si>
+  <si>
     <t>MK Dons</t>
   </si>
   <si>
-    <t>Torreense</t>
+    <t>Kabylie</t>
   </si>
   <si>
     <t>Marseille</t>
   </si>
   <si>
-    <t>NEC Nijmegen</t>
-  </si>
-  <si>
-    <t>Ferencvaros</t>
-  </si>
-  <si>
-    <t>Bournemouth</t>
-  </si>
-  <si>
-    <t>Union St Gilloise</t>
-  </si>
-  <si>
     <t>Villarreal</t>
   </si>
   <si>
@@ -547,7 +544,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 04:59:18</t>
+    <t>2026-09-16 07:13:15</t>
   </si>
 </sst>
 </file>
@@ -1129,40 +1126,40 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F2">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="H2">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="K2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="L2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
         <v>6.2</v>
@@ -1171,136 +1168,136 @@
         <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R2">
+        <v>1.72</v>
+      </c>
+      <c r="S2">
+        <v>2.26</v>
+      </c>
+      <c r="T2">
         <v>1.69</v>
       </c>
-      <c r="S2">
-        <v>2.3</v>
-      </c>
-      <c r="T2">
-        <v>1.64</v>
-      </c>
       <c r="U2">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="W2">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="X2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1363,7 +1360,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1371,28 +1368,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
         <v>94</v>
       </c>
-      <c r="C3" t="s">
-        <v>95</v>
-      </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F3">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G3">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
         <v>3.1</v>
@@ -1401,22 +1398,22 @@
         <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M3">
         <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O3">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="P3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R3">
         <v>1.14</v>
@@ -1425,22 +1422,22 @@
         <v>7.2</v>
       </c>
       <c r="T3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="X3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="Z3">
         <v>36</v>
@@ -1455,28 +1452,28 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE3">
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
         <v>12</v>
       </c>
       <c r="AH3">
+        <v>38</v>
+      </c>
+      <c r="AI3">
+        <v>160</v>
+      </c>
+      <c r="AJ3">
+        <v>28</v>
+      </c>
+      <c r="AK3">
         <v>34</v>
-      </c>
-      <c r="AI3">
-        <v>170</v>
-      </c>
-      <c r="AJ3">
-        <v>27</v>
-      </c>
-      <c r="AK3">
-        <v>32</v>
       </c>
       <c r="AL3">
         <v>85</v>
@@ -1497,13 +1494,13 @@
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AS3">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1512,100 +1509,100 @@
         <v>21</v>
       </c>
       <c r="AW3">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AZ3">
         <v>28</v>
       </c>
       <c r="BA3">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD3">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BE3">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BG3">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH3">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1613,16 +1610,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F4">
         <v>4.8</v>
@@ -1637,13 +1634,13 @@
         <v>1.85</v>
       </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1655,67 +1652,67 @@
         <v>1.32</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
         <v>2.16</v>
       </c>
       <c r="W4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X4">
         <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA4">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AB4">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF4">
         <v>40</v>
       </c>
       <c r="AG4">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI4">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AK4">
         <v>70</v>
@@ -1730,16 +1727,16 @@
         <v>75</v>
       </c>
       <c r="AO4">
+        <v>970</v>
+      </c>
+      <c r="AP4">
         <v>12.5</v>
-      </c>
-      <c r="AP4">
-        <v>13</v>
       </c>
       <c r="AQ4">
         <v>8</v>
       </c>
       <c r="AR4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS4">
         <v>17.5</v>
@@ -1751,13 +1748,13 @@
         <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW4">
         <v>17</v>
       </c>
       <c r="AX4">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AY4">
         <v>17</v>
@@ -1766,88 +1763,88 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB4">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD4">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="BE4">
-        <v>48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="BG4">
         <v>10.5</v>
       </c>
       <c r="BH4">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
         <v>6</v>
       </c>
       <c r="BP4">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1855,184 +1852,184 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F5">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="G5">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H5">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="K5">
         <v>3.15</v>
       </c>
       <c r="L5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O5">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="P5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q5">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="R5">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="S5">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="T5">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U5">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="X5">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>1.85</v>
       </c>
       <c r="AS5">
-        <v>9.4</v>
+        <v>1.85</v>
       </c>
       <c r="AT5">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>1.85</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>1.85</v>
       </c>
       <c r="AX5">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>1.73</v>
       </c>
       <c r="AZ5">
-        <v>8.199999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="BA5">
-        <v>9.4</v>
+        <v>1.85</v>
       </c>
       <c r="BB5">
-        <v>8.199999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="BC5">
-        <v>8.4</v>
+        <v>1.85</v>
       </c>
       <c r="BD5">
-        <v>9.4</v>
+        <v>1.85</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="BF5">
-        <v>8.4</v>
+        <v>1.85</v>
       </c>
       <c r="BG5">
-        <v>9.6</v>
+        <v>1.85</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -2050,7 +2047,7 @@
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -2089,7 +2086,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2097,31 +2094,31 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F6">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2136,10 +2133,10 @@
         <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
         <v>1.26</v>
@@ -2148,7 +2145,7 @@
         <v>1.08</v>
       </c>
       <c r="S6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2157,10 +2154,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2331,7 +2328,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2339,16 +2336,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F7">
         <v>1.17</v>
@@ -2360,10 +2357,10 @@
         <v>1.17</v>
       </c>
       <c r="I7">
-        <v>990</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2387,7 +2384,7 @@
         <v>1.25</v>
       </c>
       <c r="R7">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
         <v>1.26</v>
@@ -2399,10 +2396,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2573,7 +2570,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2581,31 +2578,31 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F8">
-        <v>1.12</v>
+        <v>2.08</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>2.9</v>
       </c>
       <c r="H8">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>4.7</v>
       </c>
       <c r="J8">
-        <v>1.15</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2617,22 +2614,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
+        <v>1.64</v>
+      </c>
+      <c r="Q8">
+        <v>1.35</v>
+      </c>
+      <c r="R8">
         <v>1.25</v>
       </c>
-      <c r="Q8">
-        <v>1.33</v>
-      </c>
-      <c r="R8">
-        <v>1.07</v>
-      </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>2.8</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2641,10 +2638,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2815,7 +2812,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2823,16 +2820,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F9">
         <v>3.2</v>
@@ -2841,13 +2838,13 @@
         <v>600</v>
       </c>
       <c r="H9">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="I9">
         <v>1.62</v>
       </c>
       <c r="J9">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2859,22 +2856,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
         <v>1.26</v>
       </c>
       <c r="Q9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R9">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3057,7 +3054,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3065,35 +3062,35 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
         <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G10">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
+        <v>870</v>
+      </c>
+      <c r="J10">
+        <v>1.13</v>
+      </c>
+      <c r="K10">
         <v>950</v>
       </c>
-      <c r="J10">
-        <v>1.1</v>
-      </c>
-      <c r="K10">
-        <v>920</v>
-      </c>
       <c r="L10">
         <v>1.01</v>
       </c>
@@ -3101,22 +3098,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P10">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="R10">
         <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3128,7 +3125,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3185,52 +3182,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3299,7 +3296,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3307,106 +3304,106 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
         <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F11">
+        <v>8.6</v>
+      </c>
+      <c r="G11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H11">
+        <v>1.42</v>
+      </c>
+      <c r="I11">
+        <v>1.44</v>
+      </c>
+      <c r="J11">
+        <v>5.2</v>
+      </c>
+      <c r="K11">
+        <v>5.5</v>
+      </c>
+      <c r="L11">
+        <v>1.3</v>
+      </c>
+      <c r="M11">
+        <v>1.03</v>
+      </c>
+      <c r="N11">
+        <v>5.6</v>
+      </c>
+      <c r="O11">
+        <v>1.2</v>
+      </c>
+      <c r="P11">
+        <v>2.54</v>
+      </c>
+      <c r="Q11">
+        <v>1.61</v>
+      </c>
+      <c r="R11">
+        <v>1.61</v>
+      </c>
+      <c r="S11">
+        <v>2.56</v>
+      </c>
+      <c r="T11">
+        <v>1.81</v>
+      </c>
+      <c r="U11">
+        <v>1.95</v>
+      </c>
+      <c r="V11">
+        <v>3.25</v>
+      </c>
+      <c r="W11">
         <v>1.12</v>
       </c>
-      <c r="G11">
-        <v>600</v>
-      </c>
-      <c r="H11">
-        <v>1.1</v>
-      </c>
-      <c r="I11">
-        <v>870</v>
-      </c>
-      <c r="J11">
-        <v>1.13</v>
-      </c>
-      <c r="K11">
+      <c r="X11">
         <v>950</v>
       </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>1.25</v>
-      </c>
-      <c r="O11">
-        <v>1.06</v>
-      </c>
-      <c r="P11">
-        <v>1.25</v>
-      </c>
-      <c r="Q11">
-        <v>1.01</v>
-      </c>
-      <c r="R11">
-        <v>1.08</v>
-      </c>
-      <c r="S11">
-        <v>1.07</v>
-      </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>1.01</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
         <v>1000</v>
@@ -3421,88 +3418,88 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -3514,19 +3511,19 @@
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX11">
         <v>1000</v>
@@ -3538,252 +3535,252 @@
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F12">
-        <v>8.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="G12">
-        <v>9</v>
+        <v>3.25</v>
       </c>
       <c r="H12">
-        <v>1.42</v>
+        <v>2.34</v>
       </c>
       <c r="I12">
+        <v>2.38</v>
+      </c>
+      <c r="J12">
+        <v>3.7</v>
+      </c>
+      <c r="K12">
+        <v>3.8</v>
+      </c>
+      <c r="L12">
+        <v>1.34</v>
+      </c>
+      <c r="M12">
+        <v>1.05</v>
+      </c>
+      <c r="N12">
+        <v>4.9</v>
+      </c>
+      <c r="O12">
+        <v>1.23</v>
+      </c>
+      <c r="P12">
+        <v>2.32</v>
+      </c>
+      <c r="Q12">
+        <v>1.73</v>
+      </c>
+      <c r="R12">
+        <v>1.53</v>
+      </c>
+      <c r="S12">
+        <v>2.78</v>
+      </c>
+      <c r="T12">
+        <v>1.61</v>
+      </c>
+      <c r="U12">
+        <v>2.52</v>
+      </c>
+      <c r="V12">
+        <v>1.72</v>
+      </c>
+      <c r="W12">
         <v>1.44</v>
       </c>
-      <c r="J12">
-        <v>5.2</v>
-      </c>
-      <c r="K12">
-        <v>5.5</v>
-      </c>
-      <c r="L12">
-        <v>1.3</v>
-      </c>
-      <c r="M12">
-        <v>1.04</v>
-      </c>
-      <c r="N12">
-        <v>5.5</v>
-      </c>
-      <c r="O12">
-        <v>1.2</v>
-      </c>
-      <c r="P12">
-        <v>2.54</v>
-      </c>
-      <c r="Q12">
-        <v>1.61</v>
-      </c>
-      <c r="R12">
-        <v>1.6</v>
-      </c>
-      <c r="S12">
-        <v>2.56</v>
-      </c>
-      <c r="T12">
-        <v>1.84</v>
-      </c>
-      <c r="U12">
-        <v>2.04</v>
-      </c>
-      <c r="V12">
-        <v>3.25</v>
-      </c>
-      <c r="W12">
-        <v>1.12</v>
-      </c>
       <c r="X12">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Y12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AA12">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AB12">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AC12">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE12">
+        <v>24</v>
+      </c>
+      <c r="AF12">
+        <v>25</v>
+      </c>
+      <c r="AG12">
+        <v>14.5</v>
+      </c>
+      <c r="AH12">
         <v>15</v>
-      </c>
-      <c r="AF12">
-        <v>90</v>
-      </c>
-      <c r="AG12">
-        <v>34</v>
-      </c>
-      <c r="AH12">
-        <v>25</v>
       </c>
       <c r="AI12">
         <v>34</v>
       </c>
       <c r="AJ12">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="AK12">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AL12">
+        <v>38</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>25</v>
+      </c>
+      <c r="AO12">
+        <v>16.5</v>
+      </c>
+      <c r="AP12">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12">
+        <v>12</v>
+      </c>
+      <c r="AR12">
+        <v>14</v>
+      </c>
+      <c r="AS12">
+        <v>28</v>
+      </c>
+      <c r="AT12">
+        <v>14.5</v>
+      </c>
+      <c r="AU12">
+        <v>7.8</v>
+      </c>
+      <c r="AV12">
+        <v>9.6</v>
+      </c>
+      <c r="AW12">
+        <v>16</v>
+      </c>
+      <c r="AX12">
+        <v>22</v>
+      </c>
+      <c r="AY12">
+        <v>12.5</v>
+      </c>
+      <c r="AZ12">
+        <v>13.5</v>
+      </c>
+      <c r="BA12">
+        <v>27</v>
+      </c>
+      <c r="BB12">
+        <v>28</v>
+      </c>
+      <c r="BC12">
+        <v>21</v>
+      </c>
+      <c r="BD12">
+        <v>32</v>
+      </c>
+      <c r="BE12">
+        <v>30</v>
+      </c>
+      <c r="BF12">
+        <v>21</v>
+      </c>
+      <c r="BG12">
+        <v>12</v>
+      </c>
+      <c r="BH12">
+        <v>4</v>
+      </c>
+      <c r="BI12">
+        <v>3.65</v>
+      </c>
+      <c r="BJ12">
+        <v>10.5</v>
+      </c>
+      <c r="BK12">
+        <v>7.6</v>
+      </c>
+      <c r="BL12">
         <v>110</v>
       </c>
-      <c r="AM12">
-        <v>130</v>
-      </c>
-      <c r="AN12">
-        <v>150</v>
-      </c>
-      <c r="AO12">
-        <v>5.5</v>
-      </c>
-      <c r="AP12">
-        <v>21</v>
-      </c>
-      <c r="AQ12">
-        <v>9.4</v>
-      </c>
-      <c r="AR12">
-        <v>8.4</v>
-      </c>
-      <c r="AS12">
-        <v>10.5</v>
-      </c>
-      <c r="AT12">
+      <c r="BM12">
+        <v>55</v>
+      </c>
+      <c r="BN12">
+        <v>7.8</v>
+      </c>
+      <c r="BO12">
+        <v>5.8</v>
+      </c>
+      <c r="BP12">
+        <v>27</v>
+      </c>
+      <c r="BQ12">
+        <v>15.5</v>
+      </c>
+      <c r="BR12">
+        <v>36</v>
+      </c>
+      <c r="BS12">
+        <v>12</v>
+      </c>
+      <c r="BT12">
+        <v>5.6</v>
+      </c>
+      <c r="BU12">
+        <v>5</v>
+      </c>
+      <c r="BV12">
+        <v>19.5</v>
+      </c>
+      <c r="BW12">
+        <v>12</v>
+      </c>
+      <c r="BX12">
+        <v>32</v>
+      </c>
+      <c r="BY12">
+        <v>22</v>
+      </c>
+      <c r="BZ12">
         <v>23</v>
       </c>
-      <c r="AU12">
-        <v>10.5</v>
-      </c>
-      <c r="AV12">
+      <c r="CA12">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW12">
-        <v>12.5</v>
-      </c>
-      <c r="AX12">
-        <v>32</v>
-      </c>
-      <c r="AY12">
-        <v>22</v>
-      </c>
-      <c r="AZ12">
-        <v>19.5</v>
-      </c>
-      <c r="BA12">
-        <v>23</v>
-      </c>
-      <c r="BB12">
-        <v>9.6</v>
-      </c>
-      <c r="BC12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG12">
-        <v>4.8</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>3.5</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>7.4</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>26</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>7.8</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>17</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>17.5</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>3.35</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>5.3</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>10</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>6.8</v>
-      </c>
       <c r="CB12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3791,273 +3788,273 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F13">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="H13">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="I13">
-        <v>2.38</v>
+        <v>870</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L13">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.9</v>
+        <v>1.75</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>1.45</v>
       </c>
       <c r="T13">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="W13">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="X13">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F14">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="G14">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="H14">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="I14">
-        <v>870</v>
+        <v>3.95</v>
       </c>
       <c r="J14">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4069,22 +4066,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
         <v>1.01</v>
       </c>
       <c r="P14">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q14">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="S14">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4093,10 +4090,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>4.9</v>
+        <v>1.54</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4261,48 +4258,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F15">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="G15">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="H15">
-        <v>2.68</v>
+        <v>1.86</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K15">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4311,22 +4308,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O15">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="P15">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S15">
-        <v>2.64</v>
+        <v>2.02</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4335,10 +4332,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4509,42 +4506,42 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F16">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="G16">
-        <v>3.65</v>
+        <v>970</v>
       </c>
       <c r="H16">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="I16">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4553,22 +4550,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.68</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="R16">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="S16">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4577,10 +4574,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4745,48 +4742,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F17">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="G17">
+        <v>3.45</v>
+      </c>
+      <c r="H17">
+        <v>2.1</v>
+      </c>
+      <c r="I17">
         <v>2.96</v>
       </c>
-      <c r="H17">
-        <v>2.22</v>
-      </c>
-      <c r="I17">
-        <v>2.94</v>
-      </c>
       <c r="J17">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="K17">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4795,22 +4792,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="O17">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="P17">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="R17">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="S17">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4819,10 +4816,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4987,13 +4984,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5001,563 +4998,563 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="G18">
-        <v>2.56</v>
+        <v>1.73</v>
       </c>
       <c r="H18">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="J18">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
+        <v>3.9</v>
+      </c>
+      <c r="L18">
+        <v>1.5</v>
+      </c>
+      <c r="M18">
+        <v>1.09</v>
+      </c>
+      <c r="N18">
+        <v>3.2</v>
+      </c>
+      <c r="O18">
+        <v>1.43</v>
+      </c>
+      <c r="P18">
+        <v>1.75</v>
+      </c>
+      <c r="Q18">
+        <v>2.3</v>
+      </c>
+      <c r="R18">
+        <v>1.27</v>
+      </c>
+      <c r="S18">
+        <v>4.5</v>
+      </c>
+      <c r="T18">
+        <v>2.2</v>
+      </c>
+      <c r="U18">
+        <v>1.8</v>
+      </c>
+      <c r="V18">
+        <v>1.18</v>
+      </c>
+      <c r="W18">
+        <v>2.36</v>
+      </c>
+      <c r="X18">
+        <v>11.5</v>
+      </c>
+      <c r="Y18">
+        <v>16.5</v>
+      </c>
+      <c r="Z18">
+        <v>48</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
         <v>7</v>
       </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>3.85</v>
-      </c>
-      <c r="O18">
-        <v>1.01</v>
-      </c>
-      <c r="P18">
-        <v>2.12</v>
-      </c>
-      <c r="Q18">
-        <v>1.62</v>
-      </c>
-      <c r="R18">
-        <v>1.46</v>
-      </c>
-      <c r="S18">
-        <v>2</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.38</v>
-      </c>
-      <c r="W18">
-        <v>1.64</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM18">
         <v>1000</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>70</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="CB18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F19">
-        <v>1.72</v>
+        <v>6.4</v>
       </c>
       <c r="G19">
-        <v>1.73</v>
+        <v>600</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>1.48</v>
       </c>
       <c r="I19">
-        <v>6.4</v>
+        <v>1.64</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="K19">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="L19">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N19">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O19">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P19">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S19">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="T19">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U19">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="V19">
-        <v>1.18</v>
+        <v>2.48</v>
       </c>
       <c r="W19">
-        <v>2.36</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y19">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z19">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AA19">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>10.5</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19">
-        <v>15</v>
+        <v>1.3</v>
       </c>
       <c r="AR19">
-        <v>30</v>
+        <v>1.36</v>
       </c>
       <c r="AS19">
-        <v>44</v>
+        <v>1.56</v>
       </c>
       <c r="AT19">
-        <v>6.4</v>
+        <v>1.56</v>
       </c>
       <c r="AU19">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="AV19">
-        <v>22</v>
+        <v>1.56</v>
       </c>
       <c r="AW19">
-        <v>38</v>
+        <v>1.56</v>
       </c>
       <c r="AX19">
-        <v>8.4</v>
+        <v>1.56</v>
       </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="AZ19">
-        <v>24</v>
+        <v>1.56</v>
       </c>
       <c r="BA19">
-        <v>40</v>
+        <v>1.56</v>
       </c>
       <c r="BB19">
-        <v>15.5</v>
+        <v>1.56</v>
       </c>
       <c r="BC19">
-        <v>18.5</v>
+        <v>1.56</v>
       </c>
       <c r="BD19">
-        <v>42</v>
+        <v>1.56</v>
       </c>
       <c r="BE19">
-        <v>46</v>
+        <v>1.56</v>
       </c>
       <c r="BF19">
-        <v>12.5</v>
+        <v>1.56</v>
       </c>
       <c r="BG19">
-        <v>42</v>
+        <v>1.56</v>
       </c>
       <c r="BH19">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.82</v>
+        <v>1.28</v>
       </c>
       <c r="BJ19">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>10</v>
+        <v>1.28</v>
       </c>
       <c r="BL19">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>34</v>
+        <v>1.28</v>
       </c>
       <c r="BN19">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.75</v>
+        <v>1.28</v>
       </c>
       <c r="BP19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="BR19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>1.28</v>
       </c>
       <c r="BT19">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="BV19">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>12</v>
+        <v>1.28</v>
       </c>
       <c r="BX19">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>12.5</v>
+        <v>1.28</v>
       </c>
       <c r="BZ19">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>10</v>
+        <v>1.28</v>
       </c>
       <c r="CB19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F20">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="G20">
-        <v>9.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="H20">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="I20">
-        <v>1.6</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>1.88</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L20">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
+        <v>1.09</v>
+      </c>
+      <c r="N20">
+        <v>2.3</v>
+      </c>
+      <c r="O20">
+        <v>1.1</v>
+      </c>
+      <c r="P20">
+        <v>1.08</v>
+      </c>
+      <c r="Q20">
+        <v>1.56</v>
+      </c>
+      <c r="R20">
+        <v>1.08</v>
+      </c>
+      <c r="S20">
+        <v>1.01</v>
+      </c>
+      <c r="T20">
+        <v>1.01</v>
+      </c>
+      <c r="U20">
+        <v>1.01</v>
+      </c>
+      <c r="V20">
+        <v>1.76</v>
+      </c>
+      <c r="W20">
         <v>1.11</v>
       </c>
-      <c r="N20">
-        <v>2.94</v>
-      </c>
-      <c r="O20">
-        <v>1.47</v>
-      </c>
-      <c r="P20">
-        <v>1.63</v>
-      </c>
-      <c r="Q20">
-        <v>2.46</v>
-      </c>
-      <c r="R20">
-        <v>1.23</v>
-      </c>
-      <c r="S20">
-        <v>4.9</v>
-      </c>
-      <c r="T20">
-        <v>2.34</v>
-      </c>
-      <c r="U20">
-        <v>1.52</v>
-      </c>
-      <c r="V20">
-        <v>2.66</v>
-      </c>
-      <c r="W20">
-        <v>1.12</v>
-      </c>
       <c r="X20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
         <v>1000</v>
@@ -5566,7 +5563,7 @@
         <v>1000</v>
       </c>
       <c r="AC20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
         <v>1000</v>
@@ -5605,192 +5602,192 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F21">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H21">
+        <v>1.79</v>
+      </c>
+      <c r="I21">
         <v>1.99</v>
       </c>
-      <c r="I21">
-        <v>2.24</v>
-      </c>
       <c r="J21">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="O21">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="P21">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
-        <v>1.96</v>
+        <v>1.22</v>
       </c>
       <c r="R21">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5847,55 +5844,55 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG21">
         <v>1.01</v>
@@ -5904,7 +5901,7 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5940,7 +5937,7 @@
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -5961,180 +5958,180 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
         <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F22">
-        <v>3.8</v>
+        <v>1.33</v>
       </c>
       <c r="G22">
-        <v>5.1</v>
+        <v>1.47</v>
       </c>
       <c r="H22">
-        <v>1.79</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>1.99</v>
+        <v>870</v>
       </c>
       <c r="J22">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="K22">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="L22">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="O22">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="P22">
-        <v>2.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q22">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="S22">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="T22">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>2</v>
+        <v>1.06</v>
       </c>
       <c r="W22">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="X22">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR22">
         <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW22">
         <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA22">
         <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6146,7 +6143,7 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
@@ -6203,138 +6200,138 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F23">
-        <v>1.35</v>
+        <v>2.52</v>
       </c>
       <c r="G23">
-        <v>1.44</v>
+        <v>5.1</v>
       </c>
       <c r="H23">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="I23">
-        <v>17.5</v>
+        <v>2.26</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="O23">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="P23">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="Q23">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="R23">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="S23">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="T23">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.06</v>
+        <v>1.79</v>
       </c>
       <c r="W23">
-        <v>3.2</v>
+        <v>1.24</v>
       </c>
       <c r="X23">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23">
         <v>1.03</v>
@@ -6343,34 +6340,34 @@
         <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23">
         <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23">
         <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
         <v>1.03</v>
@@ -6385,102 +6382,102 @@
         <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA23">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
-        <v>5.1</v>
+        <v>600</v>
       </c>
       <c r="H24">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
-        <v>2.14</v>
+        <v>870</v>
       </c>
       <c r="J24">
-        <v>3.5</v>
+        <v>1.15</v>
       </c>
       <c r="K24">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6489,22 +6486,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="O24">
         <v>1.02</v>
       </c>
       <c r="P24">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q24">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="R24">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="S24">
-        <v>2.24</v>
+        <v>1.02</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6513,10 +6510,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.87</v>
+        <v>1.07</v>
       </c>
       <c r="W24">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6681,2208 +6678,2208 @@
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
         <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F25">
-        <v>1.12</v>
+        <v>2.88</v>
       </c>
       <c r="G25">
-        <v>600</v>
+        <v>2.92</v>
       </c>
       <c r="H25">
-        <v>1.12</v>
+        <v>2.6</v>
       </c>
       <c r="I25">
-        <v>870</v>
+        <v>2.64</v>
       </c>
       <c r="J25">
-        <v>1.12</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
-        <v>1.24</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q25">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="R25">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="S25">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V25">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM25">
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F26">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="G26">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="H26">
+        <v>2.44</v>
+      </c>
+      <c r="I26">
+        <v>2.48</v>
+      </c>
+      <c r="J26">
+        <v>3.65</v>
+      </c>
+      <c r="K26">
+        <v>3.7</v>
+      </c>
+      <c r="L26">
+        <v>1.36</v>
+      </c>
+      <c r="M26">
+        <v>1.05</v>
+      </c>
+      <c r="N26">
+        <v>4.7</v>
+      </c>
+      <c r="O26">
+        <v>1.25</v>
+      </c>
+      <c r="P26">
+        <v>2.26</v>
+      </c>
+      <c r="Q26">
+        <v>1.77</v>
+      </c>
+      <c r="R26">
+        <v>1.5</v>
+      </c>
+      <c r="S26">
+        <v>2.92</v>
+      </c>
+      <c r="T26">
+        <v>1.63</v>
+      </c>
+      <c r="U26">
+        <v>2.5</v>
+      </c>
+      <c r="V26">
+        <v>1.67</v>
+      </c>
+      <c r="W26">
+        <v>1.47</v>
+      </c>
+      <c r="X26">
+        <v>18</v>
+      </c>
+      <c r="Y26">
+        <v>13</v>
+      </c>
+      <c r="Z26">
+        <v>17.5</v>
+      </c>
+      <c r="AA26">
+        <v>34</v>
+      </c>
+      <c r="AB26">
+        <v>15.5</v>
+      </c>
+      <c r="AC26">
+        <v>8.4</v>
+      </c>
+      <c r="AD26">
+        <v>11.5</v>
+      </c>
+      <c r="AE26">
+        <v>24</v>
+      </c>
+      <c r="AF26">
+        <v>22</v>
+      </c>
+      <c r="AG26">
+        <v>13</v>
+      </c>
+      <c r="AH26">
+        <v>14</v>
+      </c>
+      <c r="AI26">
+        <v>34</v>
+      </c>
+      <c r="AJ26">
+        <v>50</v>
+      </c>
+      <c r="AK26">
+        <v>30</v>
+      </c>
+      <c r="AL26">
+        <v>38</v>
+      </c>
+      <c r="AM26">
+        <v>70</v>
+      </c>
+      <c r="AN26">
+        <v>26</v>
+      </c>
+      <c r="AO26">
+        <v>16.5</v>
+      </c>
+      <c r="AP26">
+        <v>16.5</v>
+      </c>
+      <c r="AQ26">
+        <v>12</v>
+      </c>
+      <c r="AR26">
+        <v>16</v>
+      </c>
+      <c r="AS26">
+        <v>29</v>
+      </c>
+      <c r="AT26">
+        <v>14</v>
+      </c>
+      <c r="AU26">
         <v>8</v>
       </c>
-      <c r="I26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J26">
-        <v>5.2</v>
-      </c>
-      <c r="K26">
-        <v>5.4</v>
-      </c>
-      <c r="L26">
-        <v>1.33</v>
-      </c>
-      <c r="M26">
-        <v>1.04</v>
-      </c>
-      <c r="N26">
-        <v>5.2</v>
-      </c>
-      <c r="O26">
-        <v>1.22</v>
-      </c>
-      <c r="P26">
-        <v>2.44</v>
-      </c>
-      <c r="Q26">
-        <v>1.67</v>
-      </c>
-      <c r="R26">
-        <v>1.55</v>
-      </c>
-      <c r="S26">
-        <v>2.74</v>
-      </c>
-      <c r="T26">
-        <v>1.93</v>
-      </c>
-      <c r="U26">
+      <c r="AV26">
+        <v>10.5</v>
+      </c>
+      <c r="AW26">
+        <v>21</v>
+      </c>
+      <c r="AX26">
+        <v>20</v>
+      </c>
+      <c r="AY26">
+        <v>12</v>
+      </c>
+      <c r="AZ26">
+        <v>13</v>
+      </c>
+      <c r="BA26">
+        <v>30</v>
+      </c>
+      <c r="BB26">
+        <v>42</v>
+      </c>
+      <c r="BC26">
+        <v>27</v>
+      </c>
+      <c r="BD26">
+        <v>32</v>
+      </c>
+      <c r="BE26">
+        <v>48</v>
+      </c>
+      <c r="BF26">
+        <v>20</v>
+      </c>
+      <c r="BG26">
+        <v>14.5</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>3.15</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
         <v>2</v>
       </c>
-      <c r="V26">
-        <v>1.13</v>
-      </c>
-      <c r="W26">
-        <v>3.2</v>
-      </c>
-      <c r="X26">
-        <v>23</v>
-      </c>
-      <c r="Y26">
-        <v>30</v>
-      </c>
-      <c r="Z26">
-        <v>75</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>10</v>
-      </c>
-      <c r="AC26">
-        <v>12</v>
-      </c>
-      <c r="AD26">
-        <v>32</v>
-      </c>
-      <c r="AE26">
-        <v>120</v>
-      </c>
-      <c r="AF26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG26">
-        <v>10.5</v>
-      </c>
-      <c r="AH26">
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
         <v>25</v>
       </c>
-      <c r="AI26">
-        <v>100</v>
-      </c>
-      <c r="AJ26">
-        <v>12.5</v>
-      </c>
-      <c r="AK26">
-        <v>14</v>
-      </c>
-      <c r="AL26">
-        <v>34</v>
-      </c>
-      <c r="AM26">
-        <v>130</v>
-      </c>
-      <c r="AN26">
-        <v>5.9</v>
-      </c>
-      <c r="AO26">
-        <v>130</v>
-      </c>
-      <c r="AP26">
-        <v>20</v>
-      </c>
-      <c r="AQ26">
-        <v>26</v>
-      </c>
-      <c r="AR26">
-        <v>60</v>
-      </c>
-      <c r="AS26">
-        <v>50</v>
-      </c>
-      <c r="AT26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU26">
-        <v>10.5</v>
-      </c>
-      <c r="AV26">
-        <v>26</v>
-      </c>
-      <c r="AW26">
-        <v>40</v>
-      </c>
-      <c r="AX26">
-        <v>8.4</v>
-      </c>
-      <c r="AY26">
-        <v>9.4</v>
-      </c>
-      <c r="AZ26">
-        <v>21</v>
-      </c>
-      <c r="BA26">
-        <v>75</v>
-      </c>
-      <c r="BB26">
-        <v>11</v>
-      </c>
-      <c r="BC26">
-        <v>13</v>
-      </c>
-      <c r="BD26">
-        <v>28</v>
-      </c>
-      <c r="BE26">
-        <v>42</v>
-      </c>
-      <c r="BF26">
-        <v>5.5</v>
-      </c>
-      <c r="BG26">
-        <v>42</v>
-      </c>
-      <c r="BH26">
-        <v>4.2</v>
-      </c>
-      <c r="BI26">
-        <v>3.75</v>
-      </c>
-      <c r="BJ26">
-        <v>12.5</v>
-      </c>
-      <c r="BK26">
-        <v>9.6</v>
-      </c>
-      <c r="BL26">
-        <v>150</v>
-      </c>
-      <c r="BM26">
-        <v>9.4</v>
-      </c>
       <c r="BN26">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>3.65</v>
+        <v>1.84</v>
       </c>
       <c r="BP26">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>7.4</v>
+        <v>2.36</v>
       </c>
       <c r="BR26">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>7.2</v>
+        <v>2.36</v>
       </c>
       <c r="BT26">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>5.6</v>
+        <v>1.77</v>
       </c>
       <c r="BV26">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>17</v>
+        <v>2.36</v>
       </c>
       <c r="BX26">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>17.5</v>
+        <v>2.36</v>
       </c>
       <c r="BZ26">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>6</v>
+        <v>2.36</v>
       </c>
       <c r="CB26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
         <v>93</v>
       </c>
-      <c r="B27" t="s">
-        <v>94</v>
-      </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="G27">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="H27">
+        <v>4.8</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
+        <v>4.2</v>
+      </c>
+      <c r="K27">
+        <v>4.3</v>
+      </c>
+      <c r="L27">
+        <v>1.29</v>
+      </c>
+      <c r="M27">
+        <v>1.04</v>
+      </c>
+      <c r="N27">
+        <v>6</v>
+      </c>
+      <c r="O27">
+        <v>1.19</v>
+      </c>
+      <c r="P27">
+        <v>2.64</v>
+      </c>
+      <c r="Q27">
+        <v>1.59</v>
+      </c>
+      <c r="R27">
+        <v>1.66</v>
+      </c>
+      <c r="S27">
         <v>2.44</v>
       </c>
-      <c r="I27">
-        <v>2.54</v>
-      </c>
-      <c r="J27">
-        <v>3.55</v>
-      </c>
-      <c r="K27">
-        <v>3.65</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.06</v>
-      </c>
-      <c r="N27">
-        <v>4</v>
-      </c>
-      <c r="O27">
-        <v>1.29</v>
-      </c>
-      <c r="P27">
-        <v>2.02</v>
-      </c>
-      <c r="Q27">
-        <v>1.89</v>
-      </c>
-      <c r="R27">
-        <v>1.41</v>
-      </c>
-      <c r="S27">
-        <v>3.2</v>
-      </c>
       <c r="T27">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="U27">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="W27">
-        <v>1.46</v>
+        <v>2.24</v>
       </c>
       <c r="X27">
+        <v>24</v>
+      </c>
+      <c r="Y27">
+        <v>25</v>
+      </c>
+      <c r="Z27">
+        <v>50</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>14.5</v>
+      </c>
+      <c r="AC27">
+        <v>10</v>
+      </c>
+      <c r="AD27">
+        <v>20</v>
+      </c>
+      <c r="AE27">
+        <v>55</v>
+      </c>
+      <c r="AF27">
+        <v>13.5</v>
+      </c>
+      <c r="AG27">
+        <v>10.5</v>
+      </c>
+      <c r="AH27">
+        <v>16.5</v>
+      </c>
+      <c r="AI27">
+        <v>55</v>
+      </c>
+      <c r="AJ27">
+        <v>20</v>
+      </c>
+      <c r="AK27">
         <v>16</v>
       </c>
-      <c r="Y27">
+      <c r="AL27">
+        <v>28</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>7.8</v>
+      </c>
+      <c r="AO27">
+        <v>48</v>
+      </c>
+      <c r="AP27">
+        <v>17.5</v>
+      </c>
+      <c r="AQ27">
+        <v>22</v>
+      </c>
+      <c r="AR27">
+        <v>24</v>
+      </c>
+      <c r="AS27">
+        <v>38</v>
+      </c>
+      <c r="AT27">
         <v>12</v>
       </c>
-      <c r="Z27">
+      <c r="AU27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV27">
+        <v>17</v>
+      </c>
+      <c r="AW27">
+        <v>27</v>
+      </c>
+      <c r="AX27">
+        <v>12</v>
+      </c>
+      <c r="AY27">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27">
+        <v>14</v>
+      </c>
+      <c r="BA27">
+        <v>42</v>
+      </c>
+      <c r="BB27">
         <v>17.5</v>
       </c>
-      <c r="AA27">
-        <v>36</v>
-      </c>
-      <c r="AB27">
-        <v>13.5</v>
-      </c>
-      <c r="AC27">
-        <v>8.4</v>
-      </c>
-      <c r="AD27">
+      <c r="BC27">
+        <v>14.5</v>
+      </c>
+      <c r="BD27">
+        <v>23</v>
+      </c>
+      <c r="BE27">
+        <v>30</v>
+      </c>
+      <c r="BF27">
+        <v>7</v>
+      </c>
+      <c r="BG27">
+        <v>32</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>3.7</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.99</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>19</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>3.9</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>2.1</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>2.34</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.98</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
         <v>12.5</v>
       </c>
-      <c r="AE27">
-        <v>27</v>
-      </c>
-      <c r="AF27">
-        <v>23</v>
-      </c>
-      <c r="AG27">
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
         <v>14</v>
       </c>
-      <c r="AH27">
-        <v>17</v>
-      </c>
-      <c r="AI27">
-        <v>38</v>
-      </c>
-      <c r="AJ27">
-        <v>55</v>
-      </c>
-      <c r="AK27">
-        <v>36</v>
-      </c>
-      <c r="AL27">
-        <v>44</v>
-      </c>
-      <c r="AM27">
-        <v>80</v>
-      </c>
-      <c r="AN27">
-        <v>28</v>
-      </c>
-      <c r="AO27">
-        <v>19</v>
-      </c>
-      <c r="AP27">
-        <v>13.5</v>
-      </c>
-      <c r="AQ27">
-        <v>10</v>
-      </c>
-      <c r="AR27">
-        <v>14.5</v>
-      </c>
-      <c r="AS27">
-        <v>9.4</v>
-      </c>
-      <c r="AT27">
-        <v>11.5</v>
-      </c>
-      <c r="AU27">
-        <v>7.2</v>
-      </c>
-      <c r="AV27">
-        <v>10</v>
-      </c>
-      <c r="AW27">
-        <v>22</v>
-      </c>
-      <c r="AX27">
-        <v>18.5</v>
-      </c>
-      <c r="AY27">
-        <v>11.5</v>
-      </c>
-      <c r="AZ27">
-        <v>14.5</v>
-      </c>
-      <c r="BA27">
-        <v>30</v>
-      </c>
-      <c r="BB27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC27">
-        <v>9.4</v>
-      </c>
-      <c r="BD27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF27">
-        <v>23</v>
-      </c>
-      <c r="BG27">
-        <v>15.5</v>
-      </c>
-      <c r="BH27">
-        <v>1000</v>
-      </c>
-      <c r="BI27">
-        <v>1.04</v>
-      </c>
-      <c r="BJ27">
-        <v>1000</v>
-      </c>
-      <c r="BK27">
-        <v>1.04</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>1.04</v>
-      </c>
-      <c r="BN27">
-        <v>1000</v>
-      </c>
-      <c r="BO27">
-        <v>1.04</v>
-      </c>
-      <c r="BP27">
-        <v>1000</v>
-      </c>
-      <c r="BQ27">
-        <v>1.04</v>
-      </c>
-      <c r="BR27">
-        <v>1000</v>
-      </c>
-      <c r="BS27">
-        <v>1.04</v>
-      </c>
-      <c r="BT27">
-        <v>1000</v>
-      </c>
-      <c r="BU27">
-        <v>1.04</v>
-      </c>
-      <c r="BV27">
-        <v>1000</v>
-      </c>
-      <c r="BW27">
-        <v>1.04</v>
-      </c>
-      <c r="BX27">
-        <v>1000</v>
-      </c>
-      <c r="BY27">
-        <v>1.04</v>
-      </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F28">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="G28">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="H28">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="I28">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="J28">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="K28">
+        <v>7.8</v>
+      </c>
+      <c r="L28">
+        <v>1.25</v>
+      </c>
+      <c r="M28">
+        <v>1.02</v>
+      </c>
+      <c r="N28">
+        <v>7</v>
+      </c>
+      <c r="O28">
+        <v>1.15</v>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
+        <v>1.47</v>
+      </c>
+      <c r="R28">
+        <v>1.8</v>
+      </c>
+      <c r="S28">
+        <v>2.18</v>
+      </c>
+      <c r="T28">
+        <v>2.06</v>
+      </c>
+      <c r="U28">
+        <v>1.88</v>
+      </c>
+      <c r="V28">
+        <v>1.06</v>
+      </c>
+      <c r="W28">
+        <v>4.8</v>
+      </c>
+      <c r="X28">
+        <v>38</v>
+      </c>
+      <c r="Y28">
+        <v>65</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>700</v>
+      </c>
+      <c r="AB28">
+        <v>12.5</v>
+      </c>
+      <c r="AC28">
+        <v>17.5</v>
+      </c>
+      <c r="AD28">
+        <v>55</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>9</v>
+      </c>
+      <c r="AG28">
+        <v>13</v>
+      </c>
+      <c r="AH28">
+        <v>40</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK28">
+        <v>15</v>
+      </c>
+      <c r="AL28">
+        <v>38</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>3.55</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>28</v>
+      </c>
+      <c r="AQ28">
+        <v>27</v>
+      </c>
+      <c r="AR28">
+        <v>42</v>
+      </c>
+      <c r="AS28">
+        <v>55</v>
+      </c>
+      <c r="AT28">
+        <v>10.5</v>
+      </c>
+      <c r="AU28">
+        <v>14.5</v>
+      </c>
+      <c r="AV28">
+        <v>27</v>
+      </c>
+      <c r="AW28">
+        <v>48</v>
+      </c>
+      <c r="AX28">
+        <v>7.6</v>
+      </c>
+      <c r="AY28">
+        <v>11</v>
+      </c>
+      <c r="AZ28">
+        <v>23</v>
+      </c>
+      <c r="BA28">
+        <v>44</v>
+      </c>
+      <c r="BB28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC28">
+        <v>12</v>
+      </c>
+      <c r="BD28">
+        <v>29</v>
+      </c>
+      <c r="BE28">
+        <v>44</v>
+      </c>
+      <c r="BF28">
+        <v>3.35</v>
+      </c>
+      <c r="BG28">
+        <v>50</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>4</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>2.52</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>2.74</v>
+      </c>
+      <c r="BN28">
+        <v>4.4</v>
+      </c>
+      <c r="BO28">
+        <v>3.2</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
         <v>5</v>
       </c>
-      <c r="L28">
-        <v>1.32</v>
-      </c>
-      <c r="M28">
-        <v>1.04</v>
-      </c>
-      <c r="N28">
-        <v>5.3</v>
-      </c>
-      <c r="O28">
-        <v>1.22</v>
-      </c>
-      <c r="P28">
-        <v>2.44</v>
-      </c>
-      <c r="Q28">
-        <v>1.65</v>
-      </c>
-      <c r="R28">
-        <v>1.56</v>
-      </c>
-      <c r="S28">
-        <v>2.68</v>
-      </c>
-      <c r="T28">
-        <v>1.77</v>
-      </c>
-      <c r="U28">
-        <v>2.18</v>
-      </c>
-      <c r="V28">
-        <v>1.18</v>
-      </c>
-      <c r="W28">
-        <v>2.68</v>
-      </c>
-      <c r="X28">
-        <v>24</v>
-      </c>
-      <c r="Y28">
-        <v>26</v>
-      </c>
-      <c r="Z28">
-        <v>65</v>
-      </c>
-      <c r="AA28">
-        <v>190</v>
-      </c>
-      <c r="AB28">
-        <v>10.5</v>
-      </c>
-      <c r="AC28">
-        <v>11</v>
-      </c>
-      <c r="AD28">
-        <v>25</v>
-      </c>
-      <c r="AE28">
-        <v>90</v>
-      </c>
-      <c r="AF28">
-        <v>11</v>
-      </c>
-      <c r="AG28">
-        <v>10.5</v>
-      </c>
-      <c r="AH28">
-        <v>23</v>
-      </c>
-      <c r="AI28">
-        <v>85</v>
-      </c>
-      <c r="AJ28">
-        <v>15.5</v>
-      </c>
-      <c r="AK28">
-        <v>16.5</v>
-      </c>
-      <c r="AL28">
-        <v>36</v>
-      </c>
-      <c r="AM28">
-        <v>110</v>
-      </c>
-      <c r="AN28">
-        <v>6.8</v>
-      </c>
-      <c r="AO28">
-        <v>90</v>
-      </c>
-      <c r="AP28">
-        <v>20</v>
-      </c>
-      <c r="AQ28">
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>2.74</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>2.74</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
         <v>22</v>
       </c>
-      <c r="AR28">
-        <v>24</v>
-      </c>
-      <c r="AS28">
-        <v>9.6</v>
-      </c>
-      <c r="AT28">
-        <v>9.6</v>
-      </c>
-      <c r="AU28">
-        <v>9.6</v>
-      </c>
-      <c r="AV28">
-        <v>20</v>
-      </c>
-      <c r="AW28">
-        <v>9</v>
-      </c>
-      <c r="AX28">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY28">
-        <v>9</v>
-      </c>
-      <c r="AZ28">
-        <v>17.5</v>
-      </c>
-      <c r="BA28">
-        <v>9</v>
-      </c>
-      <c r="BB28">
-        <v>13.5</v>
-      </c>
-      <c r="BC28">
-        <v>14</v>
-      </c>
-      <c r="BD28">
-        <v>14.5</v>
-      </c>
-      <c r="BE28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF28">
-        <v>6</v>
-      </c>
-      <c r="BG28">
-        <v>9</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>3.45</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>7.2</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>25</v>
-      </c>
-      <c r="BN28">
-        <v>4.6</v>
-      </c>
-      <c r="BO28">
-        <v>3.5</v>
-      </c>
-      <c r="BP28">
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>2.74</v>
+      </c>
+      <c r="BZ28">
         <v>11.5</v>
       </c>
-      <c r="BQ28">
-        <v>6.8</v>
-      </c>
-      <c r="BR28">
-        <v>30</v>
-      </c>
-      <c r="BS28">
-        <v>13</v>
-      </c>
-      <c r="BT28">
-        <v>11.5</v>
-      </c>
-      <c r="BU28">
-        <v>6.8</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>21</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
-      <c r="BY28">
-        <v>21</v>
-      </c>
-      <c r="BZ28">
-        <v>20</v>
-      </c>
       <c r="CA28">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="CB28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F29">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="G29">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="H29">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="J29">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="L29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M29">
         <v>1.04</v>
       </c>
       <c r="N29">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P29">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q29">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R29">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S29">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T29">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="U29">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="V29">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="W29">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="X29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y29">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Z29">
+        <v>80</v>
+      </c>
+      <c r="AA29">
+        <v>320</v>
+      </c>
+      <c r="AB29">
+        <v>10.5</v>
+      </c>
+      <c r="AC29">
+        <v>12</v>
+      </c>
+      <c r="AD29">
+        <v>48</v>
+      </c>
+      <c r="AE29">
+        <v>120</v>
+      </c>
+      <c r="AF29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG29">
+        <v>11</v>
+      </c>
+      <c r="AH29">
+        <v>27</v>
+      </c>
+      <c r="AI29">
+        <v>110</v>
+      </c>
+      <c r="AJ29">
+        <v>12.5</v>
+      </c>
+      <c r="AK29">
+        <v>14</v>
+      </c>
+      <c r="AL29">
         <v>38</v>
       </c>
-      <c r="AA29">
-        <v>100</v>
-      </c>
-      <c r="AB29">
-        <v>13</v>
-      </c>
-      <c r="AC29">
-        <v>10</v>
-      </c>
-      <c r="AD29">
-        <v>18.5</v>
-      </c>
-      <c r="AE29">
-        <v>48</v>
-      </c>
-      <c r="AF29">
-        <v>13</v>
-      </c>
-      <c r="AG29">
-        <v>10.5</v>
-      </c>
-      <c r="AH29">
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>5.7</v>
+      </c>
+      <c r="AO29">
+        <v>130</v>
+      </c>
+      <c r="AP29">
         <v>16.5</v>
       </c>
-      <c r="AI29">
-        <v>48</v>
-      </c>
-      <c r="AJ29">
-        <v>20</v>
-      </c>
-      <c r="AK29">
-        <v>17</v>
-      </c>
-      <c r="AL29">
-        <v>28</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>8</v>
-      </c>
-      <c r="AO29">
-        <v>40</v>
-      </c>
-      <c r="AP29">
-        <v>20</v>
-      </c>
       <c r="AQ29">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AR29">
         <v>34</v>
       </c>
       <c r="AS29">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AT29">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU29">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AV29">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AW29">
+        <v>40</v>
+      </c>
+      <c r="AX29">
+        <v>8.6</v>
+      </c>
+      <c r="AY29">
+        <v>9.4</v>
+      </c>
+      <c r="AZ29">
+        <v>21</v>
+      </c>
+      <c r="BA29">
+        <v>38</v>
+      </c>
+      <c r="BB29">
+        <v>10.5</v>
+      </c>
+      <c r="BC29">
+        <v>13</v>
+      </c>
+      <c r="BD29">
+        <v>22</v>
+      </c>
+      <c r="BE29">
         <v>42</v>
       </c>
-      <c r="AX29">
-        <v>11.5</v>
-      </c>
-      <c r="AY29">
-        <v>9.6</v>
-      </c>
-      <c r="AZ29">
-        <v>15</v>
-      </c>
-      <c r="BA29">
-        <v>40</v>
-      </c>
-      <c r="BB29">
-        <v>17.5</v>
-      </c>
-      <c r="BC29">
-        <v>15</v>
-      </c>
-      <c r="BD29">
-        <v>23</v>
-      </c>
-      <c r="BE29">
-        <v>55</v>
-      </c>
       <c r="BF29">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG29">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI29">
-        <v>1.48</v>
+        <v>3.4</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>6.4</v>
+        <v>2.26</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>21</v>
+        <v>2.54</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO29">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>10</v>
+        <v>2.54</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>13</v>
+        <v>2.54</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>8.199999999999999</v>
+        <v>2.54</v>
       </c>
       <c r="CB29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F30">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="G30">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>6.6</v>
+      </c>
+      <c r="J30">
+        <v>4.6</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="L30">
+        <v>1.32</v>
+      </c>
+      <c r="M30">
+        <v>1.04</v>
+      </c>
+      <c r="N30">
+        <v>5.3</v>
+      </c>
+      <c r="O30">
+        <v>1.22</v>
+      </c>
+      <c r="P30">
+        <v>2.44</v>
+      </c>
+      <c r="Q30">
+        <v>1.65</v>
+      </c>
+      <c r="R30">
+        <v>1.56</v>
+      </c>
+      <c r="S30">
+        <v>2.68</v>
+      </c>
+      <c r="T30">
+        <v>1.69</v>
+      </c>
+      <c r="U30">
+        <v>2.06</v>
+      </c>
+      <c r="V30">
+        <v>1.17</v>
+      </c>
+      <c r="W30">
+        <v>2.68</v>
+      </c>
+      <c r="X30">
+        <v>950</v>
+      </c>
+      <c r="Y30">
+        <v>26</v>
+      </c>
+      <c r="Z30">
+        <v>55</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>10.5</v>
+      </c>
+      <c r="AC30">
+        <v>11</v>
+      </c>
+      <c r="AD30">
+        <v>24</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
+        <v>10.5</v>
+      </c>
+      <c r="AG30">
         <v>13</v>
       </c>
-      <c r="I30">
+      <c r="AH30">
+        <v>20</v>
+      </c>
+      <c r="AI30">
+        <v>140</v>
+      </c>
+      <c r="AJ30">
         <v>15.5</v>
       </c>
-      <c r="J30">
+      <c r="AK30">
+        <v>16</v>
+      </c>
+      <c r="AL30">
+        <v>30</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>6.8</v>
+      </c>
+      <c r="AO30">
+        <v>1000</v>
+      </c>
+      <c r="AP30">
+        <v>14</v>
+      </c>
+      <c r="AQ30">
+        <v>6.2</v>
+      </c>
+      <c r="AR30">
+        <v>13</v>
+      </c>
+      <c r="AS30">
+        <v>34</v>
+      </c>
+      <c r="AT30">
+        <v>8.4</v>
+      </c>
+      <c r="AU30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV30">
+        <v>21</v>
+      </c>
+      <c r="AW30">
         <v>7</v>
       </c>
-      <c r="K30">
-        <v>7.8</v>
-      </c>
-      <c r="L30">
-        <v>1.25</v>
-      </c>
-      <c r="M30">
-        <v>1.02</v>
-      </c>
-      <c r="N30">
+      <c r="AX30">
+        <v>8.4</v>
+      </c>
+      <c r="AY30">
+        <v>9</v>
+      </c>
+      <c r="AZ30">
+        <v>13.5</v>
+      </c>
+      <c r="BA30">
+        <v>12.5</v>
+      </c>
+      <c r="BB30">
+        <v>12</v>
+      </c>
+      <c r="BC30">
+        <v>11.5</v>
+      </c>
+      <c r="BD30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE30">
         <v>7</v>
       </c>
-      <c r="O30">
-        <v>1.15</v>
-      </c>
-      <c r="P30">
-        <v>3</v>
-      </c>
-      <c r="Q30">
-        <v>1.47</v>
-      </c>
-      <c r="R30">
-        <v>1.81</v>
-      </c>
-      <c r="S30">
-        <v>2.18</v>
-      </c>
-      <c r="T30">
-        <v>2.04</v>
-      </c>
-      <c r="U30">
-        <v>1.89</v>
-      </c>
-      <c r="V30">
-        <v>1.07</v>
-      </c>
-      <c r="W30">
-        <v>4.7</v>
-      </c>
-      <c r="X30">
-        <v>36</v>
-      </c>
-      <c r="Y30">
-        <v>55</v>
-      </c>
-      <c r="Z30">
-        <v>150</v>
-      </c>
-      <c r="AA30">
-        <v>700</v>
-      </c>
-      <c r="AB30">
-        <v>12.5</v>
-      </c>
-      <c r="AC30">
+      <c r="BF30">
+        <v>6.2</v>
+      </c>
+      <c r="BG30">
+        <v>7</v>
+      </c>
+      <c r="BH30">
+        <v>4.1</v>
+      </c>
+      <c r="BI30">
+        <v>3.85</v>
+      </c>
+      <c r="BJ30">
+        <v>12</v>
+      </c>
+      <c r="BK30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL30">
+        <v>130</v>
+      </c>
+      <c r="BM30">
+        <v>1.01</v>
+      </c>
+      <c r="BN30">
+        <v>4.3</v>
+      </c>
+      <c r="BO30">
+        <v>3.95</v>
+      </c>
+      <c r="BP30">
+        <v>11.5</v>
+      </c>
+      <c r="BQ30">
+        <v>8.4</v>
+      </c>
+      <c r="BR30">
+        <v>26</v>
+      </c>
+      <c r="BS30">
+        <v>15.5</v>
+      </c>
+      <c r="BT30">
+        <v>12</v>
+      </c>
+      <c r="BU30">
+        <v>8.6</v>
+      </c>
+      <c r="BV30">
+        <v>60</v>
+      </c>
+      <c r="BW30">
+        <v>15.5</v>
+      </c>
+      <c r="BX30">
+        <v>60</v>
+      </c>
+      <c r="BY30">
+        <v>34</v>
+      </c>
+      <c r="BZ30">
         <v>17</v>
       </c>
-      <c r="AD30">
-        <v>50</v>
-      </c>
-      <c r="AE30">
-        <v>1000</v>
-      </c>
-      <c r="AF30">
-        <v>9</v>
-      </c>
-      <c r="AG30">
-        <v>12.5</v>
-      </c>
-      <c r="AH30">
-        <v>32</v>
-      </c>
-      <c r="AI30">
-        <v>160</v>
-      </c>
-      <c r="AJ30">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK30">
-        <v>14</v>
-      </c>
-      <c r="AL30">
-        <v>38</v>
-      </c>
-      <c r="AM30">
-        <v>160</v>
-      </c>
-      <c r="AN30">
-        <v>3.5</v>
-      </c>
-      <c r="AO30">
-        <v>220</v>
-      </c>
-      <c r="AP30">
-        <v>28</v>
-      </c>
-      <c r="AQ30">
-        <v>44</v>
-      </c>
-      <c r="AR30">
-        <v>42</v>
-      </c>
-      <c r="AS30">
-        <v>55</v>
-      </c>
-      <c r="AT30">
-        <v>11</v>
-      </c>
-      <c r="AU30">
-        <v>14.5</v>
-      </c>
-      <c r="AV30">
-        <v>42</v>
-      </c>
-      <c r="AW30">
-        <v>48</v>
-      </c>
-      <c r="AX30">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY30">
-        <v>10.5</v>
-      </c>
-      <c r="AZ30">
-        <v>27</v>
-      </c>
-      <c r="BA30">
-        <v>44</v>
-      </c>
-      <c r="BB30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC30">
-        <v>12.5</v>
-      </c>
-      <c r="BD30">
-        <v>29</v>
-      </c>
-      <c r="BE30">
-        <v>44</v>
-      </c>
-      <c r="BF30">
-        <v>3.35</v>
-      </c>
-      <c r="BG30">
-        <v>50</v>
-      </c>
-      <c r="BH30">
-        <v>5.2</v>
-      </c>
-      <c r="BI30">
-        <v>4.5</v>
-      </c>
-      <c r="BJ30">
-        <v>13</v>
-      </c>
-      <c r="BK30">
+      <c r="CA30">
         <v>10</v>
       </c>
-      <c r="BL30">
-        <v>140</v>
-      </c>
-      <c r="BM30">
-        <v>28</v>
-      </c>
-      <c r="BN30">
-        <v>4</v>
-      </c>
-      <c r="BO30">
-        <v>3.5</v>
-      </c>
-      <c r="BP30">
-        <v>7</v>
-      </c>
-      <c r="BQ30">
-        <v>5.7</v>
-      </c>
-      <c r="BR30">
-        <v>21</v>
-      </c>
-      <c r="BS30">
-        <v>7.6</v>
-      </c>
-      <c r="BT30">
-        <v>17</v>
-      </c>
-      <c r="BU30">
-        <v>7</v>
-      </c>
-      <c r="BV30">
-        <v>110</v>
-      </c>
-      <c r="BW30">
-        <v>22</v>
-      </c>
-      <c r="BX30">
-        <v>85</v>
-      </c>
-      <c r="BY30">
-        <v>19</v>
-      </c>
-      <c r="BZ30">
-        <v>8.6</v>
-      </c>
-      <c r="CA30">
-        <v>5</v>
-      </c>
       <c r="CB30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F31">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="G31">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="H31">
-        <v>4.8</v>
+        <v>2.44</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="J31">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O31">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="P31">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="Q31">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="R31">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="T31">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U31">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="V31">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="W31">
-        <v>2.26</v>
+        <v>1.46</v>
       </c>
       <c r="X31">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Y31">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Z31">
-        <v>46</v>
+        <v>970</v>
       </c>
       <c r="AA31">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC31">
         <v>10</v>
       </c>
       <c r="AD31">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AE31">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF31">
-        <v>13.5</v>
+        <v>75</v>
       </c>
       <c r="AG31">
+        <v>970</v>
+      </c>
+      <c r="AH31">
+        <v>970</v>
+      </c>
+      <c r="AI31">
+        <v>1000</v>
+      </c>
+      <c r="AJ31">
+        <v>1000</v>
+      </c>
+      <c r="AK31">
+        <v>130</v>
+      </c>
+      <c r="AL31">
+        <v>1000</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>1000</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>1.65</v>
+      </c>
+      <c r="AQ31">
+        <v>10</v>
+      </c>
+      <c r="AR31">
+        <v>1.76</v>
+      </c>
+      <c r="AS31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT31">
+        <v>1.75</v>
+      </c>
+      <c r="AU31">
+        <v>7.4</v>
+      </c>
+      <c r="AV31">
+        <v>10</v>
+      </c>
+      <c r="AW31">
+        <v>1.73</v>
+      </c>
+      <c r="AX31">
+        <v>1.71</v>
+      </c>
+      <c r="AY31">
+        <v>1.75</v>
+      </c>
+      <c r="AZ31">
+        <v>1.64</v>
+      </c>
+      <c r="BA31">
+        <v>10</v>
+      </c>
+      <c r="BB31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC31">
+        <v>11.5</v>
+      </c>
+      <c r="BD31">
+        <v>11</v>
+      </c>
+      <c r="BE31">
         <v>10.5</v>
       </c>
-      <c r="AH31">
-        <v>16</v>
-      </c>
-      <c r="AI31">
-        <v>48</v>
-      </c>
-      <c r="AJ31">
-        <v>20</v>
-      </c>
-      <c r="AK31">
-        <v>16</v>
-      </c>
-      <c r="AL31">
-        <v>27</v>
-      </c>
-      <c r="AM31">
-        <v>65</v>
-      </c>
-      <c r="AN31">
-        <v>7.4</v>
-      </c>
-      <c r="AO31">
-        <v>42</v>
-      </c>
-      <c r="AP31">
-        <v>21</v>
-      </c>
-      <c r="AQ31">
-        <v>22</v>
-      </c>
-      <c r="AR31">
-        <v>38</v>
-      </c>
-      <c r="AS31">
-        <v>38</v>
-      </c>
-      <c r="AT31">
-        <v>11.5</v>
-      </c>
-      <c r="AU31">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV31">
-        <v>17.5</v>
-      </c>
-      <c r="AW31">
-        <v>44</v>
-      </c>
-      <c r="AX31">
-        <v>12</v>
-      </c>
-      <c r="AY31">
-        <v>9.4</v>
-      </c>
-      <c r="AZ31">
-        <v>14</v>
-      </c>
-      <c r="BA31">
-        <v>42</v>
-      </c>
-      <c r="BB31">
-        <v>17.5</v>
-      </c>
-      <c r="BC31">
-        <v>14.5</v>
-      </c>
-      <c r="BD31">
-        <v>23</v>
-      </c>
-      <c r="BE31">
-        <v>50</v>
-      </c>
       <c r="BF31">
-        <v>7</v>
+        <v>1.49</v>
       </c>
       <c r="BG31">
-        <v>32</v>
+        <v>1.81</v>
       </c>
       <c r="BH31">
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>19</v>
+        <v>1.04</v>
       </c>
       <c r="BN31">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP31">
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F32">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="G32">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H32">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="I32">
-        <v>2.56</v>
+        <v>1000</v>
       </c>
       <c r="J32">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K32">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L32">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>4.6</v>
+        <v>1.08</v>
       </c>
       <c r="O32">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P32">
-        <v>2.26</v>
+        <v>1.08</v>
       </c>
       <c r="Q32">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R32">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="S32">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="T32">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.2</v>
       </c>
       <c r="W32">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F33">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="G33">
-        <v>2.92</v>
+        <v>1.81</v>
       </c>
       <c r="H33">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="I33">
-        <v>2.64</v>
+        <v>4.7</v>
       </c>
       <c r="J33">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L33">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M33">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N33">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="O33">
+        <v>1.2</v>
+      </c>
+      <c r="P33">
+        <v>2.52</v>
+      </c>
+      <c r="Q33">
+        <v>1.62</v>
+      </c>
+      <c r="R33">
+        <v>1.61</v>
+      </c>
+      <c r="S33">
+        <v>2.56</v>
+      </c>
+      <c r="T33">
+        <v>1.65</v>
+      </c>
+      <c r="U33">
+        <v>2.46</v>
+      </c>
+      <c r="V33">
         <v>1.27</v>
       </c>
-      <c r="P33">
-        <v>2.14</v>
-      </c>
-      <c r="Q33">
-        <v>1.83</v>
-      </c>
-      <c r="R33">
-        <v>1.44</v>
-      </c>
-      <c r="S33">
-        <v>3.1</v>
-      </c>
-      <c r="T33">
-        <v>1.68</v>
-      </c>
-      <c r="U33">
-        <v>2.4</v>
-      </c>
-      <c r="V33">
-        <v>1.6</v>
-      </c>
       <c r="W33">
-        <v>1.52</v>
+        <v>2.22</v>
       </c>
       <c r="X33">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Y33">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="Z33">
+        <v>42</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>13</v>
+      </c>
+      <c r="AC33">
+        <v>10</v>
+      </c>
+      <c r="AD33">
         <v>18.5</v>
       </c>
-      <c r="AA33">
-        <v>38</v>
-      </c>
-      <c r="AB33">
-        <v>13.5</v>
-      </c>
-      <c r="AC33">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD33">
-        <v>12.5</v>
-      </c>
       <c r="AE33">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="AF33">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AG33">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH33">
         <v>16.5</v>
       </c>
       <c r="AI33">
+        <v>48</v>
+      </c>
+      <c r="AJ33">
+        <v>20</v>
+      </c>
+      <c r="AK33">
+        <v>17.5</v>
+      </c>
+      <c r="AL33">
+        <v>28</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>8</v>
+      </c>
+      <c r="AO33">
+        <v>38</v>
+      </c>
+      <c r="AP33">
+        <v>20</v>
+      </c>
+      <c r="AQ33">
+        <v>20</v>
+      </c>
+      <c r="AR33">
+        <v>34</v>
+      </c>
+      <c r="AS33">
         <v>36</v>
-      </c>
-      <c r="AJ33">
-        <v>44</v>
-      </c>
-      <c r="AK33">
-        <v>30</v>
-      </c>
-      <c r="AL33">
-        <v>38</v>
-      </c>
-      <c r="AM33">
-        <v>1000</v>
-      </c>
-      <c r="AN33">
-        <v>23</v>
-      </c>
-      <c r="AO33">
-        <v>20</v>
-      </c>
-      <c r="AP33">
-        <v>15</v>
-      </c>
-      <c r="AQ33">
-        <v>11.5</v>
-      </c>
-      <c r="AR33">
-        <v>16.5</v>
-      </c>
-      <c r="AS33">
-        <v>34</v>
       </c>
       <c r="AT33">
         <v>11.5</v>
       </c>
       <c r="AU33">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV33">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AW33">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX33">
+        <v>11.5</v>
+      </c>
+      <c r="AY33">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ33">
+        <v>15</v>
+      </c>
+      <c r="BA33">
+        <v>26</v>
+      </c>
+      <c r="BB33">
         <v>17.5</v>
       </c>
-      <c r="AY33">
-        <v>11.5</v>
-      </c>
-      <c r="AZ33">
+      <c r="BC33">
+        <v>15</v>
+      </c>
+      <c r="BD33">
+        <v>19</v>
+      </c>
+      <c r="BE33">
+        <v>32</v>
+      </c>
+      <c r="BF33">
+        <v>7.4</v>
+      </c>
+      <c r="BG33">
+        <v>32</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>3.45</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>2.04</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>21</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.69</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>2.18</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>10</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.98</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>13</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
         <v>14.5</v>
       </c>
-      <c r="BA33">
-        <v>32</v>
-      </c>
-      <c r="BB33">
-        <v>38</v>
-      </c>
-      <c r="BC33">
-        <v>26</v>
-      </c>
-      <c r="BD33">
-        <v>34</v>
-      </c>
-      <c r="BE33">
-        <v>34</v>
-      </c>
-      <c r="BF33">
-        <v>20</v>
-      </c>
-      <c r="BG33">
-        <v>17.5</v>
-      </c>
-      <c r="BH33">
-        <v>4.1</v>
-      </c>
-      <c r="BI33">
-        <v>3.05</v>
-      </c>
-      <c r="BJ33">
-        <v>1000</v>
-      </c>
-      <c r="BK33">
-        <v>6.4</v>
-      </c>
-      <c r="BL33">
-        <v>1000</v>
-      </c>
-      <c r="BM33">
-        <v>24</v>
-      </c>
-      <c r="BN33">
-        <v>1000</v>
-      </c>
-      <c r="BO33">
-        <v>4.6</v>
-      </c>
-      <c r="BP33">
-        <v>1000</v>
-      </c>
-      <c r="BQ33">
-        <v>12</v>
-      </c>
-      <c r="BR33">
-        <v>1000</v>
-      </c>
-      <c r="BS33">
-        <v>12.5</v>
-      </c>
-      <c r="BT33">
-        <v>1000</v>
-      </c>
-      <c r="BU33">
-        <v>4.5</v>
-      </c>
-      <c r="BV33">
-        <v>1000</v>
-      </c>
-      <c r="BW33">
-        <v>11.5</v>
-      </c>
-      <c r="BX33">
-        <v>1000</v>
-      </c>
-      <c r="BY33">
-        <v>12.5</v>
-      </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F34">
         <v>3.8</v>
@@ -8906,7 +8903,7 @@
         <v>1.33</v>
       </c>
       <c r="M34">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N34">
         <v>5.3</v>
@@ -8915,13 +8912,13 @@
         <v>1.22</v>
       </c>
       <c r="P34">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q34">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R34">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S34">
         <v>2.68</v>
@@ -8930,7 +8927,7 @@
         <v>1.62</v>
       </c>
       <c r="U34">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
         <v>1.96</v>
@@ -8942,7 +8939,7 @@
         <v>21</v>
       </c>
       <c r="Y34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z34">
         <v>14.5</v>
@@ -8960,13 +8957,13 @@
         <v>11</v>
       </c>
       <c r="AE34">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF34">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG34">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH34">
         <v>15.5</v>
@@ -8981,40 +8978,40 @@
         <v>38</v>
       </c>
       <c r="AL34">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AM34">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN34">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AO34">
         <v>10.5</v>
       </c>
       <c r="AP34">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ34">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR34">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS34">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AT34">
         <v>18</v>
       </c>
       <c r="AU34">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV34">
         <v>10</v>
       </c>
       <c r="AW34">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX34">
         <v>28</v>
@@ -9026,10 +9023,10 @@
         <v>14.5</v>
       </c>
       <c r="BA34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB34">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="BC34">
         <v>34</v>
@@ -9038,76 +9035,76 @@
         <v>36</v>
       </c>
       <c r="BE34">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF34">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BG34">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH34">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BI34">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BJ34">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK34">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL34">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM34">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BN34">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO34">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP34">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BR34">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS34">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BT34">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BU34">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV34">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW34">
-        <v>11.5</v>
+        <v>2.3</v>
       </c>
       <c r="BX34">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ34">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA34">
-        <v>7.8</v>
+        <v>2.46</v>
       </c>
       <c r="CB34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9115,31 +9112,31 @@
         <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F35">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="G35">
         <v>600</v>
       </c>
       <c r="H35">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="I35">
         <v>870</v>
       </c>
       <c r="J35">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9175,10 +9172,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9349,7 +9346,7 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9357,58 +9354,58 @@
         <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F36">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="G36">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H36">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I36">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J36">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="K36">
-        <v>500</v>
+        <v>3.75</v>
       </c>
       <c r="L36">
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N36">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O36">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P36">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Q36">
         <v>2.02</v>
       </c>
       <c r="R36">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="S36">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -9420,7 +9417,7 @@
         <v>1.29</v>
       </c>
       <c r="W36">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9591,7 +9588,7 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -544,7 +544,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 07:13:15</t>
+    <t>2026-09-16 09:27:27</t>
   </si>
 </sst>
 </file>
@@ -1141,22 +1141,22 @@
         <v>1.43</v>
       </c>
       <c r="G2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>9.4</v>
       </c>
       <c r="J2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M2">
         <v>1.02</v>
@@ -1171,133 +1171,133 @@
         <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
         <v>1.72</v>
       </c>
       <c r="S2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1395,22 +1395,22 @@
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.69</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N3">
         <v>2.32</v>
       </c>
       <c r="O3">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="P3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1422,22 +1422,22 @@
         <v>7.2</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="U3">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
         <v>1.24</v>
       </c>
       <c r="W3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y3">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
         <v>36</v>
@@ -1446,13 +1446,13 @@
         <v>170</v>
       </c>
       <c r="AB3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AE3">
         <v>120</v>
@@ -1461,10 +1461,10 @@
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI3">
         <v>160</v>
@@ -1491,13 +1491,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AT3">
         <v>5.4</v>
@@ -1509,97 +1509,97 @@
         <v>21</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AX3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="BB3">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BC3">
         <v>29</v>
       </c>
       <c r="BD3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BE3">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BF3">
         <v>30</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>176</v>
@@ -1622,22 +1622,22 @@
         <v>143</v>
       </c>
       <c r="F4">
+        <v>4.5</v>
+      </c>
+      <c r="G4">
         <v>4.8</v>
       </c>
-      <c r="G4">
-        <v>5.2</v>
-      </c>
       <c r="H4">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="J4">
+        <v>3.75</v>
+      </c>
+      <c r="K4">
         <v>3.85</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
       </c>
       <c r="L4">
         <v>1.41</v>
@@ -1646,202 +1646,202 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
         <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="W4">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X4">
         <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>11.5</v>
       </c>
       <c r="AA4">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
       </c>
       <c r="AE4">
+        <v>25</v>
+      </c>
+      <c r="AF4">
+        <v>44</v>
+      </c>
+      <c r="AG4">
+        <v>18</v>
+      </c>
+      <c r="AH4">
         <v>19.5</v>
       </c>
-      <c r="AF4">
-        <v>40</v>
-      </c>
-      <c r="AG4">
-        <v>970</v>
-      </c>
-      <c r="AH4">
-        <v>970</v>
-      </c>
       <c r="AI4">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK4">
+        <v>60</v>
+      </c>
+      <c r="AL4">
         <v>70</v>
       </c>
-      <c r="AL4">
-        <v>75</v>
-      </c>
       <c r="AM4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN4">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO4">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AP4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT4">
         <v>15</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AY4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4">
         <v>17</v>
       </c>
       <c r="BA4">
+        <v>32</v>
+      </c>
+      <c r="BB4">
+        <v>13.5</v>
+      </c>
+      <c r="BC4">
+        <v>50</v>
+      </c>
+      <c r="BD4">
+        <v>55</v>
+      </c>
+      <c r="BE4">
+        <v>13.5</v>
+      </c>
+      <c r="BF4">
+        <v>46</v>
+      </c>
+      <c r="BG4">
+        <v>11.5</v>
+      </c>
+      <c r="BH4">
+        <v>3.9</v>
+      </c>
+      <c r="BI4">
+        <v>2.84</v>
+      </c>
+      <c r="BJ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4">
+        <v>7.6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>9.6</v>
+      </c>
+      <c r="BN4">
+        <v>7.8</v>
+      </c>
+      <c r="BO4">
+        <v>6.2</v>
+      </c>
+      <c r="BP4">
+        <v>46</v>
+      </c>
+      <c r="BQ4">
+        <v>8</v>
+      </c>
+      <c r="BR4">
+        <v>60</v>
+      </c>
+      <c r="BS4">
+        <v>8.6</v>
+      </c>
+      <c r="BT4">
+        <v>4.6</v>
+      </c>
+      <c r="BU4">
+        <v>4.1</v>
+      </c>
+      <c r="BV4">
+        <v>13.5</v>
+      </c>
+      <c r="BW4">
+        <v>5.8</v>
+      </c>
+      <c r="BX4">
+        <v>28</v>
+      </c>
+      <c r="BY4">
+        <v>7.4</v>
+      </c>
+      <c r="BZ4">
+        <v>24</v>
+      </c>
+      <c r="CA4">
         <v>7.2</v>
-      </c>
-      <c r="BB4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC4">
-        <v>4.9</v>
-      </c>
-      <c r="BD4">
-        <v>8</v>
-      </c>
-      <c r="BE4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF4">
-        <v>8</v>
-      </c>
-      <c r="BG4">
-        <v>10.5</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.04</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.04</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>6</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.04</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.04</v>
-      </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
-        <v>1.04</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>1.04</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>1.04</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>176</v>
@@ -1864,58 +1864,58 @@
         <v>144</v>
       </c>
       <c r="F5">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H5">
         <v>4.2</v>
       </c>
       <c r="I5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K5">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
+        <v>1.62</v>
+      </c>
+      <c r="M5">
+        <v>1.12</v>
+      </c>
+      <c r="N5">
+        <v>2.2</v>
+      </c>
+      <c r="O5">
         <v>1.6</v>
-      </c>
-      <c r="M5">
-        <v>1.11</v>
-      </c>
-      <c r="N5">
-        <v>2.18</v>
-      </c>
-      <c r="O5">
-        <v>1.63</v>
       </c>
       <c r="P5">
         <v>1.38</v>
       </c>
       <c r="Q5">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="R5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="S5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T5">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="X5">
         <v>970</v>
@@ -1972,64 +1972,64 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ5">
-        <v>1.71</v>
+        <v>7</v>
       </c>
       <c r="AR5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AS5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AT5">
         <v>4.7</v>
       </c>
       <c r="AU5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV5">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AW5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AX5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY5">
-        <v>1.73</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BA5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BB5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BC5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BD5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BE5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BF5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BG5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -2047,7 +2047,7 @@
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -2106,166 +2106,166 @@
         <v>145</v>
       </c>
       <c r="F6">
-        <v>1.28</v>
+        <v>2.56</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H6">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>2.88</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q6">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="R6">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="S6">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA6">
         <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD6">
         <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2348,166 +2348,166 @@
         <v>146</v>
       </c>
       <c r="F7">
-        <v>1.17</v>
+        <v>2.02</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>2.24</v>
       </c>
       <c r="H7">
-        <v>1.17</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q7">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>2.64</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD7">
         <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2590,43 +2590,43 @@
         <v>147</v>
       </c>
       <c r="F8">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="H8">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>1.65</v>
+        <v>2.96</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P8">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="Q8">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S8">
         <v>2.8</v>
@@ -2638,10 +2638,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2698,52 +2698,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2832,166 +2832,166 @@
         <v>148</v>
       </c>
       <c r="F9">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>9.4</v>
       </c>
       <c r="H9">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="I9">
         <v>1.62</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.26</v>
+        <v>1.81</v>
       </c>
       <c r="Q9">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="R9">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
         <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3074,22 +3074,22 @@
         <v>149</v>
       </c>
       <c r="F10">
+        <v>1.25</v>
+      </c>
+      <c r="G10">
+        <v>1.33</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>15.5</v>
+      </c>
+      <c r="J10">
         <v>1.12</v>
       </c>
-      <c r="G10">
-        <v>600</v>
-      </c>
-      <c r="H10">
-        <v>1.04</v>
-      </c>
-      <c r="I10">
-        <v>870</v>
-      </c>
-      <c r="J10">
-        <v>1.13</v>
-      </c>
       <c r="K10">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3098,91 +3098,91 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="O10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="R10">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>1.06</v>
+        <v>1.75</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>3.9</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
         <v>1.03</v>
@@ -3194,43 +3194,43 @@
         <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
         <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
         <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
         <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BG10">
         <v>1.01</v>
@@ -3316,10 +3316,10 @@
         <v>150</v>
       </c>
       <c r="F11">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>1.42</v>
@@ -3334,10 +3334,10 @@
         <v>5.5</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
         <v>5.6</v>
@@ -3349,19 +3349,19 @@
         <v>2.54</v>
       </c>
       <c r="Q11">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R11">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T11">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U11">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
         <v>3.25</v>
@@ -3370,16 +3370,16 @@
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="Y11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Z11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AB11">
         <v>34</v>
@@ -3388,13 +3388,13 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE11">
         <v>14.5</v>
       </c>
       <c r="AF11">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AG11">
         <v>32</v>
@@ -3403,22 +3403,22 @@
         <v>25</v>
       </c>
       <c r="AI11">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AO11">
         <v>5.4</v>
@@ -3427,52 +3427,52 @@
         <v>21</v>
       </c>
       <c r="AQ11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR11">
         <v>8.4</v>
       </c>
       <c r="AS11">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT11">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AU11">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV11">
         <v>9.199999999999999</v>
       </c>
       <c r="AW11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ11">
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BB11">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BC11">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD11">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE11">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11">
         <v>4.7</v>
@@ -3481,13 +3481,13 @@
         <v>4.9</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3499,13 +3499,13 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BR11">
         <v>1000</v>
@@ -3517,19 +3517,19 @@
         <v>4.5</v>
       </c>
       <c r="BU11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
@@ -3558,7 +3558,7 @@
         <v>151</v>
       </c>
       <c r="F12">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G12">
         <v>3.25</v>
@@ -3576,7 +3576,7 @@
         <v>3.8</v>
       </c>
       <c r="L12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M12">
         <v>1.05</v>
@@ -3585,10 +3585,10 @@
         <v>4.9</v>
       </c>
       <c r="O12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
         <v>1.73</v>
@@ -3603,7 +3603,7 @@
         <v>1.61</v>
       </c>
       <c r="U12">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V12">
         <v>1.72</v>
@@ -3618,7 +3618,7 @@
         <v>13</v>
       </c>
       <c r="Z12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA12">
         <v>32</v>
@@ -3627,13 +3627,13 @@
         <v>16</v>
       </c>
       <c r="AC12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12">
         <v>11.5</v>
       </c>
       <c r="AE12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF12">
         <v>25</v>
@@ -3645,25 +3645,25 @@
         <v>15</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ12">
         <v>55</v>
       </c>
       <c r="AK12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL12">
         <v>38</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO12">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
@@ -3672,7 +3672,7 @@
         <v>12</v>
       </c>
       <c r="AR12">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS12">
         <v>28</v>
@@ -3681,13 +3681,13 @@
         <v>14.5</v>
       </c>
       <c r="AU12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AX12">
         <v>22</v>
@@ -3702,28 +3702,28 @@
         <v>27</v>
       </c>
       <c r="BB12">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BC12">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BD12">
         <v>32</v>
       </c>
       <c r="BE12">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF12">
         <v>21</v>
       </c>
       <c r="BG12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH12">
         <v>4</v>
       </c>
       <c r="BI12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ12">
         <v>10.5</v>
@@ -3735,10 +3735,10 @@
         <v>110</v>
       </c>
       <c r="BM12">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="BN12">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO12">
         <v>5.8</v>
@@ -3747,16 +3747,16 @@
         <v>27</v>
       </c>
       <c r="BQ12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BR12">
         <v>36</v>
       </c>
       <c r="BS12">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BT12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU12">
         <v>5</v>
@@ -3771,13 +3771,13 @@
         <v>32</v>
       </c>
       <c r="BY12">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BZ12">
         <v>23</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="CB12" t="s">
         <v>176</v>
@@ -3806,13 +3806,13 @@
         <v>1.25</v>
       </c>
       <c r="H13">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="I13">
         <v>870</v>
       </c>
       <c r="J13">
-        <v>8.6</v>
+        <v>1.12</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3824,22 +3824,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.75</v>
+        <v>2.68</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>2.68</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R13">
         <v>1.9</v>
       </c>
       <c r="S13">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3851,7 +3851,7 @@
         <v>1.04</v>
       </c>
       <c r="W13">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4042,46 +4042,46 @@
         <v>153</v>
       </c>
       <c r="F14">
-        <v>1.35</v>
+        <v>2.48</v>
       </c>
       <c r="G14">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="H14">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="I14">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R14">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S14">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4093,7 +4093,7 @@
         <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4168,7 +4168,7 @@
         <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
         <v>1.03</v>
@@ -4180,7 +4180,7 @@
         <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
         <v>1.03</v>
@@ -4195,7 +4195,7 @@
         <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4287,19 +4287,19 @@
         <v>2.16</v>
       </c>
       <c r="G15">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H15">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="I15">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="J15">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4308,10 +4308,10 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="O15">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
         <v>2.2</v>
@@ -4323,7 +4323,7 @@
         <v>1.43</v>
       </c>
       <c r="S15">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4335,7 +4335,7 @@
         <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4392,49 +4392,49 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
         <v>1.03</v>
@@ -4526,22 +4526,22 @@
         <v>155</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="G16">
-        <v>970</v>
+        <v>3.25</v>
       </c>
       <c r="H16">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="I16">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K16">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4550,22 +4550,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O16">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
         <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="R16">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="S16">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4574,11 +4574,11 @@
         <v>1.01</v>
       </c>
       <c r="V16">
+        <v>1.52</v>
+      </c>
+      <c r="W16">
         <v>1.45</v>
       </c>
-      <c r="W16">
-        <v>1.01</v>
-      </c>
       <c r="X16">
         <v>1000</v>
       </c>
@@ -4634,49 +4634,49 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
         <v>1.03</v>
@@ -4768,7 +4768,7 @@
         <v>156</v>
       </c>
       <c r="F17">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G17">
         <v>3.45</v>
@@ -4777,10 +4777,10 @@
         <v>2.1</v>
       </c>
       <c r="I17">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="J17">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="K17">
         <v>6.4</v>
@@ -4798,13 +4798,13 @@
         <v>1.11</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q17">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="R17">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="S17">
         <v>2.04</v>
@@ -4816,7 +4816,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
         <v>1.4</v>
@@ -5052,13 +5052,13 @@
         <v>4.5</v>
       </c>
       <c r="T18">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U18">
         <v>1.8</v>
       </c>
       <c r="V18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W18">
         <v>2.36</v>
@@ -5073,7 +5073,7 @@
         <v>48</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -5088,7 +5088,7 @@
         <v>110</v>
       </c>
       <c r="AF18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG18">
         <v>10.5</v>
@@ -5109,7 +5109,7 @@
         <v>48</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN18">
         <v>14</v>
@@ -5124,7 +5124,7 @@
         <v>15</v>
       </c>
       <c r="AR18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AS18">
         <v>44</v>
@@ -5139,19 +5139,19 @@
         <v>22</v>
       </c>
       <c r="AW18">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AX18">
         <v>8.4</v>
       </c>
       <c r="AY18">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA18">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BB18">
         <v>15.5</v>
@@ -5172,64 +5172,64 @@
         <v>42</v>
       </c>
       <c r="BH18">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BI18">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK18">
-        <v>2.64</v>
+        <v>10</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM18">
-        <v>2.96</v>
+        <v>34</v>
       </c>
       <c r="BN18">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BO18">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18">
-        <v>2.68</v>
+        <v>11</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS18">
-        <v>2.96</v>
+        <v>10</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU18">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW18">
-        <v>2.96</v>
+        <v>11.5</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY18">
-        <v>2.96</v>
+        <v>18</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA18">
-        <v>2.96</v>
+        <v>10</v>
       </c>
       <c r="CB18" t="s">
         <v>176</v>
@@ -5252,22 +5252,22 @@
         <v>158</v>
       </c>
       <c r="F19">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="G19">
-        <v>600</v>
+        <v>12.5</v>
       </c>
       <c r="H19">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="I19">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J19">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K19">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5276,34 +5276,34 @@
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O19">
         <v>1.47</v>
       </c>
       <c r="P19">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R19">
         <v>1.2</v>
       </c>
       <c r="S19">
-        <v>2.36</v>
+        <v>4.1</v>
       </c>
       <c r="T19">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="U19">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V19">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
         <v>970</v>
@@ -5324,7 +5324,7 @@
         <v>970</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE19">
         <v>1000</v>
@@ -5357,97 +5357,97 @@
         <v>1000</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP19">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ19">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AR19">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AS19">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AT19">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AU19">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AV19">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AW19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AX19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AY19">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AZ19">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BA19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BB19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BC19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BD19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BE19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BF19">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BG19">
-        <v>1.56</v>
+        <v>7.8</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BT19">
         <v>1000</v>
@@ -5459,19 +5459,19 @@
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CB19" t="s">
         <v>176</v>
@@ -5494,133 +5494,133 @@
         <v>159</v>
       </c>
       <c r="F20">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="G20">
-        <v>110</v>
+        <v>5.8</v>
       </c>
       <c r="H20">
-        <v>1.1</v>
+        <v>1.95</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>2.14</v>
       </c>
       <c r="J20">
+        <v>2.98</v>
+      </c>
+      <c r="K20">
+        <v>3.4</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.11</v>
+      </c>
+      <c r="N20">
+        <v>2.5</v>
+      </c>
+      <c r="O20">
+        <v>1.56</v>
+      </c>
+      <c r="P20">
+        <v>1.49</v>
+      </c>
+      <c r="Q20">
+        <v>2.68</v>
+      </c>
+      <c r="R20">
+        <v>1.17</v>
+      </c>
+      <c r="S20">
+        <v>5.1</v>
+      </c>
+      <c r="T20">
+        <v>2.24</v>
+      </c>
+      <c r="U20">
+        <v>1.69</v>
+      </c>
+      <c r="V20">
         <v>1.88</v>
       </c>
-      <c r="K20">
-        <v>950</v>
-      </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.09</v>
-      </c>
-      <c r="N20">
-        <v>2.3</v>
-      </c>
-      <c r="O20">
-        <v>1.1</v>
-      </c>
-      <c r="P20">
-        <v>1.08</v>
-      </c>
-      <c r="Q20">
-        <v>1.56</v>
-      </c>
-      <c r="R20">
-        <v>1.08</v>
-      </c>
-      <c r="S20">
-        <v>1.01</v>
-      </c>
-      <c r="T20">
-        <v>1.01</v>
-      </c>
-      <c r="U20">
-        <v>1.01</v>
-      </c>
-      <c r="V20">
-        <v>1.76</v>
-      </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW20">
         <v>1.03</v>
@@ -5629,10 +5629,10 @@
         <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA20">
         <v>1.03</v>
@@ -5650,10 +5650,10 @@
         <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV20">
         <v>1000</v>
@@ -5736,22 +5736,22 @@
         <v>160</v>
       </c>
       <c r="F21">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G21">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H21">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="I21">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J21">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5760,34 +5760,34 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O21">
         <v>1.04</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q21">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="R21">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="S21">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="T21">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
         <v>2</v>
       </c>
       <c r="W21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5978,169 +5978,169 @@
         <v>161</v>
       </c>
       <c r="F22">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G22">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H22">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>870</v>
+        <v>17.5</v>
       </c>
       <c r="J22">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="L22">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N22">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O22">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P22">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R22">
         <v>1.22</v>
       </c>
       <c r="S22">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="V22">
         <v>1.06</v>
       </c>
       <c r="W22">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA22">
         <v>1000</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO22">
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="AQ22">
-        <v>1.02</v>
+        <v>3.85</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS22">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="AT22">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="AU22">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="AV22">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX22">
-        <v>1.02</v>
+        <v>2.82</v>
       </c>
       <c r="AY22">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="AZ22">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB22">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="BC22">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="BD22">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI22">
         <v>1.02</v>
@@ -6149,55 +6149,55 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="CB22" t="s">
         <v>176</v>
@@ -6220,7 +6220,7 @@
         <v>162</v>
       </c>
       <c r="F23">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="G23">
         <v>5.1</v>
@@ -6235,7 +6235,7 @@
         <v>3.55</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6256,10 +6256,10 @@
         <v>1.43</v>
       </c>
       <c r="R23">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S23">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6462,19 +6462,19 @@
         <v>163</v>
       </c>
       <c r="F24">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G24">
         <v>600</v>
       </c>
       <c r="H24">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I24">
         <v>870</v>
       </c>
       <c r="J24">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6746,10 +6746,10 @@
         <v>3.1</v>
       </c>
       <c r="T25">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U25">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V25">
         <v>1.6</v>
@@ -6764,7 +6764,7 @@
         <v>12.5</v>
       </c>
       <c r="Z25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA25">
         <v>38</v>
@@ -6773,25 +6773,25 @@
         <v>13.5</v>
       </c>
       <c r="AC25">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25">
         <v>12.5</v>
       </c>
       <c r="AE25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF25">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG25">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH25">
         <v>16.5</v>
       </c>
       <c r="AI25">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ25">
         <v>44</v>
@@ -6800,25 +6800,25 @@
         <v>30</v>
       </c>
       <c r="AL25">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM25">
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO25">
         <v>20</v>
       </c>
       <c r="AP25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25">
         <v>11.5</v>
       </c>
       <c r="AR25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS25">
         <v>34</v>
@@ -6833,7 +6833,7 @@
         <v>11</v>
       </c>
       <c r="AW25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX25">
         <v>17.5</v>
@@ -6860,10 +6860,10 @@
         <v>34</v>
       </c>
       <c r="BF25">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BG25">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH25">
         <v>4.1</v>
@@ -6911,7 +6911,7 @@
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX25">
         <v>1000</v>
@@ -6961,10 +6961,10 @@
         <v>3.65</v>
       </c>
       <c r="K26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L26">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M26">
         <v>1.05</v>
@@ -6973,22 +6973,22 @@
         <v>4.7</v>
       </c>
       <c r="O26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P26">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R26">
         <v>1.5</v>
       </c>
       <c r="S26">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T26">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U26">
         <v>2.5</v>
@@ -7012,7 +7012,7 @@
         <v>34</v>
       </c>
       <c r="AB26">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC26">
         <v>8.4</v>
@@ -7027,7 +7027,7 @@
         <v>22</v>
       </c>
       <c r="AG26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH26">
         <v>14</v>
@@ -7036,7 +7036,7 @@
         <v>34</v>
       </c>
       <c r="AJ26">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK26">
         <v>30</v>
@@ -7048,13 +7048,13 @@
         <v>70</v>
       </c>
       <c r="AN26">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO26">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP26">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ26">
         <v>12</v>
@@ -7081,13 +7081,13 @@
         <v>20</v>
       </c>
       <c r="AY26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ26">
         <v>13</v>
       </c>
       <c r="BA26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB26">
         <v>42</v>
@@ -7099,7 +7099,7 @@
         <v>32</v>
       </c>
       <c r="BE26">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF26">
         <v>20</v>
@@ -7117,13 +7117,13 @@
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BN26">
         <v>1000</v>
@@ -7135,37 +7135,37 @@
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>2.36</v>
+        <v>9.6</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>2.36</v>
+        <v>12.5</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU26">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>2.36</v>
+        <v>12</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="CB26" t="s">
         <v>176</v>
@@ -7191,10 +7191,10 @@
         <v>1.78</v>
       </c>
       <c r="G27">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H27">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -7212,34 +7212,34 @@
         <v>1.04</v>
       </c>
       <c r="N27">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P27">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q27">
         <v>1.59</v>
       </c>
       <c r="R27">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S27">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T27">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U27">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
         <v>1.25</v>
       </c>
       <c r="W27">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X27">
         <v>24</v>
@@ -7248,13 +7248,13 @@
         <v>25</v>
       </c>
       <c r="Z27">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB27">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -7272,37 +7272,37 @@
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI27">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ27">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK27">
         <v>16</v>
       </c>
       <c r="AL27">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN27">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO27">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AP27">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AQ27">
         <v>22</v>
       </c>
       <c r="AR27">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AS27">
         <v>38</v>
@@ -7314,10 +7314,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV27">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW27">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AX27">
         <v>12</v>
@@ -7341,7 +7341,7 @@
         <v>23</v>
       </c>
       <c r="BE27">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF27">
         <v>7</v>
@@ -7350,16 +7350,16 @@
         <v>32</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI27">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7368,7 +7368,7 @@
         <v>19</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO27">
         <v>3.9</v>
@@ -7377,19 +7377,19 @@
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>2.34</v>
+        <v>9.6</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BV27">
         <v>1000</v>
@@ -7430,22 +7430,22 @@
         <v>167</v>
       </c>
       <c r="F28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H28">
         <v>13.5</v>
       </c>
       <c r="I28">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J28">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="K28">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>1.25</v>
@@ -7454,94 +7454,94 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O28">
         <v>1.15</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q28">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R28">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S28">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T28">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U28">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W28">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y28">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA28">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="AB28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC28">
         <v>17.5</v>
       </c>
       <c r="AD28">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE28">
         <v>1000</v>
       </c>
       <c r="AF28">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AG28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH28">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ28">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AK28">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN28">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP28">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AQ28">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AR28">
         <v>42</v>
@@ -7550,25 +7550,25 @@
         <v>55</v>
       </c>
       <c r="AT28">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU28">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV28">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AW28">
         <v>48</v>
       </c>
       <c r="AX28">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY28">
         <v>11</v>
       </c>
       <c r="AZ28">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BA28">
         <v>44</v>
@@ -7586,7 +7586,7 @@
         <v>44</v>
       </c>
       <c r="BF28">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BG28">
         <v>50</v>
@@ -7601,13 +7601,13 @@
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.74</v>
+        <v>28</v>
       </c>
       <c r="BN28">
         <v>4.4</v>
@@ -7616,7 +7616,7 @@
         <v>3.2</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ28">
         <v>5</v>
@@ -7625,13 +7625,13 @@
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7643,13 +7643,13 @@
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.74</v>
+        <v>19</v>
       </c>
       <c r="BZ28">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB28" t="s">
         <v>176</v>
@@ -7675,7 +7675,7 @@
         <v>1.43</v>
       </c>
       <c r="G29">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H29">
         <v>8</v>
@@ -7684,7 +7684,7 @@
         <v>8.6</v>
       </c>
       <c r="J29">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K29">
         <v>5.5</v>
@@ -7699,43 +7699,43 @@
         <v>5.3</v>
       </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P29">
         <v>2.48</v>
       </c>
       <c r="Q29">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R29">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S29">
         <v>2.66</v>
       </c>
       <c r="T29">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V29">
         <v>1.13</v>
       </c>
       <c r="W29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X29">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z29">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA29">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
         <v>10.5</v>
@@ -7744,49 +7744,49 @@
         <v>12</v>
       </c>
       <c r="AD29">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AE29">
         <v>120</v>
       </c>
       <c r="AF29">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG29">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH29">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK29">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL29">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN29">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO29">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP29">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AQ29">
         <v>26</v>
       </c>
       <c r="AR29">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AS29">
         <v>50</v>
@@ -7795,7 +7795,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV29">
         <v>26</v>
@@ -7816,13 +7816,13 @@
         <v>38</v>
       </c>
       <c r="BB29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC29">
         <v>13</v>
       </c>
       <c r="BD29">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE29">
         <v>42</v>
@@ -7834,64 +7834,64 @@
         <v>42</v>
       </c>
       <c r="BH29">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI29">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK29">
-        <v>2.26</v>
+        <v>9.6</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM29">
-        <v>2.54</v>
+        <v>27</v>
       </c>
       <c r="BN29">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO29">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ29">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS29">
-        <v>2.54</v>
+        <v>10</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU29">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW29">
-        <v>2.54</v>
+        <v>17</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY29">
         <v>17</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA29">
-        <v>2.54</v>
+        <v>7</v>
       </c>
       <c r="CB29" t="s">
         <v>176</v>
@@ -7920,7 +7920,7 @@
         <v>1.59</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I30">
         <v>6.6</v>
@@ -7947,7 +7947,7 @@
         <v>2.44</v>
       </c>
       <c r="Q30">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R30">
         <v>1.56</v>
@@ -7956,10 +7956,10 @@
         <v>2.68</v>
       </c>
       <c r="T30">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="U30">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
         <v>1.17</v>
@@ -7968,7 +7968,7 @@
         <v>2.68</v>
       </c>
       <c r="X30">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Y30">
         <v>26</v>
@@ -7977,7 +7977,7 @@
         <v>55</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB30">
         <v>10.5</v>
@@ -7989,52 +7989,52 @@
         <v>24</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF30">
         <v>10.5</v>
       </c>
       <c r="AG30">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH30">
         <v>20</v>
       </c>
       <c r="AI30">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AJ30">
+        <v>15</v>
+      </c>
+      <c r="AK30">
         <v>15.5</v>
       </c>
-      <c r="AK30">
-        <v>16</v>
-      </c>
       <c r="AL30">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN30">
         <v>6.8</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP30">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AQ30">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="AR30">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AS30">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AT30">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU30">
         <v>9.800000000000001</v>
@@ -8043,97 +8043,97 @@
         <v>21</v>
       </c>
       <c r="AW30">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AX30">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY30">
         <v>9</v>
       </c>
       <c r="AZ30">
+        <v>17.5</v>
+      </c>
+      <c r="BA30">
+        <v>11</v>
+      </c>
+      <c r="BB30">
         <v>13.5</v>
       </c>
-      <c r="BA30">
-        <v>12.5</v>
-      </c>
-      <c r="BB30">
-        <v>12</v>
-      </c>
       <c r="BC30">
+        <v>14</v>
+      </c>
+      <c r="BD30">
+        <v>9.4</v>
+      </c>
+      <c r="BE30">
         <v>11.5</v>
       </c>
-      <c r="BD30">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE30">
+      <c r="BF30">
+        <v>6</v>
+      </c>
+      <c r="BG30">
+        <v>11</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>3.45</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
         <v>7</v>
       </c>
-      <c r="BF30">
-        <v>6.2</v>
-      </c>
-      <c r="BG30">
-        <v>7</v>
-      </c>
-      <c r="BH30">
-        <v>4.1</v>
-      </c>
-      <c r="BI30">
-        <v>3.85</v>
-      </c>
-      <c r="BJ30">
-        <v>12</v>
-      </c>
-      <c r="BK30">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BL30">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BN30">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BO30">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP30">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR30">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BT30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
         <v>15.5</v>
       </c>
       <c r="BX30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="BZ30">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="CB30" t="s">
         <v>176</v>
@@ -8156,22 +8156,22 @@
         <v>170</v>
       </c>
       <c r="F31">
+        <v>3.05</v>
+      </c>
+      <c r="G31">
         <v>3.1</v>
-      </c>
-      <c r="G31">
-        <v>3.15</v>
       </c>
       <c r="H31">
         <v>2.44</v>
       </c>
       <c r="I31">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J31">
         <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8180,22 +8180,22 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O31">
         <v>1.3</v>
       </c>
       <c r="P31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q31">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R31">
         <v>1.4</v>
       </c>
       <c r="S31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T31">
         <v>1.74</v>
@@ -8204,79 +8204,79 @@
         <v>2.26</v>
       </c>
       <c r="V31">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W31">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X31">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y31">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z31">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB31">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="AE31">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="AF31">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="AG31">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH31">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK31">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP31">
-        <v>1.65</v>
+        <v>13.5</v>
       </c>
       <c r="AQ31">
         <v>10</v>
       </c>
       <c r="AR31">
-        <v>1.76</v>
+        <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT31">
-        <v>1.75</v>
+        <v>11.5</v>
       </c>
       <c r="AU31">
         <v>7.4</v>
@@ -8285,37 +8285,37 @@
         <v>10</v>
       </c>
       <c r="AW31">
-        <v>1.73</v>
+        <v>22</v>
       </c>
       <c r="AX31">
-        <v>1.71</v>
+        <v>19</v>
       </c>
       <c r="AY31">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="AZ31">
-        <v>1.64</v>
+        <v>14.5</v>
       </c>
       <c r="BA31">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BB31">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC31">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BD31">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BF31">
-        <v>1.49</v>
+        <v>23</v>
       </c>
       <c r="BG31">
-        <v>1.81</v>
+        <v>16</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8398,46 +8398,46 @@
         <v>171</v>
       </c>
       <c r="F32">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="G32">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H32">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="I32">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J32">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="K32">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L32">
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N32">
-        <v>1.08</v>
+        <v>2.42</v>
       </c>
       <c r="O32">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P32">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="Q32">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="R32">
         <v>1.08</v>
       </c>
       <c r="S32">
-        <v>1.54</v>
+        <v>2.86</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8446,10 +8446,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8560,10 +8560,10 @@
         <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI32">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
@@ -8640,22 +8640,22 @@
         <v>172</v>
       </c>
       <c r="F33">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="G33">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="H33">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I33">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J33">
         <v>4.2</v>
       </c>
       <c r="K33">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L33">
         <v>1.32</v>
@@ -8664,7 +8664,7 @@
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O33">
         <v>1.2</v>
@@ -8679,61 +8679,61 @@
         <v>1.61</v>
       </c>
       <c r="S33">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U33">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V33">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W33">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="X33">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y33">
         <v>22</v>
       </c>
       <c r="Z33">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB33">
         <v>13</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD33">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE33">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AF33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG33">
         <v>10.5</v>
       </c>
       <c r="AH33">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI33">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL33">
         <v>28</v>
@@ -8742,7 +8742,7 @@
         <v>1000</v>
       </c>
       <c r="AN33">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO33">
         <v>38</v>
@@ -8754,7 +8754,7 @@
         <v>20</v>
       </c>
       <c r="AR33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS33">
         <v>36</v>
@@ -8763,43 +8763,43 @@
         <v>11.5</v>
       </c>
       <c r="AU33">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV33">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW33">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AX33">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY33">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ33">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA33">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BB33">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC33">
         <v>15</v>
       </c>
       <c r="BD33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BE33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF33">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG33">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8811,7 +8811,7 @@
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BL33">
         <v>1000</v>
@@ -8820,16 +8820,16 @@
         <v>21</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO33">
-        <v>1.69</v>
+        <v>3.5</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="BR33">
         <v>1000</v>
@@ -8841,13 +8841,13 @@
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.98</v>
+        <v>5.2</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX33">
         <v>1000</v>
@@ -8888,10 +8888,10 @@
         <v>3.85</v>
       </c>
       <c r="H34">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I34">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -8900,13 +8900,13 @@
         <v>4.1</v>
       </c>
       <c r="L34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M34">
         <v>1.05</v>
       </c>
       <c r="N34">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O34">
         <v>1.22</v>
@@ -8921,7 +8921,7 @@
         <v>1.57</v>
       </c>
       <c r="S34">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T34">
         <v>1.62</v>
@@ -8930,7 +8930,7 @@
         <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W34">
         <v>1.35</v>
@@ -8939,7 +8939,7 @@
         <v>21</v>
       </c>
       <c r="Y34">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z34">
         <v>14.5</v>
@@ -8948,10 +8948,10 @@
         <v>24</v>
       </c>
       <c r="AB34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34">
         <v>11</v>
@@ -8960,7 +8960,7 @@
         <v>19</v>
       </c>
       <c r="AF34">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AG34">
         <v>15.5</v>
@@ -8978,34 +8978,34 @@
         <v>38</v>
       </c>
       <c r="AL34">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN34">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AO34">
         <v>10.5</v>
       </c>
       <c r="AP34">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ34">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR34">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS34">
+        <v>22</v>
+      </c>
+      <c r="AT34">
         <v>17</v>
       </c>
-      <c r="AT34">
-        <v>18</v>
-      </c>
       <c r="AU34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV34">
         <v>10</v>
@@ -9014,10 +9014,10 @@
         <v>17.5</v>
       </c>
       <c r="AX34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ34">
         <v>14.5</v>
@@ -9026,7 +9026,7 @@
         <v>26</v>
       </c>
       <c r="BB34">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC34">
         <v>34</v>
@@ -9035,13 +9035,13 @@
         <v>36</v>
       </c>
       <c r="BE34">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF34">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BG34">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH34">
         <v>4.6</v>
@@ -9065,7 +9065,7 @@
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BP34">
         <v>1000</v>
@@ -9080,7 +9080,7 @@
         <v>13.5</v>
       </c>
       <c r="BT34">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU34">
         <v>4.1</v>
@@ -9089,7 +9089,7 @@
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BX34">
         <v>1000</v>
@@ -9101,7 +9101,7 @@
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>2.46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB34" t="s">
         <v>176</v>
@@ -9124,19 +9124,19 @@
         <v>174</v>
       </c>
       <c r="F35">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="G35">
-        <v>600</v>
+        <v>2.78</v>
       </c>
       <c r="H35">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="I35">
-        <v>870</v>
+        <v>3.85</v>
       </c>
       <c r="J35">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9148,22 +9148,22 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="O35">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P35">
-        <v>1.26</v>
+        <v>1.95</v>
       </c>
       <c r="Q35">
-        <v>1.15</v>
+        <v>1.64</v>
       </c>
       <c r="R35">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="S35">
-        <v>1.16</v>
+        <v>2.32</v>
       </c>
       <c r="T35">
         <v>1.01</v>
@@ -9172,10 +9172,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9366,46 +9366,46 @@
         <v>175</v>
       </c>
       <c r="F36">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="G36">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="H36">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="I36">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J36">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="K36">
+        <v>500</v>
+      </c>
+      <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.06</v>
+      </c>
+      <c r="N36">
+        <v>2.54</v>
+      </c>
+      <c r="O36">
+        <v>1.42</v>
+      </c>
+      <c r="P36">
+        <v>1.56</v>
+      </c>
+      <c r="Q36">
+        <v>2.04</v>
+      </c>
+      <c r="R36">
+        <v>1.2</v>
+      </c>
+      <c r="S36">
         <v>3.75</v>
-      </c>
-      <c r="L36">
-        <v>1.01</v>
-      </c>
-      <c r="M36">
-        <v>1.1</v>
-      </c>
-      <c r="N36">
-        <v>3.05</v>
-      </c>
-      <c r="O36">
-        <v>1.43</v>
-      </c>
-      <c r="P36">
-        <v>1.7</v>
-      </c>
-      <c r="Q36">
-        <v>2.02</v>
-      </c>
-      <c r="R36">
-        <v>1.09</v>
-      </c>
-      <c r="S36">
-        <v>1.01</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -9417,7 +9417,7 @@
         <v>1.29</v>
       </c>
       <c r="W36">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="X36">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="181">
   <si>
     <t>League</t>
   </si>
@@ -292,6 +292,9 @@
     <t>South African Premier Division</t>
   </si>
   <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
     <t>English Sky Bet League 1</t>
   </si>
   <si>
@@ -322,6 +325,9 @@
     <t>17:30:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -403,6 +409,9 @@
     <t>Assyriska FF</t>
   </si>
   <si>
+    <t>Zeleznicar Pancevo</t>
+  </si>
+  <si>
     <t>Plzen</t>
   </si>
   <si>
@@ -415,15 +424,15 @@
     <t>Juventus</t>
   </si>
   <si>
+    <t>AFC Wimbledon</t>
+  </si>
+  <si>
+    <t>Lillestrom</t>
+  </si>
+  <si>
     <t>Crystal Palace</t>
   </si>
   <si>
-    <t>Lillestrom</t>
-  </si>
-  <si>
-    <t>AFC Wimbledon</t>
-  </si>
-  <si>
     <t>Cr Temouchent</t>
   </si>
   <si>
@@ -508,6 +517,9 @@
     <t>AFC Eskilstuna</t>
   </si>
   <si>
+    <t>Crvena Zvezda</t>
+  </si>
+  <si>
     <t>Union St Gilloise</t>
   </si>
   <si>
@@ -520,15 +532,15 @@
     <t>NEC Nijmegen</t>
   </si>
   <si>
+    <t>MK Dons</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
     <t>Lech Poznan</t>
   </si>
   <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>MK Dons</t>
-  </si>
-  <si>
     <t>Kabylie</t>
   </si>
   <si>
@@ -544,7 +556,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 09:27:27</t>
+    <t>2026-09-16 11:42:40</t>
   </si>
 </sst>
 </file>
@@ -876,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB36"/>
+  <dimension ref="A1:CB37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1126,241 +1138,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F2">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="G2">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="L2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Q2">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S2">
+        <v>2.28</v>
+      </c>
+      <c r="T2">
+        <v>1.61</v>
+      </c>
+      <c r="U2">
         <v>2.24</v>
       </c>
-      <c r="T2">
-        <v>1.75</v>
-      </c>
-      <c r="U2">
-        <v>2.04</v>
-      </c>
       <c r="V2">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="X2">
+        <v>29</v>
+      </c>
+      <c r="Y2">
         <v>32</v>
       </c>
-      <c r="Y2">
-        <v>38</v>
-      </c>
       <c r="Z2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
+        <v>12.5</v>
+      </c>
+      <c r="AD2">
+        <v>25</v>
+      </c>
+      <c r="AE2">
+        <v>75</v>
+      </c>
+      <c r="AF2">
+        <v>12</v>
+      </c>
+      <c r="AG2">
+        <v>11</v>
+      </c>
+      <c r="AH2">
+        <v>23</v>
+      </c>
+      <c r="AI2">
+        <v>65</v>
+      </c>
+      <c r="AJ2">
+        <v>17.5</v>
+      </c>
+      <c r="AK2">
+        <v>15</v>
+      </c>
+      <c r="AL2">
+        <v>28</v>
+      </c>
+      <c r="AM2">
+        <v>80</v>
+      </c>
+      <c r="AN2">
+        <v>5.9</v>
+      </c>
+      <c r="AO2">
+        <v>60</v>
+      </c>
+      <c r="AP2">
+        <v>23</v>
+      </c>
+      <c r="AQ2">
+        <v>25</v>
+      </c>
+      <c r="AR2">
+        <v>46</v>
+      </c>
+      <c r="AS2">
+        <v>8.6</v>
+      </c>
+      <c r="AT2">
+        <v>11</v>
+      </c>
+      <c r="AU2">
+        <v>10</v>
+      </c>
+      <c r="AV2">
+        <v>20</v>
+      </c>
+      <c r="AW2">
+        <v>46</v>
+      </c>
+      <c r="AX2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>27</v>
+      </c>
+      <c r="BB2">
+        <v>13.5</v>
+      </c>
+      <c r="BC2">
+        <v>12.5</v>
+      </c>
+      <c r="BD2">
+        <v>22</v>
+      </c>
+      <c r="BE2">
+        <v>28</v>
+      </c>
+      <c r="BF2">
+        <v>5</v>
+      </c>
+      <c r="BG2">
+        <v>36</v>
+      </c>
+      <c r="BH2">
+        <v>5.2</v>
+      </c>
+      <c r="BI2">
+        <v>3.7</v>
+      </c>
+      <c r="BJ2">
+        <v>11</v>
+      </c>
+      <c r="BK2">
+        <v>3.95</v>
+      </c>
+      <c r="BL2">
+        <v>110</v>
+      </c>
+      <c r="BM2">
+        <v>5.8</v>
+      </c>
+      <c r="BN2">
+        <v>5.1</v>
+      </c>
+      <c r="BO2">
+        <v>3.9</v>
+      </c>
+      <c r="BP2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ2">
+        <v>3.75</v>
+      </c>
+      <c r="BR2">
+        <v>21</v>
+      </c>
+      <c r="BS2">
+        <v>4.7</v>
+      </c>
+      <c r="BT2">
+        <v>11.5</v>
+      </c>
+      <c r="BU2">
+        <v>4</v>
+      </c>
+      <c r="BV2">
+        <v>50</v>
+      </c>
+      <c r="BW2">
+        <v>5.4</v>
+      </c>
+      <c r="BX2">
+        <v>46</v>
+      </c>
+      <c r="BY2">
+        <v>5.4</v>
+      </c>
+      <c r="BZ2">
         <v>14</v>
       </c>
-      <c r="AD2">
-        <v>38</v>
-      </c>
-      <c r="AE2">
-        <v>120</v>
-      </c>
-      <c r="AF2">
-        <v>11.5</v>
-      </c>
-      <c r="AG2">
-        <v>13</v>
-      </c>
-      <c r="AH2">
-        <v>27</v>
-      </c>
-      <c r="AI2">
-        <v>100</v>
-      </c>
-      <c r="AJ2">
-        <v>13.5</v>
-      </c>
-      <c r="AK2">
-        <v>16.5</v>
-      </c>
-      <c r="AL2">
-        <v>32</v>
-      </c>
-      <c r="AM2">
-        <v>110</v>
-      </c>
-      <c r="AN2">
-        <v>4.8</v>
-      </c>
-      <c r="AO2">
-        <v>110</v>
-      </c>
-      <c r="AP2">
-        <v>6.8</v>
-      </c>
-      <c r="AQ2">
-        <v>29</v>
-      </c>
-      <c r="AR2">
-        <v>7.4</v>
-      </c>
-      <c r="AS2">
-        <v>7</v>
-      </c>
-      <c r="AT2">
-        <v>10.5</v>
-      </c>
-      <c r="AU2">
-        <v>11.5</v>
-      </c>
-      <c r="AV2">
-        <v>21</v>
-      </c>
-      <c r="AW2">
-        <v>6.8</v>
-      </c>
-      <c r="AX2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>18.5</v>
-      </c>
-      <c r="BA2">
-        <v>7</v>
-      </c>
-      <c r="BB2">
-        <v>10.5</v>
-      </c>
-      <c r="BC2">
-        <v>12</v>
-      </c>
-      <c r="BD2">
-        <v>6.8</v>
-      </c>
-      <c r="BE2">
-        <v>6.8</v>
-      </c>
-      <c r="BF2">
-        <v>3.95</v>
-      </c>
-      <c r="BG2">
-        <v>6.8</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.04</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.04</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.04</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.04</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.04</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
-      <c r="BU2">
-        <v>1.04</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.04</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>1.04</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1368,85 +1380,85 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F3">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G3">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H3">
+        <v>4.8</v>
+      </c>
+      <c r="I3">
         <v>4.9</v>
       </c>
-      <c r="I3">
-        <v>5.1</v>
-      </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="M3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="P3">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Q3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T3">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="U3">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="V3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="X3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB3">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1458,7 +1470,7 @@
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1467,142 +1479,142 @@
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM3">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AO3">
         <v>230</v>
       </c>
       <c r="AP3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS3">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
         <v>21</v>
       </c>
       <c r="AW3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AX3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3">
+        <v>12</v>
+      </c>
+      <c r="AZ3">
+        <v>30</v>
+      </c>
+      <c r="BA3">
+        <v>23</v>
+      </c>
+      <c r="BB3">
+        <v>26</v>
+      </c>
+      <c r="BC3">
+        <v>34</v>
+      </c>
+      <c r="BD3">
+        <v>21</v>
+      </c>
+      <c r="BE3">
+        <v>19</v>
+      </c>
+      <c r="BF3">
+        <v>36</v>
+      </c>
+      <c r="BG3">
+        <v>20</v>
+      </c>
+      <c r="BH3">
+        <v>2.34</v>
+      </c>
+      <c r="BI3">
+        <v>2.18</v>
+      </c>
+      <c r="BJ3">
+        <v>14.5</v>
+      </c>
+      <c r="BK3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>13</v>
+      </c>
+      <c r="BN3">
+        <v>4.8</v>
+      </c>
+      <c r="BO3">
+        <v>4.1</v>
+      </c>
+      <c r="BP3">
+        <v>22</v>
+      </c>
+      <c r="BQ3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR3">
+        <v>60</v>
+      </c>
+      <c r="BS3">
         <v>11</v>
       </c>
-      <c r="AZ3">
-        <v>29</v>
-      </c>
-      <c r="BA3">
-        <v>15.5</v>
-      </c>
-      <c r="BB3">
-        <v>24</v>
-      </c>
-      <c r="BC3">
-        <v>29</v>
-      </c>
-      <c r="BD3">
-        <v>15.5</v>
-      </c>
-      <c r="BE3">
-        <v>16.5</v>
-      </c>
-      <c r="BF3">
-        <v>30</v>
-      </c>
-      <c r="BG3">
-        <v>16</v>
-      </c>
-      <c r="BH3">
-        <v>2.46</v>
-      </c>
-      <c r="BI3">
-        <v>2.28</v>
-      </c>
-      <c r="BJ3">
-        <v>14</v>
-      </c>
-      <c r="BK3">
-        <v>10.5</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>12.5</v>
-      </c>
-      <c r="BN3">
-        <v>4.6</v>
-      </c>
-      <c r="BO3">
-        <v>4</v>
-      </c>
-      <c r="BP3">
-        <v>19</v>
-      </c>
-      <c r="BQ3">
-        <v>7.6</v>
-      </c>
-      <c r="BR3">
-        <v>55</v>
-      </c>
-      <c r="BS3">
-        <v>10.5</v>
-      </c>
       <c r="BT3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BU3">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
         <v>65</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1610,157 +1622,157 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F4">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="G4">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="I4">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="J4">
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
         <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="W4">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Z4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AB4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
       </c>
       <c r="AE4">
+        <v>19</v>
+      </c>
+      <c r="AF4">
+        <v>42</v>
+      </c>
+      <c r="AG4">
+        <v>21</v>
+      </c>
+      <c r="AH4">
         <v>25</v>
       </c>
-      <c r="AF4">
-        <v>44</v>
-      </c>
-      <c r="AG4">
-        <v>18</v>
-      </c>
-      <c r="AH4">
-        <v>19.5</v>
-      </c>
       <c r="AI4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ4">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN4">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AO4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS4">
+        <v>17</v>
+      </c>
+      <c r="AT4">
+        <v>16</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>17</v>
+      </c>
+      <c r="AX4">
+        <v>34</v>
+      </c>
+      <c r="AY4">
         <v>18.5</v>
       </c>
-      <c r="AT4">
-        <v>15</v>
-      </c>
-      <c r="AU4">
-        <v>7.8</v>
-      </c>
-      <c r="AV4">
-        <v>9.4</v>
-      </c>
-      <c r="AW4">
-        <v>17.5</v>
-      </c>
-      <c r="AX4">
-        <v>30</v>
-      </c>
-      <c r="AY4">
-        <v>16.5</v>
-      </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA4">
         <v>32</v>
@@ -1769,82 +1781,82 @@
         <v>13.5</v>
       </c>
       <c r="BC4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BE4">
         <v>13.5</v>
       </c>
       <c r="BF4">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
+        <v>4.8</v>
+      </c>
+      <c r="BL4">
+        <v>170</v>
+      </c>
+      <c r="BM4">
+        <v>8.4</v>
+      </c>
+      <c r="BN4">
+        <v>8.4</v>
+      </c>
+      <c r="BO4">
+        <v>5.6</v>
+      </c>
+      <c r="BP4">
+        <v>55</v>
+      </c>
+      <c r="BQ4">
+        <v>7.4</v>
+      </c>
+      <c r="BR4">
+        <v>65</v>
+      </c>
+      <c r="BS4">
         <v>7.6</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>9.6</v>
-      </c>
-      <c r="BN4">
-        <v>7.8</v>
-      </c>
-      <c r="BO4">
-        <v>6.2</v>
-      </c>
-      <c r="BP4">
-        <v>46</v>
-      </c>
-      <c r="BQ4">
-        <v>8</v>
-      </c>
-      <c r="BR4">
-        <v>60</v>
-      </c>
-      <c r="BS4">
-        <v>8.6</v>
-      </c>
       <c r="BT4">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BU4">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BV4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BW4">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BX4">
+        <v>32</v>
+      </c>
+      <c r="BY4">
+        <v>6.8</v>
+      </c>
+      <c r="BZ4">
         <v>28</v>
       </c>
-      <c r="BY4">
-        <v>7.4</v>
-      </c>
-      <c r="BZ4">
-        <v>24</v>
-      </c>
       <c r="CA4">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1852,67 +1864,67 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G5">
         <v>2.2</v>
       </c>
       <c r="H5">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L5">
         <v>1.62</v>
       </c>
       <c r="M5">
+        <v>1.16</v>
+      </c>
+      <c r="N5">
+        <v>2.24</v>
+      </c>
+      <c r="O5">
+        <v>1.63</v>
+      </c>
+      <c r="P5">
+        <v>1.46</v>
+      </c>
+      <c r="Q5">
+        <v>2.96</v>
+      </c>
+      <c r="R5">
         <v>1.12</v>
       </c>
-      <c r="N5">
-        <v>2.2</v>
-      </c>
-      <c r="O5">
-        <v>1.6</v>
-      </c>
-      <c r="P5">
-        <v>1.38</v>
-      </c>
-      <c r="Q5">
-        <v>2.94</v>
-      </c>
-      <c r="R5">
-        <v>1.13</v>
-      </c>
       <c r="S5">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U5">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W5">
         <v>1.83</v>
@@ -1972,58 +1984,58 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ5">
-        <v>7</v>
+        <v>1.71</v>
       </c>
       <c r="AR5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AS5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AT5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AV5">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AW5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AX5">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY5">
-        <v>7.6</v>
+        <v>1.73</v>
       </c>
       <c r="AZ5">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BA5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BB5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BC5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BD5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BE5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BF5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BG5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2086,7 +2098,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2094,28 +2106,28 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F6">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H6">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -2133,22 +2145,22 @@
         <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P6">
         <v>2.12</v>
       </c>
       <c r="Q6">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R6">
         <v>1.44</v>
       </c>
       <c r="S6">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T6">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="U6">
         <v>2.3</v>
@@ -2157,7 +2169,7 @@
         <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -2172,7 +2184,7 @@
         <v>44</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2184,10 +2196,10 @@
         <v>32</v>
       </c>
       <c r="AF6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH6">
         <v>18</v>
@@ -2196,19 +2208,19 @@
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM6">
         <v>80</v>
       </c>
       <c r="AN6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO6">
         <v>21</v>
@@ -2244,25 +2256,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA6">
         <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC6">
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
         <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
         <v>13.5</v>
@@ -2328,7 +2340,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2336,154 +2348,154 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F7">
         <v>2.02</v>
       </c>
       <c r="G7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="T7">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="X7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>12</v>
+      </c>
+      <c r="AR7">
+        <v>16</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
         <v>19.5</v>
       </c>
-      <c r="Z7">
-        <v>32</v>
-      </c>
-      <c r="AA7">
-        <v>70</v>
-      </c>
-      <c r="AB7">
-        <v>14.5</v>
-      </c>
-      <c r="AC7">
-        <v>10.5</v>
-      </c>
-      <c r="AD7">
-        <v>17.5</v>
-      </c>
-      <c r="AE7">
-        <v>42</v>
-      </c>
-      <c r="AF7">
-        <v>18</v>
-      </c>
-      <c r="AG7">
-        <v>13</v>
-      </c>
-      <c r="AH7">
-        <v>18.5</v>
-      </c>
-      <c r="AI7">
-        <v>48</v>
-      </c>
-      <c r="AJ7">
-        <v>29</v>
-      </c>
-      <c r="AK7">
-        <v>23</v>
-      </c>
-      <c r="AL7">
-        <v>34</v>
-      </c>
-      <c r="AM7">
-        <v>80</v>
-      </c>
-      <c r="AN7">
-        <v>14</v>
-      </c>
-      <c r="AO7">
-        <v>34</v>
-      </c>
-      <c r="AP7">
-        <v>15.5</v>
-      </c>
-      <c r="AQ7">
-        <v>13</v>
-      </c>
-      <c r="AR7">
-        <v>20</v>
-      </c>
-      <c r="AS7">
-        <v>1.01</v>
-      </c>
-      <c r="AT7">
-        <v>9.6</v>
-      </c>
-      <c r="AU7">
-        <v>7.2</v>
-      </c>
-      <c r="AV7">
-        <v>11.5</v>
-      </c>
-      <c r="AW7">
-        <v>1.01</v>
-      </c>
       <c r="AX7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
         <v>12</v>
@@ -2492,22 +2504,22 @@
         <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2570,7 +2582,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2578,43 +2590,43 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="I8">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J8">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.31</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>1.3</v>
@@ -2623,13 +2635,13 @@
         <v>1.76</v>
       </c>
       <c r="Q8">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="R8">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S8">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2638,10 +2650,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2812,7 +2824,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2820,16 +2832,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F9">
         <v>7.2</v>
@@ -2841,7 +2853,7 @@
         <v>1.47</v>
       </c>
       <c r="I9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2850,40 +2862,40 @@
         <v>4.9</v>
       </c>
       <c r="L9">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
         <v>3.35</v>
       </c>
       <c r="O9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P9">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="Q9">
         <v>1.94</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
-        <v>3.45</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
         <v>2.62</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>17.5</v>
@@ -2892,10 +2904,10 @@
         <v>8.6</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AB9">
         <v>28</v>
@@ -2907,7 +2919,7 @@
         <v>12.5</v>
       </c>
       <c r="AE9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF9">
         <v>85</v>
@@ -2916,10 +2928,10 @@
         <v>38</v>
       </c>
       <c r="AH9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
         <v>360</v>
@@ -2937,7 +2949,7 @@
         <v>280</v>
       </c>
       <c r="AO9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP9">
         <v>10</v>
@@ -2964,31 +2976,31 @@
         <v>13</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ9">
         <v>19</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG9">
         <v>7</v>
@@ -3054,7 +3066,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3062,34 +3074,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F10">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="I10">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="J10">
         <v>1.12</v>
       </c>
       <c r="K10">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3101,139 +3113,139 @@
         <v>3.45</v>
       </c>
       <c r="O10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q10">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S10">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="T10">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W10">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="X10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y10">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="Z10">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AA10">
-        <v>430</v>
+        <v>620</v>
       </c>
       <c r="AB10">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AD10">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AE10">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="AF10">
         <v>14.5</v>
       </c>
       <c r="AG10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH10">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI10">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AJ10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK10">
         <v>16.5</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN10">
+        <v>3.25</v>
+      </c>
+      <c r="AO10">
+        <v>200</v>
+      </c>
+      <c r="AP10">
+        <v>4.3</v>
+      </c>
+      <c r="AQ10">
+        <v>4.4</v>
+      </c>
+      <c r="AR10">
+        <v>4.5</v>
+      </c>
+      <c r="AS10">
+        <v>4.6</v>
+      </c>
+      <c r="AT10">
+        <v>3.8</v>
+      </c>
+      <c r="AU10">
+        <v>3.9</v>
+      </c>
+      <c r="AV10">
+        <v>4.4</v>
+      </c>
+      <c r="AW10">
+        <v>4.6</v>
+      </c>
+      <c r="AX10">
+        <v>3.55</v>
+      </c>
+      <c r="AY10">
+        <v>3.6</v>
+      </c>
+      <c r="AZ10">
+        <v>4.1</v>
+      </c>
+      <c r="BA10">
+        <v>4.5</v>
+      </c>
+      <c r="BB10">
+        <v>3.45</v>
+      </c>
+      <c r="BC10">
         <v>3.65</v>
       </c>
-      <c r="AO10">
-        <v>140</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10">
-        <v>1.03</v>
-      </c>
-      <c r="AR10">
-        <v>1.03</v>
-      </c>
-      <c r="AS10">
-        <v>1.03</v>
-      </c>
-      <c r="AT10">
-        <v>1.01</v>
-      </c>
-      <c r="AU10">
-        <v>1.01</v>
-      </c>
-      <c r="AV10">
-        <v>1.01</v>
-      </c>
-      <c r="AW10">
-        <v>1.03</v>
-      </c>
-      <c r="AX10">
-        <v>1.01</v>
-      </c>
-      <c r="AY10">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10">
-        <v>1.01</v>
-      </c>
-      <c r="BA10">
-        <v>1.03</v>
-      </c>
-      <c r="BB10">
-        <v>1.01</v>
-      </c>
-      <c r="BC10">
-        <v>1.01</v>
-      </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF10">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3296,7 +3308,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3304,22 +3316,22 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H11">
         <v>1.42</v>
@@ -3340,7 +3352,7 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O11">
         <v>1.2</v>
@@ -3349,7 +3361,7 @@
         <v>2.54</v>
       </c>
       <c r="Q11">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R11">
         <v>1.6</v>
@@ -3361,7 +3373,7 @@
         <v>1.84</v>
       </c>
       <c r="U11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V11">
         <v>3.25</v>
@@ -3376,25 +3388,25 @@
         <v>11</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AA11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB11">
         <v>34</v>
       </c>
       <c r="AC11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE11">
         <v>14.5</v>
       </c>
       <c r="AF11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
         <v>32</v>
@@ -3406,19 +3418,19 @@
         <v>34</v>
       </c>
       <c r="AJ11">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
         <v>5.4</v>
@@ -3436,58 +3448,58 @@
         <v>11</v>
       </c>
       <c r="AT11">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AU11">
         <v>10.5</v>
       </c>
       <c r="AV11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW11">
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AY11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11">
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BB11">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BC11">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BD11">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BE11">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BG11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>2.24</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3499,7 +3511,7 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>6.6</v>
+        <v>2.28</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -3517,13 +3529,13 @@
         <v>4.5</v>
       </c>
       <c r="BU11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="BX11">
         <v>1000</v>
@@ -3538,7 +3550,7 @@
         <v>6.8</v>
       </c>
       <c r="CB11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3546,16 +3558,16 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F12">
         <v>3.2</v>
@@ -3576,7 +3588,7 @@
         <v>3.8</v>
       </c>
       <c r="L12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M12">
         <v>1.05</v>
@@ -3600,10 +3612,10 @@
         <v>2.78</v>
       </c>
       <c r="T12">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U12">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V12">
         <v>1.72</v>
@@ -3612,7 +3624,7 @@
         <v>1.44</v>
       </c>
       <c r="X12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
         <v>13</v>
@@ -3627,7 +3639,7 @@
         <v>16</v>
       </c>
       <c r="AC12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
         <v>11.5</v>
@@ -3651,7 +3663,7 @@
         <v>55</v>
       </c>
       <c r="AK12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL12">
         <v>38</v>
@@ -3660,19 +3672,19 @@
         <v>65</v>
       </c>
       <c r="AN12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO12">
         <v>14.5</v>
       </c>
       <c r="AP12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ12">
         <v>12</v>
       </c>
       <c r="AR12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS12">
         <v>28</v>
@@ -3717,10 +3729,10 @@
         <v>21</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH12">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI12">
         <v>3.6</v>
@@ -3738,7 +3750,7 @@
         <v>20</v>
       </c>
       <c r="BN12">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO12">
         <v>5.8</v>
@@ -3747,13 +3759,13 @@
         <v>27</v>
       </c>
       <c r="BQ12">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="BR12">
         <v>36</v>
       </c>
       <c r="BS12">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BT12">
         <v>5.5</v>
@@ -3762,25 +3774,25 @@
         <v>5</v>
       </c>
       <c r="BV12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BX12">
         <v>32</v>
       </c>
       <c r="BY12">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="BZ12">
         <v>23</v>
       </c>
       <c r="CA12">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3788,16 +3800,16 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F13">
         <v>1.1</v>
@@ -3812,7 +3824,7 @@
         <v>870</v>
       </c>
       <c r="J13">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3836,10 +3848,10 @@
         <v>1.29</v>
       </c>
       <c r="R13">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S13">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3851,7 +3863,7 @@
         <v>1.04</v>
       </c>
       <c r="W13">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4022,7 +4034,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4030,25 +4042,25 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F14">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="G14">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="H14">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="I14">
         <v>3.1</v>
@@ -4057,16 +4069,16 @@
         <v>3.6</v>
       </c>
       <c r="K14">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O14">
         <v>1.24</v>
@@ -4075,13 +4087,13 @@
         <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
         <v>1.38</v>
       </c>
       <c r="S14">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4093,7 +4105,7 @@
         <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4264,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4272,16 +4284,16 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F15">
         <v>2.16</v>
@@ -4308,10 +4320,10 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="P15">
         <v>2.2</v>
@@ -4323,7 +4335,7 @@
         <v>1.43</v>
       </c>
       <c r="S15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4332,10 +4344,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4506,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4514,34 +4526,34 @@
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F16">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G16">
+        <v>3.5</v>
+      </c>
+      <c r="H16">
+        <v>2.12</v>
+      </c>
+      <c r="I16">
         <v>3.25</v>
       </c>
-      <c r="H16">
-        <v>2.3</v>
-      </c>
-      <c r="I16">
-        <v>2.92</v>
-      </c>
       <c r="J16">
-        <v>3.75</v>
+        <v>2.44</v>
       </c>
       <c r="K16">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4550,7 +4562,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
         <v>1.01</v>
@@ -4565,7 +4577,7 @@
         <v>1.38</v>
       </c>
       <c r="S16">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4574,10 +4586,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4748,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4756,31 +4768,31 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F17">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G17">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="H17">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="I17">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J17">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K17">
         <v>6.4</v>
@@ -4792,7 +4804,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
         <v>1.11</v>
@@ -4801,13 +4813,13 @@
         <v>2.24</v>
       </c>
       <c r="Q17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R17">
         <v>1.46</v>
       </c>
       <c r="S17">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4816,10 +4828,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4990,7 +5002,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4998,16 +5010,16 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F18">
         <v>1.72</v>
@@ -5028,28 +5040,28 @@
         <v>3.9</v>
       </c>
       <c r="L18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M18">
         <v>1.09</v>
       </c>
       <c r="N18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P18">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R18">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S18">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T18">
         <v>2.18</v>
@@ -5067,7 +5079,7 @@
         <v>11.5</v>
       </c>
       <c r="Y18">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z18">
         <v>48</v>
@@ -5106,16 +5118,16 @@
         <v>21</v>
       </c>
       <c r="AL18">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM18">
         <v>220</v>
       </c>
       <c r="AN18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO18">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP18">
         <v>10.5</v>
@@ -5124,7 +5136,7 @@
         <v>15</v>
       </c>
       <c r="AR18">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS18">
         <v>44</v>
@@ -5133,25 +5145,25 @@
         <v>6.4</v>
       </c>
       <c r="AU18">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18">
         <v>22</v>
       </c>
       <c r="AW18">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AX18">
         <v>8.4</v>
       </c>
       <c r="AY18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18">
         <v>23</v>
       </c>
       <c r="BA18">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB18">
         <v>15.5</v>
@@ -5166,73 +5178,73 @@
         <v>46</v>
       </c>
       <c r="BF18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG18">
         <v>42</v>
       </c>
       <c r="BH18">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BI18">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="BJ18">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BL18">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
         <v>34</v>
       </c>
       <c r="BN18">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BO18">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BP18">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BQ18">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BR18">
+        <v>48</v>
+      </c>
+      <c r="BS18">
+        <v>5.4</v>
+      </c>
+      <c r="BT18">
+        <v>11.5</v>
+      </c>
+      <c r="BU18">
+        <v>7.2</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>5.6</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>5.7</v>
+      </c>
+      <c r="BZ18">
         <v>40</v>
       </c>
-      <c r="BS18">
-        <v>10</v>
-      </c>
-      <c r="BT18">
-        <v>9.4</v>
-      </c>
-      <c r="BU18">
-        <v>8</v>
-      </c>
-      <c r="BV18">
-        <v>75</v>
-      </c>
-      <c r="BW18">
-        <v>11.5</v>
-      </c>
-      <c r="BX18">
-        <v>90</v>
-      </c>
-      <c r="BY18">
-        <v>18</v>
-      </c>
-      <c r="BZ18">
-        <v>36</v>
-      </c>
       <c r="CA18">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="CB18" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5240,25 +5252,25 @@
         <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F19">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G19">
         <v>12.5</v>
       </c>
       <c r="H19">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I19">
         <v>1.63</v>
@@ -5267,7 +5279,7 @@
         <v>3.55</v>
       </c>
       <c r="K19">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5276,31 +5288,31 @@
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O19">
         <v>1.47</v>
       </c>
       <c r="P19">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q19">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R19">
         <v>1.2</v>
       </c>
       <c r="S19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T19">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="U19">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="V19">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="W19">
         <v>1.09</v>
@@ -5309,7 +5321,7 @@
         <v>970</v>
       </c>
       <c r="Y19">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="Z19">
         <v>970</v>
@@ -5360,58 +5372,58 @@
         <v>970</v>
       </c>
       <c r="AP19">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AR19">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AS19">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AT19">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AU19">
-        <v>1.57</v>
+        <v>6.8</v>
       </c>
       <c r="AV19">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="AW19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AX19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AY19">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AZ19">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BA19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BB19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BC19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BD19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BE19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BF19">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BG19">
-        <v>7.8</v>
+        <v>1.67</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5474,7 +5486,7 @@
         <v>1.27</v>
       </c>
       <c r="CB19" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5482,31 +5494,31 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F20">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G20">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H20">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="I20">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="J20">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="K20">
         <v>3.4</v>
@@ -5515,112 +5527,112 @@
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N20">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="O20">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Q20">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="R20">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S20">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="T20">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="W20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
         <v>1.03</v>
@@ -5629,10 +5641,10 @@
         <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
         <v>1.03</v>
@@ -5650,10 +5662,10 @@
         <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5695,7 +5707,7 @@
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BV20">
         <v>1000</v>
@@ -5716,7 +5728,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5724,178 +5736,178 @@
         <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G21">
         <v>5.5</v>
       </c>
       <c r="H21">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="J21">
+        <v>3.65</v>
+      </c>
+      <c r="K21">
+        <v>4.6</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.04</v>
+      </c>
+      <c r="N21">
+        <v>4</v>
+      </c>
+      <c r="O21">
+        <v>1.21</v>
+      </c>
+      <c r="P21">
+        <v>2.3</v>
+      </c>
+      <c r="Q21">
+        <v>1.63</v>
+      </c>
+      <c r="R21">
+        <v>1.53</v>
+      </c>
+      <c r="S21">
+        <v>2.52</v>
+      </c>
+      <c r="T21">
+        <v>1.63</v>
+      </c>
+      <c r="U21">
+        <v>2.3</v>
+      </c>
+      <c r="V21">
+        <v>2.06</v>
+      </c>
+      <c r="W21">
+        <v>1.23</v>
+      </c>
+      <c r="X21">
+        <v>27</v>
+      </c>
+      <c r="Y21">
+        <v>14.5</v>
+      </c>
+      <c r="Z21">
+        <v>16</v>
+      </c>
+      <c r="AA21">
+        <v>25</v>
+      </c>
+      <c r="AB21">
+        <v>25</v>
+      </c>
+      <c r="AC21">
+        <v>12</v>
+      </c>
+      <c r="AD21">
+        <v>13</v>
+      </c>
+      <c r="AE21">
+        <v>22</v>
+      </c>
+      <c r="AF21">
+        <v>44</v>
+      </c>
+      <c r="AG21">
+        <v>22</v>
+      </c>
+      <c r="AH21">
+        <v>21</v>
+      </c>
+      <c r="AI21">
+        <v>36</v>
+      </c>
+      <c r="AJ21">
+        <v>110</v>
+      </c>
+      <c r="AK21">
+        <v>60</v>
+      </c>
+      <c r="AL21">
+        <v>60</v>
+      </c>
+      <c r="AM21">
+        <v>90</v>
+      </c>
+      <c r="AN21">
+        <v>50</v>
+      </c>
+      <c r="AO21">
+        <v>11</v>
+      </c>
+      <c r="AP21">
+        <v>3.6</v>
+      </c>
+      <c r="AQ21">
+        <v>3.25</v>
+      </c>
+      <c r="AR21">
+        <v>3.3</v>
+      </c>
+      <c r="AS21">
+        <v>3.6</v>
+      </c>
+      <c r="AT21">
+        <v>3.6</v>
+      </c>
+      <c r="AU21">
         <v>3.1</v>
       </c>
-      <c r="K21">
-        <v>6.2</v>
-      </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.03</v>
-      </c>
-      <c r="N21">
-        <v>2.66</v>
-      </c>
-      <c r="O21">
-        <v>1.04</v>
-      </c>
-      <c r="P21">
-        <v>2.22</v>
-      </c>
-      <c r="Q21">
-        <v>1.58</v>
-      </c>
-      <c r="R21">
-        <v>1.41</v>
-      </c>
-      <c r="S21">
-        <v>1.98</v>
-      </c>
-      <c r="T21">
-        <v>1.01</v>
-      </c>
-      <c r="U21">
-        <v>1.01</v>
-      </c>
-      <c r="V21">
-        <v>2</v>
-      </c>
-      <c r="W21">
-        <v>1.22</v>
-      </c>
-      <c r="X21">
-        <v>1000</v>
-      </c>
-      <c r="Y21">
-        <v>1000</v>
-      </c>
-      <c r="Z21">
-        <v>1000</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>1000</v>
-      </c>
-      <c r="AC21">
-        <v>1000</v>
-      </c>
-      <c r="AD21">
-        <v>1000</v>
-      </c>
-      <c r="AE21">
-        <v>1000</v>
-      </c>
-      <c r="AF21">
-        <v>1000</v>
-      </c>
-      <c r="AG21">
-        <v>1000</v>
-      </c>
-      <c r="AH21">
-        <v>1000</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>1000</v>
-      </c>
-      <c r="AK21">
-        <v>1000</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1000</v>
-      </c>
-      <c r="AO21">
-        <v>1000</v>
-      </c>
-      <c r="AP21">
-        <v>1.02</v>
-      </c>
-      <c r="AQ21">
-        <v>1.02</v>
-      </c>
-      <c r="AR21">
-        <v>1.02</v>
-      </c>
-      <c r="AS21">
-        <v>1.02</v>
-      </c>
-      <c r="AT21">
-        <v>1.02</v>
-      </c>
-      <c r="AU21">
-        <v>1.01</v>
-      </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AW21">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="AX21">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="AY21">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="AZ21">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="BA21">
-        <v>1.02</v>
+        <v>3.75</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC21">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="BD21">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF21">
-        <v>1.02</v>
+        <v>3.85</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5958,7 +5970,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5966,16 +5978,16 @@
         <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F22">
         <v>1.35</v>
@@ -5990,7 +6002,7 @@
         <v>17.5</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
         <v>5.9</v>
@@ -6008,16 +6020,16 @@
         <v>1.34</v>
       </c>
       <c r="P22">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="Q22">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R22">
         <v>1.22</v>
       </c>
       <c r="S22">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="T22">
         <v>2.38</v>
@@ -6026,10 +6038,10 @@
         <v>1.42</v>
       </c>
       <c r="V22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X22">
         <v>14.5</v>
@@ -6140,7 +6152,7 @@
         <v>4.3</v>
       </c>
       <c r="BH22">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI22">
         <v>1.02</v>
@@ -6149,58 +6161,58 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CB22" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6208,16 +6220,16 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F23">
         <v>3.05</v>
@@ -6226,16 +6238,16 @@
         <v>5.1</v>
       </c>
       <c r="H23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I23">
         <v>2.26</v>
       </c>
       <c r="J23">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6250,16 +6262,16 @@
         <v>1.02</v>
       </c>
       <c r="P23">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R23">
         <v>1.44</v>
       </c>
       <c r="S23">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6442,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6450,16 +6462,16 @@
         <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F24">
         <v>1.12</v>
@@ -6474,7 +6486,7 @@
         <v>870</v>
       </c>
       <c r="J24">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6510,10 +6522,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6684,249 +6696,249 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F25">
-        <v>2.88</v>
+        <v>5.7</v>
       </c>
       <c r="G25">
-        <v>2.92</v>
+        <v>13.5</v>
       </c>
       <c r="H25">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="I25">
-        <v>2.64</v>
+        <v>1.65</v>
       </c>
       <c r="J25">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K25">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>3.5</v>
+      </c>
+      <c r="O25">
+        <v>1.19</v>
+      </c>
+      <c r="P25">
+        <v>1.06</v>
+      </c>
+      <c r="Q25">
+        <v>1.19</v>
+      </c>
+      <c r="R25">
         <v>1.38</v>
       </c>
-      <c r="M25">
-        <v>1.06</v>
-      </c>
-      <c r="N25">
-        <v>4.4</v>
-      </c>
-      <c r="O25">
-        <v>1.27</v>
-      </c>
-      <c r="P25">
-        <v>2.14</v>
-      </c>
-      <c r="Q25">
-        <v>1.83</v>
-      </c>
-      <c r="R25">
-        <v>1.44</v>
-      </c>
       <c r="S25">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="T25">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>2.56</v>
       </c>
       <c r="W25">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6934,208 +6946,208 @@
         <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F26">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="G26">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="H26">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="I26">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="J26">
+        <v>3.6</v>
+      </c>
+      <c r="K26">
         <v>3.65</v>
       </c>
-      <c r="K26">
-        <v>3.75</v>
-      </c>
       <c r="L26">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N26">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O26">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q26">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R26">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S26">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T26">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V26">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X26">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z26">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA26">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB26">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC26">
         <v>8.4</v>
       </c>
       <c r="AD26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH26">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI26">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ26">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL26">
         <v>38</v>
       </c>
       <c r="AM26">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN26">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO26">
+        <v>19</v>
+      </c>
+      <c r="AP26">
         <v>16</v>
-      </c>
-      <c r="AP26">
-        <v>17</v>
       </c>
       <c r="AQ26">
         <v>12</v>
       </c>
       <c r="AR26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS26">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AT26">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU26">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX26">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AY26">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA26">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB26">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BC26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD26">
         <v>32</v>
       </c>
       <c r="BE26">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG26">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI26">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>2.02</v>
+        <v>6.4</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.84</v>
+        <v>4.7</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BR26">
         <v>1000</v>
@@ -7144,22 +7156,22 @@
         <v>12.5</v>
       </c>
       <c r="BT26">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.78</v>
+        <v>4.5</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.38</v>
+        <v>11.5</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
@@ -7168,7 +7180,7 @@
         <v>10</v>
       </c>
       <c r="CB26" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7176,241 +7188,241 @@
         <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F27">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="G27">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="H27">
-        <v>4.9</v>
+        <v>2.42</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>2.46</v>
       </c>
       <c r="J27">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K27">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L27">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N27">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="O27">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P27">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="Q27">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="R27">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="S27">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="T27">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V27">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="W27">
-        <v>2.26</v>
+        <v>1.46</v>
       </c>
       <c r="X27">
+        <v>18</v>
+      </c>
+      <c r="Y27">
+        <v>13</v>
+      </c>
+      <c r="Z27">
+        <v>17</v>
+      </c>
+      <c r="AA27">
+        <v>32</v>
+      </c>
+      <c r="AB27">
+        <v>15.5</v>
+      </c>
+      <c r="AC27">
+        <v>8.4</v>
+      </c>
+      <c r="AD27">
+        <v>11.5</v>
+      </c>
+      <c r="AE27">
+        <v>23</v>
+      </c>
+      <c r="AF27">
+        <v>23</v>
+      </c>
+      <c r="AG27">
+        <v>13.5</v>
+      </c>
+      <c r="AH27">
+        <v>14</v>
+      </c>
+      <c r="AI27">
+        <v>32</v>
+      </c>
+      <c r="AJ27">
+        <v>50</v>
+      </c>
+      <c r="AK27">
+        <v>32</v>
+      </c>
+      <c r="AL27">
+        <v>38</v>
+      </c>
+      <c r="AM27">
+        <v>70</v>
+      </c>
+      <c r="AN27">
+        <v>23</v>
+      </c>
+      <c r="AO27">
+        <v>15.5</v>
+      </c>
+      <c r="AP27">
+        <v>17</v>
+      </c>
+      <c r="AQ27">
+        <v>12</v>
+      </c>
+      <c r="AR27">
+        <v>15.5</v>
+      </c>
+      <c r="AS27">
+        <v>29</v>
+      </c>
+      <c r="AT27">
+        <v>14</v>
+      </c>
+      <c r="AU27">
+        <v>8</v>
+      </c>
+      <c r="AV27">
+        <v>10.5</v>
+      </c>
+      <c r="AW27">
+        <v>21</v>
+      </c>
+      <c r="AX27">
+        <v>21</v>
+      </c>
+      <c r="AY27">
+        <v>12.5</v>
+      </c>
+      <c r="AZ27">
+        <v>13</v>
+      </c>
+      <c r="BA27">
+        <v>29</v>
+      </c>
+      <c r="BB27">
+        <v>42</v>
+      </c>
+      <c r="BC27">
+        <v>27</v>
+      </c>
+      <c r="BD27">
+        <v>32</v>
+      </c>
+      <c r="BE27">
+        <v>55</v>
+      </c>
+      <c r="BF27">
+        <v>20</v>
+      </c>
+      <c r="BG27">
+        <v>14</v>
+      </c>
+      <c r="BH27">
+        <v>3.9</v>
+      </c>
+      <c r="BI27">
+        <v>3.55</v>
+      </c>
+      <c r="BJ27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK27">
+        <v>7.8</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
         <v>24</v>
       </c>
-      <c r="Y27">
-        <v>25</v>
-      </c>
-      <c r="Z27">
-        <v>46</v>
-      </c>
-      <c r="AA27">
-        <v>120</v>
-      </c>
-      <c r="AB27">
-        <v>13</v>
-      </c>
-      <c r="AC27">
+      <c r="BN27">
+        <v>6.4</v>
+      </c>
+      <c r="BO27">
+        <v>5.7</v>
+      </c>
+      <c r="BP27">
+        <v>22</v>
+      </c>
+      <c r="BQ27">
         <v>10</v>
       </c>
-      <c r="AD27">
-        <v>20</v>
-      </c>
-      <c r="AE27">
-        <v>55</v>
-      </c>
-      <c r="AF27">
-        <v>13.5</v>
-      </c>
-      <c r="AG27">
+      <c r="BR27">
+        <v>30</v>
+      </c>
+      <c r="BS27">
+        <v>11.5</v>
+      </c>
+      <c r="BT27">
+        <v>5.5</v>
+      </c>
+      <c r="BU27">
+        <v>5.1</v>
+      </c>
+      <c r="BV27">
+        <v>17</v>
+      </c>
+      <c r="BW27">
+        <v>9</v>
+      </c>
+      <c r="BX27">
+        <v>26</v>
+      </c>
+      <c r="BY27">
         <v>10.5</v>
       </c>
-      <c r="AH27">
-        <v>16</v>
-      </c>
-      <c r="AI27">
-        <v>48</v>
-      </c>
-      <c r="AJ27">
-        <v>19</v>
-      </c>
-      <c r="AK27">
-        <v>16</v>
-      </c>
-      <c r="AL27">
-        <v>26</v>
-      </c>
-      <c r="AM27">
-        <v>65</v>
-      </c>
-      <c r="AN27">
-        <v>7.6</v>
-      </c>
-      <c r="AO27">
-        <v>38</v>
-      </c>
-      <c r="AP27">
-        <v>21</v>
-      </c>
-      <c r="AQ27">
-        <v>22</v>
-      </c>
-      <c r="AR27">
-        <v>38</v>
-      </c>
-      <c r="AS27">
-        <v>38</v>
-      </c>
-      <c r="AT27">
-        <v>12</v>
-      </c>
-      <c r="AU27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV27">
-        <v>17.5</v>
-      </c>
-      <c r="AW27">
-        <v>44</v>
-      </c>
-      <c r="AX27">
-        <v>12</v>
-      </c>
-      <c r="AY27">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27">
-        <v>14</v>
-      </c>
-      <c r="BA27">
-        <v>42</v>
-      </c>
-      <c r="BB27">
-        <v>17.5</v>
-      </c>
-      <c r="BC27">
-        <v>14.5</v>
-      </c>
-      <c r="BD27">
-        <v>23</v>
-      </c>
-      <c r="BE27">
-        <v>50</v>
-      </c>
-      <c r="BF27">
-        <v>7</v>
-      </c>
-      <c r="BG27">
-        <v>32</v>
-      </c>
-      <c r="BH27">
-        <v>5.1</v>
-      </c>
-      <c r="BI27">
-        <v>3.6</v>
-      </c>
-      <c r="BJ27">
-        <v>1000</v>
-      </c>
-      <c r="BK27">
-        <v>2.02</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>19</v>
-      </c>
-      <c r="BN27">
-        <v>5.7</v>
-      </c>
-      <c r="BO27">
-        <v>3.9</v>
-      </c>
-      <c r="BP27">
-        <v>1000</v>
-      </c>
-      <c r="BQ27">
-        <v>2.14</v>
-      </c>
-      <c r="BR27">
-        <v>1000</v>
-      </c>
-      <c r="BS27">
-        <v>9.6</v>
-      </c>
-      <c r="BT27">
-        <v>1000</v>
-      </c>
-      <c r="BU27">
-        <v>2</v>
-      </c>
-      <c r="BV27">
-        <v>1000</v>
-      </c>
-      <c r="BW27">
-        <v>12.5</v>
-      </c>
-      <c r="BX27">
-        <v>1000</v>
-      </c>
-      <c r="BY27">
-        <v>14</v>
-      </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA27">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB27" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7418,241 +7430,241 @@
         <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F28">
+        <v>1.78</v>
+      </c>
+      <c r="G28">
+        <v>1.79</v>
+      </c>
+      <c r="H28">
+        <v>4.9</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <v>4.2</v>
+      </c>
+      <c r="K28">
+        <v>4.3</v>
+      </c>
+      <c r="L28">
+        <v>1.29</v>
+      </c>
+      <c r="M28">
+        <v>1.04</v>
+      </c>
+      <c r="N28">
+        <v>5.8</v>
+      </c>
+      <c r="O28">
+        <v>1.2</v>
+      </c>
+      <c r="P28">
+        <v>2.64</v>
+      </c>
+      <c r="Q28">
+        <v>1.59</v>
+      </c>
+      <c r="R28">
+        <v>1.65</v>
+      </c>
+      <c r="S28">
+        <v>2.44</v>
+      </c>
+      <c r="T28">
+        <v>1.61</v>
+      </c>
+      <c r="U28">
+        <v>2.52</v>
+      </c>
+      <c r="V28">
         <v>1.25</v>
       </c>
-      <c r="G28">
-        <v>1.26</v>
-      </c>
-      <c r="H28">
+      <c r="W28">
+        <v>2.26</v>
+      </c>
+      <c r="X28">
+        <v>24</v>
+      </c>
+      <c r="Y28">
+        <v>25</v>
+      </c>
+      <c r="Z28">
+        <v>46</v>
+      </c>
+      <c r="AA28">
+        <v>120</v>
+      </c>
+      <c r="AB28">
+        <v>12.5</v>
+      </c>
+      <c r="AC28">
+        <v>10</v>
+      </c>
+      <c r="AD28">
+        <v>19.5</v>
+      </c>
+      <c r="AE28">
+        <v>55</v>
+      </c>
+      <c r="AF28">
         <v>13.5</v>
       </c>
-      <c r="I28">
+      <c r="AG28">
+        <v>10.5</v>
+      </c>
+      <c r="AH28">
+        <v>16</v>
+      </c>
+      <c r="AI28">
+        <v>48</v>
+      </c>
+      <c r="AJ28">
+        <v>19.5</v>
+      </c>
+      <c r="AK28">
+        <v>16</v>
+      </c>
+      <c r="AL28">
+        <v>25</v>
+      </c>
+      <c r="AM28">
+        <v>65</v>
+      </c>
+      <c r="AN28">
+        <v>7.4</v>
+      </c>
+      <c r="AO28">
+        <v>38</v>
+      </c>
+      <c r="AP28">
+        <v>22</v>
+      </c>
+      <c r="AQ28">
+        <v>22</v>
+      </c>
+      <c r="AR28">
+        <v>38</v>
+      </c>
+      <c r="AS28">
+        <v>38</v>
+      </c>
+      <c r="AT28">
+        <v>12</v>
+      </c>
+      <c r="AU28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV28">
+        <v>17.5</v>
+      </c>
+      <c r="AW28">
+        <v>44</v>
+      </c>
+      <c r="AX28">
+        <v>12</v>
+      </c>
+      <c r="AY28">
+        <v>9.6</v>
+      </c>
+      <c r="AZ28">
         <v>14</v>
       </c>
-      <c r="J28">
+      <c r="BA28">
+        <v>42</v>
+      </c>
+      <c r="BB28">
+        <v>17.5</v>
+      </c>
+      <c r="BC28">
+        <v>14.5</v>
+      </c>
+      <c r="BD28">
+        <v>23</v>
+      </c>
+      <c r="BE28">
+        <v>50</v>
+      </c>
+      <c r="BF28">
+        <v>7</v>
+      </c>
+      <c r="BG28">
+        <v>32</v>
+      </c>
+      <c r="BH28">
+        <v>5.1</v>
+      </c>
+      <c r="BI28">
+        <v>3.6</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>2.02</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>19</v>
+      </c>
+      <c r="BN28">
+        <v>5.7</v>
+      </c>
+      <c r="BO28">
+        <v>3.9</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>2.14</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>2.38</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>2</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>12.5</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>14</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
         <v>7.8</v>
       </c>
-      <c r="K28">
-        <v>8</v>
-      </c>
-      <c r="L28">
-        <v>1.25</v>
-      </c>
-      <c r="M28">
-        <v>1.02</v>
-      </c>
-      <c r="N28">
-        <v>7.2</v>
-      </c>
-      <c r="O28">
-        <v>1.15</v>
-      </c>
-      <c r="P28">
-        <v>3.05</v>
-      </c>
-      <c r="Q28">
-        <v>1.46</v>
-      </c>
-      <c r="R28">
-        <v>1.82</v>
-      </c>
-      <c r="S28">
-        <v>2.14</v>
-      </c>
-      <c r="T28">
-        <v>2.04</v>
-      </c>
-      <c r="U28">
-        <v>1.87</v>
-      </c>
-      <c r="V28">
-        <v>1.07</v>
-      </c>
-      <c r="W28">
-        <v>4.9</v>
-      </c>
-      <c r="X28">
-        <v>36</v>
-      </c>
-      <c r="Y28">
-        <v>55</v>
-      </c>
-      <c r="Z28">
-        <v>150</v>
-      </c>
-      <c r="AA28">
-        <v>690</v>
-      </c>
-      <c r="AB28">
-        <v>13</v>
-      </c>
-      <c r="AC28">
-        <v>17.5</v>
-      </c>
-      <c r="AD28">
-        <v>50</v>
-      </c>
-      <c r="AE28">
-        <v>1000</v>
-      </c>
-      <c r="AF28">
-        <v>9.4</v>
-      </c>
-      <c r="AG28">
-        <v>12</v>
-      </c>
-      <c r="AH28">
-        <v>32</v>
-      </c>
-      <c r="AI28">
-        <v>150</v>
-      </c>
-      <c r="AJ28">
-        <v>9.4</v>
-      </c>
-      <c r="AK28">
-        <v>14.5</v>
-      </c>
-      <c r="AL28">
-        <v>36</v>
-      </c>
-      <c r="AM28">
-        <v>150</v>
-      </c>
-      <c r="AN28">
-        <v>3.5</v>
-      </c>
-      <c r="AO28">
-        <v>210</v>
-      </c>
-      <c r="AP28">
-        <v>25</v>
-      </c>
-      <c r="AQ28">
-        <v>44</v>
-      </c>
-      <c r="AR28">
-        <v>42</v>
-      </c>
-      <c r="AS28">
-        <v>55</v>
-      </c>
-      <c r="AT28">
-        <v>11</v>
-      </c>
-      <c r="AU28">
-        <v>15</v>
-      </c>
-      <c r="AV28">
-        <v>42</v>
-      </c>
-      <c r="AW28">
-        <v>48</v>
-      </c>
-      <c r="AX28">
-        <v>8.4</v>
-      </c>
-      <c r="AY28">
-        <v>11</v>
-      </c>
-      <c r="AZ28">
-        <v>28</v>
-      </c>
-      <c r="BA28">
-        <v>44</v>
-      </c>
-      <c r="BB28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC28">
-        <v>12</v>
-      </c>
-      <c r="BD28">
-        <v>29</v>
-      </c>
-      <c r="BE28">
-        <v>44</v>
-      </c>
-      <c r="BF28">
-        <v>3.3</v>
-      </c>
-      <c r="BG28">
-        <v>50</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>4</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>2.06</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>28</v>
-      </c>
-      <c r="BN28">
-        <v>4.4</v>
-      </c>
-      <c r="BO28">
-        <v>3.2</v>
-      </c>
-      <c r="BP28">
-        <v>9.6</v>
-      </c>
-      <c r="BQ28">
-        <v>5</v>
-      </c>
-      <c r="BR28">
-        <v>1000</v>
-      </c>
-      <c r="BS28">
-        <v>10</v>
-      </c>
-      <c r="BT28">
-        <v>1000</v>
-      </c>
-      <c r="BU28">
-        <v>2.2</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>22</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
-      <c r="BY28">
-        <v>19</v>
-      </c>
-      <c r="BZ28">
-        <v>1000</v>
-      </c>
-      <c r="CA28">
-        <v>5.1</v>
-      </c>
       <c r="CB28" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7660,1400 +7672,1400 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F29">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="G29">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="H29">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>15.5</v>
+      </c>
+      <c r="J29">
+        <v>7.6</v>
+      </c>
+      <c r="K29">
         <v>8</v>
       </c>
-      <c r="I29">
-        <v>8.6</v>
-      </c>
-      <c r="J29">
-        <v>5.4</v>
-      </c>
-      <c r="K29">
-        <v>5.5</v>
-      </c>
       <c r="L29">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="M29">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N29">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="O29">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="Q29">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="R29">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="S29">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="T29">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="U29">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="V29">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="W29">
+        <v>5</v>
+      </c>
+      <c r="X29">
+        <v>36</v>
+      </c>
+      <c r="Y29">
+        <v>55</v>
+      </c>
+      <c r="Z29">
+        <v>160</v>
+      </c>
+      <c r="AA29">
+        <v>690</v>
+      </c>
+      <c r="AB29">
+        <v>13</v>
+      </c>
+      <c r="AC29">
+        <v>17.5</v>
+      </c>
+      <c r="AD29">
+        <v>55</v>
+      </c>
+      <c r="AE29">
+        <v>220</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>12.5</v>
+      </c>
+      <c r="AH29">
+        <v>34</v>
+      </c>
+      <c r="AI29">
+        <v>160</v>
+      </c>
+      <c r="AJ29">
+        <v>9.6</v>
+      </c>
+      <c r="AK29">
+        <v>14</v>
+      </c>
+      <c r="AL29">
+        <v>36</v>
+      </c>
+      <c r="AM29">
+        <v>150</v>
+      </c>
+      <c r="AN29">
+        <v>3.45</v>
+      </c>
+      <c r="AO29">
+        <v>210</v>
+      </c>
+      <c r="AP29">
+        <v>30</v>
+      </c>
+      <c r="AQ29">
+        <v>46</v>
+      </c>
+      <c r="AR29">
+        <v>42</v>
+      </c>
+      <c r="AS29">
+        <v>55</v>
+      </c>
+      <c r="AT29">
+        <v>11</v>
+      </c>
+      <c r="AU29">
+        <v>15</v>
+      </c>
+      <c r="AV29">
+        <v>42</v>
+      </c>
+      <c r="AW29">
+        <v>48</v>
+      </c>
+      <c r="AX29">
+        <v>8.4</v>
+      </c>
+      <c r="AY29">
+        <v>11</v>
+      </c>
+      <c r="AZ29">
+        <v>28</v>
+      </c>
+      <c r="BA29">
+        <v>44</v>
+      </c>
+      <c r="BB29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC29">
+        <v>12</v>
+      </c>
+      <c r="BD29">
+        <v>29</v>
+      </c>
+      <c r="BE29">
+        <v>44</v>
+      </c>
+      <c r="BF29">
         <v>3.25</v>
       </c>
-      <c r="X29">
+      <c r="BG29">
+        <v>50</v>
+      </c>
+      <c r="BH29">
+        <v>5.1</v>
+      </c>
+      <c r="BI29">
+        <v>4.6</v>
+      </c>
+      <c r="BJ29">
+        <v>13</v>
+      </c>
+      <c r="BK29">
+        <v>10.5</v>
+      </c>
+      <c r="BL29">
+        <v>140</v>
+      </c>
+      <c r="BM29">
+        <v>30</v>
+      </c>
+      <c r="BN29">
+        <v>4</v>
+      </c>
+      <c r="BO29">
+        <v>3.6</v>
+      </c>
+      <c r="BP29">
+        <v>6.6</v>
+      </c>
+      <c r="BQ29">
+        <v>5.8</v>
+      </c>
+      <c r="BR29">
+        <v>21</v>
+      </c>
+      <c r="BS29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT29">
+        <v>17</v>
+      </c>
+      <c r="BU29">
+        <v>7.6</v>
+      </c>
+      <c r="BV29">
+        <v>110</v>
+      </c>
+      <c r="BW29">
         <v>24</v>
       </c>
-      <c r="Y29">
-        <v>32</v>
-      </c>
-      <c r="Z29">
-        <v>75</v>
-      </c>
-      <c r="AA29">
-        <v>1000</v>
-      </c>
-      <c r="AB29">
-        <v>10.5</v>
-      </c>
-      <c r="AC29">
-        <v>12</v>
-      </c>
-      <c r="AD29">
-        <v>32</v>
-      </c>
-      <c r="AE29">
-        <v>120</v>
-      </c>
-      <c r="AF29">
-        <v>9.6</v>
-      </c>
-      <c r="AG29">
-        <v>10.5</v>
-      </c>
-      <c r="AH29">
-        <v>24</v>
-      </c>
-      <c r="AI29">
-        <v>100</v>
-      </c>
-      <c r="AJ29">
-        <v>12</v>
-      </c>
-      <c r="AK29">
-        <v>13.5</v>
-      </c>
-      <c r="AL29">
-        <v>34</v>
-      </c>
-      <c r="AM29">
-        <v>120</v>
-      </c>
-      <c r="AN29">
-        <v>5.6</v>
-      </c>
-      <c r="AO29">
-        <v>120</v>
-      </c>
-      <c r="AP29">
-        <v>20</v>
-      </c>
-      <c r="AQ29">
-        <v>26</v>
-      </c>
-      <c r="AR29">
-        <v>60</v>
-      </c>
-      <c r="AS29">
-        <v>50</v>
-      </c>
-      <c r="AT29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU29">
-        <v>11</v>
-      </c>
-      <c r="AV29">
-        <v>26</v>
-      </c>
-      <c r="AW29">
-        <v>40</v>
-      </c>
-      <c r="AX29">
-        <v>8.6</v>
-      </c>
-      <c r="AY29">
-        <v>9.4</v>
-      </c>
-      <c r="AZ29">
+      <c r="BX29">
+        <v>85</v>
+      </c>
+      <c r="BY29">
         <v>21</v>
       </c>
-      <c r="BA29">
-        <v>38</v>
-      </c>
-      <c r="BB29">
-        <v>11</v>
-      </c>
-      <c r="BC29">
-        <v>13</v>
-      </c>
-      <c r="BD29">
-        <v>27</v>
-      </c>
-      <c r="BE29">
-        <v>42</v>
-      </c>
-      <c r="BF29">
-        <v>5.3</v>
-      </c>
-      <c r="BG29">
-        <v>42</v>
-      </c>
-      <c r="BH29">
-        <v>4.2</v>
-      </c>
-      <c r="BI29">
-        <v>3.8</v>
-      </c>
-      <c r="BJ29">
-        <v>12.5</v>
-      </c>
-      <c r="BK29">
-        <v>9.6</v>
-      </c>
-      <c r="BL29">
-        <v>150</v>
-      </c>
-      <c r="BM29">
-        <v>27</v>
-      </c>
-      <c r="BN29">
-        <v>4.1</v>
-      </c>
-      <c r="BO29">
-        <v>3.7</v>
-      </c>
-      <c r="BP29">
-        <v>8.6</v>
-      </c>
-      <c r="BQ29">
-        <v>7.4</v>
-      </c>
-      <c r="BR29">
-        <v>26</v>
-      </c>
-      <c r="BS29">
-        <v>10</v>
-      </c>
-      <c r="BT29">
-        <v>12.5</v>
-      </c>
-      <c r="BU29">
-        <v>10</v>
-      </c>
-      <c r="BV29">
-        <v>80</v>
-      </c>
-      <c r="BW29">
-        <v>17</v>
-      </c>
-      <c r="BX29">
-        <v>75</v>
-      </c>
-      <c r="BY29">
-        <v>17</v>
-      </c>
       <c r="BZ29">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="CA29">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="CB29" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F30">
-        <v>1.56</v>
+        <v>3.05</v>
       </c>
       <c r="G30">
-        <v>1.59</v>
+        <v>3.15</v>
       </c>
       <c r="H30">
-        <v>6.2</v>
+        <v>2.42</v>
       </c>
       <c r="I30">
-        <v>6.6</v>
+        <v>2.46</v>
       </c>
       <c r="J30">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="L30">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
+        <v>1.06</v>
+      </c>
+      <c r="N30">
+        <v>3.9</v>
+      </c>
+      <c r="O30">
+        <v>1.3</v>
+      </c>
+      <c r="P30">
+        <v>2.04</v>
+      </c>
+      <c r="Q30">
+        <v>1.92</v>
+      </c>
+      <c r="R30">
+        <v>1.41</v>
+      </c>
+      <c r="S30">
+        <v>3.25</v>
+      </c>
+      <c r="T30">
+        <v>1.75</v>
+      </c>
+      <c r="U30">
+        <v>2.26</v>
+      </c>
+      <c r="V30">
+        <v>1.68</v>
+      </c>
+      <c r="W30">
+        <v>1.46</v>
+      </c>
+      <c r="X30">
+        <v>16</v>
+      </c>
+      <c r="Y30">
+        <v>11.5</v>
+      </c>
+      <c r="Z30">
+        <v>17</v>
+      </c>
+      <c r="AA30">
+        <v>36</v>
+      </c>
+      <c r="AB30">
+        <v>13.5</v>
+      </c>
+      <c r="AC30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD30">
+        <v>12</v>
+      </c>
+      <c r="AE30">
+        <v>28</v>
+      </c>
+      <c r="AF30">
+        <v>24</v>
+      </c>
+      <c r="AG30">
+        <v>14</v>
+      </c>
+      <c r="AH30">
+        <v>17.5</v>
+      </c>
+      <c r="AI30">
+        <v>40</v>
+      </c>
+      <c r="AJ30">
+        <v>55</v>
+      </c>
+      <c r="AK30">
+        <v>36</v>
+      </c>
+      <c r="AL30">
+        <v>46</v>
+      </c>
+      <c r="AM30">
+        <v>100</v>
+      </c>
+      <c r="AN30">
+        <v>29</v>
+      </c>
+      <c r="AO30">
+        <v>19.5</v>
+      </c>
+      <c r="AP30">
+        <v>13.5</v>
+      </c>
+      <c r="AQ30">
+        <v>10</v>
+      </c>
+      <c r="AR30">
+        <v>14.5</v>
+      </c>
+      <c r="AS30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT30">
+        <v>11.5</v>
+      </c>
+      <c r="AU30">
+        <v>7.4</v>
+      </c>
+      <c r="AV30">
+        <v>10</v>
+      </c>
+      <c r="AW30">
+        <v>23</v>
+      </c>
+      <c r="AX30">
+        <v>19</v>
+      </c>
+      <c r="AY30">
+        <v>12</v>
+      </c>
+      <c r="AZ30">
+        <v>14.5</v>
+      </c>
+      <c r="BA30">
+        <v>30</v>
+      </c>
+      <c r="BB30">
+        <v>42</v>
+      </c>
+      <c r="BC30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD30">
+        <v>9</v>
+      </c>
+      <c r="BE30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF30">
+        <v>24</v>
+      </c>
+      <c r="BG30">
+        <v>16</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
         <v>1.04</v>
       </c>
-      <c r="N30">
-        <v>5.3</v>
-      </c>
-      <c r="O30">
-        <v>1.22</v>
-      </c>
-      <c r="P30">
-        <v>2.44</v>
-      </c>
-      <c r="Q30">
-        <v>1.66</v>
-      </c>
-      <c r="R30">
-        <v>1.56</v>
-      </c>
-      <c r="S30">
-        <v>2.68</v>
-      </c>
-      <c r="T30">
-        <v>1.78</v>
-      </c>
-      <c r="U30">
-        <v>2.18</v>
-      </c>
-      <c r="V30">
-        <v>1.17</v>
-      </c>
-      <c r="W30">
-        <v>2.68</v>
-      </c>
-      <c r="X30">
-        <v>23</v>
-      </c>
-      <c r="Y30">
-        <v>26</v>
-      </c>
-      <c r="Z30">
-        <v>55</v>
-      </c>
-      <c r="AA30">
-        <v>190</v>
-      </c>
-      <c r="AB30">
-        <v>10.5</v>
-      </c>
-      <c r="AC30">
-        <v>11</v>
-      </c>
-      <c r="AD30">
-        <v>24</v>
-      </c>
-      <c r="AE30">
-        <v>95</v>
-      </c>
-      <c r="AF30">
-        <v>10.5</v>
-      </c>
-      <c r="AG30">
-        <v>10.5</v>
-      </c>
-      <c r="AH30">
-        <v>20</v>
-      </c>
-      <c r="AI30">
-        <v>85</v>
-      </c>
-      <c r="AJ30">
-        <v>15</v>
-      </c>
-      <c r="AK30">
-        <v>15.5</v>
-      </c>
-      <c r="AL30">
-        <v>36</v>
-      </c>
-      <c r="AM30">
-        <v>110</v>
-      </c>
-      <c r="AN30">
-        <v>6.8</v>
-      </c>
-      <c r="AO30">
-        <v>95</v>
-      </c>
-      <c r="AP30">
-        <v>20</v>
-      </c>
-      <c r="AQ30">
-        <v>22</v>
-      </c>
-      <c r="AR30">
-        <v>10.5</v>
-      </c>
-      <c r="AS30">
-        <v>12</v>
-      </c>
-      <c r="AT30">
-        <v>9.4</v>
-      </c>
-      <c r="AU30">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV30">
-        <v>21</v>
-      </c>
-      <c r="AW30">
-        <v>28</v>
-      </c>
-      <c r="AX30">
-        <v>9.6</v>
-      </c>
-      <c r="AY30">
-        <v>9</v>
-      </c>
-      <c r="AZ30">
-        <v>17.5</v>
-      </c>
-      <c r="BA30">
-        <v>11</v>
-      </c>
-      <c r="BB30">
-        <v>13.5</v>
-      </c>
-      <c r="BC30">
-        <v>14</v>
-      </c>
-      <c r="BD30">
-        <v>9.4</v>
-      </c>
-      <c r="BE30">
-        <v>11.5</v>
-      </c>
-      <c r="BF30">
-        <v>6</v>
-      </c>
-      <c r="BG30">
-        <v>11</v>
-      </c>
-      <c r="BH30">
-        <v>1000</v>
-      </c>
-      <c r="BI30">
-        <v>3.45</v>
-      </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>26</v>
+        <v>1.04</v>
       </c>
       <c r="BN30">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F31">
-        <v>3.05</v>
+        <v>1.56</v>
       </c>
       <c r="G31">
-        <v>3.1</v>
+        <v>1.59</v>
       </c>
       <c r="H31">
+        <v>6</v>
+      </c>
+      <c r="I31">
+        <v>6.6</v>
+      </c>
+      <c r="J31">
+        <v>4.6</v>
+      </c>
+      <c r="K31">
+        <v>5</v>
+      </c>
+      <c r="L31">
+        <v>1.32</v>
+      </c>
+      <c r="M31">
+        <v>1.04</v>
+      </c>
+      <c r="N31">
+        <v>5.3</v>
+      </c>
+      <c r="O31">
+        <v>1.22</v>
+      </c>
+      <c r="P31">
         <v>2.44</v>
       </c>
-      <c r="I31">
-        <v>2.5</v>
-      </c>
-      <c r="J31">
-        <v>3.6</v>
-      </c>
-      <c r="K31">
-        <v>3.7</v>
-      </c>
-      <c r="L31">
-        <v>1.01</v>
-      </c>
-      <c r="M31">
-        <v>1.06</v>
-      </c>
-      <c r="N31">
-        <v>3.95</v>
-      </c>
-      <c r="O31">
-        <v>1.3</v>
-      </c>
-      <c r="P31">
-        <v>2.02</v>
-      </c>
       <c r="Q31">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="R31">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="S31">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="T31">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U31">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="W31">
-        <v>1.47</v>
+        <v>2.68</v>
       </c>
       <c r="X31">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="Y31">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Z31">
+        <v>55</v>
+      </c>
+      <c r="AA31">
+        <v>190</v>
+      </c>
+      <c r="AB31">
+        <v>10.5</v>
+      </c>
+      <c r="AC31">
+        <v>11</v>
+      </c>
+      <c r="AD31">
+        <v>24</v>
+      </c>
+      <c r="AE31">
+        <v>95</v>
+      </c>
+      <c r="AF31">
+        <v>10.5</v>
+      </c>
+      <c r="AG31">
+        <v>10.5</v>
+      </c>
+      <c r="AH31">
+        <v>20</v>
+      </c>
+      <c r="AI31">
+        <v>85</v>
+      </c>
+      <c r="AJ31">
+        <v>15</v>
+      </c>
+      <c r="AK31">
+        <v>15.5</v>
+      </c>
+      <c r="AL31">
+        <v>34</v>
+      </c>
+      <c r="AM31">
+        <v>110</v>
+      </c>
+      <c r="AN31">
+        <v>6.8</v>
+      </c>
+      <c r="AO31">
+        <v>95</v>
+      </c>
+      <c r="AP31">
+        <v>20</v>
+      </c>
+      <c r="AQ31">
+        <v>22</v>
+      </c>
+      <c r="AR31">
+        <v>27</v>
+      </c>
+      <c r="AS31">
+        <v>65</v>
+      </c>
+      <c r="AT31">
+        <v>9.4</v>
+      </c>
+      <c r="AU31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV31">
+        <v>21</v>
+      </c>
+      <c r="AW31">
+        <v>38</v>
+      </c>
+      <c r="AX31">
+        <v>9.6</v>
+      </c>
+      <c r="AY31">
+        <v>9</v>
+      </c>
+      <c r="AZ31">
         <v>17.5</v>
       </c>
-      <c r="AA31">
-        <v>36</v>
-      </c>
-      <c r="AB31">
+      <c r="BA31">
+        <v>38</v>
+      </c>
+      <c r="BB31">
         <v>13.5</v>
       </c>
-      <c r="AC31">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD31">
-        <v>12.5</v>
-      </c>
-      <c r="AE31">
-        <v>28</v>
-      </c>
-      <c r="AF31">
+      <c r="BC31">
+        <v>14</v>
+      </c>
+      <c r="BD31">
         <v>24</v>
       </c>
-      <c r="AG31">
-        <v>14</v>
-      </c>
-      <c r="AH31">
-        <v>17.5</v>
-      </c>
-      <c r="AI31">
-        <v>40</v>
-      </c>
-      <c r="AJ31">
-        <v>55</v>
-      </c>
-      <c r="AK31">
-        <v>36</v>
-      </c>
-      <c r="AL31">
-        <v>46</v>
-      </c>
-      <c r="AM31">
-        <v>80</v>
-      </c>
-      <c r="AN31">
-        <v>29</v>
-      </c>
-      <c r="AO31">
-        <v>19.5</v>
-      </c>
-      <c r="AP31">
-        <v>13.5</v>
-      </c>
-      <c r="AQ31">
+      <c r="BE31">
+        <v>60</v>
+      </c>
+      <c r="BF31">
+        <v>6</v>
+      </c>
+      <c r="BG31">
+        <v>34</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>3.45</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>7</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>26</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>3.5</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>6.8</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
         <v>10</v>
       </c>
-      <c r="AR31">
-        <v>14.5</v>
-      </c>
-      <c r="AS31">
-        <v>9</v>
-      </c>
-      <c r="AT31">
-        <v>11.5</v>
-      </c>
-      <c r="AU31">
-        <v>7.4</v>
-      </c>
-      <c r="AV31">
-        <v>10</v>
-      </c>
-      <c r="AW31">
-        <v>22</v>
-      </c>
-      <c r="AX31">
-        <v>19</v>
-      </c>
-      <c r="AY31">
-        <v>12</v>
-      </c>
-      <c r="AZ31">
-        <v>14.5</v>
-      </c>
-      <c r="BA31">
-        <v>30</v>
-      </c>
-      <c r="BB31">
-        <v>8.4</v>
-      </c>
-      <c r="BC31">
-        <v>9</v>
-      </c>
-      <c r="BD31">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE31">
-        <v>9</v>
-      </c>
-      <c r="BF31">
-        <v>23</v>
-      </c>
-      <c r="BG31">
-        <v>16</v>
-      </c>
-      <c r="BH31">
-        <v>1000</v>
-      </c>
-      <c r="BI31">
-        <v>1.04</v>
-      </c>
-      <c r="BJ31">
-        <v>1000</v>
-      </c>
-      <c r="BK31">
-        <v>1.04</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>1.04</v>
-      </c>
-      <c r="BN31">
-        <v>1000</v>
-      </c>
-      <c r="BO31">
-        <v>1.04</v>
-      </c>
-      <c r="BP31">
-        <v>1000</v>
-      </c>
-      <c r="BQ31">
-        <v>1.04</v>
-      </c>
-      <c r="BR31">
-        <v>1000</v>
-      </c>
-      <c r="BS31">
-        <v>1.04</v>
-      </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB31" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F32">
-        <v>2.84</v>
+        <v>1.43</v>
       </c>
       <c r="G32">
+        <v>1.44</v>
+      </c>
+      <c r="H32">
+        <v>8</v>
+      </c>
+      <c r="I32">
+        <v>8.4</v>
+      </c>
+      <c r="J32">
+        <v>5.4</v>
+      </c>
+      <c r="K32">
+        <v>5.5</v>
+      </c>
+      <c r="L32">
+        <v>1.33</v>
+      </c>
+      <c r="M32">
+        <v>1.04</v>
+      </c>
+      <c r="N32">
+        <v>5.4</v>
+      </c>
+      <c r="O32">
+        <v>1.22</v>
+      </c>
+      <c r="P32">
+        <v>2.48</v>
+      </c>
+      <c r="Q32">
+        <v>1.66</v>
+      </c>
+      <c r="R32">
+        <v>1.57</v>
+      </c>
+      <c r="S32">
+        <v>2.66</v>
+      </c>
+      <c r="T32">
+        <v>1.93</v>
+      </c>
+      <c r="U32">
+        <v>2.04</v>
+      </c>
+      <c r="V32">
+        <v>1.13</v>
+      </c>
+      <c r="W32">
+        <v>3.25</v>
+      </c>
+      <c r="X32">
+        <v>24</v>
+      </c>
+      <c r="Y32">
+        <v>32</v>
+      </c>
+      <c r="Z32">
+        <v>75</v>
+      </c>
+      <c r="AA32">
+        <v>320</v>
+      </c>
+      <c r="AB32">
+        <v>10.5</v>
+      </c>
+      <c r="AC32">
+        <v>12</v>
+      </c>
+      <c r="AD32">
+        <v>30</v>
+      </c>
+      <c r="AE32">
+        <v>120</v>
+      </c>
+      <c r="AF32">
+        <v>9.4</v>
+      </c>
+      <c r="AG32">
+        <v>10.5</v>
+      </c>
+      <c r="AH32">
+        <v>24</v>
+      </c>
+      <c r="AI32">
+        <v>100</v>
+      </c>
+      <c r="AJ32">
+        <v>12</v>
+      </c>
+      <c r="AK32">
+        <v>13.5</v>
+      </c>
+      <c r="AL32">
+        <v>34</v>
+      </c>
+      <c r="AM32">
+        <v>120</v>
+      </c>
+      <c r="AN32">
+        <v>5.6</v>
+      </c>
+      <c r="AO32">
+        <v>120</v>
+      </c>
+      <c r="AP32">
+        <v>20</v>
+      </c>
+      <c r="AQ32">
+        <v>26</v>
+      </c>
+      <c r="AR32">
+        <v>60</v>
+      </c>
+      <c r="AS32">
+        <v>50</v>
+      </c>
+      <c r="AT32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU32">
+        <v>11</v>
+      </c>
+      <c r="AV32">
+        <v>26</v>
+      </c>
+      <c r="AW32">
+        <v>40</v>
+      </c>
+      <c r="AX32">
+        <v>8.6</v>
+      </c>
+      <c r="AY32">
+        <v>9.6</v>
+      </c>
+      <c r="AZ32">
+        <v>21</v>
+      </c>
+      <c r="BA32">
+        <v>38</v>
+      </c>
+      <c r="BB32">
+        <v>11</v>
+      </c>
+      <c r="BC32">
+        <v>12.5</v>
+      </c>
+      <c r="BD32">
+        <v>27</v>
+      </c>
+      <c r="BE32">
+        <v>42</v>
+      </c>
+      <c r="BF32">
+        <v>5.3</v>
+      </c>
+      <c r="BG32">
+        <v>42</v>
+      </c>
+      <c r="BH32">
         <v>4.2</v>
       </c>
-      <c r="H32">
-        <v>2.16</v>
-      </c>
-      <c r="I32">
-        <v>2.94</v>
-      </c>
-      <c r="J32">
-        <v>2.82</v>
-      </c>
-      <c r="K32">
-        <v>5.3</v>
-      </c>
-      <c r="L32">
-        <v>1.01</v>
-      </c>
-      <c r="M32">
-        <v>1.09</v>
-      </c>
-      <c r="N32">
-        <v>2.42</v>
-      </c>
-      <c r="O32">
-        <v>1.29</v>
-      </c>
-      <c r="P32">
-        <v>1.38</v>
-      </c>
-      <c r="Q32">
-        <v>2.38</v>
-      </c>
-      <c r="R32">
-        <v>1.08</v>
-      </c>
-      <c r="S32">
-        <v>2.86</v>
-      </c>
-      <c r="T32">
-        <v>1.01</v>
-      </c>
-      <c r="U32">
-        <v>1.01</v>
-      </c>
-      <c r="V32">
-        <v>1.52</v>
-      </c>
-      <c r="W32">
-        <v>1.32</v>
-      </c>
-      <c r="X32">
-        <v>1000</v>
-      </c>
-      <c r="Y32">
-        <v>1000</v>
-      </c>
-      <c r="Z32">
-        <v>1000</v>
-      </c>
-      <c r="AA32">
-        <v>1000</v>
-      </c>
-      <c r="AB32">
-        <v>1000</v>
-      </c>
-      <c r="AC32">
-        <v>1000</v>
-      </c>
-      <c r="AD32">
-        <v>1000</v>
-      </c>
-      <c r="AE32">
-        <v>1000</v>
-      </c>
-      <c r="AF32">
-        <v>1000</v>
-      </c>
-      <c r="AG32">
-        <v>1000</v>
-      </c>
-      <c r="AH32">
-        <v>1000</v>
-      </c>
-      <c r="AI32">
-        <v>1000</v>
-      </c>
-      <c r="AJ32">
-        <v>1000</v>
-      </c>
-      <c r="AK32">
-        <v>1000</v>
-      </c>
-      <c r="AL32">
-        <v>1000</v>
-      </c>
-      <c r="AM32">
-        <v>1000</v>
-      </c>
-      <c r="AN32">
-        <v>1000</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>1.01</v>
-      </c>
-      <c r="AQ32">
-        <v>1.01</v>
-      </c>
-      <c r="AR32">
-        <v>1.01</v>
-      </c>
-      <c r="AS32">
-        <v>1.01</v>
-      </c>
-      <c r="AT32">
-        <v>1.01</v>
-      </c>
-      <c r="AU32">
-        <v>1.01</v>
-      </c>
-      <c r="AV32">
-        <v>1.01</v>
-      </c>
-      <c r="AW32">
-        <v>1.01</v>
-      </c>
-      <c r="AX32">
-        <v>1.01</v>
-      </c>
-      <c r="AY32">
-        <v>1.01</v>
-      </c>
-      <c r="AZ32">
-        <v>1.01</v>
-      </c>
-      <c r="BA32">
-        <v>1.01</v>
-      </c>
-      <c r="BB32">
-        <v>1.01</v>
-      </c>
-      <c r="BC32">
-        <v>1.01</v>
-      </c>
-      <c r="BD32">
-        <v>1.01</v>
-      </c>
-      <c r="BE32">
-        <v>1.01</v>
-      </c>
-      <c r="BF32">
-        <v>1.01</v>
-      </c>
-      <c r="BG32">
-        <v>1.01</v>
-      </c>
-      <c r="BH32">
-        <v>3.05</v>
-      </c>
       <c r="BI32">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BL32">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F33">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="H33">
-        <v>4.2</v>
+        <v>2.22</v>
       </c>
       <c r="I33">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="J33">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="K33">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="L33">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="M33">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="N33">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="P33">
-        <v>2.52</v>
+        <v>1.37</v>
       </c>
       <c r="Q33">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>1.61</v>
+        <v>1.08</v>
       </c>
       <c r="S33">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="T33">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
+        <v>1.55</v>
+      </c>
+      <c r="W33">
         <v>1.29</v>
       </c>
-      <c r="W33">
-        <v>2.12</v>
-      </c>
       <c r="X33">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y33">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC33">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD33">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE33">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG33">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH33">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI33">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK33">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL33">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM33">
         <v>1000</v>
       </c>
       <c r="AN33">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS33">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB33">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC33">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD33">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE33">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BF33">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG33">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN33">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F34">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="G34">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="H34">
-        <v>2.04</v>
+        <v>4.3</v>
       </c>
       <c r="I34">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L34">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M34">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N34">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O34">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P34">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="Q34">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R34">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S34">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="T34">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U34">
         <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="X34">
+        <v>23</v>
+      </c>
+      <c r="Y34">
+        <v>22</v>
+      </c>
+      <c r="Z34">
+        <v>38</v>
+      </c>
+      <c r="AA34">
+        <v>90</v>
+      </c>
+      <c r="AB34">
+        <v>13.5</v>
+      </c>
+      <c r="AC34">
+        <v>9.6</v>
+      </c>
+      <c r="AD34">
+        <v>17.5</v>
+      </c>
+      <c r="AE34">
+        <v>44</v>
+      </c>
+      <c r="AF34">
+        <v>14</v>
+      </c>
+      <c r="AG34">
+        <v>10.5</v>
+      </c>
+      <c r="AH34">
+        <v>16</v>
+      </c>
+      <c r="AI34">
+        <v>46</v>
+      </c>
+      <c r="AJ34">
         <v>21</v>
       </c>
-      <c r="Y34">
-        <v>13</v>
-      </c>
-      <c r="Z34">
-        <v>14.5</v>
-      </c>
-      <c r="AA34">
-        <v>24</v>
-      </c>
-      <c r="AB34">
-        <v>18.5</v>
-      </c>
-      <c r="AC34">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD34">
-        <v>11</v>
-      </c>
-      <c r="AE34">
-        <v>19</v>
-      </c>
-      <c r="AF34">
-        <v>29</v>
-      </c>
-      <c r="AG34">
-        <v>15.5</v>
-      </c>
-      <c r="AH34">
-        <v>15.5</v>
-      </c>
-      <c r="AI34">
-        <v>28</v>
-      </c>
-      <c r="AJ34">
-        <v>70</v>
-      </c>
       <c r="AK34">
-        <v>38</v>
+        <v>17.5</v>
       </c>
       <c r="AL34">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AM34">
         <v>65</v>
       </c>
       <c r="AN34">
+        <v>8.4</v>
+      </c>
+      <c r="AO34">
+        <v>36</v>
+      </c>
+      <c r="AP34">
+        <v>20</v>
+      </c>
+      <c r="AQ34">
+        <v>20</v>
+      </c>
+      <c r="AR34">
         <v>32</v>
       </c>
-      <c r="AO34">
-        <v>10.5</v>
-      </c>
-      <c r="AP34">
-        <v>19</v>
-      </c>
-      <c r="AQ34">
+      <c r="AS34">
+        <v>70</v>
+      </c>
+      <c r="AT34">
         <v>11.5</v>
       </c>
-      <c r="AR34">
-        <v>13.5</v>
-      </c>
-      <c r="AS34">
-        <v>22</v>
-      </c>
-      <c r="AT34">
-        <v>17</v>
-      </c>
       <c r="AU34">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV34">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AW34">
-        <v>17.5</v>
+        <v>38</v>
       </c>
       <c r="AX34">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AY34">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34">
         <v>14.5</v>
       </c>
       <c r="BA34">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BB34">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="BC34">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="BD34">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BE34">
         <v>50</v>
       </c>
       <c r="BF34">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BG34">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BH34">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI34">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>6.4</v>
+        <v>1.95</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9062,533 +9074,775 @@
         <v>21</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO34">
-        <v>5.5</v>
+        <v>1.63</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>11</v>
+        <v>2.28</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BT34">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU34">
-        <v>4.1</v>
+        <v>1.86</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>2.26</v>
+        <v>12.5</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB34" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E35" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F35">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="G35">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="H35">
+        <v>2.04</v>
+      </c>
+      <c r="I35">
+        <v>2.06</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+      <c r="K35">
+        <v>4.1</v>
+      </c>
+      <c r="L35">
+        <v>1.34</v>
+      </c>
+      <c r="M35">
+        <v>1.04</v>
+      </c>
+      <c r="N35">
+        <v>5.3</v>
+      </c>
+      <c r="O35">
+        <v>1.22</v>
+      </c>
+      <c r="P35">
+        <v>2.42</v>
+      </c>
+      <c r="Q35">
+        <v>1.67</v>
+      </c>
+      <c r="R35">
+        <v>1.58</v>
+      </c>
+      <c r="S35">
+        <v>2.68</v>
+      </c>
+      <c r="T35">
+        <v>1.62</v>
+      </c>
+      <c r="U35">
         <v>2.5</v>
       </c>
-      <c r="I35">
-        <v>3.85</v>
-      </c>
-      <c r="J35">
-        <v>3.05</v>
-      </c>
-      <c r="K35">
-        <v>950</v>
-      </c>
-      <c r="L35">
-        <v>1.01</v>
-      </c>
-      <c r="M35">
-        <v>1.01</v>
-      </c>
-      <c r="N35">
-        <v>3.25</v>
-      </c>
-      <c r="O35">
-        <v>1.17</v>
-      </c>
-      <c r="P35">
-        <v>1.95</v>
-      </c>
-      <c r="Q35">
-        <v>1.64</v>
-      </c>
-      <c r="R35">
-        <v>1.36</v>
-      </c>
-      <c r="S35">
-        <v>2.32</v>
-      </c>
-      <c r="T35">
-        <v>1.01</v>
-      </c>
-      <c r="U35">
-        <v>1.01</v>
-      </c>
       <c r="V35">
+        <v>1.94</v>
+      </c>
+      <c r="W35">
         <v>1.35</v>
       </c>
-      <c r="W35">
-        <v>1.56</v>
-      </c>
       <c r="X35">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y35">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z35">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA35">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB35">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC35">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF35">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG35">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH35">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI35">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ35">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK35">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL35">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM35">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN35">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO35">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP35">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AQ35">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR35">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS35">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT35">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AU35">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AV35">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW35">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AX35">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="AY35">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AZ35">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="BB35">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BC35">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BD35">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BE35">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BF35">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BG35">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH35">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI35">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ35">
         <v>1000</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO35">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP35">
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BT35">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB35" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36">
+        <v>2.24</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>2.5</v>
+      </c>
+      <c r="I36">
+        <v>3.65</v>
+      </c>
+      <c r="J36">
+        <v>3.35</v>
+      </c>
+      <c r="K36">
+        <v>4.2</v>
+      </c>
+      <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.01</v>
+      </c>
+      <c r="N36">
+        <v>3.6</v>
+      </c>
+      <c r="O36">
+        <v>1.17</v>
+      </c>
+      <c r="P36">
+        <v>2.18</v>
+      </c>
+      <c r="Q36">
+        <v>1.54</v>
+      </c>
+      <c r="R36">
+        <v>1.39</v>
+      </c>
+      <c r="S36">
+        <v>2.28</v>
+      </c>
+      <c r="T36">
+        <v>1.01</v>
+      </c>
+      <c r="U36">
+        <v>1.01</v>
+      </c>
+      <c r="V36">
+        <v>1.39</v>
+      </c>
+      <c r="W36">
+        <v>1.5</v>
+      </c>
+      <c r="X36">
+        <v>1000</v>
+      </c>
+      <c r="Y36">
+        <v>1000</v>
+      </c>
+      <c r="Z36">
+        <v>1000</v>
+      </c>
+      <c r="AA36">
+        <v>1000</v>
+      </c>
+      <c r="AB36">
+        <v>1000</v>
+      </c>
+      <c r="AC36">
+        <v>1000</v>
+      </c>
+      <c r="AD36">
+        <v>1000</v>
+      </c>
+      <c r="AE36">
+        <v>1000</v>
+      </c>
+      <c r="AF36">
+        <v>1000</v>
+      </c>
+      <c r="AG36">
+        <v>1000</v>
+      </c>
+      <c r="AH36">
+        <v>1000</v>
+      </c>
+      <c r="AI36">
+        <v>1000</v>
+      </c>
+      <c r="AJ36">
+        <v>1000</v>
+      </c>
+      <c r="AK36">
+        <v>1000</v>
+      </c>
+      <c r="AL36">
+        <v>1000</v>
+      </c>
+      <c r="AM36">
+        <v>1000</v>
+      </c>
+      <c r="AN36">
+        <v>1000</v>
+      </c>
+      <c r="AO36">
+        <v>1000</v>
+      </c>
+      <c r="AP36">
+        <v>1.03</v>
+      </c>
+      <c r="AQ36">
+        <v>1.03</v>
+      </c>
+      <c r="AR36">
+        <v>1.03</v>
+      </c>
+      <c r="AS36">
+        <v>1.03</v>
+      </c>
+      <c r="AT36">
+        <v>1.03</v>
+      </c>
+      <c r="AU36">
+        <v>1.03</v>
+      </c>
+      <c r="AV36">
+        <v>1.03</v>
+      </c>
+      <c r="AW36">
+        <v>1.03</v>
+      </c>
+      <c r="AX36">
+        <v>1.03</v>
+      </c>
+      <c r="AY36">
+        <v>1.03</v>
+      </c>
+      <c r="AZ36">
+        <v>1.03</v>
+      </c>
+      <c r="BA36">
+        <v>1.03</v>
+      </c>
+      <c r="BB36">
+        <v>1.03</v>
+      </c>
+      <c r="BC36">
+        <v>1.03</v>
+      </c>
+      <c r="BD36">
+        <v>1.03</v>
+      </c>
+      <c r="BE36">
+        <v>1.03</v>
+      </c>
+      <c r="BF36">
+        <v>1.01</v>
+      </c>
+      <c r="BG36">
+        <v>1.01</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
+        <v>1.01</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
+        <v>1.01</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>1.01</v>
+      </c>
+      <c r="BN36">
+        <v>1000</v>
+      </c>
+      <c r="BO36">
+        <v>1.01</v>
+      </c>
+      <c r="BP36">
+        <v>1000</v>
+      </c>
+      <c r="BQ36">
+        <v>1.01</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>1.01</v>
+      </c>
+      <c r="BT36">
+        <v>1000</v>
+      </c>
+      <c r="BU36">
+        <v>1.01</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
+        <v>1.01</v>
+      </c>
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
+        <v>1.01</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
         <v>82</v>
       </c>
-      <c r="B36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" t="s">
-        <v>105</v>
-      </c>
-      <c r="D36" t="s">
-        <v>140</v>
-      </c>
-      <c r="E36" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36">
-        <v>2.06</v>
-      </c>
-      <c r="G36">
+      <c r="B37" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F37">
+        <v>2.08</v>
+      </c>
+      <c r="G37">
         <v>2.52</v>
       </c>
-      <c r="H36">
-        <v>3.1</v>
-      </c>
-      <c r="I36">
-        <v>4.6</v>
-      </c>
-      <c r="J36">
-        <v>2.58</v>
-      </c>
-      <c r="K36">
-        <v>500</v>
-      </c>
-      <c r="L36">
-        <v>1.01</v>
-      </c>
-      <c r="M36">
-        <v>1.06</v>
-      </c>
-      <c r="N36">
-        <v>2.54</v>
-      </c>
-      <c r="O36">
+      <c r="H37">
+        <v>3.2</v>
+      </c>
+      <c r="I37">
+        <v>4.7</v>
+      </c>
+      <c r="J37">
+        <v>2.56</v>
+      </c>
+      <c r="K37">
+        <v>5.3</v>
+      </c>
+      <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.05</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="O37">
         <v>1.42</v>
       </c>
-      <c r="P36">
+      <c r="P37">
         <v>1.56</v>
       </c>
-      <c r="Q36">
+      <c r="Q37">
         <v>2.04</v>
       </c>
-      <c r="R36">
+      <c r="R37">
         <v>1.2</v>
       </c>
-      <c r="S36">
+      <c r="S37">
         <v>3.75</v>
       </c>
-      <c r="T36">
-        <v>1.01</v>
-      </c>
-      <c r="U36">
-        <v>1.01</v>
-      </c>
-      <c r="V36">
-        <v>1.29</v>
-      </c>
-      <c r="W36">
+      <c r="T37">
+        <v>1.01</v>
+      </c>
+      <c r="U37">
+        <v>1.01</v>
+      </c>
+      <c r="V37">
+        <v>1.3</v>
+      </c>
+      <c r="W37">
         <v>1.65</v>
       </c>
-      <c r="X36">
-        <v>1000</v>
-      </c>
-      <c r="Y36">
-        <v>1000</v>
-      </c>
-      <c r="Z36">
-        <v>1000</v>
-      </c>
-      <c r="AA36">
-        <v>1000</v>
-      </c>
-      <c r="AB36">
-        <v>1000</v>
-      </c>
-      <c r="AC36">
-        <v>1000</v>
-      </c>
-      <c r="AD36">
-        <v>1000</v>
-      </c>
-      <c r="AE36">
-        <v>1000</v>
-      </c>
-      <c r="AF36">
-        <v>1000</v>
-      </c>
-      <c r="AG36">
-        <v>1000</v>
-      </c>
-      <c r="AH36">
-        <v>1000</v>
-      </c>
-      <c r="AI36">
-        <v>1000</v>
-      </c>
-      <c r="AJ36">
-        <v>1000</v>
-      </c>
-      <c r="AK36">
-        <v>1000</v>
-      </c>
-      <c r="AL36">
-        <v>1000</v>
-      </c>
-      <c r="AM36">
-        <v>1000</v>
-      </c>
-      <c r="AN36">
-        <v>1000</v>
-      </c>
-      <c r="AO36">
-        <v>1000</v>
-      </c>
-      <c r="AP36">
-        <v>1.01</v>
-      </c>
-      <c r="AQ36">
-        <v>1.01</v>
-      </c>
-      <c r="AR36">
-        <v>1.01</v>
-      </c>
-      <c r="AS36">
-        <v>1.01</v>
-      </c>
-      <c r="AT36">
-        <v>1.01</v>
-      </c>
-      <c r="AU36">
-        <v>1.01</v>
-      </c>
-      <c r="AV36">
-        <v>1.01</v>
-      </c>
-      <c r="AW36">
-        <v>1.01</v>
-      </c>
-      <c r="AX36">
-        <v>1.01</v>
-      </c>
-      <c r="AY36">
-        <v>1.01</v>
-      </c>
-      <c r="AZ36">
-        <v>1.01</v>
-      </c>
-      <c r="BA36">
-        <v>1.01</v>
-      </c>
-      <c r="BB36">
-        <v>1.01</v>
-      </c>
-      <c r="BC36">
-        <v>1.01</v>
-      </c>
-      <c r="BD36">
-        <v>1.01</v>
-      </c>
-      <c r="BE36">
-        <v>1.01</v>
-      </c>
-      <c r="BF36">
-        <v>1.01</v>
-      </c>
-      <c r="BG36">
-        <v>1.01</v>
-      </c>
-      <c r="BH36">
-        <v>1000</v>
-      </c>
-      <c r="BI36">
-        <v>1.01</v>
-      </c>
-      <c r="BJ36">
-        <v>1000</v>
-      </c>
-      <c r="BK36">
-        <v>1.01</v>
-      </c>
-      <c r="BL36">
-        <v>1000</v>
-      </c>
-      <c r="BM36">
-        <v>1.01</v>
-      </c>
-      <c r="BN36">
-        <v>1000</v>
-      </c>
-      <c r="BO36">
-        <v>1.01</v>
-      </c>
-      <c r="BP36">
-        <v>1000</v>
-      </c>
-      <c r="BQ36">
-        <v>1.01</v>
-      </c>
-      <c r="BR36">
-        <v>1000</v>
-      </c>
-      <c r="BS36">
-        <v>1.01</v>
-      </c>
-      <c r="BT36">
-        <v>1000</v>
-      </c>
-      <c r="BU36">
-        <v>1.01</v>
-      </c>
-      <c r="BV36">
-        <v>1000</v>
-      </c>
-      <c r="BW36">
-        <v>1.01</v>
-      </c>
-      <c r="BX36">
-        <v>1000</v>
-      </c>
-      <c r="BY36">
-        <v>1.01</v>
-      </c>
-      <c r="BZ36">
-        <v>1000</v>
-      </c>
-      <c r="CA36">
-        <v>1.01</v>
-      </c>
-      <c r="CB36" t="s">
-        <v>176</v>
+      <c r="X37">
+        <v>1000</v>
+      </c>
+      <c r="Y37">
+        <v>1000</v>
+      </c>
+      <c r="Z37">
+        <v>1000</v>
+      </c>
+      <c r="AA37">
+        <v>1000</v>
+      </c>
+      <c r="AB37">
+        <v>1000</v>
+      </c>
+      <c r="AC37">
+        <v>1000</v>
+      </c>
+      <c r="AD37">
+        <v>1000</v>
+      </c>
+      <c r="AE37">
+        <v>1000</v>
+      </c>
+      <c r="AF37">
+        <v>1000</v>
+      </c>
+      <c r="AG37">
+        <v>1000</v>
+      </c>
+      <c r="AH37">
+        <v>1000</v>
+      </c>
+      <c r="AI37">
+        <v>1000</v>
+      </c>
+      <c r="AJ37">
+        <v>1000</v>
+      </c>
+      <c r="AK37">
+        <v>1000</v>
+      </c>
+      <c r="AL37">
+        <v>1000</v>
+      </c>
+      <c r="AM37">
+        <v>1000</v>
+      </c>
+      <c r="AN37">
+        <v>1000</v>
+      </c>
+      <c r="AO37">
+        <v>1000</v>
+      </c>
+      <c r="AP37">
+        <v>1.01</v>
+      </c>
+      <c r="AQ37">
+        <v>1.01</v>
+      </c>
+      <c r="AR37">
+        <v>1.01</v>
+      </c>
+      <c r="AS37">
+        <v>1.01</v>
+      </c>
+      <c r="AT37">
+        <v>1.01</v>
+      </c>
+      <c r="AU37">
+        <v>1.01</v>
+      </c>
+      <c r="AV37">
+        <v>1.01</v>
+      </c>
+      <c r="AW37">
+        <v>1.01</v>
+      </c>
+      <c r="AX37">
+        <v>1.01</v>
+      </c>
+      <c r="AY37">
+        <v>1.01</v>
+      </c>
+      <c r="AZ37">
+        <v>1.01</v>
+      </c>
+      <c r="BA37">
+        <v>1.01</v>
+      </c>
+      <c r="BB37">
+        <v>1.01</v>
+      </c>
+      <c r="BC37">
+        <v>1.01</v>
+      </c>
+      <c r="BD37">
+        <v>1.01</v>
+      </c>
+      <c r="BE37">
+        <v>1.01</v>
+      </c>
+      <c r="BF37">
+        <v>1.01</v>
+      </c>
+      <c r="BG37">
+        <v>1.01</v>
+      </c>
+      <c r="BH37">
+        <v>1000</v>
+      </c>
+      <c r="BI37">
+        <v>1.01</v>
+      </c>
+      <c r="BJ37">
+        <v>1000</v>
+      </c>
+      <c r="BK37">
+        <v>1.01</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>1.01</v>
+      </c>
+      <c r="BN37">
+        <v>1000</v>
+      </c>
+      <c r="BO37">
+        <v>1.01</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>1.01</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>1.01</v>
+      </c>
+      <c r="BT37">
+        <v>1000</v>
+      </c>
+      <c r="BU37">
+        <v>1.01</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>1.01</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -280,12 +280,12 @@
     <t>Tunisian Ligue Professionelle 1</t>
   </si>
   <si>
+    <t>Estonian Premier League</t>
+  </si>
+  <si>
     <t>Georgian Umaglesi Liga</t>
   </si>
   <si>
-    <t>Estonian Premier League</t>
-  </si>
-  <si>
     <t>UEFA Europa League</t>
   </si>
   <si>
@@ -385,12 +385,12 @@
     <t>FK Atyrau</t>
   </si>
   <si>
+    <t>FCI Tallinn</t>
+  </si>
+  <si>
     <t>FC Iberia 1999</t>
   </si>
   <si>
-    <t>FCI Tallinn</t>
-  </si>
-  <si>
     <t>FK Loznica</t>
   </si>
   <si>
@@ -400,15 +400,15 @@
     <t>PFC Levski Sofia</t>
   </si>
   <si>
+    <t>Skovde AIK</t>
+  </si>
+  <si>
     <t>FC Stockholm Internazionale</t>
   </si>
   <si>
     <t>Rosengard</t>
   </si>
   <si>
-    <t>Skovde AIK</t>
-  </si>
-  <si>
     <t>Vasalunds IF</t>
   </si>
   <si>
@@ -451,24 +451,24 @@
     <t>Real Sociedad</t>
   </si>
   <si>
+    <t>Lillestrom</t>
+  </si>
+  <si>
     <t>Celtic</t>
   </si>
   <si>
+    <t>Cr Temouchent</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Besiktas</t>
+  </si>
+  <si>
     <t>Juventus</t>
   </si>
   <si>
-    <t>Cr Temouchent</t>
-  </si>
-  <si>
-    <t>Lillestrom</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Besiktas</t>
-  </si>
-  <si>
     <t>Malaga</t>
   </si>
   <si>
@@ -511,12 +511,12 @@
     <t>FC Ordabasy</t>
   </si>
   <si>
+    <t>Tammeka Tartu</t>
+  </si>
+  <si>
     <t>Dila Gori</t>
   </si>
   <si>
-    <t>Tammeka Tartu</t>
-  </si>
-  <si>
     <t>FK Javor Ivanjica</t>
   </si>
   <si>
@@ -526,15 +526,15 @@
     <t>Red Bull Salzburg</t>
   </si>
   <si>
+    <t>FC Trollhattan</t>
+  </si>
+  <si>
     <t>IFK Stocksund</t>
   </si>
   <si>
     <t>Trelleborgs</t>
   </si>
   <si>
-    <t>FC Trollhattan</t>
-  </si>
-  <si>
     <t>Hammarby TFF</t>
   </si>
   <si>
@@ -577,24 +577,24 @@
     <t>Bournemouth</t>
   </si>
   <si>
+    <t>Torreense</t>
+  </si>
+  <si>
     <t>Ferencvaros</t>
   </si>
   <si>
+    <t>Kabylie</t>
+  </si>
+  <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
     <t>NEC Nijmegen</t>
   </si>
   <si>
-    <t>Kabylie</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Lech Poznan</t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
     <t>Villarreal</t>
   </si>
   <si>
@@ -607,7 +607,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 16:15:38</t>
+    <t>2026-09-16 18:32:21</t>
   </si>
 </sst>
 </file>
@@ -1201,226 +1201,226 @@
         <v>155</v>
       </c>
       <c r="F2">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="G2">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="K2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M2">
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="Q2">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R2">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="S2">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T2">
         <v>1.64</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="X2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA2">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AB2">
+        <v>14.5</v>
+      </c>
+      <c r="AC2">
         <v>14</v>
       </c>
-      <c r="AC2">
-        <v>12.5</v>
-      </c>
       <c r="AD2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AL2">
         <v>26</v>
       </c>
       <c r="AM2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN2">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO2">
+        <v>65</v>
+      </c>
+      <c r="AP2">
+        <v>25</v>
+      </c>
+      <c r="AQ2">
+        <v>30</v>
+      </c>
+      <c r="AR2">
         <v>55</v>
       </c>
-      <c r="AP2">
-        <v>23</v>
-      </c>
-      <c r="AQ2">
-        <v>27</v>
-      </c>
-      <c r="AR2">
-        <v>46</v>
-      </c>
       <c r="AS2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AW2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX2">
         <v>10</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD2">
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF2">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BH2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BI2">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM2">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
         <v>3.95</v>
       </c>
       <c r="BP2">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BQ2">
-        <v>3.75</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BS2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BT2">
+        <v>13</v>
+      </c>
+      <c r="BU2">
+        <v>4.1</v>
+      </c>
+      <c r="BV2">
+        <v>55</v>
+      </c>
+      <c r="BW2">
+        <v>5.5</v>
+      </c>
+      <c r="BX2">
+        <v>50</v>
+      </c>
+      <c r="BY2">
+        <v>5.4</v>
+      </c>
+      <c r="BZ2">
         <v>11.5</v>
       </c>
-      <c r="BU2">
-        <v>3.8</v>
-      </c>
-      <c r="BV2">
-        <v>50</v>
-      </c>
-      <c r="BW2">
-        <v>5.1</v>
-      </c>
-      <c r="BX2">
-        <v>44</v>
-      </c>
-      <c r="BY2">
-        <v>5</v>
-      </c>
-      <c r="BZ2">
-        <v>13.5</v>
-      </c>
       <c r="CA2">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>197</v>
@@ -1452,43 +1452,43 @@
         <v>4.8</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
         <v>2.98</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M3">
         <v>1.18</v>
       </c>
       <c r="N3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="P3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R3">
         <v>1.13</v>
       </c>
       <c r="S3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="T3">
         <v>2.66</v>
       </c>
       <c r="U3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
         <v>1.25</v>
@@ -1500,19 +1500,19 @@
         <v>6.4</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>34</v>
       </c>
       <c r="AA3">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB3">
         <v>5.4</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
         <v>24</v>
@@ -1530,10 +1530,10 @@
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK3">
         <v>38</v>
@@ -1545,22 +1545,22 @@
         <v>400</v>
       </c>
       <c r="AN3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO3">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AP3">
         <v>6</v>
       </c>
       <c r="AQ3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AT3">
         <v>5.3</v>
@@ -1569,13 +1569,13 @@
         <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AX3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY3">
         <v>12</v>
@@ -1584,28 +1584,28 @@
         <v>30</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BB3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC3">
         <v>34</v>
       </c>
       <c r="BD3">
+        <v>65</v>
+      </c>
+      <c r="BE3">
         <v>22</v>
       </c>
-      <c r="BE3">
-        <v>18.5</v>
-      </c>
       <c r="BF3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BI3">
         <v>2.16</v>
@@ -1614,37 +1614,37 @@
         <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="BM3">
         <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
         <v>8.6</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS3">
         <v>11.5</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
         <v>65</v>
@@ -1656,13 +1656,13 @@
         <v>110</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
         <v>197</v>
@@ -1685,220 +1685,220 @@
         <v>157</v>
       </c>
       <c r="F4">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="O4">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S4">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="T4">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U4">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
+        <v>28</v>
+      </c>
+      <c r="AA4">
+        <v>55</v>
+      </c>
+      <c r="AB4">
+        <v>15</v>
+      </c>
+      <c r="AC4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>16.5</v>
+      </c>
+      <c r="AE4">
+        <v>38</v>
+      </c>
+      <c r="AF4">
+        <v>18</v>
+      </c>
+      <c r="AG4">
+        <v>12</v>
+      </c>
+      <c r="AH4">
+        <v>16</v>
+      </c>
+      <c r="AI4">
+        <v>38</v>
+      </c>
+      <c r="AJ4">
+        <v>32</v>
+      </c>
+      <c r="AK4">
         <v>23</v>
-      </c>
-      <c r="AA4">
-        <v>46</v>
-      </c>
-      <c r="AB4">
-        <v>18</v>
-      </c>
-      <c r="AC4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD4">
-        <v>13.5</v>
-      </c>
-      <c r="AE4">
-        <v>26</v>
-      </c>
-      <c r="AF4">
-        <v>25</v>
-      </c>
-      <c r="AG4">
-        <v>13.5</v>
-      </c>
-      <c r="AH4">
-        <v>17</v>
-      </c>
-      <c r="AI4">
-        <v>34</v>
-      </c>
-      <c r="AJ4">
-        <v>40</v>
-      </c>
-      <c r="AK4">
-        <v>28</v>
       </c>
       <c r="AL4">
         <v>34</v>
       </c>
       <c r="AM4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO4">
+        <v>22</v>
+      </c>
+      <c r="AP4">
+        <v>18</v>
+      </c>
+      <c r="AQ4">
         <v>15</v>
       </c>
-      <c r="AP4">
-        <v>17.5</v>
-      </c>
-      <c r="AQ4">
-        <v>15.5</v>
-      </c>
       <c r="AR4">
+        <v>21</v>
+      </c>
+      <c r="AS4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT4">
+        <v>12.5</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>12</v>
+      </c>
+      <c r="AW4">
+        <v>7.6</v>
+      </c>
+      <c r="AX4">
+        <v>15</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>13</v>
+      </c>
+      <c r="BA4">
+        <v>24</v>
+      </c>
+      <c r="BB4">
+        <v>7.4</v>
+      </c>
+      <c r="BC4">
         <v>18.5</v>
       </c>
-      <c r="AS4">
-        <v>34</v>
-      </c>
-      <c r="AT4">
-        <v>15</v>
-      </c>
-      <c r="AU4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV4">
-        <v>11.5</v>
-      </c>
-      <c r="AW4">
-        <v>22</v>
-      </c>
-      <c r="AX4">
-        <v>18.5</v>
-      </c>
-      <c r="AY4">
-        <v>11</v>
-      </c>
-      <c r="AZ4">
-        <v>12</v>
-      </c>
-      <c r="BA4">
-        <v>19</v>
-      </c>
-      <c r="BB4">
-        <v>29</v>
-      </c>
-      <c r="BC4">
-        <v>21</v>
-      </c>
       <c r="BD4">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG4">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BH4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI4">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4">
         <v>6.6</v>
       </c>
       <c r="BL4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BN4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BQ4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BR4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS4">
         <v>18</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
+        <v>23</v>
+      </c>
+      <c r="BW4">
+        <v>15</v>
+      </c>
+      <c r="BX4">
+        <v>34</v>
+      </c>
+      <c r="BY4">
         <v>21</v>
-      </c>
-      <c r="BW4">
-        <v>13</v>
-      </c>
-      <c r="BX4">
-        <v>28</v>
-      </c>
-      <c r="BY4">
-        <v>18</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1927,88 +1927,88 @@
         <v>158</v>
       </c>
       <c r="F5">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="G5">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H5">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I5">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P5">
+        <v>1.97</v>
+      </c>
+      <c r="Q5">
+        <v>1.97</v>
+      </c>
+      <c r="R5">
+        <v>1.37</v>
+      </c>
+      <c r="S5">
+        <v>3.55</v>
+      </c>
+      <c r="T5">
         <v>1.94</v>
       </c>
-      <c r="Q5">
-        <v>2</v>
-      </c>
-      <c r="R5">
-        <v>1.36</v>
-      </c>
-      <c r="S5">
-        <v>3.6</v>
-      </c>
-      <c r="T5">
-        <v>1.9</v>
-      </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V5">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA5">
+        <v>17</v>
+      </c>
+      <c r="AB5">
         <v>19</v>
       </c>
-      <c r="AB5">
-        <v>17.5</v>
-      </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF5">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AG5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH5">
         <v>22</v>
@@ -2017,37 +2017,37 @@
         <v>38</v>
       </c>
       <c r="AJ5">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AK5">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AO5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AR5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS5">
+        <v>15</v>
+      </c>
+      <c r="AT5">
         <v>17</v>
-      </c>
-      <c r="AT5">
-        <v>16</v>
       </c>
       <c r="AU5">
         <v>8</v>
@@ -2056,97 +2056,97 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY5">
         <v>18.5</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
         <v>32</v>
       </c>
       <c r="BB5">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="BC5">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BD5">
         <v>65</v>
       </c>
       <c r="BE5">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BF5">
-        <v>13.5</v>
+        <v>75</v>
       </c>
       <c r="BG5">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.9</v>
       </c>
       <c r="BI5">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL5">
         <v>170</v>
       </c>
       <c r="BM5">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO5">
+        <v>8</v>
+      </c>
+      <c r="BP5">
+        <v>60</v>
+      </c>
+      <c r="BQ5">
         <v>8.6</v>
       </c>
-      <c r="BO5">
-        <v>4.3</v>
-      </c>
-      <c r="BP5">
-        <v>50</v>
-      </c>
-      <c r="BQ5">
-        <v>7.2</v>
-      </c>
       <c r="BR5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT5">
+        <v>4.2</v>
+      </c>
+      <c r="BU5">
+        <v>3.9</v>
+      </c>
+      <c r="BV5">
+        <v>11.5</v>
+      </c>
+      <c r="BW5">
+        <v>10</v>
+      </c>
+      <c r="BX5">
+        <v>27</v>
+      </c>
+      <c r="BY5">
         <v>7.4</v>
       </c>
-      <c r="BT5">
-        <v>4.4</v>
-      </c>
-      <c r="BU5">
-        <v>3.4</v>
-      </c>
-      <c r="BV5">
-        <v>12.5</v>
-      </c>
-      <c r="BW5">
-        <v>5.1</v>
-      </c>
-      <c r="BX5">
-        <v>32</v>
-      </c>
-      <c r="BY5">
-        <v>6.8</v>
-      </c>
       <c r="BZ5">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="CA5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
         <v>197</v>
@@ -2169,226 +2169,226 @@
         <v>159</v>
       </c>
       <c r="F6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G6">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="K6">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="L6">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N6">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="P6">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R6">
         <v>1.11</v>
       </c>
       <c r="S6">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="T6">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U6">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="V6">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X6">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z6">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="AC6">
+        <v>970</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>970</v>
+      </c>
+      <c r="AG6">
+        <v>970</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>5.2</v>
+      </c>
+      <c r="AQ6">
+        <v>6.8</v>
+      </c>
+      <c r="AR6">
+        <v>1.87</v>
+      </c>
+      <c r="AS6">
+        <v>1.87</v>
+      </c>
+      <c r="AT6">
+        <v>4.8</v>
+      </c>
+      <c r="AU6">
+        <v>5.1</v>
+      </c>
+      <c r="AV6">
+        <v>1.87</v>
+      </c>
+      <c r="AW6">
+        <v>1.87</v>
+      </c>
+      <c r="AX6">
         <v>7.4</v>
       </c>
-      <c r="AD6">
-        <v>26</v>
-      </c>
-      <c r="AE6">
-        <v>130</v>
-      </c>
-      <c r="AF6">
-        <v>11.5</v>
-      </c>
-      <c r="AG6">
-        <v>13</v>
-      </c>
-      <c r="AH6">
-        <v>34</v>
-      </c>
-      <c r="AI6">
-        <v>160</v>
-      </c>
-      <c r="AJ6">
-        <v>34</v>
-      </c>
-      <c r="AK6">
-        <v>40</v>
-      </c>
-      <c r="AL6">
-        <v>90</v>
-      </c>
-      <c r="AM6">
-        <v>330</v>
-      </c>
-      <c r="AN6">
-        <v>40</v>
-      </c>
-      <c r="AO6">
-        <v>230</v>
-      </c>
-      <c r="AP6">
-        <v>6.6</v>
-      </c>
-      <c r="AQ6">
-        <v>10</v>
-      </c>
-      <c r="AR6">
-        <v>8.4</v>
-      </c>
-      <c r="AS6">
-        <v>9</v>
-      </c>
-      <c r="AT6">
-        <v>5.5</v>
-      </c>
-      <c r="AU6">
-        <v>6.6</v>
-      </c>
-      <c r="AV6">
-        <v>17</v>
-      </c>
-      <c r="AW6">
-        <v>9.6</v>
-      </c>
-      <c r="AX6">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY6">
-        <v>10.5</v>
+        <v>1.75</v>
       </c>
       <c r="AZ6">
-        <v>8</v>
+        <v>1.87</v>
       </c>
       <c r="BA6">
-        <v>9</v>
+        <v>1.87</v>
       </c>
       <c r="BB6">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BC6">
-        <v>8.199999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="BD6">
-        <v>9.4</v>
+        <v>1.87</v>
       </c>
       <c r="BE6">
-        <v>9.4</v>
+        <v>1.87</v>
       </c>
       <c r="BF6">
-        <v>8.199999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="BG6">
-        <v>9.199999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="CB6" t="s">
         <v>197</v>
@@ -2411,22 +2411,22 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G7">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H7">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2441,28 +2441,28 @@
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U7">
         <v>2.26</v>
       </c>
       <c r="V7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X7">
         <v>21</v>
@@ -2477,10 +2477,10 @@
         <v>42</v>
       </c>
       <c r="AB7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
         <v>14</v>
@@ -2489,10 +2489,10 @@
         <v>30</v>
       </c>
       <c r="AF7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH7">
         <v>18</v>
@@ -2501,76 +2501,76 @@
         <v>40</v>
       </c>
       <c r="AJ7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL7">
         <v>40</v>
       </c>
       <c r="AM7">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR7">
         <v>14.5</v>
       </c>
       <c r="AS7">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="AT7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
         <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW7">
         <v>21</v>
       </c>
       <c r="AX7">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB7">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF7">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2653,28 +2653,28 @@
         <v>161</v>
       </c>
       <c r="F8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G8">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H8">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J8">
         <v>3.65</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
         <v>4.6</v>
@@ -2689,25 +2689,25 @@
         <v>1.66</v>
       </c>
       <c r="R8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S8">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T8">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U8">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
         <v>1.8</v>
       </c>
       <c r="X8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8">
         <v>19.5</v>
@@ -2722,7 +2722,7 @@
         <v>14.5</v>
       </c>
       <c r="AC8">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
         <v>17.5</v>
@@ -2737,43 +2737,43 @@
         <v>13</v>
       </c>
       <c r="AH8">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI8">
         <v>48</v>
       </c>
       <c r="AJ8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM8">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN8">
         <v>14</v>
       </c>
       <c r="AO8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP8">
         <v>15.5</v>
       </c>
       <c r="AQ8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AS8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8">
         <v>7.8</v>
@@ -2782,31 +2782,31 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="AX8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC8">
         <v>15.5</v>
       </c>
       <c r="BD8">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF8">
         <v>9.4</v>
@@ -2895,22 +2895,22 @@
         <v>162</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2919,13 +2919,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.07</v>
+        <v>2.78</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
@@ -2934,7 +2934,7 @@
         <v>1.06</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2943,10 +2943,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2964,7 +2964,7 @@
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -3149,40 +3149,40 @@
         <v>3.1</v>
       </c>
       <c r="J10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K10">
         <v>2.96</v>
       </c>
       <c r="L10">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N10">
         <v>2.08</v>
       </c>
       <c r="O10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="P10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Q10">
         <v>3.3</v>
       </c>
       <c r="R10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="S10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="T10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V10">
         <v>1.48</v>
@@ -3191,16 +3191,16 @@
         <v>1.35</v>
       </c>
       <c r="X10">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y10">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z10">
         <v>17</v>
       </c>
       <c r="AA10">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB10">
         <v>9.199999999999999</v>
@@ -3212,40 +3212,40 @@
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AF10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI10">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AJ10">
-        <v>95</v>
+        <v>420</v>
       </c>
       <c r="AK10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL10">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AM10">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AN10">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO10">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="AP10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10">
         <v>5.9</v>
@@ -3254,10 +3254,10 @@
         <v>12.5</v>
       </c>
       <c r="AS10">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AT10">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3266,22 +3266,22 @@
         <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AX10">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY10">
         <v>13.5</v>
       </c>
       <c r="AZ10">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BA10">
         <v>6.6</v>
       </c>
       <c r="BB10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC10">
         <v>6.4</v>
@@ -3296,10 +3296,10 @@
         <v>6.6</v>
       </c>
       <c r="BG10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI10">
         <v>1.01</v>
@@ -3379,7 +3379,7 @@
         <v>164</v>
       </c>
       <c r="F11">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G11">
         <v>9.4</v>
@@ -3388,25 +3388,25 @@
         <v>1.47</v>
       </c>
       <c r="I11">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="J11">
         <v>4.1</v>
       </c>
       <c r="K11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M11">
         <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
         <v>1.81</v>
@@ -3427,28 +3427,28 @@
         <v>1.73</v>
       </c>
       <c r="V11">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="W11">
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y11">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z11">
         <v>10.5</v>
       </c>
       <c r="AA11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB11">
         <v>28</v>
       </c>
       <c r="AC11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD11">
         <v>12.5</v>
@@ -3484,7 +3484,7 @@
         <v>270</v>
       </c>
       <c r="AO11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP11">
         <v>11.5</v>
@@ -3499,10 +3499,10 @@
         <v>11.5</v>
       </c>
       <c r="AT11">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU11">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11">
         <v>8.4</v>
@@ -3511,34 +3511,34 @@
         <v>14.5</v>
       </c>
       <c r="AX11">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AY11">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="BA11">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BC11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BD11">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BG11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3612,7 +3612,7 @@
         <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>123</v>
@@ -3621,166 +3621,166 @@
         <v>165</v>
       </c>
       <c r="F12">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="G12">
-        <v>2.48</v>
+        <v>1.27</v>
       </c>
       <c r="H12">
-        <v>3.15</v>
+        <v>15</v>
       </c>
       <c r="I12">
-        <v>3.95</v>
+        <v>16.5</v>
       </c>
       <c r="J12">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="O12">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q12">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="R12">
-        <v>1.35</v>
+        <v>2.16</v>
       </c>
       <c r="S12">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="T12">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="U12">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="W12">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="X12">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="Y12">
+        <v>95</v>
+      </c>
+      <c r="Z12">
+        <v>210</v>
+      </c>
+      <c r="AA12">
+        <v>620</v>
+      </c>
+      <c r="AB12">
+        <v>18.5</v>
+      </c>
+      <c r="AC12">
+        <v>22</v>
+      </c>
+      <c r="AD12">
+        <v>70</v>
+      </c>
+      <c r="AE12">
+        <v>230</v>
+      </c>
+      <c r="AF12">
+        <v>12.5</v>
+      </c>
+      <c r="AG12">
+        <v>16</v>
+      </c>
+      <c r="AH12">
+        <v>27</v>
+      </c>
+      <c r="AI12">
+        <v>150</v>
+      </c>
+      <c r="AJ12">
+        <v>12</v>
+      </c>
+      <c r="AK12">
         <v>16.5</v>
       </c>
-      <c r="Z12">
-        <v>30</v>
-      </c>
-      <c r="AA12">
-        <v>75</v>
-      </c>
-      <c r="AB12">
+      <c r="AL12">
+        <v>32</v>
+      </c>
+      <c r="AM12">
+        <v>420</v>
+      </c>
+      <c r="AN12">
+        <v>2.9</v>
+      </c>
+      <c r="AO12">
+        <v>190</v>
+      </c>
+      <c r="AP12">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12">
+        <v>7.4</v>
+      </c>
+      <c r="AR12">
+        <v>7.8</v>
+      </c>
+      <c r="AS12">
+        <v>8</v>
+      </c>
+      <c r="AT12">
         <v>12.5</v>
       </c>
-      <c r="AC12">
+      <c r="AU12">
+        <v>13</v>
+      </c>
+      <c r="AV12">
+        <v>7.4</v>
+      </c>
+      <c r="AW12">
+        <v>7.8</v>
+      </c>
+      <c r="AX12">
+        <v>10</v>
+      </c>
+      <c r="AY12">
+        <v>11</v>
+      </c>
+      <c r="AZ12">
+        <v>21</v>
+      </c>
+      <c r="BA12">
+        <v>7.6</v>
+      </c>
+      <c r="BB12">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD12">
-        <v>17.5</v>
-      </c>
-      <c r="AE12">
-        <v>50</v>
-      </c>
-      <c r="AF12">
-        <v>18.5</v>
-      </c>
-      <c r="AG12">
-        <v>13.5</v>
-      </c>
-      <c r="AH12">
-        <v>21</v>
-      </c>
-      <c r="AI12">
-        <v>60</v>
-      </c>
-      <c r="AJ12">
-        <v>38</v>
-      </c>
-      <c r="AK12">
-        <v>30</v>
-      </c>
-      <c r="AL12">
-        <v>46</v>
-      </c>
-      <c r="AM12">
-        <v>110</v>
-      </c>
-      <c r="AN12">
-        <v>23</v>
-      </c>
-      <c r="AO12">
-        <v>46</v>
-      </c>
-      <c r="AP12">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR12">
-        <v>17.5</v>
-      </c>
-      <c r="AS12">
-        <v>4.1</v>
-      </c>
-      <c r="AT12">
-        <v>7.6</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>10.5</v>
-      </c>
-      <c r="AW12">
-        <v>4</v>
-      </c>
-      <c r="AX12">
-        <v>11</v>
-      </c>
-      <c r="AY12">
-        <v>8.4</v>
-      </c>
-      <c r="AZ12">
-        <v>12.5</v>
-      </c>
-      <c r="BA12">
-        <v>4</v>
-      </c>
-      <c r="BB12">
-        <v>3.9</v>
-      </c>
       <c r="BC12">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BD12">
-        <v>3.95</v>
+        <v>24</v>
       </c>
       <c r="BE12">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BF12">
-        <v>13.5</v>
+        <v>2.58</v>
       </c>
       <c r="BG12">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3863,166 +3863,166 @@
         <v>166</v>
       </c>
       <c r="F13">
-        <v>1.21</v>
+        <v>2.18</v>
       </c>
       <c r="G13">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="H13">
-        <v>15</v>
+        <v>3.15</v>
       </c>
       <c r="I13">
+        <v>3.75</v>
+      </c>
+      <c r="J13">
+        <v>3.45</v>
+      </c>
+      <c r="K13">
+        <v>3.9</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>3.7</v>
+      </c>
+      <c r="O13">
+        <v>1.29</v>
+      </c>
+      <c r="P13">
+        <v>1.94</v>
+      </c>
+      <c r="Q13">
+        <v>1.86</v>
+      </c>
+      <c r="R13">
+        <v>1.36</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <v>1.63</v>
+      </c>
+      <c r="U13">
+        <v>2.16</v>
+      </c>
+      <c r="V13">
+        <v>1.37</v>
+      </c>
+      <c r="W13">
+        <v>1.68</v>
+      </c>
+      <c r="X13">
+        <v>18</v>
+      </c>
+      <c r="Y13">
+        <v>16.5</v>
+      </c>
+      <c r="Z13">
+        <v>30</v>
+      </c>
+      <c r="AA13">
+        <v>70</v>
+      </c>
+      <c r="AB13">
+        <v>12.5</v>
+      </c>
+      <c r="AC13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13">
+        <v>17.5</v>
+      </c>
+      <c r="AE13">
+        <v>46</v>
+      </c>
+      <c r="AF13">
         <v>18.5</v>
       </c>
-      <c r="J13">
-        <v>7.4</v>
-      </c>
-      <c r="K13">
-        <v>8.6</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O13">
-        <v>1.09</v>
-      </c>
-      <c r="P13">
-        <v>3.75</v>
-      </c>
-      <c r="Q13">
-        <v>1.3</v>
-      </c>
-      <c r="R13">
-        <v>2.12</v>
-      </c>
-      <c r="S13">
-        <v>1.72</v>
-      </c>
-      <c r="T13">
-        <v>1.78</v>
-      </c>
-      <c r="U13">
-        <v>2.04</v>
-      </c>
-      <c r="V13">
-        <v>1.06</v>
-      </c>
-      <c r="W13">
-        <v>5</v>
-      </c>
-      <c r="X13">
-        <v>65</v>
-      </c>
-      <c r="Y13">
-        <v>95</v>
-      </c>
-      <c r="Z13">
-        <v>200</v>
-      </c>
-      <c r="AA13">
-        <v>620</v>
-      </c>
-      <c r="AB13">
+      <c r="AG13">
+        <v>13.5</v>
+      </c>
+      <c r="AH13">
         <v>21</v>
       </c>
-      <c r="AC13">
+      <c r="AI13">
+        <v>55</v>
+      </c>
+      <c r="AJ13">
+        <v>38</v>
+      </c>
+      <c r="AK13">
+        <v>30</v>
+      </c>
+      <c r="AL13">
+        <v>44</v>
+      </c>
+      <c r="AM13">
+        <v>100</v>
+      </c>
+      <c r="AN13">
         <v>21</v>
       </c>
-      <c r="AD13">
-        <v>70</v>
-      </c>
-      <c r="AE13">
-        <v>230</v>
-      </c>
-      <c r="AF13">
+      <c r="AO13">
+        <v>40</v>
+      </c>
+      <c r="AP13">
+        <v>10.5</v>
+      </c>
+      <c r="AQ13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR13">
+        <v>17.5</v>
+      </c>
+      <c r="AS13">
+        <v>4.3</v>
+      </c>
+      <c r="AT13">
+        <v>7.8</v>
+      </c>
+      <c r="AU13">
+        <v>7</v>
+      </c>
+      <c r="AV13">
+        <v>10.5</v>
+      </c>
+      <c r="AW13">
+        <v>18</v>
+      </c>
+      <c r="AX13">
+        <v>11</v>
+      </c>
+      <c r="AY13">
+        <v>8.4</v>
+      </c>
+      <c r="AZ13">
         <v>12.5</v>
       </c>
-      <c r="AG13">
-        <v>16</v>
-      </c>
-      <c r="AH13">
-        <v>32</v>
-      </c>
-      <c r="AI13">
-        <v>160</v>
-      </c>
-      <c r="AJ13">
-        <v>11.5</v>
-      </c>
-      <c r="AK13">
-        <v>16.5</v>
-      </c>
-      <c r="AL13">
-        <v>38</v>
-      </c>
-      <c r="AM13">
-        <v>130</v>
-      </c>
-      <c r="AN13">
-        <v>2.86</v>
-      </c>
-      <c r="AO13">
-        <v>200</v>
-      </c>
-      <c r="AP13">
-        <v>6.4</v>
-      </c>
-      <c r="AQ13">
-        <v>6.6</v>
-      </c>
-      <c r="AR13">
-        <v>7</v>
-      </c>
-      <c r="AS13">
-        <v>7</v>
-      </c>
-      <c r="AT13">
-        <v>12</v>
-      </c>
-      <c r="AU13">
-        <v>14.5</v>
-      </c>
-      <c r="AV13">
-        <v>6.4</v>
-      </c>
-      <c r="AW13">
-        <v>7</v>
-      </c>
-      <c r="AX13">
-        <v>10</v>
-      </c>
-      <c r="AY13">
-        <v>11</v>
-      </c>
-      <c r="AZ13">
-        <v>21</v>
-      </c>
       <c r="BA13">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB13">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BC13">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BD13">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BE13">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BF13">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG13">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4129,22 +4129,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="O14">
         <v>1.01</v>
       </c>
       <c r="P14">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="S14">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4353,7 +4353,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I15">
         <v>1.45</v>
@@ -4362,37 +4362,37 @@
         <v>5.2</v>
       </c>
       <c r="K15">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L15">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
         <v>5.8</v>
       </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P15">
         <v>2.62</v>
       </c>
       <c r="Q15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R15">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S15">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T15">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
         <v>3.2</v>
@@ -4401,22 +4401,22 @@
         <v>1.13</v>
       </c>
       <c r="X15">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB15">
         <v>34</v>
       </c>
       <c r="AC15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD15">
         <v>10.5</v>
@@ -4428,7 +4428,7 @@
         <v>80</v>
       </c>
       <c r="AG15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH15">
         <v>23</v>
@@ -4437,31 +4437,31 @@
         <v>30</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AK15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM15">
         <v>110</v>
       </c>
       <c r="AN15">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO15">
         <v>5.2</v>
       </c>
       <c r="AP15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ15">
         <v>10</v>
       </c>
       <c r="AR15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS15">
         <v>11.5</v>
@@ -4473,25 +4473,25 @@
         <v>11</v>
       </c>
       <c r="AV15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW15">
         <v>12.5</v>
       </c>
       <c r="AX15">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AY15">
         <v>27</v>
       </c>
       <c r="AZ15">
+        <v>19.5</v>
+      </c>
+      <c r="BA15">
+        <v>21</v>
+      </c>
+      <c r="BB15">
         <v>20</v>
-      </c>
-      <c r="BA15">
-        <v>26</v>
-      </c>
-      <c r="BB15">
-        <v>50</v>
       </c>
       <c r="BC15">
         <v>38</v>
@@ -4500,16 +4500,16 @@
         <v>36</v>
       </c>
       <c r="BE15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF15">
         <v>40</v>
       </c>
       <c r="BG15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH15">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI15">
         <v>4</v>
@@ -4518,13 +4518,13 @@
         <v>11</v>
       </c>
       <c r="BK15">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL15">
         <v>130</v>
       </c>
       <c r="BM15">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="BN15">
         <v>12.5</v>
@@ -4536,16 +4536,16 @@
         <v>75</v>
       </c>
       <c r="BQ15">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BR15">
         <v>70</v>
       </c>
       <c r="BS15">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BT15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BU15">
         <v>3.7</v>
@@ -4560,13 +4560,13 @@
         <v>24</v>
       </c>
       <c r="BY15">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ15">
         <v>13.5</v>
       </c>
       <c r="CA15">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="CB15" t="s">
         <v>197</v>
@@ -4592,13 +4592,13 @@
         <v>3.2</v>
       </c>
       <c r="G16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H16">
         <v>2.34</v>
       </c>
       <c r="I16">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J16">
         <v>3.7</v>
@@ -4619,7 +4619,7 @@
         <v>1.24</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q16">
         <v>1.73</v>
@@ -4637,10 +4637,10 @@
         <v>2.52</v>
       </c>
       <c r="V16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X16">
         <v>19.5</v>
@@ -4649,7 +4649,7 @@
         <v>13</v>
       </c>
       <c r="Z16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA16">
         <v>32</v>
@@ -4658,22 +4658,22 @@
         <v>16</v>
       </c>
       <c r="AC16">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI16">
         <v>30</v>
@@ -4682,7 +4682,7 @@
         <v>55</v>
       </c>
       <c r="AK16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL16">
         <v>36</v>
@@ -4697,7 +4697,7 @@
         <v>14.5</v>
       </c>
       <c r="AP16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16">
         <v>12</v>
@@ -4733,7 +4733,7 @@
         <v>27</v>
       </c>
       <c r="BB16">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC16">
         <v>29</v>
@@ -4742,13 +4742,13 @@
         <v>32</v>
       </c>
       <c r="BE16">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BF16">
         <v>21</v>
       </c>
       <c r="BG16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
         <v>3.95</v>
@@ -4766,7 +4766,7 @@
         <v>110</v>
       </c>
       <c r="BM16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BN16">
         <v>6.6</v>
@@ -4775,13 +4775,13 @@
         <v>5.9</v>
       </c>
       <c r="BP16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ16">
         <v>16</v>
       </c>
       <c r="BR16">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BS16">
         <v>21</v>
@@ -4796,19 +4796,19 @@
         <v>16</v>
       </c>
       <c r="BW16">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BY16">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BZ16">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CA16">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="CB16" t="s">
         <v>197</v>
@@ -4831,58 +4831,58 @@
         <v>170</v>
       </c>
       <c r="F17">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="G17">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="H17">
-        <v>11</v>
+        <v>2.36</v>
       </c>
       <c r="I17">
-        <v>870</v>
+        <v>2.7</v>
       </c>
       <c r="J17">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
+        <v>4</v>
+      </c>
+      <c r="O17">
+        <v>1.22</v>
+      </c>
+      <c r="P17">
+        <v>2.24</v>
+      </c>
+      <c r="Q17">
+        <v>1.65</v>
+      </c>
+      <c r="R17">
+        <v>1.48</v>
+      </c>
+      <c r="S17">
+        <v>2.56</v>
+      </c>
+      <c r="T17">
+        <v>1.51</v>
+      </c>
+      <c r="U17">
         <v>1.02</v>
       </c>
-      <c r="O17">
-        <v>1.06</v>
-      </c>
-      <c r="P17">
-        <v>2.92</v>
-      </c>
-      <c r="Q17">
-        <v>1.33</v>
-      </c>
-      <c r="R17">
-        <v>1.91</v>
-      </c>
-      <c r="S17">
-        <v>1.76</v>
-      </c>
-      <c r="T17">
-        <v>1.01</v>
-      </c>
-      <c r="U17">
-        <v>1.01</v>
-      </c>
       <c r="V17">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
-        <v>4.7</v>
+        <v>1.48</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4900,7 +4900,7 @@
         <v>1000</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD17">
         <v>1000</v>
@@ -4915,7 +4915,7 @@
         <v>1000</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI17">
         <v>1000</v>
@@ -4930,7 +4930,7 @@
         <v>1000</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN17">
         <v>1000</v>
@@ -4939,58 +4939,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ17">
         <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5047,10 +5047,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
         <v>197</v>
@@ -5073,46 +5073,46 @@
         <v>171</v>
       </c>
       <c r="F18">
-        <v>2.9</v>
+        <v>1.15</v>
       </c>
       <c r="G18">
-        <v>3.25</v>
+        <v>1.23</v>
       </c>
       <c r="H18">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="I18">
-        <v>2.6</v>
+        <v>870</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="O18">
         <v>1.02</v>
       </c>
       <c r="P18">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>2.58</v>
+        <v>1.45</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5121,10 +5121,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="W18">
-        <v>1.45</v>
+        <v>5.1</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5175,124 +5175,124 @@
         <v>1000</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO18">
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH18">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
         <v>197</v>
@@ -5315,118 +5315,118 @@
         <v>172</v>
       </c>
       <c r="F19">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="G19">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H19">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="I19">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="P19">
         <v>2.08</v>
       </c>
       <c r="Q19">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="R19">
         <v>1.38</v>
       </c>
       <c r="S19">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U19">
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD19">
         <v>1000</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH19">
         <v>1000</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM19">
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP19">
         <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
         <v>1.01</v>
@@ -5435,10 +5435,10 @@
         <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV19">
         <v>1.01</v>
@@ -5450,7 +5450,7 @@
         <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
         <v>1.01</v>
@@ -5468,67 +5468,67 @@
         <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5557,166 +5557,166 @@
         <v>173</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G20">
         <v>5.6</v>
       </c>
       <c r="H20">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="I20">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N20">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="O20">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q20">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R20">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="S20">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T20">
         <v>1.65</v>
       </c>
       <c r="U20">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V20">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="W20">
         <v>1.22</v>
       </c>
       <c r="X20">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5799,166 +5799,166 @@
         <v>174</v>
       </c>
       <c r="F21">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G21">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="H21">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="I21">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N21">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P21">
         <v>2.24</v>
       </c>
       <c r="Q21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R21">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S21">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="T21">
         <v>1.55</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.97</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6041,10 +6041,10 @@
         <v>175</v>
       </c>
       <c r="F22">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G22">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H22">
         <v>6.2</v>
@@ -6065,10 +6065,10 @@
         <v>1.09</v>
       </c>
       <c r="N22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P22">
         <v>1.79</v>
@@ -6077,28 +6077,28 @@
         <v>2.24</v>
       </c>
       <c r="R22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T22">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U22">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V22">
         <v>1.18</v>
       </c>
       <c r="W22">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z22">
         <v>48</v>
@@ -6113,7 +6113,7 @@
         <v>8.6</v>
       </c>
       <c r="AD22">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE22">
         <v>110</v>
@@ -6122,37 +6122,37 @@
         <v>9</v>
       </c>
       <c r="AG22">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI22">
         <v>110</v>
       </c>
       <c r="AJ22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL22">
         <v>46</v>
       </c>
       <c r="AM22">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN22">
         <v>13.5</v>
       </c>
       <c r="AO22">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AP22">
         <v>10.5</v>
       </c>
       <c r="AQ22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR22">
         <v>42</v>
@@ -6161,7 +6161,7 @@
         <v>44</v>
       </c>
       <c r="AT22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU22">
         <v>8.199999999999999</v>
@@ -6170,7 +6170,7 @@
         <v>22</v>
       </c>
       <c r="AW22">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AX22">
         <v>8.4</v>
@@ -6182,7 +6182,7 @@
         <v>23</v>
       </c>
       <c r="BA22">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BB22">
         <v>15.5</v>
@@ -6191,22 +6191,22 @@
         <v>18.5</v>
       </c>
       <c r="BD22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE22">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="BF22">
         <v>12</v>
       </c>
       <c r="BG22">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="BH22">
         <v>3.05</v>
       </c>
       <c r="BI22">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BJ22">
         <v>11.5</v>
@@ -6215,19 +6215,19 @@
         <v>10</v>
       </c>
       <c r="BL22">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="BM22">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="BN22">
         <v>4.1</v>
       </c>
       <c r="BO22">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ22">
         <v>10.5</v>
@@ -6236,31 +6236,31 @@
         <v>32</v>
       </c>
       <c r="BS22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU22">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BV22">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW22">
+        <v>13.5</v>
+      </c>
+      <c r="BX22">
+        <v>70</v>
+      </c>
+      <c r="BY22">
         <v>14</v>
       </c>
-      <c r="BX22">
-        <v>75</v>
-      </c>
-      <c r="BY22">
-        <v>17.5</v>
-      </c>
       <c r="BZ22">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="CA22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB22" t="s">
         <v>197</v>
@@ -6283,16 +6283,16 @@
         <v>176</v>
       </c>
       <c r="F23">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H23">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="I23">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J23">
         <v>3.9</v>
@@ -6310,19 +6310,19 @@
         <v>2.88</v>
       </c>
       <c r="O23">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="P23">
         <v>1.64</v>
       </c>
       <c r="Q23">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R23">
         <v>1.24</v>
       </c>
       <c r="S23">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T23">
         <v>2.44</v>
@@ -6331,28 +6331,28 @@
         <v>1.6</v>
       </c>
       <c r="V23">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="W23">
         <v>1.1</v>
       </c>
       <c r="X23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z23">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AA23">
         <v>17</v>
       </c>
       <c r="AB23">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AC23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>11</v>
@@ -6361,10 +6361,10 @@
         <v>22</v>
       </c>
       <c r="AF23">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AG23">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AH23">
         <v>950</v>
@@ -6373,28 +6373,28 @@
         <v>75</v>
       </c>
       <c r="AJ23">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="AK23">
+        <v>280</v>
+      </c>
+      <c r="AL23">
         <v>260</v>
       </c>
-      <c r="AL23">
-        <v>240</v>
-      </c>
       <c r="AM23">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AN23">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="AO23">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ23">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR23">
         <v>6.6</v>
@@ -6415,37 +6415,37 @@
         <v>17.5</v>
       </c>
       <c r="AX23">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY23">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ23">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA23">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB23">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC23">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD23">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE23">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG23">
         <v>10.5</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI23">
         <v>1.32</v>
@@ -6454,55 +6454,55 @@
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
+        <v>1.5</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
         <v>1.49</v>
       </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.04</v>
-      </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="CB23" t="s">
         <v>197</v>
@@ -6531,7 +6531,7 @@
         <v>5.3</v>
       </c>
       <c r="H24">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I24">
         <v>2.12</v>
@@ -6543,34 +6543,34 @@
         <v>3.35</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M24">
+        <v>1.1</v>
+      </c>
+      <c r="N24">
+        <v>2.48</v>
+      </c>
+      <c r="O24">
+        <v>1.5</v>
+      </c>
+      <c r="P24">
+        <v>1.47</v>
+      </c>
+      <c r="Q24">
+        <v>2.5</v>
+      </c>
+      <c r="R24">
         <v>1.14</v>
       </c>
-      <c r="N24">
-        <v>2.5</v>
-      </c>
-      <c r="O24">
-        <v>1.56</v>
-      </c>
-      <c r="P24">
-        <v>1.49</v>
-      </c>
-      <c r="Q24">
-        <v>2.66</v>
-      </c>
-      <c r="R24">
-        <v>1.18</v>
-      </c>
       <c r="S24">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="T24">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U24">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V24">
         <v>1.89</v>
@@ -6585,34 +6585,34 @@
         <v>6.6</v>
       </c>
       <c r="Z24">
+        <v>11</v>
+      </c>
+      <c r="AA24">
+        <v>27</v>
+      </c>
+      <c r="AB24">
         <v>12.5</v>
-      </c>
-      <c r="AA24">
-        <v>30</v>
-      </c>
-      <c r="AB24">
-        <v>14.5</v>
       </c>
       <c r="AC24">
         <v>7.6</v>
       </c>
       <c r="AD24">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF24">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AG24">
         <v>26</v>
       </c>
       <c r="AH24">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI24">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ24">
         <v>180</v>
@@ -6621,7 +6621,7 @@
         <v>120</v>
       </c>
       <c r="AL24">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AM24">
         <v>270</v>
@@ -6630,10 +6630,10 @@
         <v>200</v>
       </c>
       <c r="AO24">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP24">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ24">
         <v>5.6</v>
@@ -6645,7 +6645,7 @@
         <v>19.5</v>
       </c>
       <c r="AT24">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU24">
         <v>6.6</v>
@@ -6654,10 +6654,10 @@
         <v>10</v>
       </c>
       <c r="AW24">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="AX24">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AY24">
         <v>16.5</v>
@@ -6666,22 +6666,22 @@
         <v>20</v>
       </c>
       <c r="BA24">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BB24">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC24">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD24">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE24">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BF24">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG24">
         <v>20</v>
@@ -6690,7 +6690,7 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
@@ -6767,22 +6767,22 @@
         <v>178</v>
       </c>
       <c r="F25">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G25">
         <v>2.54</v>
       </c>
       <c r="H25">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="I25">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J25">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K25">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6791,34 +6791,34 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O25">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q25">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="R25">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S25">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6866,7 +6866,7 @@
         <v>1000</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN25">
         <v>1000</v>
@@ -6920,7 +6920,7 @@
         <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -7009,10 +7009,10 @@
         <v>179</v>
       </c>
       <c r="F26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="G26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H26">
         <v>12</v>
@@ -7027,13 +7027,13 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M26">
         <v>1.09</v>
       </c>
       <c r="N26">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O26">
         <v>1.43</v>
@@ -7042,19 +7042,19 @@
         <v>1.67</v>
       </c>
       <c r="Q26">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T26">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U26">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V26">
         <v>1.07</v>
@@ -7075,7 +7075,7 @@
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC26">
         <v>14</v>
@@ -7084,49 +7084,49 @@
         <v>65</v>
       </c>
       <c r="AE26">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AF26">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AG26">
         <v>13.5</v>
       </c>
       <c r="AH26">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AI26">
         <v>370</v>
       </c>
       <c r="AJ26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK26">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL26">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM26">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AN26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO26">
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AR26">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AS26">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT26">
         <v>5.1</v>
@@ -7135,10 +7135,10 @@
         <v>10</v>
       </c>
       <c r="AV26">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AW26">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AX26">
         <v>5.9</v>
@@ -7147,19 +7147,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA26">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BB26">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD26">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE26">
         <v>6</v>
@@ -7168,10 +7168,10 @@
         <v>8.4</v>
       </c>
       <c r="BG26">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH26">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
         <v>1.01</v>
@@ -7180,55 +7180,55 @@
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>197</v>
@@ -7251,43 +7251,43 @@
         <v>180</v>
       </c>
       <c r="F27">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I27">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J27">
         <v>3.7</v>
       </c>
       <c r="K27">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N27">
         <v>2.66</v>
       </c>
       <c r="O27">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="P27">
         <v>2.36</v>
       </c>
       <c r="Q27">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="R27">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="S27">
         <v>1.91</v>
@@ -7299,13 +7299,13 @@
         <v>1.02</v>
       </c>
       <c r="V27">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y27">
         <v>1000</v>
@@ -7314,10 +7314,10 @@
         <v>1000</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC27">
         <v>1000</v>
@@ -7326,10 +7326,10 @@
         <v>1000</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG27">
         <v>1000</v>
@@ -7338,79 +7338,79 @@
         <v>1000</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ27">
         <v>1000</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO27">
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7493,43 +7493,43 @@
         <v>181</v>
       </c>
       <c r="F28">
-        <v>1.13</v>
+        <v>1.9</v>
       </c>
       <c r="G28">
-        <v>600</v>
+        <v>6.8</v>
       </c>
       <c r="H28">
-        <v>1.13</v>
+        <v>1.9</v>
       </c>
       <c r="I28">
-        <v>870</v>
+        <v>6.8</v>
       </c>
       <c r="J28">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N28">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O28">
         <v>1.02</v>
       </c>
       <c r="P28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q28">
         <v>1.02</v>
       </c>
       <c r="R28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S28">
         <v>1.02</v>
@@ -7541,10 +7541,10 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7601,58 +7601,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7759,22 +7759,22 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Q29">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="R29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="S29">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
         <v>1.01</v>
@@ -7977,112 +7977,112 @@
         <v>183</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G30">
-        <v>15.5</v>
+        <v>110</v>
       </c>
       <c r="H30">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I30">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J30">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K30">
-        <v>8.199999999999999</v>
+        <v>670</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N30">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O30">
         <v>1.23</v>
       </c>
       <c r="P30">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q30">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R30">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S30">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="T30">
         <v>1.83</v>
       </c>
       <c r="U30">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V30">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP30">
         <v>1.01</v>
@@ -8094,10 +8094,10 @@
         <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU30">
         <v>1.01</v>
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ30">
         <v>1.01</v>
@@ -8121,19 +8121,19 @@
         <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>24</v>
+        <v>4.2</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE30">
         <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG30">
         <v>1.01</v>
@@ -8231,10 +8231,10 @@
         <v>2.5</v>
       </c>
       <c r="J31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8267,10 +8267,10 @@
         <v>2.26</v>
       </c>
       <c r="V31">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W31">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X31">
         <v>16</v>
@@ -8288,7 +8288,7 @@
         <v>13.5</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD31">
         <v>11.5</v>
@@ -8303,7 +8303,7 @@
         <v>13.5</v>
       </c>
       <c r="AH31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI31">
         <v>38</v>
@@ -8342,7 +8342,7 @@
         <v>11.5</v>
       </c>
       <c r="AU31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV31">
         <v>10.5</v>
@@ -8360,10 +8360,10 @@
         <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB31">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC31">
         <v>30</v>
@@ -8372,13 +8372,13 @@
         <v>38</v>
       </c>
       <c r="BE31">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BF31">
         <v>25</v>
       </c>
       <c r="BG31">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8461,7 +8461,7 @@
         <v>185</v>
       </c>
       <c r="F32">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G32">
         <v>2.9</v>
@@ -8473,7 +8473,7 @@
         <v>2.64</v>
       </c>
       <c r="J32">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K32">
         <v>3.7</v>
@@ -8494,7 +8494,7 @@
         <v>2.2</v>
       </c>
       <c r="Q32">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R32">
         <v>1.46</v>
@@ -8503,7 +8503,7 @@
         <v>3</v>
       </c>
       <c r="T32">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U32">
         <v>2.42</v>
@@ -8515,13 +8515,13 @@
         <v>1.52</v>
       </c>
       <c r="X32">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y32">
         <v>13.5</v>
       </c>
       <c r="Z32">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA32">
         <v>38</v>
@@ -8530,7 +8530,7 @@
         <v>14</v>
       </c>
       <c r="AC32">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32">
         <v>12</v>
@@ -8545,7 +8545,7 @@
         <v>12.5</v>
       </c>
       <c r="AH32">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI32">
         <v>36</v>
@@ -8584,7 +8584,7 @@
         <v>13</v>
       </c>
       <c r="AU32">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV32">
         <v>11</v>
@@ -8593,13 +8593,13 @@
         <v>23</v>
       </c>
       <c r="AX32">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY32">
         <v>11.5</v>
       </c>
       <c r="AZ32">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA32">
         <v>30</v>
@@ -8617,70 +8617,70 @@
         <v>60</v>
       </c>
       <c r="BF32">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG32">
         <v>17</v>
       </c>
       <c r="BH32">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI32">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ32">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL32">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP32">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BR32">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BU32">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV32">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BX32">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
         <v>197</v>
@@ -8712,7 +8712,7 @@
         <v>2.4</v>
       </c>
       <c r="I33">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J33">
         <v>3.7</v>
@@ -8733,7 +8733,7 @@
         <v>1.24</v>
       </c>
       <c r="P33">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
         <v>1.74</v>
@@ -8742,10 +8742,10 @@
         <v>1.5</v>
       </c>
       <c r="S33">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T33">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U33">
         <v>2.48</v>
@@ -8757,13 +8757,13 @@
         <v>1.46</v>
       </c>
       <c r="X33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y33">
         <v>13</v>
       </c>
       <c r="Z33">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA33">
         <v>32</v>
@@ -8772,7 +8772,7 @@
         <v>15.5</v>
       </c>
       <c r="AC33">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD33">
         <v>11</v>
@@ -8808,10 +8808,10 @@
         <v>23</v>
       </c>
       <c r="AO33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ33">
         <v>12.5</v>
@@ -8841,88 +8841,88 @@
         <v>12.5</v>
       </c>
       <c r="AZ33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA33">
         <v>29</v>
       </c>
       <c r="BB33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC33">
         <v>28</v>
       </c>
       <c r="BD33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE33">
         <v>55</v>
       </c>
       <c r="BF33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG33">
         <v>14</v>
       </c>
       <c r="BH33">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BI33">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BJ33">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL33">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
-        <v>24</v>
+        <v>2.42</v>
       </c>
       <c r="BN33">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP33">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="BR33">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
-        <v>12.5</v>
+        <v>2.42</v>
       </c>
       <c r="BT33">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BU33">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV33">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
-        <v>12</v>
+        <v>2.42</v>
       </c>
       <c r="BX33">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
-        <v>12</v>
+        <v>2.42</v>
       </c>
       <c r="BZ33">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
-        <v>10</v>
+        <v>2.42</v>
       </c>
       <c r="CB33" t="s">
         <v>197</v>
@@ -8945,226 +8945,226 @@
         <v>187</v>
       </c>
       <c r="F34">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="G34">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="H34">
+        <v>6.4</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
         <v>4.8</v>
       </c>
-      <c r="I34">
-        <v>5</v>
-      </c>
-      <c r="J34">
-        <v>4.2</v>
-      </c>
       <c r="K34">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L34">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M34">
         <v>1.04</v>
       </c>
       <c r="N34">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P34">
+        <v>2.5</v>
+      </c>
+      <c r="Q34">
+        <v>1.64</v>
+      </c>
+      <c r="R34">
+        <v>1.58</v>
+      </c>
+      <c r="S34">
         <v>2.62</v>
       </c>
-      <c r="Q34">
-        <v>1.58</v>
-      </c>
-      <c r="R34">
-        <v>1.65</v>
-      </c>
-      <c r="S34">
-        <v>2.44</v>
-      </c>
       <c r="T34">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="U34">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="V34">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W34">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="X34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y34">
+        <v>28</v>
+      </c>
+      <c r="Z34">
+        <v>60</v>
+      </c>
+      <c r="AA34">
+        <v>190</v>
+      </c>
+      <c r="AB34">
+        <v>11</v>
+      </c>
+      <c r="AC34">
+        <v>11</v>
+      </c>
+      <c r="AD34">
         <v>25</v>
       </c>
-      <c r="Z34">
-        <v>44</v>
-      </c>
-      <c r="AA34">
-        <v>120</v>
-      </c>
-      <c r="AB34">
-        <v>13</v>
-      </c>
-      <c r="AC34">
+      <c r="AE34">
+        <v>80</v>
+      </c>
+      <c r="AF34">
+        <v>10.5</v>
+      </c>
+      <c r="AG34">
         <v>10</v>
       </c>
-      <c r="AD34">
-        <v>19.5</v>
-      </c>
-      <c r="AE34">
-        <v>55</v>
-      </c>
-      <c r="AF34">
+      <c r="AH34">
+        <v>21</v>
+      </c>
+      <c r="AI34">
+        <v>75</v>
+      </c>
+      <c r="AJ34">
+        <v>14.5</v>
+      </c>
+      <c r="AK34">
+        <v>15</v>
+      </c>
+      <c r="AL34">
+        <v>29</v>
+      </c>
+      <c r="AM34">
+        <v>95</v>
+      </c>
+      <c r="AN34">
+        <v>6.4</v>
+      </c>
+      <c r="AO34">
+        <v>75</v>
+      </c>
+      <c r="AP34">
+        <v>20</v>
+      </c>
+      <c r="AQ34">
+        <v>25</v>
+      </c>
+      <c r="AR34">
+        <v>48</v>
+      </c>
+      <c r="AS34">
+        <v>46</v>
+      </c>
+      <c r="AT34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU34">
+        <v>10</v>
+      </c>
+      <c r="AV34">
+        <v>22</v>
+      </c>
+      <c r="AW34">
+        <v>34</v>
+      </c>
+      <c r="AX34">
+        <v>9.6</v>
+      </c>
+      <c r="AY34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ34">
+        <v>18</v>
+      </c>
+      <c r="BA34">
+        <v>60</v>
+      </c>
+      <c r="BB34">
         <v>13.5</v>
       </c>
-      <c r="AG34">
+      <c r="BC34">
+        <v>13.5</v>
+      </c>
+      <c r="BD34">
+        <v>25</v>
+      </c>
+      <c r="BE34">
+        <v>36</v>
+      </c>
+      <c r="BF34">
+        <v>6</v>
+      </c>
+      <c r="BG34">
+        <v>60</v>
+      </c>
+      <c r="BH34">
+        <v>4.2</v>
+      </c>
+      <c r="BI34">
+        <v>3.9</v>
+      </c>
+      <c r="BJ34">
+        <v>10</v>
+      </c>
+      <c r="BK34">
+        <v>7.4</v>
+      </c>
+      <c r="BL34">
+        <v>130</v>
+      </c>
+      <c r="BM34">
+        <v>22</v>
+      </c>
+      <c r="BN34">
+        <v>4.3</v>
+      </c>
+      <c r="BO34">
+        <v>3.95</v>
+      </c>
+      <c r="BP34">
+        <v>9.4</v>
+      </c>
+      <c r="BQ34">
+        <v>7.2</v>
+      </c>
+      <c r="BR34">
+        <v>26</v>
+      </c>
+      <c r="BS34">
+        <v>16</v>
+      </c>
+      <c r="BT34">
         <v>10.5</v>
       </c>
-      <c r="AH34">
-        <v>16</v>
-      </c>
-      <c r="AI34">
+      <c r="BU34">
+        <v>7.4</v>
+      </c>
+      <c r="BV34">
         <v>48</v>
       </c>
-      <c r="AJ34">
-        <v>19.5</v>
-      </c>
-      <c r="AK34">
-        <v>16</v>
-      </c>
-      <c r="AL34">
-        <v>26</v>
-      </c>
-      <c r="AM34">
-        <v>65</v>
-      </c>
-      <c r="AN34">
-        <v>7.4</v>
-      </c>
-      <c r="AO34">
-        <v>38</v>
-      </c>
-      <c r="AP34">
-        <v>22</v>
-      </c>
-      <c r="AQ34">
-        <v>22</v>
-      </c>
-      <c r="AR34">
-        <v>38</v>
-      </c>
-      <c r="AS34">
-        <v>38</v>
-      </c>
-      <c r="AT34">
-        <v>12</v>
-      </c>
-      <c r="AU34">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV34">
-        <v>17.5</v>
-      </c>
-      <c r="AW34">
-        <v>44</v>
-      </c>
-      <c r="AX34">
-        <v>12</v>
-      </c>
-      <c r="AY34">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ34">
-        <v>15</v>
-      </c>
-      <c r="BA34">
-        <v>42</v>
-      </c>
-      <c r="BB34">
-        <v>17.5</v>
-      </c>
-      <c r="BC34">
-        <v>14.5</v>
-      </c>
-      <c r="BD34">
-        <v>23</v>
-      </c>
-      <c r="BE34">
-        <v>50</v>
-      </c>
-      <c r="BF34">
-        <v>7</v>
-      </c>
-      <c r="BG34">
-        <v>25</v>
-      </c>
-      <c r="BH34">
-        <v>5.2</v>
-      </c>
-      <c r="BI34">
-        <v>3.65</v>
-      </c>
-      <c r="BJ34">
-        <v>15</v>
-      </c>
-      <c r="BK34">
-        <v>2</v>
-      </c>
-      <c r="BL34">
-        <v>1000</v>
-      </c>
-      <c r="BM34">
-        <v>19</v>
-      </c>
-      <c r="BN34">
-        <v>5.6</v>
-      </c>
-      <c r="BO34">
-        <v>3.85</v>
-      </c>
-      <c r="BP34">
-        <v>1000</v>
-      </c>
-      <c r="BQ34">
-        <v>2.1</v>
-      </c>
-      <c r="BR34">
-        <v>1000</v>
-      </c>
-      <c r="BS34">
-        <v>2.32</v>
-      </c>
-      <c r="BT34">
-        <v>1000</v>
-      </c>
-      <c r="BU34">
-        <v>1.96</v>
-      </c>
-      <c r="BV34">
-        <v>1000</v>
-      </c>
       <c r="BW34">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY34">
+        <v>21</v>
+      </c>
+      <c r="BZ34">
         <v>14</v>
       </c>
-      <c r="BZ34">
-        <v>1000</v>
-      </c>
       <c r="CA34">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="CB34" t="s">
         <v>197</v>
@@ -9187,226 +9187,226 @@
         <v>188</v>
       </c>
       <c r="F35">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="G35">
+        <v>1.81</v>
+      </c>
+      <c r="H35">
+        <v>4.8</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <v>4.2</v>
+      </c>
+      <c r="K35">
+        <v>4.3</v>
+      </c>
+      <c r="L35">
+        <v>1.29</v>
+      </c>
+      <c r="M35">
+        <v>1.04</v>
+      </c>
+      <c r="N35">
+        <v>6</v>
+      </c>
+      <c r="O35">
+        <v>1.19</v>
+      </c>
+      <c r="P35">
+        <v>2.64</v>
+      </c>
+      <c r="Q35">
+        <v>1.58</v>
+      </c>
+      <c r="R35">
+        <v>1.66</v>
+      </c>
+      <c r="S35">
+        <v>2.44</v>
+      </c>
+      <c r="T35">
+        <v>1.61</v>
+      </c>
+      <c r="U35">
+        <v>2.56</v>
+      </c>
+      <c r="V35">
         <v>1.25</v>
       </c>
-      <c r="H35">
-        <v>14.5</v>
-      </c>
-      <c r="I35">
-        <v>15.5</v>
-      </c>
-      <c r="J35">
-        <v>7.6</v>
-      </c>
-      <c r="K35">
-        <v>8</v>
-      </c>
-      <c r="L35">
-        <v>1.25</v>
-      </c>
-      <c r="M35">
-        <v>1.02</v>
-      </c>
-      <c r="N35">
-        <v>7.2</v>
-      </c>
-      <c r="O35">
-        <v>1.14</v>
-      </c>
-      <c r="P35">
-        <v>3.05</v>
-      </c>
-      <c r="Q35">
-        <v>1.45</v>
-      </c>
-      <c r="R35">
-        <v>1.83</v>
-      </c>
-      <c r="S35">
-        <v>2.14</v>
-      </c>
-      <c r="T35">
-        <v>2.06</v>
-      </c>
-      <c r="U35">
-        <v>1.88</v>
-      </c>
-      <c r="V35">
-        <v>1.06</v>
-      </c>
       <c r="W35">
-        <v>4.9</v>
+        <v>2.24</v>
       </c>
       <c r="X35">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Y35">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="Z35">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="AA35">
-        <v>690</v>
+        <v>90</v>
       </c>
       <c r="AB35">
         <v>13</v>
       </c>
       <c r="AC35">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD35">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="AE35">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="AF35">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AG35">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH35">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AI35">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ35">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="AK35">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL35">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AM35">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AN35">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO35">
-        <v>210</v>
+        <v>38</v>
       </c>
       <c r="AP35">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AQ35">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AR35">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AS35">
         <v>55</v>
       </c>
       <c r="AT35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU35">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV35">
+        <v>17.5</v>
+      </c>
+      <c r="AW35">
         <v>42</v>
       </c>
-      <c r="AW35">
-        <v>48</v>
-      </c>
       <c r="AX35">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AY35">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ35">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BB35">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BC35">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BD35">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE35">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BF35">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="BG35">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BH35">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI35">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BJ35">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK35">
-        <v>11</v>
+        <v>2.02</v>
       </c>
       <c r="BL35">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM35">
-        <v>27</v>
+        <v>2.36</v>
       </c>
       <c r="BN35">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BO35">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BP35">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BR35">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS35">
-        <v>8.4</v>
+        <v>2.36</v>
       </c>
       <c r="BT35">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU35">
-        <v>8.6</v>
+        <v>1.99</v>
       </c>
       <c r="BV35">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BW35">
-        <v>23</v>
+        <v>2.36</v>
       </c>
       <c r="BX35">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY35">
-        <v>20</v>
+        <v>2.36</v>
       </c>
       <c r="BZ35">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA35">
-        <v>6.2</v>
+        <v>2.36</v>
       </c>
       <c r="CB35" t="s">
         <v>197</v>
@@ -9429,58 +9429,58 @@
         <v>189</v>
       </c>
       <c r="F36">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G36">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H36">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="I36">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J36">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K36">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M36">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N36">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O36">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P36">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q36">
         <v>2.52</v>
       </c>
       <c r="R36">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S36">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="T36">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U36">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="V36">
         <v>1.58</v>
       </c>
       <c r="W36">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X36">
         <v>9.800000000000001</v>
@@ -9513,7 +9513,7 @@
         <v>18</v>
       </c>
       <c r="AH36">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI36">
         <v>75</v>
@@ -9525,37 +9525,37 @@
         <v>65</v>
       </c>
       <c r="AL36">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM36">
         <v>210</v>
       </c>
       <c r="AN36">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO36">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP36">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ36">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR36">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS36">
         <v>30</v>
       </c>
       <c r="AT36">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU36">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV36">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW36">
         <v>28</v>
@@ -9564,7 +9564,7 @@
         <v>17</v>
       </c>
       <c r="AY36">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ36">
         <v>17</v>
@@ -9582,7 +9582,7 @@
         <v>55</v>
       </c>
       <c r="BE36">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="BF36">
         <v>55</v>
@@ -9671,22 +9671,22 @@
         <v>190</v>
       </c>
       <c r="F37">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="G37">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="H37">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="I37">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J37">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="L37">
         <v>1.32</v>
@@ -9695,142 +9695,142 @@
         <v>1.04</v>
       </c>
       <c r="N37">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O37">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P37">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q37">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R37">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S37">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="T37">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="U37">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="V37">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="W37">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="X37">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y37">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z37">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AA37">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC37">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD37">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AE37">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF37">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG37">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH37">
+        <v>24</v>
+      </c>
+      <c r="AI37">
+        <v>110</v>
+      </c>
+      <c r="AJ37">
+        <v>12</v>
+      </c>
+      <c r="AK37">
+        <v>13.5</v>
+      </c>
+      <c r="AL37">
+        <v>32</v>
+      </c>
+      <c r="AM37">
+        <v>120</v>
+      </c>
+      <c r="AN37">
+        <v>5.4</v>
+      </c>
+      <c r="AO37">
+        <v>120</v>
+      </c>
+      <c r="AP37">
         <v>21</v>
       </c>
-      <c r="AI37">
-        <v>80</v>
-      </c>
-      <c r="AJ37">
-        <v>15</v>
-      </c>
-      <c r="AK37">
-        <v>15.5</v>
-      </c>
-      <c r="AL37">
-        <v>34</v>
-      </c>
-      <c r="AM37">
-        <v>110</v>
-      </c>
-      <c r="AN37">
-        <v>6.6</v>
-      </c>
-      <c r="AO37">
-        <v>95</v>
-      </c>
-      <c r="AP37">
-        <v>20</v>
-      </c>
       <c r="AQ37">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AR37">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AS37">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AT37">
         <v>9.6</v>
       </c>
       <c r="AU37">
+        <v>11</v>
+      </c>
+      <c r="AV37">
+        <v>28</v>
+      </c>
+      <c r="AW37">
+        <v>40</v>
+      </c>
+      <c r="AX37">
+        <v>8.6</v>
+      </c>
+      <c r="AY37">
         <v>9.800000000000001</v>
       </c>
-      <c r="AV37">
-        <v>21</v>
-      </c>
-      <c r="AW37">
-        <v>36</v>
-      </c>
-      <c r="AX37">
-        <v>9.6</v>
-      </c>
-      <c r="AY37">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ37">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BA37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB37">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC37">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD37">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="BE37">
         <v>42</v>
       </c>
       <c r="BF37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG37">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BH37">
         <v>4.2</v>
@@ -9839,58 +9839,58 @@
         <v>3.85</v>
       </c>
       <c r="BJ37">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK37">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BL37">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM37">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="BN37">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BO37">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BP37">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ37">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR37">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BS37">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="BT37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU37">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BV37">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BW37">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BX37">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY37">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BZ37">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CA37">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB37" t="s">
         <v>197</v>
@@ -9913,22 +9913,22 @@
         <v>191</v>
       </c>
       <c r="F38">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="G38">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="H38">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="I38">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="J38">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="K38">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="L38">
         <v>1.32</v>
@@ -9937,202 +9937,202 @@
         <v>1.04</v>
       </c>
       <c r="N38">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P38">
+        <v>2.56</v>
+      </c>
+      <c r="Q38">
+        <v>1.61</v>
+      </c>
+      <c r="R38">
+        <v>1.62</v>
+      </c>
+      <c r="S38">
         <v>2.5</v>
       </c>
-      <c r="Q38">
-        <v>1.65</v>
-      </c>
-      <c r="R38">
-        <v>1.58</v>
-      </c>
-      <c r="S38">
-        <v>2.64</v>
-      </c>
       <c r="T38">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="U38">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="W38">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="X38">
         <v>24</v>
       </c>
       <c r="Y38">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Z38">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AA38">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB38">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AC38">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AD38">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AE38">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AF38">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AG38">
         <v>10.5</v>
       </c>
       <c r="AH38">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AI38">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AJ38">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AK38">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AL38">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AM38">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AN38">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO38">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AP38">
         <v>20</v>
       </c>
       <c r="AQ38">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AR38">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AS38">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AT38">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU38">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV38">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AW38">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AX38">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY38">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BA38">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB38">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="BC38">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD38">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BE38">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BF38">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BG38">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BH38">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI38">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ38">
+        <v>9</v>
+      </c>
+      <c r="BK38">
+        <v>8</v>
+      </c>
+      <c r="BL38">
+        <v>85</v>
+      </c>
+      <c r="BM38">
+        <v>11.5</v>
+      </c>
+      <c r="BN38">
+        <v>4.9</v>
+      </c>
+      <c r="BO38">
+        <v>4.4</v>
+      </c>
+      <c r="BP38">
         <v>12.5</v>
       </c>
-      <c r="BK38">
+      <c r="BQ38">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR38">
+        <v>22</v>
+      </c>
+      <c r="BS38">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT38">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU38">
+        <v>7</v>
+      </c>
+      <c r="BV38">
+        <v>32</v>
+      </c>
+      <c r="BW38">
+        <v>9.4</v>
+      </c>
+      <c r="BX38">
+        <v>36</v>
+      </c>
+      <c r="BY38">
         <v>9.6</v>
       </c>
-      <c r="BL38">
-        <v>150</v>
-      </c>
-      <c r="BM38">
-        <v>28</v>
-      </c>
-      <c r="BN38">
-        <v>4.1</v>
-      </c>
-      <c r="BO38">
-        <v>3.65</v>
-      </c>
-      <c r="BP38">
-        <v>8.4</v>
-      </c>
-      <c r="BQ38">
-        <v>7.2</v>
-      </c>
-      <c r="BR38">
-        <v>25</v>
-      </c>
-      <c r="BS38">
-        <v>7.2</v>
-      </c>
-      <c r="BT38">
-        <v>12.5</v>
-      </c>
-      <c r="BU38">
-        <v>10</v>
-      </c>
-      <c r="BV38">
-        <v>80</v>
-      </c>
-      <c r="BW38">
-        <v>17</v>
-      </c>
-      <c r="BX38">
-        <v>75</v>
-      </c>
-      <c r="BY38">
-        <v>17</v>
-      </c>
       <c r="BZ38">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="CA38">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB38" t="s">
         <v>197</v>
@@ -10155,226 +10155,226 @@
         <v>192</v>
       </c>
       <c r="F39">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="G39">
+        <v>1.23</v>
+      </c>
+      <c r="H39">
+        <v>15.5</v>
+      </c>
+      <c r="I39">
+        <v>16.5</v>
+      </c>
+      <c r="J39">
+        <v>8</v>
+      </c>
+      <c r="K39">
+        <v>8.4</v>
+      </c>
+      <c r="L39">
+        <v>1.24</v>
+      </c>
+      <c r="M39">
+        <v>1.02</v>
+      </c>
+      <c r="N39">
+        <v>7.2</v>
+      </c>
+      <c r="O39">
+        <v>1.15</v>
+      </c>
+      <c r="P39">
+        <v>3.1</v>
+      </c>
+      <c r="Q39">
+        <v>1.45</v>
+      </c>
+      <c r="R39">
+        <v>1.83</v>
+      </c>
+      <c r="S39">
+        <v>2.14</v>
+      </c>
+      <c r="T39">
+        <v>2.08</v>
+      </c>
+      <c r="U39">
         <v>1.87</v>
       </c>
-      <c r="H39">
-        <v>4.3</v>
-      </c>
-      <c r="I39">
+      <c r="V39">
+        <v>1.06</v>
+      </c>
+      <c r="W39">
+        <v>5.3</v>
+      </c>
+      <c r="X39">
+        <v>38</v>
+      </c>
+      <c r="Y39">
+        <v>55</v>
+      </c>
+      <c r="Z39">
+        <v>1000</v>
+      </c>
+      <c r="AA39">
+        <v>1000</v>
+      </c>
+      <c r="AB39">
+        <v>12.5</v>
+      </c>
+      <c r="AC39">
+        <v>18.5</v>
+      </c>
+      <c r="AD39">
+        <v>55</v>
+      </c>
+      <c r="AE39">
+        <v>1000</v>
+      </c>
+      <c r="AF39">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG39">
+        <v>12.5</v>
+      </c>
+      <c r="AH39">
+        <v>38</v>
+      </c>
+      <c r="AI39">
+        <v>1000</v>
+      </c>
+      <c r="AJ39">
+        <v>9.4</v>
+      </c>
+      <c r="AK39">
+        <v>14</v>
+      </c>
+      <c r="AL39">
+        <v>40</v>
+      </c>
+      <c r="AM39">
+        <v>1000</v>
+      </c>
+      <c r="AN39">
+        <v>3.35</v>
+      </c>
+      <c r="AO39">
+        <v>320</v>
+      </c>
+      <c r="AP39">
+        <v>24</v>
+      </c>
+      <c r="AQ39">
+        <v>38</v>
+      </c>
+      <c r="AR39">
+        <v>44</v>
+      </c>
+      <c r="AS39">
+        <v>130</v>
+      </c>
+      <c r="AT39">
+        <v>11</v>
+      </c>
+      <c r="AU39">
+        <v>15.5</v>
+      </c>
+      <c r="AV39">
+        <v>34</v>
+      </c>
+      <c r="AW39">
+        <v>48</v>
+      </c>
+      <c r="AX39">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY39">
+        <v>11</v>
+      </c>
+      <c r="AZ39">
+        <v>29</v>
+      </c>
+      <c r="BA39">
+        <v>44</v>
+      </c>
+      <c r="BB39">
+        <v>8.4</v>
+      </c>
+      <c r="BC39">
+        <v>12.5</v>
+      </c>
+      <c r="BD39">
+        <v>30</v>
+      </c>
+      <c r="BE39">
+        <v>46</v>
+      </c>
+      <c r="BF39">
+        <v>3.2</v>
+      </c>
+      <c r="BG39">
+        <v>50</v>
+      </c>
+      <c r="BH39">
+        <v>1000</v>
+      </c>
+      <c r="BI39">
+        <v>4.1</v>
+      </c>
+      <c r="BJ39">
+        <v>1000</v>
+      </c>
+      <c r="BK39">
+        <v>2.04</v>
+      </c>
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
+        <v>2.04</v>
+      </c>
+      <c r="BN39">
         <v>4.4</v>
       </c>
-      <c r="J39">
-        <v>4.2</v>
-      </c>
-      <c r="K39">
-        <v>4.4</v>
-      </c>
-      <c r="L39">
-        <v>1.32</v>
-      </c>
-      <c r="M39">
-        <v>1.04</v>
-      </c>
-      <c r="N39">
-        <v>5.5</v>
-      </c>
-      <c r="O39">
-        <v>1.21</v>
-      </c>
-      <c r="P39">
-        <v>2.54</v>
-      </c>
-      <c r="Q39">
-        <v>1.62</v>
-      </c>
-      <c r="R39">
-        <v>1.61</v>
-      </c>
-      <c r="S39">
-        <v>2.56</v>
-      </c>
-      <c r="T39">
-        <v>1.63</v>
-      </c>
-      <c r="U39">
-        <v>2.5</v>
-      </c>
-      <c r="V39">
-        <v>1.29</v>
-      </c>
-      <c r="W39">
-        <v>2.14</v>
-      </c>
-      <c r="X39">
-        <v>24</v>
-      </c>
-      <c r="Y39">
-        <v>22</v>
-      </c>
-      <c r="Z39">
-        <v>38</v>
-      </c>
-      <c r="AA39">
-        <v>90</v>
-      </c>
-      <c r="AB39">
-        <v>13.5</v>
-      </c>
-      <c r="AC39">
-        <v>10</v>
-      </c>
-      <c r="AD39">
-        <v>17.5</v>
-      </c>
-      <c r="AE39">
-        <v>46</v>
-      </c>
-      <c r="AF39">
-        <v>13.5</v>
-      </c>
-      <c r="AG39">
-        <v>10.5</v>
-      </c>
-      <c r="AH39">
-        <v>16</v>
-      </c>
-      <c r="AI39">
-        <v>46</v>
-      </c>
-      <c r="AJ39">
-        <v>21</v>
-      </c>
-      <c r="AK39">
-        <v>17</v>
-      </c>
-      <c r="AL39">
-        <v>28</v>
-      </c>
-      <c r="AM39">
-        <v>65</v>
-      </c>
-      <c r="AN39">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO39">
-        <v>36</v>
-      </c>
-      <c r="AP39">
-        <v>21</v>
-      </c>
-      <c r="AQ39">
-        <v>20</v>
-      </c>
-      <c r="AR39">
-        <v>32</v>
-      </c>
-      <c r="AS39">
-        <v>36</v>
-      </c>
-      <c r="AT39">
+      <c r="BO39">
+        <v>3.2</v>
+      </c>
+      <c r="BP39">
+        <v>1000</v>
+      </c>
+      <c r="BQ39">
+        <v>5.1</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>2.04</v>
+      </c>
+      <c r="BT39">
+        <v>1000</v>
+      </c>
+      <c r="BU39">
         <v>11.5</v>
       </c>
-      <c r="AU39">
-        <v>9</v>
-      </c>
-      <c r="AV39">
-        <v>15.5</v>
-      </c>
-      <c r="AW39">
-        <v>38</v>
-      </c>
-      <c r="AX39">
-        <v>12</v>
-      </c>
-      <c r="AY39">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ39">
-        <v>14.5</v>
-      </c>
-      <c r="BA39">
-        <v>40</v>
-      </c>
-      <c r="BB39">
-        <v>19</v>
-      </c>
-      <c r="BC39">
-        <v>15.5</v>
-      </c>
-      <c r="BD39">
-        <v>24</v>
-      </c>
-      <c r="BE39">
-        <v>55</v>
-      </c>
-      <c r="BF39">
-        <v>7.8</v>
-      </c>
-      <c r="BG39">
-        <v>30</v>
-      </c>
-      <c r="BH39">
-        <v>4.4</v>
-      </c>
-      <c r="BI39">
-        <v>3.9</v>
-      </c>
-      <c r="BJ39">
-        <v>9</v>
-      </c>
-      <c r="BK39">
-        <v>7.8</v>
-      </c>
-      <c r="BL39">
-        <v>85</v>
-      </c>
-      <c r="BM39">
-        <v>21</v>
-      </c>
-      <c r="BN39">
-        <v>5</v>
-      </c>
-      <c r="BO39">
-        <v>4.4</v>
-      </c>
-      <c r="BP39">
-        <v>12.5</v>
-      </c>
-      <c r="BQ39">
-        <v>6.2</v>
-      </c>
-      <c r="BR39">
-        <v>22</v>
-      </c>
-      <c r="BS39">
-        <v>10</v>
-      </c>
-      <c r="BT39">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU39">
-        <v>7</v>
-      </c>
       <c r="BV39">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>8.800000000000001</v>
+        <v>2.04</v>
       </c>
       <c r="BX39">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>14</v>
+        <v>2.04</v>
       </c>
       <c r="BZ39">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA39">
-        <v>8.4</v>
+        <v>2.04</v>
       </c>
       <c r="CB39" t="s">
         <v>197</v>
@@ -10397,10 +10397,10 @@
         <v>193</v>
       </c>
       <c r="F40">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G40">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H40">
         <v>2.04</v>
@@ -10409,16 +10409,16 @@
         <v>2.06</v>
       </c>
       <c r="J40">
+        <v>3.95</v>
+      </c>
+      <c r="K40">
         <v>4</v>
-      </c>
-      <c r="K40">
-        <v>4.1</v>
       </c>
       <c r="L40">
         <v>1.33</v>
       </c>
       <c r="M40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N40">
         <v>5.3</v>
@@ -10430,13 +10430,13 @@
         <v>2.44</v>
       </c>
       <c r="Q40">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R40">
         <v>1.58</v>
       </c>
       <c r="S40">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T40">
         <v>1.62</v>
@@ -10448,7 +10448,7 @@
         <v>1.94</v>
       </c>
       <c r="W40">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X40">
         <v>21</v>
@@ -10469,7 +10469,7 @@
         <v>9</v>
       </c>
       <c r="AD40">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE40">
         <v>18</v>
@@ -10478,10 +10478,10 @@
         <v>30</v>
       </c>
       <c r="AG40">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH40">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI40">
         <v>28</v>
@@ -10505,7 +10505,7 @@
         <v>10.5</v>
       </c>
       <c r="AP40">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ40">
         <v>12</v>
@@ -10529,10 +10529,10 @@
         <v>17</v>
       </c>
       <c r="AX40">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY40">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ40">
         <v>14.5</v>
@@ -10541,7 +10541,7 @@
         <v>25</v>
       </c>
       <c r="BB40">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC40">
         <v>34</v>
@@ -10559,13 +10559,13 @@
         <v>9.6</v>
       </c>
       <c r="BH40">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI40">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ40">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK40">
         <v>6.4</v>
@@ -10574,10 +10574,10 @@
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>21</v>
+        <v>2.4</v>
       </c>
       <c r="BN40">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO40">
         <v>5.5</v>
@@ -10586,13 +10586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>13.5</v>
+        <v>2.4</v>
       </c>
       <c r="BT40">
         <v>6.2</v>
@@ -10604,19 +10604,19 @@
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="CB40" t="s">
         <v>197</v>
@@ -10663,22 +10663,22 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P41">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Q41">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R41">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="S41">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="T41">
         <v>1.01</v>
@@ -10881,7 +10881,7 @@
         <v>195</v>
       </c>
       <c r="F42">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G42">
         <v>2.72</v>
@@ -10896,31 +10896,31 @@
         <v>3.4</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L42">
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N42">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="O42">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P42">
         <v>2.18</v>
       </c>
       <c r="Q42">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R42">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S42">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="T42">
         <v>1.56</v>
@@ -10935,112 +10935,112 @@
         <v>1.58</v>
       </c>
       <c r="X42">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y42">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z42">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA42">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB42">
+        <v>15</v>
+      </c>
+      <c r="AC42">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD42">
+        <v>14.5</v>
+      </c>
+      <c r="AE42">
+        <v>32</v>
+      </c>
+      <c r="AF42">
+        <v>20</v>
+      </c>
+      <c r="AG42">
+        <v>13</v>
+      </c>
+      <c r="AH42">
         <v>16.5</v>
       </c>
-      <c r="AC42">
-        <v>11</v>
-      </c>
-      <c r="AD42">
-        <v>16</v>
-      </c>
-      <c r="AE42">
-        <v>36</v>
-      </c>
-      <c r="AF42">
-        <v>23</v>
-      </c>
-      <c r="AG42">
-        <v>14.5</v>
-      </c>
-      <c r="AH42">
-        <v>18.5</v>
-      </c>
       <c r="AI42">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ42">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK42">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL42">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM42">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN42">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO42">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP42">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR42">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS42">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT42">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AU42">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV42">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW42">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX42">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY42">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA42">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB42">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC42">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD42">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE42">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF42">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG42">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11132,43 +11132,43 @@
         <v>3.4</v>
       </c>
       <c r="I43">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J43">
-        <v>1.12</v>
+        <v>2.88</v>
       </c>
       <c r="K43">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L43">
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N43">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O43">
         <v>1.42</v>
       </c>
       <c r="P43">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q43">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R43">
         <v>1.21</v>
       </c>
       <c r="S43">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T43">
         <v>1.01</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V43">
         <v>1.33</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -607,7 +607,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 18:32:21</t>
+    <t>2026-09-16 20:49:16</t>
   </si>
 </sst>
 </file>
@@ -1201,22 +1201,22 @@
         <v>155</v>
       </c>
       <c r="F2">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="G2">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="J2">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L2">
         <v>1.25</v>
@@ -1225,202 +1225,202 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="R2">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="S2">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T2">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="U2">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="X2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Z2">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AA2">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AB2">
         <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AK2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AL2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM2">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AN2">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AP2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AR2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AS2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AT2">
         <v>12</v>
       </c>
       <c r="AU2">
+        <v>10</v>
+      </c>
+      <c r="AV2">
+        <v>18.5</v>
+      </c>
+      <c r="AW2">
+        <v>44</v>
+      </c>
+      <c r="AX2">
         <v>11.5</v>
       </c>
-      <c r="AV2">
-        <v>24</v>
-      </c>
-      <c r="AW2">
-        <v>55</v>
-      </c>
-      <c r="AX2">
-        <v>10</v>
-      </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BF2">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BH2">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BI2">
         <v>4.4</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BL2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BM2">
-        <v>6.2</v>
+        <v>70</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
         <v>3.95</v>
       </c>
       <c r="BP2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
         <v>21</v>
       </c>
       <c r="BS2">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU2">
+        <v>5.6</v>
+      </c>
+      <c r="BV2">
+        <v>40</v>
+      </c>
+      <c r="BW2">
+        <v>7</v>
+      </c>
+      <c r="BX2">
+        <v>40</v>
+      </c>
+      <c r="BY2">
+        <v>7</v>
+      </c>
+      <c r="BZ2">
         <v>13</v>
       </c>
-      <c r="BU2">
-        <v>4.1</v>
-      </c>
-      <c r="BV2">
-        <v>55</v>
-      </c>
-      <c r="BW2">
-        <v>5.5</v>
-      </c>
-      <c r="BX2">
-        <v>50</v>
-      </c>
-      <c r="BY2">
-        <v>5.4</v>
-      </c>
-      <c r="BZ2">
-        <v>11.5</v>
-      </c>
       <c r="CA2">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>197</v>
@@ -1443,85 +1443,85 @@
         <v>156</v>
       </c>
       <c r="F3">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G3">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H3">
+        <v>4.7</v>
+      </c>
+      <c r="I3">
         <v>4.8</v>
       </c>
-      <c r="I3">
-        <v>4.9</v>
-      </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="L3">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="M3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N3">
         <v>2.2</v>
       </c>
       <c r="O3">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="P3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="T3">
         <v>2.66</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y3">
         <v>10</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA3">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1530,85 +1530,85 @@
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK3">
         <v>38</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM3">
         <v>400</v>
       </c>
       <c r="AN3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO3">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP3">
         <v>6</v>
       </c>
       <c r="AQ3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS3">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AT3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AX3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3">
         <v>30</v>
       </c>
       <c r="BA3">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="BB3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BE3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BF3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BG3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BH3">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BI3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3">
         <v>14.5</v>
@@ -1617,52 +1617,52 @@
         <v>11.5</v>
       </c>
       <c r="BL3">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BN3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="BR3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
         <v>6.8</v>
       </c>
       <c r="BV3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BX3">
         <v>110</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BZ3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="s">
         <v>197</v>
@@ -1685,22 +1685,22 @@
         <v>157</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
         <v>3.8</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.31</v>
@@ -1709,40 +1709,40 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P4">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q4">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S4">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="T4">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z4">
         <v>28</v>
@@ -1751,61 +1751,61 @@
         <v>55</v>
       </c>
       <c r="AB4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG4">
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO4">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AP4">
         <v>18</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
         <v>21</v>
       </c>
       <c r="AS4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU4">
         <v>8</v>
@@ -1814,28 +1814,28 @@
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BB4">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE4">
         <v>36</v>
@@ -1844,13 +1844,13 @@
         <v>10.5</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH4">
         <v>4.9</v>
       </c>
       <c r="BI4">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
@@ -1862,7 +1862,7 @@
         <v>85</v>
       </c>
       <c r="BM4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
@@ -1886,7 +1886,7 @@
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BV4">
         <v>23</v>
@@ -1927,22 +1927,22 @@
         <v>158</v>
       </c>
       <c r="F5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H5">
+        <v>1.66</v>
+      </c>
+      <c r="I5">
         <v>1.7</v>
       </c>
-      <c r="I5">
-        <v>1.72</v>
-      </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.41</v>
@@ -1951,34 +1951,34 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O5">
         <v>1.32</v>
       </c>
       <c r="P5">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R5">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T5">
         <v>1.94</v>
       </c>
       <c r="U5">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
         <v>15</v>
@@ -1990,13 +1990,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
         <v>9.800000000000001</v>
@@ -2017,52 +2017,52 @@
         <v>38</v>
       </c>
       <c r="AJ5">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM5">
         <v>140</v>
       </c>
       <c r="AN5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS5">
+        <v>14.5</v>
+      </c>
+      <c r="AT5">
+        <v>18</v>
+      </c>
+      <c r="AU5">
+        <v>8.4</v>
+      </c>
+      <c r="AV5">
         <v>9</v>
       </c>
-      <c r="AS5">
-        <v>15</v>
-      </c>
-      <c r="AT5">
-        <v>17</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AW5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AY5">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AZ5">
         <v>19.5</v>
@@ -2074,22 +2074,22 @@
         <v>60</v>
       </c>
       <c r="BC5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BD5">
         <v>65</v>
       </c>
       <c r="BE5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BF5">
         <v>75</v>
       </c>
       <c r="BG5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI5">
         <v>3.15</v>
@@ -2104,10 +2104,10 @@
         <v>170</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BO5">
         <v>8</v>
@@ -2116,37 +2116,37 @@
         <v>60</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>70</v>
       </c>
       <c r="BS5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BU5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
         <v>27</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="CB5" t="s">
         <v>197</v>
@@ -2169,22 +2169,22 @@
         <v>159</v>
       </c>
       <c r="F6">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>1.61</v>
@@ -2193,22 +2193,22 @@
         <v>1.13</v>
       </c>
       <c r="N6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P6">
         <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R6">
         <v>1.11</v>
       </c>
       <c r="S6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T6">
         <v>2.34</v>
@@ -2217,10 +2217,10 @@
         <v>1.58</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W6">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X6">
         <v>970</v>
@@ -2229,19 +2229,19 @@
         <v>970</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6">
         <v>970</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6">
         <v>1000</v>
@@ -2250,22 +2250,22 @@
         <v>970</v>
       </c>
       <c r="AG6">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6">
         <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2283,10 +2283,10 @@
         <v>6.8</v>
       </c>
       <c r="AR6">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AS6">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AT6">
         <v>4.8</v>
@@ -2295,40 +2295,40 @@
         <v>5.1</v>
       </c>
       <c r="AV6">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AW6">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AX6">
         <v>7.4</v>
       </c>
       <c r="AY6">
-        <v>1.75</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="BA6">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BB6">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="BC6">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="BD6">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="BE6">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BF6">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BG6">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2352,7 +2352,7 @@
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BP6">
         <v>1000</v>
@@ -2414,16 +2414,16 @@
         <v>2.78</v>
       </c>
       <c r="G7">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H7">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I7">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
         <v>3.95</v>
@@ -2435,16 +2435,16 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="R7">
         <v>1.42</v>
@@ -2453,16 +2453,16 @@
         <v>2.8</v>
       </c>
       <c r="T7">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="U7">
         <v>2.26</v>
       </c>
       <c r="V7">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7">
         <v>21</v>
@@ -2474,7 +2474,7 @@
         <v>21</v>
       </c>
       <c r="AA7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB7">
         <v>16.5</v>
@@ -2486,7 +2486,7 @@
         <v>14</v>
       </c>
       <c r="AE7">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AF7">
         <v>25</v>
@@ -2516,7 +2516,7 @@
         <v>26</v>
       </c>
       <c r="AO7">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP7">
         <v>15</v>
@@ -2552,7 +2552,7 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>5.2</v>
+        <v>27</v>
       </c>
       <c r="BB7">
         <v>23</v>
@@ -2561,10 +2561,10 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="BE7">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF7">
         <v>19</v>
@@ -2659,13 +2659,13 @@
         <v>2.24</v>
       </c>
       <c r="H8">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
         <v>4.1</v>
@@ -2683,136 +2683,136 @@
         <v>1.22</v>
       </c>
       <c r="P8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T8">
         <v>1.59</v>
       </c>
       <c r="U8">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
         <v>1.8</v>
       </c>
       <c r="X8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y8">
         <v>19.5</v>
       </c>
       <c r="Z8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC8">
         <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH8">
         <v>16.5</v>
       </c>
       <c r="AI8">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ8">
         <v>29</v>
       </c>
       <c r="AK8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AM8">
         <v>200</v>
       </c>
       <c r="AN8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO8">
         <v>30</v>
       </c>
       <c r="AP8">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AR8">
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT8">
         <v>9.800000000000001</v>
       </c>
       <c r="AU8">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW8">
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AY8">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="BA8">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB8">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BC8">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD8">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BE8">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BF8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG8">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2895,13 +2895,13 @@
         <v>162</v>
       </c>
       <c r="F9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G9">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="I9">
         <v>110</v>
@@ -2919,22 +2919,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.78</v>
+        <v>1.09</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
       </c>
       <c r="R9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2946,7 +2946,7 @@
         <v>1.23</v>
       </c>
       <c r="W9">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2958,13 +2958,13 @@
         <v>1000</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9">
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -2979,13 +2979,13 @@
         <v>1000</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI9">
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9">
         <v>1000</v>
@@ -2994,7 +2994,7 @@
         <v>1000</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9">
         <v>1000</v>
@@ -3018,7 +3018,7 @@
         <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV9">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
         <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3140,19 +3140,19 @@
         <v>3.2</v>
       </c>
       <c r="G10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H10">
         <v>2.62</v>
       </c>
       <c r="I10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10">
         <v>2.62</v>
       </c>
       <c r="K10">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3161,34 +3161,34 @@
         <v>1.18</v>
       </c>
       <c r="N10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O10">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="P10">
         <v>1.35</v>
       </c>
       <c r="Q10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
         <v>1.12</v>
       </c>
       <c r="S10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="T10">
         <v>2.38</v>
       </c>
       <c r="U10">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V10">
         <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X10">
         <v>7.2</v>
@@ -3212,7 +3212,7 @@
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AF10">
         <v>25</v>
@@ -3230,7 +3230,7 @@
         <v>420</v>
       </c>
       <c r="AK10">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AL10">
         <v>540</v>
@@ -3281,7 +3281,7 @@
         <v>6.6</v>
       </c>
       <c r="BB10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC10">
         <v>6.4</v>
@@ -3308,55 +3308,55 @@
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="CB10" t="s">
         <v>197</v>
@@ -3388,13 +3388,13 @@
         <v>1.47</v>
       </c>
       <c r="I11">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="J11">
         <v>4.1</v>
       </c>
       <c r="K11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>1.37</v>
@@ -3409,85 +3409,85 @@
         <v>1.33</v>
       </c>
       <c r="P11">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q11">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R11">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
         <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V11">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="W11">
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y11">
         <v>7.6</v>
       </c>
       <c r="Z11">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA11">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC11">
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE11">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AF11">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AG11">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AH11">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AJ11">
         <v>360</v>
       </c>
       <c r="AK11">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="AL11">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AM11">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN11">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AO11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ11">
         <v>6</v>
@@ -3496,13 +3496,13 @@
         <v>7</v>
       </c>
       <c r="AS11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV11">
         <v>8.4</v>
@@ -3511,34 +3511,34 @@
         <v>14.5</v>
       </c>
       <c r="AX11">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY11">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AZ11">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BA11">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BB11">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD11">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BE11">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3624,16 +3624,16 @@
         <v>1.24</v>
       </c>
       <c r="G12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H12">
         <v>15</v>
       </c>
       <c r="I12">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="J12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="O12">
         <v>1.09</v>
@@ -3654,31 +3654,31 @@
         <v>3.75</v>
       </c>
       <c r="Q12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R12">
         <v>2.16</v>
       </c>
       <c r="S12">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="T12">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
         <v>1.07</v>
       </c>
       <c r="W12">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="X12">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="Y12">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Z12">
         <v>210</v>
@@ -3687,13 +3687,13 @@
         <v>620</v>
       </c>
       <c r="AB12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC12">
         <v>22</v>
       </c>
       <c r="AD12">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AE12">
         <v>230</v>
@@ -3729,16 +3729,16 @@
         <v>190</v>
       </c>
       <c r="AP12">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="AQ12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT12">
         <v>12.5</v>
@@ -3747,10 +3747,10 @@
         <v>13</v>
       </c>
       <c r="AV12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3762,7 +3762,7 @@
         <v>21</v>
       </c>
       <c r="BA12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB12">
         <v>9.800000000000001</v>
@@ -3771,16 +3771,16 @@
         <v>11.5</v>
       </c>
       <c r="BD12">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BE12">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF12">
         <v>2.58</v>
       </c>
       <c r="BG12">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3863,19 +3863,19 @@
         <v>166</v>
       </c>
       <c r="F13">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H13">
         <v>3.15</v>
       </c>
       <c r="I13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J13">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
         <v>3.9</v>
@@ -3905,13 +3905,13 @@
         <v>3</v>
       </c>
       <c r="T13">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U13">
         <v>2.16</v>
       </c>
       <c r="V13">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.68</v>
@@ -4129,7 +4129,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="O14">
         <v>1.01</v>
@@ -4153,10 +4153,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4347,7 +4347,7 @@
         <v>168</v>
       </c>
       <c r="F15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G15">
         <v>8.800000000000001</v>
@@ -4362,7 +4362,7 @@
         <v>5.2</v>
       </c>
       <c r="K15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L15">
         <v>1.3</v>
@@ -4371,7 +4371,7 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O15">
         <v>1.2</v>
@@ -4383,25 +4383,25 @@
         <v>1.6</v>
       </c>
       <c r="R15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S15">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T15">
         <v>1.83</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
         <v>3.2</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y15">
         <v>11.5</v>
@@ -4428,7 +4428,7 @@
         <v>80</v>
       </c>
       <c r="AG15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH15">
         <v>23</v>
@@ -4440,7 +4440,7 @@
         <v>300</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL15">
         <v>90</v>
@@ -4449,13 +4449,13 @@
         <v>110</v>
       </c>
       <c r="AN15">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AO15">
         <v>5.2</v>
       </c>
       <c r="AP15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ15">
         <v>10</v>
@@ -4473,25 +4473,25 @@
         <v>11</v>
       </c>
       <c r="AV15">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW15">
         <v>12.5</v>
       </c>
       <c r="AX15">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AY15">
         <v>27</v>
       </c>
       <c r="AZ15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA15">
         <v>21</v>
       </c>
       <c r="BB15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="BC15">
         <v>38</v>
@@ -4500,13 +4500,13 @@
         <v>36</v>
       </c>
       <c r="BE15">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF15">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BG15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH15">
         <v>4.3</v>
@@ -4524,49 +4524,49 @@
         <v>130</v>
       </c>
       <c r="BM15">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN15">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BO15">
         <v>10</v>
       </c>
       <c r="BP15">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BQ15">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BR15">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BS15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BU15">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BW15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX15">
         <v>24</v>
       </c>
       <c r="BY15">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BZ15">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA15">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="CB15" t="s">
         <v>197</v>
@@ -4589,58 +4589,58 @@
         <v>169</v>
       </c>
       <c r="F16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H16">
         <v>2.34</v>
       </c>
       <c r="I16">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J16">
         <v>3.7</v>
       </c>
       <c r="K16">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L16">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M16">
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>1.24</v>
       </c>
       <c r="P16">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R16">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S16">
         <v>2.78</v>
       </c>
       <c r="T16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V16">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X16">
         <v>19.5</v>
@@ -4655,19 +4655,19 @@
         <v>32</v>
       </c>
       <c r="AB16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE16">
         <v>22</v>
       </c>
       <c r="AF16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG16">
         <v>13.5</v>
@@ -4694,7 +4694,7 @@
         <v>24</v>
       </c>
       <c r="AO16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP16">
         <v>17.5</v>
@@ -4724,7 +4724,7 @@
         <v>22</v>
       </c>
       <c r="AY16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ16">
         <v>13.5</v>
@@ -4742,10 +4742,10 @@
         <v>32</v>
       </c>
       <c r="BE16">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BF16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG16">
         <v>12.5</v>
@@ -4766,7 +4766,7 @@
         <v>110</v>
       </c>
       <c r="BM16">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BN16">
         <v>6.6</v>
@@ -4778,13 +4778,13 @@
         <v>27</v>
       </c>
       <c r="BQ16">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR16">
         <v>30</v>
       </c>
       <c r="BS16">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BT16">
         <v>5.5</v>
@@ -4796,19 +4796,19 @@
         <v>16</v>
       </c>
       <c r="BW16">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="BX16">
         <v>26</v>
       </c>
       <c r="BY16">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="BZ16">
         <v>19</v>
       </c>
       <c r="CA16">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="CB16" t="s">
         <v>197</v>
@@ -4852,31 +4852,31 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O17">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="P17">
         <v>2.24</v>
       </c>
       <c r="Q17">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="R17">
         <v>1.48</v>
       </c>
       <c r="S17">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="T17">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U17">
-        <v>1.02</v>
+        <v>2.36</v>
       </c>
       <c r="V17">
         <v>1.58</v>
@@ -4888,49 +4888,49 @@
         <v>1000</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC17">
+        <v>42</v>
+      </c>
+      <c r="AD17">
         <v>970</v>
       </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH17">
-        <v>970</v>
+        <v>130</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AM17">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17">
         <v>1000</v>
@@ -4939,58 +4939,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AR17">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AS17">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AT17">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AU17">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="AV17">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="AW17">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AX17">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AY17">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BA17">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BB17">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BC17">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BD17">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BE17">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BF17">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG17">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5079,7 +5079,7 @@
         <v>1.23</v>
       </c>
       <c r="H18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18">
         <v>870</v>
@@ -5175,7 +5175,7 @@
         <v>1000</v>
       </c>
       <c r="AN18">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO18">
         <v>1000</v>
@@ -5190,7 +5190,7 @@
         <v>2.5</v>
       </c>
       <c r="AS18">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT18">
         <v>1.07</v>
@@ -5229,10 +5229,10 @@
         <v>1.07</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG18">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5315,22 +5315,22 @@
         <v>172</v>
       </c>
       <c r="F19">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G19">
         <v>3.25</v>
       </c>
       <c r="H19">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I19">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="J19">
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5363,70 +5363,70 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X19">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
         <v>970</v>
       </c>
       <c r="Z19">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="AA19">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB19">
         <v>970</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD19">
         <v>1000</v>
       </c>
       <c r="AE19">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AF19">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AG19">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI19">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="AJ19">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="AK19">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AL19">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19">
         <v>46</v>
       </c>
       <c r="AO19">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
         <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
         <v>1.01</v>
@@ -5474,7 +5474,7 @@
         <v>4.1</v>
       </c>
       <c r="BG19">
-        <v>3.3</v>
+        <v>1.55</v>
       </c>
       <c r="BH19">
         <v>4.5</v>
@@ -5557,7 +5557,7 @@
         <v>173</v>
       </c>
       <c r="F20">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G20">
         <v>5.6</v>
@@ -5572,7 +5572,7 @@
         <v>3.95</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5620,19 +5620,19 @@
         <v>1000</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20">
         <v>1000</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD20">
         <v>1000</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF20">
         <v>1000</v>
@@ -5641,7 +5641,7 @@
         <v>1000</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI20">
         <v>1000</v>
@@ -5659,64 +5659,64 @@
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AO20">
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5814,7 +5814,7 @@
         <v>3.6</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5853,16 +5853,16 @@
         <v>1.44</v>
       </c>
       <c r="X21">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="Y21">
         <v>26</v>
       </c>
       <c r="Z21">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AA21">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB21">
         <v>28</v>
@@ -5871,34 +5871,34 @@
         <v>42</v>
       </c>
       <c r="AD21">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE21">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF21">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AG21">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AH21">
         <v>60</v>
       </c>
       <c r="AI21">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ21">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="AK21">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AL21">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM21">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN21">
         <v>48</v>
@@ -5907,52 +5907,52 @@
         <v>36</v>
       </c>
       <c r="AP21">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AQ21">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AR21">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AS21">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AT21">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AU21">
         <v>5.1</v>
       </c>
       <c r="AV21">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AW21">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AX21">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AY21">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AZ21">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BA21">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BB21">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BC21">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BD21">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BE21">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="BF21">
         <v>3.45</v>
@@ -6041,7 +6041,7 @@
         <v>175</v>
       </c>
       <c r="F22">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G22">
         <v>1.73</v>
@@ -6053,10 +6053,10 @@
         <v>6.4</v>
       </c>
       <c r="J22">
+        <v>3.8</v>
+      </c>
+      <c r="K22">
         <v>3.85</v>
-      </c>
-      <c r="K22">
-        <v>3.9</v>
       </c>
       <c r="L22">
         <v>1.49</v>
@@ -6071,16 +6071,16 @@
         <v>1.41</v>
       </c>
       <c r="P22">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q22">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R22">
         <v>1.29</v>
       </c>
       <c r="S22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T22">
         <v>2.14</v>
@@ -6170,7 +6170,7 @@
         <v>22</v>
       </c>
       <c r="AW22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AX22">
         <v>8.4</v>
@@ -6203,64 +6203,64 @@
         <v>150</v>
       </c>
       <c r="BH22">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BI22">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="BJ22">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BL22">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>16</v>
+        <v>3.4</v>
       </c>
       <c r="BN22">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO22">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP22">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR22">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
+        <v>2.96</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>7</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>2.96</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
         <v>11</v>
       </c>
-      <c r="BT22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU22">
-        <v>8</v>
-      </c>
-      <c r="BV22">
-        <v>60</v>
-      </c>
-      <c r="BW22">
-        <v>13.5</v>
-      </c>
-      <c r="BX22">
-        <v>70</v>
-      </c>
-      <c r="BY22">
-        <v>14</v>
-      </c>
       <c r="BZ22">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB22" t="s">
         <v>197</v>
@@ -6286,7 +6286,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H23">
         <v>1.5</v>
@@ -6412,7 +6412,7 @@
         <v>9.4</v>
       </c>
       <c r="AW23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX23">
         <v>8.800000000000001</v>
@@ -6484,7 +6484,7 @@
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6531,7 +6531,7 @@
         <v>5.3</v>
       </c>
       <c r="H24">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I24">
         <v>2.12</v>
@@ -6564,10 +6564,10 @@
         <v>1.14</v>
       </c>
       <c r="S24">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T24">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U24">
         <v>1.69</v>
@@ -6606,7 +6606,7 @@
         <v>38</v>
       </c>
       <c r="AG24">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AH24">
         <v>28</v>
@@ -6615,19 +6615,19 @@
         <v>70</v>
       </c>
       <c r="AJ24">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AK24">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AL24">
         <v>540</v>
       </c>
       <c r="AM24">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN24">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AO24">
         <v>29</v>
@@ -6666,22 +6666,22 @@
         <v>20</v>
       </c>
       <c r="BA24">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB24">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF24">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG24">
         <v>20</v>
@@ -6773,7 +6773,7 @@
         <v>2.54</v>
       </c>
       <c r="H25">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I25">
         <v>3.5</v>
@@ -6791,7 +6791,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
         <v>1.13</v>
@@ -6803,10 +6803,10 @@
         <v>1.52</v>
       </c>
       <c r="R25">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S25">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="T25">
         <v>1.53</v>
@@ -6821,58 +6821,58 @@
         <v>1.65</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM25">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP25">
         <v>1.01</v>
@@ -6926,7 +6926,7 @@
         <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7012,19 +7012,19 @@
         <v>1.36</v>
       </c>
       <c r="G26">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I26">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="J26">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L26">
         <v>1.4</v>
@@ -7042,7 +7042,7 @@
         <v>1.67</v>
       </c>
       <c r="Q26">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R26">
         <v>1.25</v>
@@ -7051,16 +7051,16 @@
         <v>4.3</v>
       </c>
       <c r="T26">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U26">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="V26">
         <v>1.07</v>
       </c>
       <c r="W26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X26">
         <v>14.5</v>
@@ -7075,7 +7075,7 @@
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC26">
         <v>14</v>
@@ -7087,7 +7087,7 @@
         <v>440</v>
       </c>
       <c r="AF26">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>13.5</v>
@@ -7099,7 +7099,7 @@
         <v>370</v>
       </c>
       <c r="AJ26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK26">
         <v>24</v>
@@ -7123,10 +7123,10 @@
         <v>20</v>
       </c>
       <c r="AR26">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS26">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT26">
         <v>5.1</v>
@@ -7135,10 +7135,10 @@
         <v>10</v>
       </c>
       <c r="AV26">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW26">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX26">
         <v>5.9</v>
@@ -7147,28 +7147,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA26">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB26">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC26">
         <v>16.5</v>
       </c>
       <c r="BD26">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF26">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG26">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7251,13 +7251,13 @@
         <v>180</v>
       </c>
       <c r="F27">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H27">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I27">
         <v>2.16</v>
@@ -7266,7 +7266,7 @@
         <v>3.7</v>
       </c>
       <c r="K27">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7299,13 +7299,13 @@
         <v>1.02</v>
       </c>
       <c r="V27">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W27">
         <v>1.3</v>
       </c>
       <c r="X27">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="Y27">
         <v>1000</v>
@@ -7314,19 +7314,19 @@
         <v>1000</v>
       </c>
       <c r="AA27">
+        <v>900</v>
+      </c>
+      <c r="AB27">
         <v>85</v>
       </c>
-      <c r="AB27">
-        <v>40</v>
-      </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD27">
         <v>1000</v>
       </c>
       <c r="AE27">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF27">
         <v>90</v>
@@ -7335,19 +7335,19 @@
         <v>1000</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI27">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ27">
         <v>1000</v>
       </c>
       <c r="AK27">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AL27">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AM27">
         <v>250</v>
@@ -7359,58 +7359,58 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AQ27">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AR27">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AS27">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AT27">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AU27">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AV27">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AW27">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AX27">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AY27">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AZ27">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BA27">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BB27">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BC27">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BD27">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="BE27">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BF27">
         <v>4.6</v>
       </c>
       <c r="BG27">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7493,22 +7493,22 @@
         <v>181</v>
       </c>
       <c r="F28">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G28">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="H28">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I28">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="J28">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K28">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7556,13 +7556,13 @@
         <v>1000</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28">
         <v>1000</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD28">
         <v>1000</v>
@@ -7577,13 +7577,13 @@
         <v>1000</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI28">
         <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK28">
         <v>1000</v>
@@ -7592,7 +7592,7 @@
         <v>1000</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN28">
         <v>1000</v>
@@ -7616,7 +7616,7 @@
         <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AV28">
         <v>1.01</v>
@@ -7649,10 +7649,10 @@
         <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BG28">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7765,7 +7765,7 @@
         <v>1.02</v>
       </c>
       <c r="P29">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q29">
         <v>1.44</v>
@@ -7980,55 +7980,55 @@
         <v>6.2</v>
       </c>
       <c r="G30">
-        <v>110</v>
+        <v>15.5</v>
       </c>
       <c r="H30">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I30">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="J30">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K30">
-        <v>670</v>
+        <v>7.2</v>
       </c>
       <c r="L30">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
         <v>1.03</v>
       </c>
       <c r="N30">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O30">
         <v>1.23</v>
       </c>
       <c r="P30">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q30">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R30">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S30">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="T30">
         <v>1.83</v>
       </c>
       <c r="U30">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V30">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>25</v>
@@ -8040,7 +8040,7 @@
         <v>10.5</v>
       </c>
       <c r="AA30">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB30">
         <v>30</v>
@@ -8082,7 +8082,7 @@
         <v>120</v>
       </c>
       <c r="AO30">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AP30">
         <v>1.01</v>
@@ -8222,25 +8222,25 @@
         <v>3.05</v>
       </c>
       <c r="G31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H31">
         <v>2.44</v>
       </c>
       <c r="I31">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J31">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K31">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
         <v>4</v>
@@ -8255,31 +8255,31 @@
         <v>1.92</v>
       </c>
       <c r="R31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
         <v>3.25</v>
       </c>
       <c r="T31">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U31">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V31">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W31">
         <v>1.47</v>
       </c>
       <c r="X31">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y31">
         <v>11.5</v>
       </c>
       <c r="Z31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA31">
         <v>36</v>
@@ -8312,7 +8312,7 @@
         <v>55</v>
       </c>
       <c r="AK31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL31">
         <v>44</v>
@@ -8324,7 +8324,7 @@
         <v>29</v>
       </c>
       <c r="AO31">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP31">
         <v>13.5</v>
@@ -8336,7 +8336,7 @@
         <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT31">
         <v>11.5</v>
@@ -8351,7 +8351,7 @@
         <v>23</v>
       </c>
       <c r="AX31">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY31">
         <v>12</v>
@@ -8375,22 +8375,22 @@
         <v>28</v>
       </c>
       <c r="BF31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG31">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH31">
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8402,7 +8402,7 @@
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BP31">
         <v>1000</v>
@@ -8420,13 +8420,13 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BX31">
         <v>1000</v>
@@ -8461,16 +8461,16 @@
         <v>185</v>
       </c>
       <c r="F32">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="G32">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H32">
         <v>2.62</v>
       </c>
       <c r="I32">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J32">
         <v>3.6</v>
@@ -8485,7 +8485,7 @@
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O32">
         <v>1.26</v>
@@ -8497,7 +8497,7 @@
         <v>1.81</v>
       </c>
       <c r="R32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S32">
         <v>3</v>
@@ -8512,7 +8512,7 @@
         <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X32">
         <v>18</v>
@@ -8533,7 +8533,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE32">
         <v>26</v>
@@ -8569,7 +8569,7 @@
         <v>19</v>
       </c>
       <c r="AP32">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ32">
         <v>12</v>
@@ -8596,7 +8596,7 @@
         <v>18.5</v>
       </c>
       <c r="AY32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ32">
         <v>14</v>
@@ -8632,13 +8632,13 @@
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BN32">
         <v>1000</v>
@@ -8656,10 +8656,10 @@
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BT32">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
         <v>4.5</v>
@@ -8668,19 +8668,19 @@
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>11.5</v>
+        <v>2.52</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="CB32" t="s">
         <v>197</v>
@@ -8706,13 +8706,13 @@
         <v>3.1</v>
       </c>
       <c r="G33">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H33">
         <v>2.4</v>
       </c>
       <c r="I33">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J33">
         <v>3.7</v>
@@ -8721,7 +8721,7 @@
         <v>3.75</v>
       </c>
       <c r="L33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M33">
         <v>1.05</v>
@@ -8742,10 +8742,10 @@
         <v>1.5</v>
       </c>
       <c r="S33">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T33">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U33">
         <v>2.48</v>
@@ -8754,10 +8754,10 @@
         <v>1.7</v>
       </c>
       <c r="W33">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X33">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y33">
         <v>13</v>
@@ -8805,19 +8805,19 @@
         <v>65</v>
       </c>
       <c r="AN33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO33">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP33">
         <v>17</v>
       </c>
       <c r="AQ33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR33">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS33">
         <v>30</v>
@@ -8859,7 +8859,7 @@
         <v>55</v>
       </c>
       <c r="BF33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG33">
         <v>14</v>
@@ -8880,10 +8880,10 @@
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO33">
         <v>5.1</v>
@@ -8892,13 +8892,13 @@
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BT33">
         <v>6.8</v>
@@ -8910,19 +8910,19 @@
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="CB33" t="s">
         <v>197</v>
@@ -8948,7 +8948,7 @@
         <v>1.54</v>
       </c>
       <c r="G34">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H34">
         <v>6.4</v>
@@ -8960,7 +8960,7 @@
         <v>4.8</v>
       </c>
       <c r="K34">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>1.32</v>
@@ -8978,10 +8978,10 @@
         <v>2.5</v>
       </c>
       <c r="Q34">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R34">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S34">
         <v>2.62</v>
@@ -8990,16 +8990,16 @@
         <v>1.78</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W34">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X34">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y34">
         <v>28</v>
@@ -9008,7 +9008,7 @@
         <v>60</v>
       </c>
       <c r="AA34">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB34">
         <v>11</v>
@@ -9029,7 +9029,7 @@
         <v>10</v>
       </c>
       <c r="AH34">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI34">
         <v>75</v>
@@ -9044,7 +9044,7 @@
         <v>29</v>
       </c>
       <c r="AM34">
-        <v>95</v>
+        <v>310</v>
       </c>
       <c r="AN34">
         <v>6.4</v>
@@ -9059,7 +9059,7 @@
         <v>25</v>
       </c>
       <c r="AR34">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS34">
         <v>46</v>
@@ -9089,22 +9089,22 @@
         <v>60</v>
       </c>
       <c r="BB34">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC34">
         <v>13.5</v>
       </c>
       <c r="BD34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE34">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF34">
         <v>6</v>
       </c>
       <c r="BG34">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BH34">
         <v>4.2</v>
@@ -9113,7 +9113,7 @@
         <v>3.9</v>
       </c>
       <c r="BJ34">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BK34">
         <v>7.4</v>
@@ -9122,7 +9122,7 @@
         <v>130</v>
       </c>
       <c r="BM34">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BN34">
         <v>4.3</v>
@@ -9131,40 +9131,40 @@
         <v>3.95</v>
       </c>
       <c r="BP34">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BQ34">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR34">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BS34">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BT34">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU34">
         <v>7.4</v>
       </c>
       <c r="BV34">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BW34">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BX34">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BY34">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BZ34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA34">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="CB34" t="s">
         <v>197</v>
@@ -9187,7 +9187,7 @@
         <v>188</v>
       </c>
       <c r="F35">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G35">
         <v>1.81</v>
@@ -9199,10 +9199,10 @@
         <v>5</v>
       </c>
       <c r="J35">
+        <v>4.1</v>
+      </c>
+      <c r="K35">
         <v>4.2</v>
-      </c>
-      <c r="K35">
-        <v>4.3</v>
       </c>
       <c r="L35">
         <v>1.29</v>
@@ -9217,13 +9217,13 @@
         <v>1.19</v>
       </c>
       <c r="P35">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q35">
         <v>1.58</v>
       </c>
       <c r="R35">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S35">
         <v>2.44</v>
@@ -9238,7 +9238,7 @@
         <v>1.25</v>
       </c>
       <c r="W35">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X35">
         <v>24</v>
@@ -9247,7 +9247,7 @@
         <v>25</v>
       </c>
       <c r="Z35">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA35">
         <v>90</v>
@@ -9259,22 +9259,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD35">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE35">
         <v>46</v>
       </c>
       <c r="AF35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG35">
         <v>10.5</v>
       </c>
       <c r="AH35">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI35">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ35">
         <v>19</v>
@@ -9283,7 +9283,7 @@
         <v>16</v>
       </c>
       <c r="AL35">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM35">
         <v>65</v>
@@ -9292,25 +9292,25 @@
         <v>7.6</v>
       </c>
       <c r="AO35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP35">
         <v>22</v>
       </c>
       <c r="AQ35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR35">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS35">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AT35">
         <v>12</v>
       </c>
       <c r="AU35">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV35">
         <v>17.5</v>
@@ -9331,16 +9331,16 @@
         <v>38</v>
       </c>
       <c r="BB35">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC35">
         <v>15</v>
       </c>
       <c r="BD35">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE35">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF35">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>3.6</v>
       </c>
       <c r="BJ35">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK35">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="BL35">
         <v>1000</v>
@@ -9376,37 +9376,37 @@
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BT35">
         <v>1000</v>
       </c>
       <c r="BU35">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="CB35" t="s">
         <v>197</v>
@@ -9429,22 +9429,22 @@
         <v>189</v>
       </c>
       <c r="F36">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G36">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H36">
         <v>2.48</v>
       </c>
       <c r="I36">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J36">
         <v>2.8</v>
       </c>
       <c r="K36">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L36">
         <v>1.48</v>
@@ -9468,16 +9468,16 @@
         <v>1.16</v>
       </c>
       <c r="S36">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T36">
         <v>1.98</v>
       </c>
       <c r="U36">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V36">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W36">
         <v>1.37</v>
@@ -9528,7 +9528,7 @@
         <v>90</v>
       </c>
       <c r="AM36">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN36">
         <v>85</v>
@@ -9546,7 +9546,7 @@
         <v>12.5</v>
       </c>
       <c r="AS36">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AT36">
         <v>8.6</v>
@@ -9558,7 +9558,7 @@
         <v>11</v>
       </c>
       <c r="AW36">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AX36">
         <v>17</v>
@@ -9570,25 +9570,25 @@
         <v>17</v>
       </c>
       <c r="BA36">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BB36">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="BC36">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BD36">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BE36">
         <v>28</v>
       </c>
       <c r="BF36">
-        <v>55</v>
+        <v>1.55</v>
       </c>
       <c r="BG36">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9674,19 +9674,19 @@
         <v>1.42</v>
       </c>
       <c r="G37">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H37">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I37">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J37">
+        <v>5.3</v>
+      </c>
+      <c r="K37">
         <v>5.5</v>
-      </c>
-      <c r="K37">
-        <v>5.7</v>
       </c>
       <c r="L37">
         <v>1.32</v>
@@ -9701,31 +9701,31 @@
         <v>1.21</v>
       </c>
       <c r="P37">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q37">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R37">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S37">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T37">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U37">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V37">
         <v>1.12</v>
       </c>
       <c r="W37">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y37">
         <v>32</v>
@@ -9758,7 +9758,7 @@
         <v>24</v>
       </c>
       <c r="AI37">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ37">
         <v>12</v>
@@ -9797,13 +9797,13 @@
         <v>11</v>
       </c>
       <c r="AV37">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW37">
         <v>40</v>
       </c>
       <c r="AX37">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY37">
         <v>9.800000000000001</v>
@@ -9812,7 +9812,7 @@
         <v>22</v>
       </c>
       <c r="BA37">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BB37">
         <v>11</v>
@@ -9824,7 +9824,7 @@
         <v>28</v>
       </c>
       <c r="BE37">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BF37">
         <v>5</v>
@@ -9848,7 +9848,7 @@
         <v>140</v>
       </c>
       <c r="BM37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN37">
         <v>4.1</v>
@@ -9863,25 +9863,25 @@
         <v>7.2</v>
       </c>
       <c r="BR37">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS37">
         <v>8.4</v>
       </c>
       <c r="BT37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU37">
         <v>10</v>
       </c>
       <c r="BV37">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BW37">
         <v>10</v>
       </c>
       <c r="BX37">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BY37">
         <v>10</v>
@@ -9890,7 +9890,7 @@
         <v>14</v>
       </c>
       <c r="CA37">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB37" t="s">
         <v>197</v>
@@ -9913,31 +9913,31 @@
         <v>191</v>
       </c>
       <c r="F38">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G38">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H38">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I38">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K38">
         <v>4.3</v>
       </c>
       <c r="L38">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M38">
         <v>1.04</v>
       </c>
       <c r="N38">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O38">
         <v>1.2</v>
@@ -9952,22 +9952,22 @@
         <v>1.62</v>
       </c>
       <c r="S38">
+        <v>2.52</v>
+      </c>
+      <c r="T38">
+        <v>1.63</v>
+      </c>
+      <c r="U38">
         <v>2.5</v>
       </c>
-      <c r="T38">
-        <v>1.62</v>
-      </c>
-      <c r="U38">
-        <v>2.48</v>
-      </c>
       <c r="V38">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W38">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X38">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y38">
         <v>22</v>
@@ -9976,19 +9976,19 @@
         <v>38</v>
       </c>
       <c r="AA38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB38">
         <v>13</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD38">
         <v>17.5</v>
       </c>
       <c r="AE38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF38">
         <v>13</v>
@@ -10009,7 +10009,7 @@
         <v>17</v>
       </c>
       <c r="AL38">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM38">
         <v>65</v>
@@ -10024,7 +10024,7 @@
         <v>20</v>
       </c>
       <c r="AQ38">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR38">
         <v>32</v>
@@ -10036,10 +10036,10 @@
         <v>11.5</v>
       </c>
       <c r="AU38">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV38">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW38">
         <v>40</v>
@@ -10051,13 +10051,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA38">
         <v>40</v>
       </c>
       <c r="BB38">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC38">
         <v>15.5</v>
@@ -10066,73 +10066,73 @@
         <v>24</v>
       </c>
       <c r="BE38">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF38">
         <v>7.6</v>
       </c>
       <c r="BG38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH38">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI38">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BJ38">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK38">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BL38">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM38">
-        <v>11.5</v>
+        <v>2.48</v>
       </c>
       <c r="BN38">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO38">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="BP38">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>8.800000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="BR38">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS38">
-        <v>8.199999999999999</v>
+        <v>2.56</v>
       </c>
       <c r="BT38">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BU38">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="BV38">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW38">
-        <v>9.4</v>
+        <v>2.56</v>
       </c>
       <c r="BX38">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY38">
-        <v>9.6</v>
+        <v>2.56</v>
       </c>
       <c r="BZ38">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA38">
-        <v>7</v>
+        <v>2.56</v>
       </c>
       <c r="CB38" t="s">
         <v>197</v>
@@ -10161,10 +10161,10 @@
         <v>1.23</v>
       </c>
       <c r="H39">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I39">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="J39">
         <v>8</v>
@@ -10179,10 +10179,10 @@
         <v>1.02</v>
       </c>
       <c r="N39">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O39">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P39">
         <v>3.1</v>
@@ -10191,16 +10191,16 @@
         <v>1.45</v>
       </c>
       <c r="R39">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S39">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T39">
         <v>2.08</v>
       </c>
       <c r="U39">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V39">
         <v>1.06</v>
@@ -10212,7 +10212,7 @@
         <v>38</v>
       </c>
       <c r="Y39">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z39">
         <v>1000</v>
@@ -10227,13 +10227,13 @@
         <v>18.5</v>
       </c>
       <c r="AD39">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE39">
         <v>1000</v>
       </c>
       <c r="AF39">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG39">
         <v>12.5</v>
@@ -10245,7 +10245,7 @@
         <v>1000</v>
       </c>
       <c r="AJ39">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK39">
         <v>14</v>
@@ -10254,40 +10254,40 @@
         <v>40</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN39">
         <v>3.35</v>
       </c>
       <c r="AO39">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AP39">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AQ39">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AR39">
         <v>44</v>
       </c>
       <c r="AS39">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="AT39">
         <v>11</v>
       </c>
       <c r="AU39">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AV39">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AW39">
         <v>48</v>
       </c>
       <c r="AX39">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY39">
         <v>11</v>
@@ -10296,7 +10296,7 @@
         <v>29</v>
       </c>
       <c r="BA39">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB39">
         <v>8.4</v>
@@ -10308,16 +10308,16 @@
         <v>30</v>
       </c>
       <c r="BE39">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF39">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG39">
         <v>50</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BI39">
         <v>4.1</v>
@@ -10326,13 +10326,13 @@
         <v>1000</v>
       </c>
       <c r="BK39">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BN39">
         <v>4.4</v>
@@ -10362,19 +10362,19 @@
         <v>1000</v>
       </c>
       <c r="BW39">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CB39" t="s">
         <v>197</v>
@@ -10397,22 +10397,22 @@
         <v>193</v>
       </c>
       <c r="F40">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G40">
         <v>3.9</v>
       </c>
       <c r="H40">
+        <v>2.02</v>
+      </c>
+      <c r="I40">
         <v>2.04</v>
       </c>
-      <c r="I40">
-        <v>2.06</v>
-      </c>
       <c r="J40">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L40">
         <v>1.33</v>
@@ -10424,28 +10424,28 @@
         <v>5.3</v>
       </c>
       <c r="O40">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P40">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q40">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R40">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S40">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T40">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U40">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W40">
         <v>1.34</v>
@@ -10457,13 +10457,13 @@
         <v>13</v>
       </c>
       <c r="Z40">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA40">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB40">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC40">
         <v>9</v>
@@ -10499,7 +10499,7 @@
         <v>65</v>
       </c>
       <c r="AN40">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO40">
         <v>10.5</v>
@@ -10532,28 +10532,28 @@
         <v>27</v>
       </c>
       <c r="AY40">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ40">
         <v>14.5</v>
       </c>
       <c r="BA40">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB40">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BC40">
         <v>34</v>
       </c>
       <c r="BD40">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE40">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF40">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG40">
         <v>9.6</v>
@@ -10577,7 +10577,7 @@
         <v>2.4</v>
       </c>
       <c r="BN40">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO40">
         <v>5.5</v>
@@ -10881,7 +10881,7 @@
         <v>195</v>
       </c>
       <c r="F42">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G42">
         <v>2.72</v>
@@ -10890,10 +10890,10 @@
         <v>2.7</v>
       </c>
       <c r="I42">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="J42">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K42">
         <v>3.85</v>
@@ -10923,13 +10923,13 @@
         <v>2.3</v>
       </c>
       <c r="T42">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U42">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V42">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W42">
         <v>1.58</v>
@@ -10950,10 +10950,10 @@
         <v>15</v>
       </c>
       <c r="AC42">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD42">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE42">
         <v>32</v>
@@ -10989,58 +10989,58 @@
         <v>22</v>
       </c>
       <c r="AP42">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ42">
+        <v>5.2</v>
+      </c>
+      <c r="AR42">
+        <v>5.8</v>
+      </c>
+      <c r="AS42">
+        <v>6.6</v>
+      </c>
+      <c r="AT42">
         <v>5.1</v>
       </c>
-      <c r="AR42">
-        <v>5.6</v>
-      </c>
-      <c r="AS42">
-        <v>6.4</v>
-      </c>
-      <c r="AT42">
-        <v>4.9</v>
-      </c>
       <c r="AU42">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AV42">
         <v>4.9</v>
       </c>
       <c r="AW42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX42">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY42">
         <v>6.4</v>
       </c>
       <c r="AZ42">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA42">
+        <v>6.4</v>
+      </c>
+      <c r="BB42">
+        <v>6.4</v>
+      </c>
+      <c r="BC42">
+        <v>5.9</v>
+      </c>
+      <c r="BD42">
         <v>6.2</v>
       </c>
-      <c r="BB42">
-        <v>6.2</v>
-      </c>
-      <c r="BC42">
+      <c r="BE42">
+        <v>6.8</v>
+      </c>
+      <c r="BF42">
+        <v>5.3</v>
+      </c>
+      <c r="BG42">
         <v>5.7</v>
-      </c>
-      <c r="BD42">
-        <v>6</v>
-      </c>
-      <c r="BE42">
-        <v>6.6</v>
-      </c>
-      <c r="BF42">
-        <v>5.1</v>
-      </c>
-      <c r="BG42">
-        <v>5.5</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11123,34 +11123,34 @@
         <v>196</v>
       </c>
       <c r="F43">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G43">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H43">
+        <v>3.55</v>
+      </c>
+      <c r="I43">
+        <v>3.95</v>
+      </c>
+      <c r="J43">
+        <v>2.96</v>
+      </c>
+      <c r="K43">
         <v>3.4</v>
       </c>
-      <c r="I43">
-        <v>4</v>
-      </c>
-      <c r="J43">
-        <v>2.88</v>
-      </c>
-      <c r="K43">
-        <v>3.55</v>
-      </c>
       <c r="L43">
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N43">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O43">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P43">
         <v>1.65</v>
@@ -11159,67 +11159,67 @@
         <v>2.16</v>
       </c>
       <c r="R43">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S43">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U43">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V43">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W43">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y43">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA43">
         <v>1000</v>
       </c>
       <c r="AB43">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE43">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF43">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI43">
         <v>1000</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK43">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM43">
         <v>1000</v>
@@ -11231,58 +11231,58 @@
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BH43">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -607,7 +607,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-09-16 20:49:16</t>
+    <t>2026-09-16 23:06:05</t>
   </si>
 </sst>
 </file>
@@ -1201,46 +1201,46 @@
         <v>155</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>4.9</v>
       </c>
       <c r="G2">
-        <v>1.71</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>2.18</v>
       </c>
       <c r="J2">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="K2">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
-        <v>1.51</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
-        <v>1.72</v>
+        <v>1.13</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>7.8</v>
       </c>
       <c r="T2">
         <v>1.56</v>
@@ -1249,178 +1249,178 @@
         <v>2.54</v>
       </c>
       <c r="V2">
-        <v>1.23</v>
+        <v>1.81</v>
       </c>
       <c r="W2">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="X2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="Z2">
+        <v>13</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>3.55</v>
+      </c>
+      <c r="AD2">
+        <v>990</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>7.2</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>32</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>5.3</v>
+      </c>
+      <c r="AQ2">
+        <v>4</v>
+      </c>
+      <c r="AR2">
+        <v>10.5</v>
+      </c>
+      <c r="AS2">
+        <v>5.3</v>
+      </c>
+      <c r="AT2">
+        <v>5.3</v>
+      </c>
+      <c r="AU2">
+        <v>3.3</v>
+      </c>
+      <c r="AV2">
+        <v>11.5</v>
+      </c>
+      <c r="AW2">
+        <v>60</v>
+      </c>
+      <c r="AX2">
+        <v>5.3</v>
+      </c>
+      <c r="AY2">
+        <v>6.2</v>
+      </c>
+      <c r="AZ2">
+        <v>18.5</v>
+      </c>
+      <c r="BA2">
+        <v>5.3</v>
+      </c>
+      <c r="BB2">
+        <v>5.3</v>
+      </c>
+      <c r="BC2">
+        <v>4.5</v>
+      </c>
+      <c r="BD2">
+        <v>55</v>
+      </c>
+      <c r="BE2">
+        <v>5.3</v>
+      </c>
+      <c r="BF2">
         <v>50</v>
       </c>
-      <c r="AA2">
-        <v>140</v>
-      </c>
-      <c r="AB2">
-        <v>14.5</v>
-      </c>
-      <c r="AC2">
-        <v>11.5</v>
-      </c>
-      <c r="AD2">
-        <v>22</v>
-      </c>
-      <c r="AE2">
-        <v>60</v>
-      </c>
-      <c r="AF2">
-        <v>15.5</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>17.5</v>
-      </c>
-      <c r="AI2">
-        <v>55</v>
-      </c>
-      <c r="AJ2">
-        <v>19.5</v>
-      </c>
-      <c r="AK2">
-        <v>15.5</v>
-      </c>
-      <c r="AL2">
-        <v>25</v>
-      </c>
-      <c r="AM2">
-        <v>65</v>
-      </c>
-      <c r="AN2">
-        <v>6.6</v>
-      </c>
-      <c r="AO2">
-        <v>46</v>
-      </c>
-      <c r="AP2">
-        <v>24</v>
-      </c>
-      <c r="AQ2">
-        <v>24</v>
-      </c>
-      <c r="AR2">
-        <v>32</v>
-      </c>
-      <c r="AS2">
-        <v>11</v>
-      </c>
-      <c r="AT2">
-        <v>12</v>
-      </c>
-      <c r="AU2">
-        <v>10</v>
-      </c>
-      <c r="AV2">
-        <v>18.5</v>
-      </c>
-      <c r="AW2">
-        <v>44</v>
-      </c>
-      <c r="AX2">
-        <v>11.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>38</v>
-      </c>
-      <c r="BB2">
-        <v>15.5</v>
-      </c>
-      <c r="BC2">
-        <v>13.5</v>
-      </c>
-      <c r="BD2">
-        <v>21</v>
-      </c>
-      <c r="BE2">
-        <v>48</v>
-      </c>
-      <c r="BF2">
-        <v>5.8</v>
-      </c>
       <c r="BG2">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="BH2">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>197</v>
@@ -1443,226 +1443,226 @@
         <v>156</v>
       </c>
       <c r="F3">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>1.53</v>
       </c>
       <c r="K3">
-        <v>2.96</v>
+        <v>1.55</v>
       </c>
       <c r="L3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.19</v>
+        <v>2.6</v>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="O3">
-        <v>1.81</v>
+        <v>8.6</v>
       </c>
       <c r="P3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="Q3">
-        <v>3.6</v>
+        <v>65</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="S3">
-        <v>8.6</v>
+        <v>220</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>14</v>
       </c>
       <c r="U3">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="V3">
+        <v>1.15</v>
+      </c>
+      <c r="W3">
         <v>1.26</v>
       </c>
-      <c r="W3">
-        <v>1.8</v>
-      </c>
       <c r="X3">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="Y3">
+        <v>9</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>5.9</v>
+      </c>
+      <c r="AC3">
+        <v>360</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.53</v>
+      </c>
+      <c r="AQ3">
+        <v>7.8</v>
+      </c>
+      <c r="AR3">
+        <v>14</v>
+      </c>
+      <c r="AS3">
         <v>10</v>
       </c>
-      <c r="Z3">
+      <c r="AT3">
+        <v>5.2</v>
+      </c>
+      <c r="AU3">
+        <v>19</v>
+      </c>
+      <c r="AV3">
+        <v>65</v>
+      </c>
+      <c r="AW3">
+        <v>10</v>
+      </c>
+      <c r="AX3">
+        <v>14</v>
+      </c>
+      <c r="AY3">
+        <v>65</v>
+      </c>
+      <c r="AZ3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA3">
+        <v>10</v>
+      </c>
+      <c r="BB3">
         <v>32</v>
       </c>
-      <c r="AA3">
-        <v>140</v>
-      </c>
-      <c r="AB3">
-        <v>5.6</v>
-      </c>
-      <c r="AC3">
-        <v>7.2</v>
-      </c>
-      <c r="AD3">
-        <v>22</v>
-      </c>
-      <c r="AE3">
-        <v>110</v>
-      </c>
-      <c r="AF3">
-        <v>11.5</v>
-      </c>
-      <c r="AG3">
-        <v>13</v>
-      </c>
-      <c r="AH3">
-        <v>34</v>
-      </c>
-      <c r="AI3">
-        <v>160</v>
-      </c>
-      <c r="AJ3">
-        <v>34</v>
-      </c>
-      <c r="AK3">
-        <v>38</v>
-      </c>
-      <c r="AL3">
-        <v>90</v>
-      </c>
-      <c r="AM3">
-        <v>400</v>
-      </c>
-      <c r="AN3">
-        <v>44</v>
-      </c>
-      <c r="AO3">
-        <v>220</v>
-      </c>
-      <c r="AP3">
-        <v>6</v>
-      </c>
-      <c r="AQ3">
-        <v>9.6</v>
-      </c>
-      <c r="AR3">
-        <v>28</v>
-      </c>
-      <c r="AS3">
-        <v>110</v>
-      </c>
-      <c r="AT3">
-        <v>5.5</v>
-      </c>
-      <c r="AU3">
-        <v>7</v>
-      </c>
-      <c r="AV3">
-        <v>20</v>
-      </c>
-      <c r="AW3">
-        <v>90</v>
-      </c>
-      <c r="AX3">
-        <v>10.5</v>
-      </c>
-      <c r="AY3">
-        <v>12.5</v>
-      </c>
-      <c r="AZ3">
-        <v>30</v>
-      </c>
-      <c r="BA3">
-        <v>110</v>
-      </c>
-      <c r="BB3">
-        <v>30</v>
-      </c>
       <c r="BC3">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BD3">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="BE3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="BG3">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="BH3">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>197</v>
@@ -1685,220 +1685,220 @@
         <v>157</v>
       </c>
       <c r="F4">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>2</v>
+      </c>
+      <c r="AQ4">
+        <v>130</v>
+      </c>
+      <c r="AR4">
+        <v>130</v>
+      </c>
+      <c r="AS4">
+        <v>130</v>
+      </c>
+      <c r="AT4">
+        <v>130</v>
+      </c>
+      <c r="AU4">
+        <v>130</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>130</v>
+      </c>
+      <c r="AY4">
+        <v>130</v>
+      </c>
+      <c r="AZ4">
+        <v>30</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>130</v>
+      </c>
+      <c r="BC4">
+        <v>130</v>
+      </c>
+      <c r="BD4">
         <v>26</v>
       </c>
-      <c r="Y4">
-        <v>20</v>
-      </c>
-      <c r="Z4">
-        <v>28</v>
-      </c>
-      <c r="AA4">
-        <v>55</v>
-      </c>
-      <c r="AB4">
-        <v>17</v>
-      </c>
-      <c r="AC4">
-        <v>9.4</v>
-      </c>
-      <c r="AD4">
-        <v>14</v>
-      </c>
-      <c r="AE4">
-        <v>34</v>
-      </c>
-      <c r="AF4">
-        <v>20</v>
-      </c>
-      <c r="AG4">
-        <v>12</v>
-      </c>
-      <c r="AH4">
-        <v>15.5</v>
-      </c>
-      <c r="AI4">
-        <v>34</v>
-      </c>
-      <c r="AJ4">
+      <c r="BE4">
         <v>30</v>
       </c>
-      <c r="AK4">
-        <v>22</v>
-      </c>
-      <c r="AL4">
-        <v>29</v>
-      </c>
-      <c r="AM4">
-        <v>60</v>
-      </c>
-      <c r="AN4">
-        <v>12</v>
-      </c>
-      <c r="AO4">
-        <v>19.5</v>
-      </c>
-      <c r="AP4">
-        <v>18</v>
-      </c>
-      <c r="AQ4">
-        <v>16.5</v>
-      </c>
-      <c r="AR4">
-        <v>21</v>
-      </c>
-      <c r="AS4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT4">
-        <v>14</v>
-      </c>
-      <c r="AU4">
-        <v>8</v>
-      </c>
-      <c r="AV4">
-        <v>12</v>
-      </c>
-      <c r="AW4">
-        <v>8</v>
-      </c>
-      <c r="AX4">
-        <v>16.5</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>12.5</v>
-      </c>
-      <c r="BA4">
-        <v>8</v>
-      </c>
-      <c r="BB4">
-        <v>25</v>
-      </c>
-      <c r="BC4">
-        <v>18.5</v>
-      </c>
-      <c r="BD4">
-        <v>7.6</v>
-      </c>
-      <c r="BE4">
-        <v>36</v>
-      </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>2.02</v>
       </c>
       <c r="BG4">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1927,226 +1927,226 @@
         <v>158</v>
       </c>
       <c r="F5">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="H5">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="I5">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="Q5">
-        <v>1.95</v>
+        <v>1.16</v>
       </c>
       <c r="R5">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>3.45</v>
+        <v>1.69</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AE5">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="AF5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="AI5">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AJ5">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AL5">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="AN5">
         <v>120</v>
       </c>
       <c r="AO5">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP5">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AR5">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AS5">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT5">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="AW5">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="AX5">
-        <v>42</v>
+        <v>4.4</v>
       </c>
       <c r="AY5">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="BB5">
-        <v>60</v>
+        <v>4.4</v>
       </c>
       <c r="BC5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BD5">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="BE5">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="BF5">
-        <v>75</v>
+        <v>6.4</v>
       </c>
       <c r="BG5">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BH5">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>1.43</v>
       </c>
       <c r="BK5">
-        <v>9.199999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="BL5">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>3.55</v>
       </c>
       <c r="BN5">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>8</v>
+        <v>3.55</v>
       </c>
       <c r="BP5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="BR5">
-        <v>70</v>
+        <v>860</v>
       </c>
       <c r="BS5">
-        <v>9.4</v>
+        <v>3.55</v>
       </c>
       <c r="BT5">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BV5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="BX5">
-        <v>27</v>
+        <v>870</v>
       </c>
       <c r="BY5">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ5">
-        <v>21</v>
+        <v>860</v>
       </c>
       <c r="CA5">
-        <v>14.5</v>
+        <v>3.25</v>
       </c>
       <c r="CB5" t="s">
         <v>197</v>
@@ -2169,7 +2169,7 @@
         <v>159</v>
       </c>
       <c r="F6">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G6">
         <v>2.18</v>
@@ -2181,40 +2181,40 @@
         <v>5.3</v>
       </c>
       <c r="J6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="L6">
         <v>1.61</v>
       </c>
       <c r="M6">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="P6">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Q6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="S6">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="T6">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="V6">
         <v>1.23</v>
@@ -2223,112 +2223,112 @@
         <v>1.84</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="Y6">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z6">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AA6">
         <v>900</v>
       </c>
       <c r="AB6">
-        <v>970</v>
+        <v>6</v>
       </c>
       <c r="AC6">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF6">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG6">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="AH6">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK6">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="AL6">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP6">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="AS6">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="AT6">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU6">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>2.04</v>
+        <v>17</v>
       </c>
       <c r="AW6">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="AX6">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6">
+        <v>13.5</v>
+      </c>
+      <c r="BA6">
+        <v>10</v>
+      </c>
+      <c r="BB6">
+        <v>21</v>
+      </c>
+      <c r="BC6">
         <v>8.4</v>
       </c>
-      <c r="AZ6">
-        <v>2</v>
-      </c>
-      <c r="BA6">
-        <v>2.08</v>
-      </c>
-      <c r="BB6">
-        <v>2.06</v>
-      </c>
-      <c r="BC6">
-        <v>2.02</v>
-      </c>
       <c r="BD6">
-        <v>2.06</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE6">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
-        <v>2.08</v>
+        <v>8.4</v>
       </c>
       <c r="BG6">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2411,37 +2411,37 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G7">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="I7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q7">
         <v>1.65</v>
@@ -2453,16 +2453,16 @@
         <v>2.8</v>
       </c>
       <c r="T7">
+        <v>1.63</v>
+      </c>
+      <c r="U7">
+        <v>2.28</v>
+      </c>
+      <c r="V7">
         <v>1.6</v>
       </c>
-      <c r="U7">
-        <v>2.26</v>
-      </c>
-      <c r="V7">
-        <v>1.58</v>
-      </c>
       <c r="W7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X7">
         <v>21</v>
@@ -2474,13 +2474,13 @@
         <v>21</v>
       </c>
       <c r="AA7">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7">
         <v>14</v>
@@ -2498,10 +2498,10 @@
         <v>18</v>
       </c>
       <c r="AI7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK7">
         <v>36</v>
@@ -2510,127 +2510,127 @@
         <v>40</v>
       </c>
       <c r="AM7">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AN7">
         <v>26</v>
       </c>
       <c r="AO7">
-        <v>18.5</v>
+        <v>600</v>
       </c>
       <c r="AP7">
-        <v>15</v>
+        <v>3.85</v>
       </c>
       <c r="AQ7">
+        <v>3.55</v>
+      </c>
+      <c r="AR7">
+        <v>12</v>
+      </c>
+      <c r="AS7">
+        <v>4.2</v>
+      </c>
+      <c r="AT7">
+        <v>3.65</v>
+      </c>
+      <c r="AU7">
+        <v>4.9</v>
+      </c>
+      <c r="AV7">
+        <v>3.5</v>
+      </c>
+      <c r="AW7">
+        <v>16.5</v>
+      </c>
+      <c r="AX7">
+        <v>16</v>
+      </c>
+      <c r="AY7">
+        <v>3.55</v>
+      </c>
+      <c r="AZ7">
+        <v>12</v>
+      </c>
+      <c r="BA7">
+        <v>4.1</v>
+      </c>
+      <c r="BB7">
+        <v>4.3</v>
+      </c>
+      <c r="BC7">
+        <v>4.1</v>
+      </c>
+      <c r="BD7">
+        <v>4.2</v>
+      </c>
+      <c r="BE7">
+        <v>4.4</v>
+      </c>
+      <c r="BF7">
+        <v>5.5</v>
+      </c>
+      <c r="BG7">
+        <v>5.2</v>
+      </c>
+      <c r="BH7">
+        <v>4.3</v>
+      </c>
+      <c r="BI7">
+        <v>3.1</v>
+      </c>
+      <c r="BJ7">
         <v>10.5</v>
       </c>
-      <c r="AR7">
-        <v>14.5</v>
-      </c>
-      <c r="AS7">
-        <v>19.5</v>
-      </c>
-      <c r="AT7">
-        <v>11.5</v>
-      </c>
-      <c r="AU7">
-        <v>7.2</v>
-      </c>
-      <c r="AV7">
-        <v>10</v>
-      </c>
-      <c r="AW7">
+      <c r="BK7">
+        <v>3.6</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>5.3</v>
+      </c>
+      <c r="BN7">
+        <v>7</v>
+      </c>
+      <c r="BO7">
+        <v>4.9</v>
+      </c>
+      <c r="BP7">
+        <v>24</v>
+      </c>
+      <c r="BQ7">
+        <v>4.5</v>
+      </c>
+      <c r="BR7">
+        <v>36</v>
+      </c>
+      <c r="BS7">
+        <v>4.8</v>
+      </c>
+      <c r="BT7">
+        <v>6.6</v>
+      </c>
+      <c r="BU7">
+        <v>4.5</v>
+      </c>
+      <c r="BV7">
         <v>21</v>
       </c>
-      <c r="AX7">
-        <v>17.5</v>
-      </c>
-      <c r="AY7">
-        <v>11</v>
-      </c>
-      <c r="AZ7">
-        <v>13</v>
-      </c>
-      <c r="BA7">
-        <v>27</v>
-      </c>
-      <c r="BB7">
-        <v>23</v>
-      </c>
-      <c r="BC7">
-        <v>16</v>
-      </c>
-      <c r="BD7">
-        <v>5</v>
-      </c>
-      <c r="BE7">
-        <v>5.4</v>
-      </c>
-      <c r="BF7">
-        <v>19</v>
-      </c>
-      <c r="BG7">
-        <v>14.5</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.01</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.01</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.01</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.01</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.01</v>
-      </c>
-      <c r="BT7">
-        <v>1000</v>
-      </c>
-      <c r="BU7">
-        <v>1.01</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB7" t="s">
         <v>197</v>
@@ -2653,25 +2653,25 @@
         <v>161</v>
       </c>
       <c r="F8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G8">
         <v>2.24</v>
       </c>
       <c r="H8">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I8">
         <v>3.8</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
         <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2689,13 +2689,13 @@
         <v>1.65</v>
       </c>
       <c r="R8">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S8">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T8">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
         <v>2.38</v>
@@ -2713,7 +2713,7 @@
         <v>19.5</v>
       </c>
       <c r="Z8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA8">
         <v>65</v>
@@ -2746,7 +2746,7 @@
         <v>29</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL8">
         <v>30</v>
@@ -2761,118 +2761,118 @@
         <v>30</v>
       </c>
       <c r="AP8">
+        <v>6.4</v>
+      </c>
+      <c r="AQ8">
         <v>6.2</v>
       </c>
-      <c r="AQ8">
-        <v>6</v>
-      </c>
       <c r="AR8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT8">
         <v>9.800000000000001</v>
       </c>
       <c r="AU8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW8">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AX8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY8">
         <v>9.4</v>
       </c>
       <c r="AZ8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA8">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BB8">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BC8">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD8">
         <v>19.5</v>
       </c>
       <c r="BE8">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BF8">
         <v>10</v>
       </c>
       <c r="BG8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="CB8" t="s">
         <v>197</v>
@@ -2895,22 +2895,22 @@
         <v>162</v>
       </c>
       <c r="F9">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>2.7</v>
       </c>
       <c r="H9">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I9">
         <v>110</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="K9">
-        <v>110</v>
+        <v>8.6</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2919,22 +2919,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="S9">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2946,7 +2946,7 @@
         <v>1.23</v>
       </c>
       <c r="W9">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2964,7 +2964,7 @@
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -2997,7 +2997,7 @@
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -3143,16 +3143,16 @@
         <v>3.8</v>
       </c>
       <c r="H10">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I10">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J10">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="K10">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3161,10 +3161,10 @@
         <v>1.18</v>
       </c>
       <c r="N10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="P10">
         <v>1.35</v>
@@ -3185,7 +3185,7 @@
         <v>1.58</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W10">
         <v>1.36</v>
@@ -3379,13 +3379,13 @@
         <v>164</v>
       </c>
       <c r="F11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I11">
         <v>1.59</v>
@@ -3406,7 +3406,7 @@
         <v>3.4</v>
       </c>
       <c r="O11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P11">
         <v>1.84</v>
@@ -3421,7 +3421,7 @@
         <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
         <v>1.74</v>
@@ -3496,7 +3496,7 @@
         <v>7</v>
       </c>
       <c r="AS11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT11">
         <v>19</v>
@@ -3520,10 +3520,10 @@
         <v>21</v>
       </c>
       <c r="BA11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC11">
         <v>8</v>
@@ -3621,13 +3621,13 @@
         <v>165</v>
       </c>
       <c r="F12">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="G12">
         <v>1.26</v>
       </c>
       <c r="H12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I12">
         <v>18</v>
@@ -3651,25 +3651,25 @@
         <v>1.09</v>
       </c>
       <c r="P12">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q12">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="R12">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="T12">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U12">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W12">
         <v>4.8</v>
@@ -3687,10 +3687,10 @@
         <v>620</v>
       </c>
       <c r="AB12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AD12">
         <v>320</v>
@@ -3699,7 +3699,7 @@
         <v>230</v>
       </c>
       <c r="AF12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG12">
         <v>16</v>
@@ -3711,19 +3711,19 @@
         <v>150</v>
       </c>
       <c r="AJ12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK12">
         <v>16.5</v>
       </c>
       <c r="AL12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM12">
         <v>420</v>
       </c>
       <c r="AN12">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AO12">
         <v>190</v>
@@ -3732,13 +3732,13 @@
         <v>38</v>
       </c>
       <c r="AQ12">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12">
         <v>12.5</v>
@@ -3747,22 +3747,22 @@
         <v>13</v>
       </c>
       <c r="AV12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX12">
         <v>10</v>
       </c>
       <c r="AY12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
         <v>21</v>
       </c>
       <c r="BA12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB12">
         <v>9.800000000000001</v>
@@ -3774,10 +3774,10 @@
         <v>14.5</v>
       </c>
       <c r="BE12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BG12">
         <v>10.5</v>
@@ -3875,7 +3875,7 @@
         <v>3.6</v>
       </c>
       <c r="J13">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K13">
         <v>3.9</v>
@@ -4105,22 +4105,22 @@
         <v>167</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J14">
         <v>1.1</v>
       </c>
       <c r="K14">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4135,7 +4135,7 @@
         <v>1.01</v>
       </c>
       <c r="P14">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q14">
         <v>1.32</v>
@@ -4153,10 +4153,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4261,7 +4261,7 @@
         <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG14">
         <v>1.01</v>
@@ -4347,10 +4347,10 @@
         <v>168</v>
       </c>
       <c r="F15">
+        <v>8.4</v>
+      </c>
+      <c r="G15">
         <v>8.6</v>
-      </c>
-      <c r="G15">
-        <v>8.800000000000001</v>
       </c>
       <c r="H15">
         <v>1.44</v>
@@ -4359,46 +4359,46 @@
         <v>1.45</v>
       </c>
       <c r="J15">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K15">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L15">
         <v>1.3</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S15">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T15">
         <v>1.83</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
         <v>3.2</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4407,13 +4407,13 @@
         <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA15">
         <v>13</v>
       </c>
       <c r="AB15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC15">
         <v>12</v>
@@ -4428,7 +4428,7 @@
         <v>80</v>
       </c>
       <c r="AG15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH15">
         <v>23</v>
@@ -4437,7 +4437,7 @@
         <v>30</v>
       </c>
       <c r="AJ15">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AK15">
         <v>110</v>
@@ -4449,7 +4449,7 @@
         <v>110</v>
       </c>
       <c r="AN15">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO15">
         <v>5.2</v>
@@ -4485,10 +4485,10 @@
         <v>27</v>
       </c>
       <c r="AZ15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BB15">
         <v>50</v>
@@ -4497,19 +4497,19 @@
         <v>38</v>
       </c>
       <c r="BD15">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BE15">
         <v>55</v>
       </c>
       <c r="BF15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BG15">
         <v>4.8</v>
       </c>
       <c r="BH15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI15">
         <v>4</v>
@@ -4533,7 +4533,7 @@
         <v>10</v>
       </c>
       <c r="BP15">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BQ15">
         <v>11.5</v>
@@ -4542,7 +4542,7 @@
         <v>60</v>
       </c>
       <c r="BS15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT15">
         <v>4</v>
@@ -4560,13 +4560,13 @@
         <v>24</v>
       </c>
       <c r="BY15">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15">
         <v>12.5</v>
       </c>
       <c r="CA15">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="s">
         <v>197</v>
@@ -4592,7 +4592,7 @@
         <v>3.25</v>
       </c>
       <c r="G16">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H16">
         <v>2.34</v>
@@ -4604,7 +4604,7 @@
         <v>3.7</v>
       </c>
       <c r="K16">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
         <v>1.35</v>
@@ -4721,10 +4721,10 @@
         <v>20</v>
       </c>
       <c r="AX16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16">
         <v>13.5</v>
@@ -4751,13 +4751,13 @@
         <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI16">
         <v>3.65</v>
       </c>
       <c r="BJ16">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BK16">
         <v>7.6</v>
@@ -4781,10 +4781,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR16">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BS16">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT16">
         <v>5.5</v>
@@ -4799,16 +4799,16 @@
         <v>7</v>
       </c>
       <c r="BX16">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BY16">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="CA16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="s">
         <v>197</v>
@@ -4831,7 +4831,7 @@
         <v>170</v>
       </c>
       <c r="F17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G17">
         <v>3.1</v>
@@ -4840,13 +4840,13 @@
         <v>2.36</v>
       </c>
       <c r="I17">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J17">
         <v>3.7</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4876,7 +4876,7 @@
         <v>1.52</v>
       </c>
       <c r="U17">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
         <v>1.58</v>
@@ -4885,13 +4885,13 @@
         <v>1.48</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y17">
         <v>970</v>
       </c>
       <c r="Z17">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AA17">
         <v>900</v>
@@ -4906,10 +4906,10 @@
         <v>970</v>
       </c>
       <c r="AE17">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AF17">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AG17">
         <v>970</v>
@@ -4918,40 +4918,40 @@
         <v>130</v>
       </c>
       <c r="AI17">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ17">
         <v>900</v>
       </c>
       <c r="AK17">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AL17">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AM17">
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP17">
+        <v>1.3</v>
+      </c>
+      <c r="AQ17">
+        <v>7.6</v>
+      </c>
+      <c r="AR17">
         <v>1.29</v>
       </c>
-      <c r="AQ17">
-        <v>1.27</v>
-      </c>
-      <c r="AR17">
+      <c r="AS17">
+        <v>1.3</v>
+      </c>
+      <c r="AT17">
         <v>1.28</v>
-      </c>
-      <c r="AS17">
-        <v>1.29</v>
-      </c>
-      <c r="AT17">
-        <v>1.27</v>
       </c>
       <c r="AU17">
         <v>5.1</v>
@@ -4960,31 +4960,31 @@
         <v>7</v>
       </c>
       <c r="AW17">
+        <v>1.3</v>
+      </c>
+      <c r="AX17">
         <v>1.29</v>
       </c>
-      <c r="AX17">
-        <v>1.28</v>
-      </c>
       <c r="AY17">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="AZ17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BA17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BB17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BD17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BE17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BF17">
         <v>1.55</v>
@@ -5082,13 +5082,13 @@
         <v>12</v>
       </c>
       <c r="I18">
-        <v>870</v>
+        <v>25</v>
       </c>
       <c r="J18">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="K18">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5124,7 +5124,7 @@
         <v>1.04</v>
       </c>
       <c r="W18">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5315,7 +5315,7 @@
         <v>172</v>
       </c>
       <c r="F19">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G19">
         <v>3.25</v>
@@ -5324,13 +5324,13 @@
         <v>2.28</v>
       </c>
       <c r="I19">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J19">
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5351,7 +5351,7 @@
         <v>1.68</v>
       </c>
       <c r="R19">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S19">
         <v>2.58</v>
@@ -5360,22 +5360,22 @@
         <v>1.05</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
         <v>1.45</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y19">
         <v>970</v>
       </c>
       <c r="Z19">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AA19">
         <v>900</v>
@@ -5387,88 +5387,88 @@
         <v>42</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE19">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF19">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AG19">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AH19">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI19">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AJ19">
         <v>900</v>
       </c>
       <c r="AK19">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL19">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AM19">
         <v>580</v>
       </c>
       <c r="AN19">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AU19">
         <v>5.1</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BF19">
         <v>4.1</v>
@@ -5480,28 +5480,28 @@
         <v>4.5</v>
       </c>
       <c r="BI19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19">
         <v>11</v>
       </c>
       <c r="BK19">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BL19">
         <v>110</v>
       </c>
       <c r="BM19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN19">
         <v>7.6</v>
       </c>
       <c r="BO19">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="BP19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ19">
         <v>3.95</v>
@@ -5516,7 +5516,7 @@
         <v>6.6</v>
       </c>
       <c r="BU19">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="BV19">
         <v>21</v>
@@ -5557,22 +5557,22 @@
         <v>173</v>
       </c>
       <c r="F20">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="G20">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="H20">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="I20">
         <v>1.83</v>
       </c>
       <c r="J20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5581,142 +5581,142 @@
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P20">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R20">
         <v>1.5</v>
       </c>
       <c r="S20">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="T20">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="U20">
+        <v>2.26</v>
+      </c>
+      <c r="V20">
         <v>2.16</v>
       </c>
-      <c r="V20">
-        <v>2.14</v>
-      </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA20">
         <v>900</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC20">
         <v>970</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE20">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH20">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN20">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP20">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AS20">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AT20">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AU20">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AV20">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AW20">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AX20">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AY20">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AZ20">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="BA20">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="BB20">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="BC20">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="BD20">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="BE20">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="BF20">
         <v>1.55</v>
       </c>
       <c r="BG20">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5814,7 +5814,7 @@
         <v>3.6</v>
       </c>
       <c r="K21">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5844,28 +5844,28 @@
         <v>1.55</v>
       </c>
       <c r="U21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X21">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="Y21">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="Z21">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AA21">
         <v>900</v>
       </c>
       <c r="AB21">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AC21">
         <v>42</v>
@@ -5874,37 +5874,37 @@
         <v>970</v>
       </c>
       <c r="AE21">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF21">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AG21">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AH21">
         <v>60</v>
       </c>
       <c r="AI21">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ21">
         <v>900</v>
       </c>
       <c r="AK21">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL21">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM21">
         <v>580</v>
       </c>
       <c r="AN21">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AO21">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP21">
         <v>1.93</v>
@@ -6041,22 +6041,22 @@
         <v>175</v>
       </c>
       <c r="F22">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G22">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H22">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K22">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L22">
         <v>1.49</v>
@@ -6074,7 +6074,7 @@
         <v>1.78</v>
       </c>
       <c r="Q22">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R22">
         <v>1.29</v>
@@ -6092,13 +6092,13 @@
         <v>1.18</v>
       </c>
       <c r="W22">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X22">
         <v>12</v>
       </c>
       <c r="Y22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z22">
         <v>48</v>
@@ -6119,7 +6119,7 @@
         <v>110</v>
       </c>
       <c r="AF22">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG22">
         <v>9.800000000000001</v>
@@ -6134,7 +6134,7 @@
         <v>16.5</v>
       </c>
       <c r="AK22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL22">
         <v>46</v>
@@ -6155,7 +6155,7 @@
         <v>15.5</v>
       </c>
       <c r="AR22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS22">
         <v>44</v>
@@ -6170,7 +6170,7 @@
         <v>22</v>
       </c>
       <c r="AW22">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AX22">
         <v>8.4</v>
@@ -6185,7 +6185,7 @@
         <v>95</v>
       </c>
       <c r="BB22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC22">
         <v>18.5</v>
@@ -6203,64 +6203,64 @@
         <v>150</v>
       </c>
       <c r="BH22">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI22">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM22">
-        <v>3.4</v>
+        <v>19</v>
       </c>
       <c r="BN22">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BO22">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ22">
+        <v>10.5</v>
+      </c>
+      <c r="BR22">
+        <v>32</v>
+      </c>
+      <c r="BS22">
+        <v>13</v>
+      </c>
+      <c r="BT22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU22">
         <v>8.199999999999999</v>
       </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>2.96</v>
-      </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
-      <c r="BU22">
-        <v>7</v>
-      </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW22">
-        <v>2.96</v>
+        <v>15.5</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY22">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA22">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="CB22" t="s">
         <v>197</v>
@@ -6289,7 +6289,7 @@
         <v>10.5</v>
       </c>
       <c r="H23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I23">
         <v>1.57</v>
@@ -6316,7 +6316,7 @@
         <v>1.64</v>
       </c>
       <c r="Q23">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R23">
         <v>1.24</v>
@@ -6388,10 +6388,10 @@
         <v>570</v>
       </c>
       <c r="AO23">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AP23">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ23">
         <v>5.3</v>
@@ -6415,31 +6415,31 @@
         <v>18</v>
       </c>
       <c r="AX23">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AY23">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ23">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA23">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BB23">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC23">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BD23">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE23">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BF23">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG23">
         <v>10.5</v>
@@ -6531,7 +6531,7 @@
         <v>5.3</v>
       </c>
       <c r="H24">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I24">
         <v>2.12</v>
@@ -6543,7 +6543,7 @@
         <v>3.35</v>
       </c>
       <c r="L24">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
         <v>1.1</v>
@@ -6561,13 +6561,13 @@
         <v>2.5</v>
       </c>
       <c r="R24">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S24">
         <v>3.1</v>
       </c>
       <c r="T24">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U24">
         <v>1.69</v>
@@ -6621,13 +6621,13 @@
         <v>240</v>
       </c>
       <c r="AL24">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AM24">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN24">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AO24">
         <v>29</v>
@@ -6642,7 +6642,7 @@
         <v>9.4</v>
       </c>
       <c r="AS24">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT24">
         <v>10.5</v>
@@ -6660,10 +6660,10 @@
         <v>13</v>
       </c>
       <c r="AY24">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ24">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA24">
         <v>9.800000000000001</v>
@@ -6684,13 +6684,13 @@
         <v>10.5</v>
       </c>
       <c r="BG24">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
@@ -6726,7 +6726,7 @@
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BV24">
         <v>1000</v>
@@ -6773,7 +6773,7 @@
         <v>2.54</v>
       </c>
       <c r="H25">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I25">
         <v>3.5</v>
@@ -6782,7 +6782,7 @@
         <v>3.2</v>
       </c>
       <c r="K25">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6806,13 +6806,13 @@
         <v>1.4</v>
       </c>
       <c r="S25">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="T25">
         <v>1.53</v>
       </c>
       <c r="U25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
         <v>1.41</v>
@@ -6875,55 +6875,55 @@
         <v>500</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG25">
         <v>1.55</v>
@@ -7021,10 +7021,10 @@
         <v>14.5</v>
       </c>
       <c r="J26">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L26">
         <v>1.4</v>
@@ -7051,7 +7051,7 @@
         <v>4.3</v>
       </c>
       <c r="T26">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U26">
         <v>1.52</v>
@@ -7078,7 +7078,7 @@
         <v>5.8</v>
       </c>
       <c r="AC26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD26">
         <v>65</v>
@@ -7087,7 +7087,7 @@
         <v>440</v>
       </c>
       <c r="AF26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG26">
         <v>13.5</v>
@@ -7102,10 +7102,10 @@
         <v>13</v>
       </c>
       <c r="AK26">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL26">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM26">
         <v>470</v>
@@ -7120,13 +7120,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR26">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS26">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AT26">
         <v>5.1</v>
@@ -7135,10 +7135,10 @@
         <v>10</v>
       </c>
       <c r="AV26">
+        <v>5.6</v>
+      </c>
+      <c r="AW26">
         <v>6</v>
-      </c>
-      <c r="AW26">
-        <v>5.9</v>
       </c>
       <c r="AX26">
         <v>5.9</v>
@@ -7147,10 +7147,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BA26">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BB26">
         <v>9.6</v>
@@ -7159,10 +7159,10 @@
         <v>16.5</v>
       </c>
       <c r="BD26">
+        <v>5.6</v>
+      </c>
+      <c r="BE26">
         <v>6</v>
-      </c>
-      <c r="BE26">
-        <v>6.4</v>
       </c>
       <c r="BF26">
         <v>8</v>
@@ -7251,22 +7251,22 @@
         <v>180</v>
       </c>
       <c r="F27">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G27">
         <v>4.5</v>
       </c>
       <c r="H27">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="I27">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J27">
         <v>3.7</v>
       </c>
       <c r="K27">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7275,7 +7275,7 @@
         <v>1.03</v>
       </c>
       <c r="N27">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="O27">
         <v>1.04</v>
@@ -7290,127 +7290,127 @@
         <v>1.56</v>
       </c>
       <c r="S27">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="T27">
         <v>1.6</v>
       </c>
       <c r="U27">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="V27">
         <v>1.87</v>
       </c>
       <c r="W27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X27">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA27">
         <v>900</v>
       </c>
       <c r="AB27">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AC27">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE27">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF27">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH27">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI27">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK27">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AL27">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AM27">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN27">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP27">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AQ27">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AR27">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AS27">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AT27">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AU27">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AV27">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AW27">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AX27">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AY27">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AZ27">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="BA27">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="BB27">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="BC27">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="BD27">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="BE27">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="BF27">
         <v>4.6</v>
       </c>
       <c r="BG27">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7493,16 +7493,16 @@
         <v>181</v>
       </c>
       <c r="F28">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G28">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I28">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="J28">
         <v>3.2</v>
@@ -7538,115 +7538,115 @@
         <v>1.51</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA28">
         <v>900</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC28">
         <v>42</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH28">
         <v>60</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ28">
         <v>900</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM28">
         <v>580</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AU28">
         <v>2.5</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF28">
         <v>1.55</v>
@@ -7738,13 +7738,13 @@
         <v>1.1</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H29">
         <v>1.1</v>
       </c>
       <c r="I29">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J29">
         <v>1.1</v>
@@ -7783,10 +7783,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7977,58 +7977,58 @@
         <v>183</v>
       </c>
       <c r="F30">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G30">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="H30">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="I30">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="J30">
         <v>4.5</v>
       </c>
       <c r="K30">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N30">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O30">
         <v>1.23</v>
       </c>
       <c r="P30">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q30">
         <v>1.66</v>
       </c>
       <c r="R30">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S30">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T30">
         <v>1.83</v>
       </c>
       <c r="U30">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
         <v>25</v>
@@ -8055,7 +8055,7 @@
         <v>16</v>
       </c>
       <c r="AF30">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="AG30">
         <v>32</v>
@@ -8070,7 +8070,7 @@
         <v>230</v>
       </c>
       <c r="AK30">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AL30">
         <v>390</v>
@@ -8085,58 +8085,58 @@
         <v>6.8</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT30">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX30">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AY30">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB30">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC30">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD30">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF30">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8219,10 +8219,10 @@
         <v>184</v>
       </c>
       <c r="F31">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G31">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H31">
         <v>2.44</v>
@@ -8255,7 +8255,7 @@
         <v>1.92</v>
       </c>
       <c r="R31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S31">
         <v>3.25</v>
@@ -8270,7 +8270,7 @@
         <v>1.67</v>
       </c>
       <c r="W31">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X31">
         <v>15.5</v>
@@ -8312,7 +8312,7 @@
         <v>55</v>
       </c>
       <c r="AK31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL31">
         <v>44</v>
@@ -8324,7 +8324,7 @@
         <v>29</v>
       </c>
       <c r="AO31">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP31">
         <v>13.5</v>
@@ -8336,7 +8336,7 @@
         <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT31">
         <v>11.5</v>
@@ -8461,10 +8461,10 @@
         <v>185</v>
       </c>
       <c r="F32">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G32">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H32">
         <v>2.62</v>
@@ -8494,7 +8494,7 @@
         <v>2.2</v>
       </c>
       <c r="Q32">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R32">
         <v>1.47</v>
@@ -8503,7 +8503,7 @@
         <v>3</v>
       </c>
       <c r="T32">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U32">
         <v>2.42</v>
@@ -8539,7 +8539,7 @@
         <v>26</v>
       </c>
       <c r="AF32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG32">
         <v>12.5</v>
@@ -8590,7 +8590,7 @@
         <v>11</v>
       </c>
       <c r="AW32">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX32">
         <v>18.5</v>
@@ -8632,7 +8632,7 @@
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8656,7 +8656,7 @@
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BT32">
         <v>1000</v>
@@ -8668,19 +8668,19 @@
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="CB32" t="s">
         <v>197</v>
@@ -8709,7 +8709,7 @@
         <v>3.2</v>
       </c>
       <c r="H33">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I33">
         <v>2.42</v>
@@ -8733,10 +8733,10 @@
         <v>1.24</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q33">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R33">
         <v>1.5</v>
@@ -8748,7 +8748,7 @@
         <v>1.63</v>
       </c>
       <c r="U33">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
         <v>1.7</v>
@@ -8757,7 +8757,7 @@
         <v>1.45</v>
       </c>
       <c r="X33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y33">
         <v>13</v>
@@ -8772,7 +8772,7 @@
         <v>15.5</v>
       </c>
       <c r="AC33">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD33">
         <v>11</v>
@@ -8853,76 +8853,76 @@
         <v>28</v>
       </c>
       <c r="BD33">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE33">
         <v>55</v>
       </c>
       <c r="BF33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH33">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BI33">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK33">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL33">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM33">
-        <v>2.58</v>
+        <v>16.5</v>
       </c>
       <c r="BN33">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BO33">
+        <v>5.9</v>
+      </c>
+      <c r="BP33">
+        <v>22</v>
+      </c>
+      <c r="BQ33">
+        <v>10.5</v>
+      </c>
+      <c r="BR33">
+        <v>30</v>
+      </c>
+      <c r="BS33">
+        <v>11</v>
+      </c>
+      <c r="BT33">
+        <v>5.5</v>
+      </c>
+      <c r="BU33">
         <v>5.1</v>
       </c>
-      <c r="BP33">
-        <v>1000</v>
-      </c>
-      <c r="BQ33">
-        <v>2.54</v>
-      </c>
-      <c r="BR33">
-        <v>1000</v>
-      </c>
-      <c r="BS33">
-        <v>2.54</v>
-      </c>
-      <c r="BT33">
-        <v>6.8</v>
-      </c>
-      <c r="BU33">
-        <v>4.6</v>
-      </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW33">
-        <v>2.58</v>
+        <v>14.5</v>
       </c>
       <c r="BX33">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY33">
-        <v>2.54</v>
+        <v>11</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA33">
-        <v>2.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB33" t="s">
         <v>197</v>
@@ -8963,25 +8963,25 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M34">
         <v>1.04</v>
       </c>
       <c r="N34">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O34">
         <v>1.21</v>
       </c>
       <c r="P34">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q34">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R34">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S34">
         <v>2.62</v>
@@ -9101,70 +9101,70 @@
         <v>50</v>
       </c>
       <c r="BF34">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG34">
         <v>34</v>
       </c>
       <c r="BH34">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI34">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ34">
         <v>12</v>
       </c>
       <c r="BK34">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BL34">
         <v>130</v>
       </c>
       <c r="BM34">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BN34">
         <v>4.3</v>
       </c>
       <c r="BO34">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP34">
         <v>11.5</v>
       </c>
       <c r="BQ34">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR34">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BS34">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BT34">
         <v>12.5</v>
       </c>
       <c r="BU34">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BV34">
         <v>60</v>
       </c>
       <c r="BW34">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX34">
         <v>60</v>
       </c>
       <c r="BY34">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ34">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA34">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="CB34" t="s">
         <v>197</v>
@@ -9193,10 +9193,10 @@
         <v>1.81</v>
       </c>
       <c r="H35">
+        <v>4.7</v>
+      </c>
+      <c r="I35">
         <v>4.8</v>
-      </c>
-      <c r="I35">
-        <v>5</v>
       </c>
       <c r="J35">
         <v>4.1</v>
@@ -9217,16 +9217,16 @@
         <v>1.19</v>
       </c>
       <c r="P35">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q35">
         <v>1.58</v>
       </c>
       <c r="R35">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S35">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T35">
         <v>1.61</v>
@@ -9235,13 +9235,13 @@
         <v>2.56</v>
       </c>
       <c r="V35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W35">
         <v>2.22</v>
       </c>
       <c r="X35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y35">
         <v>25</v>
@@ -9265,7 +9265,7 @@
         <v>46</v>
       </c>
       <c r="AF35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG35">
         <v>10.5</v>
@@ -9274,7 +9274,7 @@
         <v>15.5</v>
       </c>
       <c r="AI35">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ35">
         <v>19</v>
@@ -9328,7 +9328,7 @@
         <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB35">
         <v>18</v>
@@ -9346,7 +9346,7 @@
         <v>7</v>
       </c>
       <c r="BG35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH35">
         <v>5.2</v>
@@ -9358,7 +9358,7 @@
         <v>13.5</v>
       </c>
       <c r="BK35">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="BL35">
         <v>1000</v>
@@ -9382,31 +9382,31 @@
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BT35">
         <v>1000</v>
       </c>
       <c r="BU35">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="CB35" t="s">
         <v>197</v>
@@ -9432,7 +9432,7 @@
         <v>3.3</v>
       </c>
       <c r="G36">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="H36">
         <v>2.48</v>
@@ -9441,10 +9441,10 @@
         <v>2.68</v>
       </c>
       <c r="J36">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K36">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L36">
         <v>1.48</v>
@@ -9671,19 +9671,19 @@
         <v>190</v>
       </c>
       <c r="F37">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G37">
         <v>1.44</v>
       </c>
       <c r="H37">
+        <v>8.4</v>
+      </c>
+      <c r="I37">
         <v>8.6</v>
       </c>
-      <c r="I37">
-        <v>9</v>
-      </c>
       <c r="J37">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K37">
         <v>5.5</v>
@@ -9695,7 +9695,7 @@
         <v>1.04</v>
       </c>
       <c r="N37">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O37">
         <v>1.21</v>
@@ -9713,25 +9713,25 @@
         <v>2.6</v>
       </c>
       <c r="T37">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U37">
         <v>2.06</v>
       </c>
       <c r="V37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X37">
         <v>25</v>
       </c>
       <c r="Y37">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z37">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AA37">
         <v>1000</v>
@@ -9749,7 +9749,7 @@
         <v>120</v>
       </c>
       <c r="AF37">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -9758,7 +9758,7 @@
         <v>24</v>
       </c>
       <c r="AI37">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="AJ37">
         <v>12</v>
@@ -9770,13 +9770,13 @@
         <v>32</v>
       </c>
       <c r="AM37">
-        <v>120</v>
+        <v>380</v>
       </c>
       <c r="AN37">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AO37">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP37">
         <v>21</v>
@@ -9785,7 +9785,7 @@
         <v>28</v>
       </c>
       <c r="AR37">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AS37">
         <v>50</v>
@@ -9797,28 +9797,28 @@
         <v>11</v>
       </c>
       <c r="AV37">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW37">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX37">
         <v>8.800000000000001</v>
       </c>
       <c r="AY37">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ37">
         <v>22</v>
       </c>
       <c r="BA37">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BB37">
         <v>11</v>
       </c>
       <c r="BC37">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD37">
         <v>28</v>
@@ -9842,34 +9842,34 @@
         <v>11.5</v>
       </c>
       <c r="BK37">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL37">
         <v>140</v>
       </c>
       <c r="BM37">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN37">
         <v>4.1</v>
       </c>
       <c r="BO37">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP37">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BQ37">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR37">
         <v>25</v>
       </c>
       <c r="BS37">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU37">
         <v>10</v>
@@ -9878,19 +9878,19 @@
         <v>80</v>
       </c>
       <c r="BW37">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX37">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY37">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ37">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA37">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="CB37" t="s">
         <v>197</v>
@@ -9916,7 +9916,7 @@
         <v>1.85</v>
       </c>
       <c r="G38">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H38">
         <v>4.4</v>
@@ -9949,10 +9949,10 @@
         <v>1.61</v>
       </c>
       <c r="R38">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S38">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T38">
         <v>1.63</v>
@@ -9964,7 +9964,7 @@
         <v>1.28</v>
       </c>
       <c r="W38">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X38">
         <v>22</v>
@@ -9976,7 +9976,7 @@
         <v>38</v>
       </c>
       <c r="AA38">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB38">
         <v>13</v>
@@ -10021,7 +10021,7 @@
         <v>36</v>
       </c>
       <c r="AP38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ38">
         <v>19.5</v>
@@ -10030,7 +10030,7 @@
         <v>32</v>
       </c>
       <c r="AS38">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AT38">
         <v>11.5</v>
@@ -10072,67 +10072,67 @@
         <v>7.6</v>
       </c>
       <c r="BG38">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH38">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI38">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BJ38">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK38">
+        <v>7.6</v>
+      </c>
+      <c r="BL38">
+        <v>85</v>
+      </c>
+      <c r="BM38">
+        <v>9.4</v>
+      </c>
+      <c r="BN38">
+        <v>5.2</v>
+      </c>
+      <c r="BO38">
+        <v>4.3</v>
+      </c>
+      <c r="BP38">
+        <v>12</v>
+      </c>
+      <c r="BQ38">
         <v>6.6</v>
       </c>
-      <c r="BL38">
-        <v>1000</v>
-      </c>
-      <c r="BM38">
-        <v>2.48</v>
-      </c>
-      <c r="BN38">
-        <v>1000</v>
-      </c>
-      <c r="BO38">
-        <v>1.8</v>
-      </c>
-      <c r="BP38">
-        <v>1000</v>
-      </c>
-      <c r="BQ38">
-        <v>2.34</v>
-      </c>
       <c r="BR38">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS38">
-        <v>2.56</v>
+        <v>8</v>
       </c>
       <c r="BT38">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BU38">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
       <c r="BV38">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW38">
-        <v>2.56</v>
+        <v>8</v>
       </c>
       <c r="BX38">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY38">
-        <v>2.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ38">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA38">
-        <v>2.56</v>
+        <v>6.8</v>
       </c>
       <c r="CB38" t="s">
         <v>197</v>
@@ -10161,16 +10161,16 @@
         <v>1.23</v>
       </c>
       <c r="H39">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="I39">
         <v>17.5</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K39">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L39">
         <v>1.24</v>
@@ -10185,10 +10185,10 @@
         <v>1.14</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q39">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R39">
         <v>1.85</v>
@@ -10212,7 +10212,7 @@
         <v>38</v>
       </c>
       <c r="Y39">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Z39">
         <v>1000</v>
@@ -10233,7 +10233,7 @@
         <v>1000</v>
       </c>
       <c r="AF39">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG39">
         <v>12.5</v>
@@ -10257,13 +10257,13 @@
         <v>490</v>
       </c>
       <c r="AN39">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AO39">
         <v>290</v>
       </c>
       <c r="AP39">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ39">
         <v>46</v>
@@ -10272,7 +10272,7 @@
         <v>44</v>
       </c>
       <c r="AS39">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT39">
         <v>11</v>
@@ -10281,7 +10281,7 @@
         <v>16</v>
       </c>
       <c r="AV39">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AW39">
         <v>48</v>
@@ -10305,13 +10305,13 @@
         <v>12.5</v>
       </c>
       <c r="BD39">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE39">
         <v>60</v>
       </c>
       <c r="BF39">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BG39">
         <v>50</v>
@@ -10409,7 +10409,7 @@
         <v>2.04</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K40">
         <v>4.1</v>
@@ -10421,16 +10421,16 @@
         <v>1.05</v>
       </c>
       <c r="N40">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O40">
         <v>1.23</v>
       </c>
       <c r="P40">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q40">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R40">
         <v>1.57</v>
@@ -10448,13 +10448,13 @@
         <v>1.96</v>
       </c>
       <c r="W40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X40">
         <v>21</v>
       </c>
       <c r="Y40">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z40">
         <v>14</v>
@@ -10466,7 +10466,7 @@
         <v>18.5</v>
       </c>
       <c r="AC40">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD40">
         <v>10.5</v>
@@ -10508,7 +10508,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ40">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR40">
         <v>13.5</v>
@@ -10520,22 +10520,22 @@
         <v>17.5</v>
       </c>
       <c r="AU40">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV40">
         <v>10</v>
       </c>
       <c r="AW40">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX40">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY40">
         <v>14</v>
       </c>
       <c r="AZ40">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA40">
         <v>26</v>
@@ -10884,16 +10884,16 @@
         <v>2.42</v>
       </c>
       <c r="G42">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H42">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="I42">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J42">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K42">
         <v>3.85</v>
@@ -10902,25 +10902,25 @@
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N42">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O42">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P42">
         <v>2.18</v>
       </c>
       <c r="Q42">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R42">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S42">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="T42">
         <v>1.01</v>
@@ -10929,118 +10929,118 @@
         <v>1.01</v>
       </c>
       <c r="V42">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X42">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="Y42">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z42">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AA42">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AB42">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC42">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="AD42">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE42">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF42">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AG42">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH42">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI42">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ42">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK42">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AL42">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM42">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN42">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AO42">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AP42">
-        <v>5.7</v>
+        <v>1.97</v>
       </c>
       <c r="AQ42">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR42">
-        <v>5.8</v>
+        <v>1.97</v>
       </c>
       <c r="AS42">
-        <v>6.6</v>
+        <v>1.99</v>
       </c>
       <c r="AT42">
-        <v>5.1</v>
+        <v>1.87</v>
       </c>
       <c r="AU42">
-        <v>4.2</v>
+        <v>1.76</v>
       </c>
       <c r="AV42">
-        <v>4.9</v>
+        <v>1.82</v>
       </c>
       <c r="AW42">
-        <v>6.2</v>
+        <v>1.96</v>
       </c>
       <c r="AX42">
-        <v>5.5</v>
+        <v>1.91</v>
       </c>
       <c r="AY42">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="AZ42">
-        <v>5.2</v>
+        <v>1.86</v>
       </c>
       <c r="BA42">
-        <v>6.4</v>
+        <v>1.96</v>
       </c>
       <c r="BB42">
-        <v>6.4</v>
+        <v>1.98</v>
       </c>
       <c r="BC42">
-        <v>5.9</v>
+        <v>1.96</v>
       </c>
       <c r="BD42">
-        <v>6.2</v>
+        <v>1.96</v>
       </c>
       <c r="BE42">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="BF42">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="BG42">
-        <v>5.7</v>
+        <v>1.94</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11126,16 +11126,16 @@
         <v>2.28</v>
       </c>
       <c r="G43">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H43">
         <v>3.55</v>
       </c>
       <c r="I43">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J43">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K43">
         <v>3.4</v>
@@ -11150,7 +11150,7 @@
         <v>3.15</v>
       </c>
       <c r="O43">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P43">
         <v>1.65</v>
@@ -11159,7 +11159,7 @@
         <v>2.16</v>
       </c>
       <c r="R43">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S43">
         <v>3.85</v>
@@ -11171,10 +11171,10 @@
         <v>1.92</v>
       </c>
       <c r="V43">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W43">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X43">
         <v>970</v>
@@ -11183,7 +11183,7 @@
         <v>970</v>
       </c>
       <c r="Z43">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA43">
         <v>1000</v>
@@ -11192,19 +11192,19 @@
         <v>970</v>
       </c>
       <c r="AC43">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD43">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AE43">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF43">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AG43">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AH43">
         <v>29</v>
@@ -11216,10 +11216,10 @@
         <v>55</v>
       </c>
       <c r="AK43">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL43">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM43">
         <v>1000</v>
@@ -11231,16 +11231,16 @@
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>7.4</v>
+        <v>1.78</v>
       </c>
       <c r="AQ43">
-        <v>1.91</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR43">
         <v>16</v>
       </c>
       <c r="AS43">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AT43">
         <v>6.8</v>
@@ -11249,40 +11249,40 @@
         <v>6</v>
       </c>
       <c r="AV43">
+        <v>12</v>
+      </c>
+      <c r="AW43">
         <v>1.93</v>
       </c>
-      <c r="AW43">
-        <v>2.06</v>
-      </c>
       <c r="AX43">
+        <v>9</v>
+      </c>
+      <c r="AY43">
+        <v>1.85</v>
+      </c>
+      <c r="AZ43">
+        <v>1.85</v>
+      </c>
+      <c r="BA43">
+        <v>1.98</v>
+      </c>
+      <c r="BB43">
+        <v>1.91</v>
+      </c>
+      <c r="BC43">
+        <v>1.9</v>
+      </c>
+      <c r="BD43">
         <v>1.93</v>
       </c>
-      <c r="AY43">
-        <v>1.93</v>
-      </c>
-      <c r="AZ43">
-        <v>15</v>
-      </c>
-      <c r="BA43">
-        <v>2.1</v>
-      </c>
-      <c r="BB43">
-        <v>2.02</v>
-      </c>
-      <c r="BC43">
-        <v>2.02</v>
-      </c>
-      <c r="BD43">
-        <v>2.06</v>
-      </c>
       <c r="BE43">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="BF43">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="BG43">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="BH43">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -559,7 +559,7 @@
     <t>Oriente Petrolero</t>
   </si>
   <si>
-    <t>2026-09-17 01:25:34</t>
+    <t>2026-09-17 03:45:33</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1153,7 @@
         <v>144</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
         <v>2.16</v>
@@ -1162,13 +1162,13 @@
         <v>4.8</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.69</v>
@@ -1183,19 +1183,19 @@
         <v>1.67</v>
       </c>
       <c r="P2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
         <v>1.64</v>
@@ -1228,7 +1228,7 @@
         <v>23</v>
       </c>
       <c r="AE2">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
@@ -1243,10 +1243,10 @@
         <v>160</v>
       </c>
       <c r="AJ2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL2">
         <v>85</v>
@@ -1255,7 +1255,7 @@
         <v>360</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO2">
         <v>600</v>
@@ -1282,7 +1282,7 @@
         <v>19</v>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
@@ -1297,22 +1297,22 @@
         <v>11.5</v>
       </c>
       <c r="BB2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF2">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH2">
         <v>2.76</v>
@@ -1339,7 +1339,7 @@
         <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
         <v>4.9</v>
@@ -1354,7 +1354,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
         <v>65</v>
@@ -1395,73 +1395,73 @@
         <v>145</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
         <v>2.54</v>
       </c>
       <c r="I3">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O3">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q3">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R3">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S3">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T3">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W3">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X3">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC3">
         <v>8.800000000000001</v>
@@ -1470,73 +1470,73 @@
         <v>13</v>
       </c>
       <c r="AE3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK3">
         <v>34</v>
       </c>
       <c r="AL3">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AM3">
         <v>260</v>
       </c>
       <c r="AN3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AO3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BB3">
         <v>36</v>
@@ -1545,37 +1545,37 @@
         <v>24</v>
       </c>
       <c r="BD3">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BE3">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BG3">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BN3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO3">
         <v>4.8</v>
@@ -1584,37 +1584,37 @@
         <v>25</v>
       </c>
       <c r="BQ3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS3">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
         <v>4.5</v>
       </c>
       <c r="BV3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW3">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY3">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BZ3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="CA3">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="CB3" t="s">
         <v>181</v>
@@ -1643,7 +1643,7 @@
         <v>2.32</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
         <v>3.4</v>
@@ -1664,7 +1664,7 @@
         <v>4.8</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P4">
         <v>2.28</v>
@@ -1673,13 +1673,13 @@
         <v>1.71</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
         <v>2.78</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U4">
         <v>2.44</v>
@@ -1691,10 +1691,10 @@
         <v>1.76</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z4">
         <v>26</v>
@@ -1751,25 +1751,25 @@
         <v>14</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT4">
         <v>9.800000000000001</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY4">
         <v>9.4</v>
@@ -1778,7 +1778,7 @@
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB4">
         <v>20</v>
@@ -1787,7 +1787,7 @@
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE4">
         <v>50</v>
@@ -1796,7 +1796,7 @@
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN4">
         <v>5.6</v>
@@ -1826,7 +1826,7 @@
         <v>16</v>
       </c>
       <c r="BQ4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR4">
         <v>26</v>
@@ -1844,10 +1844,10 @@
         <v>25</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY4">
         <v>7.6</v>
@@ -1882,16 +1882,16 @@
         <v>1.68</v>
       </c>
       <c r="G5">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H5">
         <v>2.16</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -1903,7 +1903,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="O5">
         <v>1.02</v>
@@ -1915,7 +1915,7 @@
         <v>1.02</v>
       </c>
       <c r="R5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S5">
         <v>1.83</v>
@@ -1930,7 +1930,7 @@
         <v>1.25</v>
       </c>
       <c r="W5">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1984,7 +1984,7 @@
         <v>600</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP5">
         <v>1.01</v>
@@ -2124,13 +2124,13 @@
         <v>7.2</v>
       </c>
       <c r="G6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>1.52</v>
       </c>
       <c r="I6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J6">
         <v>4.2</v>
@@ -2151,10 +2151,10 @@
         <v>1.33</v>
       </c>
       <c r="P6">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>1.34</v>
@@ -2166,16 +2166,16 @@
         <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
         <v>7.6</v>
@@ -2187,7 +2187,7 @@
         <v>14.5</v>
       </c>
       <c r="AB6">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2196,7 +2196,7 @@
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="AF6">
         <v>160</v>
@@ -2205,7 +2205,7 @@
         <v>40</v>
       </c>
       <c r="AH6">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AI6">
         <v>55</v>
@@ -2220,127 +2220,127 @@
         <v>460</v>
       </c>
       <c r="AM6">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN6">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AO6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AP6">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR6">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AT6">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV6">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AW6">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX6">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AZ6">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BA6">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC6">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD6">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BG6">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH6">
         <v>3.6</v>
       </c>
       <c r="BI6">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
+        <v>12.5</v>
+      </c>
+      <c r="BK6">
+        <v>5.2</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>8.4</v>
+      </c>
+      <c r="BN6">
         <v>12</v>
       </c>
-      <c r="BK6">
-        <v>1.01</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.01</v>
-      </c>
-      <c r="BN6">
-        <v>11.5</v>
-      </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BU6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BV6">
         <v>10.5</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>181</v>
@@ -2363,22 +2363,22 @@
         <v>149</v>
       </c>
       <c r="F7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
         <v>2.96</v>
       </c>
       <c r="J7">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="K7">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="L7">
         <v>1.73</v>
@@ -2387,7 +2387,7 @@
         <v>1.17</v>
       </c>
       <c r="N7">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="O7">
         <v>1.74</v>
@@ -2420,7 +2420,7 @@
         <v>7.4</v>
       </c>
       <c r="Y7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>17</v>
@@ -2453,7 +2453,7 @@
         <v>540</v>
       </c>
       <c r="AJ7">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AK7">
         <v>170</v>
@@ -2462,7 +2462,7 @@
         <v>540</v>
       </c>
       <c r="AM7">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AN7">
         <v>600</v>
@@ -2474,91 +2474,91 @@
         <v>5.5</v>
       </c>
       <c r="AQ7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS7">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU7">
         <v>6</v>
       </c>
       <c r="AV7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX7">
         <v>18</v>
       </c>
       <c r="AY7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7">
         <v>18</v>
       </c>
       <c r="BA7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC7">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE7">
+        <v>6.8</v>
+      </c>
+      <c r="BF7">
         <v>6.6</v>
       </c>
-      <c r="BF7">
-        <v>6.4</v>
-      </c>
       <c r="BG7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH7">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BI7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK7">
         <v>9.800000000000001</v>
       </c>
       <c r="BL7">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="BM7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BN7">
         <v>7.2</v>
       </c>
       <c r="BO7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BQ7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BS7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT7">
         <v>6.2</v>
@@ -2570,19 +2570,19 @@
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="CA7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
         <v>181</v>
@@ -2605,25 +2605,25 @@
         <v>150</v>
       </c>
       <c r="F8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I8">
         <v>15.5</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K8">
         <v>8</v>
       </c>
       <c r="L8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2632,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P8">
         <v>4</v>
@@ -2641,22 +2641,22 @@
         <v>1.29</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="T8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
         <v>1.07</v>
       </c>
       <c r="W8">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="X8">
         <v>320</v>
@@ -2683,13 +2683,13 @@
         <v>190</v>
       </c>
       <c r="AF8">
+        <v>13</v>
+      </c>
+      <c r="AG8">
         <v>14</v>
       </c>
-      <c r="AG8">
-        <v>16</v>
-      </c>
       <c r="AH8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8">
         <v>130</v>
@@ -2707,22 +2707,22 @@
         <v>420</v>
       </c>
       <c r="AN8">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AO8">
         <v>140</v>
       </c>
       <c r="AP8">
+        <v>23</v>
+      </c>
+      <c r="AQ8">
+        <v>9</v>
+      </c>
+      <c r="AR8">
         <v>9.6</v>
       </c>
-      <c r="AQ8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR8">
-        <v>8.6</v>
-      </c>
       <c r="AS8">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT8">
         <v>16.5</v>
@@ -2734,7 +2734,7 @@
         <v>20</v>
       </c>
       <c r="AW8">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX8">
         <v>11</v>
@@ -2749,25 +2749,25 @@
         <v>28</v>
       </c>
       <c r="BB8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD8">
         <v>23</v>
       </c>
       <c r="BE8">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="BF8">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="BG8">
         <v>10.5</v>
       </c>
       <c r="BH8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BI8">
         <v>5</v>
@@ -2776,13 +2776,13 @@
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN8">
         <v>4.6</v>
@@ -2800,25 +2800,25 @@
         <v>17</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT8">
         <v>16.5</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV8">
         <v>90</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX8">
         <v>65</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8">
         <v>6.6</v>
@@ -2850,19 +2850,19 @@
         <v>2.28</v>
       </c>
       <c r="G9">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H9">
         <v>3.3</v>
       </c>
       <c r="I9">
+        <v>3.5</v>
+      </c>
+      <c r="J9">
         <v>3.45</v>
       </c>
-      <c r="J9">
-        <v>3.5</v>
-      </c>
       <c r="K9">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L9">
         <v>1.39</v>
@@ -2880,10 +2880,10 @@
         <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
         <v>3.3</v>
@@ -2892,7 +2892,7 @@
         <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.4</v>
@@ -2904,7 +2904,7 @@
         <v>18</v>
       </c>
       <c r="Y9">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z9">
         <v>26</v>
@@ -2919,16 +2919,16 @@
         <v>8.6</v>
       </c>
       <c r="AD9">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF9">
         <v>16.5</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH9">
         <v>18</v>
@@ -2955,7 +2955,7 @@
         <v>38</v>
       </c>
       <c r="AP9">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
         <v>11.5</v>
@@ -2964,16 +2964,16 @@
         <v>17.5</v>
       </c>
       <c r="AS9">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="AT9">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9">
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW9">
         <v>28</v>
@@ -2982,25 +2982,25 @@
         <v>13</v>
       </c>
       <c r="AY9">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC9">
         <v>18</v>
       </c>
       <c r="BD9">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BE9">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BF9">
         <v>14.5</v>
@@ -3012,7 +3012,7 @@
         <v>4.1</v>
       </c>
       <c r="BI9">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9">
         <v>9.800000000000001</v>
@@ -3024,28 +3024,28 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN9">
         <v>5.5</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP9">
         <v>17.5</v>
       </c>
       <c r="BQ9">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR9">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BS9">
         <v>6</v>
       </c>
       <c r="BT9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU9">
         <v>5</v>
@@ -3054,10 +3054,10 @@
         <v>28</v>
       </c>
       <c r="BW9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX9">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BY9">
         <v>6.2</v>
@@ -3066,7 +3066,7 @@
         <v>26</v>
       </c>
       <c r="CA9">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="CB9" t="s">
         <v>181</v>
@@ -3098,10 +3098,10 @@
         <v>1.41</v>
       </c>
       <c r="I10">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="J10">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -3113,22 +3113,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
         <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="Q10">
         <v>1.31</v>
       </c>
       <c r="R10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="S10">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3137,16 +3137,16 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W10">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X10">
         <v>1000</v>
       </c>
       <c r="Y10">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="Z10">
         <v>120</v>
@@ -3331,16 +3331,16 @@
         <v>153</v>
       </c>
       <c r="F11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G11">
         <v>8.6</v>
-      </c>
-      <c r="G11">
-        <v>8.800000000000001</v>
       </c>
       <c r="H11">
         <v>1.44</v>
       </c>
       <c r="I11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J11">
         <v>5.2</v>
@@ -3352,40 +3352,40 @@
         <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
         <v>6</v>
       </c>
       <c r="O11">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q11">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R11">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S11">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="V11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y11">
         <v>11.5</v>
@@ -3403,7 +3403,7 @@
         <v>12</v>
       </c>
       <c r="AD11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE11">
         <v>14</v>
@@ -3412,40 +3412,40 @@
         <v>80</v>
       </c>
       <c r="AG11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ11">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AK11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN11">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AP11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ11">
         <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS11">
         <v>11.5</v>
@@ -3457,13 +3457,13 @@
         <v>11</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW11">
         <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AY11">
         <v>27</v>
@@ -3475,40 +3475,40 @@
         <v>26</v>
       </c>
       <c r="BB11">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="BC11">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BD11">
+        <v>70</v>
+      </c>
+      <c r="BE11">
         <v>75</v>
       </c>
-      <c r="BE11">
-        <v>65</v>
-      </c>
       <c r="BF11">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="BG11">
         <v>4.8</v>
       </c>
       <c r="BH11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ11">
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL11">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN11">
         <v>12</v>
@@ -3520,37 +3520,37 @@
         <v>65</v>
       </c>
       <c r="BQ11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BR11">
         <v>60</v>
       </c>
       <c r="BS11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BT11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BU11">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW11">
         <v>7.4</v>
       </c>
       <c r="BX11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY11">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BZ11">
         <v>12</v>
       </c>
       <c r="CA11">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB11" t="s">
         <v>181</v>
@@ -3573,19 +3573,19 @@
         <v>154</v>
       </c>
       <c r="F12">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G12">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="I12">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
         <v>3.8</v>
@@ -3606,37 +3606,37 @@
         <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T12">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U12">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V12">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X12">
         <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z12">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB12">
         <v>16.5</v>
@@ -3645,22 +3645,22 @@
         <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG12">
         <v>14</v>
       </c>
       <c r="AH12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ12">
         <v>60</v>
@@ -3669,46 +3669,46 @@
         <v>32</v>
       </c>
       <c r="AL12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM12">
         <v>65</v>
       </c>
       <c r="AN12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
       </c>
       <c r="AQ12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR12">
+        <v>14.5</v>
+      </c>
+      <c r="AS12">
+        <v>27</v>
+      </c>
+      <c r="AT12">
         <v>15.5</v>
-      </c>
-      <c r="AS12">
-        <v>28</v>
-      </c>
-      <c r="AT12">
-        <v>15</v>
       </c>
       <c r="AU12">
         <v>8</v>
       </c>
       <c r="AV12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY12">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12">
         <v>13.5</v>
@@ -3720,16 +3720,16 @@
         <v>50</v>
       </c>
       <c r="BC12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE12">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG12">
         <v>12.5</v>
@@ -3744,13 +3744,13 @@
         <v>8.6</v>
       </c>
       <c r="BK12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL12">
         <v>110</v>
       </c>
       <c r="BM12">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="BN12">
         <v>6.6</v>
@@ -3768,19 +3768,19 @@
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT12">
         <v>5.4</v>
       </c>
       <c r="BU12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
         <v>25</v>
@@ -3792,7 +3792,7 @@
         <v>19</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB12" t="s">
         <v>181</v>
@@ -3815,22 +3815,22 @@
         <v>155</v>
       </c>
       <c r="F13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G13">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="H13">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="I13">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J13">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="K13">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="L13">
         <v>1.18</v>
@@ -3839,139 +3839,139 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O13">
         <v>1.09</v>
       </c>
       <c r="P13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q13">
         <v>1.33</v>
       </c>
       <c r="R13">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S13">
         <v>1.78</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AA13">
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN13">
         <v>2.8</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP13">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="AR13">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS13">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT13">
-        <v>1.55</v>
+        <v>13</v>
       </c>
       <c r="AU13">
-        <v>1.55</v>
+        <v>18.5</v>
       </c>
       <c r="AV13">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW13">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="AX13">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13">
-        <v>1.55</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BA13">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB13">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="BC13">
-        <v>1.55</v>
+        <v>11.5</v>
       </c>
       <c r="BD13">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BE13">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13">
-        <v>1.13</v>
+        <v>2.44</v>
       </c>
       <c r="BG13">
         <v>10.5</v>
@@ -4057,19 +4057,19 @@
         <v>156</v>
       </c>
       <c r="F14">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G14">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H14">
         <v>2.42</v>
       </c>
       <c r="I14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
         <v>4.4</v>
@@ -4081,7 +4081,7 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>1.21</v>
@@ -4090,16 +4090,16 @@
         <v>2.38</v>
       </c>
       <c r="Q14">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R14">
         <v>1.54</v>
       </c>
       <c r="S14">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T14">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U14">
         <v>2.5</v>
@@ -4108,169 +4108,169 @@
         <v>1.62</v>
       </c>
       <c r="W14">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X14">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="Y14">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z14">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AA14">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB14">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC14">
-        <v>42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE14">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AF14">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AG14">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH14">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="AI14">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ14">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AK14">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AL14">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM14">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN14">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AO14">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AP14">
-        <v>1.3</v>
+        <v>16</v>
       </c>
       <c r="AQ14">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AR14">
-        <v>1.29</v>
+        <v>16</v>
       </c>
       <c r="AS14">
-        <v>1.3</v>
+        <v>16</v>
       </c>
       <c r="AT14">
-        <v>1.28</v>
+        <v>13</v>
       </c>
       <c r="AU14">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AV14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW14">
-        <v>1.3</v>
+        <v>20</v>
       </c>
       <c r="AX14">
-        <v>1.29</v>
+        <v>18.5</v>
       </c>
       <c r="AY14">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
-        <v>1.24</v>
+        <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>1.3</v>
+        <v>16</v>
       </c>
       <c r="BB14">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="BC14">
-        <v>1.3</v>
+        <v>13</v>
       </c>
       <c r="BD14">
-        <v>1.3</v>
+        <v>16</v>
       </c>
       <c r="BE14">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>1.55</v>
+        <v>15.5</v>
       </c>
       <c r="BG14">
-        <v>1.55</v>
+        <v>12.5</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>157</v>
       </c>
       <c r="F15">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="G15">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H15">
         <v>2.34</v>
       </c>
       <c r="I15">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
         <v>1.28</v>
@@ -4323,19 +4323,19 @@
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q15">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S15">
         <v>2.44</v>
@@ -4344,13 +4344,13 @@
         <v>1.55</v>
       </c>
       <c r="U15">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X15">
         <v>500</v>
@@ -4401,10 +4401,10 @@
         <v>580</v>
       </c>
       <c r="AN15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP15">
         <v>1.93</v>
@@ -4425,7 +4425,7 @@
         <v>5.1</v>
       </c>
       <c r="AV15">
-        <v>1.79</v>
+        <v>6.4</v>
       </c>
       <c r="AW15">
         <v>1.94</v>
@@ -4434,10 +4434,10 @@
         <v>1.95</v>
       </c>
       <c r="AY15">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="AZ15">
-        <v>1.85</v>
+        <v>8.4</v>
       </c>
       <c r="BA15">
         <v>1.94</v>
@@ -4541,19 +4541,19 @@
         <v>158</v>
       </c>
       <c r="F16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>1.76</v>
       </c>
       <c r="I16">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K16">
         <v>4.5</v>
@@ -4565,7 +4565,7 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O16">
         <v>1.21</v>
@@ -4574,19 +4574,19 @@
         <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R16">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S16">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T16">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
         <v>2.2</v>
@@ -4595,172 +4595,172 @@
         <v>1.25</v>
       </c>
       <c r="X16">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Y16">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z16">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AA16">
-        <v>900</v>
+        <v>19.5</v>
       </c>
       <c r="AB16">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AC16">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE16">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AF16">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG16">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AH16">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="AI16">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AJ16">
         <v>900</v>
       </c>
       <c r="AK16">
+        <v>55</v>
+      </c>
+      <c r="AL16">
+        <v>55</v>
+      </c>
+      <c r="AM16">
         <v>500</v>
       </c>
-      <c r="AL16">
-        <v>500</v>
-      </c>
-      <c r="AM16">
-        <v>580</v>
-      </c>
       <c r="AN16">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO16">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AP16">
-        <v>1.31</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16">
-        <v>1.29</v>
+        <v>10</v>
       </c>
       <c r="AR16">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="AS16">
-        <v>1.33</v>
+        <v>16.5</v>
       </c>
       <c r="AT16">
-        <v>1.32</v>
+        <v>18.5</v>
       </c>
       <c r="AU16">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>1.29</v>
+        <v>9</v>
       </c>
       <c r="AW16">
-        <v>1.31</v>
+        <v>14.5</v>
       </c>
       <c r="AX16">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="AY16">
-        <v>1.32</v>
+        <v>16</v>
       </c>
       <c r="AZ16">
-        <v>1.27</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="BB16">
-        <v>1.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC16">
-        <v>1.31</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16">
-        <v>1.31</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16">
-        <v>1.32</v>
+        <v>8.6</v>
       </c>
       <c r="BF16">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BG16">
-        <v>1.31</v>
+        <v>7.2</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="s">
         <v>181</v>
@@ -4783,22 +4783,22 @@
         <v>159</v>
       </c>
       <c r="F17">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="G17">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H17">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I17">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J17">
         <v>3.8</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>1.34</v>
@@ -4810,7 +4810,7 @@
         <v>4.4</v>
       </c>
       <c r="O17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P17">
         <v>2.2</v>
@@ -4819,148 +4819,148 @@
         <v>1.74</v>
       </c>
       <c r="R17">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S17">
         <v>2.92</v>
       </c>
       <c r="T17">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="U17">
         <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X17">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="Y17">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z17">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AA17">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB17">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC17">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="AD17">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AE17">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AF17">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AG17">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AH17">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ17">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AK17">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL17">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM17">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AN17">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AO17">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="AR17">
-        <v>1.47</v>
+        <v>12.5</v>
       </c>
       <c r="AS17">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT17">
-        <v>1.41</v>
+        <v>12.5</v>
       </c>
       <c r="AU17">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AV17">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="AW17">
-        <v>1.49</v>
+        <v>17.5</v>
       </c>
       <c r="AX17">
-        <v>1.46</v>
+        <v>19.5</v>
       </c>
       <c r="AY17">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>1.42</v>
+        <v>11.5</v>
       </c>
       <c r="BA17">
-        <v>1.49</v>
+        <v>5.7</v>
       </c>
       <c r="BB17">
-        <v>1.49</v>
+        <v>32</v>
       </c>
       <c r="BC17">
-        <v>1.48</v>
+        <v>14.5</v>
       </c>
       <c r="BD17">
-        <v>1.48</v>
+        <v>6</v>
       </c>
       <c r="BE17">
-        <v>1.49</v>
+        <v>6.2</v>
       </c>
       <c r="BF17">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BG17">
-        <v>1.55</v>
+        <v>13.5</v>
       </c>
       <c r="BH17">
         <v>4.5</v>
       </c>
       <c r="BI17">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BK17">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="BL17">
         <v>110</v>
       </c>
       <c r="BM17">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BN17">
         <v>7.6</v>
@@ -4969,34 +4969,34 @@
         <v>4.8</v>
       </c>
       <c r="BP17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ17">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BR17">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS17">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BT17">
         <v>6.6</v>
       </c>
       <c r="BU17">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV17">
         <v>21</v>
       </c>
       <c r="BW17">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BX17">
         <v>34</v>
       </c>
       <c r="BY17">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5025,10 +5025,10 @@
         <v>160</v>
       </c>
       <c r="F18">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G18">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H18">
         <v>6.4</v>
@@ -5037,10 +5037,10 @@
         <v>6.6</v>
       </c>
       <c r="J18">
+        <v>3.8</v>
+      </c>
+      <c r="K18">
         <v>3.85</v>
-      </c>
-      <c r="K18">
-        <v>3.9</v>
       </c>
       <c r="L18">
         <v>1.49</v>
@@ -5049,16 +5049,16 @@
         <v>1.09</v>
       </c>
       <c r="N18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O18">
         <v>1.42</v>
       </c>
       <c r="P18">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q18">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
         <v>1.28</v>
@@ -5070,13 +5070,13 @@
         <v>2.16</v>
       </c>
       <c r="U18">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V18">
         <v>1.17</v>
       </c>
       <c r="W18">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X18">
         <v>12</v>
@@ -5088,13 +5088,13 @@
         <v>50</v>
       </c>
       <c r="AA18">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD18">
         <v>24</v>
@@ -5103,7 +5103,7 @@
         <v>120</v>
       </c>
       <c r="AF18">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG18">
         <v>9.6</v>
@@ -5112,19 +5112,19 @@
         <v>25</v>
       </c>
       <c r="AI18">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL18">
         <v>46</v>
       </c>
       <c r="AM18">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN18">
         <v>13.5</v>
@@ -5136,16 +5136,16 @@
         <v>11</v>
       </c>
       <c r="AQ18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR18">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS18">
         <v>46</v>
       </c>
       <c r="AT18">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU18">
         <v>8.199999999999999</v>
@@ -5154,10 +5154,10 @@
         <v>23</v>
       </c>
       <c r="AW18">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AX18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY18">
         <v>9.199999999999999</v>
@@ -5172,10 +5172,10 @@
         <v>15.5</v>
       </c>
       <c r="BC18">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE18">
         <v>160</v>
@@ -5202,7 +5202,7 @@
         <v>230</v>
       </c>
       <c r="BM18">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BN18">
         <v>4.1</v>
@@ -5220,10 +5220,10 @@
         <v>32</v>
       </c>
       <c r="BS18">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BT18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU18">
         <v>8.199999999999999</v>
@@ -5232,13 +5232,13 @@
         <v>65</v>
       </c>
       <c r="BW18">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BX18">
         <v>75</v>
       </c>
       <c r="BY18">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BZ18">
         <v>27</v>
@@ -5267,19 +5267,19 @@
         <v>161</v>
       </c>
       <c r="F19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I19">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>4.2</v>
@@ -5297,13 +5297,13 @@
         <v>1.45</v>
       </c>
       <c r="P19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
         <v>4.7</v>
@@ -5315,13 +5315,13 @@
         <v>1.62</v>
       </c>
       <c r="V19">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -5330,7 +5330,7 @@
         <v>7.6</v>
       </c>
       <c r="AA19">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB19">
         <v>22</v>
@@ -5339,19 +5339,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE19">
         <v>22</v>
       </c>
       <c r="AF19">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AG19">
         <v>950</v>
       </c>
       <c r="AH19">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="AI19">
         <v>75</v>
@@ -5369,13 +5369,13 @@
         <v>330</v>
       </c>
       <c r="AN19">
-        <v>490</v>
+        <v>860</v>
       </c>
       <c r="AO19">
         <v>12</v>
       </c>
       <c r="AP19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19">
         <v>5.4</v>
@@ -5387,106 +5387,106 @@
         <v>12</v>
       </c>
       <c r="AT19">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV19">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19">
         <v>18</v>
       </c>
       <c r="AX19">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AY19">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AZ19">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BA19">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="BB19">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC19">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BD19">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BE19">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BF19">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BG19">
         <v>10.5</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI19">
-        <v>1.32</v>
+        <v>2.74</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU19">
-        <v>1.45</v>
+        <v>3.3</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB19" t="s">
         <v>181</v>
@@ -5515,16 +5515,16 @@
         <v>5.2</v>
       </c>
       <c r="H20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I20">
         <v>2.12</v>
       </c>
       <c r="J20">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L20">
         <v>1.59</v>
@@ -5533,28 +5533,28 @@
         <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P20">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q20">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R20">
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T20">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U20">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="V20">
         <v>1.89</v>
@@ -5563,7 +5563,7 @@
         <v>1.23</v>
       </c>
       <c r="X20">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y20">
         <v>6.6</v>
@@ -5602,7 +5602,7 @@
         <v>900</v>
       </c>
       <c r="AK20">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AL20">
         <v>700</v>
@@ -5614,16 +5614,16 @@
         <v>700</v>
       </c>
       <c r="AO20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP20">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ20">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR20">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS20">
         <v>21</v>
@@ -5638,97 +5638,97 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AX20">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AY20">
         <v>18.5</v>
       </c>
       <c r="AZ20">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BA20">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BB20">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BC20">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BD20">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="BE20">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF20">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG20">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI20">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU20">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="CB20" t="s">
         <v>181</v>
@@ -5754,19 +5754,19 @@
         <v>2.28</v>
       </c>
       <c r="G21">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H21">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J21">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
         <v>1.32</v>
@@ -5775,151 +5775,151 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q21">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R21">
         <v>1.5</v>
       </c>
       <c r="S21">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T21">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
         <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X21">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Y21">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z21">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AA21">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AB21">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC21">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD21">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE21">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AF21">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AG21">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH21">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AI21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AJ21">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK21">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AL21">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AM21">
         <v>580</v>
       </c>
       <c r="AN21">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO21">
         <v>500</v>
       </c>
       <c r="AP21">
-        <v>1.24</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21">
-        <v>1.22</v>
+        <v>12</v>
       </c>
       <c r="AR21">
-        <v>1.23</v>
+        <v>18</v>
       </c>
       <c r="AS21">
-        <v>1.24</v>
+        <v>9</v>
       </c>
       <c r="AT21">
-        <v>1.21</v>
+        <v>11</v>
       </c>
       <c r="AU21">
-        <v>1.21</v>
+        <v>7.8</v>
       </c>
       <c r="AV21">
-        <v>1.22</v>
+        <v>10.5</v>
       </c>
       <c r="AW21">
-        <v>1.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21">
-        <v>1.22</v>
+        <v>13</v>
       </c>
       <c r="AY21">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="AZ21">
-        <v>1.18</v>
+        <v>12</v>
       </c>
       <c r="BA21">
-        <v>1.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21">
-        <v>1.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC21">
-        <v>1.23</v>
+        <v>17</v>
       </c>
       <c r="BD21">
-        <v>1.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE21">
-        <v>1.24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21">
-        <v>1.55</v>
+        <v>12</v>
       </c>
       <c r="BG21">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK21">
         <v>1.01</v>
@@ -5931,13 +5931,13 @@
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
@@ -5949,10 +5949,10 @@
         <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -5961,7 +5961,7 @@
         <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY21">
         <v>1.01</v>
@@ -5996,7 +5996,7 @@
         <v>1.36</v>
       </c>
       <c r="G22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H22">
         <v>13</v>
@@ -6005,7 +6005,7 @@
         <v>15</v>
       </c>
       <c r="J22">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K22">
         <v>5.3</v>
@@ -6014,7 +6014,7 @@
         <v>1.47</v>
       </c>
       <c r="M22">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N22">
         <v>3.2</v>
@@ -6035,19 +6035,19 @@
         <v>4.3</v>
       </c>
       <c r="T22">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="U22">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V22">
         <v>1.07</v>
       </c>
       <c r="W22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y22">
         <v>30</v>
@@ -6059,7 +6059,7 @@
         <v>1000</v>
       </c>
       <c r="AB22">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AC22">
         <v>14.5</v>
@@ -6071,13 +6071,13 @@
         <v>610</v>
       </c>
       <c r="AF22">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AG22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH22">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AI22">
         <v>370</v>
@@ -6095,7 +6095,7 @@
         <v>470</v>
       </c>
       <c r="AN22">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO22">
         <v>1000</v>
@@ -6107,34 +6107,34 @@
         <v>21</v>
       </c>
       <c r="AR22">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS22">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT22">
         <v>5.1</v>
       </c>
       <c r="AU22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV22">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW22">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX22">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AY22">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BA22">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BB22">
         <v>9.199999999999999</v>
@@ -6143,76 +6143,76 @@
         <v>16.5</v>
       </c>
       <c r="BD22">
+        <v>29</v>
+      </c>
+      <c r="BE22">
+        <v>8.4</v>
+      </c>
+      <c r="BF22">
         <v>7.6</v>
       </c>
-      <c r="BE22">
+      <c r="BG22">
+        <v>10.5</v>
+      </c>
+      <c r="BH22">
+        <v>3.65</v>
+      </c>
+      <c r="BI22">
+        <v>2.88</v>
+      </c>
+      <c r="BJ22">
+        <v>16</v>
+      </c>
+      <c r="BK22">
+        <v>4.9</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
         <v>7</v>
       </c>
-      <c r="BF22">
-        <v>8</v>
-      </c>
-      <c r="BG22">
-        <v>15</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.01</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.01</v>
-      </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB22" t="s">
         <v>181</v>
@@ -6235,19 +6235,19 @@
         <v>165</v>
       </c>
       <c r="F23">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H23">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I23">
         <v>2.06</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K23">
         <v>4.5</v>
@@ -6262,7 +6262,7 @@
         <v>5.5</v>
       </c>
       <c r="O23">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P23">
         <v>2.58</v>
@@ -6274,181 +6274,181 @@
         <v>1.63</v>
       </c>
       <c r="S23">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T23">
         <v>1.6</v>
       </c>
       <c r="U23">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="V23">
         <v>1.94</v>
       </c>
       <c r="W23">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X23">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="Y23">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="Z23">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AA23">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AB23">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AC23">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD23">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE23">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AF23">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG23">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AH23">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="AI23">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ23">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AK23">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AL23">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AM23">
-        <v>580</v>
+        <v>70</v>
       </c>
       <c r="AN23">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO23">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP23">
-        <v>1.41</v>
+        <v>18.5</v>
       </c>
       <c r="AQ23">
-        <v>1.36</v>
+        <v>12</v>
       </c>
       <c r="AR23">
-        <v>1.38</v>
+        <v>13.5</v>
       </c>
       <c r="AS23">
-        <v>1.4</v>
+        <v>20</v>
       </c>
       <c r="AT23">
-        <v>1.38</v>
+        <v>17</v>
       </c>
       <c r="AU23">
-        <v>1.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV23">
-        <v>1.36</v>
+        <v>9.6</v>
       </c>
       <c r="AW23">
-        <v>1.38</v>
+        <v>15.5</v>
       </c>
       <c r="AX23">
-        <v>1.39</v>
+        <v>21</v>
       </c>
       <c r="AY23">
-        <v>1.39</v>
+        <v>13.5</v>
       </c>
       <c r="AZ23">
-        <v>1.34</v>
+        <v>13.5</v>
       </c>
       <c r="BA23">
-        <v>1.4</v>
+        <v>19</v>
       </c>
       <c r="BB23">
-        <v>1.41</v>
+        <v>36</v>
       </c>
       <c r="BC23">
-        <v>1.4</v>
+        <v>25</v>
       </c>
       <c r="BD23">
-        <v>1.41</v>
+        <v>25</v>
       </c>
       <c r="BE23">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF23">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BG23">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ23">
         <v>0</v>
@@ -6477,58 +6477,58 @@
         <v>166</v>
       </c>
       <c r="F24">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="G24">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="I24">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="J24">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
+        <v>1.02</v>
+      </c>
+      <c r="N24">
+        <v>1.26</v>
+      </c>
+      <c r="O24">
         <v>1.03</v>
       </c>
-      <c r="N24">
-        <v>5.1</v>
-      </c>
-      <c r="O24">
-        <v>1.17</v>
-      </c>
       <c r="P24">
-        <v>2.62</v>
+        <v>1.26</v>
       </c>
       <c r="Q24">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="R24">
-        <v>1.64</v>
+        <v>1.08</v>
       </c>
       <c r="S24">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="T24">
         <v>1.51</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="V24">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="X24">
         <v>500</v>
@@ -6579,28 +6579,28 @@
         <v>580</v>
       </c>
       <c r="AN24">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO24">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP24">
         <v>1.34</v>
       </c>
       <c r="AQ24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AR24">
         <v>1.32</v>
       </c>
       <c r="AS24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AT24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AU24">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV24">
         <v>1.31</v>
@@ -6615,19 +6615,19 @@
         <v>1.31</v>
       </c>
       <c r="AZ24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BA24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BB24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BC24">
         <v>1.33</v>
       </c>
       <c r="BD24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BE24">
         <v>1.33</v>
@@ -6719,220 +6719,220 @@
         <v>167</v>
       </c>
       <c r="F25">
-        <v>1.12</v>
+        <v>1.84</v>
       </c>
       <c r="G25">
-        <v>950</v>
+        <v>1.99</v>
       </c>
       <c r="H25">
-        <v>1.12</v>
+        <v>5.1</v>
       </c>
       <c r="I25">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="K25">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N25">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="O25">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P25">
-        <v>1.09</v>
+        <v>1.58</v>
       </c>
       <c r="Q25">
-        <v>1.44</v>
+        <v>2.46</v>
       </c>
       <c r="R25">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S25">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V25">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         <v>168</v>
       </c>
       <c r="F26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G26">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H26">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I26">
         <v>1.52</v>
@@ -6985,7 +6985,7 @@
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O26">
         <v>1.23</v>
@@ -6994,22 +6994,22 @@
         <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R26">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S26">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T26">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V26">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="W26">
         <v>1.13</v>
@@ -7018,13 +7018,13 @@
         <v>25</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z26">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA26">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AB26">
         <v>30</v>
@@ -7036,7 +7036,7 @@
         <v>12</v>
       </c>
       <c r="AE26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF26">
         <v>160</v>
@@ -7045,7 +7045,7 @@
         <v>32</v>
       </c>
       <c r="AH26">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI26">
         <v>38</v>
@@ -7063,121 +7063,121 @@
         <v>380</v>
       </c>
       <c r="AN26">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AO26">
         <v>6.6</v>
       </c>
       <c r="AP26">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AQ26">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR26">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS26">
+        <v>10</v>
+      </c>
+      <c r="AT26">
+        <v>21</v>
+      </c>
+      <c r="AU26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV26">
+        <v>7.6</v>
+      </c>
+      <c r="AW26">
         <v>10.5</v>
       </c>
-      <c r="AT26">
-        <v>7.6</v>
-      </c>
-      <c r="AU26">
-        <v>4.7</v>
-      </c>
-      <c r="AV26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW26">
-        <v>11.5</v>
-      </c>
       <c r="AX26">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AY26">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="AZ26">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BA26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB26">
-        <v>7.8</v>
+        <v>65</v>
       </c>
       <c r="BC26">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BD26">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BE26">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BF26">
-        <v>7.4</v>
+        <v>48</v>
       </c>
       <c r="BG26">
         <v>5.7</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL26">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM26">
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ26">
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS26">
         <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA26">
         <v>1.01</v>
@@ -7203,16 +7203,16 @@
         <v>169</v>
       </c>
       <c r="F27">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="G27">
+        <v>2.62</v>
+      </c>
+      <c r="H27">
+        <v>2.88</v>
+      </c>
+      <c r="I27">
         <v>2.9</v>
-      </c>
-      <c r="H27">
-        <v>2.62</v>
-      </c>
-      <c r="I27">
-        <v>2.66</v>
       </c>
       <c r="J27">
         <v>3.65</v>
@@ -7221,7 +7221,7 @@
         <v>3.7</v>
       </c>
       <c r="L27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M27">
         <v>1.06</v>
@@ -7233,13 +7233,13 @@
         <v>1.26</v>
       </c>
       <c r="P27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q27">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R27">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S27">
         <v>3</v>
@@ -7251,25 +7251,25 @@
         <v>2.44</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W27">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="X27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y27">
         <v>13.5</v>
       </c>
       <c r="Z27">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AA27">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB27">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC27">
         <v>8.199999999999999</v>
@@ -7278,151 +7278,151 @@
         <v>12.5</v>
       </c>
       <c r="AE27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AF27">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG27">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH27">
         <v>15.5</v>
       </c>
       <c r="AI27">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ27">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK27">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL27">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM27">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN27">
+        <v>18.5</v>
+      </c>
+      <c r="AO27">
         <v>22</v>
-      </c>
-      <c r="AO27">
-        <v>19</v>
       </c>
       <c r="AP27">
         <v>16</v>
       </c>
       <c r="AQ27">
+        <v>13</v>
+      </c>
+      <c r="AR27">
+        <v>18.5</v>
+      </c>
+      <c r="AS27">
+        <v>40</v>
+      </c>
+      <c r="AT27">
         <v>12</v>
-      </c>
-      <c r="AR27">
-        <v>16.5</v>
-      </c>
-      <c r="AS27">
-        <v>34</v>
-      </c>
-      <c r="AT27">
-        <v>13</v>
       </c>
       <c r="AU27">
         <v>7.8</v>
       </c>
       <c r="AV27">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX27">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA27">
+        <v>32</v>
+      </c>
+      <c r="BB27">
+        <v>32</v>
+      </c>
+      <c r="BC27">
+        <v>23</v>
+      </c>
+      <c r="BD27">
         <v>30</v>
-      </c>
-      <c r="BB27">
-        <v>38</v>
-      </c>
-      <c r="BC27">
-        <v>26</v>
-      </c>
-      <c r="BD27">
-        <v>32</v>
       </c>
       <c r="BE27">
         <v>60</v>
       </c>
       <c r="BF27">
+        <v>16.5</v>
+      </c>
+      <c r="BG27">
         <v>19.5</v>
       </c>
-      <c r="BG27">
-        <v>17</v>
-      </c>
       <c r="BH27">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BI27">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK27">
-        <v>2.14</v>
+        <v>7.8</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM27">
-        <v>2.46</v>
+        <v>14</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO27">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ27">
+        <v>16</v>
+      </c>
+      <c r="BR27">
+        <v>28</v>
+      </c>
+      <c r="BS27">
+        <v>10.5</v>
+      </c>
+      <c r="BT27">
+        <v>6.2</v>
+      </c>
+      <c r="BU27">
+        <v>5.5</v>
+      </c>
+      <c r="BV27">
+        <v>21</v>
+      </c>
+      <c r="BW27">
+        <v>17.5</v>
+      </c>
+      <c r="BX27">
+        <v>30</v>
+      </c>
+      <c r="BY27">
         <v>11</v>
       </c>
-      <c r="BR27">
-        <v>1000</v>
-      </c>
-      <c r="BS27">
-        <v>2.46</v>
-      </c>
-      <c r="BT27">
-        <v>1000</v>
-      </c>
-      <c r="BU27">
-        <v>4.5</v>
-      </c>
-      <c r="BV27">
-        <v>1000</v>
-      </c>
-      <c r="BW27">
-        <v>2.48</v>
-      </c>
-      <c r="BX27">
-        <v>1000</v>
-      </c>
-      <c r="BY27">
-        <v>2.46</v>
-      </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA27">
-        <v>2.46</v>
+        <v>9.4</v>
       </c>
       <c r="CB27" t="s">
         <v>181</v>
@@ -7445,16 +7445,16 @@
         <v>170</v>
       </c>
       <c r="F28">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G28">
         <v>3.2</v>
       </c>
       <c r="H28">
+        <v>2.38</v>
+      </c>
+      <c r="I28">
         <v>2.4</v>
-      </c>
-      <c r="I28">
-        <v>2.44</v>
       </c>
       <c r="J28">
         <v>3.7</v>
@@ -7469,7 +7469,7 @@
         <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O28">
         <v>1.24</v>
@@ -7484,16 +7484,16 @@
         <v>1.51</v>
       </c>
       <c r="S28">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T28">
         <v>1.63</v>
       </c>
       <c r="U28">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W28">
         <v>1.45</v>
@@ -7505,7 +7505,7 @@
         <v>13</v>
       </c>
       <c r="Z28">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA28">
         <v>32</v>
@@ -7523,7 +7523,7 @@
         <v>23</v>
       </c>
       <c r="AF28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG28">
         <v>13.5</v>
@@ -7550,10 +7550,10 @@
         <v>24</v>
       </c>
       <c r="AO28">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP28">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ28">
         <v>12</v>
@@ -7562,10 +7562,10 @@
         <v>16</v>
       </c>
       <c r="AS28">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU28">
         <v>8</v>
@@ -7592,7 +7592,7 @@
         <v>44</v>
       </c>
       <c r="BC28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD28">
         <v>34</v>
@@ -7601,13 +7601,13 @@
         <v>55</v>
       </c>
       <c r="BF28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG28">
         <v>14</v>
       </c>
       <c r="BH28">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI28">
         <v>3.6</v>
@@ -7622,7 +7622,7 @@
         <v>90</v>
       </c>
       <c r="BM28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BN28">
         <v>6.4</v>
@@ -7634,7 +7634,7 @@
         <v>22</v>
       </c>
       <c r="BQ28">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BR28">
         <v>30</v>
@@ -7646,13 +7646,13 @@
         <v>5.5</v>
       </c>
       <c r="BU28">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX28">
         <v>26</v>
@@ -7687,67 +7687,67 @@
         <v>171</v>
       </c>
       <c r="F29">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G29">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="H29">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I29">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J29">
+        <v>4.4</v>
+      </c>
+      <c r="K29">
         <v>4.5</v>
       </c>
-      <c r="K29">
-        <v>4.6</v>
-      </c>
       <c r="L29">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P29">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="Q29">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R29">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S29">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T29">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U29">
         <v>2.24</v>
       </c>
       <c r="V29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W29">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="X29">
+        <v>21</v>
+      </c>
+      <c r="Y29">
         <v>22</v>
       </c>
-      <c r="Y29">
-        <v>27</v>
-      </c>
       <c r="Z29">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA29">
         <v>160</v>
@@ -7756,52 +7756,52 @@
         <v>10.5</v>
       </c>
       <c r="AC29">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD29">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE29">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AF29">
         <v>11</v>
       </c>
       <c r="AG29">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH29">
         <v>19</v>
       </c>
       <c r="AI29">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ29">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AK29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM29">
-        <v>310</v>
+        <v>95</v>
       </c>
       <c r="AN29">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AO29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP29">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AQ29">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AR29">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AS29">
         <v>44</v>
@@ -7810,19 +7810,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU29">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV29">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW29">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AX29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY29">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29">
         <v>17</v>
@@ -7831,40 +7831,40 @@
         <v>55</v>
       </c>
       <c r="BB29">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC29">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE29">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BF29">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG29">
         <v>55</v>
       </c>
       <c r="BH29">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BI29">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BJ29">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BK29">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL29">
         <v>120</v>
       </c>
       <c r="BM29">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BN29">
         <v>4.4</v>
@@ -7873,40 +7873,40 @@
         <v>3.95</v>
       </c>
       <c r="BP29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ29">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR29">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BS29">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BT29">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU29">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV29">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BW29">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BX29">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BY29">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="BZ29">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="CA29">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CB29" t="s">
         <v>181</v>
@@ -7929,19 +7929,19 @@
         <v>172</v>
       </c>
       <c r="F30">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G30">
         <v>1.81</v>
       </c>
       <c r="H30">
+        <v>4.7</v>
+      </c>
+      <c r="I30">
         <v>4.8</v>
       </c>
-      <c r="I30">
-        <v>4.9</v>
-      </c>
       <c r="J30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K30">
         <v>4.3</v>
@@ -7959,37 +7959,37 @@
         <v>1.19</v>
       </c>
       <c r="P30">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q30">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R30">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S30">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T30">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U30">
         <v>2.58</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W30">
         <v>2.22</v>
       </c>
       <c r="X30">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z30">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA30">
         <v>90</v>
@@ -8001,7 +8001,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD30">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE30">
         <v>48</v>
@@ -8010,7 +8010,7 @@
         <v>13.5</v>
       </c>
       <c r="AG30">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH30">
         <v>15.5</v>
@@ -8034,19 +8034,19 @@
         <v>7.6</v>
       </c>
       <c r="AO30">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP30">
         <v>22</v>
       </c>
       <c r="AQ30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR30">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS30">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AT30">
         <v>12</v>
@@ -8058,13 +8058,13 @@
         <v>17.5</v>
       </c>
       <c r="AW30">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX30">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY30">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30">
         <v>14.5</v>
@@ -8079,76 +8079,76 @@
         <v>15.5</v>
       </c>
       <c r="BD30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE30">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF30">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG30">
         <v>32</v>
       </c>
       <c r="BH30">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI30">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BJ30">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK30">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM30">
-        <v>2.36</v>
+        <v>13</v>
       </c>
       <c r="BN30">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO30">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ30">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS30">
-        <v>2.38</v>
+        <v>17</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU30">
-        <v>2.04</v>
+        <v>7.4</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW30">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY30">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA30">
-        <v>2.36</v>
+        <v>8</v>
       </c>
       <c r="CB30" t="s">
         <v>181</v>
@@ -8171,7 +8171,7 @@
         <v>173</v>
       </c>
       <c r="F31">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G31">
         <v>3.15</v>
@@ -8180,7 +8180,7 @@
         <v>2.44</v>
       </c>
       <c r="I31">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J31">
         <v>3.65</v>
@@ -8207,7 +8207,7 @@
         <v>1.92</v>
       </c>
       <c r="R31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
         <v>3.3</v>
@@ -8219,13 +8219,13 @@
         <v>2.28</v>
       </c>
       <c r="V31">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W31">
         <v>1.46</v>
       </c>
       <c r="X31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y31">
         <v>11.5</v>
@@ -8240,7 +8240,7 @@
         <v>13.5</v>
       </c>
       <c r="AC31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD31">
         <v>11.5</v>
@@ -8252,7 +8252,7 @@
         <v>23</v>
       </c>
       <c r="AG31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH31">
         <v>17</v>
@@ -8264,7 +8264,7 @@
         <v>55</v>
       </c>
       <c r="AK31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL31">
         <v>44</v>
@@ -8279,16 +8279,16 @@
         <v>19</v>
       </c>
       <c r="AP31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ31">
         <v>10.5</v>
       </c>
       <c r="AR31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT31">
         <v>11.5</v>
@@ -8312,7 +8312,7 @@
         <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB31">
         <v>46</v>
@@ -8324,73 +8324,73 @@
         <v>36</v>
       </c>
       <c r="BE31">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BF31">
         <v>24</v>
       </c>
       <c r="BG31">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI31">
-        <v>1.38</v>
+        <v>3.2</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK31">
-        <v>1.15</v>
+        <v>5.7</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO31">
-        <v>1.18</v>
+        <v>5.6</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ31">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS31">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU31">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW31">
-        <v>1.38</v>
+        <v>7.4</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB31" t="s">
         <v>181</v>
@@ -8416,7 +8416,7 @@
         <v>1.42</v>
       </c>
       <c r="G32">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H32">
         <v>8.4</v>
@@ -8425,106 +8425,106 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J32">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K32">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L32">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M32">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N32">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P32">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="Q32">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R32">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S32">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T32">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U32">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W32">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X32">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z32">
         <v>80</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD32">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE32">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF32">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG32">
         <v>10</v>
       </c>
       <c r="AH32">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI32">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ32">
         <v>12</v>
       </c>
       <c r="AK32">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL32">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM32">
+        <v>100</v>
+      </c>
+      <c r="AN32">
+        <v>5</v>
+      </c>
+      <c r="AO32">
         <v>120</v>
       </c>
-      <c r="AN32">
-        <v>5.4</v>
-      </c>
-      <c r="AO32">
-        <v>110</v>
-      </c>
       <c r="AP32">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AQ32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR32">
         <v>65</v>
@@ -8533,19 +8533,19 @@
         <v>50</v>
       </c>
       <c r="AT32">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU32">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV32">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW32">
         <v>38</v>
       </c>
       <c r="AX32">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY32">
         <v>9.6</v>
@@ -8554,7 +8554,7 @@
         <v>22</v>
       </c>
       <c r="BA32">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BB32">
         <v>11.5</v>
@@ -8563,52 +8563,52 @@
         <v>13</v>
       </c>
       <c r="BD32">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BE32">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BF32">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG32">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="BH32">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BI32">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BJ32">
         <v>11</v>
       </c>
       <c r="BK32">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL32">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="BM32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN32">
         <v>4.1</v>
       </c>
       <c r="BO32">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP32">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ32">
         <v>7.4</v>
       </c>
       <c r="BR32">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BS32">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BT32">
         <v>12</v>
@@ -8617,19 +8617,19 @@
         <v>10</v>
       </c>
       <c r="BV32">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BW32">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BX32">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BZ32">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CA32">
         <v>9.800000000000001</v>
@@ -8655,22 +8655,22 @@
         <v>175</v>
       </c>
       <c r="F33">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G33">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H33">
+        <v>4.3</v>
+      </c>
+      <c r="I33">
         <v>4.4</v>
       </c>
-      <c r="I33">
-        <v>4.5</v>
-      </c>
       <c r="J33">
+        <v>4.1</v>
+      </c>
+      <c r="K33">
         <v>4.2</v>
-      </c>
-      <c r="K33">
-        <v>4.3</v>
       </c>
       <c r="L33">
         <v>1.31</v>
@@ -8679,73 +8679,73 @@
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O33">
         <v>1.2</v>
       </c>
       <c r="P33">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q33">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R33">
+        <v>1.6</v>
+      </c>
+      <c r="S33">
+        <v>2.58</v>
+      </c>
+      <c r="T33">
         <v>1.63</v>
       </c>
-      <c r="S33">
-        <v>2.52</v>
-      </c>
-      <c r="T33">
-        <v>1.62</v>
-      </c>
       <c r="U33">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W33">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y33">
         <v>22</v>
       </c>
       <c r="Z33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB33">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC33">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH33">
         <v>16</v>
       </c>
       <c r="AI33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK33">
         <v>17</v>
@@ -8757,19 +8757,19 @@
         <v>65</v>
       </c>
       <c r="AN33">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP33">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ33">
         <v>19.5</v>
       </c>
       <c r="AR33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS33">
         <v>55</v>
@@ -8778,19 +8778,19 @@
         <v>11.5</v>
       </c>
       <c r="AU33">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV33">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW33">
         <v>40</v>
       </c>
       <c r="AX33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY33">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33">
         <v>15</v>
@@ -8799,10 +8799,10 @@
         <v>40</v>
       </c>
       <c r="BB33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD33">
         <v>24</v>
@@ -8811,10 +8811,10 @@
         <v>50</v>
       </c>
       <c r="BF33">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH33">
         <v>4.4</v>
@@ -8823,7 +8823,7 @@
         <v>3.9</v>
       </c>
       <c r="BJ33">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK33">
         <v>7.8</v>
@@ -8832,7 +8832,7 @@
         <v>85</v>
       </c>
       <c r="BM33">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BN33">
         <v>5</v>
@@ -8841,37 +8841,37 @@
         <v>4.4</v>
       </c>
       <c r="BP33">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ33">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BR33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS33">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT33">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU33">
         <v>7</v>
       </c>
       <c r="BV33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW33">
         <v>9.6</v>
       </c>
       <c r="BX33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY33">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA33">
         <v>7.4</v>
@@ -8897,10 +8897,10 @@
         <v>176</v>
       </c>
       <c r="F34">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H34">
         <v>2.48</v>
@@ -8909,10 +8909,10 @@
         <v>2.68</v>
       </c>
       <c r="J34">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="K34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L34">
         <v>1.48</v>
@@ -8927,22 +8927,22 @@
         <v>1.55</v>
       </c>
       <c r="P34">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q34">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R34">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S34">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="T34">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U34">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V34">
         <v>1.59</v>
@@ -8954,34 +8954,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y34">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z34">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA34">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB34">
         <v>11.5</v>
       </c>
       <c r="AC34">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD34">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE34">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF34">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG34">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH34">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI34">
         <v>75</v>
@@ -9014,7 +9014,7 @@
         <v>12.5</v>
       </c>
       <c r="AS34">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="AT34">
         <v>8.6</v>
@@ -9026,16 +9026,16 @@
         <v>11</v>
       </c>
       <c r="AW34">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AX34">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY34">
         <v>13</v>
       </c>
       <c r="AZ34">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA34">
         <v>28</v>
@@ -9053,10 +9053,10 @@
         <v>28</v>
       </c>
       <c r="BF34">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="BG34">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9148,13 +9148,13 @@
         <v>16.5</v>
       </c>
       <c r="I35">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J35">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K35">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L35">
         <v>1.24</v>
@@ -9178,7 +9178,7 @@
         <v>1.85</v>
       </c>
       <c r="S35">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T35">
         <v>2.08</v>
@@ -9193,13 +9193,13 @@
         <v>5.5</v>
       </c>
       <c r="X35">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y35">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z35">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA35">
         <v>1000</v>
@@ -9214,22 +9214,22 @@
         <v>60</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF35">
         <v>8.800000000000001</v>
       </c>
       <c r="AG35">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH35">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI35">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ35">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AK35">
         <v>13.5</v>
@@ -9238,28 +9238,28 @@
         <v>36</v>
       </c>
       <c r="AM35">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN35">
         <v>3.3</v>
       </c>
       <c r="AO35">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AP35">
         <v>32</v>
       </c>
       <c r="AQ35">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AR35">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS35">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="AT35">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU35">
         <v>16.5</v>
@@ -9271,52 +9271,52 @@
         <v>48</v>
       </c>
       <c r="AX35">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY35">
         <v>11</v>
       </c>
       <c r="AZ35">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA35">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BB35">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD35">
         <v>30</v>
       </c>
       <c r="BE35">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BF35">
         <v>3.2</v>
       </c>
       <c r="BG35">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BH35">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI35">
         <v>4.7</v>
       </c>
       <c r="BJ35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK35">
         <v>11</v>
       </c>
       <c r="BL35">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BM35">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BN35">
         <v>3.9</v>
@@ -9334,31 +9334,31 @@
         <v>21</v>
       </c>
       <c r="BS35">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BT35">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BU35">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BW35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX35">
         <v>90</v>
       </c>
       <c r="BY35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ35">
         <v>8</v>
       </c>
       <c r="CA35">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="CB35" t="s">
         <v>181</v>
@@ -9381,22 +9381,22 @@
         <v>178</v>
       </c>
       <c r="F36">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G36">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H36">
         <v>2.02</v>
       </c>
       <c r="I36">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J36">
         <v>3.95</v>
       </c>
       <c r="K36">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L36">
         <v>1.33</v>
@@ -9411,13 +9411,13 @@
         <v>1.23</v>
       </c>
       <c r="P36">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q36">
         <v>1.68</v>
       </c>
       <c r="R36">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S36">
         <v>2.72</v>
@@ -9426,13 +9426,13 @@
         <v>1.63</v>
       </c>
       <c r="U36">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V36">
         <v>1.96</v>
       </c>
       <c r="W36">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X36">
         <v>21</v>
@@ -9441,22 +9441,22 @@
         <v>12.5</v>
       </c>
       <c r="Z36">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB36">
         <v>18.5</v>
       </c>
       <c r="AC36">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD36">
         <v>10.5</v>
       </c>
       <c r="AE36">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF36">
         <v>30</v>
@@ -9489,19 +9489,19 @@
         <v>10.5</v>
       </c>
       <c r="AP36">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ36">
         <v>11.5</v>
       </c>
       <c r="AR36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS36">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT36">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU36">
         <v>8.800000000000001</v>
@@ -9525,13 +9525,13 @@
         <v>26</v>
       </c>
       <c r="BB36">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC36">
         <v>34</v>
       </c>
       <c r="BD36">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE36">
         <v>55</v>
@@ -9540,10 +9540,10 @@
         <v>27</v>
       </c>
       <c r="BG36">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH36">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI36">
         <v>3.8</v>
@@ -9555,10 +9555,10 @@
         <v>8</v>
       </c>
       <c r="BL36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BM36">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN36">
         <v>7.2</v>
@@ -9567,16 +9567,16 @@
         <v>6.6</v>
       </c>
       <c r="BP36">
+        <v>28</v>
+      </c>
+      <c r="BQ36">
+        <v>19</v>
+      </c>
+      <c r="BR36">
         <v>34</v>
       </c>
-      <c r="BQ36">
-        <v>9.6</v>
-      </c>
-      <c r="BR36">
-        <v>40</v>
-      </c>
       <c r="BS36">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT36">
         <v>5.1</v>
@@ -9594,13 +9594,13 @@
         <v>24</v>
       </c>
       <c r="BY36">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BZ36">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="CA36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB36" t="s">
         <v>181</v>
@@ -9629,7 +9629,7 @@
         <v>1000</v>
       </c>
       <c r="H37">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="I37">
         <v>1000</v>
@@ -9638,7 +9638,7 @@
         <v>1.12</v>
       </c>
       <c r="K37">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9782,7 +9782,7 @@
         <v>1.01</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9865,19 +9865,19 @@
         <v>180</v>
       </c>
       <c r="F38">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G38">
         <v>2.62</v>
       </c>
       <c r="H38">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="I38">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J38">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K38">
         <v>4.2</v>
@@ -9886,43 +9886,43 @@
         <v>1.31</v>
       </c>
       <c r="M38">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N38">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P38">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q38">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R38">
+        <v>1.52</v>
+      </c>
+      <c r="S38">
+        <v>2.6</v>
+      </c>
+      <c r="T38">
         <v>1.53</v>
-      </c>
-      <c r="S38">
-        <v>2.68</v>
-      </c>
-      <c r="T38">
-        <v>1.56</v>
       </c>
       <c r="U38">
         <v>2.42</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W38">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X38">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y38">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z38">
         <v>23</v>
@@ -9934,7 +9934,7 @@
         <v>15</v>
       </c>
       <c r="AC38">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD38">
         <v>13.5</v>
@@ -9973,58 +9973,58 @@
         <v>19.5</v>
       </c>
       <c r="AP38">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="AQ38">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR38">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="AS38">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT38">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AU38">
+        <v>4.6</v>
+      </c>
+      <c r="AV38">
+        <v>5.3</v>
+      </c>
+      <c r="AW38">
+        <v>6.8</v>
+      </c>
+      <c r="AX38">
+        <v>6</v>
+      </c>
+      <c r="AY38">
+        <v>6.4</v>
+      </c>
+      <c r="AZ38">
+        <v>5.7</v>
+      </c>
+      <c r="BA38">
+        <v>7</v>
+      </c>
+      <c r="BB38">
+        <v>7</v>
+      </c>
+      <c r="BC38">
+        <v>6.6</v>
+      </c>
+      <c r="BD38">
+        <v>7</v>
+      </c>
+      <c r="BE38">
         <v>7.8</v>
       </c>
-      <c r="AV38">
-        <v>11</v>
-      </c>
-      <c r="AW38">
-        <v>7.4</v>
-      </c>
-      <c r="AX38">
-        <v>16</v>
-      </c>
-      <c r="AY38">
-        <v>10</v>
-      </c>
-      <c r="AZ38">
-        <v>12.5</v>
-      </c>
-      <c r="BA38">
-        <v>7.8</v>
-      </c>
-      <c r="BB38">
-        <v>16</v>
-      </c>
-      <c r="BC38">
-        <v>20</v>
-      </c>
-      <c r="BD38">
-        <v>14.5</v>
-      </c>
-      <c r="BE38">
-        <v>8.6</v>
-      </c>
       <c r="BF38">
-        <v>13.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG38">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="BH38">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-17.xlsx
@@ -577,7 +577,7 @@
     <t>Oriente Petrolero</t>
   </si>
   <si>
-    <t>2026-09-17 06:05:55</t>
+    <t>2026-09-17 08:27:38</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1171,7 @@
         <v>148</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G2">
         <v>2.18</v>
@@ -1180,16 +1180,16 @@
         <v>4.7</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M2">
         <v>1.16</v>
@@ -1201,25 +1201,25 @@
         <v>1.67</v>
       </c>
       <c r="P2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
         <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
         <v>1.65</v>
       </c>
       <c r="V2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
         <v>1.84</v>
@@ -1234,7 +1234,7 @@
         <v>36</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB2">
         <v>6.2</v>
@@ -1246,7 +1246,7 @@
         <v>23</v>
       </c>
       <c r="AE2">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
@@ -1261,22 +1261,22 @@
         <v>160</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AM2">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="AP2">
         <v>6.4</v>
@@ -1285,112 +1285,112 @@
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AS2">
         <v>11.5</v>
       </c>
       <c r="AT2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY2">
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA2">
         <v>11.5</v>
       </c>
       <c r="BB2">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BC2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BD2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE2">
         <v>12</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH2">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BI2">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2">
         <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="BM2">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
         <v>22</v>
       </c>
       <c r="BQ2">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS2">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV2">
         <v>65</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BY2">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>65</v>
       </c>
       <c r="CA2">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1413,226 +1413,226 @@
         <v>149</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="H3">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O3">
         <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
         <v>1.9</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U3">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
+        <v>17</v>
+      </c>
+      <c r="Y3">
+        <v>13</v>
+      </c>
+      <c r="Z3">
+        <v>22</v>
+      </c>
+      <c r="AA3">
+        <v>55</v>
+      </c>
+      <c r="AB3">
+        <v>12</v>
+      </c>
+      <c r="AC3">
+        <v>8.4</v>
+      </c>
+      <c r="AD3">
+        <v>14</v>
+      </c>
+      <c r="AE3">
+        <v>38</v>
+      </c>
+      <c r="AF3">
+        <v>21</v>
+      </c>
+      <c r="AG3">
+        <v>13</v>
+      </c>
+      <c r="AH3">
         <v>17.5</v>
       </c>
-      <c r="Y3">
-        <v>970</v>
-      </c>
-      <c r="Z3">
-        <v>970</v>
-      </c>
-      <c r="AA3">
-        <v>900</v>
-      </c>
-      <c r="AB3">
-        <v>970</v>
-      </c>
-      <c r="AC3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>970</v>
-      </c>
-      <c r="AE3">
-        <v>60</v>
-      </c>
-      <c r="AF3">
-        <v>23</v>
-      </c>
-      <c r="AG3">
-        <v>970</v>
-      </c>
-      <c r="AH3">
-        <v>970</v>
-      </c>
       <c r="AI3">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AL3">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>600</v>
+        <v>26</v>
       </c>
       <c r="AO3">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AP3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS3">
-        <v>2.66</v>
+        <v>32</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3">
         <v>7</v>
       </c>
       <c r="AV3">
+        <v>11</v>
+      </c>
+      <c r="AW3">
+        <v>24</v>
+      </c>
+      <c r="AX3">
+        <v>15</v>
+      </c>
+      <c r="AY3">
         <v>10.5</v>
       </c>
-      <c r="AW3">
-        <v>2.62</v>
-      </c>
-      <c r="AX3">
-        <v>9.6</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3">
-        <v>2.66</v>
+        <v>30</v>
       </c>
       <c r="BB3">
-        <v>2.7</v>
+        <v>25</v>
       </c>
       <c r="BC3">
-        <v>2.66</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>2.66</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>2.72</v>
+        <v>60</v>
       </c>
       <c r="BF3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BG3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BH3">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI3">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
         <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BQ3">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BZ3">
         <v>29</v>
       </c>
       <c r="CA3">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1655,61 +1655,61 @@
         <v>150</v>
       </c>
       <c r="F4">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
         <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="T4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U4">
         <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y4">
         <v>16.5</v>
@@ -1724,85 +1724,85 @@
         <v>13.5</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE4">
         <v>34</v>
       </c>
       <c r="AF4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
         <v>16</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL4">
         <v>32</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN4">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AO4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP4">
         <v>17</v>
       </c>
       <c r="AQ4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
         <v>24</v>
@@ -1811,10 +1811,10 @@
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
@@ -1826,55 +1826,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ4">
         <v>6.2</v>
       </c>
       <c r="BR4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX4">
         <v>32</v>
       </c>
       <c r="BY4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1897,94 +1897,94 @@
         <v>151</v>
       </c>
       <c r="F5">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G5">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I5">
         <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X5">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z5">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AA5">
         <v>900</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>19.5</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ5">
         <v>23</v>
@@ -1999,70 +1999,70 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>60</v>
       </c>
       <c r="AP5">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="AS5">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="AW5">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="AX5">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AY5">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="BB5">
-        <v>5.1</v>
+        <v>17</v>
       </c>
       <c r="BC5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BD5">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BG5">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5">
         <v>11</v>
@@ -2080,7 +2080,7 @@
         <v>5.3</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
         <v>14.5</v>
@@ -2101,19 +2101,19 @@
         <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -2139,25 +2139,25 @@
         <v>152</v>
       </c>
       <c r="F6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2172,31 +2172,31 @@
         <v>1.97</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>8.800000000000001</v>
@@ -2205,31 +2205,31 @@
         <v>14</v>
       </c>
       <c r="AB6">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD6">
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>46</v>
+        <v>17.5</v>
       </c>
       <c r="AF6">
         <v>270</v>
       </c>
       <c r="AG6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AH6">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AI6">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AK6">
         <v>480</v>
@@ -2238,127 +2238,127 @@
         <v>460</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>790</v>
       </c>
       <c r="AN6">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AO6">
         <v>8.800000000000001</v>
       </c>
       <c r="AP6">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AR6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AT6">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AU6">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AY6">
         <v>25</v>
       </c>
       <c r="AZ6">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BA6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD6">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE6">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF6">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2381,22 +2381,22 @@
         <v>153</v>
       </c>
       <c r="F7">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="G7">
+        <v>3.1</v>
+      </c>
+      <c r="H7">
         <v>3.25</v>
       </c>
-      <c r="H7">
-        <v>3.05</v>
-      </c>
       <c r="I7">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J7">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="K7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="L7">
         <v>1.78</v>
@@ -2411,7 +2411,7 @@
         <v>1.81</v>
       </c>
       <c r="P7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2423,46 +2423,46 @@
         <v>8.4</v>
       </c>
       <c r="T7">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U7">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>22</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC7">
         <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE7">
         <v>160</v>
       </c>
       <c r="AF7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG7">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH7">
         <v>36</v>
@@ -2471,133 +2471,133 @@
         <v>500</v>
       </c>
       <c r="AJ7">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AK7">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AL7">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS7">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AT7">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU7">
         <v>6</v>
       </c>
       <c r="AV7">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AX7">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AY7">
         <v>13.5</v>
       </c>
       <c r="AZ7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB7">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BC7">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BD7">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF7">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BI7">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BJ7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL7">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="BM7">
         <v>6.4</v>
       </c>
       <c r="BN7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP7">
         <v>38</v>
       </c>
       <c r="BQ7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BS7">
         <v>6</v>
       </c>
       <c r="BT7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY7">
         <v>6</v>
       </c>
       <c r="BZ7">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="CA7">
         <v>6</v>
@@ -2623,25 +2623,25 @@
         <v>154</v>
       </c>
       <c r="F8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G8">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I8">
         <v>15.5</v>
       </c>
       <c r="J8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2653,58 +2653,58 @@
         <v>1.09</v>
       </c>
       <c r="P8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T8">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U8">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W8">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="X8">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y8">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="Z8">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AA8">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="AB8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AC8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD8">
         <v>55</v>
       </c>
       <c r="AE8">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AF8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
         <v>26</v>
@@ -2713,82 +2713,82 @@
         <v>240</v>
       </c>
       <c r="AJ8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK8">
         <v>14</v>
       </c>
       <c r="AL8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM8">
         <v>420</v>
       </c>
       <c r="AN8">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="AO8">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP8">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AQ8">
+        <v>10</v>
+      </c>
+      <c r="AR8">
+        <v>10</v>
+      </c>
+      <c r="AS8">
+        <v>10</v>
+      </c>
+      <c r="AT8">
+        <v>15.5</v>
+      </c>
+      <c r="AU8">
+        <v>15</v>
+      </c>
+      <c r="AV8">
+        <v>23</v>
+      </c>
+      <c r="AW8">
+        <v>10</v>
+      </c>
+      <c r="AX8">
+        <v>10.5</v>
+      </c>
+      <c r="AY8">
         <v>11</v>
       </c>
-      <c r="AR8">
-        <v>12</v>
-      </c>
-      <c r="AS8">
+      <c r="AZ8">
+        <v>21</v>
+      </c>
+      <c r="BA8">
         <v>10.5</v>
       </c>
-      <c r="AT8">
-        <v>16.5</v>
-      </c>
-      <c r="AU8">
-        <v>15.5</v>
-      </c>
-      <c r="AV8">
-        <v>21</v>
-      </c>
-      <c r="AW8">
-        <v>10.5</v>
-      </c>
-      <c r="AX8">
-        <v>11</v>
-      </c>
-      <c r="AY8">
-        <v>11.5</v>
-      </c>
-      <c r="AZ8">
-        <v>19.5</v>
-      </c>
-      <c r="BA8">
-        <v>11</v>
-      </c>
       <c r="BB8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC8">
         <v>11.5</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BE8">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="BF8">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BG8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH8">
         <v>6.6</v>
       </c>
       <c r="BI8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2800,7 +2800,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8">
         <v>4.6</v>
@@ -2809,40 +2809,40 @@
         <v>3.95</v>
       </c>
       <c r="BP8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BQ8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR8">
         <v>17</v>
       </c>
       <c r="BS8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT8">
         <v>16.5</v>
       </c>
       <c r="BU8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV8">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY8">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8">
         <v>6.6</v>
       </c>
       <c r="CA8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB8" t="s">
         <v>187</v>
@@ -2874,13 +2874,13 @@
         <v>3.35</v>
       </c>
       <c r="I9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9">
         <v>1.42</v>
@@ -2889,7 +2889,7 @@
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O9">
         <v>1.33</v>
@@ -2901,19 +2901,19 @@
         <v>2</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
         <v>3.55</v>
       </c>
       <c r="T9">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U9">
         <v>2.1</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W9">
         <v>1.71</v>
@@ -2922,58 +2922,58 @@
         <v>17</v>
       </c>
       <c r="Y9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA9">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH9">
         <v>22</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ9">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AK9">
         <v>32</v>
       </c>
       <c r="AL9">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM9">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO9">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AP9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ9">
         <v>11</v>
@@ -2982,109 +2982,109 @@
         <v>20</v>
       </c>
       <c r="AS9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9">
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AX9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA9">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB9">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="BC9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE9">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BH9">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>187</v>
@@ -3110,19 +3110,19 @@
         <v>3.4</v>
       </c>
       <c r="G10">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="H10">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="I10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
         <v>1.44</v>
@@ -3131,97 +3131,97 @@
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P10">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T10">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
         <v>1.72</v>
       </c>
       <c r="W10">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X10">
         <v>14</v>
       </c>
       <c r="Y10">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA10">
         <v>36</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG10">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH10">
         <v>22</v>
       </c>
       <c r="AI10">
+        <v>48</v>
+      </c>
+      <c r="AJ10">
+        <v>80</v>
+      </c>
+      <c r="AK10">
         <v>50</v>
       </c>
-      <c r="AJ10">
-        <v>90</v>
-      </c>
-      <c r="AK10">
-        <v>60</v>
-      </c>
       <c r="AL10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS10">
         <v>12</v>
@@ -3230,13 +3230,13 @@
         <v>10.5</v>
       </c>
       <c r="AU10">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW10">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AX10">
         <v>21</v>
@@ -3245,34 +3245,34 @@
         <v>13</v>
       </c>
       <c r="AZ10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA10">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="BB10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD10">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE10">
+        <v>6.8</v>
+      </c>
+      <c r="BF10">
         <v>6.4</v>
       </c>
-      <c r="BF10">
-        <v>38</v>
-      </c>
       <c r="BG10">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH10">
         <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10">
         <v>11.5</v>
@@ -3287,31 +3287,31 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO10">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV10">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
@@ -3349,226 +3349,226 @@
         <v>157</v>
       </c>
       <c r="F11">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="G11">
-        <v>23</v>
+        <v>4.2</v>
       </c>
       <c r="H11">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="I11">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="J11">
         <v>3.05</v>
       </c>
       <c r="K11">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="Q11">
-        <v>1.31</v>
+        <v>2.06</v>
       </c>
       <c r="R11">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V11">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y11">
-        <v>95</v>
+        <v>10.5</v>
       </c>
       <c r="Z11">
-        <v>120</v>
+        <v>16.5</v>
       </c>
       <c r="AA11">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AB11">
-        <v>130</v>
+        <v>14.5</v>
       </c>
       <c r="AC11">
-        <v>95</v>
+        <v>8.4</v>
       </c>
       <c r="AD11">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="AE11">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="AF11">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AG11">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="AH11">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="AI11">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AJ11">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO11">
-        <v>600</v>
+        <v>24</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF11">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="BG11">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
         <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ11">
         <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS11">
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW11">
         <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY11">
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB11" t="s">
         <v>187</v>
@@ -3591,22 +3591,22 @@
         <v>158</v>
       </c>
       <c r="F12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H12">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="I12">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="J12">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K12">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L12">
         <v>1.27</v>
@@ -3615,52 +3615,52 @@
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S12">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T12">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>32</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z12">
         <v>9.6</v>
       </c>
       <c r="AA12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AB12">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AC12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD12">
         <v>10.5</v>
@@ -3669,40 +3669,40 @@
         <v>13</v>
       </c>
       <c r="AF12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI12">
         <v>30</v>
       </c>
       <c r="AJ12">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AK12">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AL12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM12">
         <v>100</v>
       </c>
       <c r="AN12">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AO12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AP12">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR12">
         <v>9.199999999999999</v>
@@ -3711,13 +3711,13 @@
         <v>11</v>
       </c>
       <c r="AT12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AU12">
         <v>12</v>
       </c>
       <c r="AV12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12">
         <v>12.5</v>
@@ -3738,25 +3738,25 @@
         <v>140</v>
       </c>
       <c r="BC12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BD12">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BE12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF12">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BG12">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BH12">
         <v>4.7</v>
       </c>
       <c r="BI12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
@@ -3768,49 +3768,49 @@
         <v>130</v>
       </c>
       <c r="BM12">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BN12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BP12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BQ12">
+        <v>11.5</v>
+      </c>
+      <c r="BR12">
+        <v>75</v>
+      </c>
+      <c r="BS12">
+        <v>11</v>
+      </c>
+      <c r="BT12">
+        <v>3.95</v>
+      </c>
+      <c r="BU12">
+        <v>3.7</v>
+      </c>
+      <c r="BV12">
+        <v>7.6</v>
+      </c>
+      <c r="BW12">
+        <v>6.8</v>
+      </c>
+      <c r="BX12">
+        <v>23</v>
+      </c>
+      <c r="BY12">
         <v>17</v>
       </c>
-      <c r="BR12">
-        <v>65</v>
-      </c>
-      <c r="BS12">
-        <v>17</v>
-      </c>
-      <c r="BT12">
-        <v>4</v>
-      </c>
-      <c r="BU12">
-        <v>3.6</v>
-      </c>
-      <c r="BV12">
-        <v>7.8</v>
-      </c>
-      <c r="BW12">
-        <v>7</v>
-      </c>
-      <c r="BX12">
-        <v>21</v>
-      </c>
-      <c r="BY12">
-        <v>10</v>
-      </c>
       <c r="BZ12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA12">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="s">
         <v>187</v>
@@ -3833,10 +3833,10 @@
         <v>159</v>
       </c>
       <c r="F13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H13">
         <v>2.2</v>
@@ -3851,7 +3851,7 @@
         <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.05</v>
@@ -3860,16 +3860,16 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q13">
         <v>1.72</v>
       </c>
       <c r="R13">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S13">
         <v>2.8</v>
@@ -3881,10 +3881,10 @@
         <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X13">
         <v>19</v>
@@ -3908,16 +3908,16 @@
         <v>11</v>
       </c>
       <c r="AE13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG13">
         <v>14.5</v>
       </c>
       <c r="AH13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI13">
         <v>29</v>
@@ -3935,13 +3935,13 @@
         <v>65</v>
       </c>
       <c r="AN13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ13">
         <v>11.5</v>
@@ -3965,7 +3965,7 @@
         <v>19.5</v>
       </c>
       <c r="AX13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY13">
         <v>13.5</v>
@@ -3989,28 +3989,28 @@
         <v>55</v>
       </c>
       <c r="BF13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG13">
         <v>12</v>
       </c>
       <c r="BH13">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI13">
         <v>3.6</v>
       </c>
       <c r="BJ13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL13">
         <v>110</v>
       </c>
       <c r="BM13">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BN13">
         <v>7</v>
@@ -4019,16 +4019,16 @@
         <v>6.2</v>
       </c>
       <c r="BP13">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BQ13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT13">
         <v>5.2</v>
@@ -4037,22 +4037,22 @@
         <v>4.8</v>
       </c>
       <c r="BV13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BW13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX13">
         <v>25</v>
       </c>
       <c r="BY13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ13">
+        <v>19</v>
+      </c>
+      <c r="CA13">
         <v>8.6</v>
-      </c>
-      <c r="BZ13">
-        <v>18.5</v>
-      </c>
-      <c r="CA13">
-        <v>9.6</v>
       </c>
       <c r="CB13" t="s">
         <v>187</v>
@@ -4087,10 +4087,10 @@
         <v>21</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L14">
         <v>1.18</v>
@@ -4099,25 +4099,25 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P14">
         <v>3.85</v>
       </c>
       <c r="Q14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R14">
         <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T14">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U14">
         <v>1.87</v>
@@ -4129,13 +4129,13 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="Y14">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Z14">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AA14">
         <v>1000</v>
@@ -4144,22 +4144,22 @@
         <v>17.5</v>
       </c>
       <c r="AC14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AD14">
         <v>70</v>
       </c>
       <c r="AE14">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AF14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH14">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI14">
         <v>190</v>
@@ -4171,10 +4171,10 @@
         <v>15</v>
       </c>
       <c r="AL14">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM14">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN14">
         <v>2.78</v>
@@ -4183,10 +4183,10 @@
         <v>280</v>
       </c>
       <c r="AP14">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR14">
         <v>8.4</v>
@@ -4201,10 +4201,10 @@
         <v>18.5</v>
       </c>
       <c r="AV14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4213,37 +4213,37 @@
         <v>11.5</v>
       </c>
       <c r="AZ14">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BA14">
         <v>8.4</v>
       </c>
       <c r="BB14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC14">
         <v>11.5</v>
       </c>
       <c r="BD14">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BE14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="BG14">
         <v>10.5</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK14">
         <v>1.01</v>
@@ -4255,25 +4255,25 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS14">
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BU14">
         <v>1.01</v>
@@ -4291,10 +4291,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB14" t="s">
         <v>187</v>
@@ -4320,13 +4320,13 @@
         <v>2.8</v>
       </c>
       <c r="G15">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I15">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J15">
         <v>3.8</v>
@@ -4335,7 +4335,7 @@
         <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M15">
         <v>1.05</v>
@@ -4344,7 +4344,7 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
         <v>2.4</v>
@@ -4356,10 +4356,10 @@
         <v>1.55</v>
       </c>
       <c r="S15">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T15">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="U15">
         <v>2.5</v>
@@ -4380,10 +4380,10 @@
         <v>19.5</v>
       </c>
       <c r="AA15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
@@ -4398,7 +4398,7 @@
         <v>24</v>
       </c>
       <c r="AG15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH15">
         <v>16</v>
@@ -4410,7 +4410,7 @@
         <v>48</v>
       </c>
       <c r="AK15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL15">
         <v>36</v>
@@ -4419,19 +4419,19 @@
         <v>200</v>
       </c>
       <c r="AN15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO15">
         <v>15</v>
       </c>
       <c r="AP15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS15">
         <v>16</v>
@@ -4440,16 +4440,16 @@
         <v>13.5</v>
       </c>
       <c r="AU15">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV15">
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY15">
         <v>11</v>
@@ -4473,10 +4473,10 @@
         <v>7.6</v>
       </c>
       <c r="BF15">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH15">
         <v>4.3</v>
@@ -4485,34 +4485,34 @@
         <v>3.25</v>
       </c>
       <c r="BJ15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN15">
         <v>6.8</v>
       </c>
       <c r="BO15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP15">
         <v>22</v>
       </c>
       <c r="BQ15">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS15">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT15">
         <v>6</v>
@@ -4524,13 +4524,13 @@
         <v>17.5</v>
       </c>
       <c r="BW15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX15">
         <v>26</v>
       </c>
       <c r="BY15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4559,19 +4559,19 @@
         <v>162</v>
       </c>
       <c r="F16">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G16">
         <v>3.05</v>
       </c>
       <c r="H16">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I16">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J16">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K16">
         <v>4.3</v>
@@ -4580,7 +4580,7 @@
         <v>1.28</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
         <v>5.5</v>
@@ -4589,7 +4589,7 @@
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q16">
         <v>1.58</v>
@@ -4607,7 +4607,7 @@
         <v>2.6</v>
       </c>
       <c r="V16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W16">
         <v>1.48</v>
@@ -4619,7 +4619,7 @@
         <v>19</v>
       </c>
       <c r="Z16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA16">
         <v>40</v>
@@ -4634,7 +4634,7 @@
         <v>15</v>
       </c>
       <c r="AE16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF16">
         <v>29</v>
@@ -4664,28 +4664,28 @@
         <v>21</v>
       </c>
       <c r="AO16">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AP16">
         <v>21</v>
       </c>
       <c r="AQ16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR16">
         <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU16">
         <v>8.6</v>
       </c>
       <c r="AV16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW16">
         <v>19</v>
@@ -4700,85 +4700,85 @@
         <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB16">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BC16">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE16">
         <v>12.5</v>
       </c>
       <c r="BF16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG16">
         <v>10.5</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="CB16" t="s">
         <v>187</v>
@@ -4801,7 +4801,7 @@
         <v>163</v>
       </c>
       <c r="F17">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -4810,7 +4810,7 @@
         <v>1.74</v>
       </c>
       <c r="I17">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="J17">
         <v>4.1</v>
@@ -4834,22 +4834,22 @@
         <v>2.42</v>
       </c>
       <c r="Q17">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R17">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S17">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V17">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="W17">
         <v>1.25</v>
@@ -4879,13 +4879,13 @@
         <v>17.5</v>
       </c>
       <c r="AF17">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AG17">
         <v>19.5</v>
       </c>
       <c r="AH17">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI17">
         <v>29</v>
@@ -4903,7 +4903,7 @@
         <v>500</v>
       </c>
       <c r="AN17">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AO17">
         <v>8.4</v>
@@ -4933,28 +4933,28 @@
         <v>14.5</v>
       </c>
       <c r="AX17">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY17">
         <v>16</v>
       </c>
       <c r="AZ17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA17">
         <v>13</v>
       </c>
       <c r="BB17">
+        <v>9.6</v>
+      </c>
+      <c r="BC17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE17">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC17">
-        <v>8.6</v>
-      </c>
-      <c r="BD17">
-        <v>8.6</v>
-      </c>
-      <c r="BE17">
-        <v>9</v>
       </c>
       <c r="BF17">
         <v>8.4</v>
@@ -4990,10 +4990,10 @@
         <v>36</v>
       </c>
       <c r="BQ17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
         <v>9.6</v>
@@ -5014,13 +5014,13 @@
         <v>22</v>
       </c>
       <c r="BY17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17">
         <v>16</v>
       </c>
       <c r="CA17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB17" t="s">
         <v>187</v>
@@ -5043,13 +5043,13 @@
         <v>164</v>
       </c>
       <c r="F18">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H18">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I18">
         <v>2.54</v>
@@ -5058,79 +5058,79 @@
         <v>3.8</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M18">
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O18">
         <v>1.24</v>
       </c>
       <c r="P18">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S18">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T18">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U18">
         <v>2.4</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X18">
+        <v>21</v>
+      </c>
+      <c r="Y18">
+        <v>14</v>
+      </c>
+      <c r="Z18">
         <v>23</v>
       </c>
-      <c r="Y18">
-        <v>16</v>
-      </c>
-      <c r="Z18">
-        <v>21</v>
-      </c>
       <c r="AA18">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AB18">
         <v>15</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
         <v>14.5</v>
       </c>
       <c r="AE18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AF18">
         <v>27</v>
       </c>
       <c r="AG18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH18">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI18">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AJ18">
         <v>55</v>
@@ -5151,16 +5151,16 @@
         <v>16.5</v>
       </c>
       <c r="AP18">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AQ18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR18">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS18">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT18">
         <v>12.5</v>
@@ -5172,22 +5172,22 @@
         <v>10</v>
       </c>
       <c r="AW18">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AX18">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY18">
         <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA18">
         <v>5.5</v>
       </c>
       <c r="BB18">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BC18">
         <v>14.5</v>
@@ -5196,67 +5196,67 @@
         <v>17.5</v>
       </c>
       <c r="BE18">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BF18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG18">
         <v>13.5</v>
       </c>
       <c r="BH18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI18">
         <v>3.1</v>
       </c>
       <c r="BJ18">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="BL18">
         <v>110</v>
       </c>
       <c r="BM18">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BN18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP18">
         <v>25</v>
       </c>
       <c r="BQ18">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BR18">
         <v>36</v>
       </c>
       <c r="BS18">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BT18">
         <v>6.8</v>
       </c>
       <c r="BU18">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BV18">
         <v>21</v>
       </c>
       <c r="BW18">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BX18">
         <v>32</v>
       </c>
       <c r="BY18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5285,19 +5285,19 @@
         <v>165</v>
       </c>
       <c r="F19">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G19">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H19">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I19">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J19">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -5309,10 +5309,10 @@
         <v>1.08</v>
       </c>
       <c r="N19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P19">
         <v>1.87</v>
@@ -5327,16 +5327,16 @@
         <v>3.9</v>
       </c>
       <c r="T19">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U19">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W19">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X19">
         <v>13</v>
@@ -5345,13 +5345,13 @@
         <v>18.5</v>
       </c>
       <c r="Z19">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA19">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC19">
         <v>8.6</v>
@@ -5366,19 +5366,19 @@
         <v>8.6</v>
       </c>
       <c r="AG19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19">
         <v>110</v>
       </c>
       <c r="AJ19">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK19">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL19">
         <v>44</v>
@@ -5387,22 +5387,22 @@
         <v>160</v>
       </c>
       <c r="AN19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO19">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP19">
         <v>12</v>
       </c>
       <c r="AQ19">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR19">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AS19">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="AT19">
         <v>7.2</v>
@@ -5411,46 +5411,46 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AX19">
         <v>8.4</v>
       </c>
       <c r="AY19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA19">
         <v>100</v>
       </c>
       <c r="BB19">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD19">
         <v>40</v>
       </c>
       <c r="BE19">
+        <v>140</v>
+      </c>
+      <c r="BF19">
+        <v>10</v>
+      </c>
+      <c r="BG19">
         <v>130</v>
-      </c>
-      <c r="BF19">
-        <v>10.5</v>
-      </c>
-      <c r="BG19">
-        <v>110</v>
       </c>
       <c r="BH19">
         <v>3.25</v>
       </c>
       <c r="BI19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19">
         <v>11</v>
@@ -5459,46 +5459,46 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BL19">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BM19">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="BN19">
         <v>4.1</v>
       </c>
       <c r="BO19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ19">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR19">
         <v>29</v>
       </c>
       <c r="BS19">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="BT19">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV19">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BW19">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BX19">
         <v>80</v>
       </c>
       <c r="BY19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BZ19">
         <v>23</v>
@@ -5530,130 +5530,130 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H20">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I20">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="J20">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
         <v>1.51</v>
       </c>
       <c r="M20">
+        <v>1.09</v>
+      </c>
+      <c r="N20">
+        <v>3.15</v>
+      </c>
+      <c r="O20">
+        <v>1.44</v>
+      </c>
+      <c r="P20">
+        <v>1.71</v>
+      </c>
+      <c r="Q20">
+        <v>2.32</v>
+      </c>
+      <c r="R20">
+        <v>1.26</v>
+      </c>
+      <c r="S20">
+        <v>4.6</v>
+      </c>
+      <c r="T20">
+        <v>2.44</v>
+      </c>
+      <c r="U20">
+        <v>1.61</v>
+      </c>
+      <c r="V20">
+        <v>2.92</v>
+      </c>
+      <c r="W20">
         <v>1.1</v>
       </c>
-      <c r="N20">
-        <v>3.1</v>
-      </c>
-      <c r="O20">
-        <v>1.45</v>
-      </c>
-      <c r="P20">
-        <v>1.7</v>
-      </c>
-      <c r="Q20">
-        <v>2.34</v>
-      </c>
-      <c r="R20">
-        <v>1.25</v>
-      </c>
-      <c r="S20">
-        <v>4.7</v>
-      </c>
-      <c r="T20">
-        <v>2.42</v>
-      </c>
-      <c r="U20">
-        <v>1.63</v>
-      </c>
-      <c r="V20">
-        <v>2.78</v>
-      </c>
-      <c r="W20">
-        <v>1.11</v>
-      </c>
       <c r="X20">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y20">
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AA20">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AB20">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC20">
         <v>10</v>
       </c>
       <c r="AD20">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AE20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF20">
         <v>100</v>
       </c>
       <c r="AG20">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AH20">
         <v>38</v>
       </c>
       <c r="AI20">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ20">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="AK20">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="AL20">
-        <v>230</v>
+        <v>340</v>
       </c>
       <c r="AM20">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="AN20">
-        <v>730</v>
+        <v>510</v>
       </c>
       <c r="AO20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ20">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR20">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT20">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW20">
         <v>18</v>
@@ -5662,91 +5662,91 @@
         <v>50</v>
       </c>
       <c r="AY20">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AZ20">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA20">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BB20">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="BC20">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="BD20">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="BE20">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="BF20">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BG20">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH20">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI20">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ20">
         <v>16.5</v>
       </c>
       <c r="BK20">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BN20">
         <v>15</v>
       </c>
       <c r="BO20">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BT20">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="BU20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BV20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW20">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="BX20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY20">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ20">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="CA20">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB20" t="s">
         <v>187</v>
@@ -5772,13 +5772,13 @@
         <v>4.9</v>
       </c>
       <c r="G21">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H21">
         <v>2</v>
       </c>
       <c r="I21">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J21">
         <v>3</v>
@@ -5787,7 +5787,7 @@
         <v>3.2</v>
       </c>
       <c r="L21">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M21">
         <v>1.15</v>
@@ -5796,13 +5796,13 @@
         <v>2.42</v>
       </c>
       <c r="O21">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="P21">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q21">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R21">
         <v>1.16</v>
@@ -5811,13 +5811,13 @@
         <v>6.4</v>
       </c>
       <c r="T21">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U21">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V21">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W21">
         <v>1.23</v>
@@ -5832,7 +5832,7 @@
         <v>11</v>
       </c>
       <c r="AA21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB21">
         <v>12</v>
@@ -5847,7 +5847,7 @@
         <v>34</v>
       </c>
       <c r="AF21">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG21">
         <v>25</v>
@@ -5856,7 +5856,7 @@
         <v>32</v>
       </c>
       <c r="AI21">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AJ21">
         <v>900</v>
@@ -5871,16 +5871,16 @@
         <v>500</v>
       </c>
       <c r="AN21">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AO21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP21">
         <v>6.6</v>
       </c>
       <c r="AQ21">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AR21">
         <v>9.199999999999999</v>
@@ -5889,106 +5889,106 @@
         <v>12</v>
       </c>
       <c r="AT21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU21">
         <v>6.6</v>
       </c>
       <c r="AV21">
+        <v>10</v>
+      </c>
+      <c r="AW21">
+        <v>15</v>
+      </c>
+      <c r="AX21">
+        <v>16.5</v>
+      </c>
+      <c r="AY21">
+        <v>19.5</v>
+      </c>
+      <c r="AZ21">
+        <v>15</v>
+      </c>
+      <c r="BA21">
         <v>10.5</v>
       </c>
-      <c r="AW21">
-        <v>14.5</v>
-      </c>
-      <c r="AX21">
-        <v>13</v>
-      </c>
-      <c r="AY21">
-        <v>20</v>
-      </c>
-      <c r="AZ21">
-        <v>14.5</v>
-      </c>
-      <c r="BA21">
-        <v>9</v>
-      </c>
       <c r="BB21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC21">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE21">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF21">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG21">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI21">
         <v>2.34</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU21">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="CB21" t="s">
         <v>187</v>
@@ -6014,88 +6014,88 @@
         <v>2.28</v>
       </c>
       <c r="G22">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I22">
         <v>3.25</v>
       </c>
       <c r="J22">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O22">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="Q22">
+        <v>1.61</v>
+      </c>
+      <c r="R22">
+        <v>1.58</v>
+      </c>
+      <c r="S22">
+        <v>2.54</v>
+      </c>
+      <c r="T22">
+        <v>1.55</v>
+      </c>
+      <c r="U22">
+        <v>2.52</v>
+      </c>
+      <c r="V22">
+        <v>1.47</v>
+      </c>
+      <c r="W22">
         <v>1.69</v>
       </c>
-      <c r="R22">
-        <v>1.5</v>
-      </c>
-      <c r="S22">
-        <v>2.76</v>
-      </c>
-      <c r="T22">
-        <v>1.62</v>
-      </c>
-      <c r="U22">
-        <v>2.4</v>
-      </c>
-      <c r="V22">
-        <v>1.44</v>
-      </c>
-      <c r="W22">
-        <v>1.71</v>
-      </c>
       <c r="X22">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Y22">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z22">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AA22">
         <v>220</v>
       </c>
       <c r="AB22">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC22">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE22">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="AF22">
-        <v>70</v>
+        <v>18.5</v>
       </c>
       <c r="AG22">
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI22">
         <v>300</v>
@@ -6107,49 +6107,49 @@
         <v>38</v>
       </c>
       <c r="AL22">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="AM22">
         <v>580</v>
       </c>
       <c r="AN22">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO22">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AP22">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AQ22">
+        <v>15</v>
+      </c>
+      <c r="AR22">
+        <v>20</v>
+      </c>
+      <c r="AS22">
+        <v>9.6</v>
+      </c>
+      <c r="AT22">
+        <v>12.5</v>
+      </c>
+      <c r="AU22">
+        <v>8.4</v>
+      </c>
+      <c r="AV22">
         <v>12</v>
-      </c>
-      <c r="AR22">
-        <v>18</v>
-      </c>
-      <c r="AS22">
-        <v>9</v>
-      </c>
-      <c r="AT22">
-        <v>11</v>
-      </c>
-      <c r="AU22">
-        <v>8</v>
-      </c>
-      <c r="AV22">
-        <v>10.5</v>
       </c>
       <c r="AW22">
         <v>13</v>
       </c>
       <c r="AX22">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AY22">
         <v>10</v>
       </c>
       <c r="AZ22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA22">
         <v>15</v>
@@ -6158,55 +6158,55 @@
         <v>12.5</v>
       </c>
       <c r="BC22">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD22">
         <v>12.5</v>
       </c>
       <c r="BE22">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF22">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="BH22">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI22">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BJ22">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN22">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO22">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP22">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT22">
         <v>6.8</v>
@@ -6215,16 +6215,16 @@
         <v>5.2</v>
       </c>
       <c r="BV22">
+        <v>22</v>
+      </c>
+      <c r="BW22">
+        <v>7.8</v>
+      </c>
+      <c r="BX22">
         <v>1000</v>
       </c>
-      <c r="BW22">
-        <v>1.01</v>
-      </c>
-      <c r="BX22">
-        <v>32</v>
-      </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6253,13 +6253,13 @@
         <v>169</v>
       </c>
       <c r="F23">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G23">
         <v>1.39</v>
       </c>
       <c r="H23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I23">
         <v>15</v>
@@ -6268,13 +6268,13 @@
         <v>4.9</v>
       </c>
       <c r="K23">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L23">
         <v>1.47</v>
       </c>
       <c r="M23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
         <v>3.2</v>
@@ -6283,22 +6283,22 @@
         <v>1.42</v>
       </c>
       <c r="P23">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q23">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R23">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T23">
         <v>2.74</v>
       </c>
       <c r="U23">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V23">
         <v>1.07</v>
@@ -6313,10 +6313,10 @@
         <v>28</v>
       </c>
       <c r="Z23">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AA23">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="AB23">
         <v>5.8</v>
@@ -6325,91 +6325,91 @@
         <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AE23">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="AF23">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH23">
         <v>55</v>
       </c>
       <c r="AI23">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AJ23">
         <v>10.5</v>
       </c>
       <c r="AK23">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL23">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AM23">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AN23">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO23">
         <v>950</v>
       </c>
       <c r="AP23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ23">
         <v>25</v>
       </c>
       <c r="AR23">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AS23">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV23">
         <v>46</v>
       </c>
       <c r="AW23">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AX23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ23">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BA23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BB23">
         <v>9.199999999999999</v>
       </c>
       <c r="BC23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD23">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BE23">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BF23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG23">
         <v>15</v>
@@ -6421,19 +6421,19 @@
         <v>2.88</v>
       </c>
       <c r="BJ23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BK23">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BN23">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BO23">
         <v>3.05</v>
@@ -6442,37 +6442,37 @@
         <v>9</v>
       </c>
       <c r="BQ23">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BR23">
         <v>38</v>
       </c>
       <c r="BS23">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT23">
         <v>16.5</v>
       </c>
       <c r="BU23">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CA23">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="CB23" t="s">
         <v>187</v>
@@ -6495,16 +6495,16 @@
         <v>170</v>
       </c>
       <c r="F24">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="G24">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="H24">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="I24">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -6528,91 +6528,91 @@
         <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
         <v>1.63</v>
       </c>
       <c r="S24">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T24">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U24">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V24">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="W24">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X24">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y24">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA24">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AB24">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AC24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD24">
         <v>13.5</v>
       </c>
       <c r="AE24">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AF24">
         <v>38</v>
       </c>
       <c r="AG24">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH24">
         <v>19</v>
       </c>
       <c r="AI24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK24">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL24">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM24">
         <v>70</v>
       </c>
       <c r="AN24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO24">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP24">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR24">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT24">
         <v>17</v>
@@ -6627,28 +6627,28 @@
         <v>15.5</v>
       </c>
       <c r="AX24">
+        <v>17.5</v>
+      </c>
+      <c r="AY24">
+        <v>14.5</v>
+      </c>
+      <c r="AZ24">
+        <v>13</v>
+      </c>
+      <c r="BA24">
+        <v>22</v>
+      </c>
+      <c r="BB24">
+        <v>24</v>
+      </c>
+      <c r="BC24">
+        <v>20</v>
+      </c>
+      <c r="BD24">
         <v>21</v>
       </c>
-      <c r="AY24">
-        <v>13.5</v>
-      </c>
-      <c r="AZ24">
-        <v>13.5</v>
-      </c>
-      <c r="BA24">
-        <v>19</v>
-      </c>
-      <c r="BB24">
-        <v>36</v>
-      </c>
-      <c r="BC24">
-        <v>25</v>
-      </c>
-      <c r="BD24">
-        <v>25</v>
-      </c>
       <c r="BE24">
-        <v>4.6</v>
+        <v>26</v>
       </c>
       <c r="BF24">
         <v>21</v>
@@ -6666,7 +6666,7 @@
         <v>10.5</v>
       </c>
       <c r="BK24">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="BL24">
         <v>90</v>
@@ -6696,7 +6696,7 @@
         <v>6.2</v>
       </c>
       <c r="BU24">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BV24">
         <v>16</v>
@@ -6737,28 +6737,28 @@
         <v>171</v>
       </c>
       <c r="F25">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G25">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="H25">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I25">
         <v>3.05</v>
       </c>
       <c r="J25">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K25">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L25">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25">
         <v>5.3</v>
@@ -6767,196 +6767,196 @@
         <v>1.16</v>
       </c>
       <c r="P25">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q25">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R25">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S25">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T25">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="U25">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.53</v>
       </c>
       <c r="X25">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Y25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z25">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AA25">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="AB25">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD25">
         <v>970</v>
       </c>
       <c r="AE25">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF25">
         <v>500</v>
       </c>
       <c r="AG25">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH25">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AI25">
+        <v>75</v>
+      </c>
+      <c r="AJ25">
+        <v>170</v>
+      </c>
+      <c r="AK25">
         <v>500</v>
-      </c>
-      <c r="AJ25">
-        <v>40</v>
-      </c>
-      <c r="AK25">
-        <v>26</v>
       </c>
       <c r="AL25">
         <v>75</v>
       </c>
       <c r="AM25">
-        <v>55</v>
+        <v>580</v>
       </c>
       <c r="AN25">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="AO25">
-        <v>14.5</v>
+        <v>600</v>
       </c>
       <c r="AP25">
-        <v>3.75</v>
+        <v>1.88</v>
       </c>
       <c r="AQ25">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="AR25">
-        <v>3.65</v>
+        <v>1.88</v>
       </c>
       <c r="AS25">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="AT25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AU25">
         <v>5.6</v>
       </c>
       <c r="AV25">
-        <v>4</v>
+        <v>1.87</v>
       </c>
       <c r="AW25">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="AX25">
-        <v>4.1</v>
+        <v>1.89</v>
       </c>
       <c r="AY25">
         <v>5.7</v>
       </c>
       <c r="AZ25">
-        <v>3.4</v>
+        <v>1.78</v>
       </c>
       <c r="BA25">
-        <v>4.1</v>
+        <v>1.83</v>
       </c>
       <c r="BB25">
-        <v>3.9</v>
+        <v>1.89</v>
       </c>
       <c r="BC25">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="BD25">
-        <v>3.85</v>
+        <v>1.83</v>
       </c>
       <c r="BE25">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BF25">
-        <v>3.35</v>
+        <v>1.86</v>
       </c>
       <c r="BG25">
-        <v>3.3</v>
+        <v>1.86</v>
       </c>
       <c r="BH25">
         <v>4.8</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ25">
         <v>8.800000000000001</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL25">
         <v>75</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BN25">
         <v>6.6</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP25">
         <v>18.5</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR25">
         <v>25</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT25">
         <v>6.6</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV25">
         <v>18.5</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX25">
         <v>25</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ25">
         <v>16</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB25" t="s">
         <v>187</v>
@@ -6979,64 +6979,64 @@
         <v>172</v>
       </c>
       <c r="F26">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G26">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I26">
         <v>6</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K26">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L26">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N26">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O26">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="P26">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Q26">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="R26">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S26">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T26">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="U26">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="V26">
         <v>1.2</v>
       </c>
       <c r="W26">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X26">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y26">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z26">
         <v>50</v>
@@ -7045,106 +7045,106 @@
         <v>900</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AC26">
         <v>8.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE26">
         <v>120</v>
       </c>
       <c r="AF26">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG26">
         <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI26">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="AJ26">
         <v>27</v>
       </c>
       <c r="AK26">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AL26">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM26">
         <v>580</v>
       </c>
       <c r="AN26">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO26">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP26">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR26">
-        <v>5.9</v>
+        <v>26</v>
       </c>
       <c r="AS26">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT26">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AU26">
         <v>6.8</v>
       </c>
       <c r="AV26">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW26">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX26">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY26">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
+        <v>22</v>
+      </c>
+      <c r="BA26">
+        <v>6.8</v>
+      </c>
+      <c r="BB26">
+        <v>20</v>
+      </c>
+      <c r="BC26">
+        <v>23</v>
+      </c>
+      <c r="BD26">
+        <v>25</v>
+      </c>
+      <c r="BE26">
+        <v>7</v>
+      </c>
+      <c r="BF26">
         <v>21</v>
       </c>
-      <c r="BA26">
-        <v>6</v>
-      </c>
-      <c r="BB26">
-        <v>19</v>
-      </c>
-      <c r="BC26">
-        <v>21</v>
-      </c>
-      <c r="BD26">
-        <v>6.4</v>
-      </c>
-      <c r="BE26">
-        <v>6.2</v>
-      </c>
-      <c r="BF26">
-        <v>17.5</v>
-      </c>
       <c r="BG26">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH26">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI26">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ26">
         <v>14</v>
@@ -7153,7 +7153,7 @@
         <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="BM26">
         <v>1.01</v>
@@ -7221,25 +7221,25 @@
         <v>173</v>
       </c>
       <c r="F27">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G27">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H27">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="I27">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="J27">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>5.4</v>
       </c>
       <c r="L27">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M27">
         <v>1.04</v>
@@ -7248,199 +7248,199 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P27">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q27">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R27">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S27">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T27">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V27">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y27">
+        <v>10</v>
+      </c>
+      <c r="Z27">
+        <v>9.4</v>
+      </c>
+      <c r="AA27">
+        <v>14</v>
+      </c>
+      <c r="AB27">
+        <v>80</v>
+      </c>
+      <c r="AC27">
+        <v>12</v>
+      </c>
+      <c r="AD27">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z27">
-        <v>9.6</v>
-      </c>
-      <c r="AA27">
-        <v>13.5</v>
-      </c>
-      <c r="AB27">
-        <v>34</v>
-      </c>
-      <c r="AC27">
-        <v>11.5</v>
-      </c>
-      <c r="AD27">
-        <v>12</v>
-      </c>
       <c r="AE27">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF27">
+        <v>110</v>
+      </c>
+      <c r="AG27">
+        <v>36</v>
+      </c>
+      <c r="AH27">
+        <v>26</v>
+      </c>
+      <c r="AI27">
+        <v>36</v>
+      </c>
+      <c r="AJ27">
+        <v>300</v>
+      </c>
+      <c r="AK27">
+        <v>170</v>
+      </c>
+      <c r="AL27">
+        <v>240</v>
+      </c>
+      <c r="AM27">
+        <v>120</v>
+      </c>
+      <c r="AN27">
         <v>160</v>
       </c>
-      <c r="AG27">
-        <v>32</v>
-      </c>
-      <c r="AH27">
-        <v>23</v>
-      </c>
-      <c r="AI27">
-        <v>38</v>
-      </c>
-      <c r="AJ27">
-        <v>270</v>
-      </c>
-      <c r="AK27">
-        <v>240</v>
-      </c>
-      <c r="AL27">
-        <v>390</v>
-      </c>
-      <c r="AM27">
-        <v>380</v>
-      </c>
-      <c r="AN27">
-        <v>140</v>
-      </c>
       <c r="AO27">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AP27">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ27">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR27">
         <v>8.4</v>
       </c>
       <c r="AS27">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT27">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AU27">
         <v>10</v>
       </c>
       <c r="AV27">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AW27">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX27">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AY27">
-        <v>22</v>
+        <v>24</v>
       </c>
 